--- a/Soubhanik/checkupp_product_backlog_final.xlsx
+++ b/Soubhanik/checkupp_product_backlog_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anodiam\2026\CheckUpp_Parent\CheckUpp\Soubhanik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="11_D94C620D5273205F6B5D70B55D9C46FE70986E68" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{277A931B-5C20-4135-8FCF-678BD972299A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -23,7 +23,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="296" uniqueCount="222">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="224">
   <si>
     <t>Epic #</t>
   </si>
@@ -275,9 +275,6 @@
 2. Uploaded document must be visible in wallet</t>
   </si>
   <si>
-    <t>Slide 12</t>
-  </si>
-  <si>
     <t>Discussion #10 – NATHAN</t>
   </si>
   <si>
@@ -320,9 +317,6 @@
     <t>1. 'Save as link' action must be available on the eScript screen
 2. Short link must be generated (checkupp.app/s/…)
 3. Link must be copyable</t>
-  </si>
-  <si>
-    <t>Slide 13</t>
   </si>
   <si>
     <t>Discussion #11 – NATHAN; per wireframe user story</t>
@@ -340,9 +334,6 @@
 4. Copyable short link must be shown below QR</t>
   </si>
   <si>
-    <t>Slides 13–14</t>
-  </si>
-  <si>
     <t>view the details of my e-Script before sharing</t>
   </si>
   <si>
@@ -364,9 +355,6 @@
   <si>
     <t>1. Health check list screen must be accessible from home
 2. All available checks must be displayed</t>
-  </si>
-  <si>
-    <t>Slide 16</t>
   </si>
   <si>
     <t>user who has completed a health check</t>
@@ -604,9 +592,6 @@
     <t>1. App must display the current week, trimester, and EDD.</t>
   </si>
   <si>
-    <t>Slide 11</t>
-  </si>
-  <si>
     <t>view recommended prenatal tests and doctor visits</t>
   </si>
   <si>
@@ -658,9 +643,6 @@
     <t>1. User must be able to select and save symptoms.</t>
   </si>
   <si>
-    <t>Slide 9, 11</t>
-  </si>
-  <si>
     <t>Post-menopausal user</t>
   </si>
   <si>
@@ -752,13 +734,37 @@
   </si>
   <si>
     <t>1. User must be able to attach documents to the custom health check.</t>
+  </si>
+  <si>
+    <t>Slide 5</t>
+  </si>
+  <si>
+    <t>Slide 1</t>
+  </si>
+  <si>
+    <t>Slide 2,3,4</t>
+  </si>
+  <si>
+    <t>Slide 8-11</t>
+  </si>
+  <si>
+    <t>Slide 14</t>
+  </si>
+  <si>
+    <t>Slide 15</t>
+  </si>
+  <si>
+    <t>Slides 15</t>
+  </si>
+  <si>
+    <t>Slide 24</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -797,8 +803,14 @@
       <sz val="10"/>
       <name val="Calibri"/>
     </font>
+    <font>
+      <sz val="8"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="18">
+  <fills count="19">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -886,6 +898,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFF00"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1007,7 +1025,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="73">
+  <cellXfs count="76">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1168,51 +1186,64 @@
     <xf numFmtId="0" fontId="5" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1506,41 +1537,41 @@
     <col min="5" max="5" width="65" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="41" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="49.77734375" style="3" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="10.77734375" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" style="2" customWidth="1"/>
     <col min="9" max="9" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
     <col min="10" max="12" width="8.88671875" style="5" customWidth="1"/>
     <col min="13" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="72" t="s">
+      <c r="A1" s="70" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="60" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="59" t="s">
+      <c r="C1" s="60" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="59" t="s">
+      <c r="D1" s="60" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="70"/>
-      <c r="F1" s="71"/>
-      <c r="G1" s="59" t="s">
+      <c r="E1" s="71"/>
+      <c r="F1" s="72"/>
+      <c r="G1" s="73" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="59" t="s">
+      <c r="H1" s="60" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="59" t="s">
+      <c r="I1" s="60" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="56"/>
-      <c r="B2" s="60"/>
-      <c r="C2" s="60"/>
+      <c r="A2" s="55"/>
+      <c r="B2" s="61"/>
+      <c r="C2" s="61"/>
       <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1550,9 +1581,9 @@
       <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="60"/>
-      <c r="H2" s="60"/>
-      <c r="I2" s="60"/>
+      <c r="G2" s="74"/>
+      <c r="H2" s="61"/>
+      <c r="I2" s="61"/>
     </row>
     <row r="3" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A3" s="36">
@@ -1577,17 +1608,17 @@
         <v>14</v>
       </c>
       <c r="H3" s="9" t="s">
-        <v>15</v>
+        <v>158</v>
       </c>
       <c r="I3" s="10" t="s">
         <v>16</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="62">
+      <c r="A4" s="69">
         <v>3</v>
       </c>
-      <c r="B4" s="62" t="s">
+      <c r="B4" s="69" t="s">
         <v>17</v>
       </c>
       <c r="C4" s="11">
@@ -1606,15 +1637,15 @@
         <v>20</v>
       </c>
       <c r="H4" s="11" t="s">
-        <v>21</v>
+        <v>217</v>
       </c>
       <c r="I4" s="12" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A5" s="55"/>
-      <c r="B5" s="55"/>
+      <c r="A5" s="57"/>
+      <c r="B5" s="57"/>
       <c r="C5" s="11">
         <v>3.2</v>
       </c>
@@ -1630,14 +1661,16 @@
       <c r="G5" s="42" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="11"/>
+      <c r="H5" s="11" t="s">
+        <v>218</v>
+      </c>
       <c r="I5" s="12" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="6" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="56"/>
-      <c r="B6" s="56"/>
+      <c r="A6" s="55"/>
+      <c r="B6" s="55"/>
       <c r="C6" s="11">
         <v>3.3</v>
       </c>
@@ -1654,17 +1687,17 @@
         <v>28</v>
       </c>
       <c r="H6" s="11" t="s">
-        <v>21</v>
+        <v>217</v>
       </c>
       <c r="I6" s="12" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="7" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="57">
+      <c r="A7" s="56">
         <v>4</v>
       </c>
-      <c r="B7" s="57" t="s">
+      <c r="B7" s="56" t="s">
         <v>29</v>
       </c>
       <c r="C7" s="13">
@@ -1683,15 +1716,15 @@
         <v>33</v>
       </c>
       <c r="H7" s="13" t="s">
-        <v>34</v>
+        <v>216</v>
       </c>
       <c r="I7" s="14" t="s">
         <v>35</v>
       </c>
     </row>
     <row r="8" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="55"/>
-      <c r="B8" s="55"/>
+      <c r="A8" s="57"/>
+      <c r="B8" s="57"/>
       <c r="C8" s="13">
         <v>4.2</v>
       </c>
@@ -1708,13 +1741,13 @@
         <v>38</v>
       </c>
       <c r="H8" s="13" t="s">
-        <v>34</v>
+        <v>216</v>
       </c>
       <c r="I8" s="14"/>
     </row>
     <row r="9" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="55"/>
-      <c r="B9" s="55"/>
+      <c r="A9" s="57"/>
+      <c r="B9" s="57"/>
       <c r="C9" s="13">
         <v>4.3</v>
       </c>
@@ -1731,15 +1764,15 @@
         <v>42</v>
       </c>
       <c r="H9" s="13" t="s">
-        <v>43</v>
+        <v>21</v>
       </c>
       <c r="I9" s="14" t="s">
         <v>44</v>
       </c>
     </row>
     <row r="10" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="55"/>
-      <c r="B10" s="55"/>
+      <c r="A10" s="57"/>
+      <c r="B10" s="57"/>
       <c r="C10" s="13">
         <v>4.4000000000000004</v>
       </c>
@@ -1756,16 +1789,16 @@
         <v>48</v>
       </c>
       <c r="H10" s="13" t="s">
-        <v>43</v>
+        <v>34</v>
       </c>
       <c r="I10" s="14" t="s">
         <v>49</v>
       </c>
     </row>
     <row r="11" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="55"/>
-      <c r="B11" s="55"/>
-      <c r="C11" s="13">
+      <c r="A11" s="57"/>
+      <c r="B11" s="57"/>
+      <c r="C11" s="75">
         <v>4.5</v>
       </c>
       <c r="D11" s="14" t="s">
@@ -1786,9 +1819,9 @@
       <c r="I11" s="14"/>
     </row>
     <row r="12" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="56"/>
-      <c r="B12" s="56"/>
-      <c r="C12" s="13">
+      <c r="A12" s="55"/>
+      <c r="B12" s="55"/>
+      <c r="C12" s="75">
         <v>4.5999999999999996</v>
       </c>
       <c r="D12" s="14" t="s">
@@ -1809,10 +1842,10 @@
       <c r="I12" s="14"/>
     </row>
     <row r="13" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="61">
+      <c r="A13" s="59">
         <v>5</v>
       </c>
-      <c r="B13" s="61" t="s">
+      <c r="B13" s="59" t="s">
         <v>58</v>
       </c>
       <c r="C13" s="15">
@@ -1838,8 +1871,8 @@
       </c>
     </row>
     <row r="14" spans="1:9" s="8" customFormat="1" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="55"/>
-      <c r="B14" s="55"/>
+      <c r="A14" s="57"/>
+      <c r="B14" s="57"/>
       <c r="C14" s="15">
         <v>5.2</v>
       </c>
@@ -1856,15 +1889,15 @@
         <v>66</v>
       </c>
       <c r="H14" s="17" t="s">
-        <v>62</v>
+        <v>219</v>
       </c>
       <c r="I14" s="16" t="s">
         <v>67</v>
       </c>
     </row>
     <row r="15" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="56"/>
-      <c r="B15" s="56"/>
+      <c r="A15" s="55"/>
+      <c r="B15" s="55"/>
       <c r="C15" s="15">
         <v>5.3</v>
       </c>
@@ -1881,15 +1914,15 @@
         <v>70</v>
       </c>
       <c r="H15" s="17" t="s">
-        <v>62</v>
+        <v>219</v>
       </c>
       <c r="I15" s="16"/>
     </row>
     <row r="16" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="66">
+      <c r="A16" s="62">
         <v>6</v>
       </c>
-      <c r="B16" s="66" t="s">
+      <c r="B16" s="62" t="s">
         <v>71</v>
       </c>
       <c r="C16" s="18">
@@ -1908,15 +1941,15 @@
         <v>74</v>
       </c>
       <c r="H16" s="20" t="s">
+        <v>220</v>
+      </c>
+      <c r="I16" s="19" t="s">
         <v>75</v>
       </c>
-      <c r="I16" s="19" t="s">
-        <v>76</v>
-      </c>
     </row>
     <row r="17" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="55"/>
-      <c r="B17" s="55"/>
+      <c r="A17" s="57"/>
+      <c r="B17" s="57"/>
       <c r="C17" s="18">
         <v>6.2</v>
       </c>
@@ -1924,24 +1957,24 @@
         <v>30</v>
       </c>
       <c r="E17" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="F17" s="19" t="s">
         <v>77</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="G17" s="45" t="s">
         <v>78</v>
       </c>
-      <c r="G17" s="45" t="s">
+      <c r="H17" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="I17" s="19" t="s">
         <v>79</v>
       </c>
-      <c r="H17" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="I17" s="19" t="s">
-        <v>80</v>
-      </c>
     </row>
     <row r="18" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="56"/>
-      <c r="B18" s="56"/>
+      <c r="A18" s="55"/>
+      <c r="B18" s="55"/>
       <c r="C18" s="18">
         <v>6.3</v>
       </c>
@@ -1949,102 +1982,102 @@
         <v>30</v>
       </c>
       <c r="E18" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="F18" s="19" t="s">
         <v>81</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="G18" s="45" t="s">
         <v>82</v>
       </c>
-      <c r="G18" s="45" t="s">
+      <c r="H18" s="18" t="s">
+        <v>220</v>
+      </c>
+      <c r="I18" s="19"/>
+    </row>
+    <row r="19" spans="1:9" s="8" customFormat="1" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="58">
+        <v>7</v>
+      </c>
+      <c r="B19" s="58" t="s">
         <v>83</v>
-      </c>
-      <c r="H18" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="I18" s="19"/>
-    </row>
-    <row r="19" spans="1:9" s="8" customFormat="1" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="64">
-        <v>7</v>
-      </c>
-      <c r="B19" s="64" t="s">
-        <v>84</v>
       </c>
       <c r="C19" s="21">
         <v>7.1</v>
       </c>
       <c r="D19" s="22" t="s">
+        <v>84</v>
+      </c>
+      <c r="E19" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="E19" s="22" t="s">
+      <c r="F19" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="F19" s="22" t="s">
+      <c r="G19" s="46" t="s">
         <v>87</v>
       </c>
-      <c r="G19" s="46" t="s">
+      <c r="H19" s="23" t="s">
+        <v>221</v>
+      </c>
+      <c r="I19" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="H19" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="I19" s="22" t="s">
-        <v>90</v>
-      </c>
     </row>
     <row r="20" spans="1:9" s="8" customFormat="1" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="55"/>
-      <c r="B20" s="55"/>
+      <c r="A20" s="57"/>
+      <c r="B20" s="57"/>
       <c r="C20" s="21">
         <v>7.2</v>
       </c>
       <c r="D20" s="22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E20" s="22" t="s">
+        <v>89</v>
+      </c>
+      <c r="F20" s="22" t="s">
+        <v>90</v>
+      </c>
+      <c r="G20" s="46" t="s">
         <v>91</v>
       </c>
-      <c r="F20" s="22" t="s">
-        <v>92</v>
-      </c>
-      <c r="G20" s="46" t="s">
-        <v>93</v>
-      </c>
       <c r="H20" s="21" t="s">
-        <v>94</v>
+        <v>222</v>
       </c>
       <c r="I20" s="22" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="56"/>
-      <c r="B21" s="56"/>
+      <c r="A21" s="55"/>
+      <c r="B21" s="55"/>
       <c r="C21" s="21">
         <v>7.3</v>
       </c>
       <c r="D21" s="22" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="E21" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="F21" s="22" t="s">
+        <v>93</v>
+      </c>
+      <c r="G21" s="46" t="s">
+        <v>94</v>
+      </c>
+      <c r="H21" s="21" t="s">
+        <v>221</v>
+      </c>
+      <c r="I21" s="22"/>
+    </row>
+    <row r="22" spans="1:9" s="8" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="68">
+        <v>9</v>
+      </c>
+      <c r="B22" s="68" t="s">
         <v>95</v>
-      </c>
-      <c r="F21" s="22" t="s">
-        <v>96</v>
-      </c>
-      <c r="G21" s="46" t="s">
-        <v>97</v>
-      </c>
-      <c r="H21" s="21" t="s">
-        <v>89</v>
-      </c>
-      <c r="I21" s="22"/>
-    </row>
-    <row r="22" spans="1:9" s="8" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="54">
-        <v>9</v>
-      </c>
-      <c r="B22" s="54" t="s">
-        <v>98</v>
       </c>
       <c r="C22" s="24">
         <v>9.1</v>
@@ -2053,70 +2086,64 @@
         <v>30</v>
       </c>
       <c r="E22" s="25" t="s">
-        <v>99</v>
+        <v>96</v>
       </c>
       <c r="F22" s="25" t="s">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="G22" s="47" t="s">
-        <v>101</v>
-      </c>
-      <c r="H22" s="24" t="s">
-        <v>102</v>
-      </c>
+        <v>98</v>
+      </c>
+      <c r="H22" s="24"/>
       <c r="I22" s="25"/>
     </row>
     <row r="23" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="55"/>
-      <c r="B23" s="55"/>
+      <c r="A23" s="57"/>
+      <c r="B23" s="57"/>
       <c r="C23" s="24">
         <v>9.1999999999999993</v>
       </c>
       <c r="D23" s="25" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="E23" s="25" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="F23" s="25" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
       <c r="G23" s="47" t="s">
-        <v>106</v>
-      </c>
-      <c r="H23" s="24" t="s">
         <v>102</v>
       </c>
+      <c r="H23" s="24"/>
       <c r="I23" s="25"/>
     </row>
     <row r="24" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="55"/>
-      <c r="B24" s="55"/>
+      <c r="A24" s="57"/>
+      <c r="B24" s="57"/>
       <c r="C24" s="24">
         <v>9.3000000000000007</v>
       </c>
       <c r="D24" s="25" t="s">
+        <v>103</v>
+      </c>
+      <c r="E24" s="25" t="s">
+        <v>104</v>
+      </c>
+      <c r="F24" s="25" t="s">
+        <v>105</v>
+      </c>
+      <c r="G24" s="47" t="s">
+        <v>106</v>
+      </c>
+      <c r="H24" s="24"/>
+      <c r="I24" s="25" t="s">
         <v>107</v>
       </c>
-      <c r="E24" s="25" t="s">
-        <v>108</v>
-      </c>
-      <c r="F24" s="25" t="s">
-        <v>109</v>
-      </c>
-      <c r="G24" s="47" t="s">
-        <v>110</v>
-      </c>
-      <c r="H24" s="24" t="s">
-        <v>102</v>
-      </c>
-      <c r="I24" s="25" t="s">
-        <v>111</v>
-      </c>
     </row>
     <row r="25" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="56"/>
-      <c r="B25" s="56"/>
+      <c r="A25" s="55"/>
+      <c r="B25" s="55"/>
       <c r="C25" s="24">
         <v>9.4</v>
       </c>
@@ -2124,27 +2151,25 @@
         <v>30</v>
       </c>
       <c r="E25" s="25" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="F25" s="25" t="s">
-        <v>113</v>
+        <v>109</v>
       </c>
       <c r="G25" s="47" t="s">
-        <v>114</v>
-      </c>
-      <c r="H25" s="24" t="s">
-        <v>102</v>
-      </c>
+        <v>110</v>
+      </c>
+      <c r="H25" s="24"/>
       <c r="I25" s="25" t="s">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="39" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="54">
+        <v>10</v>
+      </c>
+      <c r="B26" s="54" t="s">
         <v>111</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" s="39" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="63">
-        <v>10</v>
-      </c>
-      <c r="B26" s="63" t="s">
-        <v>115</v>
       </c>
       <c r="C26" s="37">
         <v>10.1</v>
@@ -2153,22 +2178,22 @@
         <v>30</v>
       </c>
       <c r="E26" s="38" t="s">
-        <v>116</v>
+        <v>112</v>
       </c>
       <c r="F26" s="38" t="s">
-        <v>117</v>
+        <v>113</v>
       </c>
       <c r="G26" s="48" t="s">
-        <v>118</v>
+        <v>114</v>
       </c>
       <c r="H26" s="37" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="I26" s="38"/>
     </row>
     <row r="27" spans="1:9" s="39" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="56"/>
-      <c r="B27" s="56"/>
+      <c r="A27" s="55"/>
+      <c r="B27" s="55"/>
       <c r="C27" s="37">
         <v>10.199999999999999</v>
       </c>
@@ -2176,25 +2201,25 @@
         <v>30</v>
       </c>
       <c r="E27" s="38" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="F27" s="38" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="G27" s="48" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="H27" s="37" t="s">
+        <v>115</v>
+      </c>
+      <c r="I27" s="38"/>
+    </row>
+    <row r="28" spans="1:9" s="39" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="54">
+        <v>11</v>
+      </c>
+      <c r="B28" s="54" t="s">
         <v>119</v>
-      </c>
-      <c r="I27" s="38"/>
-    </row>
-    <row r="28" spans="1:9" s="39" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="63">
-        <v>11</v>
-      </c>
-      <c r="B28" s="63" t="s">
-        <v>123</v>
       </c>
       <c r="C28" s="37">
         <v>11.1</v>
@@ -2203,22 +2228,22 @@
         <v>30</v>
       </c>
       <c r="E28" s="38" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="F28" s="38" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="G28" s="48" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="H28" s="37" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="I28" s="38"/>
     </row>
     <row r="29" spans="1:9" s="39" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="56"/>
-      <c r="B29" s="56"/>
+      <c r="A29" s="55"/>
+      <c r="B29" s="55"/>
       <c r="C29" s="37">
         <v>11.2</v>
       </c>
@@ -2226,25 +2251,25 @@
         <v>30</v>
       </c>
       <c r="E29" s="38" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="F29" s="38" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="G29" s="48" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="H29" s="37" t="s">
+        <v>123</v>
+      </c>
+      <c r="I29" s="38"/>
+    </row>
+    <row r="30" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="66">
+        <v>12</v>
+      </c>
+      <c r="B30" s="66" t="s">
         <v>127</v>
-      </c>
-      <c r="I29" s="38"/>
-    </row>
-    <row r="30" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="58">
-        <v>12</v>
-      </c>
-      <c r="B30" s="58" t="s">
-        <v>131</v>
       </c>
       <c r="C30" s="26">
         <v>12.1</v>
@@ -2253,24 +2278,24 @@
         <v>30</v>
       </c>
       <c r="E30" s="27" t="s">
+        <v>128</v>
+      </c>
+      <c r="F30" s="27" t="s">
+        <v>129</v>
+      </c>
+      <c r="G30" s="49" t="s">
+        <v>130</v>
+      </c>
+      <c r="H30" s="26" t="s">
+        <v>131</v>
+      </c>
+      <c r="I30" s="27" t="s">
         <v>132</v>
       </c>
-      <c r="F30" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="G30" s="49" t="s">
-        <v>134</v>
-      </c>
-      <c r="H30" s="26" t="s">
-        <v>135</v>
-      </c>
-      <c r="I30" s="27" t="s">
-        <v>136</v>
-      </c>
     </row>
     <row r="31" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="55"/>
-      <c r="B31" s="55"/>
+      <c r="A31" s="57"/>
+      <c r="B31" s="57"/>
       <c r="C31" s="26">
         <v>12.2</v>
       </c>
@@ -2278,24 +2303,24 @@
         <v>30</v>
       </c>
       <c r="E31" s="27" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="F31" s="27" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="G31" s="49" t="s">
-        <v>139</v>
+        <v>135</v>
       </c>
       <c r="H31" s="26" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I31" s="27" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
     </row>
     <row r="32" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="56"/>
-      <c r="B32" s="56"/>
+      <c r="A32" s="55"/>
+      <c r="B32" s="55"/>
       <c r="C32" s="26">
         <v>12.3</v>
       </c>
@@ -2303,25 +2328,25 @@
         <v>30</v>
       </c>
       <c r="E32" s="27" t="s">
-        <v>140</v>
+        <v>136</v>
       </c>
       <c r="F32" s="27" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="G32" s="49" t="s">
-        <v>142</v>
+        <v>138</v>
       </c>
       <c r="H32" s="26" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="I32" s="27"/>
     </row>
     <row r="33" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="67">
+      <c r="A33" s="63">
         <v>13</v>
       </c>
-      <c r="B33" s="67" t="s">
-        <v>143</v>
+      <c r="B33" s="63" t="s">
+        <v>139</v>
       </c>
       <c r="C33" s="28">
         <v>13.1</v>
@@ -2330,24 +2355,24 @@
         <v>30</v>
       </c>
       <c r="E33" s="29" t="s">
+        <v>140</v>
+      </c>
+      <c r="F33" s="29" t="s">
+        <v>141</v>
+      </c>
+      <c r="G33" s="50" t="s">
+        <v>142</v>
+      </c>
+      <c r="H33" s="28" t="s">
+        <v>143</v>
+      </c>
+      <c r="I33" s="29" t="s">
         <v>144</v>
       </c>
-      <c r="F33" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="G33" s="50" t="s">
-        <v>146</v>
-      </c>
-      <c r="H33" s="28" t="s">
-        <v>147</v>
-      </c>
-      <c r="I33" s="29" t="s">
-        <v>148</v>
-      </c>
     </row>
     <row r="34" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="55"/>
-      <c r="B34" s="55"/>
+      <c r="A34" s="57"/>
+      <c r="B34" s="57"/>
       <c r="C34" s="28">
         <v>13.2</v>
       </c>
@@ -2355,29 +2380,29 @@
         <v>30</v>
       </c>
       <c r="E34" s="29" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="F34" s="29" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="G34" s="50" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="H34" s="28" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="I34" s="29" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
     </row>
     <row r="35" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A35" s="55"/>
-      <c r="B35" s="55"/>
+      <c r="A35" s="57"/>
+      <c r="B35" s="57"/>
       <c r="C35" s="28">
         <v>13.3</v>
       </c>
       <c r="D35" s="29" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="E35" s="29" t="s">
         <v>12</v>
@@ -2389,15 +2414,15 @@
         <v>14</v>
       </c>
       <c r="H35" s="28" t="s">
-        <v>15</v>
+        <v>158</v>
       </c>
       <c r="I35" s="29" t="s">
-        <v>153</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" s="8" customFormat="1" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="56"/>
-      <c r="B36" s="56"/>
+        <v>149</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" s="8" customFormat="1" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="55"/>
+      <c r="B36" s="55"/>
       <c r="C36" s="28">
         <v>13.4</v>
       </c>
@@ -2405,27 +2430,27 @@
         <v>30</v>
       </c>
       <c r="E36" s="29" t="s">
+        <v>150</v>
+      </c>
+      <c r="F36" s="29" t="s">
+        <v>151</v>
+      </c>
+      <c r="G36" s="50" t="s">
+        <v>152</v>
+      </c>
+      <c r="H36" s="28" t="s">
+        <v>15</v>
+      </c>
+      <c r="I36" s="29" t="s">
+        <v>153</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="64">
+        <v>14</v>
+      </c>
+      <c r="B37" s="64" t="s">
         <v>154</v>
-      </c>
-      <c r="F36" s="29" t="s">
-        <v>155</v>
-      </c>
-      <c r="G36" s="50" t="s">
-        <v>156</v>
-      </c>
-      <c r="H36" s="28" t="s">
-        <v>147</v>
-      </c>
-      <c r="I36" s="29" t="s">
-        <v>157</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="65">
-        <v>14</v>
-      </c>
-      <c r="B37" s="65" t="s">
-        <v>158</v>
       </c>
       <c r="C37" s="30">
         <v>14.1</v>
@@ -2434,24 +2459,24 @@
         <v>30</v>
       </c>
       <c r="E37" s="31" t="s">
+        <v>155</v>
+      </c>
+      <c r="F37" s="31" t="s">
+        <v>156</v>
+      </c>
+      <c r="G37" s="51" t="s">
+        <v>157</v>
+      </c>
+      <c r="H37" s="30" t="s">
+        <v>223</v>
+      </c>
+      <c r="I37" s="31" t="s">
         <v>159</v>
       </c>
-      <c r="F37" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="G37" s="51" t="s">
-        <v>161</v>
-      </c>
-      <c r="H37" s="30" t="s">
-        <v>162</v>
-      </c>
-      <c r="I37" s="31" t="s">
-        <v>163</v>
-      </c>
     </row>
     <row r="38" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="56"/>
-      <c r="B38" s="56"/>
+      <c r="A38" s="55"/>
+      <c r="B38" s="55"/>
       <c r="C38" s="30">
         <v>14.2</v>
       </c>
@@ -2459,362 +2484,346 @@
         <v>30</v>
       </c>
       <c r="E38" s="31" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="F38" s="31" t="s">
-        <v>165</v>
+        <v>161</v>
       </c>
       <c r="G38" s="51" t="s">
-        <v>166</v>
+        <v>162</v>
       </c>
       <c r="H38" s="30" t="s">
-        <v>162</v>
+        <v>223</v>
       </c>
       <c r="I38" s="31" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A39" s="67">
+        <v>15</v>
+      </c>
+      <c r="B39" s="67" t="s">
         <v>163</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="69">
-        <v>15</v>
-      </c>
-      <c r="B39" s="69" t="s">
-        <v>167</v>
       </c>
       <c r="C39" s="32">
         <v>15.1</v>
       </c>
       <c r="D39" s="33" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E39" s="33" t="s">
-        <v>169</v>
+        <v>165</v>
       </c>
       <c r="F39" s="33" t="s">
-        <v>170</v>
+        <v>166</v>
       </c>
       <c r="G39" s="52" t="s">
-        <v>171</v>
-      </c>
-      <c r="H39" s="32" t="s">
-        <v>172</v>
-      </c>
+        <v>167</v>
+      </c>
+      <c r="H39" s="32"/>
       <c r="I39" s="33"/>
     </row>
     <row r="40" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="55"/>
-      <c r="B40" s="55"/>
+      <c r="A40" s="57"/>
+      <c r="B40" s="57"/>
       <c r="C40" s="32">
         <v>15.2</v>
       </c>
       <c r="D40" s="33" t="s">
+        <v>164</v>
+      </c>
+      <c r="E40" s="33" t="s">
         <v>168</v>
       </c>
-      <c r="E40" s="33" t="s">
-        <v>173</v>
-      </c>
       <c r="F40" s="33" t="s">
-        <v>174</v>
+        <v>169</v>
       </c>
       <c r="G40" s="52" t="s">
-        <v>175</v>
-      </c>
-      <c r="H40" s="32" t="s">
-        <v>172</v>
-      </c>
+        <v>170</v>
+      </c>
+      <c r="H40" s="32"/>
       <c r="I40" s="33"/>
     </row>
     <row r="41" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="55"/>
-      <c r="B41" s="55"/>
+      <c r="A41" s="57"/>
+      <c r="B41" s="57"/>
       <c r="C41" s="32">
         <v>15.3</v>
       </c>
       <c r="D41" s="33" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E41" s="33" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="F41" s="33" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="G41" s="52" t="s">
-        <v>178</v>
-      </c>
-      <c r="H41" s="32" t="s">
-        <v>172</v>
-      </c>
+        <v>173</v>
+      </c>
+      <c r="H41" s="32"/>
       <c r="I41" s="33"/>
     </row>
     <row r="42" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="55"/>
-      <c r="B42" s="55"/>
+      <c r="A42" s="57"/>
+      <c r="B42" s="57"/>
       <c r="C42" s="32">
         <v>15.4</v>
       </c>
       <c r="D42" s="33" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E42" s="33" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="F42" s="33" t="s">
-        <v>180</v>
+        <v>175</v>
       </c>
       <c r="G42" s="52" t="s">
-        <v>181</v>
-      </c>
-      <c r="H42" s="32" t="s">
-        <v>172</v>
-      </c>
+        <v>176</v>
+      </c>
+      <c r="H42" s="32"/>
       <c r="I42" s="33"/>
     </row>
     <row r="43" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="56"/>
-      <c r="B43" s="56"/>
+      <c r="A43" s="55"/>
+      <c r="B43" s="55"/>
       <c r="C43" s="32">
         <v>15.5</v>
       </c>
       <c r="D43" s="33" t="s">
-        <v>168</v>
+        <v>164</v>
       </c>
       <c r="E43" s="33" t="s">
-        <v>182</v>
+        <v>177</v>
       </c>
       <c r="F43" s="33" t="s">
-        <v>183</v>
+        <v>178</v>
       </c>
       <c r="G43" s="52" t="s">
-        <v>184</v>
-      </c>
-      <c r="H43" s="32" t="s">
-        <v>172</v>
-      </c>
+        <v>179</v>
+      </c>
+      <c r="H43" s="32"/>
       <c r="I43" s="33"/>
     </row>
     <row r="44" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="68">
+      <c r="A44" s="65">
         <v>16</v>
       </c>
-      <c r="B44" s="68" t="s">
-        <v>185</v>
+      <c r="B44" s="65" t="s">
+        <v>180</v>
       </c>
       <c r="C44" s="34">
         <v>16.100000000000001</v>
       </c>
       <c r="D44" s="35" t="s">
-        <v>186</v>
+        <v>181</v>
       </c>
       <c r="E44" s="35" t="s">
-        <v>187</v>
+        <v>182</v>
       </c>
       <c r="F44" s="35" t="s">
-        <v>188</v>
+        <v>183</v>
       </c>
       <c r="G44" s="53" t="s">
-        <v>189</v>
-      </c>
-      <c r="H44" s="34" t="s">
-        <v>190</v>
-      </c>
+        <v>184</v>
+      </c>
+      <c r="H44" s="34"/>
       <c r="I44" s="35"/>
     </row>
     <row r="45" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="56"/>
-      <c r="B45" s="56"/>
+      <c r="A45" s="55"/>
+      <c r="B45" s="55"/>
       <c r="C45" s="34">
         <v>16.2</v>
       </c>
       <c r="D45" s="35" t="s">
-        <v>191</v>
+        <v>185</v>
       </c>
       <c r="E45" s="35" t="s">
-        <v>192</v>
+        <v>186</v>
       </c>
       <c r="F45" s="35" t="s">
-        <v>193</v>
+        <v>187</v>
       </c>
       <c r="G45" s="53" t="s">
-        <v>194</v>
-      </c>
-      <c r="H45" s="34" t="s">
-        <v>190</v>
-      </c>
+        <v>188</v>
+      </c>
+      <c r="H45" s="34"/>
       <c r="I45" s="35"/>
     </row>
     <row r="46" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="61">
+      <c r="A46" s="59">
         <v>17</v>
       </c>
-      <c r="B46" s="61" t="s">
-        <v>195</v>
+      <c r="B46" s="59" t="s">
+        <v>189</v>
       </c>
       <c r="C46" s="15">
         <v>17.100000000000001</v>
       </c>
       <c r="D46" s="16" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E46" s="16" t="s">
-        <v>197</v>
+        <v>191</v>
       </c>
       <c r="F46" s="16" t="s">
-        <v>198</v>
+        <v>192</v>
       </c>
       <c r="G46" s="44" t="s">
-        <v>199</v>
-      </c>
-      <c r="H46" s="15" t="s">
-        <v>102</v>
-      </c>
+        <v>193</v>
+      </c>
+      <c r="H46" s="15"/>
       <c r="I46" s="16" t="s">
-        <v>200</v>
+        <v>194</v>
       </c>
     </row>
     <row r="47" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="55"/>
-      <c r="B47" s="55"/>
+      <c r="A47" s="57"/>
+      <c r="B47" s="57"/>
       <c r="C47" s="15">
         <v>17.2</v>
       </c>
       <c r="D47" s="16" t="s">
+        <v>190</v>
+      </c>
+      <c r="E47" s="16" t="s">
+        <v>195</v>
+      </c>
+      <c r="F47" s="16" t="s">
         <v>196</v>
       </c>
-      <c r="E47" s="16" t="s">
-        <v>201</v>
-      </c>
-      <c r="F47" s="16" t="s">
-        <v>202</v>
-      </c>
       <c r="G47" s="44" t="s">
-        <v>203</v>
+        <v>197</v>
       </c>
       <c r="H47" s="15"/>
       <c r="I47" s="16"/>
     </row>
     <row r="48" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="55"/>
-      <c r="B48" s="55"/>
+      <c r="A48" s="57"/>
+      <c r="B48" s="57"/>
       <c r="C48" s="15">
         <v>17.3</v>
       </c>
       <c r="D48" s="16" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E48" s="16" t="s">
-        <v>204</v>
+        <v>198</v>
       </c>
       <c r="F48" s="16" t="s">
-        <v>205</v>
+        <v>199</v>
       </c>
       <c r="G48" s="44" t="s">
-        <v>206</v>
+        <v>200</v>
       </c>
       <c r="H48" s="15"/>
       <c r="I48" s="16"/>
     </row>
     <row r="49" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="55"/>
-      <c r="B49" s="55"/>
+      <c r="A49" s="57"/>
+      <c r="B49" s="57"/>
       <c r="C49" s="15">
         <v>17.399999999999999</v>
       </c>
       <c r="D49" s="16" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E49" s="16" t="s">
-        <v>207</v>
+        <v>201</v>
       </c>
       <c r="F49" s="16" t="s">
-        <v>208</v>
+        <v>202</v>
       </c>
       <c r="G49" s="44" t="s">
-        <v>209</v>
+        <v>203</v>
       </c>
       <c r="H49" s="15"/>
       <c r="I49" s="16"/>
     </row>
     <row r="50" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="55"/>
-      <c r="B50" s="55"/>
+      <c r="A50" s="57"/>
+      <c r="B50" s="57"/>
       <c r="C50" s="15">
         <v>17.5</v>
       </c>
       <c r="D50" s="16" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E50" s="16" t="s">
-        <v>210</v>
+        <v>204</v>
       </c>
       <c r="F50" s="16" t="s">
-        <v>211</v>
+        <v>205</v>
       </c>
       <c r="G50" s="44" t="s">
-        <v>212</v>
+        <v>206</v>
       </c>
       <c r="H50" s="15"/>
       <c r="I50" s="16"/>
     </row>
     <row r="51" spans="1:9" s="8" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="55"/>
-      <c r="B51" s="55"/>
+      <c r="A51" s="57"/>
+      <c r="B51" s="57"/>
       <c r="C51" s="15">
         <v>17.600000000000001</v>
       </c>
       <c r="D51" s="16" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E51" s="16" t="s">
-        <v>213</v>
+        <v>207</v>
       </c>
       <c r="F51" s="16" t="s">
-        <v>214</v>
+        <v>208</v>
       </c>
       <c r="G51" s="44" t="s">
-        <v>215</v>
+        <v>209</v>
       </c>
       <c r="H51" s="15"/>
       <c r="I51" s="16"/>
     </row>
     <row r="52" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A52" s="55"/>
-      <c r="B52" s="55"/>
+      <c r="A52" s="57"/>
+      <c r="B52" s="57"/>
       <c r="C52" s="15">
         <v>17.7</v>
       </c>
       <c r="D52" s="16" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E52" s="16" t="s">
-        <v>216</v>
+        <v>210</v>
       </c>
       <c r="F52" s="16" t="s">
-        <v>217</v>
+        <v>211</v>
       </c>
       <c r="G52" s="44" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
       <c r="H52" s="15"/>
       <c r="I52" s="16"/>
     </row>
     <row r="53" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A53" s="56"/>
-      <c r="B53" s="56"/>
+      <c r="A53" s="55"/>
+      <c r="B53" s="55"/>
       <c r="C53" s="15">
         <v>17.8</v>
       </c>
       <c r="D53" s="16" t="s">
-        <v>196</v>
+        <v>190</v>
       </c>
       <c r="E53" s="16" t="s">
-        <v>219</v>
+        <v>213</v>
       </c>
       <c r="F53" s="16" t="s">
-        <v>220</v>
+        <v>214</v>
       </c>
       <c r="G53" s="44" t="s">
-        <v>221</v>
+        <v>215</v>
       </c>
       <c r="H53" s="15"/>
       <c r="I53" s="16"/>
@@ -2856,8 +2865,6 @@
   </sheetData>
   <autoFilter ref="I1:I33" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="35">
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="B33:B36"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="A44:A45"/>
@@ -2871,6 +2878,15 @@
     <mergeCell ref="B39:B43"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="A37:A38"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A7:A12"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="B46:B53"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="B16:B18"/>
@@ -2884,14 +2900,8 @@
     <mergeCell ref="B22:B25"/>
     <mergeCell ref="B7:B12"/>
     <mergeCell ref="B30:B32"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="A13:A15"/>
-    <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A7:A12"/>
-    <mergeCell ref="A19:A21"/>
   </mergeCells>
+  <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait"/>
 </worksheet>

--- a/Soubhanik/checkupp_product_backlog_final.xlsx
+++ b/Soubhanik/checkupp_product_backlog_final.xlsx
@@ -1,16 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30026"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anodiam\2026\CheckUpp_Parent\CheckUpp\Soubhanik\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CheckUpp\Soubhanik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{277A931B-5C20-4135-8FCF-678BD972299A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="-105" windowWidth="23258" windowHeight="13898"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -22,6 +21,136 @@
 </workbook>
 </file>
 
+<file path=xl/comments1.xml><?xml version="1.0" encoding="utf-8"?>
+<comments xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <authors>
+    <author>User</author>
+  </authors>
+  <commentList>
+    <comment ref="E3" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anirban:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Invalid User Story: This is not an action by the user.</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F3" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anirban:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Invalid "system change".</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G3" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anirban:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Which exact form, field, Unclear requirement?</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anirban:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Seeing is not a valid user action</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F4" authorId="0" shapeId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anirban:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+This should be about the system, not about user.</t>
+        </r>
+      </text>
+    </comment>
+  </commentList>
+</comments>
+</file>
+
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="285" uniqueCount="224">
   <si>
@@ -763,8 +892,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <fonts count="12" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -808,6 +937,39 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="9"/>
+      <color indexed="81"/>
+      <name val="Tahoma"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="19">
@@ -1025,7 +1187,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="76">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1051,12 +1213,6 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1132,9 +1288,6 @@
     <xf numFmtId="0" fontId="5" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1144,12 +1297,6 @@
     <xf numFmtId="0" fontId="0" fillId="17" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1186,65 +1333,89 @@
     <xf numFmtId="0" fontId="5" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="18" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="8" fillId="6" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1526,52 +1697,52 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:I59"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="5.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.88671875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="5.86328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.86328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.1328125" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.86328125" style="3" customWidth="1"/>
     <col min="5" max="5" width="65" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="41" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="49.77734375" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="49.796875" style="3" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="11.6640625" style="2" customWidth="1"/>
     <col min="9" max="9" width="10.33203125" style="3" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="8.88671875" style="5" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="5"/>
+    <col min="10" max="12" width="8.86328125" style="5" customWidth="1"/>
+    <col min="13" max="16384" width="8.86328125" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="70" t="s">
+    <row r="1" spans="1:9" ht="39.6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="60" t="s">
+      <c r="B1" s="50" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="60" t="s">
+      <c r="C1" s="50" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="60" t="s">
+      <c r="D1" s="50" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="71"/>
-      <c r="F1" s="72"/>
-      <c r="G1" s="73" t="s">
+      <c r="E1" s="52"/>
+      <c r="F1" s="53"/>
+      <c r="G1" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="60" t="s">
+      <c r="H1" s="50" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="60" t="s">
+      <c r="I1" s="50" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A2" s="55"/>
-      <c r="B2" s="61"/>
-      <c r="C2" s="61"/>
+      <c r="B2" s="51"/>
+      <c r="C2" s="51"/>
       <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1581,1254 +1752,1254 @@
       <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="74"/>
-      <c r="H2" s="61"/>
-      <c r="I2" s="61"/>
-    </row>
-    <row r="3" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="36">
+      <c r="G2" s="67"/>
+      <c r="H2" s="51"/>
+      <c r="I2" s="51"/>
+    </row>
+    <row r="3" spans="1:9" s="75" customFormat="1" ht="55.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A3" s="72">
         <v>1</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="72" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="9">
+      <c r="C3" s="73">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D3" s="10" t="s">
+      <c r="D3" s="71" t="s">
         <v>11</v>
       </c>
-      <c r="E3" s="10" t="s">
+      <c r="E3" s="71" t="s">
         <v>12</v>
       </c>
-      <c r="F3" s="10" t="s">
+      <c r="F3" s="71" t="s">
         <v>13</v>
       </c>
-      <c r="G3" s="40" t="s">
+      <c r="G3" s="74" t="s">
         <v>14</v>
       </c>
-      <c r="H3" s="9" t="s">
+      <c r="H3" s="73" t="s">
         <v>158</v>
       </c>
-      <c r="I3" s="10" t="s">
+      <c r="I3" s="71" t="s">
         <v>16</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="69">
+    <row r="4" spans="1:9" s="75" customFormat="1" ht="41.45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A4" s="65">
         <v>3</v>
       </c>
-      <c r="B4" s="69" t="s">
+      <c r="B4" s="65" t="s">
         <v>17</v>
       </c>
-      <c r="C4" s="11">
+      <c r="C4" s="77">
         <v>3.1</v>
       </c>
-      <c r="D4" s="12" t="s">
+      <c r="D4" s="76" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="12" t="s">
+      <c r="E4" s="76" t="s">
         <v>18</v>
       </c>
-      <c r="F4" s="12" t="s">
+      <c r="F4" s="76" t="s">
         <v>19</v>
       </c>
-      <c r="G4" s="41" t="s">
+      <c r="G4" s="78" t="s">
         <v>20</v>
       </c>
-      <c r="H4" s="11" t="s">
+      <c r="H4" s="77" t="s">
         <v>217</v>
       </c>
-      <c r="I4" s="12" t="s">
+      <c r="I4" s="76" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" s="8" customFormat="1" ht="55.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A5" s="57"/>
       <c r="B5" s="57"/>
-      <c r="C5" s="11">
+      <c r="C5" s="9">
         <v>3.2</v>
       </c>
-      <c r="D5" s="12" t="s">
+      <c r="D5" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="12" t="s">
+      <c r="E5" s="10" t="s">
         <v>23</v>
       </c>
-      <c r="F5" s="12" t="s">
+      <c r="F5" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="G5" s="42" t="s">
+      <c r="G5" s="37" t="s">
         <v>25</v>
       </c>
-      <c r="H5" s="11" t="s">
+      <c r="H5" s="9" t="s">
         <v>218</v>
       </c>
-      <c r="I5" s="12" t="s">
+      <c r="I5" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:9" s="8" customFormat="1" ht="41.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A6" s="55"/>
       <c r="B6" s="55"/>
-      <c r="C6" s="11">
+      <c r="C6" s="9">
         <v>3.3</v>
       </c>
-      <c r="D6" s="12" t="s">
+      <c r="D6" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="12" t="s">
+      <c r="E6" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="F6" s="12" t="s">
+      <c r="F6" s="10" t="s">
         <v>27</v>
       </c>
-      <c r="G6" s="42" t="s">
+      <c r="G6" s="37" t="s">
         <v>28</v>
       </c>
-      <c r="H6" s="11" t="s">
+      <c r="H6" s="9" t="s">
         <v>217</v>
       </c>
-      <c r="I6" s="12" t="s">
+      <c r="I6" s="10" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="56">
+    <row r="7" spans="1:9" s="8" customFormat="1" ht="41.45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A7" s="69">
         <v>4</v>
       </c>
-      <c r="B7" s="56" t="s">
+      <c r="B7" s="69" t="s">
         <v>29</v>
       </c>
-      <c r="C7" s="13">
+      <c r="C7" s="11">
         <v>4.0999999999999996</v>
       </c>
-      <c r="D7" s="14" t="s">
+      <c r="D7" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E7" s="14" t="s">
+      <c r="E7" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="F7" s="14" t="s">
+      <c r="F7" s="12" t="s">
         <v>32</v>
       </c>
-      <c r="G7" s="43" t="s">
+      <c r="G7" s="38" t="s">
         <v>33</v>
       </c>
-      <c r="H7" s="13" t="s">
+      <c r="H7" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="I7" s="14" t="s">
+      <c r="I7" s="12" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:9" s="8" customFormat="1" ht="41.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A8" s="57"/>
       <c r="B8" s="57"/>
-      <c r="C8" s="13">
+      <c r="C8" s="11">
         <v>4.2</v>
       </c>
-      <c r="D8" s="14" t="s">
+      <c r="D8" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E8" s="14" t="s">
+      <c r="E8" s="12" t="s">
         <v>36</v>
       </c>
-      <c r="F8" s="14" t="s">
+      <c r="F8" s="12" t="s">
         <v>37</v>
       </c>
-      <c r="G8" s="43" t="s">
+      <c r="G8" s="38" t="s">
         <v>38</v>
       </c>
-      <c r="H8" s="13" t="s">
+      <c r="H8" s="11" t="s">
         <v>216</v>
       </c>
-      <c r="I8" s="14"/>
-    </row>
-    <row r="9" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I8" s="12"/>
+    </row>
+    <row r="9" spans="1:9" s="8" customFormat="1" ht="41.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A9" s="57"/>
       <c r="B9" s="57"/>
-      <c r="C9" s="13">
+      <c r="C9" s="11">
         <v>4.3</v>
       </c>
-      <c r="D9" s="14" t="s">
+      <c r="D9" s="12" t="s">
         <v>39</v>
       </c>
-      <c r="E9" s="14" t="s">
+      <c r="E9" s="12" t="s">
         <v>40</v>
       </c>
-      <c r="F9" s="14" t="s">
+      <c r="F9" s="12" t="s">
         <v>41</v>
       </c>
-      <c r="G9" s="43" t="s">
+      <c r="G9" s="38" t="s">
         <v>42</v>
       </c>
-      <c r="H9" s="13" t="s">
+      <c r="H9" s="11" t="s">
         <v>21</v>
       </c>
-      <c r="I9" s="14" t="s">
+      <c r="I9" s="12" t="s">
         <v>44</v>
       </c>
     </row>
-    <row r="10" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:9" s="8" customFormat="1" ht="41.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A10" s="57"/>
       <c r="B10" s="57"/>
-      <c r="C10" s="13">
+      <c r="C10" s="11">
         <v>4.4000000000000004</v>
       </c>
-      <c r="D10" s="14" t="s">
+      <c r="D10" s="12" t="s">
         <v>45</v>
       </c>
-      <c r="E10" s="14" t="s">
+      <c r="E10" s="12" t="s">
         <v>46</v>
       </c>
-      <c r="F10" s="14" t="s">
+      <c r="F10" s="12" t="s">
         <v>47</v>
       </c>
-      <c r="G10" s="43" t="s">
+      <c r="G10" s="38" t="s">
         <v>48</v>
       </c>
-      <c r="H10" s="13" t="s">
+      <c r="H10" s="11" t="s">
         <v>34</v>
       </c>
-      <c r="I10" s="14" t="s">
+      <c r="I10" s="12" t="s">
         <v>49</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:9" s="8" customFormat="1" ht="41.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A11" s="57"/>
       <c r="B11" s="57"/>
-      <c r="C11" s="75">
+      <c r="C11" s="49">
         <v>4.5</v>
       </c>
-      <c r="D11" s="14" t="s">
+      <c r="D11" s="12" t="s">
         <v>50</v>
       </c>
-      <c r="E11" s="14" t="s">
+      <c r="E11" s="12" t="s">
         <v>51</v>
       </c>
-      <c r="F11" s="14" t="s">
+      <c r="F11" s="12" t="s">
         <v>52</v>
       </c>
-      <c r="G11" s="43" t="s">
+      <c r="G11" s="38" t="s">
         <v>53</v>
       </c>
-      <c r="H11" s="13" t="s">
+      <c r="H11" s="11" t="s">
         <v>54</v>
       </c>
-      <c r="I11" s="14"/>
-    </row>
-    <row r="12" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I11" s="12"/>
+    </row>
+    <row r="12" spans="1:9" s="8" customFormat="1" ht="55.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A12" s="55"/>
       <c r="B12" s="55"/>
-      <c r="C12" s="75">
+      <c r="C12" s="49">
         <v>4.5999999999999996</v>
       </c>
-      <c r="D12" s="14" t="s">
+      <c r="D12" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="E12" s="14" t="s">
+      <c r="E12" s="12" t="s">
         <v>55</v>
       </c>
-      <c r="F12" s="14" t="s">
+      <c r="F12" s="12" t="s">
         <v>56</v>
       </c>
-      <c r="G12" s="43" t="s">
+      <c r="G12" s="38" t="s">
         <v>57</v>
       </c>
-      <c r="H12" s="13" t="s">
+      <c r="H12" s="11" t="s">
         <v>43</v>
       </c>
-      <c r="I12" s="14"/>
-    </row>
-    <row r="13" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="59">
+      <c r="I12" s="12"/>
+    </row>
+    <row r="13" spans="1:9" s="8" customFormat="1" ht="41.45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A13" s="60">
         <v>5</v>
       </c>
-      <c r="B13" s="59" t="s">
+      <c r="B13" s="60" t="s">
         <v>58</v>
       </c>
-      <c r="C13" s="15">
+      <c r="C13" s="13">
         <v>5.0999999999999996</v>
       </c>
-      <c r="D13" s="16" t="s">
+      <c r="D13" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="E13" s="16" t="s">
+      <c r="E13" s="14" t="s">
         <v>59</v>
       </c>
-      <c r="F13" s="16" t="s">
+      <c r="F13" s="14" t="s">
         <v>60</v>
       </c>
-      <c r="G13" s="44" t="s">
+      <c r="G13" s="39" t="s">
         <v>61</v>
       </c>
-      <c r="H13" s="17" t="s">
+      <c r="H13" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="I13" s="16" t="s">
+      <c r="I13" s="14" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="8" customFormat="1" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:9" s="8" customFormat="1" ht="96.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A14" s="57"/>
       <c r="B14" s="57"/>
-      <c r="C14" s="15">
+      <c r="C14" s="13">
         <v>5.2</v>
       </c>
-      <c r="D14" s="16" t="s">
+      <c r="D14" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="E14" s="16" t="s">
+      <c r="E14" s="14" t="s">
         <v>64</v>
       </c>
-      <c r="F14" s="16" t="s">
+      <c r="F14" s="14" t="s">
         <v>65</v>
       </c>
-      <c r="G14" s="44" t="s">
+      <c r="G14" s="39" t="s">
         <v>66</v>
       </c>
-      <c r="H14" s="17" t="s">
+      <c r="H14" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="I14" s="16" t="s">
+      <c r="I14" s="14" t="s">
         <v>67</v>
       </c>
     </row>
-    <row r="15" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:9" s="8" customFormat="1" ht="41.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A15" s="55"/>
       <c r="B15" s="55"/>
-      <c r="C15" s="15">
+      <c r="C15" s="13">
         <v>5.3</v>
       </c>
-      <c r="D15" s="16" t="s">
+      <c r="D15" s="14" t="s">
         <v>30</v>
       </c>
-      <c r="E15" s="16" t="s">
+      <c r="E15" s="14" t="s">
         <v>68</v>
       </c>
-      <c r="F15" s="16" t="s">
+      <c r="F15" s="14" t="s">
         <v>69</v>
       </c>
-      <c r="G15" s="44" t="s">
+      <c r="G15" s="39" t="s">
         <v>70</v>
       </c>
-      <c r="H15" s="17" t="s">
+      <c r="H15" s="15" t="s">
         <v>219</v>
       </c>
-      <c r="I15" s="16"/>
-    </row>
-    <row r="16" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="62">
+      <c r="I15" s="14"/>
+    </row>
+    <row r="16" spans="1:9" s="8" customFormat="1" ht="41.45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A16" s="58">
         <v>6</v>
       </c>
-      <c r="B16" s="62" t="s">
+      <c r="B16" s="58" t="s">
         <v>71</v>
       </c>
-      <c r="C16" s="18">
+      <c r="C16" s="16">
         <v>6.1</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="17" t="s">
         <v>72</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="17" t="s">
         <v>73</v>
       </c>
-      <c r="G16" s="45" t="s">
+      <c r="G16" s="40" t="s">
         <v>74</v>
       </c>
-      <c r="H16" s="20" t="s">
+      <c r="H16" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="I16" s="19" t="s">
+      <c r="I16" s="17" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="17" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:9" s="8" customFormat="1" ht="41.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A17" s="57"/>
       <c r="B17" s="57"/>
-      <c r="C17" s="18">
+      <c r="C17" s="16">
         <v>6.2</v>
       </c>
-      <c r="D17" s="19" t="s">
+      <c r="D17" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E17" s="19" t="s">
+      <c r="E17" s="17" t="s">
         <v>76</v>
       </c>
-      <c r="F17" s="19" t="s">
+      <c r="F17" s="17" t="s">
         <v>77</v>
       </c>
-      <c r="G17" s="45" t="s">
+      <c r="G17" s="40" t="s">
         <v>78</v>
       </c>
-      <c r="H17" s="18" t="s">
+      <c r="H17" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="I17" s="19" t="s">
+      <c r="I17" s="17" t="s">
         <v>79</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:9" s="8" customFormat="1" ht="41.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A18" s="55"/>
       <c r="B18" s="55"/>
-      <c r="C18" s="18">
+      <c r="C18" s="16">
         <v>6.3</v>
       </c>
-      <c r="D18" s="19" t="s">
+      <c r="D18" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="E18" s="19" t="s">
+      <c r="E18" s="17" t="s">
         <v>80</v>
       </c>
-      <c r="F18" s="19" t="s">
+      <c r="F18" s="17" t="s">
         <v>81</v>
       </c>
-      <c r="G18" s="45" t="s">
+      <c r="G18" s="40" t="s">
         <v>82</v>
       </c>
-      <c r="H18" s="18" t="s">
+      <c r="H18" s="16" t="s">
         <v>220</v>
       </c>
-      <c r="I18" s="19"/>
-    </row>
-    <row r="19" spans="1:9" s="8" customFormat="1" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="58">
+      <c r="I18" s="17"/>
+    </row>
+    <row r="19" spans="1:9" s="8" customFormat="1" ht="82.8" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A19" s="61">
         <v>7</v>
       </c>
-      <c r="B19" s="58" t="s">
+      <c r="B19" s="61" t="s">
         <v>83</v>
       </c>
-      <c r="C19" s="21">
+      <c r="C19" s="19">
         <v>7.1</v>
       </c>
-      <c r="D19" s="22" t="s">
+      <c r="D19" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="E19" s="22" t="s">
+      <c r="E19" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="F19" s="22" t="s">
+      <c r="F19" s="20" t="s">
         <v>86</v>
       </c>
-      <c r="G19" s="46" t="s">
+      <c r="G19" s="41" t="s">
         <v>87</v>
       </c>
-      <c r="H19" s="23" t="s">
+      <c r="H19" s="21" t="s">
         <v>221</v>
       </c>
-      <c r="I19" s="22" t="s">
+      <c r="I19" s="20" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="20" spans="1:9" s="8" customFormat="1" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:9" s="8" customFormat="1" ht="82.8" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A20" s="57"/>
       <c r="B20" s="57"/>
-      <c r="C20" s="21">
+      <c r="C20" s="19">
         <v>7.2</v>
       </c>
-      <c r="D20" s="22" t="s">
+      <c r="D20" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="E20" s="22" t="s">
+      <c r="E20" s="20" t="s">
         <v>89</v>
       </c>
-      <c r="F20" s="22" t="s">
+      <c r="F20" s="20" t="s">
         <v>90</v>
       </c>
-      <c r="G20" s="46" t="s">
+      <c r="G20" s="41" t="s">
         <v>91</v>
       </c>
-      <c r="H20" s="21" t="s">
+      <c r="H20" s="19" t="s">
         <v>222</v>
       </c>
-      <c r="I20" s="22" t="s">
+      <c r="I20" s="20" t="s">
         <v>88</v>
       </c>
     </row>
-    <row r="21" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:9" s="8" customFormat="1" ht="41.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A21" s="55"/>
       <c r="B21" s="55"/>
-      <c r="C21" s="21">
+      <c r="C21" s="19">
         <v>7.3</v>
       </c>
-      <c r="D21" s="22" t="s">
+      <c r="D21" s="20" t="s">
         <v>84</v>
       </c>
-      <c r="E21" s="22" t="s">
+      <c r="E21" s="20" t="s">
         <v>92</v>
       </c>
-      <c r="F21" s="22" t="s">
+      <c r="F21" s="20" t="s">
         <v>93</v>
       </c>
-      <c r="G21" s="46" t="s">
+      <c r="G21" s="41" t="s">
         <v>94</v>
       </c>
-      <c r="H21" s="21" t="s">
+      <c r="H21" s="19" t="s">
         <v>221</v>
       </c>
-      <c r="I21" s="22"/>
-    </row>
-    <row r="22" spans="1:9" s="8" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="68">
+      <c r="I21" s="20"/>
+    </row>
+    <row r="22" spans="1:9" s="8" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A22" s="56">
         <v>9</v>
       </c>
-      <c r="B22" s="68" t="s">
+      <c r="B22" s="56" t="s">
         <v>95</v>
       </c>
-      <c r="C22" s="24">
+      <c r="C22" s="22">
         <v>9.1</v>
       </c>
-      <c r="D22" s="25" t="s">
+      <c r="D22" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="E22" s="25" t="s">
+      <c r="E22" s="23" t="s">
         <v>96</v>
       </c>
-      <c r="F22" s="25" t="s">
+      <c r="F22" s="23" t="s">
         <v>97</v>
       </c>
-      <c r="G22" s="47" t="s">
+      <c r="G22" s="42" t="s">
         <v>98</v>
       </c>
-      <c r="H22" s="24"/>
-      <c r="I22" s="25"/>
-    </row>
-    <row r="23" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H22" s="22"/>
+      <c r="I22" s="23"/>
+    </row>
+    <row r="23" spans="1:9" s="8" customFormat="1" ht="41.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A23" s="57"/>
       <c r="B23" s="57"/>
-      <c r="C23" s="24">
+      <c r="C23" s="22">
         <v>9.1999999999999993</v>
       </c>
-      <c r="D23" s="25" t="s">
+      <c r="D23" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="E23" s="25" t="s">
+      <c r="E23" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="F23" s="25" t="s">
+      <c r="F23" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="G23" s="47" t="s">
+      <c r="G23" s="42" t="s">
         <v>102</v>
       </c>
-      <c r="H23" s="24"/>
-      <c r="I23" s="25"/>
-    </row>
-    <row r="24" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H23" s="22"/>
+      <c r="I23" s="23"/>
+    </row>
+    <row r="24" spans="1:9" s="8" customFormat="1" ht="41.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A24" s="57"/>
       <c r="B24" s="57"/>
-      <c r="C24" s="24">
+      <c r="C24" s="22">
         <v>9.3000000000000007</v>
       </c>
-      <c r="D24" s="25" t="s">
+      <c r="D24" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="E24" s="25" t="s">
+      <c r="E24" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="F24" s="25" t="s">
+      <c r="F24" s="23" t="s">
         <v>105</v>
       </c>
-      <c r="G24" s="47" t="s">
+      <c r="G24" s="42" t="s">
         <v>106</v>
       </c>
-      <c r="H24" s="24"/>
-      <c r="I24" s="25" t="s">
+      <c r="H24" s="22"/>
+      <c r="I24" s="23" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" s="8" customFormat="1" ht="55.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A25" s="55"/>
       <c r="B25" s="55"/>
-      <c r="C25" s="24">
+      <c r="C25" s="22">
         <v>9.4</v>
       </c>
-      <c r="D25" s="25" t="s">
+      <c r="D25" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="E25" s="25" t="s">
+      <c r="E25" s="23" t="s">
         <v>108</v>
       </c>
-      <c r="F25" s="25" t="s">
+      <c r="F25" s="23" t="s">
         <v>109</v>
       </c>
-      <c r="G25" s="47" t="s">
+      <c r="G25" s="42" t="s">
         <v>110</v>
       </c>
-      <c r="H25" s="24"/>
-      <c r="I25" s="25" t="s">
+      <c r="H25" s="22"/>
+      <c r="I25" s="23" t="s">
         <v>107</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="39" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="54">
+    <row r="26" spans="1:9" s="36" customFormat="1" ht="41.45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A26" s="59">
         <v>10</v>
       </c>
-      <c r="B26" s="54" t="s">
+      <c r="B26" s="59" t="s">
         <v>111</v>
       </c>
-      <c r="C26" s="37">
+      <c r="C26" s="34">
         <v>10.1</v>
       </c>
-      <c r="D26" s="38" t="s">
+      <c r="D26" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="E26" s="38" t="s">
+      <c r="E26" s="35" t="s">
         <v>112</v>
       </c>
-      <c r="F26" s="38" t="s">
+      <c r="F26" s="35" t="s">
         <v>113</v>
       </c>
-      <c r="G26" s="48" t="s">
+      <c r="G26" s="43" t="s">
         <v>114</v>
       </c>
-      <c r="H26" s="37" t="s">
+      <c r="H26" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="I26" s="38"/>
-    </row>
-    <row r="27" spans="1:9" s="39" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I26" s="35"/>
+    </row>
+    <row r="27" spans="1:9" s="36" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A27" s="55"/>
       <c r="B27" s="55"/>
-      <c r="C27" s="37">
+      <c r="C27" s="34">
         <v>10.199999999999999</v>
       </c>
-      <c r="D27" s="38" t="s">
+      <c r="D27" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="E27" s="38" t="s">
+      <c r="E27" s="35" t="s">
         <v>116</v>
       </c>
-      <c r="F27" s="38" t="s">
+      <c r="F27" s="35" t="s">
         <v>117</v>
       </c>
-      <c r="G27" s="48" t="s">
+      <c r="G27" s="43" t="s">
         <v>118</v>
       </c>
-      <c r="H27" s="37" t="s">
+      <c r="H27" s="34" t="s">
         <v>115</v>
       </c>
-      <c r="I27" s="38"/>
-    </row>
-    <row r="28" spans="1:9" s="39" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="54">
+      <c r="I27" s="35"/>
+    </row>
+    <row r="28" spans="1:9" s="36" customFormat="1" ht="41.45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A28" s="59">
         <v>11</v>
       </c>
-      <c r="B28" s="54" t="s">
+      <c r="B28" s="59" t="s">
         <v>119</v>
       </c>
-      <c r="C28" s="37">
+      <c r="C28" s="34">
         <v>11.1</v>
       </c>
-      <c r="D28" s="38" t="s">
+      <c r="D28" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="E28" s="38" t="s">
+      <c r="E28" s="35" t="s">
         <v>120</v>
       </c>
-      <c r="F28" s="38" t="s">
+      <c r="F28" s="35" t="s">
         <v>121</v>
       </c>
-      <c r="G28" s="48" t="s">
+      <c r="G28" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="H28" s="37" t="s">
+      <c r="H28" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="I28" s="38"/>
-    </row>
-    <row r="29" spans="1:9" s="39" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="I28" s="35"/>
+    </row>
+    <row r="29" spans="1:9" s="36" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A29" s="55"/>
       <c r="B29" s="55"/>
-      <c r="C29" s="37">
+      <c r="C29" s="34">
         <v>11.2</v>
       </c>
-      <c r="D29" s="38" t="s">
+      <c r="D29" s="35" t="s">
         <v>30</v>
       </c>
-      <c r="E29" s="38" t="s">
+      <c r="E29" s="35" t="s">
         <v>124</v>
       </c>
-      <c r="F29" s="38" t="s">
+      <c r="F29" s="35" t="s">
         <v>125</v>
       </c>
-      <c r="G29" s="48" t="s">
+      <c r="G29" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="H29" s="37" t="s">
+      <c r="H29" s="34" t="s">
         <v>123</v>
       </c>
-      <c r="I29" s="38"/>
-    </row>
-    <row r="30" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="66">
+      <c r="I29" s="35"/>
+    </row>
+    <row r="30" spans="1:9" s="8" customFormat="1" ht="55.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A30" s="70">
         <v>12</v>
       </c>
-      <c r="B30" s="66" t="s">
+      <c r="B30" s="70" t="s">
         <v>127</v>
       </c>
-      <c r="C30" s="26">
+      <c r="C30" s="24">
         <v>12.1</v>
       </c>
-      <c r="D30" s="27" t="s">
+      <c r="D30" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="E30" s="27" t="s">
+      <c r="E30" s="25" t="s">
         <v>128</v>
       </c>
-      <c r="F30" s="27" t="s">
+      <c r="F30" s="25" t="s">
         <v>129</v>
       </c>
-      <c r="G30" s="49" t="s">
+      <c r="G30" s="44" t="s">
         <v>130</v>
       </c>
-      <c r="H30" s="26" t="s">
+      <c r="H30" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="I30" s="27" t="s">
+      <c r="I30" s="25" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" s="8" customFormat="1" ht="55.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A31" s="57"/>
       <c r="B31" s="57"/>
-      <c r="C31" s="26">
+      <c r="C31" s="24">
         <v>12.2</v>
       </c>
-      <c r="D31" s="27" t="s">
+      <c r="D31" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="E31" s="27" t="s">
+      <c r="E31" s="25" t="s">
         <v>133</v>
       </c>
-      <c r="F31" s="27" t="s">
+      <c r="F31" s="25" t="s">
         <v>134</v>
       </c>
-      <c r="G31" s="49" t="s">
+      <c r="G31" s="44" t="s">
         <v>135</v>
       </c>
-      <c r="H31" s="26" t="s">
+      <c r="H31" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="I31" s="27" t="s">
+      <c r="I31" s="25" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" s="8" customFormat="1" ht="55.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A32" s="55"/>
       <c r="B32" s="55"/>
-      <c r="C32" s="26">
+      <c r="C32" s="24">
         <v>12.3</v>
       </c>
-      <c r="D32" s="27" t="s">
+      <c r="D32" s="25" t="s">
         <v>30</v>
       </c>
-      <c r="E32" s="27" t="s">
+      <c r="E32" s="25" t="s">
         <v>136</v>
       </c>
-      <c r="F32" s="27" t="s">
+      <c r="F32" s="25" t="s">
         <v>137</v>
       </c>
-      <c r="G32" s="49" t="s">
+      <c r="G32" s="44" t="s">
         <v>138</v>
       </c>
-      <c r="H32" s="26" t="s">
+      <c r="H32" s="24" t="s">
         <v>131</v>
       </c>
-      <c r="I32" s="27"/>
-    </row>
-    <row r="33" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="63">
+      <c r="I32" s="25"/>
+    </row>
+    <row r="33" spans="1:9" s="8" customFormat="1" ht="55.25" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A33" s="68">
         <v>13</v>
       </c>
-      <c r="B33" s="63" t="s">
+      <c r="B33" s="68" t="s">
         <v>139</v>
       </c>
-      <c r="C33" s="28">
+      <c r="C33" s="26">
         <v>13.1</v>
       </c>
-      <c r="D33" s="29" t="s">
+      <c r="D33" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E33" s="29" t="s">
+      <c r="E33" s="27" t="s">
         <v>140</v>
       </c>
-      <c r="F33" s="29" t="s">
+      <c r="F33" s="27" t="s">
         <v>141</v>
       </c>
-      <c r="G33" s="50" t="s">
+      <c r="G33" s="45" t="s">
         <v>142</v>
       </c>
-      <c r="H33" s="28" t="s">
+      <c r="H33" s="26" t="s">
         <v>143</v>
       </c>
-      <c r="I33" s="29" t="s">
+      <c r="I33" s="27" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:9" s="8" customFormat="1" ht="41.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A34" s="57"/>
       <c r="B34" s="57"/>
-      <c r="C34" s="28">
+      <c r="C34" s="26">
         <v>13.2</v>
       </c>
-      <c r="D34" s="29" t="s">
+      <c r="D34" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E34" s="29" t="s">
+      <c r="E34" s="27" t="s">
         <v>145</v>
       </c>
-      <c r="F34" s="29" t="s">
+      <c r="F34" s="27" t="s">
         <v>146</v>
       </c>
-      <c r="G34" s="50" t="s">
+      <c r="G34" s="45" t="s">
         <v>147</v>
       </c>
-      <c r="H34" s="28" t="s">
+      <c r="H34" s="26" t="s">
         <v>143</v>
       </c>
-      <c r="I34" s="29" t="s">
+      <c r="I34" s="27" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:9" s="8" customFormat="1" ht="55.25" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A35" s="57"/>
       <c r="B35" s="57"/>
-      <c r="C35" s="28">
+      <c r="C35" s="26">
         <v>13.3</v>
       </c>
-      <c r="D35" s="29" t="s">
+      <c r="D35" s="27" t="s">
         <v>148</v>
       </c>
-      <c r="E35" s="29" t="s">
+      <c r="E35" s="27" t="s">
         <v>12</v>
       </c>
-      <c r="F35" s="29" t="s">
+      <c r="F35" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="G35" s="50" t="s">
+      <c r="G35" s="45" t="s">
         <v>14</v>
       </c>
-      <c r="H35" s="28" t="s">
+      <c r="H35" s="26" t="s">
         <v>158</v>
       </c>
-      <c r="I35" s="29" t="s">
+      <c r="I35" s="27" t="s">
         <v>149</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="8" customFormat="1" ht="60.6" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:9" s="8" customFormat="1" ht="60.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A36" s="55"/>
       <c r="B36" s="55"/>
-      <c r="C36" s="28">
+      <c r="C36" s="26">
         <v>13.4</v>
       </c>
-      <c r="D36" s="29" t="s">
+      <c r="D36" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="E36" s="29" t="s">
+      <c r="E36" s="27" t="s">
         <v>150</v>
       </c>
-      <c r="F36" s="29" t="s">
+      <c r="F36" s="27" t="s">
         <v>151</v>
       </c>
-      <c r="G36" s="50" t="s">
+      <c r="G36" s="45" t="s">
         <v>152</v>
       </c>
-      <c r="H36" s="28" t="s">
+      <c r="H36" s="26" t="s">
         <v>15</v>
       </c>
-      <c r="I36" s="29" t="s">
+      <c r="I36" s="27" t="s">
         <v>153</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:9" s="8" customFormat="1" ht="41.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A37" s="64">
         <v>14</v>
       </c>
       <c r="B37" s="64" t="s">
         <v>154</v>
       </c>
-      <c r="C37" s="30">
+      <c r="C37" s="28">
         <v>14.1</v>
       </c>
-      <c r="D37" s="31" t="s">
+      <c r="D37" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="E37" s="31" t="s">
+      <c r="E37" s="29" t="s">
         <v>155</v>
       </c>
-      <c r="F37" s="31" t="s">
+      <c r="F37" s="29" t="s">
         <v>156</v>
       </c>
-      <c r="G37" s="51" t="s">
+      <c r="G37" s="46" t="s">
         <v>157</v>
       </c>
-      <c r="H37" s="30" t="s">
+      <c r="H37" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="I37" s="31" t="s">
+      <c r="I37" s="29" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:9" s="8" customFormat="1" ht="41.45" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A38" s="55"/>
       <c r="B38" s="55"/>
-      <c r="C38" s="30">
+      <c r="C38" s="28">
         <v>14.2</v>
       </c>
-      <c r="D38" s="31" t="s">
+      <c r="D38" s="29" t="s">
         <v>30</v>
       </c>
-      <c r="E38" s="31" t="s">
+      <c r="E38" s="29" t="s">
         <v>160</v>
       </c>
-      <c r="F38" s="31" t="s">
+      <c r="F38" s="29" t="s">
         <v>161</v>
       </c>
-      <c r="G38" s="51" t="s">
+      <c r="G38" s="46" t="s">
         <v>162</v>
       </c>
-      <c r="H38" s="30" t="s">
+      <c r="H38" s="28" t="s">
         <v>223</v>
       </c>
-      <c r="I38" s="31" t="s">
+      <c r="I38" s="29" t="s">
         <v>159</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="67">
+    <row r="39" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A39" s="62">
         <v>15</v>
       </c>
-      <c r="B39" s="67" t="s">
+      <c r="B39" s="62" t="s">
         <v>163</v>
       </c>
-      <c r="C39" s="32">
+      <c r="C39" s="30">
         <v>15.1</v>
       </c>
-      <c r="D39" s="33" t="s">
+      <c r="D39" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="E39" s="33" t="s">
+      <c r="E39" s="31" t="s">
         <v>165</v>
       </c>
-      <c r="F39" s="33" t="s">
+      <c r="F39" s="31" t="s">
         <v>166</v>
       </c>
-      <c r="G39" s="52" t="s">
+      <c r="G39" s="47" t="s">
         <v>167</v>
       </c>
-      <c r="H39" s="32"/>
-      <c r="I39" s="33"/>
-    </row>
-    <row r="40" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H39" s="30"/>
+      <c r="I39" s="31"/>
+    </row>
+    <row r="40" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A40" s="57"/>
       <c r="B40" s="57"/>
-      <c r="C40" s="32">
+      <c r="C40" s="30">
         <v>15.2</v>
       </c>
-      <c r="D40" s="33" t="s">
+      <c r="D40" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="E40" s="33" t="s">
+      <c r="E40" s="31" t="s">
         <v>168</v>
       </c>
-      <c r="F40" s="33" t="s">
+      <c r="F40" s="31" t="s">
         <v>169</v>
       </c>
-      <c r="G40" s="52" t="s">
+      <c r="G40" s="47" t="s">
         <v>170</v>
       </c>
-      <c r="H40" s="32"/>
-      <c r="I40" s="33"/>
-    </row>
-    <row r="41" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H40" s="30"/>
+      <c r="I40" s="31"/>
+    </row>
+    <row r="41" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A41" s="57"/>
       <c r="B41" s="57"/>
-      <c r="C41" s="32">
+      <c r="C41" s="30">
         <v>15.3</v>
       </c>
-      <c r="D41" s="33" t="s">
+      <c r="D41" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="E41" s="33" t="s">
+      <c r="E41" s="31" t="s">
         <v>171</v>
       </c>
-      <c r="F41" s="33" t="s">
+      <c r="F41" s="31" t="s">
         <v>172</v>
       </c>
-      <c r="G41" s="52" t="s">
+      <c r="G41" s="47" t="s">
         <v>173</v>
       </c>
-      <c r="H41" s="32"/>
-      <c r="I41" s="33"/>
-    </row>
-    <row r="42" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="H41" s="30"/>
+      <c r="I41" s="31"/>
+    </row>
+    <row r="42" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A42" s="57"/>
       <c r="B42" s="57"/>
-      <c r="C42" s="32">
+      <c r="C42" s="30">
         <v>15.4</v>
       </c>
-      <c r="D42" s="33" t="s">
+      <c r="D42" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="E42" s="33" t="s">
+      <c r="E42" s="31" t="s">
         <v>174</v>
       </c>
-      <c r="F42" s="33" t="s">
+      <c r="F42" s="31" t="s">
         <v>175</v>
       </c>
-      <c r="G42" s="52" t="s">
+      <c r="G42" s="47" t="s">
         <v>176</v>
       </c>
-      <c r="H42" s="32"/>
-      <c r="I42" s="33"/>
-    </row>
-    <row r="43" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H42" s="30"/>
+      <c r="I42" s="31"/>
+    </row>
+    <row r="43" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A43" s="55"/>
       <c r="B43" s="55"/>
-      <c r="C43" s="32">
+      <c r="C43" s="30">
         <v>15.5</v>
       </c>
-      <c r="D43" s="33" t="s">
+      <c r="D43" s="31" t="s">
         <v>164</v>
       </c>
-      <c r="E43" s="33" t="s">
+      <c r="E43" s="31" t="s">
         <v>177</v>
       </c>
-      <c r="F43" s="33" t="s">
+      <c r="F43" s="31" t="s">
         <v>178</v>
       </c>
-      <c r="G43" s="52" t="s">
+      <c r="G43" s="47" t="s">
         <v>179</v>
       </c>
-      <c r="H43" s="32"/>
-      <c r="I43" s="33"/>
-    </row>
-    <row r="44" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A44" s="65">
+      <c r="H43" s="30"/>
+      <c r="I43" s="31"/>
+    </row>
+    <row r="44" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A44" s="54">
         <v>16</v>
       </c>
-      <c r="B44" s="65" t="s">
+      <c r="B44" s="54" t="s">
         <v>180</v>
       </c>
-      <c r="C44" s="34">
+      <c r="C44" s="32">
         <v>16.100000000000001</v>
       </c>
-      <c r="D44" s="35" t="s">
+      <c r="D44" s="33" t="s">
         <v>181</v>
       </c>
-      <c r="E44" s="35" t="s">
+      <c r="E44" s="33" t="s">
         <v>182</v>
       </c>
-      <c r="F44" s="35" t="s">
+      <c r="F44" s="33" t="s">
         <v>183</v>
       </c>
-      <c r="G44" s="53" t="s">
+      <c r="G44" s="48" t="s">
         <v>184</v>
       </c>
-      <c r="H44" s="34"/>
-      <c r="I44" s="35"/>
-    </row>
-    <row r="45" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="H44" s="32"/>
+      <c r="I44" s="33"/>
+    </row>
+    <row r="45" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A45" s="55"/>
       <c r="B45" s="55"/>
-      <c r="C45" s="34">
+      <c r="C45" s="32">
         <v>16.2</v>
       </c>
-      <c r="D45" s="35" t="s">
+      <c r="D45" s="33" t="s">
         <v>185</v>
       </c>
-      <c r="E45" s="35" t="s">
+      <c r="E45" s="33" t="s">
         <v>186</v>
       </c>
-      <c r="F45" s="35" t="s">
+      <c r="F45" s="33" t="s">
         <v>187</v>
       </c>
-      <c r="G45" s="53" t="s">
+      <c r="G45" s="48" t="s">
         <v>188</v>
       </c>
-      <c r="H45" s="34"/>
-      <c r="I45" s="35"/>
-    </row>
-    <row r="46" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="59">
+      <c r="H45" s="32"/>
+      <c r="I45" s="33"/>
+    </row>
+    <row r="46" spans="1:9" s="8" customFormat="1" ht="41.45" customHeight="1" x14ac:dyDescent="0.45">
+      <c r="A46" s="60">
         <v>17</v>
       </c>
-      <c r="B46" s="59" t="s">
+      <c r="B46" s="60" t="s">
         <v>189</v>
       </c>
-      <c r="C46" s="15">
+      <c r="C46" s="13">
         <v>17.100000000000001</v>
       </c>
-      <c r="D46" s="16" t="s">
+      <c r="D46" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="E46" s="16" t="s">
+      <c r="E46" s="14" t="s">
         <v>191</v>
       </c>
-      <c r="F46" s="16" t="s">
+      <c r="F46" s="14" t="s">
         <v>192</v>
       </c>
-      <c r="G46" s="44" t="s">
+      <c r="G46" s="39" t="s">
         <v>193</v>
       </c>
-      <c r="H46" s="15"/>
-      <c r="I46" s="16" t="s">
+      <c r="H46" s="13"/>
+      <c r="I46" s="14" t="s">
         <v>194</v>
       </c>
     </row>
-    <row r="47" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:9" s="8" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A47" s="57"/>
       <c r="B47" s="57"/>
-      <c r="C47" s="15">
+      <c r="C47" s="13">
         <v>17.2</v>
       </c>
-      <c r="D47" s="16" t="s">
+      <c r="D47" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="E47" s="16" t="s">
+      <c r="E47" s="14" t="s">
         <v>195</v>
       </c>
-      <c r="F47" s="16" t="s">
+      <c r="F47" s="14" t="s">
         <v>196</v>
       </c>
-      <c r="G47" s="44" t="s">
+      <c r="G47" s="39" t="s">
         <v>197</v>
       </c>
-      <c r="H47" s="15"/>
-      <c r="I47" s="16"/>
-    </row>
-    <row r="48" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H47" s="13"/>
+      <c r="I47" s="14"/>
+    </row>
+    <row r="48" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A48" s="57"/>
       <c r="B48" s="57"/>
-      <c r="C48" s="15">
+      <c r="C48" s="13">
         <v>17.3</v>
       </c>
-      <c r="D48" s="16" t="s">
+      <c r="D48" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="E48" s="16" t="s">
+      <c r="E48" s="14" t="s">
         <v>198</v>
       </c>
-      <c r="F48" s="16" t="s">
+      <c r="F48" s="14" t="s">
         <v>199</v>
       </c>
-      <c r="G48" s="44" t="s">
+      <c r="G48" s="39" t="s">
         <v>200</v>
       </c>
-      <c r="H48" s="15"/>
-      <c r="I48" s="16"/>
-    </row>
-    <row r="49" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="H48" s="13"/>
+      <c r="I48" s="14"/>
+    </row>
+    <row r="49" spans="1:9" s="8" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A49" s="57"/>
       <c r="B49" s="57"/>
-      <c r="C49" s="15">
+      <c r="C49" s="13">
         <v>17.399999999999999</v>
       </c>
-      <c r="D49" s="16" t="s">
+      <c r="D49" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="E49" s="16" t="s">
+      <c r="E49" s="14" t="s">
         <v>201</v>
       </c>
-      <c r="F49" s="16" t="s">
+      <c r="F49" s="14" t="s">
         <v>202</v>
       </c>
-      <c r="G49" s="44" t="s">
+      <c r="G49" s="39" t="s">
         <v>203</v>
       </c>
-      <c r="H49" s="15"/>
-      <c r="I49" s="16"/>
-    </row>
-    <row r="50" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="H49" s="13"/>
+      <c r="I49" s="14"/>
+    </row>
+    <row r="50" spans="1:9" s="8" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A50" s="57"/>
       <c r="B50" s="57"/>
-      <c r="C50" s="15">
+      <c r="C50" s="13">
         <v>17.5</v>
       </c>
-      <c r="D50" s="16" t="s">
+      <c r="D50" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="E50" s="16" t="s">
+      <c r="E50" s="14" t="s">
         <v>204</v>
       </c>
-      <c r="F50" s="16" t="s">
+      <c r="F50" s="14" t="s">
         <v>205</v>
       </c>
-      <c r="G50" s="44" t="s">
+      <c r="G50" s="39" t="s">
         <v>206</v>
       </c>
-      <c r="H50" s="15"/>
-      <c r="I50" s="16"/>
-    </row>
-    <row r="51" spans="1:9" s="8" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="H50" s="13"/>
+      <c r="I50" s="14"/>
+    </row>
+    <row r="51" spans="1:9" s="8" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.45">
       <c r="A51" s="57"/>
       <c r="B51" s="57"/>
-      <c r="C51" s="15">
+      <c r="C51" s="13">
         <v>17.600000000000001</v>
       </c>
-      <c r="D51" s="16" t="s">
+      <c r="D51" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="E51" s="16" t="s">
+      <c r="E51" s="14" t="s">
         <v>207</v>
       </c>
-      <c r="F51" s="16" t="s">
+      <c r="F51" s="14" t="s">
         <v>208</v>
       </c>
-      <c r="G51" s="44" t="s">
+      <c r="G51" s="39" t="s">
         <v>209</v>
       </c>
-      <c r="H51" s="15"/>
-      <c r="I51" s="16"/>
-    </row>
-    <row r="52" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="H51" s="13"/>
+      <c r="I51" s="14"/>
+    </row>
+    <row r="52" spans="1:9" s="8" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A52" s="57"/>
       <c r="B52" s="57"/>
-      <c r="C52" s="15">
+      <c r="C52" s="13">
         <v>17.7</v>
       </c>
-      <c r="D52" s="16" t="s">
+      <c r="D52" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="E52" s="16" t="s">
+      <c r="E52" s="14" t="s">
         <v>210</v>
       </c>
-      <c r="F52" s="16" t="s">
+      <c r="F52" s="14" t="s">
         <v>211</v>
       </c>
-      <c r="G52" s="44" t="s">
+      <c r="G52" s="39" t="s">
         <v>212</v>
       </c>
-      <c r="H52" s="15"/>
-      <c r="I52" s="16"/>
-    </row>
-    <row r="53" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="H52" s="13"/>
+      <c r="I52" s="14"/>
+    </row>
+    <row r="53" spans="1:9" s="8" customFormat="1" ht="26.25" x14ac:dyDescent="0.45">
       <c r="A53" s="55"/>
       <c r="B53" s="55"/>
-      <c r="C53" s="15">
+      <c r="C53" s="13">
         <v>17.8</v>
       </c>
-      <c r="D53" s="16" t="s">
+      <c r="D53" s="14" t="s">
         <v>190</v>
       </c>
-      <c r="E53" s="16" t="s">
+      <c r="E53" s="14" t="s">
         <v>213</v>
       </c>
-      <c r="F53" s="16" t="s">
+      <c r="F53" s="14" t="s">
         <v>214</v>
       </c>
-      <c r="G53" s="44" t="s">
+      <c r="G53" s="39" t="s">
         <v>215</v>
       </c>
-      <c r="H53" s="15"/>
-      <c r="I53" s="16"/>
-    </row>
-    <row r="54" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="H53" s="13"/>
+      <c r="I53" s="14"/>
+    </row>
+    <row r="54" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A54" s="2"/>
       <c r="B54" s="3"/>
       <c r="C54" s="3"/>
@@ -2839,7 +3010,7 @@
       <c r="H54" s="6"/>
       <c r="I54" s="3"/>
     </row>
-    <row r="55" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.45">
       <c r="A55" s="7"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
@@ -2850,21 +3021,40 @@
       <c r="H55" s="2"/>
       <c r="I55" s="3"/>
     </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A56" s="7"/>
     </row>
-    <row r="57" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A57" s="7"/>
     </row>
-    <row r="58" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A58" s="7"/>
     </row>
-    <row r="59" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:9" x14ac:dyDescent="0.45">
       <c r="A59" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="I1:I33" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="I1:I33"/>
   <mergeCells count="35">
+    <mergeCell ref="B46:B53"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="B28:B29"/>
+    <mergeCell ref="A33:A36"/>
+    <mergeCell ref="B37:B38"/>
+    <mergeCell ref="B44:B45"/>
+    <mergeCell ref="A30:A32"/>
+    <mergeCell ref="A39:A43"/>
+    <mergeCell ref="A46:A53"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B7:B12"/>
+    <mergeCell ref="B30:B32"/>
+    <mergeCell ref="B4:B6"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="B33:B36"/>
+    <mergeCell ref="A26:A27"/>
+    <mergeCell ref="A7:A12"/>
+    <mergeCell ref="A19:A21"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="A44:A45"/>
@@ -2881,28 +3071,10 @@
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="A13:A15"/>
     <mergeCell ref="A4:A6"/>
-    <mergeCell ref="B4:B6"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="B33:B36"/>
-    <mergeCell ref="A26:A27"/>
-    <mergeCell ref="A7:A12"/>
-    <mergeCell ref="A19:A21"/>
-    <mergeCell ref="B46:B53"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="B16:B18"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="A33:A36"/>
-    <mergeCell ref="B37:B38"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="A30:A32"/>
-    <mergeCell ref="A39:A43"/>
-    <mergeCell ref="A46:A53"/>
-    <mergeCell ref="B22:B25"/>
-    <mergeCell ref="B7:B12"/>
-    <mergeCell ref="B30:B32"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup orientation="portrait"/>
+  <pageSetup orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
--- a/Soubhanik/checkupp_product_backlog_final.xlsx
+++ b/Soubhanik/checkupp_product_backlog_final.xlsx
@@ -5,18 +5,18 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anodiam\2026\CheckUpp_Parent\CheckUpp\Soubhanik\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Soubhanik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6C006A76-8F12-41AA-88E8-916CA6962C66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{358008D2-FFA6-4719-BE17-0CA60866B10F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$I$1:$I$33</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$I$1:$I$28</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -105,7 +105,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="277" uniqueCount="219">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="241" uniqueCount="192">
   <si>
     <t>Epic #</t>
   </si>
@@ -153,17 +153,6 @@
   </si>
   <si>
     <t>Discussion #12 – SOUBHANIK</t>
-  </si>
-  <si>
-    <t>tap a Quick Actions option (Cancer screenings, Health checkups, Immunization Checkups)</t>
-  </si>
-  <si>
-    <t>I can see my appointment date, time, clinic name, address and doctor for the same</t>
-  </si>
-  <si>
-    <t>1. Tapping must open the detail view
-2. App must clearly display appointment date and time, clinic name, clinic address, and doctor name
-3. Back navigation must return to the Health Overview screen</t>
   </si>
   <si>
     <t>Cancer Screenings</t>
@@ -311,16 +300,6 @@
     <t>Document Wallet</t>
   </si>
   <si>
-    <t>store health documents locally or in a cloud service I choose</t>
-  </si>
-  <si>
-    <t>my records are accessible securely anywhere</t>
-  </si>
-  <si>
-    <t>1. Option to save locally or to cloud (Google Drive, iCloud) must be available
-2. Uploaded document must be visible in wallet</t>
-  </si>
-  <si>
     <t>Discussion #10 – NATHAN</t>
   </si>
   <si>
@@ -328,10 +307,6 @@
   </si>
   <si>
     <t>my sensitive documents are protected and accessible</t>
-  </si>
-  <si>
-    <t>1. Document categories must include insurance, Medicare, and identity
-2. Documents must be stored with encryption</t>
   </si>
   <si>
     <t>Discussion #10, #17 – NATHAN</t>
@@ -444,60 +419,6 @@
 3. Booking confirmation must be displayed on success</t>
   </si>
   <si>
-    <t>Vision Check</t>
-  </si>
-  <si>
-    <t>log my vision check results</t>
-  </si>
-  <si>
-    <t>I can track changes in my eyesight over time</t>
-  </si>
-  <si>
-    <t>1. Vision check entry screen must have relevant measurement fields
-2. Results must be saved with date
-3. Screen must be accessible from the Health Checks Hub</t>
-  </si>
-  <si>
-    <t>Slide 17</t>
-  </si>
-  <si>
-    <t>view my vision check history</t>
-  </si>
-  <si>
-    <t>I can monitor changes in my eyesight across visits</t>
-  </si>
-  <si>
-    <t>1. Past vision check entries must be listed in chronological order
-2. Each entry must show date and key measurements</t>
-  </si>
-  <si>
-    <t>Dental Health Check</t>
-  </si>
-  <si>
-    <t>log my dental health check results</t>
-  </si>
-  <si>
-    <t>I maintain a digital record of my oral health</t>
-  </si>
-  <si>
-    <t>1. Dental health check entry screen must have relevant fields
-2. Results must be saved with date
-3. Screen must be accessible from the Health Checks Hub</t>
-  </si>
-  <si>
-    <t>Slide 18</t>
-  </si>
-  <si>
-    <t>view my dental health check history</t>
-  </si>
-  <si>
-    <t>I can track my oral health over time</t>
-  </si>
-  <si>
-    <t>1. Past dental check entries must be listed in chronological order
-2. Each entry must show date and recorded findings</t>
-  </si>
-  <si>
     <t>Mental Health Check</t>
   </si>
   <si>
@@ -544,9 +465,6 @@
     <t>Slide 20</t>
   </si>
   <si>
-    <t>Discussion #1 – SOUBHANIK</t>
-  </si>
-  <si>
     <t>Screenings Schedule</t>
   </si>
   <si>
@@ -686,9 +604,6 @@
     <t>Slide 1</t>
   </si>
   <si>
-    <t>Slide 2,3,4</t>
-  </si>
-  <si>
     <t>Slide 8-11</t>
   </si>
   <si>
@@ -702,24 +617,6 @@
   </si>
   <si>
     <t>Slide 24</t>
-  </si>
-  <si>
-    <t>Cardiovascular Health Check</t>
-  </si>
-  <si>
-    <t>capture a photo of my cardiovascular health screening result (digital sphygmomanometer) and have the reading data filled by the system in the respective fields (Systolic, Diastolic, Heart Rate)</t>
-  </si>
-  <si>
-    <t>I don't have to manually enter the data</t>
-  </si>
-  <si>
-    <t>1. Tapping the 'Tap to Upload' button in Cardiovascular Reading screen should open the camera
-2. Data must be extracted from the image captured by the user
-3. System must pre-fill the fields (Systolic, Diastolic, Heart Rate) with the extracted data
-4. User must be able to edit the data filled by the system</t>
-  </si>
-  <si>
-    <t>logged in user navigating Cardiovascular Reading screen</t>
   </si>
   <si>
     <t>have the data I enter in any health screening section (eg. Cardiovascular Health, Diabetes Check, Mental Health Check, etc) autosaved in the system if I move away from that screen or close the app</t>
@@ -730,9 +627,6 @@
   <si>
     <t>1. User must be able to see the previously entered data upon revisiting the screen (e.g. Cardiovascular Reading)
 2. User must be notified with a toast (or similar) that previously saved data was restored.</t>
-  </si>
-  <si>
-    <t>Quick Actions</t>
   </si>
   <si>
     <t xml:space="preserve">tap Your Health Overview section </t>
@@ -798,9 +692,6 @@
     <t>my information is saved in the system</t>
   </si>
   <si>
-    <t>1. Custom ailment must be saved and appear in Health Check History.</t>
-  </si>
-  <si>
     <t>Discussion #4 – TANVI</t>
   </si>
   <si>
@@ -816,23 +707,40 @@
     <t>I don't have to manually enter the report data</t>
   </si>
   <si>
-    <t>1. Tapping the 'Tap to Upload' button in any reading screen (e.g. Cardiovascular Health) should open the camera 
+    <t>Discussion #2, #3 – SOUBHANIK</t>
+  </si>
+  <si>
+    <t>1. Custom ailment must be saved and must appear in Health Check History.</t>
+  </si>
+  <si>
+    <t>1. Tapping the 'Tap to Upload' button in any reading screen (e.g. CardiovascularReading) should open the camera 
 2. Data must be extracted from the image captured by the user
 3. System must pre-fill the fields (e.g. Systolic, Diastolic, Heart Rate) with the extracted data
 4. User must be able to edit the data filled by the system</t>
   </si>
   <si>
-    <t>Discussion #3, #7 – SOUBHANIK</t>
-  </si>
-  <si>
-    <t>Discussion #2, #3 – SOUBHANIK</t>
+    <t>Discussion #1, #3, #7 – SOUBHANIK</t>
+  </si>
+  <si>
+    <t>store health documents locally or in a cloud service of my choice</t>
+  </si>
+  <si>
+    <t>I can access them in app or locally</t>
+  </si>
+  <si>
+    <t>1. Option to save locally or to cloud of my choice (Google Drive, iCloud) must be available
+2. Uploaded document must be visible in the Document Wallet</t>
+  </si>
+  <si>
+    <t>1. Document categories must include insurance, Medicare, and identity
+2. Documents must be stored with encryption (in cloud)</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="14" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -885,12 +793,6 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
@@ -906,13 +808,6 @@
     <font>
       <b/>
       <sz val="10"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -923,14 +818,19 @@
     </font>
     <font>
       <b/>
-      <sz val="11"/>
+      <sz val="10"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -1008,12 +908,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFE6F5FF"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFF0000"/>
-        <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
@@ -1140,7 +1034,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="78">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1214,9 +1108,6 @@
     <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1235,151 +1126,139 @@
     <xf numFmtId="0" fontId="5" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="5" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="17" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1663,7 +1542,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I56"/>
+  <dimension ref="A1:I50"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.88671875" style="2" bestFit="1" customWidth="1"/>
@@ -1680,34 +1559,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="69" t="s">
+      <c r="A1" s="63" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="54" t="s">
+      <c r="B1" s="51" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="54" t="s">
+      <c r="C1" s="51" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="54" t="s">
+      <c r="D1" s="51" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="67"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="64" t="s">
+      <c r="E1" s="53"/>
+      <c r="F1" s="54"/>
+      <c r="G1" s="65" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="54" t="s">
+      <c r="H1" s="51" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="54" t="s">
+      <c r="I1" s="51" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="53"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
+      <c r="A2" s="56"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
       <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1717,1270 +1596,1110 @@
       <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="65"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
+      <c r="G2" s="66"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
     </row>
     <row r="3" spans="1:9" s="8" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="70">
+      <c r="A3" s="42">
         <v>13</v>
       </c>
-      <c r="B3" s="70" t="s">
-        <v>212</v>
+      <c r="B3" s="42" t="s">
+        <v>180</v>
       </c>
       <c r="C3" s="24">
         <v>13.2</v>
       </c>
-      <c r="D3" s="71" t="s">
-        <v>213</v>
-      </c>
-      <c r="E3" s="71" t="s">
-        <v>214</v>
-      </c>
-      <c r="F3" s="71" t="s">
-        <v>215</v>
-      </c>
-      <c r="G3" s="72" t="s">
-        <v>216</v>
+      <c r="D3" s="43" t="s">
+        <v>181</v>
+      </c>
+      <c r="E3" s="43" t="s">
+        <v>182</v>
+      </c>
+      <c r="F3" s="43" t="s">
+        <v>183</v>
+      </c>
+      <c r="G3" s="44" t="s">
+        <v>186</v>
       </c>
       <c r="H3" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="I3" s="71" t="s">
-        <v>217</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" s="50" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="47">
+        <v>106</v>
+      </c>
+      <c r="I3" s="43" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="75" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="71">
         <v>1</v>
       </c>
-      <c r="B4" s="47" t="s">
+      <c r="B4" s="71" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="48">
+      <c r="C4" s="72">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D4" s="46" t="s">
+      <c r="D4" s="73" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="46" t="s">
-        <v>187</v>
-      </c>
-      <c r="F4" s="46" t="s">
+      <c r="E4" s="73" t="s">
+        <v>157</v>
+      </c>
+      <c r="F4" s="73" t="s">
+        <v>158</v>
+      </c>
+      <c r="G4" s="74" t="s">
+        <v>159</v>
+      </c>
+      <c r="H4" s="72" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="73" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="41" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="68">
+        <v>3</v>
+      </c>
+      <c r="B5" s="68" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="40">
+        <v>3.1</v>
+      </c>
+      <c r="D5" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="46" t="s">
+        <v>160</v>
+      </c>
+      <c r="F5" s="46" t="s">
+        <v>161</v>
+      </c>
+      <c r="G5" s="47" t="s">
+        <v>164</v>
+      </c>
+      <c r="H5" s="48" t="s">
+        <v>151</v>
+      </c>
+      <c r="I5" s="45" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" s="8" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="69"/>
+      <c r="B6" s="69"/>
+      <c r="C6" s="40">
+        <v>3.2</v>
+      </c>
+      <c r="D6" s="45" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="46" t="s">
+        <v>162</v>
+      </c>
+      <c r="F6" s="46" t="s">
+        <v>163</v>
+      </c>
+      <c r="G6" s="47" t="s">
+        <v>165</v>
+      </c>
+      <c r="H6" s="40" t="s">
+        <v>151</v>
+      </c>
+      <c r="I6" s="45" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="67">
+        <v>4</v>
+      </c>
+      <c r="B7" s="67" t="s">
+        <v>16</v>
+      </c>
+      <c r="C7" s="9">
+        <v>4.0999999999999996</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>18</v>
+      </c>
+      <c r="F7" s="10" t="s">
+        <v>19</v>
+      </c>
+      <c r="G7" s="31" t="s">
+        <v>20</v>
+      </c>
+      <c r="H7" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="I7" s="10" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="58"/>
+      <c r="B8" s="58"/>
+      <c r="C8" s="9">
+        <v>4.2</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E8" s="10" t="s">
+        <v>23</v>
+      </c>
+      <c r="F8" s="10" t="s">
+        <v>24</v>
+      </c>
+      <c r="G8" s="31" t="s">
+        <v>25</v>
+      </c>
+      <c r="H8" s="9" t="s">
+        <v>150</v>
+      </c>
+      <c r="I8" s="10"/>
+    </row>
+    <row r="9" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="58"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="9">
+        <v>4.3</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>26</v>
+      </c>
+      <c r="E9" s="10" t="s">
+        <v>27</v>
+      </c>
+      <c r="F9" s="10" t="s">
+        <v>28</v>
+      </c>
+      <c r="G9" s="31" t="s">
+        <v>29</v>
+      </c>
+      <c r="H9" s="9" t="s">
+        <v>14</v>
+      </c>
+      <c r="I9" s="10" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="58"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="9">
+        <v>4.4000000000000004</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>32</v>
+      </c>
+      <c r="E10" s="10" t="s">
+        <v>33</v>
+      </c>
+      <c r="F10" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="G10" s="31" t="s">
+        <v>35</v>
+      </c>
+      <c r="H10" s="9" t="s">
+        <v>21</v>
+      </c>
+      <c r="I10" s="10" t="s">
+        <v>36</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A11" s="58"/>
+      <c r="B11" s="58"/>
+      <c r="C11" s="40">
+        <v>4.5</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>37</v>
+      </c>
+      <c r="E11" s="10" t="s">
+        <v>38</v>
+      </c>
+      <c r="F11" s="10" t="s">
+        <v>39</v>
+      </c>
+      <c r="G11" s="31" t="s">
+        <v>40</v>
+      </c>
+      <c r="H11" s="9" t="s">
+        <v>41</v>
+      </c>
+      <c r="I11" s="10"/>
+    </row>
+    <row r="12" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A12" s="56"/>
+      <c r="B12" s="56"/>
+      <c r="C12" s="40">
+        <v>4.5999999999999996</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>17</v>
+      </c>
+      <c r="E12" s="10" t="s">
+        <v>42</v>
+      </c>
+      <c r="F12" s="10" t="s">
+        <v>43</v>
+      </c>
+      <c r="G12" s="31" t="s">
+        <v>44</v>
+      </c>
+      <c r="H12" s="9" t="s">
+        <v>30</v>
+      </c>
+      <c r="I12" s="10"/>
+    </row>
+    <row r="13" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A13" s="60">
+        <v>5</v>
+      </c>
+      <c r="B13" s="60" t="s">
+        <v>45</v>
+      </c>
+      <c r="C13" s="11">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>46</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>47</v>
+      </c>
+      <c r="G13" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="H13" s="13" t="s">
+        <v>49</v>
+      </c>
+      <c r="I13" s="12" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="8" customFormat="1" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="58"/>
+      <c r="B14" s="58"/>
+      <c r="C14" s="11">
+        <v>5.2</v>
+      </c>
+      <c r="D14" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E14" s="12" t="s">
+        <v>51</v>
+      </c>
+      <c r="F14" s="12" t="s">
+        <v>52</v>
+      </c>
+      <c r="G14" s="32" t="s">
+        <v>53</v>
+      </c>
+      <c r="H14" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="I14" s="12" t="s">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="15" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="56"/>
+      <c r="B15" s="56"/>
+      <c r="C15" s="11">
+        <v>5.3</v>
+      </c>
+      <c r="D15" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="E15" s="12" t="s">
+        <v>55</v>
+      </c>
+      <c r="F15" s="12" t="s">
+        <v>56</v>
+      </c>
+      <c r="G15" s="32" t="s">
+        <v>57</v>
+      </c>
+      <c r="H15" s="13" t="s">
+        <v>152</v>
+      </c>
+      <c r="I15" s="12"/>
+    </row>
+    <row r="16" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="59">
+        <v>6</v>
+      </c>
+      <c r="B16" s="59" t="s">
+        <v>58</v>
+      </c>
+      <c r="C16" s="14">
+        <v>6.1</v>
+      </c>
+      <c r="D16" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E16" s="76" t="s">
         <v>188</v>
       </c>
-      <c r="G4" s="49" t="s">
+      <c r="F16" s="76" t="s">
         <v>189</v>
       </c>
-      <c r="H4" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="46" t="s">
-        <v>218</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A5" s="34"/>
-      <c r="B5" s="76" t="s">
+      <c r="G16" s="77" t="s">
         <v>190</v>
       </c>
-      <c r="C5" s="32">
-        <v>3.2</v>
-      </c>
-      <c r="D5" s="33" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="75" t="s">
-        <v>16</v>
-      </c>
-      <c r="F5" s="33" t="s">
+      <c r="H16" s="16" t="s">
+        <v>153</v>
+      </c>
+      <c r="I16" s="15" t="s">
+        <v>59</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="58"/>
+      <c r="B17" s="58"/>
+      <c r="C17" s="14">
+        <v>6.2</v>
+      </c>
+      <c r="D17" s="15" t="s">
         <v>17</v>
       </c>
-      <c r="G5" s="40" t="s">
-        <v>18</v>
-      </c>
-      <c r="H5" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="I5" s="33" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="6" spans="1:9" s="50" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="77">
-        <v>3</v>
-      </c>
-      <c r="B6" s="77" t="s">
-        <v>13</v>
-      </c>
-      <c r="C6" s="45">
-        <v>3.1</v>
-      </c>
-      <c r="D6" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="74" t="s">
+      <c r="E17" s="15" t="s">
+        <v>60</v>
+      </c>
+      <c r="F17" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="G17" s="77" t="s">
         <v>191</v>
       </c>
-      <c r="F6" s="74" t="s">
-        <v>192</v>
-      </c>
-      <c r="G6" s="78" t="s">
-        <v>195</v>
-      </c>
-      <c r="H6" s="79" t="s">
-        <v>175</v>
-      </c>
-      <c r="I6" s="73" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" s="8" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="80"/>
-      <c r="B7" s="80"/>
-      <c r="C7" s="45">
-        <v>3.2</v>
-      </c>
-      <c r="D7" s="73" t="s">
-        <v>11</v>
-      </c>
-      <c r="E7" s="74" t="s">
-        <v>193</v>
-      </c>
-      <c r="F7" s="74" t="s">
-        <v>194</v>
-      </c>
-      <c r="G7" s="78" t="s">
-        <v>196</v>
-      </c>
-      <c r="H7" s="45" t="s">
-        <v>175</v>
-      </c>
-      <c r="I7" s="73" t="s">
-        <v>15</v>
-      </c>
-    </row>
-    <row r="8" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="63">
-        <v>4</v>
-      </c>
-      <c r="B8" s="63" t="s">
-        <v>19</v>
-      </c>
-      <c r="C8" s="9">
-        <v>4.0999999999999996</v>
-      </c>
-      <c r="D8" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E8" s="10" t="s">
-        <v>21</v>
-      </c>
-      <c r="F8" s="10" t="s">
-        <v>22</v>
-      </c>
-      <c r="G8" s="35" t="s">
-        <v>23</v>
-      </c>
-      <c r="H8" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="I8" s="10" t="s">
-        <v>25</v>
-      </c>
-    </row>
-    <row r="9" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="52"/>
-      <c r="B9" s="52"/>
-      <c r="C9" s="9">
-        <v>4.2</v>
-      </c>
-      <c r="D9" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E9" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="F9" s="10" t="s">
-        <v>27</v>
-      </c>
-      <c r="G9" s="35" t="s">
-        <v>28</v>
-      </c>
-      <c r="H9" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="I9" s="10"/>
-    </row>
-    <row r="10" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="52"/>
-      <c r="B10" s="52"/>
-      <c r="C10" s="9">
-        <v>4.3</v>
-      </c>
-      <c r="D10" s="10" t="s">
-        <v>29</v>
-      </c>
-      <c r="E10" s="10" t="s">
-        <v>30</v>
-      </c>
-      <c r="F10" s="10" t="s">
-        <v>31</v>
-      </c>
-      <c r="G10" s="35" t="s">
-        <v>32</v>
-      </c>
-      <c r="H10" s="9" t="s">
-        <v>14</v>
-      </c>
-      <c r="I10" s="10" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="11" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="52"/>
-      <c r="B11" s="52"/>
-      <c r="C11" s="9">
-        <v>4.4000000000000004</v>
-      </c>
-      <c r="D11" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="E11" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="F11" s="10" t="s">
-        <v>37</v>
-      </c>
-      <c r="G11" s="35" t="s">
-        <v>38</v>
-      </c>
-      <c r="H11" s="9" t="s">
-        <v>24</v>
-      </c>
-      <c r="I11" s="10" t="s">
-        <v>39</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="52"/>
-      <c r="B12" s="52"/>
-      <c r="C12" s="45">
-        <v>4.5</v>
-      </c>
-      <c r="D12" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="E12" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="F12" s="10" t="s">
-        <v>42</v>
-      </c>
-      <c r="G12" s="35" t="s">
-        <v>43</v>
-      </c>
-      <c r="H12" s="9" t="s">
-        <v>44</v>
-      </c>
-      <c r="I12" s="10"/>
-    </row>
-    <row r="13" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="53"/>
-      <c r="B13" s="53"/>
-      <c r="C13" s="45">
-        <v>4.5999999999999996</v>
-      </c>
-      <c r="D13" s="10" t="s">
-        <v>20</v>
-      </c>
-      <c r="E13" s="10" t="s">
-        <v>45</v>
-      </c>
-      <c r="F13" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G13" s="35" t="s">
-        <v>47</v>
-      </c>
-      <c r="H13" s="9" t="s">
-        <v>33</v>
-      </c>
-      <c r="I13" s="10"/>
-    </row>
-    <row r="14" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="51">
-        <v>5</v>
-      </c>
-      <c r="B14" s="51" t="s">
-        <v>48</v>
-      </c>
-      <c r="C14" s="11">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="D14" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E14" s="12" t="s">
-        <v>49</v>
-      </c>
-      <c r="F14" s="12" t="s">
-        <v>50</v>
-      </c>
-      <c r="G14" s="36" t="s">
-        <v>51</v>
-      </c>
-      <c r="H14" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="I14" s="12" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="15" spans="1:9" s="8" customFormat="1" ht="96.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="52"/>
-      <c r="B15" s="52"/>
-      <c r="C15" s="11">
-        <v>5.2</v>
-      </c>
-      <c r="D15" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E15" s="12" t="s">
-        <v>54</v>
-      </c>
-      <c r="F15" s="12" t="s">
-        <v>55</v>
-      </c>
-      <c r="G15" s="36" t="s">
-        <v>56</v>
-      </c>
-      <c r="H15" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="I15" s="12" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="16" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="53"/>
-      <c r="B16" s="53"/>
-      <c r="C16" s="11">
-        <v>5.3</v>
-      </c>
-      <c r="D16" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="E16" s="12" t="s">
-        <v>58</v>
-      </c>
-      <c r="F16" s="12" t="s">
-        <v>59</v>
-      </c>
-      <c r="G16" s="36" t="s">
-        <v>60</v>
-      </c>
-      <c r="H16" s="13" t="s">
-        <v>177</v>
-      </c>
-      <c r="I16" s="12"/>
-    </row>
-    <row r="17" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="56">
-        <v>6</v>
-      </c>
-      <c r="B17" s="56" t="s">
-        <v>61</v>
-      </c>
-      <c r="C17" s="14">
-        <v>6.1</v>
-      </c>
-      <c r="D17" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E17" s="15" t="s">
+      <c r="H17" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="I17" s="15" t="s">
         <v>62</v>
       </c>
-      <c r="F17" s="15" t="s">
+    </row>
+    <row r="18" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="56"/>
+      <c r="B18" s="56"/>
+      <c r="C18" s="14">
+        <v>6.3</v>
+      </c>
+      <c r="D18" s="15" t="s">
+        <v>17</v>
+      </c>
+      <c r="E18" s="15" t="s">
         <v>63</v>
       </c>
-      <c r="G17" s="37" t="s">
+      <c r="F18" s="15" t="s">
         <v>64</v>
       </c>
-      <c r="H17" s="16" t="s">
-        <v>178</v>
-      </c>
-      <c r="I17" s="15" t="s">
+      <c r="G18" s="33" t="s">
         <v>65</v>
       </c>
-    </row>
-    <row r="18" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="52"/>
-      <c r="B18" s="52"/>
-      <c r="C18" s="14">
-        <v>6.2</v>
-      </c>
-      <c r="D18" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E18" s="15" t="s">
+      <c r="H18" s="14" t="s">
+        <v>153</v>
+      </c>
+      <c r="I18" s="15"/>
+    </row>
+    <row r="19" spans="1:9" s="8" customFormat="1" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="61">
+        <v>7</v>
+      </c>
+      <c r="B19" s="61" t="s">
         <v>66</v>
       </c>
-      <c r="F18" s="15" t="s">
+      <c r="C19" s="17">
+        <v>7.1</v>
+      </c>
+      <c r="D19" s="18" t="s">
         <v>67</v>
       </c>
-      <c r="G18" s="37" t="s">
+      <c r="E19" s="18" t="s">
         <v>68</v>
       </c>
-      <c r="H18" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="I18" s="15" t="s">
+      <c r="F19" s="18" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="19" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="53"/>
-      <c r="B19" s="53"/>
-      <c r="C19" s="14">
-        <v>6.3</v>
-      </c>
-      <c r="D19" s="15" t="s">
-        <v>20</v>
-      </c>
-      <c r="E19" s="15" t="s">
+      <c r="G19" s="34" t="s">
         <v>70</v>
       </c>
-      <c r="F19" s="15" t="s">
+      <c r="H19" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="I19" s="18" t="s">
         <v>71</v>
       </c>
-      <c r="G19" s="37" t="s">
+    </row>
+    <row r="20" spans="1:9" s="8" customFormat="1" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="58"/>
+      <c r="B20" s="58"/>
+      <c r="C20" s="17">
+        <v>7.2</v>
+      </c>
+      <c r="D20" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E20" s="18" t="s">
         <v>72</v>
       </c>
-      <c r="H19" s="14" t="s">
-        <v>178</v>
-      </c>
-      <c r="I19" s="15"/>
-    </row>
-    <row r="20" spans="1:9" s="8" customFormat="1" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="66">
-        <v>7</v>
-      </c>
-      <c r="B20" s="66" t="s">
+      <c r="F20" s="18" t="s">
         <v>73</v>
       </c>
-      <c r="C20" s="17">
-        <v>7.1</v>
-      </c>
-      <c r="D20" s="18" t="s">
+      <c r="G20" s="34" t="s">
         <v>74</v>
       </c>
-      <c r="E20" s="18" t="s">
+      <c r="H20" s="17" t="s">
+        <v>155</v>
+      </c>
+      <c r="I20" s="18" t="s">
+        <v>71</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="56"/>
+      <c r="B21" s="56"/>
+      <c r="C21" s="17">
+        <v>7.3</v>
+      </c>
+      <c r="D21" s="18" t="s">
+        <v>67</v>
+      </c>
+      <c r="E21" s="18" t="s">
         <v>75</v>
       </c>
-      <c r="F20" s="18" t="s">
+      <c r="F21" s="18" t="s">
         <v>76</v>
       </c>
-      <c r="G20" s="38" t="s">
+      <c r="G21" s="34" t="s">
         <v>77</v>
       </c>
-      <c r="H20" s="19" t="s">
-        <v>179</v>
-      </c>
-      <c r="I20" s="18" t="s">
+      <c r="H21" s="17" t="s">
+        <v>154</v>
+      </c>
+      <c r="I21" s="18"/>
+    </row>
+    <row r="22" spans="1:9" s="8" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="57">
+        <v>9</v>
+      </c>
+      <c r="B22" s="57" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" s="8" customFormat="1" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="52"/>
-      <c r="B21" s="52"/>
-      <c r="C21" s="17">
-        <v>7.2</v>
-      </c>
-      <c r="D21" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E21" s="18" t="s">
+      <c r="C22" s="20">
+        <v>9.1</v>
+      </c>
+      <c r="D22" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E22" s="21" t="s">
         <v>79</v>
       </c>
-      <c r="F21" s="18" t="s">
+      <c r="F22" s="21" t="s">
         <v>80</v>
       </c>
-      <c r="G21" s="38" t="s">
+      <c r="G22" s="35" t="s">
         <v>81</v>
       </c>
-      <c r="H21" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="I21" s="18" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="53"/>
-      <c r="B22" s="53"/>
-      <c r="C22" s="17">
-        <v>7.3</v>
-      </c>
-      <c r="D22" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="E22" s="18" t="s">
+      <c r="H22" s="20"/>
+      <c r="I22" s="21"/>
+    </row>
+    <row r="23" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="58"/>
+      <c r="B23" s="58"/>
+      <c r="C23" s="20">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="D23" s="21" t="s">
         <v>82</v>
       </c>
-      <c r="F22" s="18" t="s">
+      <c r="E23" s="21" t="s">
         <v>83</v>
       </c>
-      <c r="G22" s="38" t="s">
+      <c r="F23" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="H22" s="17" t="s">
-        <v>179</v>
-      </c>
-      <c r="I22" s="18"/>
-    </row>
-    <row r="23" spans="1:9" s="8" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="62">
-        <v>9</v>
-      </c>
-      <c r="B23" s="62" t="s">
+      <c r="G23" s="35" t="s">
         <v>85</v>
-      </c>
-      <c r="C23" s="20">
-        <v>9.1</v>
-      </c>
-      <c r="D23" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="E23" s="21" t="s">
-        <v>86</v>
-      </c>
-      <c r="F23" s="21" t="s">
-        <v>87</v>
-      </c>
-      <c r="G23" s="39" t="s">
-        <v>88</v>
       </c>
       <c r="H23" s="20"/>
       <c r="I23" s="21"/>
     </row>
     <row r="24" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="52"/>
-      <c r="B24" s="52"/>
+      <c r="A24" s="58"/>
+      <c r="B24" s="58"/>
       <c r="C24" s="20">
-        <v>9.1999999999999993</v>
+        <v>9.3000000000000007</v>
       </c>
       <c r="D24" s="21" t="s">
+        <v>86</v>
+      </c>
+      <c r="E24" s="21" t="s">
+        <v>87</v>
+      </c>
+      <c r="F24" s="21" t="s">
+        <v>88</v>
+      </c>
+      <c r="G24" s="35" t="s">
         <v>89</v>
       </c>
-      <c r="E24" s="21" t="s">
+      <c r="H24" s="20"/>
+      <c r="I24" s="21" t="s">
         <v>90</v>
       </c>
-      <c r="F24" s="21" t="s">
+    </row>
+    <row r="25" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="56"/>
+      <c r="B25" s="56"/>
+      <c r="C25" s="20">
+        <v>9.4</v>
+      </c>
+      <c r="D25" s="21" t="s">
+        <v>17</v>
+      </c>
+      <c r="E25" s="21" t="s">
         <v>91</v>
       </c>
-      <c r="G24" s="39" t="s">
+      <c r="F25" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="H24" s="20"/>
-      <c r="I24" s="21"/>
-    </row>
-    <row r="25" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="52"/>
-      <c r="B25" s="52"/>
-      <c r="C25" s="20">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="D25" s="21" t="s">
+      <c r="G25" s="35" t="s">
         <v>93</v>
-      </c>
-      <c r="E25" s="21" t="s">
-        <v>94</v>
-      </c>
-      <c r="F25" s="21" t="s">
-        <v>95</v>
-      </c>
-      <c r="G25" s="39" t="s">
-        <v>96</v>
       </c>
       <c r="H25" s="20"/>
       <c r="I25" s="21" t="s">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="70">
+        <v>12</v>
+      </c>
+      <c r="B26" s="70" t="s">
+        <v>94</v>
+      </c>
+      <c r="C26" s="22">
+        <v>12.1</v>
+      </c>
+      <c r="D26" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="E26" s="23" t="s">
+        <v>95</v>
+      </c>
+      <c r="F26" s="23" t="s">
+        <v>96</v>
+      </c>
+      <c r="G26" s="36" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="26" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="53"/>
-      <c r="B26" s="53"/>
-      <c r="C26" s="20">
-        <v>9.4</v>
-      </c>
-      <c r="D26" s="21" t="s">
-        <v>20</v>
-      </c>
-      <c r="E26" s="21" t="s">
+      <c r="H26" s="22" t="s">
         <v>98</v>
       </c>
-      <c r="F26" s="21" t="s">
+      <c r="I26" s="23" t="s">
         <v>99</v>
       </c>
-      <c r="G26" s="39" t="s">
+    </row>
+    <row r="27" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="58"/>
+      <c r="B27" s="58"/>
+      <c r="C27" s="22">
+        <v>12.2</v>
+      </c>
+      <c r="D27" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="E27" s="23" t="s">
         <v>100</v>
       </c>
-      <c r="H26" s="20"/>
-      <c r="I26" s="21" t="s">
-        <v>97</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" s="34" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="57">
-        <v>10</v>
-      </c>
-      <c r="B27" s="57" t="s">
+      <c r="F27" s="23" t="s">
         <v>101</v>
       </c>
-      <c r="C27" s="32">
-        <v>10.1</v>
-      </c>
-      <c r="D27" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E27" s="33" t="s">
+      <c r="G27" s="36" t="s">
         <v>102</v>
       </c>
-      <c r="F27" s="33" t="s">
+      <c r="H27" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="I27" s="23" t="s">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="56"/>
+      <c r="B28" s="56"/>
+      <c r="C28" s="22">
+        <v>12.3</v>
+      </c>
+      <c r="D28" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="E28" s="23" t="s">
         <v>103</v>
       </c>
-      <c r="G27" s="40" t="s">
+      <c r="F28" s="23" t="s">
         <v>104</v>
       </c>
-      <c r="H27" s="32" t="s">
+      <c r="G28" s="36" t="s">
         <v>105</v>
       </c>
-      <c r="I27" s="33"/>
-    </row>
-    <row r="28" spans="1:9" s="34" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="53"/>
-      <c r="B28" s="53"/>
-      <c r="C28" s="32">
-        <v>10.199999999999999</v>
-      </c>
-      <c r="D28" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E28" s="33" t="s">
-        <v>106</v>
-      </c>
-      <c r="F28" s="33" t="s">
+      <c r="H28" s="22" t="s">
+        <v>98</v>
+      </c>
+      <c r="I28" s="23"/>
+    </row>
+    <row r="29" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="64">
+        <v>14</v>
+      </c>
+      <c r="B29" s="64" t="s">
         <v>107</v>
       </c>
-      <c r="G28" s="40" t="s">
+      <c r="C29" s="25">
+        <v>14.1</v>
+      </c>
+      <c r="D29" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="E29" s="26" t="s">
         <v>108</v>
       </c>
-      <c r="H28" s="32" t="s">
-        <v>105</v>
-      </c>
-      <c r="I28" s="33"/>
-    </row>
-    <row r="29" spans="1:9" s="34" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="57">
-        <v>11</v>
-      </c>
-      <c r="B29" s="57" t="s">
+      <c r="F29" s="26" t="s">
         <v>109</v>
       </c>
-      <c r="C29" s="32">
-        <v>11.1</v>
-      </c>
-      <c r="D29" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E29" s="33" t="s">
+      <c r="G29" s="37" t="s">
         <v>110</v>
       </c>
-      <c r="F29" s="33" t="s">
+      <c r="H29" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="I29" s="26" t="s">
         <v>111</v>
       </c>
-      <c r="G29" s="40" t="s">
+    </row>
+    <row r="30" spans="1:9" s="8" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A30" s="56"/>
+      <c r="B30" s="56"/>
+      <c r="C30" s="25">
+        <v>14.2</v>
+      </c>
+      <c r="D30" s="26" t="s">
+        <v>17</v>
+      </c>
+      <c r="E30" s="26" t="s">
         <v>112</v>
       </c>
-      <c r="H29" s="32" t="s">
+      <c r="F30" s="26" t="s">
         <v>113</v>
       </c>
-      <c r="I29" s="33"/>
-    </row>
-    <row r="30" spans="1:9" s="34" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="53"/>
-      <c r="B30" s="53"/>
-      <c r="C30" s="32">
-        <v>11.2</v>
-      </c>
-      <c r="D30" s="33" t="s">
-        <v>20</v>
-      </c>
-      <c r="E30" s="33" t="s">
+      <c r="G30" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="F30" s="33" t="s">
+      <c r="H30" s="25" t="s">
+        <v>156</v>
+      </c>
+      <c r="I30" s="26" t="s">
+        <v>111</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="62">
+        <v>15</v>
+      </c>
+      <c r="B31" s="62" t="s">
         <v>115</v>
       </c>
-      <c r="G30" s="40" t="s">
+      <c r="C31" s="27">
+        <v>15.1</v>
+      </c>
+      <c r="D31" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="H30" s="32" t="s">
-        <v>113</v>
-      </c>
-      <c r="I30" s="33"/>
-    </row>
-    <row r="31" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="60">
-        <v>12</v>
-      </c>
-      <c r="B31" s="60" t="s">
+      <c r="E31" s="28" t="s">
         <v>117</v>
       </c>
-      <c r="C31" s="22">
-        <v>12.1</v>
-      </c>
-      <c r="D31" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="E31" s="23" t="s">
+      <c r="F31" s="28" t="s">
         <v>118</v>
       </c>
-      <c r="F31" s="23" t="s">
+      <c r="G31" s="38" t="s">
         <v>119</v>
       </c>
-      <c r="G31" s="41" t="s">
+      <c r="H31" s="27"/>
+      <c r="I31" s="28"/>
+    </row>
+    <row r="32" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A32" s="58"/>
+      <c r="B32" s="58"/>
+      <c r="C32" s="27">
+        <v>15.2</v>
+      </c>
+      <c r="D32" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="E32" s="28" t="s">
         <v>120</v>
       </c>
-      <c r="H31" s="22" t="s">
+      <c r="F32" s="28" t="s">
         <v>121</v>
       </c>
-      <c r="I31" s="23" t="s">
+      <c r="G32" s="38" t="s">
         <v>122</v>
       </c>
-    </row>
-    <row r="32" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="52"/>
-      <c r="B32" s="52"/>
-      <c r="C32" s="22">
-        <v>12.2</v>
-      </c>
-      <c r="D32" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="E32" s="23" t="s">
+      <c r="H32" s="27"/>
+      <c r="I32" s="28"/>
+    </row>
+    <row r="33" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A33" s="58"/>
+      <c r="B33" s="58"/>
+      <c r="C33" s="27">
+        <v>15.3</v>
+      </c>
+      <c r="D33" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="E33" s="28" t="s">
         <v>123</v>
       </c>
-      <c r="F32" s="23" t="s">
+      <c r="F33" s="28" t="s">
         <v>124</v>
       </c>
-      <c r="G32" s="41" t="s">
+      <c r="G33" s="38" t="s">
         <v>125</v>
       </c>
-      <c r="H32" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="I32" s="23" t="s">
-        <v>122</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="53"/>
-      <c r="B33" s="53"/>
-      <c r="C33" s="22">
-        <v>12.3</v>
-      </c>
-      <c r="D33" s="23" t="s">
-        <v>20</v>
-      </c>
-      <c r="E33" s="23" t="s">
+      <c r="H33" s="27"/>
+      <c r="I33" s="28"/>
+    </row>
+    <row r="34" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A34" s="58"/>
+      <c r="B34" s="58"/>
+      <c r="C34" s="27">
+        <v>15.4</v>
+      </c>
+      <c r="D34" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="E34" s="28" t="s">
         <v>126</v>
       </c>
-      <c r="F33" s="23" t="s">
+      <c r="F34" s="28" t="s">
         <v>127</v>
       </c>
-      <c r="G33" s="41" t="s">
+      <c r="G34" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="H33" s="22" t="s">
-        <v>121</v>
-      </c>
-      <c r="I33" s="23"/>
-    </row>
-    <row r="34" spans="1:9" s="8" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A34" s="70">
-        <v>13</v>
-      </c>
-      <c r="B34" s="70" t="s">
-        <v>182</v>
-      </c>
-      <c r="C34" s="24">
-        <v>13.2</v>
-      </c>
-      <c r="D34" s="71" t="s">
-        <v>186</v>
-      </c>
-      <c r="E34" s="71" t="s">
-        <v>183</v>
-      </c>
-      <c r="F34" s="71" t="s">
-        <v>184</v>
-      </c>
-      <c r="G34" s="72" t="s">
+      <c r="H34" s="27"/>
+      <c r="I34" s="28"/>
+    </row>
+    <row r="35" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A35" s="56"/>
+      <c r="B35" s="56"/>
+      <c r="C35" s="27">
+        <v>15.5</v>
+      </c>
+      <c r="D35" s="28" t="s">
+        <v>116</v>
+      </c>
+      <c r="E35" s="28" t="s">
+        <v>129</v>
+      </c>
+      <c r="F35" s="28" t="s">
+        <v>130</v>
+      </c>
+      <c r="G35" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="H35" s="27"/>
+      <c r="I35" s="28"/>
+    </row>
+    <row r="36" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A36" s="55">
+        <v>16</v>
+      </c>
+      <c r="B36" s="55" t="s">
+        <v>132</v>
+      </c>
+      <c r="C36" s="29">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="D36" s="30" t="s">
+        <v>133</v>
+      </c>
+      <c r="E36" s="30" t="s">
+        <v>134</v>
+      </c>
+      <c r="F36" s="30" t="s">
+        <v>135</v>
+      </c>
+      <c r="G36" s="39" t="s">
+        <v>136</v>
+      </c>
+      <c r="H36" s="29"/>
+      <c r="I36" s="30"/>
+    </row>
+    <row r="37" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A37" s="56"/>
+      <c r="B37" s="56"/>
+      <c r="C37" s="29">
+        <v>16.2</v>
+      </c>
+      <c r="D37" s="30" t="s">
+        <v>137</v>
+      </c>
+      <c r="E37" s="30" t="s">
+        <v>138</v>
+      </c>
+      <c r="F37" s="30" t="s">
+        <v>139</v>
+      </c>
+      <c r="G37" s="39" t="s">
+        <v>140</v>
+      </c>
+      <c r="H37" s="29"/>
+      <c r="I37" s="30"/>
+    </row>
+    <row r="38" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="60">
+        <v>17</v>
+      </c>
+      <c r="B38" s="60" t="s">
+        <v>141</v>
+      </c>
+      <c r="C38" s="11">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="D38" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="E38" s="49" t="s">
+        <v>143</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>144</v>
+      </c>
+      <c r="G38" s="50" t="s">
+        <v>166</v>
+      </c>
+      <c r="H38" s="11"/>
+      <c r="I38" s="49" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="58"/>
+      <c r="B39" s="58"/>
+      <c r="C39" s="11">
+        <v>17.2</v>
+      </c>
+      <c r="D39" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="E39" s="49" t="s">
+        <v>167</v>
+      </c>
+      <c r="F39" s="12" t="s">
+        <v>145</v>
+      </c>
+      <c r="G39" s="50" t="s">
+        <v>146</v>
+      </c>
+      <c r="H39" s="11"/>
+      <c r="I39" s="49" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="58"/>
+      <c r="B40" s="58"/>
+      <c r="C40" s="11">
+        <v>17.3</v>
+      </c>
+      <c r="D40" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="E40" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="F40" s="49" t="s">
+        <v>168</v>
+      </c>
+      <c r="G40" s="50" t="s">
+        <v>171</v>
+      </c>
+      <c r="H40" s="11"/>
+      <c r="I40" s="49" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="58"/>
+      <c r="B41" s="58"/>
+      <c r="C41" s="11">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="D41" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="E41" s="49" t="s">
+        <v>170</v>
+      </c>
+      <c r="F41" s="49" t="s">
+        <v>169</v>
+      </c>
+      <c r="G41" s="50" t="s">
+        <v>175</v>
+      </c>
+      <c r="H41" s="11"/>
+      <c r="I41" s="49" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="58"/>
+      <c r="B42" s="58"/>
+      <c r="C42" s="11">
+        <v>17.5</v>
+      </c>
+      <c r="D42" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="E42" s="49" t="s">
+        <v>172</v>
+      </c>
+      <c r="F42" s="49" t="s">
+        <v>173</v>
+      </c>
+      <c r="G42" s="50" t="s">
+        <v>174</v>
+      </c>
+      <c r="H42" s="11"/>
+      <c r="I42" s="49" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="58"/>
+      <c r="B43" s="58"/>
+      <c r="C43" s="11">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="D43" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>148</v>
+      </c>
+      <c r="F43" s="49" t="s">
+        <v>176</v>
+      </c>
+      <c r="G43" s="50" t="s">
+        <v>177</v>
+      </c>
+      <c r="H43" s="11"/>
+      <c r="I43" s="49" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="58"/>
+      <c r="B44" s="58"/>
+      <c r="C44" s="11">
+        <v>17.7</v>
+      </c>
+      <c r="D44" s="12" t="s">
+        <v>142</v>
+      </c>
+      <c r="E44" s="12" t="s">
+        <v>149</v>
+      </c>
+      <c r="F44" s="49" t="s">
+        <v>178</v>
+      </c>
+      <c r="G44" s="50" t="s">
         <v>185</v>
       </c>
-      <c r="H34" s="24" t="s">
-        <v>129</v>
-      </c>
-      <c r="I34" s="25" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="58">
-        <v>14</v>
-      </c>
-      <c r="B35" s="58" t="s">
-        <v>131</v>
-      </c>
-      <c r="C35" s="26">
-        <v>14.1</v>
-      </c>
-      <c r="D35" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="E35" s="27" t="s">
-        <v>132</v>
-      </c>
-      <c r="F35" s="27" t="s">
-        <v>133</v>
-      </c>
-      <c r="G35" s="42" t="s">
-        <v>134</v>
-      </c>
-      <c r="H35" s="26" t="s">
-        <v>181</v>
-      </c>
-      <c r="I35" s="27" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" s="8" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A36" s="53"/>
-      <c r="B36" s="53"/>
-      <c r="C36" s="26">
-        <v>14.2</v>
-      </c>
-      <c r="D36" s="27" t="s">
-        <v>20</v>
-      </c>
-      <c r="E36" s="27" t="s">
-        <v>136</v>
-      </c>
-      <c r="F36" s="27" t="s">
-        <v>137</v>
-      </c>
-      <c r="G36" s="42" t="s">
-        <v>138</v>
-      </c>
-      <c r="H36" s="26" t="s">
-        <v>181</v>
-      </c>
-      <c r="I36" s="27" t="s">
-        <v>135</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="61">
-        <v>15</v>
-      </c>
-      <c r="B37" s="61" t="s">
-        <v>139</v>
-      </c>
-      <c r="C37" s="28">
-        <v>15.1</v>
-      </c>
-      <c r="D37" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="E37" s="29" t="s">
-        <v>141</v>
-      </c>
-      <c r="F37" s="29" t="s">
-        <v>142</v>
-      </c>
-      <c r="G37" s="43" t="s">
-        <v>143</v>
-      </c>
-      <c r="H37" s="28"/>
-      <c r="I37" s="29"/>
-    </row>
-    <row r="38" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="52"/>
-      <c r="B38" s="52"/>
-      <c r="C38" s="28">
-        <v>15.2</v>
-      </c>
-      <c r="D38" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="E38" s="29" t="s">
-        <v>144</v>
-      </c>
-      <c r="F38" s="29" t="s">
-        <v>145</v>
-      </c>
-      <c r="G38" s="43" t="s">
-        <v>146</v>
-      </c>
-      <c r="H38" s="28"/>
-      <c r="I38" s="29"/>
-    </row>
-    <row r="39" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="52"/>
-      <c r="B39" s="52"/>
-      <c r="C39" s="28">
-        <v>15.3</v>
-      </c>
-      <c r="D39" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="E39" s="29" t="s">
-        <v>147</v>
-      </c>
-      <c r="F39" s="29" t="s">
-        <v>148</v>
-      </c>
-      <c r="G39" s="43" t="s">
-        <v>149</v>
-      </c>
-      <c r="H39" s="28"/>
-      <c r="I39" s="29"/>
-    </row>
-    <row r="40" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A40" s="52"/>
-      <c r="B40" s="52"/>
-      <c r="C40" s="28">
-        <v>15.4</v>
-      </c>
-      <c r="D40" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="E40" s="29" t="s">
-        <v>150</v>
-      </c>
-      <c r="F40" s="29" t="s">
-        <v>151</v>
-      </c>
-      <c r="G40" s="43" t="s">
-        <v>152</v>
-      </c>
-      <c r="H40" s="28"/>
-      <c r="I40" s="29"/>
-    </row>
-    <row r="41" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A41" s="53"/>
-      <c r="B41" s="53"/>
-      <c r="C41" s="28">
-        <v>15.5</v>
-      </c>
-      <c r="D41" s="29" t="s">
-        <v>140</v>
-      </c>
-      <c r="E41" s="29" t="s">
-        <v>153</v>
-      </c>
-      <c r="F41" s="29" t="s">
-        <v>154</v>
-      </c>
-      <c r="G41" s="43" t="s">
-        <v>155</v>
-      </c>
-      <c r="H41" s="28"/>
-      <c r="I41" s="29"/>
-    </row>
-    <row r="42" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A42" s="59">
-        <v>16</v>
-      </c>
-      <c r="B42" s="59" t="s">
-        <v>156</v>
-      </c>
-      <c r="C42" s="30">
-        <v>16.100000000000001</v>
-      </c>
-      <c r="D42" s="31" t="s">
-        <v>157</v>
-      </c>
-      <c r="E42" s="31" t="s">
-        <v>158</v>
-      </c>
-      <c r="F42" s="31" t="s">
-        <v>159</v>
-      </c>
-      <c r="G42" s="44" t="s">
-        <v>160</v>
-      </c>
-      <c r="H42" s="30"/>
-      <c r="I42" s="31"/>
-    </row>
-    <row r="43" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A43" s="53"/>
-      <c r="B43" s="53"/>
-      <c r="C43" s="30">
-        <v>16.2</v>
-      </c>
-      <c r="D43" s="31" t="s">
-        <v>161</v>
-      </c>
-      <c r="E43" s="31" t="s">
-        <v>162</v>
-      </c>
-      <c r="F43" s="31" t="s">
-        <v>163</v>
-      </c>
-      <c r="G43" s="44" t="s">
-        <v>164</v>
-      </c>
-      <c r="H43" s="30"/>
-      <c r="I43" s="31"/>
-    </row>
-    <row r="44" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="51">
-        <v>17</v>
-      </c>
-      <c r="B44" s="51" t="s">
-        <v>165</v>
-      </c>
-      <c r="C44" s="11">
-        <v>17.100000000000001</v>
-      </c>
-      <c r="D44" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="E44" s="81" t="s">
-        <v>167</v>
-      </c>
-      <c r="F44" s="12" t="s">
-        <v>168</v>
-      </c>
-      <c r="G44" s="82" t="s">
-        <v>197</v>
-      </c>
       <c r="H44" s="11"/>
-      <c r="I44" s="81" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="52"/>
-      <c r="B45" s="52"/>
-      <c r="C45" s="11">
-        <v>17.2</v>
-      </c>
-      <c r="D45" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="E45" s="81" t="s">
-        <v>198</v>
-      </c>
-      <c r="F45" s="12" t="s">
-        <v>169</v>
-      </c>
-      <c r="G45" s="82" t="s">
-        <v>170</v>
-      </c>
-      <c r="H45" s="11"/>
-      <c r="I45" s="81" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="52"/>
-      <c r="B46" s="52"/>
-      <c r="C46" s="11">
-        <v>17.3</v>
-      </c>
-      <c r="D46" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="E46" s="12" t="s">
-        <v>171</v>
-      </c>
-      <c r="F46" s="81" t="s">
-        <v>199</v>
-      </c>
-      <c r="G46" s="82" t="s">
-        <v>202</v>
-      </c>
-      <c r="H46" s="11"/>
-      <c r="I46" s="81" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A47" s="52"/>
-      <c r="B47" s="52"/>
-      <c r="C47" s="11">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="D47" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="E47" s="81" t="s">
-        <v>201</v>
-      </c>
-      <c r="F47" s="81" t="s">
-        <v>200</v>
-      </c>
-      <c r="G47" s="82" t="s">
-        <v>206</v>
-      </c>
-      <c r="H47" s="11"/>
-      <c r="I47" s="81" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="52"/>
-      <c r="B48" s="52"/>
-      <c r="C48" s="11">
-        <v>17.5</v>
-      </c>
-      <c r="D48" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="E48" s="81" t="s">
-        <v>203</v>
-      </c>
-      <c r="F48" s="81" t="s">
-        <v>204</v>
-      </c>
-      <c r="G48" s="82" t="s">
-        <v>205</v>
-      </c>
-      <c r="H48" s="11"/>
-      <c r="I48" s="81" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A49" s="52"/>
-      <c r="B49" s="52"/>
-      <c r="C49" s="11">
-        <v>17.600000000000001</v>
-      </c>
-      <c r="D49" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="E49" s="12" t="s">
-        <v>172</v>
-      </c>
-      <c r="F49" s="81" t="s">
-        <v>207</v>
-      </c>
-      <c r="G49" s="82" t="s">
-        <v>208</v>
-      </c>
-      <c r="H49" s="11"/>
-      <c r="I49" s="81" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A50" s="52"/>
-      <c r="B50" s="52"/>
-      <c r="C50" s="11">
-        <v>17.7</v>
-      </c>
-      <c r="D50" s="12" t="s">
-        <v>166</v>
-      </c>
-      <c r="E50" s="12" t="s">
-        <v>173</v>
-      </c>
-      <c r="F50" s="81" t="s">
-        <v>209</v>
-      </c>
-      <c r="G50" s="82" t="s">
-        <v>210</v>
-      </c>
-      <c r="H50" s="11"/>
-      <c r="I50" s="81" t="s">
-        <v>211</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="2"/>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="D51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="F51" s="3"/>
-      <c r="G51" s="4"/>
-      <c r="H51" s="6"/>
-      <c r="I51" s="3"/>
-    </row>
-    <row r="52" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="7"/>
-      <c r="B52" s="2"/>
-      <c r="C52" s="2"/>
-      <c r="D52" s="3"/>
-      <c r="E52" s="2"/>
-      <c r="F52" s="3"/>
-      <c r="G52" s="4"/>
-      <c r="H52" s="2"/>
-      <c r="I52" s="3"/>
-    </row>
-    <row r="53" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A53" s="7"/>
-    </row>
-    <row r="54" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A54" s="7"/>
-    </row>
-    <row r="55" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A55" s="7"/>
-    </row>
-    <row r="56" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A56" s="7"/>
+      <c r="I44" s="49" t="s">
+        <v>179</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A45" s="2"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="3"/>
+    </row>
+    <row r="46" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="7"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="3"/>
+    </row>
+    <row r="47" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A47" s="7"/>
+    </row>
+    <row r="48" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A48" s="7"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="7"/>
+    </row>
+    <row r="50" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A50" s="7"/>
     </row>
   </sheetData>
-  <autoFilter ref="I1:I33" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <mergeCells count="33">
+  <autoFilter ref="I1:I28" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <mergeCells count="29">
+    <mergeCell ref="A26:A28"/>
+    <mergeCell ref="A31:A35"/>
+    <mergeCell ref="A38:A44"/>
+    <mergeCell ref="B22:B25"/>
+    <mergeCell ref="B7:B12"/>
+    <mergeCell ref="B26:B28"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="B16:B18"/>
+    <mergeCell ref="B29:B30"/>
+    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="A7:A12"/>
+    <mergeCell ref="A19:A21"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="A5:A6"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="D1:F1"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A36:A37"/>
+    <mergeCell ref="A22:A25"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="B13:B15"/>
+    <mergeCell ref="B19:B21"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="B31:B35"/>
+    <mergeCell ref="A1:A2"/>
     <mergeCell ref="A29:A30"/>
-    <mergeCell ref="B14:B16"/>
-    <mergeCell ref="B20:B22"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="B37:B41"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A35:A36"/>
     <mergeCell ref="C1:C2"/>
-    <mergeCell ref="A14:A16"/>
+    <mergeCell ref="A13:A15"/>
     <mergeCell ref="G1:G2"/>
-    <mergeCell ref="A27:A28"/>
-    <mergeCell ref="A8:A13"/>
-    <mergeCell ref="A20:A22"/>
-    <mergeCell ref="B6:B7"/>
-    <mergeCell ref="A6:A7"/>
-    <mergeCell ref="B44:B50"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="B29:B30"/>
-    <mergeCell ref="B35:B36"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="A31:A33"/>
-    <mergeCell ref="A37:A41"/>
-    <mergeCell ref="A44:A50"/>
-    <mergeCell ref="B23:B26"/>
-    <mergeCell ref="B8:B13"/>
-    <mergeCell ref="B31:B33"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Soubhanik/checkupp_product_backlog_final.xlsx
+++ b/Soubhanik/checkupp_product_backlog_final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anodiam\2026\CheckUpp_Parent\CheckUpp\Soubhanik\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Checkupp\CheckUpp\Soubhanik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F47E8F26-9D1B-4D6F-8625-8AAB133B5B06}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B421AD34-2558-489C-B84F-60DF859C85DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -130,7 +130,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="151">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="183">
   <si>
     <t>Epic #</t>
   </si>
@@ -340,31 +340,9 @@
     <t>Screenings Schedule</t>
   </si>
   <si>
-    <t>view my upcoming and overdue screenings in a schedule view</t>
-  </si>
-  <si>
-    <t>I know exactly what health checks I need and when</t>
-  </si>
-  <si>
-    <t>1. Screenings schedule screen must show upcoming and due tests
-2. Overdue tests must be highlighted
-3. Dates must be clearly shown</t>
-  </si>
-  <si>
     <t>Discussion #9 – TANVI</t>
   </si>
   <si>
-    <t>sync health check appointments to my device calendar</t>
-  </si>
-  <si>
-    <t>I receive reminders and don't miss health checks</t>
-  </si>
-  <si>
-    <t>1. Calendar sync must be available per appointment
-2. App must sync to Google Calendar / iCal
-3. Appointment details must be included in the calendar entry</t>
-  </si>
-  <si>
     <t>Pregnancy Tracking</t>
   </si>
   <si>
@@ -447,9 +425,6 @@
   </si>
   <si>
     <t>Logged-in User</t>
-  </si>
-  <si>
-    <t>access an "Other Ailments" option from Health Checks</t>
   </si>
   <si>
     <t>I can document conditions not listed in the app</t>
@@ -518,10 +493,6 @@
     <t>1. Tapping must open the detailed view of the selected appointment
 2. Detail view must clearly display Appointment date and time, medical facility, facility address, and doctor's name
 3. Tapping on the back button must take the user back to the Your Appointments screen</t>
-  </si>
-  <si>
-    <t>1. "Other Ailments" tab must appear in the Health Checks list.
-2. The tab must be tappable.</t>
   </si>
   <si>
     <t>select a condition from a dropdown or enter a custom condition</t>
@@ -624,6 +595,148 @@
   </si>
   <si>
     <t xml:space="preserve"> </t>
+  </si>
+  <si>
+    <t>Slide 25</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Slide 13 </t>
+  </si>
+  <si>
+    <t>Discussion #8 – TANVI</t>
+  </si>
+  <si>
+    <t>Slide 13</t>
+  </si>
+  <si>
+    <t>add appointment details when creating a custom health check</t>
+  </si>
+  <si>
+    <t>I can schedule future health appointments</t>
+  </si>
+  <si>
+    <t>receive an option to add my appointment to my device calendar after saving a health check</t>
+  </si>
+  <si>
+    <t>I can easily sync important appointments</t>
+  </si>
+  <si>
+    <t>first-time user</t>
+  </si>
+  <si>
+    <t>grant calendar access</t>
+  </si>
+  <si>
+    <t>the app can add appointments to my device calendar</t>
+  </si>
+  <si>
+    <t>choose which calendar to sync my appointments with</t>
+  </si>
+  <si>
+    <t>appointments are added to my preferred calendar</t>
+  </si>
+  <si>
+    <t>preview appointment details before syncing</t>
+  </si>
+  <si>
+    <t>I can verify the information is correct</t>
+  </si>
+  <si>
+    <t>receive confirmation when my appointment has been added to my calendar</t>
+  </si>
+  <si>
+    <t>I know the sync was successful</t>
+  </si>
+  <si>
+    <t>view all synced health appointments in one place</t>
+  </si>
+  <si>
+    <t>I can manage my upcoming appointments</t>
+  </si>
+  <si>
+    <t>access Calendar &amp; Sync Settings from the calendar icon in the Screenings tab</t>
+  </si>
+  <si>
+    <t>I can manage my calendar preferences</t>
+  </si>
+  <si>
+    <t>enable or disable calendar syncing</t>
+  </si>
+  <si>
+    <t>I can control whether appointments are synced</t>
+  </si>
+  <si>
+    <t>choose which health modules sync appointments</t>
+  </si>
+  <si>
+    <t>only relevant appointments appear in my calendar</t>
+  </si>
+  <si>
+    <t>configure reminder preferences for synced appointments</t>
+  </si>
+  <si>
+    <t>I receive reminders at my preferred time</t>
+  </si>
+  <si>
+    <t>access an Other Ailments option from Health Checks</t>
+  </si>
+  <si>
+    <t>1. Other Ailments tab must appear in the Health Checks list.
+2. The tab must be tappable.</t>
+  </si>
+  <si>
+    <t>1. User must be able to enter appointment date, time and location 2. Appointment details must be linked to the health check
+3. Appointment information must be saved successfully</t>
+  </si>
+  <si>
+    <t>1. App must display an 'Add to Calendar' prompt after saving
+2. User must be able to add or dismiss the prompt
+3. Appointment details must be retained regardless of the user's choice</t>
+  </si>
+  <si>
+    <t>1. App must request calendar permission before the first sync
+2. User must be able to allow or deny access
+3. Permission request should not appear again once a choice has been made</t>
+  </si>
+  <si>
+    <t>1. User must be able to choose Google Calendar, Apple Calendar/iCal or Outlook (where supported)
+2. Selected calendar must be remembered for future syncs
+3. User must be able to change the selected calendar later</t>
+  </si>
+  <si>
+    <t>1. Event preview must display title, date, time, location and reminder
+2. User must be able to edit or cancel before syncing
+3. Calendar event must match the displayed details</t>
+  </si>
+  <si>
+    <t>1. Upcoming Appointments screen must display all synced appointments
+2. Appointments must be grouped by date
+3. User must be able to open the device calendar from this screen</t>
+  </si>
+  <si>
+    <t>1. Tapping the calendar icon must open Calendar &amp; Sync Settings
+2. Settings must display current sync status
+3. User must be able to access settings at any time</t>
+  </si>
+  <si>
+    <t>1. User must be able to turn Calendar Sync on or off
+2. Preference must be saved across sessions
+3. Existing calendar events must remain unaffected when sync is disabled</t>
+  </si>
+  <si>
+    <t>1. User must be able to enable or disable sync for individual modules
+2. Modules include Screenings, Pregnancy, Midlife Health, Menopause and Other Ailments
+3. Only enabled modules should sync appointments</t>
+  </si>
+  <si>
+    <t>1. User must be able to choose reminder intervals
+2. Reminder settings must apply to newly synced appointments
+3. Default reminder must be configurable</t>
+  </si>
+  <si>
+    <t>1. App must display a success message after syncing
+2. User must be able to view the calendar event
+3. Appointment must exist in the selected calendar</t>
   </si>
 </sst>
 </file>
@@ -733,7 +846,7 @@
       <charset val="1"/>
     </font>
   </fonts>
-  <fills count="16">
+  <fills count="17">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -811,6 +924,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -932,7 +1051,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="74">
+  <cellXfs count="79">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1000,12 +1119,6 @@
     <xf numFmtId="0" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1096,56 +1209,77 @@
     <xf numFmtId="0" fontId="11" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1163,10 +1297,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1432,51 +1562,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:I41"/>
-  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <dimension ref="A1:L59"/>
+  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="5.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.88671875" style="3" customWidth="1"/>
+    <col min="1" max="1" width="5.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.90625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.08984375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.90625" style="3" customWidth="1"/>
     <col min="5" max="5" width="65" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="41" style="3" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="52" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="15.33203125" style="3" customWidth="1"/>
-    <col min="10" max="12" width="8.88671875" style="5" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="5"/>
+    <col min="8" max="8" width="11.6328125" style="2" customWidth="1"/>
+    <col min="9" max="9" width="15.36328125" style="3" customWidth="1"/>
+    <col min="10" max="12" width="8.90625" style="5" customWidth="1"/>
+    <col min="13" max="16384" width="8.90625" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="71" t="s">
+    <row r="1" spans="1:9" ht="39.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A1" s="64" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="61" t="s">
+      <c r="B1" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="61" t="s">
+      <c r="C1" s="53" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="61" t="s">
+      <c r="D1" s="53" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="69"/>
-      <c r="F1" s="70"/>
-      <c r="G1" s="72" t="s">
+      <c r="E1" s="55"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="66" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="61" t="s">
+      <c r="H1" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="61" t="s">
+      <c r="I1" s="53" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="57"/>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A2" s="58"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="54"/>
       <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1486,188 +1616,188 @@
       <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="73"/>
-      <c r="H2" s="62"/>
-      <c r="I2" s="62"/>
-    </row>
-    <row r="3" spans="1:9" s="8" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="39" t="s">
-        <v>150</v>
-      </c>
-      <c r="B3" s="39" t="s">
-        <v>134</v>
+      <c r="G2" s="67"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
+    </row>
+    <row r="3" spans="1:9" s="8" customFormat="1" ht="78" x14ac:dyDescent="0.35">
+      <c r="A3" s="37" t="s">
+        <v>142</v>
+      </c>
+      <c r="B3" s="37" t="s">
+        <v>126</v>
       </c>
       <c r="C3" s="22">
         <v>13.2</v>
       </c>
-      <c r="D3" s="40" t="s">
-        <v>135</v>
-      </c>
-      <c r="E3" s="40" t="s">
-        <v>136</v>
-      </c>
-      <c r="F3" s="40" t="s">
-        <v>137</v>
-      </c>
-      <c r="G3" s="41" t="s">
-        <v>140</v>
+      <c r="D3" s="38" t="s">
+        <v>127</v>
+      </c>
+      <c r="E3" s="38" t="s">
+        <v>128</v>
+      </c>
+      <c r="F3" s="38" t="s">
+        <v>129</v>
+      </c>
+      <c r="G3" s="39" t="s">
+        <v>132</v>
       </c>
       <c r="H3" s="22" t="s">
         <v>61</v>
       </c>
-      <c r="I3" s="40" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="49">
+      <c r="I3" s="38" t="s">
+        <v>133</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="8" customFormat="1" ht="52" x14ac:dyDescent="0.35">
+      <c r="A4" s="47">
         <v>1</v>
       </c>
-      <c r="B4" s="49" t="s">
+      <c r="B4" s="47" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="50">
+      <c r="C4" s="48">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D4" s="51" t="s">
+      <c r="D4" s="49" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="51" t="s">
+      <c r="E4" s="49" t="s">
+        <v>104</v>
+      </c>
+      <c r="F4" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="G4" s="50" t="s">
+        <v>106</v>
+      </c>
+      <c r="H4" s="48" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="49" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" s="36" customFormat="1" ht="78" x14ac:dyDescent="0.35">
+      <c r="A5" s="68">
+        <v>3</v>
+      </c>
+      <c r="B5" s="68" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="35">
+        <v>3.1</v>
+      </c>
+      <c r="D5" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E5" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="F5" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="G5" s="42" t="s">
         <v>111</v>
       </c>
-      <c r="F4" s="51" t="s">
+      <c r="H5" s="43" t="s">
+        <v>98</v>
+      </c>
+      <c r="I5" s="40" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" s="8" customFormat="1" ht="78" x14ac:dyDescent="0.35">
+      <c r="A6" s="69"/>
+      <c r="B6" s="69"/>
+      <c r="C6" s="35">
+        <v>3.2</v>
+      </c>
+      <c r="D6" s="40" t="s">
+        <v>11</v>
+      </c>
+      <c r="E6" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="F6" s="41" t="s">
+        <v>110</v>
+      </c>
+      <c r="G6" s="42" t="s">
         <v>112</v>
       </c>
-      <c r="G4" s="52" t="s">
-        <v>113</v>
-      </c>
-      <c r="H4" s="50" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="51" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" s="38" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A5" s="67">
-        <v>3</v>
-      </c>
-      <c r="B5" s="67" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="37">
-        <v>3.1</v>
-      </c>
-      <c r="D5" s="42" t="s">
-        <v>11</v>
-      </c>
-      <c r="E5" s="43" t="s">
-        <v>114</v>
-      </c>
-      <c r="F5" s="43" t="s">
-        <v>115</v>
-      </c>
-      <c r="G5" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="H5" s="45" t="s">
-        <v>105</v>
-      </c>
-      <c r="I5" s="42" t="s">
+      <c r="H6" s="35" t="s">
+        <v>98</v>
+      </c>
+      <c r="I6" s="40" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="8" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="68"/>
-      <c r="B6" s="68"/>
-      <c r="C6" s="37">
-        <v>3.2</v>
-      </c>
-      <c r="D6" s="42" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="F6" s="43" t="s">
-        <v>117</v>
-      </c>
-      <c r="G6" s="44" t="s">
-        <v>119</v>
-      </c>
-      <c r="H6" s="37" t="s">
-        <v>105</v>
-      </c>
-      <c r="I6" s="42" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" s="8" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="48">
+    <row r="7" spans="1:9" s="8" customFormat="1" ht="117" x14ac:dyDescent="0.35">
+      <c r="A7" s="46">
         <v>5</v>
       </c>
-      <c r="B7" s="48" t="s">
+      <c r="B7" s="46" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="9">
         <v>5.2</v>
       </c>
       <c r="D7" s="10" t="s">
-        <v>142</v>
+        <v>134</v>
       </c>
       <c r="E7" s="10" t="s">
-        <v>144</v>
+        <v>136</v>
       </c>
       <c r="F7" s="10" t="s">
-        <v>143</v>
-      </c>
-      <c r="G7" s="29" t="s">
-        <v>145</v>
+        <v>135</v>
+      </c>
+      <c r="G7" s="27" t="s">
+        <v>137</v>
       </c>
       <c r="H7" s="11" t="s">
-        <v>106</v>
+        <v>99</v>
       </c>
       <c r="I7" s="10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="63">
+    <row r="8" spans="1:9" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
+      <c r="A8" s="61">
         <v>6</v>
       </c>
-      <c r="B8" s="63" t="s">
+      <c r="B8" s="61" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="12">
         <v>6.1</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>135</v>
-      </c>
-      <c r="E8" s="53" t="s">
-        <v>146</v>
-      </c>
-      <c r="F8" s="53" t="s">
-        <v>147</v>
-      </c>
-      <c r="G8" s="54" t="s">
-        <v>148</v>
+        <v>127</v>
+      </c>
+      <c r="E8" s="51" t="s">
+        <v>138</v>
+      </c>
+      <c r="F8" s="51" t="s">
+        <v>139</v>
+      </c>
+      <c r="G8" s="52" t="s">
+        <v>140</v>
       </c>
       <c r="H8" s="14" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="57"/>
-      <c r="B9" s="57"/>
+    <row r="9" spans="1:9" s="8" customFormat="1" ht="52" x14ac:dyDescent="0.35">
+      <c r="A9" s="58"/>
+      <c r="B9" s="58"/>
       <c r="C9" s="12">
         <v>6.3</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>20</v>
@@ -1675,26 +1805,26 @@
       <c r="F9" s="13" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="30" t="s">
-        <v>149</v>
+      <c r="G9" s="28" t="s">
+        <v>141</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>107</v>
+        <v>100</v>
       </c>
       <c r="I9" s="13"/>
     </row>
-    <row r="10" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="66">
+    <row r="10" spans="1:9" s="8" customFormat="1" ht="52" x14ac:dyDescent="0.35">
+      <c r="A10" s="62">
         <v>7</v>
       </c>
-      <c r="B10" s="66" t="s">
+      <c r="B10" s="62" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="15">
         <v>7.1</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>23</v>
@@ -1702,24 +1832,24 @@
       <c r="F10" s="16" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="31" t="s">
+      <c r="G10" s="29" t="s">
         <v>25</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="I10" s="16" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="56"/>
-      <c r="B11" s="56"/>
+    <row r="11" spans="1:9" s="8" customFormat="1" ht="52" x14ac:dyDescent="0.35">
+      <c r="A11" s="60"/>
+      <c r="B11" s="60"/>
       <c r="C11" s="15">
         <v>7.2</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E11" s="16" t="s">
         <v>27</v>
@@ -1727,24 +1857,24 @@
       <c r="F11" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="31" t="s">
+      <c r="G11" s="29" t="s">
         <v>29</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>109</v>
+        <v>102</v>
       </c>
       <c r="I11" s="16" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="8" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="57"/>
-      <c r="B12" s="57"/>
+    <row r="12" spans="1:9" s="8" customFormat="1" ht="39" x14ac:dyDescent="0.35">
+      <c r="A12" s="58"/>
+      <c r="B12" s="58"/>
       <c r="C12" s="15">
         <v>7.3</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>30</v>
@@ -1752,19 +1882,19 @@
       <c r="F12" s="16" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="31" t="s">
+      <c r="G12" s="29" t="s">
         <v>32</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>108</v>
+        <v>101</v>
       </c>
       <c r="I12" s="16"/>
     </row>
-    <row r="13" spans="1:9" s="8" customFormat="1" ht="82.8" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="60">
+    <row r="13" spans="1:9" s="8" customFormat="1" ht="82.75" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A13" s="59">
         <v>9</v>
       </c>
-      <c r="B13" s="60" t="s">
+      <c r="B13" s="59" t="s">
         <v>33</v>
       </c>
       <c r="C13" s="18">
@@ -1779,15 +1909,15 @@
       <c r="F13" s="19" t="s">
         <v>35</v>
       </c>
-      <c r="G13" s="32" t="s">
+      <c r="G13" s="30" t="s">
         <v>36</v>
       </c>
       <c r="H13" s="18"/>
       <c r="I13" s="19"/>
     </row>
-    <row r="14" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="56"/>
-      <c r="B14" s="56"/>
+    <row r="14" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A14" s="60"/>
+      <c r="B14" s="60"/>
       <c r="C14" s="18">
         <v>9.1999999999999993</v>
       </c>
@@ -1800,15 +1930,15 @@
       <c r="F14" s="19" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="32" t="s">
+      <c r="G14" s="30" t="s">
         <v>40</v>
       </c>
       <c r="H14" s="18"/>
       <c r="I14" s="19"/>
     </row>
-    <row r="15" spans="1:9" s="8" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="56"/>
-      <c r="B15" s="56"/>
+    <row r="15" spans="1:9" s="8" customFormat="1" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A15" s="60"/>
+      <c r="B15" s="60"/>
       <c r="C15" s="18">
         <v>9.3000000000000007</v>
       </c>
@@ -1821,7 +1951,7 @@
       <c r="F15" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="32" t="s">
+      <c r="G15" s="30" t="s">
         <v>44</v>
       </c>
       <c r="H15" s="18"/>
@@ -1829,9 +1959,9 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="57"/>
-      <c r="B16" s="57"/>
+    <row r="16" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A16" s="58"/>
+      <c r="B16" s="58"/>
       <c r="C16" s="18">
         <v>9.4</v>
       </c>
@@ -1844,7 +1974,7 @@
       <c r="F16" s="19" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="32" t="s">
+      <c r="G16" s="30" t="s">
         <v>48</v>
       </c>
       <c r="H16" s="18"/>
@@ -1852,11 +1982,11 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="55">
+    <row r="17" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A17" s="70">
         <v>12</v>
       </c>
-      <c r="B17" s="55" t="s">
+      <c r="B17" s="70" t="s">
         <v>49</v>
       </c>
       <c r="C17" s="20">
@@ -1871,7 +2001,7 @@
       <c r="F17" s="21" t="s">
         <v>51</v>
       </c>
-      <c r="G17" s="33" t="s">
+      <c r="G17" s="31" t="s">
         <v>52</v>
       </c>
       <c r="H17" s="20" t="s">
@@ -1881,9 +2011,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="56"/>
-      <c r="B18" s="56"/>
+    <row r="18" spans="1:9" s="8" customFormat="1" ht="55.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A18" s="60"/>
+      <c r="B18" s="60"/>
       <c r="C18" s="20">
         <v>12.2</v>
       </c>
@@ -1896,7 +2026,7 @@
       <c r="F18" s="21" t="s">
         <v>56</v>
       </c>
-      <c r="G18" s="33" t="s">
+      <c r="G18" s="31" t="s">
         <v>57</v>
       </c>
       <c r="H18" s="20" t="s">
@@ -1906,9 +2036,9 @@
         <v>54</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="57"/>
-      <c r="B19" s="57"/>
+    <row r="19" spans="1:9" s="8" customFormat="1" ht="55.25" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A19" s="58"/>
+      <c r="B19" s="58"/>
       <c r="C19" s="20">
         <v>12.3</v>
       </c>
@@ -1921,7 +2051,7 @@
       <c r="F19" s="21" t="s">
         <v>59</v>
       </c>
-      <c r="G19" s="33" t="s">
+      <c r="G19" s="31" t="s">
         <v>60</v>
       </c>
       <c r="H19" s="20" t="s">
@@ -1929,458 +2059,801 @@
       </c>
       <c r="I19" s="21"/>
     </row>
-    <row r="20" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="64">
+    <row r="20" spans="1:9" s="8" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A20" s="65">
         <v>14</v>
       </c>
-      <c r="B20" s="64" t="s">
+      <c r="B20" s="65" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="23">
+      <c r="C20" s="76">
         <v>14.1</v>
       </c>
-      <c r="D20" s="24" t="s">
+      <c r="D20" s="32" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="24" t="s">
+      <c r="E20" s="32" t="s">
+        <v>147</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>148</v>
+      </c>
+      <c r="G20" s="32" t="s">
+        <v>172</v>
+      </c>
+      <c r="H20" s="76" t="s">
+        <v>103</v>
+      </c>
+      <c r="I20" s="32" t="s">
         <v>63</v>
       </c>
-      <c r="F20" s="24" t="s">
+    </row>
+    <row r="21" spans="1:9" s="8" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A21" s="75"/>
+      <c r="B21" s="75"/>
+      <c r="C21" s="76">
+        <v>14.2</v>
+      </c>
+      <c r="D21" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E21" s="32" t="s">
+        <v>149</v>
+      </c>
+      <c r="F21" s="32" t="s">
+        <v>150</v>
+      </c>
+      <c r="G21" s="32" t="s">
+        <v>173</v>
+      </c>
+      <c r="H21" s="76" t="s">
+        <v>103</v>
+      </c>
+      <c r="I21" s="32" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="8" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A22" s="75"/>
+      <c r="B22" s="75"/>
+      <c r="C22" s="76">
+        <v>14.3</v>
+      </c>
+      <c r="D22" s="32" t="s">
+        <v>151</v>
+      </c>
+      <c r="E22" s="32" t="s">
+        <v>152</v>
+      </c>
+      <c r="F22" s="32" t="s">
+        <v>153</v>
+      </c>
+      <c r="G22" s="32" t="s">
+        <v>174</v>
+      </c>
+      <c r="H22" s="76" t="s">
+        <v>103</v>
+      </c>
+      <c r="I22" s="32" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="8" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A23" s="75"/>
+      <c r="B23" s="75"/>
+      <c r="C23" s="76">
+        <v>14.4</v>
+      </c>
+      <c r="D23" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="32" t="s">
+        <v>154</v>
+      </c>
+      <c r="F23" s="32" t="s">
+        <v>155</v>
+      </c>
+      <c r="G23" s="32" t="s">
+        <v>175</v>
+      </c>
+      <c r="H23" s="76" t="s">
+        <v>103</v>
+      </c>
+      <c r="I23" s="32" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="8" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A24" s="75"/>
+      <c r="B24" s="75"/>
+      <c r="C24" s="76">
+        <v>14.5</v>
+      </c>
+      <c r="D24" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E24" s="32" t="s">
+        <v>156</v>
+      </c>
+      <c r="F24" s="32" t="s">
+        <v>157</v>
+      </c>
+      <c r="G24" s="32" t="s">
+        <v>176</v>
+      </c>
+      <c r="H24" s="76" t="s">
+        <v>103</v>
+      </c>
+      <c r="I24" s="32" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="8" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A25" s="75"/>
+      <c r="B25" s="75"/>
+      <c r="C25" s="76">
+        <v>14.6</v>
+      </c>
+      <c r="D25" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="32" t="s">
+        <v>158</v>
+      </c>
+      <c r="F25" s="32" t="s">
+        <v>159</v>
+      </c>
+      <c r="G25" s="32" t="s">
+        <v>182</v>
+      </c>
+      <c r="H25" s="76" t="s">
+        <v>103</v>
+      </c>
+      <c r="I25" s="32" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="8" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A26" s="75"/>
+      <c r="B26" s="75"/>
+      <c r="C26" s="76">
+        <v>14.7</v>
+      </c>
+      <c r="D26" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="32" t="s">
+        <v>160</v>
+      </c>
+      <c r="F26" s="32" t="s">
+        <v>161</v>
+      </c>
+      <c r="G26" s="32" t="s">
+        <v>177</v>
+      </c>
+      <c r="H26" s="76" t="s">
+        <v>103</v>
+      </c>
+      <c r="I26" s="32" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="8" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A27" s="75"/>
+      <c r="B27" s="75"/>
+      <c r="C27" s="76">
+        <v>14.8</v>
+      </c>
+      <c r="D27" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="32" t="s">
+        <v>162</v>
+      </c>
+      <c r="F27" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="G27" s="32" t="s">
+        <v>178</v>
+      </c>
+      <c r="H27" s="76" t="s">
+        <v>143</v>
+      </c>
+      <c r="I27" s="32" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="8" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A28" s="75"/>
+      <c r="B28" s="75"/>
+      <c r="C28" s="76">
+        <v>14.9</v>
+      </c>
+      <c r="D28" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="32" t="s">
+        <v>164</v>
+      </c>
+      <c r="F28" s="32" t="s">
+        <v>165</v>
+      </c>
+      <c r="G28" s="32" t="s">
+        <v>179</v>
+      </c>
+      <c r="H28" s="76" t="s">
+        <v>143</v>
+      </c>
+      <c r="I28" s="32" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="8" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A29" s="75"/>
+      <c r="B29" s="75"/>
+      <c r="C29" s="76">
+        <v>14.1</v>
+      </c>
+      <c r="D29" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="32" t="s">
+        <v>166</v>
+      </c>
+      <c r="F29" s="32" t="s">
+        <v>167</v>
+      </c>
+      <c r="G29" s="32" t="s">
+        <v>180</v>
+      </c>
+      <c r="H29" s="76" t="s">
+        <v>143</v>
+      </c>
+      <c r="I29" s="32" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" s="8" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A30" s="75"/>
+      <c r="B30" s="75"/>
+      <c r="C30" s="76">
+        <v>14.11</v>
+      </c>
+      <c r="D30" s="32" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="32" t="s">
+        <v>168</v>
+      </c>
+      <c r="F30" s="32" t="s">
+        <v>169</v>
+      </c>
+      <c r="G30" s="32" t="s">
+        <v>181</v>
+      </c>
+      <c r="H30" s="76" t="s">
+        <v>143</v>
+      </c>
+      <c r="I30" s="32" t="s">
+        <v>63</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
+      <c r="A31" s="63">
+        <v>15</v>
+      </c>
+      <c r="B31" s="63" t="s">
         <v>64</v>
       </c>
-      <c r="G20" s="34" t="s">
+      <c r="C31" s="23">
+        <v>15.1</v>
+      </c>
+      <c r="D31" s="24" t="s">
         <v>65</v>
       </c>
-      <c r="H20" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="I20" s="24" t="s">
+      <c r="E31" s="24" t="s">
         <v>66</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="57"/>
-      <c r="B21" s="57"/>
-      <c r="C21" s="23">
-        <v>14.2</v>
-      </c>
-      <c r="D21" s="24" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="24" t="s">
+      <c r="F31" s="24" t="s">
         <v>67</v>
       </c>
-      <c r="F21" s="24" t="s">
+      <c r="G31" s="33" t="s">
         <v>68</v>
       </c>
-      <c r="G21" s="34" t="s">
+      <c r="H31" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="I31" s="24" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
+      <c r="A32" s="60"/>
+      <c r="B32" s="60"/>
+      <c r="C32" s="23">
+        <v>15.2</v>
+      </c>
+      <c r="D32" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="E32" s="24" t="s">
         <v>69</v>
       </c>
-      <c r="H21" s="23" t="s">
-        <v>110</v>
-      </c>
-      <c r="I21" s="24" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="58">
-        <v>15</v>
-      </c>
-      <c r="B22" s="58" t="s">
+      <c r="F32" s="24" t="s">
         <v>70</v>
       </c>
-      <c r="C22" s="25">
-        <v>15.1</v>
-      </c>
-      <c r="D22" s="26" t="s">
+      <c r="G32" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="E22" s="26" t="s">
+      <c r="H32" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="I32" s="24" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="33" spans="1:12" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
+      <c r="A33" s="60"/>
+      <c r="B33" s="60"/>
+      <c r="C33" s="23">
+        <v>15.3</v>
+      </c>
+      <c r="D33" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="E33" s="24" t="s">
         <v>72</v>
       </c>
-      <c r="F22" s="26" t="s">
+      <c r="F33" s="24" t="s">
         <v>73</v>
       </c>
-      <c r="G22" s="35" t="s">
+      <c r="G33" s="33" t="s">
         <v>74</v>
       </c>
-      <c r="H22" s="25"/>
-      <c r="I22" s="26"/>
-    </row>
-    <row r="23" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="56"/>
-      <c r="B23" s="56"/>
-      <c r="C23" s="25">
-        <v>15.2</v>
-      </c>
-      <c r="D23" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="E23" s="26" t="s">
+      <c r="H33" s="23" t="s">
+        <v>144</v>
+      </c>
+      <c r="I33" s="24" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="34" spans="1:12" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
+      <c r="A34" s="60"/>
+      <c r="B34" s="60"/>
+      <c r="C34" s="23">
+        <v>15.4</v>
+      </c>
+      <c r="D34" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="E34" s="24" t="s">
         <v>75</v>
       </c>
-      <c r="F23" s="26" t="s">
+      <c r="F34" s="24" t="s">
         <v>76</v>
       </c>
-      <c r="G23" s="35" t="s">
+      <c r="G34" s="33" t="s">
         <v>77</v>
       </c>
-      <c r="H23" s="25"/>
-      <c r="I23" s="26"/>
-    </row>
-    <row r="24" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="56"/>
-      <c r="B24" s="56"/>
-      <c r="C24" s="25">
-        <v>15.3</v>
-      </c>
-      <c r="D24" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="E24" s="26" t="s">
+      <c r="H34" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="I34" s="24" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="35" spans="1:12" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
+      <c r="A35" s="58"/>
+      <c r="B35" s="58"/>
+      <c r="C35" s="23">
+        <v>15.5</v>
+      </c>
+      <c r="D35" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="E35" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="F24" s="26" t="s">
+      <c r="F35" s="24" t="s">
         <v>79</v>
       </c>
-      <c r="G24" s="35" t="s">
+      <c r="G35" s="33" t="s">
         <v>80</v>
       </c>
-      <c r="H24" s="25"/>
-      <c r="I24" s="26"/>
-    </row>
-    <row r="25" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="56"/>
-      <c r="B25" s="56"/>
-      <c r="C25" s="25">
-        <v>15.4</v>
-      </c>
-      <c r="D25" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="E25" s="26" t="s">
+      <c r="H35" s="23" t="s">
+        <v>146</v>
+      </c>
+      <c r="I35" s="24" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="36" spans="1:12" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
+      <c r="A36" s="57">
+        <v>16</v>
+      </c>
+      <c r="B36" s="57" t="s">
         <v>81</v>
       </c>
-      <c r="F25" s="26" t="s">
+      <c r="C36" s="25">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="D36" s="26" t="s">
         <v>82</v>
       </c>
-      <c r="G25" s="35" t="s">
+      <c r="E36" s="26" t="s">
         <v>83</v>
       </c>
-      <c r="H25" s="25"/>
-      <c r="I25" s="26"/>
-    </row>
-    <row r="26" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="57"/>
-      <c r="B26" s="57"/>
-      <c r="C26" s="25">
-        <v>15.5</v>
-      </c>
-      <c r="D26" s="26" t="s">
-        <v>71</v>
-      </c>
-      <c r="E26" s="26" t="s">
+      <c r="F36" s="26" t="s">
         <v>84</v>
       </c>
-      <c r="F26" s="26" t="s">
+      <c r="G36" s="72" t="s">
         <v>85</v>
       </c>
-      <c r="G26" s="35" t="s">
+      <c r="H36" s="73" t="s">
+        <v>146</v>
+      </c>
+      <c r="I36" s="74" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="37" spans="1:12" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
+      <c r="A37" s="58"/>
+      <c r="B37" s="58"/>
+      <c r="C37" s="25">
+        <v>16.2</v>
+      </c>
+      <c r="D37" s="26" t="s">
         <v>86</v>
       </c>
-      <c r="H26" s="25"/>
-      <c r="I26" s="26"/>
-    </row>
-    <row r="27" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="65">
-        <v>16</v>
-      </c>
-      <c r="B27" s="65" t="s">
+      <c r="E37" s="26" t="s">
         <v>87</v>
       </c>
-      <c r="C27" s="27">
-        <v>16.100000000000001</v>
-      </c>
-      <c r="D27" s="28" t="s">
+      <c r="F37" s="26" t="s">
         <v>88</v>
       </c>
-      <c r="E27" s="28" t="s">
+      <c r="G37" s="34" t="s">
         <v>89</v>
       </c>
-      <c r="F27" s="28" t="s">
+      <c r="H37" s="73" t="s">
+        <v>146</v>
+      </c>
+      <c r="I37" s="74" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="38" spans="1:12" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
+      <c r="A38" s="71">
+        <v>17</v>
+      </c>
+      <c r="B38" s="71" t="s">
         <v>90</v>
       </c>
-      <c r="G27" s="36" t="s">
+      <c r="C38" s="9">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="D38" s="10" t="s">
         <v>91</v>
       </c>
-      <c r="H27" s="27"/>
-      <c r="I27" s="28"/>
-    </row>
-    <row r="28" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="57"/>
-      <c r="B28" s="57"/>
-      <c r="C28" s="27">
-        <v>16.2</v>
-      </c>
-      <c r="D28" s="28" t="s">
+      <c r="E38" s="44" t="s">
+        <v>170</v>
+      </c>
+      <c r="F38" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="E28" s="28" t="s">
+      <c r="G38" s="45" t="s">
+        <v>171</v>
+      </c>
+      <c r="H38" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="I38" s="44" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="39" spans="1:12" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
+      <c r="A39" s="60"/>
+      <c r="B39" s="60"/>
+      <c r="C39" s="9">
+        <v>17.2</v>
+      </c>
+      <c r="D39" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E39" s="44" t="s">
+        <v>113</v>
+      </c>
+      <c r="F39" s="10" t="s">
         <v>93</v>
       </c>
-      <c r="F28" s="28" t="s">
+      <c r="G39" s="45" t="s">
         <v>94</v>
       </c>
-      <c r="G28" s="36" t="s">
+      <c r="H39" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="I39" s="44" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12" s="8" customFormat="1" ht="39" x14ac:dyDescent="0.35">
+      <c r="A40" s="60"/>
+      <c r="B40" s="60"/>
+      <c r="C40" s="9">
+        <v>17.3</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E40" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="H28" s="27"/>
-      <c r="I28" s="28"/>
-    </row>
-    <row r="29" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="59">
-        <v>17</v>
-      </c>
-      <c r="B29" s="59" t="s">
+      <c r="F40" s="44" t="s">
+        <v>114</v>
+      </c>
+      <c r="G40" s="45" t="s">
+        <v>117</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="I40" s="44" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="41" spans="1:12" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
+      <c r="A41" s="60"/>
+      <c r="B41" s="60"/>
+      <c r="C41" s="9">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="D41" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E41" s="44" t="s">
+        <v>116</v>
+      </c>
+      <c r="F41" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="G41" s="45" t="s">
+        <v>121</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="I41" s="44" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="42" spans="1:12" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
+      <c r="A42" s="60"/>
+      <c r="B42" s="60"/>
+      <c r="C42" s="9">
+        <v>17.5</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E42" s="44" t="s">
+        <v>118</v>
+      </c>
+      <c r="F42" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="G42" s="45" t="s">
+        <v>120</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="I42" s="44" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="43" spans="1:12" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
+      <c r="A43" s="60"/>
+      <c r="B43" s="60"/>
+      <c r="C43" s="9">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E43" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="C29" s="9">
-        <v>17.100000000000001</v>
-      </c>
-      <c r="D29" s="10" t="s">
+      <c r="F43" s="44" t="s">
+        <v>122</v>
+      </c>
+      <c r="G43" s="45" t="s">
+        <v>123</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="I43" s="44" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="44" spans="1:12" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
+      <c r="A44" s="60"/>
+      <c r="B44" s="60"/>
+      <c r="C44" s="9">
+        <v>17.7</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="E44" s="10" t="s">
         <v>97</v>
       </c>
-      <c r="E29" s="46" t="s">
-        <v>98</v>
-      </c>
-      <c r="F29" s="10" t="s">
-        <v>99</v>
-      </c>
-      <c r="G29" s="47" t="s">
-        <v>120</v>
-      </c>
-      <c r="H29" s="9"/>
-      <c r="I29" s="46" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A30" s="56"/>
-      <c r="B30" s="56"/>
-      <c r="C30" s="9">
-        <v>17.2</v>
-      </c>
-      <c r="D30" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="E30" s="46" t="s">
-        <v>121</v>
-      </c>
-      <c r="F30" s="10" t="s">
-        <v>100</v>
-      </c>
-      <c r="G30" s="47" t="s">
-        <v>101</v>
-      </c>
-      <c r="H30" s="9"/>
-      <c r="I30" s="46" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A31" s="56"/>
-      <c r="B31" s="56"/>
-      <c r="C31" s="9">
-        <v>17.3</v>
-      </c>
-      <c r="D31" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="E31" s="10" t="s">
-        <v>102</v>
-      </c>
-      <c r="F31" s="46" t="s">
-        <v>122</v>
-      </c>
-      <c r="G31" s="47" t="s">
+      <c r="F44" s="44" t="s">
+        <v>124</v>
+      </c>
+      <c r="G44" s="45" t="s">
+        <v>131</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="I44" s="44" t="s">
         <v>125</v>
       </c>
-      <c r="H31" s="9"/>
-      <c r="I31" s="46" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="56"/>
-      <c r="B32" s="56"/>
-      <c r="C32" s="9">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="D32" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="E32" s="46" t="s">
-        <v>124</v>
-      </c>
-      <c r="F32" s="46" t="s">
-        <v>123</v>
-      </c>
-      <c r="G32" s="47" t="s">
-        <v>129</v>
-      </c>
-      <c r="H32" s="9"/>
-      <c r="I32" s="46" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="56"/>
-      <c r="B33" s="56"/>
-      <c r="C33" s="9">
-        <v>17.5</v>
-      </c>
-      <c r="D33" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="E33" s="46" t="s">
-        <v>126</v>
-      </c>
-      <c r="F33" s="46" t="s">
-        <v>127</v>
-      </c>
-      <c r="G33" s="47" t="s">
-        <v>128</v>
-      </c>
-      <c r="H33" s="9"/>
-      <c r="I33" s="46" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="56"/>
-      <c r="B34" s="56"/>
-      <c r="C34" s="9">
-        <v>17.600000000000001</v>
-      </c>
-      <c r="D34" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="E34" s="10" t="s">
-        <v>103</v>
-      </c>
-      <c r="F34" s="46" t="s">
-        <v>130</v>
-      </c>
-      <c r="G34" s="47" t="s">
-        <v>131</v>
-      </c>
-      <c r="H34" s="9"/>
-      <c r="I34" s="46" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="56"/>
-      <c r="B35" s="56"/>
-      <c r="C35" s="9">
-        <v>17.7</v>
-      </c>
-      <c r="D35" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="E35" s="10" t="s">
-        <v>104</v>
-      </c>
-      <c r="F35" s="46" t="s">
-        <v>132</v>
-      </c>
-      <c r="G35" s="47" t="s">
-        <v>139</v>
-      </c>
-      <c r="H35" s="9"/>
-      <c r="I35" s="46" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A36" s="2"/>
-      <c r="B36" s="3"/>
-      <c r="C36" s="3"/>
-      <c r="D36" s="3"/>
-      <c r="E36" s="3"/>
-      <c r="F36" s="3"/>
-      <c r="G36" s="4"/>
-      <c r="H36" s="6"/>
-      <c r="I36" s="3"/>
-    </row>
-    <row r="37" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A37" s="7"/>
-      <c r="B37" s="2"/>
-      <c r="C37" s="2"/>
-      <c r="D37" s="3"/>
-      <c r="E37" s="2"/>
-      <c r="F37" s="3"/>
-      <c r="G37" s="4"/>
-      <c r="H37" s="2"/>
-      <c r="I37" s="3"/>
-    </row>
-    <row r="38" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A38" s="7"/>
-      <c r="B38" s="2"/>
-      <c r="C38" s="2"/>
-      <c r="D38" s="3"/>
-      <c r="E38" s="2"/>
-      <c r="F38" s="3"/>
-      <c r="G38" s="3"/>
-      <c r="H38" s="2"/>
-      <c r="I38" s="3"/>
-    </row>
-    <row r="39" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A39" s="7"/>
-      <c r="B39" s="2"/>
-      <c r="C39" s="2"/>
-      <c r="D39" s="3"/>
-      <c r="E39" s="2"/>
-      <c r="F39" s="3"/>
-      <c r="G39" s="3"/>
-      <c r="H39" s="2"/>
-      <c r="I39" s="3"/>
-    </row>
-    <row r="40" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A40" s="7"/>
-    </row>
-    <row r="41" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A41" s="7"/>
+    </row>
+    <row r="45" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="2"/>
+      <c r="B45" s="3"/>
+      <c r="C45" s="3"/>
+      <c r="D45" s="3"/>
+      <c r="E45" s="3"/>
+      <c r="F45" s="3"/>
+      <c r="G45" s="4"/>
+      <c r="H45" s="6"/>
+      <c r="I45" s="3"/>
+    </row>
+    <row r="46" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A46" s="7"/>
+      <c r="B46" s="2"/>
+      <c r="C46" s="2"/>
+      <c r="D46" s="3"/>
+      <c r="E46" s="2"/>
+      <c r="F46" s="3"/>
+      <c r="G46" s="4"/>
+      <c r="H46" s="2"/>
+      <c r="I46" s="3"/>
+    </row>
+    <row r="47" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A47" s="7"/>
+      <c r="B47" s="2"/>
+      <c r="C47" s="2"/>
+      <c r="D47" s="3"/>
+      <c r="E47" s="2"/>
+      <c r="F47" s="3"/>
+      <c r="G47" s="3"/>
+      <c r="H47" s="2"/>
+      <c r="I47" s="3"/>
+    </row>
+    <row r="48" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.35">
+      <c r="A48" s="7"/>
+      <c r="B48" s="77"/>
+      <c r="C48" s="78"/>
+      <c r="D48" s="78"/>
+      <c r="E48" s="78"/>
+      <c r="F48" s="78"/>
+      <c r="G48" s="78"/>
+      <c r="H48" s="78"/>
+      <c r="I48" s="78"/>
+      <c r="J48" s="5"/>
+      <c r="K48" s="5"/>
+      <c r="L48" s="5"/>
+    </row>
+    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
+      <c r="A49" s="3"/>
+      <c r="B49" s="3"/>
+      <c r="C49" s="3"/>
+      <c r="E49" s="3"/>
+      <c r="H49" s="3"/>
+    </row>
+    <row r="50" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D50" s="2"/>
+      <c r="F50" s="2"/>
+      <c r="G50" s="2"/>
+      <c r="I50" s="2"/>
+    </row>
+    <row r="51" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D51" s="2"/>
+      <c r="F51" s="2"/>
+      <c r="G51" s="2"/>
+      <c r="I51" s="2"/>
+    </row>
+    <row r="52" spans="1:9" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A52" s="77"/>
+      <c r="B52" s="77"/>
+      <c r="C52" s="77"/>
+      <c r="D52" s="77"/>
+      <c r="E52" s="77"/>
+      <c r="F52" s="77"/>
+      <c r="G52" s="77"/>
+      <c r="H52" s="77"/>
+      <c r="I52" s="77"/>
+    </row>
+    <row r="53" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A53" s="3"/>
+      <c r="B53" s="3"/>
+      <c r="C53" s="3"/>
+      <c r="E53" s="3"/>
+      <c r="H53" s="3"/>
+    </row>
+    <row r="54" spans="1:9" ht="31" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D54" s="2"/>
+      <c r="F54" s="2"/>
+      <c r="G54" s="2"/>
+      <c r="I54" s="2"/>
+    </row>
+    <row r="55" spans="1:9" ht="35" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D55" s="2"/>
+      <c r="F55" s="2"/>
+      <c r="G55" s="2"/>
+      <c r="I55" s="2"/>
+    </row>
+    <row r="56" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A56" s="77"/>
+      <c r="B56" s="77"/>
+      <c r="C56" s="77"/>
+      <c r="D56" s="77"/>
+      <c r="E56" s="77"/>
+      <c r="F56" s="77"/>
+      <c r="G56" s="77"/>
+      <c r="H56" s="77"/>
+      <c r="I56" s="77"/>
+    </row>
+    <row r="57" spans="1:9" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="A57" s="3"/>
+      <c r="B57" s="3"/>
+      <c r="C57" s="3"/>
+      <c r="E57" s="3"/>
+      <c r="H57" s="3"/>
+    </row>
+    <row r="58" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="D58" s="2"/>
+      <c r="F58" s="2"/>
+      <c r="G58" s="2"/>
+      <c r="I58" s="2"/>
+    </row>
+    <row r="59" spans="1:9" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B59" s="3"/>
+      <c r="F59" s="2"/>
+      <c r="G59" s="2"/>
+      <c r="I59" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="I1:I19" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="25">
+    <mergeCell ref="A38:A44"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="B17:B19"/>
+    <mergeCell ref="B38:B44"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B5:B6"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A17:A19"/>
+    <mergeCell ref="A31:A35"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="D1:F1"/>
-    <mergeCell ref="A27:A28"/>
+    <mergeCell ref="A36:A37"/>
     <mergeCell ref="A13:A16"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="H1:H2"/>
-    <mergeCell ref="B22:B26"/>
+    <mergeCell ref="B31:B35"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A20:A21"/>
+    <mergeCell ref="A20:A30"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B20:B21"/>
-    <mergeCell ref="B27:B28"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="B5:B6"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="A22:A26"/>
-    <mergeCell ref="A29:A35"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="B29:B35"/>
+    <mergeCell ref="B20:B30"/>
+    <mergeCell ref="B36:B37"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Soubhanik/checkupp_product_backlog_final.xlsx
+++ b/Soubhanik/checkupp_product_backlog_final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30131"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Checkupp\CheckUpp\Soubhanik\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anodiam\2026\CheckUpp_Parent\CheckUpp\Soubhanik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B421AD34-2558-489C-B84F-60DF859C85DF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3EDB0C3-02C7-43A0-8C41-F3EFE5342C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -125,12 +125,36 @@
         </r>
       </text>
     </comment>
+    <comment ref="E20" authorId="0" shapeId="0" xr:uid="{3CA1A3BC-210A-4820-BB92-615ED01D6D27}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Anirban:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Invalid User Story: This is not an action by the user.</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="266" uniqueCount="183">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="188">
   <si>
     <t>Epic #</t>
   </si>
@@ -289,9 +313,6 @@
     <t>1. Book Appointment screen must be accessible after selecting 'No' on a health check
 2. Integration with HotDocs API via Railway must be in place
 3. Booking confirmation must be displayed on success</t>
-  </si>
-  <si>
-    <t>Mental Health Check</t>
   </si>
   <si>
     <t>complete the K-10 and DASS-21 mental health assessments</t>
@@ -737,6 +758,28 @@
     <t>1. App must display a success message after syncing
 2. User must be able to view the calendar event
 3. Appointment must exist in the selected calendar</t>
+  </si>
+  <si>
+    <t>logged in user navigating the Mental Health Assessment screen</t>
+  </si>
+  <si>
+    <t>Mental Health Assessment</t>
+  </si>
+  <si>
+    <t>have the data I enter in the available fields(K-10 score, DASS-21 Depression, DASS-21 Anxiety, etc) or used the toggle switches (difficulty falling asleep and frequent night waking) autosaved in the system if I tap the 'Back' button or close/remove the app from the background</t>
+  </si>
+  <si>
+    <t>I don't have to re-enter the data in the fields(K-10 score, DASS-21 Depression, DASS-21 Anxiety, etc.) or re-toggle the switches (difficulty falling asleep and frequent night waking) again</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. All entered assessment field values (e.g., K-10 score, DASS-21 Depression, DASS-21 Anxiety) must be automatically saved whenever the user enters or updates them.
+2. All toggle switch states (e.g., Difficulty Falling Asleep, Frequent Night Waking) must be automatically saved whenever they are changed.
+3. All autosaved assessment data must be restored when the user returns to the Mental Health Assessment screen after tapping the Back button.
+4. All autosaved assessment data must be restored when the user reopens the app after it has been closed or removed from the background.
+</t>
+  </si>
+  <si>
+    <t>5. The most recent changes made to all assessment fields and toggle switches must be displayed when the assessment is resumed, without requiring the user to re-enter the information.</t>
   </si>
 </sst>
 </file>
@@ -1051,7 +1094,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="82">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1146,9 +1189,6 @@
     <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
@@ -1208,6 +1248,41 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1222,64 +1297,41 @@
     <xf numFmtId="0" fontId="4" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1562,51 +1614,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L59"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:L61"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.90625" style="3" customWidth="1"/>
+    <col min="1" max="1" width="5.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.88671875" style="3" customWidth="1"/>
     <col min="5" max="5" width="65" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="41" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="52" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.6328125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="15.36328125" style="3" customWidth="1"/>
-    <col min="10" max="12" width="8.90625" style="5" customWidth="1"/>
-    <col min="13" max="16384" width="8.90625" style="5"/>
+    <col min="7" max="7" width="61.44140625" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="15.33203125" style="3" customWidth="1"/>
+    <col min="10" max="12" width="8.88671875" style="5" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" ht="39.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="64" t="s">
+    <row r="1" spans="1:9" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="65" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="53" t="s">
+      <c r="C1" s="65" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="53" t="s">
+      <c r="D1" s="65" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="66" t="s">
+      <c r="E1" s="67"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="74" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="53" t="s">
+      <c r="H1" s="65" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="53" t="s">
+      <c r="I1" s="65" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="58"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="54"/>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="60"/>
+      <c r="B2" s="66"/>
+      <c r="C2" s="66"/>
       <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
@@ -1616,188 +1668,188 @@
       <c r="F2" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="67"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
-    </row>
-    <row r="3" spans="1:9" s="8" customFormat="1" ht="78" x14ac:dyDescent="0.35">
-      <c r="A3" s="37" t="s">
-        <v>142</v>
-      </c>
-      <c r="B3" s="37" t="s">
-        <v>126</v>
+      <c r="G2" s="75"/>
+      <c r="H2" s="66"/>
+      <c r="I2" s="66"/>
+    </row>
+    <row r="3" spans="1:9" s="8" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="36" t="s">
+        <v>141</v>
+      </c>
+      <c r="B3" s="36" t="s">
+        <v>125</v>
       </c>
       <c r="C3" s="22">
         <v>13.2</v>
       </c>
-      <c r="D3" s="38" t="s">
+      <c r="D3" s="37" t="s">
+        <v>126</v>
+      </c>
+      <c r="E3" s="37" t="s">
         <v>127</v>
       </c>
-      <c r="E3" s="38" t="s">
+      <c r="F3" s="37" t="s">
         <v>128</v>
       </c>
-      <c r="F3" s="38" t="s">
+      <c r="G3" s="38" t="s">
+        <v>131</v>
+      </c>
+      <c r="H3" s="22" t="s">
+        <v>60</v>
+      </c>
+      <c r="I3" s="37" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="46">
+        <v>1</v>
+      </c>
+      <c r="B4" s="46" t="s">
+        <v>10</v>
+      </c>
+      <c r="C4" s="47">
+        <v>1.1000000000000001</v>
+      </c>
+      <c r="D4" s="48" t="s">
+        <v>11</v>
+      </c>
+      <c r="E4" s="48" t="s">
+        <v>103</v>
+      </c>
+      <c r="F4" s="48" t="s">
+        <v>104</v>
+      </c>
+      <c r="G4" s="49" t="s">
+        <v>105</v>
+      </c>
+      <c r="H4" s="47" t="s">
+        <v>12</v>
+      </c>
+      <c r="I4" s="48" t="s">
         <v>129</v>
       </c>
-      <c r="G3" s="39" t="s">
-        <v>132</v>
-      </c>
-      <c r="H3" s="22" t="s">
-        <v>61</v>
-      </c>
-      <c r="I3" s="38" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" s="8" customFormat="1" ht="52" x14ac:dyDescent="0.35">
-      <c r="A4" s="47">
-        <v>1</v>
-      </c>
-      <c r="B4" s="47" t="s">
-        <v>10</v>
-      </c>
-      <c r="C4" s="48">
-        <v>1.1000000000000001</v>
-      </c>
-      <c r="D4" s="49" t="s">
+    </row>
+    <row r="5" spans="1:9" s="35" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A5" s="62">
+        <v>3</v>
+      </c>
+      <c r="B5" s="62" t="s">
+        <v>13</v>
+      </c>
+      <c r="C5" s="34">
+        <v>3.1</v>
+      </c>
+      <c r="D5" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="49" t="s">
-        <v>104</v>
-      </c>
-      <c r="F4" s="49" t="s">
-        <v>105</v>
-      </c>
-      <c r="G4" s="50" t="s">
+      <c r="E5" s="40" t="s">
         <v>106</v>
       </c>
-      <c r="H4" s="48" t="s">
-        <v>12</v>
-      </c>
-      <c r="I4" s="49" t="s">
-        <v>130</v>
-      </c>
-    </row>
-    <row r="5" spans="1:9" s="36" customFormat="1" ht="78" x14ac:dyDescent="0.35">
-      <c r="A5" s="68">
-        <v>3</v>
-      </c>
-      <c r="B5" s="68" t="s">
-        <v>13</v>
-      </c>
-      <c r="C5" s="35">
-        <v>3.1</v>
-      </c>
-      <c r="D5" s="40" t="s">
+      <c r="F5" s="40" t="s">
+        <v>107</v>
+      </c>
+      <c r="G5" s="41" t="s">
+        <v>110</v>
+      </c>
+      <c r="H5" s="42" t="s">
+        <v>97</v>
+      </c>
+      <c r="I5" s="39" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" s="8" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A6" s="63"/>
+      <c r="B6" s="63"/>
+      <c r="C6" s="34">
+        <v>3.2</v>
+      </c>
+      <c r="D6" s="39" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="41" t="s">
-        <v>107</v>
-      </c>
-      <c r="F5" s="41" t="s">
+      <c r="E6" s="40" t="s">
         <v>108</v>
       </c>
-      <c r="G5" s="42" t="s">
+      <c r="F6" s="40" t="s">
+        <v>109</v>
+      </c>
+      <c r="G6" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="H5" s="43" t="s">
-        <v>98</v>
-      </c>
-      <c r="I5" s="40" t="s">
+      <c r="H6" s="34" t="s">
+        <v>97</v>
+      </c>
+      <c r="I6" s="39" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="8" customFormat="1" ht="78" x14ac:dyDescent="0.35">
-      <c r="A6" s="69"/>
-      <c r="B6" s="69"/>
-      <c r="C6" s="35">
-        <v>3.2</v>
-      </c>
-      <c r="D6" s="40" t="s">
-        <v>11</v>
-      </c>
-      <c r="E6" s="41" t="s">
-        <v>109</v>
-      </c>
-      <c r="F6" s="41" t="s">
-        <v>110</v>
-      </c>
-      <c r="G6" s="42" t="s">
-        <v>112</v>
-      </c>
-      <c r="H6" s="35" t="s">
-        <v>98</v>
-      </c>
-      <c r="I6" s="40" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="7" spans="1:9" s="8" customFormat="1" ht="117" x14ac:dyDescent="0.35">
-      <c r="A7" s="46">
+    <row r="7" spans="1:9" s="8" customFormat="1" ht="138" x14ac:dyDescent="0.3">
+      <c r="A7" s="45">
         <v>5</v>
       </c>
-      <c r="B7" s="46" t="s">
+      <c r="B7" s="45" t="s">
         <v>16</v>
       </c>
       <c r="C7" s="9">
         <v>5.2</v>
       </c>
       <c r="D7" s="10" t="s">
+        <v>133</v>
+      </c>
+      <c r="E7" s="10" t="s">
+        <v>135</v>
+      </c>
+      <c r="F7" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="G7" s="27" t="s">
         <v>136</v>
       </c>
-      <c r="F7" s="10" t="s">
-        <v>135</v>
-      </c>
-      <c r="G7" s="27" t="s">
-        <v>137</v>
-      </c>
       <c r="H7" s="11" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="I7" s="10" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
-      <c r="A8" s="61">
+    <row r="8" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="70">
         <v>6</v>
       </c>
-      <c r="B8" s="61" t="s">
+      <c r="B8" s="70" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="12">
         <v>6.1</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>127</v>
-      </c>
-      <c r="E8" s="51" t="s">
+        <v>126</v>
+      </c>
+      <c r="E8" s="50" t="s">
+        <v>137</v>
+      </c>
+      <c r="F8" s="50" t="s">
         <v>138</v>
       </c>
-      <c r="F8" s="51" t="s">
+      <c r="G8" s="51" t="s">
         <v>139</v>
       </c>
-      <c r="G8" s="52" t="s">
-        <v>140</v>
-      </c>
       <c r="H8" s="14" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I8" s="13" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="8" customFormat="1" ht="52" x14ac:dyDescent="0.35">
-      <c r="A9" s="58"/>
-      <c r="B9" s="58"/>
+    <row r="9" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="60"/>
+      <c r="B9" s="60"/>
       <c r="C9" s="12">
         <v>6.3</v>
       </c>
       <c r="D9" s="13" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E9" s="13" t="s">
         <v>20</v>
@@ -1806,25 +1858,25 @@
         <v>21</v>
       </c>
       <c r="G9" s="28" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="H9" s="12" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="I9" s="13"/>
     </row>
-    <row r="10" spans="1:9" s="8" customFormat="1" ht="52" x14ac:dyDescent="0.35">
-      <c r="A10" s="62">
+    <row r="10" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="61">
         <v>7</v>
       </c>
-      <c r="B10" s="62" t="s">
+      <c r="B10" s="61" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="15">
         <v>7.1</v>
       </c>
       <c r="D10" s="16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E10" s="16" t="s">
         <v>23</v>
@@ -1836,20 +1888,20 @@
         <v>25</v>
       </c>
       <c r="H10" s="17" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I10" s="16" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="8" customFormat="1" ht="52" x14ac:dyDescent="0.35">
-      <c r="A11" s="60"/>
-      <c r="B11" s="60"/>
+    <row r="11" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="58"/>
+      <c r="B11" s="58"/>
       <c r="C11" s="15">
         <v>7.2</v>
       </c>
       <c r="D11" s="16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E11" s="16" t="s">
         <v>27</v>
@@ -1861,20 +1913,20 @@
         <v>29</v>
       </c>
       <c r="H11" s="15" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I11" s="16" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="8" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A12" s="58"/>
-      <c r="B12" s="58"/>
+    <row r="12" spans="1:9" s="8" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="60"/>
+      <c r="B12" s="60"/>
       <c r="C12" s="15">
         <v>7.3</v>
       </c>
       <c r="D12" s="16" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="E12" s="16" t="s">
         <v>30</v>
@@ -1886,11 +1938,11 @@
         <v>32</v>
       </c>
       <c r="H12" s="15" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="I12" s="16"/>
     </row>
-    <row r="13" spans="1:9" s="8" customFormat="1" ht="82.75" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A13" s="59">
         <v>9</v>
       </c>
@@ -1915,9 +1967,9 @@
       <c r="H13" s="18"/>
       <c r="I13" s="19"/>
     </row>
-    <row r="14" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A14" s="60"/>
-      <c r="B14" s="60"/>
+    <row r="14" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="58"/>
+      <c r="B14" s="58"/>
       <c r="C14" s="18">
         <v>9.1999999999999993</v>
       </c>
@@ -1936,9 +1988,9 @@
       <c r="H14" s="18"/>
       <c r="I14" s="19"/>
     </row>
-    <row r="15" spans="1:9" s="8" customFormat="1" ht="27.65" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A15" s="60"/>
-      <c r="B15" s="60"/>
+    <row r="15" spans="1:9" s="8" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="58"/>
+      <c r="B15" s="58"/>
       <c r="C15" s="18">
         <v>9.3000000000000007</v>
       </c>
@@ -1959,9 +2011,9 @@
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A16" s="58"/>
-      <c r="B16" s="58"/>
+    <row r="16" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="60"/>
+      <c r="B16" s="60"/>
       <c r="C16" s="18">
         <v>9.4</v>
       </c>
@@ -1982,878 +2034,912 @@
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A17" s="70">
+    <row r="17" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="78">
         <v>12</v>
       </c>
-      <c r="B17" s="70" t="s">
-        <v>49</v>
+      <c r="B17" s="78" t="s">
+        <v>183</v>
       </c>
       <c r="C17" s="20">
         <v>12.1</v>
       </c>
       <c r="D17" s="21" t="s">
-        <v>15</v>
+        <v>126</v>
       </c>
       <c r="E17" s="21" t="s">
+        <v>49</v>
+      </c>
+      <c r="F17" s="21" t="s">
         <v>50</v>
       </c>
-      <c r="F17" s="21" t="s">
+      <c r="G17" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="G17" s="31" t="s">
+      <c r="H17" s="20" t="s">
         <v>52</v>
       </c>
-      <c r="H17" s="20" t="s">
+      <c r="I17" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="I17" s="21" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" s="8" customFormat="1" ht="55.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A18" s="60"/>
-      <c r="B18" s="60"/>
+    </row>
+    <row r="18" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="79"/>
+      <c r="B18" s="79"/>
       <c r="C18" s="20">
         <v>12.2</v>
       </c>
       <c r="D18" s="21" t="s">
-        <v>15</v>
+        <v>126</v>
       </c>
       <c r="E18" s="21" t="s">
+        <v>54</v>
+      </c>
+      <c r="F18" s="21" t="s">
         <v>55</v>
       </c>
-      <c r="F18" s="21" t="s">
+      <c r="G18" s="31" t="s">
         <v>56</v>
       </c>
-      <c r="G18" s="31" t="s">
-        <v>57</v>
-      </c>
       <c r="H18" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="I18" s="21" t="s">
         <v>53</v>
       </c>
-      <c r="I18" s="21" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" s="8" customFormat="1" ht="55.25" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A19" s="58"/>
-      <c r="B19" s="58"/>
+    </row>
+    <row r="19" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="79"/>
+      <c r="B19" s="79"/>
       <c r="C19" s="20">
         <v>12.3</v>
       </c>
       <c r="D19" s="21" t="s">
+        <v>126</v>
+      </c>
+      <c r="E19" s="21" t="s">
+        <v>57</v>
+      </c>
+      <c r="F19" s="21" t="s">
+        <v>58</v>
+      </c>
+      <c r="G19" s="31" t="s">
+        <v>59</v>
+      </c>
+      <c r="H19" s="20" t="s">
+        <v>52</v>
+      </c>
+      <c r="I19" s="21"/>
+    </row>
+    <row r="20" spans="1:9" s="8" customFormat="1" ht="138" x14ac:dyDescent="0.3">
+      <c r="A20" s="80"/>
+      <c r="B20" s="80"/>
+      <c r="C20" s="20">
+        <v>12.4</v>
+      </c>
+      <c r="D20" s="21" t="s">
+        <v>182</v>
+      </c>
+      <c r="E20" s="21" t="s">
+        <v>184</v>
+      </c>
+      <c r="F20" s="21" t="s">
+        <v>185</v>
+      </c>
+      <c r="G20" s="21" t="s">
+        <v>186</v>
+      </c>
+      <c r="H20" s="20"/>
+      <c r="I20" s="21"/>
+    </row>
+    <row r="21" spans="1:9" s="8" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="81"/>
+      <c r="B21" s="81"/>
+      <c r="C21" s="20"/>
+      <c r="D21" s="21"/>
+      <c r="E21" s="21"/>
+      <c r="F21" s="21"/>
+      <c r="G21" s="31" t="s">
+        <v>187</v>
+      </c>
+      <c r="H21" s="20"/>
+      <c r="I21" s="21"/>
+    </row>
+    <row r="22" spans="1:9" s="8" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="72">
+        <v>14</v>
+      </c>
+      <c r="B22" s="72" t="s">
+        <v>61</v>
+      </c>
+      <c r="C22" s="76">
+        <v>14.1</v>
+      </c>
+      <c r="D22" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="E19" s="21" t="s">
-        <v>58</v>
-      </c>
-      <c r="F19" s="21" t="s">
-        <v>59</v>
-      </c>
-      <c r="G19" s="31" t="s">
-        <v>60</v>
-      </c>
-      <c r="H19" s="20" t="s">
-        <v>53</v>
-      </c>
-      <c r="I19" s="21"/>
-    </row>
-    <row r="20" spans="1:9" s="8" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A20" s="65">
-        <v>14</v>
-      </c>
-      <c r="B20" s="65" t="s">
+      <c r="E22" s="77" t="s">
+        <v>146</v>
+      </c>
+      <c r="F22" s="77" t="s">
+        <v>147</v>
+      </c>
+      <c r="G22" s="77" t="s">
+        <v>171</v>
+      </c>
+      <c r="H22" s="76" t="s">
+        <v>102</v>
+      </c>
+      <c r="I22" s="77" t="s">
         <v>62</v>
       </c>
-      <c r="C20" s="76">
+    </row>
+    <row r="23" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="73"/>
+      <c r="B23" s="73"/>
+      <c r="C23" s="76">
+        <v>14.2</v>
+      </c>
+      <c r="D23" s="77" t="s">
+        <v>15</v>
+      </c>
+      <c r="E23" s="77" t="s">
+        <v>148</v>
+      </c>
+      <c r="F23" s="77" t="s">
+        <v>149</v>
+      </c>
+      <c r="G23" s="77" t="s">
+        <v>172</v>
+      </c>
+      <c r="H23" s="76" t="s">
+        <v>102</v>
+      </c>
+      <c r="I23" s="77" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="73"/>
+      <c r="B24" s="73"/>
+      <c r="C24" s="76">
+        <v>14.3</v>
+      </c>
+      <c r="D24" s="77" t="s">
+        <v>150</v>
+      </c>
+      <c r="E24" s="77" t="s">
+        <v>151</v>
+      </c>
+      <c r="F24" s="77" t="s">
+        <v>152</v>
+      </c>
+      <c r="G24" s="77" t="s">
+        <v>173</v>
+      </c>
+      <c r="H24" s="76" t="s">
+        <v>102</v>
+      </c>
+      <c r="I24" s="77" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="73"/>
+      <c r="B25" s="73"/>
+      <c r="C25" s="76">
+        <v>14.4</v>
+      </c>
+      <c r="D25" s="77" t="s">
+        <v>15</v>
+      </c>
+      <c r="E25" s="77" t="s">
+        <v>153</v>
+      </c>
+      <c r="F25" s="77" t="s">
+        <v>154</v>
+      </c>
+      <c r="G25" s="77" t="s">
+        <v>174</v>
+      </c>
+      <c r="H25" s="76" t="s">
+        <v>102</v>
+      </c>
+      <c r="I25" s="77" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="73"/>
+      <c r="B26" s="73"/>
+      <c r="C26" s="76">
+        <v>14.5</v>
+      </c>
+      <c r="D26" s="77" t="s">
+        <v>15</v>
+      </c>
+      <c r="E26" s="77" t="s">
+        <v>155</v>
+      </c>
+      <c r="F26" s="77" t="s">
+        <v>156</v>
+      </c>
+      <c r="G26" s="77" t="s">
+        <v>175</v>
+      </c>
+      <c r="H26" s="76" t="s">
+        <v>102</v>
+      </c>
+      <c r="I26" s="77" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="8" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="73"/>
+      <c r="B27" s="73"/>
+      <c r="C27" s="76">
+        <v>14.6</v>
+      </c>
+      <c r="D27" s="77" t="s">
+        <v>15</v>
+      </c>
+      <c r="E27" s="77" t="s">
+        <v>157</v>
+      </c>
+      <c r="F27" s="77" t="s">
+        <v>158</v>
+      </c>
+      <c r="G27" s="77" t="s">
+        <v>181</v>
+      </c>
+      <c r="H27" s="76" t="s">
+        <v>102</v>
+      </c>
+      <c r="I27" s="77" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="8" customFormat="1" ht="69" x14ac:dyDescent="0.3">
+      <c r="A28" s="73"/>
+      <c r="B28" s="73"/>
+      <c r="C28" s="76">
+        <v>14.7</v>
+      </c>
+      <c r="D28" s="77" t="s">
+        <v>15</v>
+      </c>
+      <c r="E28" s="77" t="s">
+        <v>159</v>
+      </c>
+      <c r="F28" s="77" t="s">
+        <v>160</v>
+      </c>
+      <c r="G28" s="77" t="s">
+        <v>176</v>
+      </c>
+      <c r="H28" s="76" t="s">
+        <v>102</v>
+      </c>
+      <c r="I28" s="77" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="73"/>
+      <c r="B29" s="73"/>
+      <c r="C29" s="76">
+        <v>14.8</v>
+      </c>
+      <c r="D29" s="77" t="s">
+        <v>15</v>
+      </c>
+      <c r="E29" s="77" t="s">
+        <v>161</v>
+      </c>
+      <c r="F29" s="77" t="s">
+        <v>162</v>
+      </c>
+      <c r="G29" s="77" t="s">
+        <v>177</v>
+      </c>
+      <c r="H29" s="76" t="s">
+        <v>142</v>
+      </c>
+      <c r="I29" s="77" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" s="8" customFormat="1" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="73"/>
+      <c r="B30" s="73"/>
+      <c r="C30" s="76">
+        <v>14.9</v>
+      </c>
+      <c r="D30" s="77" t="s">
+        <v>15</v>
+      </c>
+      <c r="E30" s="77" t="s">
+        <v>163</v>
+      </c>
+      <c r="F30" s="77" t="s">
+        <v>164</v>
+      </c>
+      <c r="G30" s="77" t="s">
+        <v>178</v>
+      </c>
+      <c r="H30" s="76" t="s">
+        <v>142</v>
+      </c>
+      <c r="I30" s="77" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" s="8" customFormat="1" ht="69" x14ac:dyDescent="0.3">
+      <c r="A31" s="73"/>
+      <c r="B31" s="73"/>
+      <c r="C31" s="76">
         <v>14.1</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D31" s="77" t="s">
         <v>15</v>
       </c>
-      <c r="E20" s="32" t="s">
-        <v>147</v>
-      </c>
-      <c r="F20" s="32" t="s">
-        <v>148</v>
-      </c>
-      <c r="G20" s="32" t="s">
-        <v>172</v>
-      </c>
-      <c r="H20" s="76" t="s">
-        <v>103</v>
-      </c>
-      <c r="I20" s="32" t="s">
+      <c r="E31" s="77" t="s">
+        <v>165</v>
+      </c>
+      <c r="F31" s="77" t="s">
+        <v>166</v>
+      </c>
+      <c r="G31" s="77" t="s">
+        <v>179</v>
+      </c>
+      <c r="H31" s="76" t="s">
+        <v>142</v>
+      </c>
+      <c r="I31" s="77" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="8" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="73"/>
+      <c r="B32" s="73"/>
+      <c r="C32" s="76">
+        <v>14.11</v>
+      </c>
+      <c r="D32" s="77" t="s">
+        <v>15</v>
+      </c>
+      <c r="E32" s="77" t="s">
+        <v>167</v>
+      </c>
+      <c r="F32" s="77" t="s">
+        <v>168</v>
+      </c>
+      <c r="G32" s="77" t="s">
+        <v>180</v>
+      </c>
+      <c r="H32" s="76" t="s">
+        <v>142</v>
+      </c>
+      <c r="I32" s="77" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="64">
+        <v>15</v>
+      </c>
+      <c r="B33" s="64" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="21" spans="1:9" s="8" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A21" s="75"/>
-      <c r="B21" s="75"/>
-      <c r="C21" s="76">
-        <v>14.2</v>
-      </c>
-      <c r="D21" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="E21" s="32" t="s">
-        <v>149</v>
-      </c>
-      <c r="F21" s="32" t="s">
-        <v>150</v>
-      </c>
-      <c r="G21" s="32" t="s">
-        <v>173</v>
-      </c>
-      <c r="H21" s="76" t="s">
-        <v>103</v>
-      </c>
-      <c r="I21" s="32" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" s="8" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A22" s="75"/>
-      <c r="B22" s="75"/>
-      <c r="C22" s="76">
-        <v>14.3</v>
-      </c>
-      <c r="D22" s="32" t="s">
-        <v>151</v>
-      </c>
-      <c r="E22" s="32" t="s">
-        <v>152</v>
-      </c>
-      <c r="F22" s="32" t="s">
-        <v>153</v>
-      </c>
-      <c r="G22" s="32" t="s">
-        <v>174</v>
-      </c>
-      <c r="H22" s="76" t="s">
-        <v>103</v>
-      </c>
-      <c r="I22" s="32" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" s="8" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A23" s="75"/>
-      <c r="B23" s="75"/>
-      <c r="C23" s="76">
-        <v>14.4</v>
-      </c>
-      <c r="D23" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" s="32" t="s">
-        <v>154</v>
-      </c>
-      <c r="F23" s="32" t="s">
-        <v>155</v>
-      </c>
-      <c r="G23" s="32" t="s">
-        <v>175</v>
-      </c>
-      <c r="H23" s="76" t="s">
-        <v>103</v>
-      </c>
-      <c r="I23" s="32" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" s="8" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A24" s="75"/>
-      <c r="B24" s="75"/>
-      <c r="C24" s="76">
-        <v>14.5</v>
-      </c>
-      <c r="D24" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="E24" s="32" t="s">
-        <v>156</v>
-      </c>
-      <c r="F24" s="32" t="s">
-        <v>157</v>
-      </c>
-      <c r="G24" s="32" t="s">
-        <v>176</v>
-      </c>
-      <c r="H24" s="76" t="s">
-        <v>103</v>
-      </c>
-      <c r="I24" s="32" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" s="8" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A25" s="75"/>
-      <c r="B25" s="75"/>
-      <c r="C25" s="76">
-        <v>14.6</v>
-      </c>
-      <c r="D25" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="E25" s="32" t="s">
-        <v>158</v>
-      </c>
-      <c r="F25" s="32" t="s">
-        <v>159</v>
-      </c>
-      <c r="G25" s="32" t="s">
-        <v>182</v>
-      </c>
-      <c r="H25" s="76" t="s">
-        <v>103</v>
-      </c>
-      <c r="I25" s="32" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" s="8" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A26" s="75"/>
-      <c r="B26" s="75"/>
-      <c r="C26" s="76">
-        <v>14.7</v>
-      </c>
-      <c r="D26" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="E26" s="32" t="s">
-        <v>160</v>
-      </c>
-      <c r="F26" s="32" t="s">
-        <v>161</v>
-      </c>
-      <c r="G26" s="32" t="s">
-        <v>177</v>
-      </c>
-      <c r="H26" s="76" t="s">
-        <v>103</v>
-      </c>
-      <c r="I26" s="32" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" s="8" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A27" s="75"/>
-      <c r="B27" s="75"/>
-      <c r="C27" s="76">
-        <v>14.8</v>
-      </c>
-      <c r="D27" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="E27" s="32" t="s">
-        <v>162</v>
-      </c>
-      <c r="F27" s="32" t="s">
-        <v>163</v>
-      </c>
-      <c r="G27" s="32" t="s">
-        <v>178</v>
-      </c>
-      <c r="H27" s="76" t="s">
+      <c r="C33" s="23">
+        <v>15.1</v>
+      </c>
+      <c r="D33" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="E33" s="24" t="s">
+        <v>65</v>
+      </c>
+      <c r="F33" s="24" t="s">
+        <v>66</v>
+      </c>
+      <c r="G33" s="32" t="s">
+        <v>67</v>
+      </c>
+      <c r="H33" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="I27" s="32" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" s="8" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A28" s="75"/>
-      <c r="B28" s="75"/>
-      <c r="C28" s="76">
-        <v>14.9</v>
-      </c>
-      <c r="D28" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="E28" s="32" t="s">
-        <v>164</v>
-      </c>
-      <c r="F28" s="32" t="s">
-        <v>165</v>
-      </c>
-      <c r="G28" s="32" t="s">
-        <v>179</v>
-      </c>
-      <c r="H28" s="76" t="s">
+      <c r="I33" s="24" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="58"/>
+      <c r="B34" s="58"/>
+      <c r="C34" s="23">
+        <v>15.2</v>
+      </c>
+      <c r="D34" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="E34" s="24" t="s">
+        <v>68</v>
+      </c>
+      <c r="F34" s="24" t="s">
+        <v>69</v>
+      </c>
+      <c r="G34" s="32" t="s">
+        <v>70</v>
+      </c>
+      <c r="H34" s="23" t="s">
         <v>143</v>
       </c>
-      <c r="I28" s="32" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" s="8" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A29" s="75"/>
-      <c r="B29" s="75"/>
-      <c r="C29" s="76">
-        <v>14.1</v>
-      </c>
-      <c r="D29" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="E29" s="32" t="s">
-        <v>166</v>
-      </c>
-      <c r="F29" s="32" t="s">
-        <v>167</v>
-      </c>
-      <c r="G29" s="32" t="s">
-        <v>180</v>
-      </c>
-      <c r="H29" s="76" t="s">
-        <v>143</v>
-      </c>
-      <c r="I29" s="32" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" s="8" customFormat="1" ht="55" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="75"/>
-      <c r="B30" s="75"/>
-      <c r="C30" s="76">
-        <v>14.11</v>
-      </c>
-      <c r="D30" s="32" t="s">
-        <v>15</v>
-      </c>
-      <c r="E30" s="32" t="s">
-        <v>168</v>
-      </c>
-      <c r="F30" s="32" t="s">
-        <v>169</v>
-      </c>
-      <c r="G30" s="32" t="s">
-        <v>181</v>
-      </c>
-      <c r="H30" s="76" t="s">
-        <v>143</v>
-      </c>
-      <c r="I30" s="32" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
-      <c r="A31" s="63">
-        <v>15</v>
-      </c>
-      <c r="B31" s="63" t="s">
-        <v>64</v>
-      </c>
-      <c r="C31" s="23">
-        <v>15.1</v>
-      </c>
-      <c r="D31" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="E31" s="24" t="s">
-        <v>66</v>
-      </c>
-      <c r="F31" s="24" t="s">
-        <v>67</v>
-      </c>
-      <c r="G31" s="33" t="s">
-        <v>68</v>
-      </c>
-      <c r="H31" s="23" t="s">
+      <c r="I34" s="24" t="s">
         <v>144</v>
       </c>
-      <c r="I31" s="24" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
-      <c r="A32" s="60"/>
-      <c r="B32" s="60"/>
-      <c r="C32" s="23">
-        <v>15.2</v>
-      </c>
-      <c r="D32" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="E32" s="24" t="s">
-        <v>69</v>
-      </c>
-      <c r="F32" s="24" t="s">
-        <v>70</v>
-      </c>
-      <c r="G32" s="33" t="s">
-        <v>71</v>
-      </c>
-      <c r="H32" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="I32" s="24" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="33" spans="1:12" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
-      <c r="A33" s="60"/>
-      <c r="B33" s="60"/>
-      <c r="C33" s="23">
-        <v>15.3</v>
-      </c>
-      <c r="D33" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="E33" s="24" t="s">
-        <v>72</v>
-      </c>
-      <c r="F33" s="24" t="s">
-        <v>73</v>
-      </c>
-      <c r="G33" s="33" t="s">
-        <v>74</v>
-      </c>
-      <c r="H33" s="23" t="s">
-        <v>144</v>
-      </c>
-      <c r="I33" s="24" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="34" spans="1:12" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
-      <c r="A34" s="60"/>
-      <c r="B34" s="60"/>
-      <c r="C34" s="23">
-        <v>15.4</v>
-      </c>
-      <c r="D34" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="E34" s="24" t="s">
-        <v>75</v>
-      </c>
-      <c r="F34" s="24" t="s">
-        <v>76</v>
-      </c>
-      <c r="G34" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="H34" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="I34" s="24" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="35" spans="1:12" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
+    </row>
+    <row r="35" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A35" s="58"/>
       <c r="B35" s="58"/>
       <c r="C35" s="23">
+        <v>15.3</v>
+      </c>
+      <c r="D35" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="E35" s="24" t="s">
+        <v>71</v>
+      </c>
+      <c r="F35" s="24" t="s">
+        <v>72</v>
+      </c>
+      <c r="G35" s="32" t="s">
+        <v>73</v>
+      </c>
+      <c r="H35" s="23" t="s">
+        <v>143</v>
+      </c>
+      <c r="I35" s="24" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="58"/>
+      <c r="B36" s="58"/>
+      <c r="C36" s="23">
+        <v>15.4</v>
+      </c>
+      <c r="D36" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="E36" s="24" t="s">
+        <v>74</v>
+      </c>
+      <c r="F36" s="24" t="s">
+        <v>75</v>
+      </c>
+      <c r="G36" s="32" t="s">
+        <v>76</v>
+      </c>
+      <c r="H36" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="I36" s="24" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="60"/>
+      <c r="B37" s="60"/>
+      <c r="C37" s="23">
         <v>15.5</v>
       </c>
-      <c r="D35" s="24" t="s">
-        <v>65</v>
-      </c>
-      <c r="E35" s="24" t="s">
+      <c r="D37" s="24" t="s">
+        <v>64</v>
+      </c>
+      <c r="E37" s="24" t="s">
+        <v>77</v>
+      </c>
+      <c r="F37" s="24" t="s">
         <v>78</v>
       </c>
-      <c r="F35" s="24" t="s">
+      <c r="G37" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="G35" s="33" t="s">
+      <c r="H37" s="23" t="s">
+        <v>145</v>
+      </c>
+      <c r="I37" s="24" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="69">
+        <v>16</v>
+      </c>
+      <c r="B38" s="69" t="s">
         <v>80</v>
       </c>
-      <c r="H35" s="23" t="s">
-        <v>146</v>
-      </c>
-      <c r="I35" s="24" t="s">
+      <c r="C38" s="25">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="D38" s="26" t="s">
+        <v>81</v>
+      </c>
+      <c r="E38" s="26" t="s">
+        <v>82</v>
+      </c>
+      <c r="F38" s="26" t="s">
+        <v>83</v>
+      </c>
+      <c r="G38" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="H38" s="53" t="s">
         <v>145</v>
       </c>
-    </row>
-    <row r="36" spans="1:12" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
-      <c r="A36" s="57">
-        <v>16</v>
-      </c>
-      <c r="B36" s="57" t="s">
-        <v>81</v>
-      </c>
-      <c r="C36" s="25">
-        <v>16.100000000000001</v>
-      </c>
-      <c r="D36" s="26" t="s">
-        <v>82</v>
-      </c>
-      <c r="E36" s="26" t="s">
-        <v>83</v>
-      </c>
-      <c r="F36" s="26" t="s">
-        <v>84</v>
-      </c>
-      <c r="G36" s="72" t="s">
-        <v>85</v>
-      </c>
-      <c r="H36" s="73" t="s">
-        <v>146</v>
-      </c>
-      <c r="I36" s="74" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="37" spans="1:12" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
-      <c r="A37" s="58"/>
-      <c r="B37" s="58"/>
-      <c r="C37" s="25">
-        <v>16.2</v>
-      </c>
-      <c r="D37" s="26" t="s">
-        <v>86</v>
-      </c>
-      <c r="E37" s="26" t="s">
-        <v>87</v>
-      </c>
-      <c r="F37" s="26" t="s">
-        <v>88</v>
-      </c>
-      <c r="G37" s="34" t="s">
-        <v>89</v>
-      </c>
-      <c r="H37" s="73" t="s">
-        <v>146</v>
-      </c>
-      <c r="I37" s="74" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="38" spans="1:12" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
-      <c r="A38" s="71">
-        <v>17</v>
-      </c>
-      <c r="B38" s="71" t="s">
-        <v>90</v>
-      </c>
-      <c r="C38" s="9">
-        <v>17.100000000000001</v>
-      </c>
-      <c r="D38" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E38" s="44" t="s">
-        <v>170</v>
-      </c>
-      <c r="F38" s="10" t="s">
-        <v>92</v>
-      </c>
-      <c r="G38" s="45" t="s">
-        <v>171</v>
-      </c>
-      <c r="H38" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="I38" s="44" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="39" spans="1:12" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
+      <c r="I38" s="54" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A39" s="60"/>
       <c r="B39" s="60"/>
-      <c r="C39" s="9">
+      <c r="C39" s="25">
+        <v>16.2</v>
+      </c>
+      <c r="D39" s="26" t="s">
+        <v>85</v>
+      </c>
+      <c r="E39" s="26" t="s">
+        <v>86</v>
+      </c>
+      <c r="F39" s="26" t="s">
+        <v>87</v>
+      </c>
+      <c r="G39" s="33" t="s">
+        <v>88</v>
+      </c>
+      <c r="H39" s="53" t="s">
+        <v>145</v>
+      </c>
+      <c r="I39" s="54" t="s">
+        <v>144</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="57">
+        <v>17</v>
+      </c>
+      <c r="B40" s="57" t="s">
+        <v>89</v>
+      </c>
+      <c r="C40" s="9">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="D40" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E40" s="43" t="s">
+        <v>169</v>
+      </c>
+      <c r="F40" s="10" t="s">
+        <v>91</v>
+      </c>
+      <c r="G40" s="44" t="s">
+        <v>170</v>
+      </c>
+      <c r="H40" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="I40" s="43" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="58"/>
+      <c r="B41" s="58"/>
+      <c r="C41" s="9">
         <v>17.2</v>
       </c>
-      <c r="D39" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E39" s="44" t="s">
+      <c r="D41" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E41" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="F41" s="10" t="s">
+        <v>92</v>
+      </c>
+      <c r="G41" s="44" t="s">
+        <v>93</v>
+      </c>
+      <c r="H41" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="I41" s="43" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" s="8" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A42" s="58"/>
+      <c r="B42" s="58"/>
+      <c r="C42" s="9">
+        <v>17.3</v>
+      </c>
+      <c r="D42" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E42" s="10" t="s">
+        <v>94</v>
+      </c>
+      <c r="F42" s="43" t="s">
         <v>113</v>
       </c>
-      <c r="F39" s="10" t="s">
-        <v>93</v>
-      </c>
-      <c r="G39" s="45" t="s">
-        <v>94</v>
-      </c>
-      <c r="H39" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="I39" s="44" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="40" spans="1:12" s="8" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A40" s="60"/>
-      <c r="B40" s="60"/>
-      <c r="C40" s="9">
-        <v>17.3</v>
-      </c>
-      <c r="D40" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E40" s="10" t="s">
+      <c r="G42" s="44" t="s">
+        <v>116</v>
+      </c>
+      <c r="H42" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="I42" s="43" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="58"/>
+      <c r="B43" s="58"/>
+      <c r="C43" s="9">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="D43" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E43" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="F43" s="43" t="s">
+        <v>114</v>
+      </c>
+      <c r="G43" s="44" t="s">
+        <v>120</v>
+      </c>
+      <c r="H43" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="I43" s="43" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="58"/>
+      <c r="B44" s="58"/>
+      <c r="C44" s="9">
+        <v>17.5</v>
+      </c>
+      <c r="D44" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E44" s="43" t="s">
+        <v>117</v>
+      </c>
+      <c r="F44" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="G44" s="44" t="s">
+        <v>119</v>
+      </c>
+      <c r="H44" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="I44" s="43" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="58"/>
+      <c r="B45" s="58"/>
+      <c r="C45" s="9">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="D45" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E45" s="10" t="s">
         <v>95</v>
       </c>
-      <c r="F40" s="44" t="s">
-        <v>114</v>
-      </c>
-      <c r="G40" s="45" t="s">
-        <v>117</v>
-      </c>
-      <c r="H40" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="I40" s="44" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="41" spans="1:12" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
-      <c r="A41" s="60"/>
-      <c r="B41" s="60"/>
-      <c r="C41" s="9">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="D41" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E41" s="44" t="s">
-        <v>116</v>
-      </c>
-      <c r="F41" s="44" t="s">
-        <v>115</v>
-      </c>
-      <c r="G41" s="45" t="s">
+      <c r="F45" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="H41" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="I41" s="44" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="42" spans="1:12" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
-      <c r="A42" s="60"/>
-      <c r="B42" s="60"/>
-      <c r="C42" s="9">
-        <v>17.5</v>
-      </c>
-      <c r="D42" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E42" s="44" t="s">
-        <v>118</v>
-      </c>
-      <c r="F42" s="44" t="s">
-        <v>119</v>
-      </c>
-      <c r="G42" s="45" t="s">
-        <v>120</v>
-      </c>
-      <c r="H42" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="I42" s="44" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="43" spans="1:12" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
-      <c r="A43" s="60"/>
-      <c r="B43" s="60"/>
-      <c r="C43" s="9">
-        <v>17.600000000000001</v>
-      </c>
-      <c r="D43" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E43" s="10" t="s">
+      <c r="G45" s="44" t="s">
+        <v>122</v>
+      </c>
+      <c r="H45" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="I45" s="43" t="s">
+        <v>124</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="58"/>
+      <c r="B46" s="58"/>
+      <c r="C46" s="9">
+        <v>17.7</v>
+      </c>
+      <c r="D46" s="10" t="s">
+        <v>90</v>
+      </c>
+      <c r="E46" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="F43" s="44" t="s">
-        <v>122</v>
-      </c>
-      <c r="G43" s="45" t="s">
+      <c r="F46" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="H43" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="I43" s="44" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="44" spans="1:12" s="8" customFormat="1" ht="26" x14ac:dyDescent="0.35">
-      <c r="A44" s="60"/>
-      <c r="B44" s="60"/>
-      <c r="C44" s="9">
-        <v>17.7</v>
-      </c>
-      <c r="D44" s="10" t="s">
-        <v>91</v>
-      </c>
-      <c r="E44" s="10" t="s">
-        <v>97</v>
-      </c>
-      <c r="F44" s="44" t="s">
+      <c r="G46" s="44" t="s">
+        <v>130</v>
+      </c>
+      <c r="H46" s="9" t="s">
+        <v>102</v>
+      </c>
+      <c r="I46" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="G44" s="45" t="s">
-        <v>131</v>
-      </c>
-      <c r="H44" s="9" t="s">
-        <v>103</v>
-      </c>
-      <c r="I44" s="44" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="45" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="2"/>
-      <c r="B45" s="3"/>
-      <c r="C45" s="3"/>
-      <c r="D45" s="3"/>
-      <c r="E45" s="3"/>
-      <c r="F45" s="3"/>
-      <c r="G45" s="4"/>
-      <c r="H45" s="6"/>
-      <c r="I45" s="3"/>
-    </row>
-    <row r="46" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A46" s="7"/>
-      <c r="B46" s="2"/>
-      <c r="C46" s="2"/>
-      <c r="D46" s="3"/>
-      <c r="E46" s="2"/>
-      <c r="F46" s="3"/>
-      <c r="G46" s="4"/>
-      <c r="H46" s="2"/>
-      <c r="I46" s="3"/>
-    </row>
-    <row r="47" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.35">
-      <c r="A47" s="7"/>
-      <c r="B47" s="2"/>
-      <c r="C47" s="2"/>
+    </row>
+    <row r="47" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A47" s="2"/>
+      <c r="B47" s="3"/>
+      <c r="C47" s="3"/>
       <c r="D47" s="3"/>
-      <c r="E47" s="2"/>
+      <c r="E47" s="3"/>
       <c r="F47" s="3"/>
-      <c r="G47" s="3"/>
-      <c r="H47" s="2"/>
+      <c r="G47" s="4"/>
+      <c r="H47" s="6"/>
       <c r="I47" s="3"/>
     </row>
-    <row r="48" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.35">
+    <row r="48" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A48" s="7"/>
-      <c r="B48" s="77"/>
-      <c r="C48" s="78"/>
-      <c r="D48" s="78"/>
-      <c r="E48" s="78"/>
-      <c r="F48" s="78"/>
-      <c r="G48" s="78"/>
-      <c r="H48" s="78"/>
-      <c r="I48" s="78"/>
-      <c r="J48" s="5"/>
-      <c r="K48" s="5"/>
-      <c r="L48" s="5"/>
-    </row>
-    <row r="49" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A49" s="3"/>
-      <c r="B49" s="3"/>
-      <c r="C49" s="3"/>
-      <c r="E49" s="3"/>
-      <c r="H49" s="3"/>
-    </row>
-    <row r="50" spans="1:9" ht="17" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D50" s="2"/>
-      <c r="F50" s="2"/>
-      <c r="G50" s="2"/>
-      <c r="I50" s="2"/>
-    </row>
-    <row r="51" spans="1:9" ht="14.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D51" s="2"/>
-      <c r="F51" s="2"/>
-      <c r="G51" s="2"/>
-      <c r="I51" s="2"/>
-    </row>
-    <row r="52" spans="1:9" ht="36.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A52" s="77"/>
-      <c r="B52" s="77"/>
-      <c r="C52" s="77"/>
-      <c r="D52" s="77"/>
-      <c r="E52" s="77"/>
-      <c r="F52" s="77"/>
-      <c r="G52" s="77"/>
-      <c r="H52" s="77"/>
-      <c r="I52" s="77"/>
-    </row>
-    <row r="53" spans="1:9" ht="36" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A53" s="3"/>
-      <c r="B53" s="3"/>
-      <c r="C53" s="3"/>
-      <c r="E53" s="3"/>
-      <c r="H53" s="3"/>
-    </row>
-    <row r="54" spans="1:9" ht="31" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D54" s="2"/>
-      <c r="F54" s="2"/>
-      <c r="G54" s="2"/>
-      <c r="I54" s="2"/>
-    </row>
-    <row r="55" spans="1:9" ht="35" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D55" s="2"/>
-      <c r="F55" s="2"/>
-      <c r="G55" s="2"/>
-      <c r="I55" s="2"/>
-    </row>
-    <row r="56" spans="1:9" ht="32" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="77"/>
-      <c r="B56" s="77"/>
-      <c r="C56" s="77"/>
-      <c r="D56" s="77"/>
-      <c r="E56" s="77"/>
-      <c r="F56" s="77"/>
-      <c r="G56" s="77"/>
-      <c r="H56" s="77"/>
-      <c r="I56" s="77"/>
-    </row>
-    <row r="57" spans="1:9" ht="33.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A57" s="3"/>
-      <c r="B57" s="3"/>
-      <c r="C57" s="3"/>
-      <c r="E57" s="3"/>
-      <c r="H57" s="3"/>
-    </row>
-    <row r="58" spans="1:9" ht="31.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="D58" s="2"/>
-      <c r="F58" s="2"/>
-      <c r="G58" s="2"/>
-      <c r="I58" s="2"/>
-    </row>
-    <row r="59" spans="1:9" ht="27.5" customHeight="1" x14ac:dyDescent="0.35">
+      <c r="B48" s="2"/>
+      <c r="C48" s="2"/>
+      <c r="D48" s="3"/>
+      <c r="E48" s="2"/>
+      <c r="F48" s="3"/>
+      <c r="G48" s="4"/>
+      <c r="H48" s="2"/>
+      <c r="I48" s="3"/>
+    </row>
+    <row r="49" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A49" s="7"/>
+      <c r="B49" s="2"/>
+      <c r="C49" s="2"/>
+      <c r="D49" s="3"/>
+      <c r="E49" s="2"/>
+      <c r="F49" s="3"/>
+      <c r="G49" s="3"/>
+      <c r="H49" s="2"/>
+      <c r="I49" s="3"/>
+    </row>
+    <row r="50" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A50" s="7"/>
+      <c r="B50" s="55"/>
+      <c r="C50" s="56"/>
+      <c r="D50" s="56"/>
+      <c r="E50" s="56"/>
+      <c r="F50" s="56"/>
+      <c r="G50" s="56"/>
+      <c r="H50" s="56"/>
+      <c r="I50" s="56"/>
+      <c r="J50" s="5"/>
+      <c r="K50" s="5"/>
+      <c r="L50" s="5"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A51" s="3"/>
+      <c r="B51" s="3"/>
+      <c r="C51" s="3"/>
+      <c r="E51" s="3"/>
+      <c r="H51" s="3"/>
+    </row>
+    <row r="52" spans="1:12" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D52" s="2"/>
+      <c r="F52" s="2"/>
+      <c r="G52" s="2"/>
+      <c r="I52" s="2"/>
+    </row>
+    <row r="53" spans="1:12" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D53" s="2"/>
+      <c r="F53" s="2"/>
+      <c r="G53" s="2"/>
+      <c r="I53" s="2"/>
+    </row>
+    <row r="54" spans="1:12" ht="36.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="55"/>
+      <c r="B54" s="55"/>
+      <c r="C54" s="55"/>
+      <c r="D54" s="55"/>
+      <c r="E54" s="55"/>
+      <c r="F54" s="55"/>
+      <c r="G54" s="55"/>
+      <c r="H54" s="55"/>
+      <c r="I54" s="55"/>
+    </row>
+    <row r="55" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A55" s="3"/>
+      <c r="B55" s="3"/>
+      <c r="C55" s="3"/>
+      <c r="E55" s="3"/>
+      <c r="H55" s="3"/>
+    </row>
+    <row r="56" spans="1:12" ht="31.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D56" s="2"/>
+      <c r="F56" s="2"/>
+      <c r="G56" s="2"/>
+      <c r="I56" s="2"/>
+    </row>
+    <row r="57" spans="1:12" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D57" s="2"/>
+      <c r="F57" s="2"/>
+      <c r="G57" s="2"/>
+      <c r="I57" s="2"/>
+    </row>
+    <row r="58" spans="1:12" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A58" s="55"/>
+      <c r="B58" s="55"/>
+      <c r="C58" s="55"/>
+      <c r="D58" s="55"/>
+      <c r="E58" s="55"/>
+      <c r="F58" s="55"/>
+      <c r="G58" s="55"/>
+      <c r="H58" s="55"/>
+      <c r="I58" s="55"/>
+    </row>
+    <row r="59" spans="1:12" ht="33.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A59" s="3"/>
       <c r="B59" s="3"/>
-      <c r="F59" s="2"/>
-      <c r="G59" s="2"/>
-      <c r="I59" s="2"/>
+      <c r="C59" s="3"/>
+      <c r="E59" s="3"/>
+      <c r="H59" s="3"/>
+    </row>
+    <row r="60" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="D60" s="2"/>
+      <c r="F60" s="2"/>
+      <c r="G60" s="2"/>
+      <c r="I60" s="2"/>
+    </row>
+    <row r="61" spans="1:12" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="B61" s="3"/>
+      <c r="F61" s="2"/>
+      <c r="G61" s="2"/>
+      <c r="I61" s="2"/>
     </row>
   </sheetData>
   <autoFilter ref="I1:I19" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="25">
-    <mergeCell ref="A38:A44"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="B17:B19"/>
-    <mergeCell ref="B38:B44"/>
-    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B22:B32"/>
+    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="A17:A20"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A17:A19"/>
-    <mergeCell ref="A31:A35"/>
+    <mergeCell ref="A33:A37"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="D1:F1"/>
-    <mergeCell ref="A36:A37"/>
     <mergeCell ref="A13:A16"/>
     <mergeCell ref="A8:A9"/>
     <mergeCell ref="B10:B12"/>
     <mergeCell ref="H1:H2"/>
-    <mergeCell ref="B31:B35"/>
+    <mergeCell ref="B33:B37"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A20:A30"/>
+    <mergeCell ref="A22:A32"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B20:B30"/>
-    <mergeCell ref="B36:B37"/>
+    <mergeCell ref="A40:A46"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="B40:B46"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A38:A39"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Soubhanik/checkupp_product_backlog_final.xlsx
+++ b/Soubhanik/checkupp_product_backlog_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anodiam\2026\CheckUpp_Parent\CheckUpp\Soubhanik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3EDB0C3-02C7-43A0-8C41-F3EFE5342C94}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6480953D-E16A-4C70-83B6-EA3AE4CB5417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -125,36 +125,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="E20" authorId="0" shapeId="0" xr:uid="{3CA1A3BC-210A-4820-BB92-615ED01D6D27}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Anirban:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Invalid User Story: This is not an action by the user.</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="271" uniqueCount="188">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="223">
   <si>
     <t>Epic #</t>
   </si>
@@ -779,7 +755,138 @@
 </t>
   </si>
   <si>
-    <t>5. The most recent changes made to all assessment fields and toggle switches must be displayed when the assessment is resumed, without requiring the user to re-enter the information.</t>
+    <t>logged in user revisiting the mental health assessment</t>
+  </si>
+  <si>
+    <t>I am informed that my autosaved data was restored.</t>
+  </si>
+  <si>
+    <t>see my previously entered data in available fields(K-10 score, DASS-21 Depression, DASS-21 Anxiety, etc) or the status of the toggle switches (difficulty falling asleep and frequent night waking) restored along with an affirming notification(toast)</t>
+  </si>
+  <si>
+    <t>1. Previously autosaved assessment data must be restored automatically when the logged-in user revisits the Mental Health Assessment screen.
+2. An affirming notification (toast) saying 'Data restored', indicating that the autosaved data has been restored must be displayed after the assessment data is successfully loaded and must not appear if no saved data exists.
+3. The restored values for all available fields and toggle switches must be identical to the most recently autosaved data. 
+4. The restored data and affirming notification must be visible without requiring any additional action from the user.</t>
+  </si>
+  <si>
+    <t>Cardiovascular Reading</t>
+  </si>
+  <si>
+    <t>logged in user navigating the Cardiovascular Reading screen</t>
+  </si>
+  <si>
+    <t>have the data I enter in the available fields(systolic, diastolic, heart rate, etc.)  autosaved in the system if I tap the 'Back' button or close/remove the app from the background</t>
+  </si>
+  <si>
+    <t>I don't have to re-enter the data in the fields(systolic, diastolic, heart rate, etc.) again</t>
+  </si>
+  <si>
+    <t>logged in user revisiting the Cardiovascular Reading</t>
+  </si>
+  <si>
+    <t>see my previously entered data in available fields(systolic, diastolic, heart rate, etc.) restored along with an affirming notification(toast)</t>
+  </si>
+  <si>
+    <t>1. Previously autosaved available data must be restored automatically when the logged-in user revisits the Cardiovascular Reading screen.
+2. An affirming notification (toast) saying 'Data restored', indicating that the autosaved data has been restored must be displayed after the assessment data is successfully loaded and must not appear if no saved data exists.
+3. The restored values for all available fields must be identical to the most recently autosaved data. 
+4. The restored data and affirming notification must be visible without requiring any additional action from the user.</t>
+  </si>
+  <si>
+    <t>1. All entered assessment field fields(systolic, diastolic, heart rate, etc.) must be automatically saved whenever the user enters or updates them.
+2. All autosaved assessment data must be restored when the user returns to the Cardiovascular Reading screen after tapping the Back button.
+3. All autosaved assessment data must be restored when the user reopens the app after it has been closed or removed from the background.</t>
+  </si>
+  <si>
+    <t>Diabetes Test</t>
+  </si>
+  <si>
+    <t>logged in user navigating the Diabetes Test screen</t>
+  </si>
+  <si>
+    <t>logged in user revisiting the Diabetes Test</t>
+  </si>
+  <si>
+    <t>have the data I enter in the available fields(fasting glucose, random glucose, etc.)  autosaved in the system if I tap the 'Back' button or close/remove the app from the background</t>
+  </si>
+  <si>
+    <t>see my previously entered data in available fields(fasting glucose, random glucose, etc.) restored along with an affirming notification(toast)</t>
+  </si>
+  <si>
+    <t>I don't have to re-enter the data in the fields(fasting glucose, random glucose, etc.) again</t>
+  </si>
+  <si>
+    <t>1. All entered assessment fields(fasting glucose, random glucose, etc.) must be automatically saved whenever the user enters or updates them.
+2. All autosaved assessment data must be restored when the user returns to the Diabetes Test screen after tapping the Back button.
+3. All autosaved assessment data must be restored when the user reopens the app after it has been closed or removed from the background.</t>
+  </si>
+  <si>
+    <t>1. Previously autosaved available data must be restored automatically when the logged-in user revisits the Diabetes Test screen.
+2. An affirming notification (toast) saying 'Data restored', indicating that the autosaved data has been restored must be displayed after the assessment data is successfully loaded and must not appear if no saved data exists.
+3. The restored values for all available fields must be identical to the most recently autosaved data. 
+4. The restored data and affirming notification must be visible without requiring any additional action from the user.</t>
+  </si>
+  <si>
+    <t>Vision Test</t>
+  </si>
+  <si>
+    <t>logged in user navigating the Vision Test screen</t>
+  </si>
+  <si>
+    <t>logged in user revisiting the Vision Test</t>
+  </si>
+  <si>
+    <t>1. Previously autosaved available data must be restored automatically when the logged-in user revisits the Vision Test screen.
+2. An affirming notification (toast) saying 'Data restored', indicating that the autosaved data has been restored must be displayed after the assessment data is successfully loaded and must not appear if no saved data exists.
+3. The restored values for all available fields must be identical to the most recently autosaved data. 
+4. The restored data and affirming notification must be visible without requiring any additional action from the user.</t>
+  </si>
+  <si>
+    <t>see my previously entered data in available fields(Right Eye, Left Eye, etc.) restored along with an affirming notification(toast)</t>
+  </si>
+  <si>
+    <t>I don't have to re-enter the data in the fields(Right Eye, Left Eye, etc.) again</t>
+  </si>
+  <si>
+    <t>have the data I enter in the available fields(Right Eye, Left Eye, etc.)  autosaved in the system if I tap the 'Back' button or close/remove the app from the background</t>
+  </si>
+  <si>
+    <t>1. All entered assessment fields(Right Eye, Left Eye, etc.) must be automatically saved whenever the user enters or updates them.
+2. All autosaved assessment data must be restored when the user returns to the Vision Test screen after tapping the Back button.
+3. All autosaved assessment data must be restored when the user reopens the app after it has been closed or removed from the background.</t>
+  </si>
+  <si>
+    <t>Dental Health Check</t>
+  </si>
+  <si>
+    <t>logged in user navigating the Dental Health Check screen</t>
+  </si>
+  <si>
+    <t>logged in user revisiting the Dental Health Check</t>
+  </si>
+  <si>
+    <t>1. Previously autosaved available data must be restored automatically when the logged-in user revisits the Dental Health Check screen.
+2. An affirming notification (toast) saying 'Data restored', indicating that the autosaved data has been restored must be displayed after the assessment data is successfully loaded and must not appear if no saved data exists.
+3. The restored values for all available fields must be identical to the most recently autosaved data. 
+4. The restored data and affirming notification must be visible without requiring any additional action from the user.</t>
+  </si>
+  <si>
+    <t>have the data I enter in the available fields (cavities, fillings, etc), used the toggle switches (Use mouthwash regularly) and the dropdown options (Brushing frequency and flossing frequency) autosaved in the system if I tap the 'Back' button or close/remove the app from the background</t>
+  </si>
+  <si>
+    <t>I don't have to re-enter the data in the fields (cavities, fillings, etc), re-toggle the switches (Use mouthwash regularly) and the re-use dropdown options (Brushing frequency and flossing frequency)</t>
+  </si>
+  <si>
+    <t>1. All entered dental health field values (e.g., cavities, fillings, etc.) must be automatically saved whenever they are entered or updated.
+2. All toggle switch states (e.g., Use Mouthwash Regularly) must be automatically saved whenever they are changed.
+3. All selected dropdown options (e.g., Brushing Frequency and Flossing Frequency) must be automatically saved whenever they are changed.
+4. All autosaved dental health data must be restored when the user returns to the Dental Health Check screen after tapping the Back button.
+5. All autosaved dental health data must be restored when the user reopens the app after it has been closed or removed from the background.
+6. The most recent values entered in all fields, toggle switches, and dropdown selections must be displayed when the Dental Health Check is resumed, without requiring the user to re-enter or reselect the information.</t>
+  </si>
+  <si>
+    <t>see my previously entered data in the available fields (e.g., cavities, fillings, etc.), the status of the toggle switch (Use Mouthwash Regularly), and the selected dropdown options (Brushing Frequency and Flossing Frequency) restored along with an affirming notification (toast)</t>
   </si>
 </sst>
 </file>
@@ -977,7 +1084,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="9">
+  <borders count="3">
     <border>
       <left/>
       <right/>
@@ -989,43 +1096,6 @@
       <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color indexed="64"/>
-      </left>
-      <right style="thin">
-        <color indexed="64"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color indexed="64"/>
-      </top>
-      <bottom style="thin">
-        <color indexed="64"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color indexed="64"/>
       </right>
@@ -1052,286 +1122,217 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom/>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top/>
-      <bottom style="thin">
-        <color auto="1"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color auto="1"/>
-      </left>
-      <right style="thin">
-        <color auto="1"/>
-      </right>
-      <top style="thin">
-        <color auto="1"/>
-      </top>
-      <bottom/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="82">
+  <cellXfs count="70">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="10" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="11" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="11" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="15" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="16" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="16" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="12" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="8" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1617,1309 +1618,1437 @@
   <dimension ref="A1:L61"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.88671875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.109375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.88671875" style="3" customWidth="1"/>
-    <col min="5" max="5" width="65" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="41" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="61.44140625" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.6640625" style="2" customWidth="1"/>
-    <col min="9" max="9" width="15.33203125" style="3" customWidth="1"/>
-    <col min="10" max="12" width="8.88671875" style="5" customWidth="1"/>
-    <col min="13" max="16384" width="8.88671875" style="5"/>
+    <col min="1" max="1" width="5.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="32.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.88671875" style="2" customWidth="1"/>
+    <col min="5" max="5" width="64.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="61.44140625" style="2" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="15.33203125" style="2" customWidth="1"/>
+    <col min="10" max="12" width="8.88671875" style="3" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="3"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="65" t="s">
+      <c r="B1" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="65" t="s">
+      <c r="C1" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="65" t="s">
+      <c r="D1" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="67"/>
-      <c r="F1" s="68"/>
-      <c r="G1" s="74" t="s">
+      <c r="E1" s="58"/>
+      <c r="F1" s="58"/>
+      <c r="G1" s="55" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="65" t="s">
+      <c r="H1" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="65" t="s">
+      <c r="I1" s="55" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="60"/>
-      <c r="B2" s="66"/>
-      <c r="C2" s="66"/>
-      <c r="D2" s="1" t="s">
+      <c r="A2" s="59"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
+      <c r="D2" s="60" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" s="60" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" s="60" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="75"/>
-      <c r="H2" s="66"/>
-      <c r="I2" s="66"/>
-    </row>
-    <row r="3" spans="1:9" s="8" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="36" t="s">
+      <c r="G2" s="55"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
+    </row>
+    <row r="3" spans="1:9" s="4" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="B3" s="36" t="s">
+      <c r="B3" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="C3" s="22">
+      <c r="C3" s="18">
         <v>13.2</v>
       </c>
-      <c r="D3" s="37" t="s">
+      <c r="D3" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="E3" s="37" t="s">
+      <c r="E3" s="31" t="s">
         <v>127</v>
       </c>
-      <c r="F3" s="37" t="s">
+      <c r="F3" s="31" t="s">
         <v>128</v>
       </c>
-      <c r="G3" s="38" t="s">
+      <c r="G3" s="32" t="s">
         <v>131</v>
       </c>
-      <c r="H3" s="22" t="s">
+      <c r="H3" s="18" t="s">
         <v>60</v>
       </c>
-      <c r="I3" s="37" t="s">
+      <c r="I3" s="31" t="s">
         <v>132</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="46">
+    <row r="4" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A4" s="61">
         <v>1</v>
       </c>
-      <c r="B4" s="46" t="s">
+      <c r="B4" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="C4" s="47">
+      <c r="C4" s="39">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D4" s="48" t="s">
+      <c r="D4" s="40" t="s">
         <v>11</v>
       </c>
-      <c r="E4" s="48" t="s">
+      <c r="E4" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="F4" s="48" t="s">
+      <c r="F4" s="40" t="s">
         <v>104</v>
       </c>
-      <c r="G4" s="49" t="s">
+      <c r="G4" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="H4" s="47" t="s">
+      <c r="H4" s="39" t="s">
         <v>12</v>
       </c>
-      <c r="I4" s="48" t="s">
+      <c r="I4" s="40" t="s">
         <v>129</v>
       </c>
     </row>
-    <row r="5" spans="1:9" s="35" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:9" s="29" customFormat="1" ht="69" x14ac:dyDescent="0.3">
       <c r="A5" s="62">
         <v>3</v>
       </c>
       <c r="B5" s="62" t="s">
         <v>13</v>
       </c>
-      <c r="C5" s="34">
+      <c r="C5" s="28">
         <v>3.1</v>
       </c>
-      <c r="D5" s="39" t="s">
+      <c r="D5" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="40" t="s">
+      <c r="E5" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="F5" s="40" t="s">
+      <c r="F5" s="34" t="s">
         <v>107</v>
       </c>
-      <c r="G5" s="41" t="s">
+      <c r="G5" s="35" t="s">
         <v>110</v>
       </c>
-      <c r="H5" s="42" t="s">
+      <c r="H5" s="36" t="s">
         <v>97</v>
       </c>
-      <c r="I5" s="39" t="s">
+      <c r="I5" s="33" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:9" s="8" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A6" s="63"/>
-      <c r="B6" s="63"/>
-      <c r="C6" s="34">
+    <row r="6" spans="1:9" s="4" customFormat="1" ht="69" x14ac:dyDescent="0.3">
+      <c r="A6" s="62"/>
+      <c r="B6" s="62"/>
+      <c r="C6" s="28">
         <v>3.2</v>
       </c>
-      <c r="D6" s="39" t="s">
+      <c r="D6" s="33" t="s">
         <v>11</v>
       </c>
-      <c r="E6" s="40" t="s">
+      <c r="E6" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="F6" s="40" t="s">
+      <c r="F6" s="34" t="s">
         <v>109</v>
       </c>
-      <c r="G6" s="41" t="s">
+      <c r="G6" s="35" t="s">
         <v>111</v>
       </c>
-      <c r="H6" s="34" t="s">
+      <c r="H6" s="28" t="s">
         <v>97</v>
       </c>
-      <c r="I6" s="39" t="s">
+      <c r="I6" s="33" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:9" s="8" customFormat="1" ht="138" x14ac:dyDescent="0.3">
-      <c r="A7" s="45">
+    <row r="7" spans="1:9" s="4" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="38">
         <v>5</v>
       </c>
-      <c r="B7" s="45" t="s">
+      <c r="B7" s="38" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="9">
+      <c r="C7" s="5">
         <v>5.2</v>
       </c>
-      <c r="D7" s="10" t="s">
+      <c r="D7" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="E7" s="10" t="s">
+      <c r="E7" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="F7" s="10" t="s">
+      <c r="F7" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="G7" s="27" t="s">
+      <c r="G7" s="23" t="s">
         <v>136</v>
       </c>
-      <c r="H7" s="11" t="s">
+      <c r="H7" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="I7" s="10" t="s">
+      <c r="I7" s="6" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="70">
+    <row r="8" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="49">
         <v>6</v>
       </c>
-      <c r="B8" s="70" t="s">
+      <c r="B8" s="49" t="s">
         <v>18</v>
       </c>
-      <c r="C8" s="12">
+      <c r="C8" s="8">
         <v>6.1</v>
       </c>
-      <c r="D8" s="13" t="s">
+      <c r="D8" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="E8" s="50" t="s">
+      <c r="E8" s="42" t="s">
         <v>137</v>
       </c>
-      <c r="F8" s="50" t="s">
+      <c r="F8" s="42" t="s">
         <v>138</v>
       </c>
-      <c r="G8" s="51" t="s">
+      <c r="G8" s="43" t="s">
         <v>139</v>
       </c>
-      <c r="H8" s="14" t="s">
+      <c r="H8" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="I8" s="13" t="s">
+      <c r="I8" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="60"/>
-      <c r="B9" s="60"/>
-      <c r="C9" s="12">
+    <row r="9" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="59"/>
+      <c r="B9" s="59"/>
+      <c r="C9" s="8">
         <v>6.3</v>
       </c>
-      <c r="D9" s="13" t="s">
+      <c r="D9" s="9" t="s">
         <v>126</v>
       </c>
-      <c r="E9" s="13" t="s">
+      <c r="E9" s="9" t="s">
         <v>20</v>
       </c>
-      <c r="F9" s="13" t="s">
+      <c r="F9" s="9" t="s">
         <v>21</v>
       </c>
-      <c r="G9" s="28" t="s">
+      <c r="G9" s="24" t="s">
         <v>140</v>
       </c>
-      <c r="H9" s="12" t="s">
+      <c r="H9" s="8" t="s">
         <v>99</v>
       </c>
-      <c r="I9" s="13"/>
-    </row>
-    <row r="10" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="61">
+      <c r="I9" s="9"/>
+    </row>
+    <row r="10" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="54">
         <v>7</v>
       </c>
-      <c r="B10" s="61" t="s">
+      <c r="B10" s="54" t="s">
         <v>22</v>
       </c>
-      <c r="C10" s="15">
+      <c r="C10" s="11">
         <v>7.1</v>
       </c>
-      <c r="D10" s="16" t="s">
+      <c r="D10" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="E10" s="16" t="s">
+      <c r="E10" s="12" t="s">
         <v>23</v>
       </c>
-      <c r="F10" s="16" t="s">
+      <c r="F10" s="12" t="s">
         <v>24</v>
       </c>
-      <c r="G10" s="29" t="s">
+      <c r="G10" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="H10" s="17" t="s">
+      <c r="H10" s="13" t="s">
         <v>100</v>
       </c>
-      <c r="I10" s="16" t="s">
+      <c r="I10" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="58"/>
-      <c r="B11" s="58"/>
-      <c r="C11" s="15">
+    <row r="11" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A11" s="59"/>
+      <c r="B11" s="59"/>
+      <c r="C11" s="11">
         <v>7.2</v>
       </c>
-      <c r="D11" s="16" t="s">
+      <c r="D11" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="E11" s="16" t="s">
+      <c r="E11" s="12" t="s">
         <v>27</v>
       </c>
-      <c r="F11" s="16" t="s">
+      <c r="F11" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="G11" s="29" t="s">
+      <c r="G11" s="25" t="s">
         <v>29</v>
       </c>
-      <c r="H11" s="15" t="s">
+      <c r="H11" s="11" t="s">
         <v>101</v>
       </c>
-      <c r="I11" s="16" t="s">
+      <c r="I11" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="12" spans="1:9" s="8" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="60"/>
-      <c r="B12" s="60"/>
-      <c r="C12" s="15">
+    <row r="12" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="59"/>
+      <c r="B12" s="59"/>
+      <c r="C12" s="11">
         <v>7.3</v>
       </c>
-      <c r="D12" s="16" t="s">
+      <c r="D12" s="12" t="s">
         <v>126</v>
       </c>
-      <c r="E12" s="16" t="s">
+      <c r="E12" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="16" t="s">
+      <c r="F12" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="29" t="s">
+      <c r="G12" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="15" t="s">
+      <c r="H12" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="I12" s="16"/>
-    </row>
-    <row r="13" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="59">
+      <c r="I12" s="12"/>
+    </row>
+    <row r="13" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A13" s="53">
         <v>9</v>
       </c>
-      <c r="B13" s="59" t="s">
+      <c r="B13" s="53" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="18">
+      <c r="C13" s="14">
         <v>9.1</v>
       </c>
-      <c r="D13" s="19" t="s">
+      <c r="D13" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="19" t="s">
+      <c r="E13" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="F13" s="19" t="s">
+      <c r="F13" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="G13" s="30" t="s">
+      <c r="G13" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="H13" s="18"/>
-      <c r="I13" s="19"/>
-    </row>
-    <row r="14" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="58"/>
-      <c r="B14" s="58"/>
-      <c r="C14" s="18">
+      <c r="H13" s="14"/>
+      <c r="I13" s="15"/>
+    </row>
+    <row r="14" spans="1:9" s="4" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="59"/>
+      <c r="B14" s="59"/>
+      <c r="C14" s="14">
         <v>9.1999999999999993</v>
       </c>
-      <c r="D14" s="19" t="s">
+      <c r="D14" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="19" t="s">
+      <c r="E14" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="19" t="s">
+      <c r="F14" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="30" t="s">
+      <c r="G14" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="18"/>
-      <c r="I14" s="19"/>
-    </row>
-    <row r="15" spans="1:9" s="8" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="58"/>
-      <c r="B15" s="58"/>
-      <c r="C15" s="18">
+      <c r="H14" s="14"/>
+      <c r="I14" s="15"/>
+    </row>
+    <row r="15" spans="1:9" s="4" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="59"/>
+      <c r="B15" s="59"/>
+      <c r="C15" s="14">
         <v>9.3000000000000007</v>
       </c>
-      <c r="D15" s="19" t="s">
+      <c r="D15" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="19" t="s">
+      <c r="E15" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="19" t="s">
+      <c r="F15" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="30" t="s">
+      <c r="G15" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="18"/>
-      <c r="I15" s="19" t="s">
+      <c r="H15" s="14"/>
+      <c r="I15" s="15" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="60"/>
-      <c r="B16" s="60"/>
-      <c r="C16" s="18">
+    <row r="16" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A16" s="59"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="14">
         <v>9.4</v>
       </c>
-      <c r="D16" s="19" t="s">
+      <c r="D16" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="19" t="s">
+      <c r="E16" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="19" t="s">
+      <c r="F16" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="30" t="s">
+      <c r="G16" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="H16" s="18"/>
-      <c r="I16" s="19" t="s">
+      <c r="H16" s="14"/>
+      <c r="I16" s="15" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:9" s="8" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="78">
+    <row r="17" spans="1:9" s="4" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="63">
         <v>12</v>
       </c>
-      <c r="B17" s="78" t="s">
+      <c r="B17" s="63" t="s">
         <v>183</v>
       </c>
-      <c r="C17" s="20">
+      <c r="C17" s="16">
         <v>12.1</v>
       </c>
-      <c r="D17" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="E17" s="21" t="s">
+      <c r="D17" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="E17" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="F17" s="21" t="s">
+      <c r="F17" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="G17" s="31" t="s">
+      <c r="G17" s="27" t="s">
         <v>51</v>
       </c>
-      <c r="H17" s="20" t="s">
+      <c r="H17" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="I17" s="21" t="s">
+      <c r="I17" s="17" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="79"/>
-      <c r="B18" s="79"/>
-      <c r="C18" s="20">
+    <row r="18" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="63"/>
+      <c r="B18" s="63"/>
+      <c r="C18" s="16">
         <v>12.2</v>
       </c>
-      <c r="D18" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="E18" s="21" t="s">
+      <c r="D18" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="E18" s="17" t="s">
         <v>54</v>
       </c>
-      <c r="F18" s="21" t="s">
+      <c r="F18" s="17" t="s">
         <v>55</v>
       </c>
-      <c r="G18" s="31" t="s">
+      <c r="G18" s="27" t="s">
         <v>56</v>
       </c>
-      <c r="H18" s="20" t="s">
+      <c r="H18" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="I18" s="21" t="s">
+      <c r="I18" s="17" t="s">
         <v>53</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="8" customFormat="1" ht="55.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="79"/>
-      <c r="B19" s="79"/>
-      <c r="C19" s="20">
+    <row r="19" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="63"/>
+      <c r="B19" s="63"/>
+      <c r="C19" s="16">
         <v>12.3</v>
       </c>
-      <c r="D19" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="E19" s="21" t="s">
+      <c r="D19" s="17" t="s">
+        <v>182</v>
+      </c>
+      <c r="E19" s="17" t="s">
         <v>57</v>
       </c>
-      <c r="F19" s="21" t="s">
+      <c r="F19" s="17" t="s">
         <v>58</v>
       </c>
-      <c r="G19" s="31" t="s">
+      <c r="G19" s="27" t="s">
         <v>59</v>
       </c>
-      <c r="H19" s="20" t="s">
+      <c r="H19" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="I19" s="21"/>
-    </row>
-    <row r="20" spans="1:9" s="8" customFormat="1" ht="138" x14ac:dyDescent="0.3">
-      <c r="A20" s="80"/>
-      <c r="B20" s="80"/>
-      <c r="C20" s="20">
+      <c r="I19" s="17"/>
+    </row>
+    <row r="20" spans="1:9" s="4" customFormat="1" ht="138" x14ac:dyDescent="0.3">
+      <c r="A20" s="63"/>
+      <c r="B20" s="63"/>
+      <c r="C20" s="16">
         <v>12.4</v>
       </c>
-      <c r="D20" s="21" t="s">
+      <c r="D20" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="E20" s="21" t="s">
+      <c r="E20" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="F20" s="21" t="s">
+      <c r="F20" s="17" t="s">
         <v>185</v>
       </c>
-      <c r="G20" s="21" t="s">
+      <c r="G20" s="17" t="s">
         <v>186</v>
       </c>
-      <c r="H20" s="20"/>
-      <c r="I20" s="21"/>
-    </row>
-    <row r="21" spans="1:9" s="8" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="81"/>
-      <c r="B21" s="81"/>
-      <c r="C21" s="20"/>
-      <c r="D21" s="21"/>
-      <c r="E21" s="21"/>
-      <c r="F21" s="21"/>
-      <c r="G21" s="31" t="s">
+      <c r="H20" s="16"/>
+      <c r="I20" s="17"/>
+    </row>
+    <row r="21" spans="1:9" s="4" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="63"/>
+      <c r="B21" s="63"/>
+      <c r="C21" s="16">
+        <v>12.5</v>
+      </c>
+      <c r="D21" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="H21" s="20"/>
-      <c r="I21" s="21"/>
-    </row>
-    <row r="22" spans="1:9" s="8" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="72">
+      <c r="E21" s="17" t="s">
+        <v>189</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>188</v>
+      </c>
+      <c r="G21" s="27" t="s">
+        <v>190</v>
+      </c>
+      <c r="H21" s="16"/>
+      <c r="I21" s="17"/>
+    </row>
+    <row r="22" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="50">
         <v>14</v>
       </c>
-      <c r="B22" s="72" t="s">
+      <c r="B22" s="50" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="76">
+      <c r="C22" s="47">
         <v>14.1</v>
       </c>
-      <c r="D22" s="77" t="s">
+      <c r="D22" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="E22" s="77" t="s">
+      <c r="E22" s="48" t="s">
         <v>146</v>
       </c>
-      <c r="F22" s="77" t="s">
+      <c r="F22" s="48" t="s">
         <v>147</v>
       </c>
-      <c r="G22" s="77" t="s">
+      <c r="G22" s="48" t="s">
         <v>171</v>
       </c>
-      <c r="H22" s="76" t="s">
+      <c r="H22" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="I22" s="77" t="s">
+      <c r="I22" s="48" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="73"/>
-      <c r="B23" s="73"/>
-      <c r="C23" s="76">
+    <row r="23" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="50"/>
+      <c r="B23" s="50"/>
+      <c r="C23" s="47">
         <v>14.2</v>
       </c>
-      <c r="D23" s="77" t="s">
+      <c r="D23" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="E23" s="77" t="s">
+      <c r="E23" s="48" t="s">
         <v>148</v>
       </c>
-      <c r="F23" s="77" t="s">
+      <c r="F23" s="48" t="s">
         <v>149</v>
       </c>
-      <c r="G23" s="77" t="s">
+      <c r="G23" s="48" t="s">
         <v>172</v>
       </c>
-      <c r="H23" s="76" t="s">
+      <c r="H23" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="I23" s="77" t="s">
+      <c r="I23" s="48" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="73"/>
-      <c r="B24" s="73"/>
-      <c r="C24" s="76">
+    <row r="24" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="50"/>
+      <c r="B24" s="50"/>
+      <c r="C24" s="47">
         <v>14.3</v>
       </c>
-      <c r="D24" s="77" t="s">
+      <c r="D24" s="48" t="s">
         <v>150</v>
       </c>
-      <c r="E24" s="77" t="s">
+      <c r="E24" s="48" t="s">
         <v>151</v>
       </c>
-      <c r="F24" s="77" t="s">
+      <c r="F24" s="48" t="s">
         <v>152</v>
       </c>
-      <c r="G24" s="77" t="s">
+      <c r="G24" s="48" t="s">
         <v>173</v>
       </c>
-      <c r="H24" s="76" t="s">
+      <c r="H24" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="I24" s="77" t="s">
+      <c r="I24" s="48" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A25" s="73"/>
-      <c r="B25" s="73"/>
-      <c r="C25" s="76">
+    <row r="25" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="50"/>
+      <c r="B25" s="50"/>
+      <c r="C25" s="47">
         <v>14.4</v>
       </c>
-      <c r="D25" s="77" t="s">
+      <c r="D25" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="E25" s="77" t="s">
+      <c r="E25" s="48" t="s">
         <v>153</v>
       </c>
-      <c r="F25" s="77" t="s">
+      <c r="F25" s="48" t="s">
         <v>154</v>
       </c>
-      <c r="G25" s="77" t="s">
+      <c r="G25" s="48" t="s">
         <v>174</v>
       </c>
-      <c r="H25" s="76" t="s">
+      <c r="H25" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="I25" s="77" t="s">
+      <c r="I25" s="48" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="73"/>
-      <c r="B26" s="73"/>
-      <c r="C26" s="76">
+    <row r="26" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A26" s="50"/>
+      <c r="B26" s="50"/>
+      <c r="C26" s="47">
         <v>14.5</v>
       </c>
-      <c r="D26" s="77" t="s">
+      <c r="D26" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="E26" s="77" t="s">
+      <c r="E26" s="48" t="s">
         <v>155</v>
       </c>
-      <c r="F26" s="77" t="s">
+      <c r="F26" s="48" t="s">
         <v>156</v>
       </c>
-      <c r="G26" s="77" t="s">
+      <c r="G26" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="H26" s="76" t="s">
+      <c r="H26" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="I26" s="77" t="s">
+      <c r="I26" s="48" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="8" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A27" s="73"/>
-      <c r="B27" s="73"/>
-      <c r="C27" s="76">
+    <row r="27" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A27" s="50"/>
+      <c r="B27" s="50"/>
+      <c r="C27" s="47">
         <v>14.6</v>
       </c>
-      <c r="D27" s="77" t="s">
+      <c r="D27" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="E27" s="77" t="s">
+      <c r="E27" s="48" t="s">
         <v>157</v>
       </c>
-      <c r="F27" s="77" t="s">
+      <c r="F27" s="48" t="s">
         <v>158</v>
       </c>
-      <c r="G27" s="77" t="s">
+      <c r="G27" s="48" t="s">
         <v>181</v>
       </c>
-      <c r="H27" s="76" t="s">
+      <c r="H27" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="I27" s="77" t="s">
+      <c r="I27" s="48" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="8" customFormat="1" ht="69" x14ac:dyDescent="0.3">
-      <c r="A28" s="73"/>
-      <c r="B28" s="73"/>
-      <c r="C28" s="76">
+    <row r="28" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A28" s="50"/>
+      <c r="B28" s="50"/>
+      <c r="C28" s="47">
         <v>14.7</v>
       </c>
-      <c r="D28" s="77" t="s">
+      <c r="D28" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="E28" s="77" t="s">
+      <c r="E28" s="48" t="s">
         <v>159</v>
       </c>
-      <c r="F28" s="77" t="s">
+      <c r="F28" s="48" t="s">
         <v>160</v>
       </c>
-      <c r="G28" s="77" t="s">
+      <c r="G28" s="48" t="s">
         <v>176</v>
       </c>
-      <c r="H28" s="76" t="s">
+      <c r="H28" s="47" t="s">
         <v>102</v>
       </c>
-      <c r="I28" s="77" t="s">
+      <c r="I28" s="48" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="8" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A29" s="73"/>
-      <c r="B29" s="73"/>
-      <c r="C29" s="76">
+    <row r="29" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A29" s="50"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="47">
         <v>14.8</v>
       </c>
-      <c r="D29" s="77" t="s">
+      <c r="D29" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="E29" s="77" t="s">
+      <c r="E29" s="48" t="s">
         <v>161</v>
       </c>
-      <c r="F29" s="77" t="s">
+      <c r="F29" s="48" t="s">
         <v>162</v>
       </c>
-      <c r="G29" s="77" t="s">
+      <c r="G29" s="48" t="s">
         <v>177</v>
       </c>
-      <c r="H29" s="76" t="s">
+      <c r="H29" s="47" t="s">
         <v>142</v>
       </c>
-      <c r="I29" s="77" t="s">
+      <c r="I29" s="48" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="8" customFormat="1" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="73"/>
-      <c r="B30" s="73"/>
-      <c r="C30" s="76">
+    <row r="30" spans="1:9" s="4" customFormat="1" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="50"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="47">
         <v>14.9</v>
       </c>
-      <c r="D30" s="77" t="s">
+      <c r="D30" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="E30" s="77" t="s">
+      <c r="E30" s="48" t="s">
         <v>163</v>
       </c>
-      <c r="F30" s="77" t="s">
+      <c r="F30" s="48" t="s">
         <v>164</v>
       </c>
-      <c r="G30" s="77" t="s">
+      <c r="G30" s="48" t="s">
         <v>178</v>
       </c>
-      <c r="H30" s="76" t="s">
+      <c r="H30" s="47" t="s">
         <v>142</v>
       </c>
-      <c r="I30" s="77" t="s">
+      <c r="I30" s="48" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="8" customFormat="1" ht="69" x14ac:dyDescent="0.3">
-      <c r="A31" s="73"/>
-      <c r="B31" s="73"/>
-      <c r="C31" s="76">
+    <row r="31" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="50"/>
+      <c r="B31" s="50"/>
+      <c r="C31" s="47">
         <v>14.1</v>
       </c>
-      <c r="D31" s="77" t="s">
+      <c r="D31" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="E31" s="77" t="s">
+      <c r="E31" s="48" t="s">
         <v>165</v>
       </c>
-      <c r="F31" s="77" t="s">
+      <c r="F31" s="48" t="s">
         <v>166</v>
       </c>
-      <c r="G31" s="77" t="s">
+      <c r="G31" s="48" t="s">
         <v>179</v>
       </c>
-      <c r="H31" s="76" t="s">
+      <c r="H31" s="47" t="s">
         <v>142</v>
       </c>
-      <c r="I31" s="77" t="s">
+      <c r="I31" s="48" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="8" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="73"/>
-      <c r="B32" s="73"/>
-      <c r="C32" s="76">
+    <row r="32" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A32" s="50"/>
+      <c r="B32" s="50"/>
+      <c r="C32" s="47">
         <v>14.11</v>
       </c>
-      <c r="D32" s="77" t="s">
+      <c r="D32" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="E32" s="77" t="s">
+      <c r="E32" s="48" t="s">
         <v>167</v>
       </c>
-      <c r="F32" s="77" t="s">
+      <c r="F32" s="48" t="s">
         <v>168</v>
       </c>
-      <c r="G32" s="77" t="s">
+      <c r="G32" s="48" t="s">
         <v>180</v>
       </c>
-      <c r="H32" s="76" t="s">
+      <c r="H32" s="47" t="s">
         <v>142</v>
       </c>
-      <c r="I32" s="77" t="s">
+      <c r="I32" s="48" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="64">
+    <row r="33" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="52">
         <v>15</v>
       </c>
-      <c r="B33" s="64" t="s">
+      <c r="B33" s="52" t="s">
         <v>63</v>
       </c>
-      <c r="C33" s="23">
+      <c r="C33" s="19">
         <v>15.1</v>
       </c>
-      <c r="D33" s="24" t="s">
+      <c r="D33" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="E33" s="24" t="s">
+      <c r="E33" s="20" t="s">
         <v>65</v>
       </c>
-      <c r="F33" s="24" t="s">
+      <c r="F33" s="20" t="s">
         <v>66</v>
       </c>
-      <c r="G33" s="32" t="s">
+      <c r="G33" s="20" t="s">
         <v>67</v>
       </c>
-      <c r="H33" s="23" t="s">
+      <c r="H33" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="I33" s="24" t="s">
+      <c r="I33" s="20" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="58"/>
-      <c r="B34" s="58"/>
-      <c r="C34" s="23">
+    <row r="34" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A34" s="59"/>
+      <c r="B34" s="59"/>
+      <c r="C34" s="19">
         <v>15.2</v>
       </c>
-      <c r="D34" s="24" t="s">
+      <c r="D34" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="E34" s="24" t="s">
+      <c r="E34" s="20" t="s">
         <v>68</v>
       </c>
-      <c r="F34" s="24" t="s">
+      <c r="F34" s="20" t="s">
         <v>69</v>
       </c>
-      <c r="G34" s="32" t="s">
+      <c r="G34" s="20" t="s">
         <v>70</v>
       </c>
-      <c r="H34" s="23" t="s">
+      <c r="H34" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="I34" s="24" t="s">
+      <c r="I34" s="20" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="23">
+    <row r="35" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="59"/>
+      <c r="B35" s="59"/>
+      <c r="C35" s="19">
         <v>15.3</v>
       </c>
-      <c r="D35" s="24" t="s">
+      <c r="D35" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="E35" s="24" t="s">
+      <c r="E35" s="20" t="s">
         <v>71</v>
       </c>
-      <c r="F35" s="24" t="s">
+      <c r="F35" s="20" t="s">
         <v>72</v>
       </c>
-      <c r="G35" s="32" t="s">
+      <c r="G35" s="20" t="s">
         <v>73</v>
       </c>
-      <c r="H35" s="23" t="s">
+      <c r="H35" s="19" t="s">
         <v>143</v>
       </c>
-      <c r="I35" s="24" t="s">
+      <c r="I35" s="20" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="58"/>
-      <c r="B36" s="58"/>
-      <c r="C36" s="23">
+    <row r="36" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="59"/>
+      <c r="B36" s="59"/>
+      <c r="C36" s="19">
         <v>15.4</v>
       </c>
-      <c r="D36" s="24" t="s">
+      <c r="D36" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="E36" s="24" t="s">
+      <c r="E36" s="20" t="s">
         <v>74</v>
       </c>
-      <c r="F36" s="24" t="s">
+      <c r="F36" s="20" t="s">
         <v>75</v>
       </c>
-      <c r="G36" s="32" t="s">
+      <c r="G36" s="20" t="s">
         <v>76</v>
       </c>
-      <c r="H36" s="23" t="s">
+      <c r="H36" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="I36" s="24" t="s">
+      <c r="I36" s="20" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="60"/>
-      <c r="B37" s="60"/>
-      <c r="C37" s="23">
+    <row r="37" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A37" s="59"/>
+      <c r="B37" s="59"/>
+      <c r="C37" s="19">
         <v>15.5</v>
       </c>
-      <c r="D37" s="24" t="s">
+      <c r="D37" s="20" t="s">
         <v>64</v>
       </c>
-      <c r="E37" s="24" t="s">
+      <c r="E37" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="F37" s="24" t="s">
+      <c r="F37" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="G37" s="32" t="s">
+      <c r="G37" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="H37" s="23" t="s">
+      <c r="H37" s="19" t="s">
         <v>145</v>
       </c>
-      <c r="I37" s="24" t="s">
+      <c r="I37" s="20" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="69">
+    <row r="38" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="51">
         <v>16</v>
       </c>
-      <c r="B38" s="69" t="s">
+      <c r="B38" s="51" t="s">
         <v>80</v>
       </c>
-      <c r="C38" s="25">
+      <c r="C38" s="21">
         <v>16.100000000000001</v>
       </c>
-      <c r="D38" s="26" t="s">
+      <c r="D38" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="E38" s="26" t="s">
+      <c r="E38" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="F38" s="26" t="s">
+      <c r="F38" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="G38" s="52" t="s">
+      <c r="G38" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="H38" s="53" t="s">
+      <c r="H38" s="44" t="s">
         <v>145</v>
       </c>
-      <c r="I38" s="54" t="s">
+      <c r="I38" s="45" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="60"/>
-      <c r="B39" s="60"/>
-      <c r="C39" s="25">
+    <row r="39" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="59"/>
+      <c r="B39" s="59"/>
+      <c r="C39" s="21">
         <v>16.2</v>
       </c>
-      <c r="D39" s="26" t="s">
+      <c r="D39" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="E39" s="26" t="s">
+      <c r="E39" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="F39" s="26" t="s">
+      <c r="F39" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="G39" s="33" t="s">
+      <c r="G39" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="H39" s="53" t="s">
+      <c r="H39" s="44" t="s">
         <v>145</v>
       </c>
-      <c r="I39" s="54" t="s">
+      <c r="I39" s="45" t="s">
         <v>144</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="57">
+    <row r="40" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="56">
         <v>17</v>
       </c>
-      <c r="B40" s="57" t="s">
+      <c r="B40" s="56" t="s">
         <v>89</v>
       </c>
-      <c r="C40" s="9">
+      <c r="C40" s="5">
         <v>17.100000000000001</v>
       </c>
-      <c r="D40" s="10" t="s">
+      <c r="D40" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E40" s="43" t="s">
+      <c r="E40" s="37" t="s">
         <v>169</v>
       </c>
-      <c r="F40" s="10" t="s">
+      <c r="F40" s="6" t="s">
         <v>91</v>
       </c>
-      <c r="G40" s="44" t="s">
+      <c r="G40" s="37" t="s">
         <v>170</v>
       </c>
-      <c r="H40" s="9" t="s">
+      <c r="H40" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="I40" s="43" t="s">
+      <c r="I40" s="37" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="58"/>
-      <c r="B41" s="58"/>
-      <c r="C41" s="9">
+    <row r="41" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="59"/>
+      <c r="B41" s="59"/>
+      <c r="C41" s="5">
         <v>17.2</v>
       </c>
-      <c r="D41" s="10" t="s">
+      <c r="D41" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E41" s="43" t="s">
+      <c r="E41" s="37" t="s">
         <v>112</v>
       </c>
-      <c r="F41" s="10" t="s">
+      <c r="F41" s="6" t="s">
         <v>92</v>
       </c>
-      <c r="G41" s="44" t="s">
+      <c r="G41" s="37" t="s">
         <v>93</v>
       </c>
-      <c r="H41" s="9" t="s">
+      <c r="H41" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="I41" s="43" t="s">
+      <c r="I41" s="37" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="8" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A42" s="58"/>
-      <c r="B42" s="58"/>
-      <c r="C42" s="9">
+    <row r="42" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="59"/>
+      <c r="B42" s="59"/>
+      <c r="C42" s="5">
         <v>17.3</v>
       </c>
-      <c r="D42" s="10" t="s">
+      <c r="D42" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E42" s="10" t="s">
+      <c r="E42" s="6" t="s">
         <v>94</v>
       </c>
-      <c r="F42" s="43" t="s">
+      <c r="F42" s="37" t="s">
         <v>113</v>
       </c>
-      <c r="G42" s="44" t="s">
+      <c r="G42" s="37" t="s">
         <v>116</v>
       </c>
-      <c r="H42" s="9" t="s">
+      <c r="H42" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="I42" s="43" t="s">
+      <c r="I42" s="37" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="43" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="58"/>
-      <c r="B43" s="58"/>
-      <c r="C43" s="9">
+    <row r="43" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="59"/>
+      <c r="B43" s="59"/>
+      <c r="C43" s="5">
         <v>17.399999999999999</v>
       </c>
-      <c r="D43" s="10" t="s">
+      <c r="D43" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E43" s="43" t="s">
+      <c r="E43" s="37" t="s">
         <v>115</v>
       </c>
-      <c r="F43" s="43" t="s">
+      <c r="F43" s="37" t="s">
         <v>114</v>
       </c>
-      <c r="G43" s="44" t="s">
+      <c r="G43" s="37" t="s">
         <v>120</v>
       </c>
-      <c r="H43" s="9" t="s">
+      <c r="H43" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="I43" s="43" t="s">
+      <c r="I43" s="37" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="44" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="58"/>
-      <c r="B44" s="58"/>
-      <c r="C44" s="9">
+    <row r="44" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A44" s="59"/>
+      <c r="B44" s="59"/>
+      <c r="C44" s="5">
         <v>17.5</v>
       </c>
-      <c r="D44" s="10" t="s">
+      <c r="D44" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E44" s="43" t="s">
+      <c r="E44" s="37" t="s">
         <v>117</v>
       </c>
-      <c r="F44" s="43" t="s">
+      <c r="F44" s="37" t="s">
         <v>118</v>
       </c>
-      <c r="G44" s="44" t="s">
+      <c r="G44" s="37" t="s">
         <v>119</v>
       </c>
-      <c r="H44" s="9" t="s">
+      <c r="H44" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="I44" s="43" t="s">
+      <c r="I44" s="37" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="45" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="58"/>
-      <c r="B45" s="58"/>
-      <c r="C45" s="9">
+    <row r="45" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="59"/>
+      <c r="B45" s="59"/>
+      <c r="C45" s="5">
         <v>17.600000000000001</v>
       </c>
-      <c r="D45" s="10" t="s">
+      <c r="D45" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E45" s="10" t="s">
+      <c r="E45" s="6" t="s">
         <v>95</v>
       </c>
-      <c r="F45" s="43" t="s">
+      <c r="F45" s="37" t="s">
         <v>121</v>
       </c>
-      <c r="G45" s="44" t="s">
+      <c r="G45" s="37" t="s">
         <v>122</v>
       </c>
-      <c r="H45" s="9" t="s">
+      <c r="H45" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="I45" s="43" t="s">
+      <c r="I45" s="37" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="46" spans="1:9" s="8" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="58"/>
-      <c r="B46" s="58"/>
-      <c r="C46" s="9">
+    <row r="46" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="59"/>
+      <c r="B46" s="59"/>
+      <c r="C46" s="5">
         <v>17.7</v>
       </c>
-      <c r="D46" s="10" t="s">
+      <c r="D46" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E46" s="10" t="s">
+      <c r="E46" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="F46" s="43" t="s">
+      <c r="F46" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="G46" s="44" t="s">
+      <c r="G46" s="37" t="s">
         <v>130</v>
       </c>
-      <c r="H46" s="9" t="s">
+      <c r="H46" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="I46" s="43" t="s">
+      <c r="I46" s="37" t="s">
         <v>124</v>
       </c>
     </row>
-    <row r="47" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A47" s="2"/>
-      <c r="B47" s="3"/>
-      <c r="C47" s="3"/>
-      <c r="D47" s="3"/>
-      <c r="E47" s="3"/>
-      <c r="F47" s="3"/>
-      <c r="G47" s="4"/>
-      <c r="H47" s="6"/>
-      <c r="I47" s="3"/>
-    </row>
-    <row r="48" spans="1:9" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A48" s="7"/>
-      <c r="B48" s="2"/>
-      <c r="C48" s="2"/>
-      <c r="D48" s="3"/>
-      <c r="E48" s="2"/>
-      <c r="F48" s="3"/>
-      <c r="G48" s="4"/>
-      <c r="H48" s="2"/>
-      <c r="I48" s="3"/>
-    </row>
-    <row r="49" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A49" s="7"/>
-      <c r="B49" s="2"/>
-      <c r="C49" s="2"/>
-      <c r="D49" s="3"/>
-      <c r="E49" s="2"/>
-      <c r="F49" s="3"/>
-      <c r="G49" s="3"/>
-      <c r="H49" s="2"/>
-      <c r="I49" s="3"/>
-    </row>
-    <row r="50" spans="1:12" s="8" customFormat="1" x14ac:dyDescent="0.3">
-      <c r="A50" s="7"/>
-      <c r="B50" s="55"/>
-      <c r="C50" s="56"/>
-      <c r="D50" s="56"/>
-      <c r="E50" s="56"/>
-      <c r="F50" s="56"/>
-      <c r="G50" s="56"/>
-      <c r="H50" s="56"/>
-      <c r="I50" s="56"/>
-      <c r="J50" s="5"/>
-      <c r="K50" s="5"/>
-      <c r="L50" s="5"/>
-    </row>
-    <row r="51" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A51" s="3"/>
-      <c r="B51" s="3"/>
-      <c r="C51" s="3"/>
-      <c r="E51" s="3"/>
-      <c r="H51" s="3"/>
-    </row>
-    <row r="52" spans="1:12" ht="16.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D52" s="2"/>
-      <c r="F52" s="2"/>
-      <c r="G52" s="2"/>
-      <c r="I52" s="2"/>
-    </row>
-    <row r="53" spans="1:12" ht="14.55" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D53" s="2"/>
-      <c r="F53" s="2"/>
-      <c r="G53" s="2"/>
-      <c r="I53" s="2"/>
-    </row>
-    <row r="54" spans="1:12" ht="36.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A54" s="55"/>
-      <c r="B54" s="55"/>
-      <c r="C54" s="55"/>
-      <c r="D54" s="55"/>
-      <c r="E54" s="55"/>
-      <c r="F54" s="55"/>
-      <c r="G54" s="55"/>
-      <c r="H54" s="55"/>
-      <c r="I54" s="55"/>
+    <row r="47" spans="1:9" s="4" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A47" s="64">
+        <v>18</v>
+      </c>
+      <c r="B47" s="65" t="s">
+        <v>191</v>
+      </c>
+      <c r="C47" s="66">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="D47" s="57" t="s">
+        <v>192</v>
+      </c>
+      <c r="E47" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="F47" s="57" t="s">
+        <v>194</v>
+      </c>
+      <c r="G47" s="57" t="s">
+        <v>198</v>
+      </c>
+      <c r="H47" s="66"/>
+      <c r="I47" s="67"/>
+    </row>
+    <row r="48" spans="1:9" s="4" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A48" s="64"/>
+      <c r="B48" s="65"/>
+      <c r="C48" s="68">
+        <v>18.2</v>
+      </c>
+      <c r="D48" s="57" t="s">
+        <v>195</v>
+      </c>
+      <c r="E48" s="57" t="s">
+        <v>196</v>
+      </c>
+      <c r="F48" s="57" t="s">
+        <v>188</v>
+      </c>
+      <c r="G48" s="57" t="s">
+        <v>197</v>
+      </c>
+      <c r="H48" s="66"/>
+      <c r="I48" s="67"/>
+    </row>
+    <row r="49" spans="1:12" s="4" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="64">
+        <v>19</v>
+      </c>
+      <c r="B49" s="65" t="s">
+        <v>199</v>
+      </c>
+      <c r="C49" s="66">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="D49" s="57" t="s">
+        <v>200</v>
+      </c>
+      <c r="E49" s="57" t="s">
+        <v>202</v>
+      </c>
+      <c r="F49" s="57" t="s">
+        <v>204</v>
+      </c>
+      <c r="G49" s="57" t="s">
+        <v>205</v>
+      </c>
+      <c r="H49" s="66"/>
+      <c r="I49" s="67"/>
+    </row>
+    <row r="50" spans="1:12" s="4" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A50" s="64"/>
+      <c r="B50" s="65"/>
+      <c r="C50" s="68">
+        <v>19.2</v>
+      </c>
+      <c r="D50" s="57" t="s">
+        <v>201</v>
+      </c>
+      <c r="E50" s="57" t="s">
+        <v>203</v>
+      </c>
+      <c r="F50" s="57" t="s">
+        <v>188</v>
+      </c>
+      <c r="G50" s="57" t="s">
+        <v>206</v>
+      </c>
+      <c r="H50" s="66"/>
+      <c r="I50" s="67"/>
+      <c r="J50" s="3"/>
+      <c r="K50" s="3"/>
+      <c r="L50" s="3"/>
+    </row>
+    <row r="51" spans="1:12" ht="104.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A51" s="64">
+        <v>20</v>
+      </c>
+      <c r="B51" s="65" t="s">
+        <v>207</v>
+      </c>
+      <c r="C51" s="66">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="D51" s="57" t="s">
+        <v>208</v>
+      </c>
+      <c r="E51" s="57" t="s">
+        <v>213</v>
+      </c>
+      <c r="F51" s="57" t="s">
+        <v>212</v>
+      </c>
+      <c r="G51" s="57" t="s">
+        <v>214</v>
+      </c>
+      <c r="H51" s="66"/>
+      <c r="I51" s="67"/>
+    </row>
+    <row r="52" spans="1:12" ht="135" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="64"/>
+      <c r="B52" s="65"/>
+      <c r="C52" s="68">
+        <v>20.2</v>
+      </c>
+      <c r="D52" s="57" t="s">
+        <v>209</v>
+      </c>
+      <c r="E52" s="57" t="s">
+        <v>211</v>
+      </c>
+      <c r="F52" s="57" t="s">
+        <v>188</v>
+      </c>
+      <c r="G52" s="57" t="s">
+        <v>210</v>
+      </c>
+      <c r="H52" s="66"/>
+      <c r="I52" s="67"/>
+    </row>
+    <row r="53" spans="1:12" ht="179.4" x14ac:dyDescent="0.3">
+      <c r="A53" s="64">
+        <v>21</v>
+      </c>
+      <c r="B53" s="65" t="s">
+        <v>215</v>
+      </c>
+      <c r="C53" s="66">
+        <v>21.1</v>
+      </c>
+      <c r="D53" s="57" t="s">
+        <v>216</v>
+      </c>
+      <c r="E53" s="57" t="s">
+        <v>219</v>
+      </c>
+      <c r="F53" s="57" t="s">
+        <v>220</v>
+      </c>
+      <c r="G53" s="57" t="s">
+        <v>221</v>
+      </c>
+      <c r="H53" s="66"/>
+      <c r="I53" s="67"/>
+    </row>
+    <row r="54" spans="1:12" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A54" s="64"/>
+      <c r="B54" s="65"/>
+      <c r="C54" s="68">
+        <v>21.2</v>
+      </c>
+      <c r="D54" s="57" t="s">
+        <v>217</v>
+      </c>
+      <c r="E54" s="69" t="s">
+        <v>222</v>
+      </c>
+      <c r="F54" s="57" t="s">
+        <v>188</v>
+      </c>
+      <c r="G54" s="57" t="s">
+        <v>218</v>
+      </c>
+      <c r="H54" s="66"/>
+      <c r="I54" s="67"/>
     </row>
     <row r="55" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="3"/>
-      <c r="B55" s="3"/>
-      <c r="C55" s="3"/>
-      <c r="E55" s="3"/>
-      <c r="H55" s="3"/>
+      <c r="A55" s="2"/>
+      <c r="B55" s="2"/>
+      <c r="C55" s="2"/>
+      <c r="E55" s="57"/>
+      <c r="H55" s="2"/>
     </row>
     <row r="56" spans="1:12" ht="31.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D56" s="2"/>
-      <c r="F56" s="2"/>
-      <c r="G56" s="2"/>
-      <c r="I56" s="2"/>
+      <c r="D56" s="1"/>
+      <c r="F56" s="1"/>
+      <c r="G56" s="1"/>
+      <c r="I56" s="1"/>
     </row>
     <row r="57" spans="1:12" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D57" s="2"/>
-      <c r="F57" s="2"/>
-      <c r="G57" s="2"/>
-      <c r="I57" s="2"/>
+      <c r="D57" s="1"/>
+      <c r="F57" s="1"/>
+      <c r="G57" s="1"/>
+      <c r="I57" s="1"/>
     </row>
     <row r="58" spans="1:12" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="55"/>
-      <c r="B58" s="55"/>
-      <c r="C58" s="55"/>
-      <c r="D58" s="55"/>
-      <c r="E58" s="55"/>
-      <c r="F58" s="55"/>
-      <c r="G58" s="55"/>
-      <c r="H58" s="55"/>
-      <c r="I58" s="55"/>
+      <c r="A58" s="46"/>
+      <c r="B58" s="46"/>
+      <c r="C58" s="46"/>
+      <c r="D58" s="46"/>
+      <c r="E58" s="46"/>
+      <c r="F58" s="46"/>
+      <c r="G58" s="46"/>
+      <c r="H58" s="46"/>
+      <c r="I58" s="46"/>
     </row>
     <row r="59" spans="1:12" ht="33.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="3"/>
-      <c r="B59" s="3"/>
-      <c r="C59" s="3"/>
-      <c r="E59" s="3"/>
-      <c r="H59" s="3"/>
+      <c r="A59" s="2"/>
+      <c r="B59" s="2"/>
+      <c r="C59" s="2"/>
+      <c r="E59" s="2"/>
+      <c r="H59" s="2"/>
     </row>
     <row r="60" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D60" s="2"/>
-      <c r="F60" s="2"/>
-      <c r="G60" s="2"/>
-      <c r="I60" s="2"/>
+      <c r="D60" s="1"/>
+      <c r="F60" s="1"/>
+      <c r="G60" s="1"/>
+      <c r="I60" s="1"/>
     </row>
     <row r="61" spans="1:12" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="B61" s="3"/>
-      <c r="F61" s="2"/>
-      <c r="G61" s="2"/>
-      <c r="I61" s="2"/>
+      <c r="B61" s="2"/>
+      <c r="F61" s="1"/>
+      <c r="G61" s="1"/>
+      <c r="I61" s="1"/>
     </row>
   </sheetData>
   <autoFilter ref="I1:I19" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
-  <mergeCells count="25">
-    <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B22:B32"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="B17:B20"/>
-    <mergeCell ref="A17:A20"/>
+  <mergeCells count="33">
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B53:B54"/>
+    <mergeCell ref="B47:B48"/>
+    <mergeCell ref="A47:A48"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="A40:A46"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="B40:B46"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B17:B21"/>
+    <mergeCell ref="A17:A21"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A33:A37"/>
@@ -2935,11 +3064,9 @@
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="A40:A46"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="B40:B46"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A38:A39"/>
+    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="B22:B32"/>
+    <mergeCell ref="B38:B39"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Soubhanik/checkupp_product_backlog_final.xlsx
+++ b/Soubhanik/checkupp_product_backlog_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anodiam\2026\CheckUpp_Parent\CheckUpp\Soubhanik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6480953D-E16A-4C70-83B6-EA3AE4CB5417}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F541787C-31D8-4746-8E0E-39AE90D3A9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -130,7 +130,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="223">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="224">
   <si>
     <t>Epic #</t>
   </si>
@@ -577,14 +577,7 @@
 d. Travel (age agnostic)</t>
   </si>
   <si>
-    <t>store health documents in the app, saved locally</t>
-  </si>
-  <si>
     <t>I can access them in app and in device's local file manager</t>
-  </si>
-  <si>
-    <t>1. User must have the option to save locally (mobile/pc)
-2. Uploaded document must be visible in the Document Wallet</t>
   </si>
   <si>
     <t>1. Document wallet must list all the uploaded documents with name and date
@@ -887,6 +880,16 @@
   </si>
   <si>
     <t>see my previously entered data in the available fields (e.g., cavities, fillings, etc.), the status of the toggle switch (Use Mouthwash Regularly), and the selected dropdown options (Brushing Frequency and Flossing Frequency) restored along with an affirming notification (toast)</t>
+  </si>
+  <si>
+    <t>logged in user navigating the Document Wallet screen</t>
+  </si>
+  <si>
+    <t>store health documents(reports) in the app's cloud storage and my local device</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. Document captured/scanned must be visible in the Document Wallet
+2. User must be able to click on the download icon to save the document/image in their local device storage </t>
   </si>
 </sst>
 </file>
@@ -1273,44 +1276,56 @@
     <xf numFmtId="0" fontId="5" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="4" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1321,18 +1336,6 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1632,50 +1635,50 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="59" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="59" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="55" t="s">
+      <c r="C1" s="59" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="55" t="s">
+      <c r="D1" s="59" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="58"/>
-      <c r="F1" s="58"/>
-      <c r="G1" s="55" t="s">
+      <c r="E1" s="60"/>
+      <c r="F1" s="60"/>
+      <c r="G1" s="59" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="55" t="s">
+      <c r="H1" s="59" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="55" t="s">
+      <c r="I1" s="59" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="59"/>
-      <c r="B2" s="59"/>
-      <c r="C2" s="59"/>
-      <c r="D2" s="60" t="s">
+      <c r="A2" s="58"/>
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="50" t="s">
         <v>7</v>
       </c>
-      <c r="E2" s="60" t="s">
+      <c r="E2" s="50" t="s">
         <v>8</v>
       </c>
-      <c r="F2" s="60" t="s">
+      <c r="F2" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="55"/>
-      <c r="H2" s="59"/>
-      <c r="I2" s="59"/>
+      <c r="G2" s="59"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
     </row>
     <row r="3" spans="1:9" s="4" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A3" s="30" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="B3" s="30" t="s">
         <v>125</v>
@@ -1703,10 +1706,10 @@
       </c>
     </row>
     <row r="4" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A4" s="61">
+      <c r="A4" s="51">
         <v>1</v>
       </c>
-      <c r="B4" s="61" t="s">
+      <c r="B4" s="51" t="s">
         <v>10</v>
       </c>
       <c r="C4" s="39">
@@ -1732,10 +1735,10 @@
       </c>
     </row>
     <row r="5" spans="1:9" s="29" customFormat="1" ht="69" x14ac:dyDescent="0.3">
-      <c r="A5" s="62">
+      <c r="A5" s="56">
         <v>3</v>
       </c>
-      <c r="B5" s="62" t="s">
+      <c r="B5" s="56" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="28">
@@ -1761,8 +1764,8 @@
       </c>
     </row>
     <row r="6" spans="1:9" s="4" customFormat="1" ht="69" x14ac:dyDescent="0.3">
-      <c r="A6" s="62"/>
-      <c r="B6" s="62"/>
+      <c r="A6" s="56"/>
+      <c r="B6" s="56"/>
       <c r="C6" s="28">
         <v>3.2</v>
       </c>
@@ -1814,27 +1817,27 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="49">
+    <row r="8" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="62">
         <v>6</v>
       </c>
-      <c r="B8" s="49" t="s">
+      <c r="B8" s="62" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="8">
         <v>6.1</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>126</v>
+        <v>221</v>
       </c>
       <c r="E8" s="42" t="s">
+        <v>222</v>
+      </c>
+      <c r="F8" s="42" t="s">
         <v>137</v>
       </c>
-      <c r="F8" s="42" t="s">
-        <v>138</v>
-      </c>
       <c r="G8" s="43" t="s">
-        <v>139</v>
+        <v>223</v>
       </c>
       <c r="H8" s="10" t="s">
         <v>99</v>
@@ -1844,13 +1847,13 @@
       </c>
     </row>
     <row r="9" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="59"/>
-      <c r="B9" s="59"/>
+      <c r="A9" s="58"/>
+      <c r="B9" s="58"/>
       <c r="C9" s="8">
-        <v>6.3</v>
+        <v>6.2</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>126</v>
+        <v>221</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>20</v>
@@ -1859,7 +1862,7 @@
         <v>21</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="H9" s="8" t="s">
         <v>99</v>
@@ -1867,10 +1870,10 @@
       <c r="I9" s="9"/>
     </row>
     <row r="10" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="54">
+      <c r="A10" s="63">
         <v>7</v>
       </c>
-      <c r="B10" s="54" t="s">
+      <c r="B10" s="63" t="s">
         <v>22</v>
       </c>
       <c r="C10" s="11">
@@ -1896,8 +1899,8 @@
       </c>
     </row>
     <row r="11" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="59"/>
-      <c r="B11" s="59"/>
+      <c r="A11" s="58"/>
+      <c r="B11" s="58"/>
       <c r="C11" s="11">
         <v>7.2</v>
       </c>
@@ -1921,8 +1924,8 @@
       </c>
     </row>
     <row r="12" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="59"/>
-      <c r="B12" s="59"/>
+      <c r="A12" s="58"/>
+      <c r="B12" s="58"/>
       <c r="C12" s="11">
         <v>7.3</v>
       </c>
@@ -1944,10 +1947,10 @@
       <c r="I12" s="12"/>
     </row>
     <row r="13" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="53">
+      <c r="A13" s="61">
         <v>9</v>
       </c>
-      <c r="B13" s="53" t="s">
+      <c r="B13" s="61" t="s">
         <v>33</v>
       </c>
       <c r="C13" s="14">
@@ -1969,8 +1972,8 @@
       <c r="I13" s="15"/>
     </row>
     <row r="14" spans="1:9" s="4" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="59"/>
-      <c r="B14" s="59"/>
+      <c r="A14" s="58"/>
+      <c r="B14" s="58"/>
       <c r="C14" s="14">
         <v>9.1999999999999993</v>
       </c>
@@ -1990,8 +1993,8 @@
       <c r="I14" s="15"/>
     </row>
     <row r="15" spans="1:9" s="4" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="59"/>
-      <c r="B15" s="59"/>
+      <c r="A15" s="58"/>
+      <c r="B15" s="58"/>
       <c r="C15" s="14">
         <v>9.3000000000000007</v>
       </c>
@@ -2013,8 +2016,8 @@
       </c>
     </row>
     <row r="16" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="59"/>
-      <c r="B16" s="59"/>
+      <c r="A16" s="58"/>
+      <c r="B16" s="58"/>
       <c r="C16" s="14">
         <v>9.4</v>
       </c>
@@ -2036,17 +2039,17 @@
       </c>
     </row>
     <row r="17" spans="1:9" s="4" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="63">
+      <c r="A17" s="67">
         <v>12</v>
       </c>
-      <c r="B17" s="63" t="s">
-        <v>183</v>
+      <c r="B17" s="67" t="s">
+        <v>181</v>
       </c>
       <c r="C17" s="16">
         <v>12.1</v>
       </c>
       <c r="D17" s="17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E17" s="17" t="s">
         <v>49</v>
@@ -2065,13 +2068,13 @@
       </c>
     </row>
     <row r="18" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="63"/>
-      <c r="B18" s="63"/>
+      <c r="A18" s="67"/>
+      <c r="B18" s="67"/>
       <c r="C18" s="16">
         <v>12.2</v>
       </c>
       <c r="D18" s="17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E18" s="17" t="s">
         <v>54</v>
@@ -2090,13 +2093,13 @@
       </c>
     </row>
     <row r="19" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="63"/>
-      <c r="B19" s="63"/>
+      <c r="A19" s="67"/>
+      <c r="B19" s="67"/>
       <c r="C19" s="16">
         <v>12.3</v>
       </c>
       <c r="D19" s="17" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="E19" s="17" t="s">
         <v>57</v>
@@ -2113,52 +2116,52 @@
       <c r="I19" s="17"/>
     </row>
     <row r="20" spans="1:9" s="4" customFormat="1" ht="138" x14ac:dyDescent="0.3">
-      <c r="A20" s="63"/>
-      <c r="B20" s="63"/>
+      <c r="A20" s="67"/>
+      <c r="B20" s="67"/>
       <c r="C20" s="16">
         <v>12.4</v>
       </c>
       <c r="D20" s="17" t="s">
+        <v>180</v>
+      </c>
+      <c r="E20" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="F20" s="17" t="s">
+        <v>183</v>
+      </c>
+      <c r="G20" s="17" t="s">
         <v>184</v>
-      </c>
-      <c r="F20" s="17" t="s">
-        <v>185</v>
-      </c>
-      <c r="G20" s="17" t="s">
-        <v>186</v>
       </c>
       <c r="H20" s="16"/>
       <c r="I20" s="17"/>
     </row>
     <row r="21" spans="1:9" s="4" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="63"/>
-      <c r="B21" s="63"/>
+      <c r="A21" s="67"/>
+      <c r="B21" s="67"/>
       <c r="C21" s="16">
         <v>12.5</v>
       </c>
       <c r="D21" s="17" t="s">
+        <v>185</v>
+      </c>
+      <c r="E21" s="17" t="s">
         <v>187</v>
       </c>
-      <c r="E21" s="17" t="s">
-        <v>189</v>
-      </c>
       <c r="F21" s="17" t="s">
+        <v>186</v>
+      </c>
+      <c r="G21" s="27" t="s">
         <v>188</v>
-      </c>
-      <c r="G21" s="27" t="s">
-        <v>190</v>
       </c>
       <c r="H21" s="16"/>
       <c r="I21" s="17"/>
     </row>
     <row r="22" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="50">
+      <c r="A22" s="64">
         <v>14</v>
       </c>
-      <c r="B22" s="50" t="s">
+      <c r="B22" s="64" t="s">
         <v>61</v>
       </c>
       <c r="C22" s="47">
@@ -2168,13 +2171,13 @@
         <v>15</v>
       </c>
       <c r="E22" s="48" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F22" s="48" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G22" s="48" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="H22" s="47" t="s">
         <v>102</v>
@@ -2184,8 +2187,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="50"/>
-      <c r="B23" s="50"/>
+      <c r="A23" s="64"/>
+      <c r="B23" s="64"/>
       <c r="C23" s="47">
         <v>14.2</v>
       </c>
@@ -2193,13 +2196,13 @@
         <v>15</v>
       </c>
       <c r="E23" s="48" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F23" s="48" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G23" s="48" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="H23" s="47" t="s">
         <v>102</v>
@@ -2209,22 +2212,22 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="50"/>
-      <c r="B24" s="50"/>
+      <c r="A24" s="64"/>
+      <c r="B24" s="64"/>
       <c r="C24" s="47">
         <v>14.3</v>
       </c>
       <c r="D24" s="48" t="s">
+        <v>148</v>
+      </c>
+      <c r="E24" s="48" t="s">
+        <v>149</v>
+      </c>
+      <c r="F24" s="48" t="s">
         <v>150</v>
       </c>
-      <c r="E24" s="48" t="s">
-        <v>151</v>
-      </c>
-      <c r="F24" s="48" t="s">
-        <v>152</v>
-      </c>
       <c r="G24" s="48" t="s">
-        <v>173</v>
+        <v>171</v>
       </c>
       <c r="H24" s="47" t="s">
         <v>102</v>
@@ -2234,8 +2237,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A25" s="50"/>
-      <c r="B25" s="50"/>
+      <c r="A25" s="64"/>
+      <c r="B25" s="64"/>
       <c r="C25" s="47">
         <v>14.4</v>
       </c>
@@ -2243,13 +2246,13 @@
         <v>15</v>
       </c>
       <c r="E25" s="48" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="F25" s="48" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="G25" s="48" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="H25" s="47" t="s">
         <v>102</v>
@@ -2259,8 +2262,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A26" s="50"/>
-      <c r="B26" s="50"/>
+      <c r="A26" s="64"/>
+      <c r="B26" s="64"/>
       <c r="C26" s="47">
         <v>14.5</v>
       </c>
@@ -2268,13 +2271,13 @@
         <v>15</v>
       </c>
       <c r="E26" s="48" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="F26" s="48" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="G26" s="48" t="s">
-        <v>175</v>
+        <v>173</v>
       </c>
       <c r="H26" s="47" t="s">
         <v>102</v>
@@ -2284,8 +2287,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A27" s="50"/>
-      <c r="B27" s="50"/>
+      <c r="A27" s="64"/>
+      <c r="B27" s="64"/>
       <c r="C27" s="47">
         <v>14.6</v>
       </c>
@@ -2293,13 +2296,13 @@
         <v>15</v>
       </c>
       <c r="E27" s="48" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="F27" s="48" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="G27" s="48" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="H27" s="47" t="s">
         <v>102</v>
@@ -2309,8 +2312,8 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A28" s="50"/>
-      <c r="B28" s="50"/>
+      <c r="A28" s="64"/>
+      <c r="B28" s="64"/>
       <c r="C28" s="47">
         <v>14.7</v>
       </c>
@@ -2318,13 +2321,13 @@
         <v>15</v>
       </c>
       <c r="E28" s="48" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="F28" s="48" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="G28" s="48" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
       <c r="H28" s="47" t="s">
         <v>102</v>
@@ -2334,8 +2337,8 @@
       </c>
     </row>
     <row r="29" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A29" s="50"/>
-      <c r="B29" s="50"/>
+      <c r="A29" s="64"/>
+      <c r="B29" s="64"/>
       <c r="C29" s="47">
         <v>14.8</v>
       </c>
@@ -2343,24 +2346,24 @@
         <v>15</v>
       </c>
       <c r="E29" s="48" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="F29" s="48" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="G29" s="48" t="s">
-        <v>177</v>
+        <v>175</v>
       </c>
       <c r="H29" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I29" s="48" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="30" spans="1:9" s="4" customFormat="1" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="50"/>
-      <c r="B30" s="50"/>
+      <c r="A30" s="64"/>
+      <c r="B30" s="64"/>
       <c r="C30" s="47">
         <v>14.9</v>
       </c>
@@ -2368,24 +2371,24 @@
         <v>15</v>
       </c>
       <c r="E30" s="48" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F30" s="48" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="G30" s="48" t="s">
-        <v>178</v>
+        <v>176</v>
       </c>
       <c r="H30" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I30" s="48" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="50"/>
-      <c r="B31" s="50"/>
+      <c r="A31" s="64"/>
+      <c r="B31" s="64"/>
       <c r="C31" s="47">
         <v>14.1</v>
       </c>
@@ -2393,24 +2396,24 @@
         <v>15</v>
       </c>
       <c r="E31" s="48" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F31" s="48" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="G31" s="48" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
       <c r="H31" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I31" s="48" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A32" s="50"/>
-      <c r="B32" s="50"/>
+      <c r="A32" s="64"/>
+      <c r="B32" s="64"/>
       <c r="C32" s="47">
         <v>14.11</v>
       </c>
@@ -2418,26 +2421,26 @@
         <v>15</v>
       </c>
       <c r="E32" s="48" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="F32" s="48" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="G32" s="48" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="H32" s="47" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="I32" s="48" t="s">
         <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="52">
+      <c r="A33" s="57">
         <v>15</v>
       </c>
-      <c r="B33" s="52" t="s">
+      <c r="B33" s="57" t="s">
         <v>63</v>
       </c>
       <c r="C33" s="19">
@@ -2456,15 +2459,15 @@
         <v>67</v>
       </c>
       <c r="H33" s="19" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I33" s="20" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="34" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="59"/>
-      <c r="B34" s="59"/>
+      <c r="A34" s="58"/>
+      <c r="B34" s="58"/>
       <c r="C34" s="19">
         <v>15.2</v>
       </c>
@@ -2481,15 +2484,15 @@
         <v>70</v>
       </c>
       <c r="H34" s="19" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I34" s="20" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="35" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="59"/>
-      <c r="B35" s="59"/>
+      <c r="A35" s="58"/>
+      <c r="B35" s="58"/>
       <c r="C35" s="19">
         <v>15.3</v>
       </c>
@@ -2506,15 +2509,15 @@
         <v>73</v>
       </c>
       <c r="H35" s="19" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="I35" s="20" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="36" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="59"/>
-      <c r="B36" s="59"/>
+      <c r="A36" s="58"/>
+      <c r="B36" s="58"/>
       <c r="C36" s="19">
         <v>15.4</v>
       </c>
@@ -2531,15 +2534,15 @@
         <v>76</v>
       </c>
       <c r="H36" s="19" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I36" s="20" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="37" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="59"/>
-      <c r="B37" s="59"/>
+      <c r="A37" s="58"/>
+      <c r="B37" s="58"/>
       <c r="C37" s="19">
         <v>15.5</v>
       </c>
@@ -2556,17 +2559,17 @@
         <v>79</v>
       </c>
       <c r="H37" s="19" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I37" s="20" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="38" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="51">
+      <c r="A38" s="66">
         <v>16</v>
       </c>
-      <c r="B38" s="51" t="s">
+      <c r="B38" s="66" t="s">
         <v>80</v>
       </c>
       <c r="C38" s="21">
@@ -2585,15 +2588,15 @@
         <v>84</v>
       </c>
       <c r="H38" s="44" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I38" s="45" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="39" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="59"/>
-      <c r="B39" s="59"/>
+      <c r="A39" s="58"/>
+      <c r="B39" s="58"/>
       <c r="C39" s="21">
         <v>16.2</v>
       </c>
@@ -2610,17 +2613,17 @@
         <v>88</v>
       </c>
       <c r="H39" s="44" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="I39" s="45" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
     </row>
     <row r="40" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="56">
+      <c r="A40" s="65">
         <v>17</v>
       </c>
-      <c r="B40" s="56" t="s">
+      <c r="B40" s="65" t="s">
         <v>89</v>
       </c>
       <c r="C40" s="5">
@@ -2630,13 +2633,13 @@
         <v>90</v>
       </c>
       <c r="E40" s="37" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="F40" s="6" t="s">
         <v>91</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="H40" s="5" t="s">
         <v>102</v>
@@ -2646,8 +2649,8 @@
       </c>
     </row>
     <row r="41" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="59"/>
-      <c r="B41" s="59"/>
+      <c r="A41" s="58"/>
+      <c r="B41" s="58"/>
       <c r="C41" s="5">
         <v>17.2</v>
       </c>
@@ -2671,8 +2674,8 @@
       </c>
     </row>
     <row r="42" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="59"/>
-      <c r="B42" s="59"/>
+      <c r="A42" s="58"/>
+      <c r="B42" s="58"/>
       <c r="C42" s="5">
         <v>17.3</v>
       </c>
@@ -2696,8 +2699,8 @@
       </c>
     </row>
     <row r="43" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="59"/>
-      <c r="B43" s="59"/>
+      <c r="A43" s="58"/>
+      <c r="B43" s="58"/>
       <c r="C43" s="5">
         <v>17.399999999999999</v>
       </c>
@@ -2721,8 +2724,8 @@
       </c>
     </row>
     <row r="44" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="59"/>
-      <c r="B44" s="59"/>
+      <c r="A44" s="58"/>
+      <c r="B44" s="58"/>
       <c r="C44" s="5">
         <v>17.5</v>
       </c>
@@ -2746,8 +2749,8 @@
       </c>
     </row>
     <row r="45" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="59"/>
-      <c r="B45" s="59"/>
+      <c r="A45" s="58"/>
+      <c r="B45" s="58"/>
       <c r="C45" s="5">
         <v>17.600000000000001</v>
       </c>
@@ -2771,8 +2774,8 @@
       </c>
     </row>
     <row r="46" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="59"/>
-      <c r="B46" s="59"/>
+      <c r="A46" s="58"/>
+      <c r="B46" s="58"/>
       <c r="C46" s="5">
         <v>17.7</v>
       </c>
@@ -2796,197 +2799,197 @@
       </c>
     </row>
     <row r="47" spans="1:9" s="4" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A47" s="64">
+      <c r="A47" s="68">
         <v>18</v>
       </c>
-      <c r="B47" s="65" t="s">
+      <c r="B47" s="69" t="s">
+        <v>189</v>
+      </c>
+      <c r="C47" s="53">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="D47" s="49" t="s">
+        <v>190</v>
+      </c>
+      <c r="E47" s="49" t="s">
         <v>191</v>
       </c>
-      <c r="C47" s="66">
-        <v>18.100000000000001</v>
-      </c>
-      <c r="D47" s="57" t="s">
+      <c r="F47" s="49" t="s">
         <v>192</v>
       </c>
-      <c r="E47" s="57" t="s">
+      <c r="G47" s="49" t="s">
+        <v>196</v>
+      </c>
+      <c r="H47" s="53"/>
+      <c r="I47" s="54"/>
+    </row>
+    <row r="48" spans="1:9" s="4" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A48" s="68"/>
+      <c r="B48" s="69"/>
+      <c r="C48" s="52">
+        <v>18.2</v>
+      </c>
+      <c r="D48" s="49" t="s">
         <v>193</v>
       </c>
-      <c r="F47" s="57" t="s">
+      <c r="E48" s="49" t="s">
         <v>194</v>
       </c>
-      <c r="G47" s="57" t="s">
+      <c r="F48" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="G48" s="49" t="s">
+        <v>195</v>
+      </c>
+      <c r="H48" s="53"/>
+      <c r="I48" s="54"/>
+    </row>
+    <row r="49" spans="1:12" s="4" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="68">
+        <v>19</v>
+      </c>
+      <c r="B49" s="69" t="s">
+        <v>197</v>
+      </c>
+      <c r="C49" s="53">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="D49" s="49" t="s">
         <v>198</v>
       </c>
-      <c r="H47" s="66"/>
-      <c r="I47" s="67"/>
-    </row>
-    <row r="48" spans="1:9" s="4" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A48" s="64"/>
-      <c r="B48" s="65"/>
-      <c r="C48" s="68">
-        <v>18.2</v>
-      </c>
-      <c r="D48" s="57" t="s">
-        <v>195</v>
-      </c>
-      <c r="E48" s="57" t="s">
-        <v>196</v>
-      </c>
-      <c r="F48" s="57" t="s">
-        <v>188</v>
-      </c>
-      <c r="G48" s="57" t="s">
-        <v>197</v>
-      </c>
-      <c r="H48" s="66"/>
-      <c r="I48" s="67"/>
-    </row>
-    <row r="49" spans="1:12" s="4" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A49" s="64">
-        <v>19</v>
-      </c>
-      <c r="B49" s="65" t="s">
+      <c r="E49" s="49" t="s">
+        <v>200</v>
+      </c>
+      <c r="F49" s="49" t="s">
+        <v>202</v>
+      </c>
+      <c r="G49" s="49" t="s">
+        <v>203</v>
+      </c>
+      <c r="H49" s="53"/>
+      <c r="I49" s="54"/>
+    </row>
+    <row r="50" spans="1:12" s="4" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A50" s="68"/>
+      <c r="B50" s="69"/>
+      <c r="C50" s="52">
+        <v>19.2</v>
+      </c>
+      <c r="D50" s="49" t="s">
         <v>199</v>
       </c>
-      <c r="C49" s="66">
-        <v>19.100000000000001</v>
-      </c>
-      <c r="D49" s="57" t="s">
-        <v>200</v>
-      </c>
-      <c r="E49" s="57" t="s">
-        <v>202</v>
-      </c>
-      <c r="F49" s="57" t="s">
+      <c r="E50" s="49" t="s">
+        <v>201</v>
+      </c>
+      <c r="F50" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="G50" s="49" t="s">
         <v>204</v>
       </c>
-      <c r="G49" s="57" t="s">
-        <v>205</v>
-      </c>
-      <c r="H49" s="66"/>
-      <c r="I49" s="67"/>
-    </row>
-    <row r="50" spans="1:12" s="4" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A50" s="64"/>
-      <c r="B50" s="65"/>
-      <c r="C50" s="68">
-        <v>19.2</v>
-      </c>
-      <c r="D50" s="57" t="s">
-        <v>201</v>
-      </c>
-      <c r="E50" s="57" t="s">
-        <v>203</v>
-      </c>
-      <c r="F50" s="57" t="s">
-        <v>188</v>
-      </c>
-      <c r="G50" s="57" t="s">
-        <v>206</v>
-      </c>
-      <c r="H50" s="66"/>
-      <c r="I50" s="67"/>
+      <c r="H50" s="53"/>
+      <c r="I50" s="54"/>
       <c r="J50" s="3"/>
       <c r="K50" s="3"/>
       <c r="L50" s="3"/>
     </row>
     <row r="51" spans="1:12" ht="104.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="64">
+      <c r="A51" s="68">
         <v>20</v>
       </c>
-      <c r="B51" s="65" t="s">
+      <c r="B51" s="69" t="s">
+        <v>205</v>
+      </c>
+      <c r="C51" s="53">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="D51" s="49" t="s">
+        <v>206</v>
+      </c>
+      <c r="E51" s="49" t="s">
+        <v>211</v>
+      </c>
+      <c r="F51" s="49" t="s">
+        <v>210</v>
+      </c>
+      <c r="G51" s="49" t="s">
+        <v>212</v>
+      </c>
+      <c r="H51" s="53"/>
+      <c r="I51" s="54"/>
+    </row>
+    <row r="52" spans="1:12" ht="135" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A52" s="68"/>
+      <c r="B52" s="69"/>
+      <c r="C52" s="52">
+        <v>20.2</v>
+      </c>
+      <c r="D52" s="49" t="s">
         <v>207</v>
       </c>
-      <c r="C51" s="66">
-        <v>20.100000000000001</v>
-      </c>
-      <c r="D51" s="57" t="s">
+      <c r="E52" s="49" t="s">
+        <v>209</v>
+      </c>
+      <c r="F52" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="G52" s="49" t="s">
         <v>208</v>
       </c>
-      <c r="E51" s="57" t="s">
+      <c r="H52" s="53"/>
+      <c r="I52" s="54"/>
+    </row>
+    <row r="53" spans="1:12" ht="179.4" x14ac:dyDescent="0.3">
+      <c r="A53" s="68">
+        <v>21</v>
+      </c>
+      <c r="B53" s="69" t="s">
         <v>213</v>
       </c>
-      <c r="F51" s="57" t="s">
-        <v>212</v>
-      </c>
-      <c r="G51" s="57" t="s">
+      <c r="C53" s="53">
+        <v>21.1</v>
+      </c>
+      <c r="D53" s="49" t="s">
         <v>214</v>
       </c>
-      <c r="H51" s="66"/>
-      <c r="I51" s="67"/>
-    </row>
-    <row r="52" spans="1:12" ht="135" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="64"/>
-      <c r="B52" s="65"/>
-      <c r="C52" s="68">
-        <v>20.2</v>
-      </c>
-      <c r="D52" s="57" t="s">
-        <v>209</v>
-      </c>
-      <c r="E52" s="57" t="s">
-        <v>211</v>
-      </c>
-      <c r="F52" s="57" t="s">
-        <v>188</v>
-      </c>
-      <c r="G52" s="57" t="s">
-        <v>210</v>
-      </c>
-      <c r="H52" s="66"/>
-      <c r="I52" s="67"/>
-    </row>
-    <row r="53" spans="1:12" ht="179.4" x14ac:dyDescent="0.3">
-      <c r="A53" s="64">
-        <v>21</v>
-      </c>
-      <c r="B53" s="65" t="s">
+      <c r="E53" s="49" t="s">
+        <v>217</v>
+      </c>
+      <c r="F53" s="49" t="s">
+        <v>218</v>
+      </c>
+      <c r="G53" s="49" t="s">
+        <v>219</v>
+      </c>
+      <c r="H53" s="53"/>
+      <c r="I53" s="54"/>
+    </row>
+    <row r="54" spans="1:12" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A54" s="68"/>
+      <c r="B54" s="69"/>
+      <c r="C54" s="52">
+        <v>21.2</v>
+      </c>
+      <c r="D54" s="49" t="s">
         <v>215</v>
       </c>
-      <c r="C53" s="66">
-        <v>21.1</v>
-      </c>
-      <c r="D53" s="57" t="s">
+      <c r="E54" s="55" t="s">
+        <v>220</v>
+      </c>
+      <c r="F54" s="49" t="s">
+        <v>186</v>
+      </c>
+      <c r="G54" s="49" t="s">
         <v>216</v>
       </c>
-      <c r="E53" s="57" t="s">
-        <v>219</v>
-      </c>
-      <c r="F53" s="57" t="s">
-        <v>220</v>
-      </c>
-      <c r="G53" s="57" t="s">
-        <v>221</v>
-      </c>
-      <c r="H53" s="66"/>
-      <c r="I53" s="67"/>
-    </row>
-    <row r="54" spans="1:12" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A54" s="64"/>
-      <c r="B54" s="65"/>
-      <c r="C54" s="68">
-        <v>21.2</v>
-      </c>
-      <c r="D54" s="57" t="s">
-        <v>217</v>
-      </c>
-      <c r="E54" s="69" t="s">
-        <v>222</v>
-      </c>
-      <c r="F54" s="57" t="s">
-        <v>188</v>
-      </c>
-      <c r="G54" s="57" t="s">
-        <v>218</v>
-      </c>
-      <c r="H54" s="66"/>
-      <c r="I54" s="67"/>
+      <c r="H54" s="53"/>
+      <c r="I54" s="54"/>
     </row>
     <row r="55" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A55" s="2"/>
       <c r="B55" s="2"/>
       <c r="C55" s="2"/>
-      <c r="E55" s="57"/>
+      <c r="E55" s="49"/>
       <c r="H55" s="2"/>
     </row>
     <row r="56" spans="1:12" ht="31.05" customHeight="1" x14ac:dyDescent="0.3">
@@ -3049,6 +3052,8 @@
     <mergeCell ref="A38:A39"/>
     <mergeCell ref="B17:B21"/>
     <mergeCell ref="A17:A21"/>
+    <mergeCell ref="B22:B32"/>
+    <mergeCell ref="B38:B39"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="A5:A6"/>
     <mergeCell ref="A33:A37"/>
@@ -3065,8 +3070,6 @@
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="B8:B9"/>
-    <mergeCell ref="B22:B32"/>
-    <mergeCell ref="B38:B39"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Soubhanik/checkupp_product_backlog_final.xlsx
+++ b/Soubhanik/checkupp_product_backlog_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anodiam\2026\CheckUpp_Parent\CheckUpp\Soubhanik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F541787C-31D8-4746-8E0E-39AE90D3A9A8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BA235ADE-84B4-42B6-8ADC-8CDC68A9616A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -16,7 +16,7 @@
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$I$1:$I$19</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$I$1:$I$21</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
@@ -101,7 +101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B10" authorId="1" shapeId="0" xr:uid="{79DA11BF-BFE2-49FE-916B-7BBF40F206E7}">
+    <comment ref="B12" authorId="1" shapeId="0" xr:uid="{79DA11BF-BFE2-49FE-916B-7BBF40F206E7}">
       <text>
         <r>
           <rPr>
@@ -130,7 +130,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="310" uniqueCount="224">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="322" uniqueCount="231">
   <si>
     <t>Epic #</t>
   </si>
@@ -446,9 +446,6 @@
   </si>
   <si>
     <t>Slide 8-11</t>
-  </si>
-  <si>
-    <t>Slide 14</t>
   </si>
   <si>
     <t>Slide 15</t>
@@ -577,13 +574,6 @@
 d. Travel (age agnostic)</t>
   </si>
   <si>
-    <t>I can access them in app and in device's local file manager</t>
-  </si>
-  <si>
-    <t>1. Document wallet must list all the uploaded documents with name and date
-2. User must be able to interact with the options to download, view and delete the documents</t>
-  </si>
-  <si>
     <t xml:space="preserve"> </t>
   </si>
   <si>
@@ -882,14 +872,54 @@
     <t>see my previously entered data in the available fields (e.g., cavities, fillings, etc.), the status of the toggle switch (Use Mouthwash Regularly), and the selected dropdown options (Brushing Frequency and Flossing Frequency) restored along with an affirming notification (toast)</t>
   </si>
   <si>
-    <t>logged in user navigating the Document Wallet screen</t>
-  </si>
-  <si>
-    <t>store health documents(reports) in the app's cloud storage and my local device</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. Document captured/scanned must be visible in the Document Wallet
-2. User must be able to click on the download icon to save the document/image in their local device storage </t>
+    <t>upload health documents(reports) in the app's cloud storage from my local device</t>
+  </si>
+  <si>
+    <t>I can access them in app</t>
+  </si>
+  <si>
+    <t>1. The logged-in user must be able to select one or more health documents (e.g., reports) from their local device for upload to the Document Wallet.
+2. The selected health documents must be uploaded securely to the app's cloud storage and associated with the logged-in user's account.
+3. A confirmation message must be displayed to the user after each document has been successfully uploaded.
+4. If a document upload fails, an appropriate error message must be displayed, and the user must be able to retry the upload without affecting previously uploaded documents.</t>
+  </si>
+  <si>
+    <t>1. Document wallet must list all the uploaded documents with name and date
+2. User must be able to interact with the options to download, view and delete options for each document stored in the Document Wallet
+3. If a document cannot be opened, an appropriate error message must be displayed, and the user must be able to retry opening the document.
+4. The selected document must be displayed in a readable format within the app or using the device's supported document viewer.</t>
+  </si>
+  <si>
+    <t>logged in user navigating the 'Documents' section of the Document Wallet screen</t>
+  </si>
+  <si>
+    <t>logged in user navigating the 'Links' section of the Document Wallet screen</t>
+  </si>
+  <si>
+    <t>store my e-script links along with any associated text of my choice</t>
+  </si>
+  <si>
+    <t>I can view all my e-script links as a list along with a description of my choice for each link</t>
+  </si>
+  <si>
+    <t>1. User must be able to add an e-script link along with an associated text description of their choice in the Links section of the Document Wallet.
+2. The entered e-script link and its associated description must be securely saved
+3. All saved e-script links and their associated descriptions must be displayed as a list in the Links section of the Document Wallet.
+4. If an e-script link cannot be saved, an appropriate error message must be displayed, and the user must be able to retry the action without affecting previously saved links.</t>
+  </si>
+  <si>
+    <t>Slide 11</t>
+  </si>
+  <si>
+    <t>view a link stored in my wallet</t>
+  </si>
+  <si>
+    <t>I can review my e-script links at any time</t>
+  </si>
+  <si>
+    <t>1. Document wallet must list all the saved links with name and date
+2. User must be able to interact with the options to view and delete options for each link stored in the Document Wallet
+3. If the detailed view of a link cannot be opened, an appropriate error message must be displayed, and the user must be able to retry opening the detailed view of the link.</t>
   </si>
 </sst>
 </file>
@@ -1087,7 +1117,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="3">
+  <borders count="6">
     <border>
       <left/>
       <right/>
@@ -1125,12 +1155,49 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="72">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1297,44 +1364,50 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="4" fillId="15" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="8" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="12" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="10" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="7" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -1618,11 +1691,11 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L61"/>
+  <dimension ref="A1:L63"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="32.88671875" style="1" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="11.109375" style="1" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="20.88671875" style="2" customWidth="1"/>
     <col min="5" max="5" width="64.88671875" style="1" bestFit="1" customWidth="1"/>
@@ -1635,34 +1708,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" ht="39.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="59" t="s">
+      <c r="A1" s="67" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="59" t="s">
+      <c r="B1" s="67" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="59" t="s">
+      <c r="C1" s="67" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="59" t="s">
+      <c r="D1" s="67" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="60"/>
-      <c r="F1" s="60"/>
-      <c r="G1" s="59" t="s">
+      <c r="E1" s="68"/>
+      <c r="F1" s="68"/>
+      <c r="G1" s="67" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="59" t="s">
+      <c r="H1" s="67" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="59" t="s">
+      <c r="I1" s="67" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="58"/>
-      <c r="B2" s="58"/>
-      <c r="C2" s="58"/>
+      <c r="A2" s="59"/>
+      <c r="B2" s="59"/>
+      <c r="C2" s="59"/>
       <c r="D2" s="50" t="s">
         <v>7</v>
       </c>
@@ -1672,37 +1745,37 @@
       <c r="F2" s="50" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="59"/>
-      <c r="H2" s="58"/>
-      <c r="I2" s="58"/>
+      <c r="G2" s="67"/>
+      <c r="H2" s="59"/>
+      <c r="I2" s="59"/>
     </row>
     <row r="3" spans="1:9" s="4" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
       <c r="A3" s="30" t="s">
-        <v>139</v>
+        <v>136</v>
       </c>
       <c r="B3" s="30" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="C3" s="18">
         <v>13.2</v>
       </c>
       <c r="D3" s="31" t="s">
+        <v>125</v>
+      </c>
+      <c r="E3" s="31" t="s">
         <v>126</v>
       </c>
-      <c r="E3" s="31" t="s">
+      <c r="F3" s="31" t="s">
         <v>127</v>
       </c>
-      <c r="F3" s="31" t="s">
-        <v>128</v>
-      </c>
       <c r="G3" s="32" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="H3" s="18" t="s">
         <v>60</v>
       </c>
       <c r="I3" s="31" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="4" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
@@ -1719,26 +1792,26 @@
         <v>11</v>
       </c>
       <c r="E4" s="40" t="s">
+        <v>102</v>
+      </c>
+      <c r="F4" s="40" t="s">
         <v>103</v>
       </c>
-      <c r="F4" s="40" t="s">
+      <c r="G4" s="41" t="s">
         <v>104</v>
-      </c>
-      <c r="G4" s="41" t="s">
-        <v>105</v>
       </c>
       <c r="H4" s="39" t="s">
         <v>12</v>
       </c>
       <c r="I4" s="40" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="5" spans="1:9" s="29" customFormat="1" ht="69" x14ac:dyDescent="0.3">
-      <c r="A5" s="56">
+      <c r="A5" s="65">
         <v>3</v>
       </c>
-      <c r="B5" s="56" t="s">
+      <c r="B5" s="65" t="s">
         <v>13</v>
       </c>
       <c r="C5" s="28">
@@ -1748,13 +1821,13 @@
         <v>11</v>
       </c>
       <c r="E5" s="34" t="s">
+        <v>105</v>
+      </c>
+      <c r="F5" s="34" t="s">
         <v>106</v>
       </c>
-      <c r="F5" s="34" t="s">
-        <v>107</v>
-      </c>
       <c r="G5" s="35" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="H5" s="36" t="s">
         <v>97</v>
@@ -1764,8 +1837,8 @@
       </c>
     </row>
     <row r="6" spans="1:9" s="4" customFormat="1" ht="69" x14ac:dyDescent="0.3">
-      <c r="A6" s="56"/>
-      <c r="B6" s="56"/>
+      <c r="A6" s="65"/>
+      <c r="B6" s="65"/>
       <c r="C6" s="28">
         <v>3.2</v>
       </c>
@@ -1773,13 +1846,13 @@
         <v>11</v>
       </c>
       <c r="E6" s="34" t="s">
+        <v>107</v>
+      </c>
+      <c r="F6" s="34" t="s">
         <v>108</v>
       </c>
-      <c r="F6" s="34" t="s">
-        <v>109</v>
-      </c>
       <c r="G6" s="35" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="H6" s="28" t="s">
         <v>97</v>
@@ -1799,16 +1872,16 @@
         <v>5.2</v>
       </c>
       <c r="D7" s="6" t="s">
+        <v>132</v>
+      </c>
+      <c r="E7" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="F7" s="6" t="s">
         <v>133</v>
       </c>
-      <c r="E7" s="6" t="s">
+      <c r="G7" s="23" t="s">
         <v>135</v>
-      </c>
-      <c r="F7" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="G7" s="23" t="s">
-        <v>136</v>
       </c>
       <c r="H7" s="7" t="s">
         <v>98</v>
@@ -1817,43 +1890,43 @@
         <v>17</v>
       </c>
     </row>
-    <row r="8" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="62">
+    <row r="8" spans="1:9" s="4" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="69">
         <v>6</v>
       </c>
-      <c r="B8" s="62" t="s">
+      <c r="B8" s="69" t="s">
         <v>18</v>
       </c>
       <c r="C8" s="8">
         <v>6.1</v>
       </c>
       <c r="D8" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E8" s="42" t="s">
-        <v>222</v>
+        <v>218</v>
       </c>
       <c r="F8" s="42" t="s">
-        <v>137</v>
+        <v>219</v>
       </c>
       <c r="G8" s="43" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H8" s="10" t="s">
-        <v>99</v>
+        <v>227</v>
       </c>
       <c r="I8" s="9" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="58"/>
-      <c r="B9" s="58"/>
+    <row r="9" spans="1:9" s="4" customFormat="1" ht="110.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="70"/>
+      <c r="B9" s="70"/>
       <c r="C9" s="8">
         <v>6.2</v>
       </c>
       <c r="D9" s="9" t="s">
-        <v>221</v>
+        <v>222</v>
       </c>
       <c r="E9" s="9" t="s">
         <v>20</v>
@@ -1862,400 +1935,400 @@
         <v>21</v>
       </c>
       <c r="G9" s="24" t="s">
-        <v>138</v>
-      </c>
-      <c r="H9" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="H9" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="I9" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" s="4" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A10" s="70"/>
+      <c r="B10" s="70"/>
+      <c r="C10" s="8">
+        <v>6.3</v>
+      </c>
+      <c r="D10" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="E10" s="9" t="s">
+        <v>224</v>
+      </c>
+      <c r="F10" s="9" t="s">
+        <v>225</v>
+      </c>
+      <c r="G10" s="24" t="s">
+        <v>226</v>
+      </c>
+      <c r="H10" s="10" t="s">
+        <v>227</v>
+      </c>
+      <c r="I10" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" s="4" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="71"/>
+      <c r="B11" s="71"/>
+      <c r="C11" s="8">
+        <v>6.4</v>
+      </c>
+      <c r="D11" s="9" t="s">
+        <v>223</v>
+      </c>
+      <c r="E11" s="9" t="s">
+        <v>228</v>
+      </c>
+      <c r="F11" s="9" t="s">
+        <v>229</v>
+      </c>
+      <c r="G11" s="24" t="s">
+        <v>230</v>
+      </c>
+      <c r="H11" s="10"/>
+      <c r="I11" s="9" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A12" s="61">
+        <v>7</v>
+      </c>
+      <c r="B12" s="61" t="s">
+        <v>22</v>
+      </c>
+      <c r="C12" s="11">
+        <v>7.1</v>
+      </c>
+      <c r="D12" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="E12" s="12" t="s">
+        <v>23</v>
+      </c>
+      <c r="F12" s="12" t="s">
+        <v>24</v>
+      </c>
+      <c r="G12" s="25" t="s">
+        <v>25</v>
+      </c>
+      <c r="H12" s="13" t="s">
         <v>99</v>
       </c>
-      <c r="I9" s="9"/>
-    </row>
-    <row r="10" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A10" s="63">
-        <v>7</v>
-      </c>
-      <c r="B10" s="63" t="s">
-        <v>22</v>
-      </c>
-      <c r="C10" s="11">
-        <v>7.1</v>
-      </c>
-      <c r="D10" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="E10" s="12" t="s">
-        <v>23</v>
-      </c>
-      <c r="F10" s="12" t="s">
-        <v>24</v>
-      </c>
-      <c r="G10" s="25" t="s">
-        <v>25</v>
-      </c>
-      <c r="H10" s="13" t="s">
+      <c r="I12" s="12" t="s">
+        <v>26</v>
+      </c>
+    </row>
+    <row r="13" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A13" s="59"/>
+      <c r="B13" s="59"/>
+      <c r="C13" s="11">
+        <v>7.2</v>
+      </c>
+      <c r="D13" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="E13" s="12" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="25" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="11" t="s">
         <v>100</v>
       </c>
-      <c r="I10" s="12" t="s">
+      <c r="I13" s="12" t="s">
         <v>26</v>
       </c>
     </row>
-    <row r="11" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A11" s="58"/>
-      <c r="B11" s="58"/>
-      <c r="C11" s="11">
-        <v>7.2</v>
-      </c>
-      <c r="D11" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="E11" s="12" t="s">
-        <v>27</v>
-      </c>
-      <c r="F11" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="G11" s="25" t="s">
-        <v>29</v>
-      </c>
-      <c r="H11" s="11" t="s">
-        <v>101</v>
-      </c>
-      <c r="I11" s="12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="12" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="58"/>
-      <c r="B12" s="58"/>
-      <c r="C12" s="11">
+    <row r="14" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="59"/>
+      <c r="B14" s="59"/>
+      <c r="C14" s="11">
         <v>7.3</v>
       </c>
-      <c r="D12" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="E12" s="12" t="s">
+      <c r="D14" s="12" t="s">
+        <v>125</v>
+      </c>
+      <c r="E14" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F12" s="12" t="s">
+      <c r="F14" s="12" t="s">
         <v>31</v>
       </c>
-      <c r="G12" s="25" t="s">
+      <c r="G14" s="25" t="s">
         <v>32</v>
       </c>
-      <c r="H12" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="I12" s="12"/>
-    </row>
-    <row r="13" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A13" s="61">
+      <c r="H14" s="11" t="s">
+        <v>99</v>
+      </c>
+      <c r="I14" s="12"/>
+    </row>
+    <row r="15" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="60">
         <v>9</v>
       </c>
-      <c r="B13" s="61" t="s">
+      <c r="B15" s="60" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="14">
+      <c r="C15" s="14">
         <v>9.1</v>
       </c>
-      <c r="D13" s="15" t="s">
+      <c r="D15" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E13" s="15" t="s">
+      <c r="E15" s="15" t="s">
         <v>34</v>
       </c>
-      <c r="F13" s="15" t="s">
+      <c r="F15" s="15" t="s">
         <v>35</v>
       </c>
-      <c r="G13" s="26" t="s">
+      <c r="G15" s="26" t="s">
         <v>36</v>
       </c>
-      <c r="H13" s="14"/>
-      <c r="I13" s="15"/>
-    </row>
-    <row r="14" spans="1:9" s="4" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="58"/>
-      <c r="B14" s="58"/>
-      <c r="C14" s="14">
+      <c r="H15" s="14"/>
+      <c r="I15" s="15"/>
+    </row>
+    <row r="16" spans="1:9" s="4" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="59"/>
+      <c r="B16" s="59"/>
+      <c r="C16" s="14">
         <v>9.1999999999999993</v>
       </c>
-      <c r="D14" s="15" t="s">
+      <c r="D16" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="E14" s="15" t="s">
+      <c r="E16" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="F14" s="15" t="s">
+      <c r="F16" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="G14" s="26" t="s">
+      <c r="G16" s="26" t="s">
         <v>40</v>
       </c>
-      <c r="H14" s="14"/>
-      <c r="I14" s="15"/>
-    </row>
-    <row r="15" spans="1:9" s="4" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="58"/>
-      <c r="B15" s="58"/>
-      <c r="C15" s="14">
+      <c r="H16" s="14"/>
+      <c r="I16" s="15"/>
+    </row>
+    <row r="17" spans="1:9" s="4" customFormat="1" ht="27.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="59"/>
+      <c r="B17" s="59"/>
+      <c r="C17" s="14">
         <v>9.3000000000000007</v>
       </c>
-      <c r="D15" s="15" t="s">
+      <c r="D17" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E15" s="15" t="s">
+      <c r="E17" s="15" t="s">
         <v>42</v>
       </c>
-      <c r="F15" s="15" t="s">
+      <c r="F17" s="15" t="s">
         <v>43</v>
       </c>
-      <c r="G15" s="26" t="s">
+      <c r="G17" s="26" t="s">
         <v>44</v>
       </c>
-      <c r="H15" s="14"/>
-      <c r="I15" s="15" t="s">
+      <c r="H17" s="14"/>
+      <c r="I17" s="15" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="16" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A16" s="58"/>
-      <c r="B16" s="58"/>
-      <c r="C16" s="14">
+    <row r="18" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A18" s="59"/>
+      <c r="B18" s="59"/>
+      <c r="C18" s="14">
         <v>9.4</v>
       </c>
-      <c r="D16" s="15" t="s">
+      <c r="D18" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="E16" s="15" t="s">
+      <c r="E18" s="15" t="s">
         <v>46</v>
       </c>
-      <c r="F16" s="15" t="s">
+      <c r="F18" s="15" t="s">
         <v>47</v>
       </c>
-      <c r="G16" s="26" t="s">
+      <c r="G18" s="26" t="s">
         <v>48</v>
       </c>
-      <c r="H16" s="14"/>
-      <c r="I16" s="15" t="s">
+      <c r="H18" s="14"/>
+      <c r="I18" s="15" t="s">
         <v>45</v>
       </c>
     </row>
-    <row r="17" spans="1:9" s="4" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="67">
+    <row r="19" spans="1:9" s="4" customFormat="1" ht="41.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="63">
         <v>12</v>
       </c>
-      <c r="B17" s="67" t="s">
-        <v>181</v>
-      </c>
-      <c r="C17" s="16">
+      <c r="B19" s="63" t="s">
+        <v>178</v>
+      </c>
+      <c r="C19" s="16">
         <v>12.1</v>
       </c>
-      <c r="D17" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="E17" s="17" t="s">
+      <c r="D19" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="E19" s="17" t="s">
         <v>49</v>
       </c>
-      <c r="F17" s="17" t="s">
+      <c r="F19" s="17" t="s">
         <v>50</v>
       </c>
-      <c r="G17" s="27" t="s">
+      <c r="G19" s="27" t="s">
         <v>51</v>
-      </c>
-      <c r="H17" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="I17" s="17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A18" s="67"/>
-      <c r="B18" s="67"/>
-      <c r="C18" s="16">
-        <v>12.2</v>
-      </c>
-      <c r="D18" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="E18" s="17" t="s">
-        <v>54</v>
-      </c>
-      <c r="F18" s="17" t="s">
-        <v>55</v>
-      </c>
-      <c r="G18" s="27" t="s">
-        <v>56</v>
-      </c>
-      <c r="H18" s="16" t="s">
-        <v>52</v>
-      </c>
-      <c r="I18" s="17" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="67"/>
-      <c r="B19" s="67"/>
-      <c r="C19" s="16">
-        <v>12.3</v>
-      </c>
-      <c r="D19" s="17" t="s">
-        <v>180</v>
-      </c>
-      <c r="E19" s="17" t="s">
-        <v>57</v>
-      </c>
-      <c r="F19" s="17" t="s">
-        <v>58</v>
-      </c>
-      <c r="G19" s="27" t="s">
-        <v>59</v>
       </c>
       <c r="H19" s="16" t="s">
         <v>52</v>
       </c>
-      <c r="I19" s="17"/>
-    </row>
-    <row r="20" spans="1:9" s="4" customFormat="1" ht="138" x14ac:dyDescent="0.3">
-      <c r="A20" s="67"/>
-      <c r="B20" s="67"/>
+      <c r="I19" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="20" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A20" s="63"/>
+      <c r="B20" s="63"/>
       <c r="C20" s="16">
+        <v>12.2</v>
+      </c>
+      <c r="D20" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="E20" s="17" t="s">
+        <v>54</v>
+      </c>
+      <c r="F20" s="17" t="s">
+        <v>55</v>
+      </c>
+      <c r="G20" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="H20" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="I20" s="17" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="63"/>
+      <c r="B21" s="63"/>
+      <c r="C21" s="16">
+        <v>12.3</v>
+      </c>
+      <c r="D21" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="E21" s="17" t="s">
+        <v>57</v>
+      </c>
+      <c r="F21" s="17" t="s">
+        <v>58</v>
+      </c>
+      <c r="G21" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="H21" s="16" t="s">
+        <v>52</v>
+      </c>
+      <c r="I21" s="17"/>
+    </row>
+    <row r="22" spans="1:9" s="4" customFormat="1" ht="138" x14ac:dyDescent="0.3">
+      <c r="A22" s="63"/>
+      <c r="B22" s="63"/>
+      <c r="C22" s="16">
         <v>12.4</v>
       </c>
-      <c r="D20" s="17" t="s">
+      <c r="D22" s="17" t="s">
+        <v>177</v>
+      </c>
+      <c r="E22" s="17" t="s">
+        <v>179</v>
+      </c>
+      <c r="F22" s="17" t="s">
         <v>180</v>
       </c>
-      <c r="E20" s="17" t="s">
+      <c r="G22" s="17" t="s">
+        <v>181</v>
+      </c>
+      <c r="H22" s="16"/>
+      <c r="I22" s="17"/>
+    </row>
+    <row r="23" spans="1:9" s="4" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="63"/>
+      <c r="B23" s="63"/>
+      <c r="C23" s="16">
+        <v>12.5</v>
+      </c>
+      <c r="D23" s="17" t="s">
         <v>182</v>
       </c>
-      <c r="F20" s="17" t="s">
+      <c r="E23" s="17" t="s">
+        <v>184</v>
+      </c>
+      <c r="F23" s="17" t="s">
         <v>183</v>
       </c>
-      <c r="G20" s="17" t="s">
-        <v>184</v>
-      </c>
-      <c r="H20" s="16"/>
-      <c r="I20" s="17"/>
-    </row>
-    <row r="21" spans="1:9" s="4" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="67"/>
-      <c r="B21" s="67"/>
-      <c r="C21" s="16">
-        <v>12.5</v>
-      </c>
-      <c r="D21" s="17" t="s">
+      <c r="G23" s="27" t="s">
         <v>185</v>
       </c>
-      <c r="E21" s="17" t="s">
-        <v>187</v>
-      </c>
-      <c r="F21" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="G21" s="27" t="s">
-        <v>188</v>
-      </c>
-      <c r="H21" s="16"/>
-      <c r="I21" s="17"/>
-    </row>
-    <row r="22" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="64">
+      <c r="H23" s="16"/>
+      <c r="I23" s="17"/>
+    </row>
+    <row r="24" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="64">
         <v>14</v>
       </c>
-      <c r="B22" s="64" t="s">
+      <c r="B24" s="64" t="s">
         <v>61</v>
       </c>
-      <c r="C22" s="47">
+      <c r="C24" s="47">
         <v>14.1</v>
       </c>
-      <c r="D22" s="48" t="s">
+      <c r="D24" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="E22" s="48" t="s">
-        <v>144</v>
-      </c>
-      <c r="F22" s="48" t="s">
-        <v>145</v>
-      </c>
-      <c r="G22" s="48" t="s">
-        <v>169</v>
-      </c>
-      <c r="H22" s="47" t="s">
-        <v>102</v>
-      </c>
-      <c r="I22" s="48" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="64"/>
-      <c r="B23" s="64"/>
-      <c r="C23" s="47">
-        <v>14.2</v>
-      </c>
-      <c r="D23" s="48" t="s">
-        <v>15</v>
-      </c>
-      <c r="E23" s="48" t="s">
-        <v>146</v>
-      </c>
-      <c r="F23" s="48" t="s">
-        <v>147</v>
-      </c>
-      <c r="G23" s="48" t="s">
-        <v>170</v>
-      </c>
-      <c r="H23" s="47" t="s">
-        <v>102</v>
-      </c>
-      <c r="I23" s="48" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="64"/>
-      <c r="B24" s="64"/>
-      <c r="C24" s="47">
-        <v>14.3</v>
-      </c>
-      <c r="D24" s="48" t="s">
-        <v>148</v>
-      </c>
       <c r="E24" s="48" t="s">
-        <v>149</v>
+        <v>141</v>
       </c>
       <c r="F24" s="48" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="G24" s="48" t="s">
-        <v>171</v>
+        <v>166</v>
       </c>
       <c r="H24" s="47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I24" s="48" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A25" s="64"/>
       <c r="B25" s="64"/>
       <c r="C25" s="47">
-        <v>14.4</v>
+        <v>14.2</v>
       </c>
       <c r="D25" s="48" t="s">
         <v>15</v>
       </c>
       <c r="E25" s="48" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="F25" s="48" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="G25" s="48" t="s">
-        <v>172</v>
+        <v>167</v>
       </c>
       <c r="H25" s="47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I25" s="48" t="s">
         <v>62</v>
@@ -2265,47 +2338,47 @@
       <c r="A26" s="64"/>
       <c r="B26" s="64"/>
       <c r="C26" s="47">
-        <v>14.5</v>
+        <v>14.3</v>
       </c>
       <c r="D26" s="48" t="s">
-        <v>15</v>
+        <v>145</v>
       </c>
       <c r="E26" s="48" t="s">
-        <v>153</v>
+        <v>146</v>
       </c>
       <c r="F26" s="48" t="s">
-        <v>154</v>
+        <v>147</v>
       </c>
       <c r="G26" s="48" t="s">
-        <v>173</v>
+        <v>168</v>
       </c>
       <c r="H26" s="47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I26" s="48" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
       <c r="A27" s="64"/>
       <c r="B27" s="64"/>
       <c r="C27" s="47">
-        <v>14.6</v>
+        <v>14.4</v>
       </c>
       <c r="D27" s="48" t="s">
         <v>15</v>
       </c>
       <c r="E27" s="48" t="s">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="F27" s="48" t="s">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="G27" s="48" t="s">
-        <v>179</v>
+        <v>169</v>
       </c>
       <c r="H27" s="47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I27" s="48" t="s">
         <v>62</v>
@@ -2315,22 +2388,22 @@
       <c r="A28" s="64"/>
       <c r="B28" s="64"/>
       <c r="C28" s="47">
-        <v>14.7</v>
+        <v>14.5</v>
       </c>
       <c r="D28" s="48" t="s">
         <v>15</v>
       </c>
       <c r="E28" s="48" t="s">
-        <v>157</v>
+        <v>150</v>
       </c>
       <c r="F28" s="48" t="s">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="G28" s="48" t="s">
-        <v>174</v>
+        <v>170</v>
       </c>
       <c r="H28" s="47" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I28" s="48" t="s">
         <v>62</v>
@@ -2340,736 +2413,786 @@
       <c r="A29" s="64"/>
       <c r="B29" s="64"/>
       <c r="C29" s="47">
-        <v>14.8</v>
+        <v>14.6</v>
       </c>
       <c r="D29" s="48" t="s">
         <v>15</v>
       </c>
       <c r="E29" s="48" t="s">
-        <v>159</v>
+        <v>152</v>
       </c>
       <c r="F29" s="48" t="s">
-        <v>160</v>
+        <v>153</v>
       </c>
       <c r="G29" s="48" t="s">
-        <v>175</v>
+        <v>176</v>
       </c>
       <c r="H29" s="47" t="s">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="I29" s="48" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="4" customFormat="1" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A30" s="64"/>
       <c r="B30" s="64"/>
       <c r="C30" s="47">
-        <v>14.9</v>
+        <v>14.7</v>
       </c>
       <c r="D30" s="48" t="s">
         <v>15</v>
       </c>
       <c r="E30" s="48" t="s">
-        <v>161</v>
+        <v>154</v>
       </c>
       <c r="F30" s="48" t="s">
-        <v>162</v>
+        <v>155</v>
       </c>
       <c r="G30" s="48" t="s">
-        <v>176</v>
+        <v>171</v>
       </c>
       <c r="H30" s="47" t="s">
-        <v>140</v>
+        <v>101</v>
       </c>
       <c r="I30" s="48" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
       <c r="A31" s="64"/>
       <c r="B31" s="64"/>
       <c r="C31" s="47">
-        <v>14.1</v>
+        <v>14.8</v>
       </c>
       <c r="D31" s="48" t="s">
         <v>15</v>
       </c>
       <c r="E31" s="48" t="s">
-        <v>163</v>
+        <v>156</v>
       </c>
       <c r="F31" s="48" t="s">
-        <v>164</v>
+        <v>157</v>
       </c>
       <c r="G31" s="48" t="s">
-        <v>177</v>
+        <v>172</v>
       </c>
       <c r="H31" s="47" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I31" s="48" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:9" s="4" customFormat="1" ht="55.05" customHeight="1" x14ac:dyDescent="0.3">
       <c r="A32" s="64"/>
       <c r="B32" s="64"/>
       <c r="C32" s="47">
-        <v>14.11</v>
+        <v>14.9</v>
       </c>
       <c r="D32" s="48" t="s">
         <v>15</v>
       </c>
       <c r="E32" s="48" t="s">
-        <v>165</v>
+        <v>158</v>
       </c>
       <c r="F32" s="48" t="s">
-        <v>166</v>
+        <v>159</v>
       </c>
       <c r="G32" s="48" t="s">
-        <v>178</v>
+        <v>173</v>
       </c>
       <c r="H32" s="47" t="s">
-        <v>140</v>
+        <v>137</v>
       </c>
       <c r="I32" s="48" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="57">
+    <row r="33" spans="1:9" s="4" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A33" s="64"/>
+      <c r="B33" s="64"/>
+      <c r="C33" s="47">
+        <v>14.1</v>
+      </c>
+      <c r="D33" s="48" t="s">
         <v>15</v>
       </c>
-      <c r="B33" s="57" t="s">
+      <c r="E33" s="48" t="s">
+        <v>160</v>
+      </c>
+      <c r="F33" s="48" t="s">
+        <v>161</v>
+      </c>
+      <c r="G33" s="48" t="s">
+        <v>174</v>
+      </c>
+      <c r="H33" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="I33" s="48" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" s="4" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A34" s="64"/>
+      <c r="B34" s="64"/>
+      <c r="C34" s="47">
+        <v>14.11</v>
+      </c>
+      <c r="D34" s="48" t="s">
+        <v>15</v>
+      </c>
+      <c r="E34" s="48" t="s">
+        <v>162</v>
+      </c>
+      <c r="F34" s="48" t="s">
+        <v>163</v>
+      </c>
+      <c r="G34" s="48" t="s">
+        <v>175</v>
+      </c>
+      <c r="H34" s="47" t="s">
+        <v>137</v>
+      </c>
+      <c r="I34" s="48" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A35" s="66">
+        <v>15</v>
+      </c>
+      <c r="B35" s="66" t="s">
         <v>63</v>
       </c>
-      <c r="C33" s="19">
+      <c r="C35" s="19">
         <v>15.1</v>
-      </c>
-      <c r="D33" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="E33" s="20" t="s">
-        <v>65</v>
-      </c>
-      <c r="F33" s="20" t="s">
-        <v>66</v>
-      </c>
-      <c r="G33" s="20" t="s">
-        <v>67</v>
-      </c>
-      <c r="H33" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="I33" s="20" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A34" s="58"/>
-      <c r="B34" s="58"/>
-      <c r="C34" s="19">
-        <v>15.2</v>
-      </c>
-      <c r="D34" s="20" t="s">
-        <v>64</v>
-      </c>
-      <c r="E34" s="20" t="s">
-        <v>68</v>
-      </c>
-      <c r="F34" s="20" t="s">
-        <v>69</v>
-      </c>
-      <c r="G34" s="20" t="s">
-        <v>70</v>
-      </c>
-      <c r="H34" s="19" t="s">
-        <v>141</v>
-      </c>
-      <c r="I34" s="20" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A35" s="58"/>
-      <c r="B35" s="58"/>
-      <c r="C35" s="19">
-        <v>15.3</v>
       </c>
       <c r="D35" s="20" t="s">
         <v>64</v>
       </c>
       <c r="E35" s="20" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
       <c r="F35" s="20" t="s">
-        <v>72</v>
+        <v>66</v>
       </c>
       <c r="G35" s="20" t="s">
-        <v>73</v>
+        <v>67</v>
       </c>
       <c r="H35" s="19" t="s">
-        <v>141</v>
+        <v>138</v>
       </c>
       <c r="I35" s="20" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="36" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A36" s="58"/>
-      <c r="B36" s="58"/>
+      <c r="A36" s="59"/>
+      <c r="B36" s="59"/>
       <c r="C36" s="19">
-        <v>15.4</v>
+        <v>15.2</v>
       </c>
       <c r="D36" s="20" t="s">
         <v>64</v>
       </c>
       <c r="E36" s="20" t="s">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>76</v>
+        <v>70</v>
       </c>
       <c r="H36" s="19" t="s">
-        <v>143</v>
+        <v>138</v>
       </c>
       <c r="I36" s="20" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
     </row>
     <row r="37" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A37" s="58"/>
-      <c r="B37" s="58"/>
+      <c r="A37" s="59"/>
+      <c r="B37" s="59"/>
       <c r="C37" s="19">
-        <v>15.5</v>
+        <v>15.3</v>
       </c>
       <c r="D37" s="20" t="s">
         <v>64</v>
       </c>
       <c r="E37" s="20" t="s">
+        <v>71</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>72</v>
+      </c>
+      <c r="G37" s="20" t="s">
+        <v>73</v>
+      </c>
+      <c r="H37" s="19" t="s">
+        <v>138</v>
+      </c>
+      <c r="I37" s="20" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="59"/>
+      <c r="B38" s="59"/>
+      <c r="C38" s="19">
+        <v>15.4</v>
+      </c>
+      <c r="D38" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E38" s="20" t="s">
+        <v>74</v>
+      </c>
+      <c r="F38" s="20" t="s">
+        <v>75</v>
+      </c>
+      <c r="G38" s="20" t="s">
+        <v>76</v>
+      </c>
+      <c r="H38" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="I38" s="20" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="59"/>
+      <c r="B39" s="59"/>
+      <c r="C39" s="19">
+        <v>15.5</v>
+      </c>
+      <c r="D39" s="20" t="s">
+        <v>64</v>
+      </c>
+      <c r="E39" s="20" t="s">
         <v>77</v>
       </c>
-      <c r="F37" s="20" t="s">
+      <c r="F39" s="20" t="s">
         <v>78</v>
       </c>
-      <c r="G37" s="20" t="s">
+      <c r="G39" s="20" t="s">
         <v>79</v>
       </c>
-      <c r="H37" s="19" t="s">
-        <v>143</v>
-      </c>
-      <c r="I37" s="20" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="66">
+      <c r="H39" s="19" t="s">
+        <v>140</v>
+      </c>
+      <c r="I39" s="20" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A40" s="62">
         <v>16</v>
       </c>
-      <c r="B38" s="66" t="s">
+      <c r="B40" s="62" t="s">
         <v>80</v>
       </c>
-      <c r="C38" s="21">
+      <c r="C40" s="21">
         <v>16.100000000000001</v>
       </c>
-      <c r="D38" s="22" t="s">
+      <c r="D40" s="22" t="s">
         <v>81</v>
       </c>
-      <c r="E38" s="22" t="s">
+      <c r="E40" s="22" t="s">
         <v>82</v>
       </c>
-      <c r="F38" s="22" t="s">
+      <c r="F40" s="22" t="s">
         <v>83</v>
       </c>
-      <c r="G38" s="45" t="s">
+      <c r="G40" s="45" t="s">
         <v>84</v>
       </c>
-      <c r="H38" s="44" t="s">
-        <v>143</v>
-      </c>
-      <c r="I38" s="45" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="58"/>
-      <c r="B39" s="58"/>
-      <c r="C39" s="21">
+      <c r="H40" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="I40" s="45" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A41" s="59"/>
+      <c r="B41" s="59"/>
+      <c r="C41" s="21">
         <v>16.2</v>
       </c>
-      <c r="D39" s="22" t="s">
+      <c r="D41" s="22" t="s">
         <v>85</v>
       </c>
-      <c r="E39" s="22" t="s">
+      <c r="E41" s="22" t="s">
         <v>86</v>
       </c>
-      <c r="F39" s="22" t="s">
+      <c r="F41" s="22" t="s">
         <v>87</v>
       </c>
-      <c r="G39" s="22" t="s">
+      <c r="G41" s="22" t="s">
         <v>88</v>
       </c>
-      <c r="H39" s="44" t="s">
-        <v>143</v>
-      </c>
-      <c r="I39" s="45" t="s">
-        <v>142</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A40" s="65">
+      <c r="H41" s="44" t="s">
+        <v>140</v>
+      </c>
+      <c r="I41" s="45" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="58">
         <v>17</v>
       </c>
-      <c r="B40" s="65" t="s">
+      <c r="B42" s="58" t="s">
         <v>89</v>
       </c>
-      <c r="C40" s="5">
+      <c r="C42" s="5">
         <v>17.100000000000001</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E40" s="37" t="s">
-        <v>167</v>
-      </c>
-      <c r="F40" s="6" t="s">
-        <v>91</v>
-      </c>
-      <c r="G40" s="37" t="s">
-        <v>168</v>
-      </c>
-      <c r="H40" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="I40" s="37" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A41" s="58"/>
-      <c r="B41" s="58"/>
-      <c r="C41" s="5">
-        <v>17.2</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>90</v>
-      </c>
-      <c r="E41" s="37" t="s">
-        <v>112</v>
-      </c>
-      <c r="F41" s="6" t="s">
-        <v>92</v>
-      </c>
-      <c r="G41" s="37" t="s">
-        <v>93</v>
-      </c>
-      <c r="H41" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="I41" s="37" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="58"/>
-      <c r="B42" s="58"/>
-      <c r="C42" s="5">
-        <v>17.3</v>
       </c>
       <c r="D42" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E42" s="6" t="s">
-        <v>94</v>
-      </c>
-      <c r="F42" s="37" t="s">
-        <v>113</v>
+      <c r="E42" s="37" t="s">
+        <v>164</v>
+      </c>
+      <c r="F42" s="6" t="s">
+        <v>91</v>
       </c>
       <c r="G42" s="37" t="s">
-        <v>116</v>
+        <v>165</v>
       </c>
       <c r="H42" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I42" s="37" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="43" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="58"/>
-      <c r="B43" s="58"/>
+      <c r="A43" s="59"/>
+      <c r="B43" s="59"/>
       <c r="C43" s="5">
-        <v>17.399999999999999</v>
+        <v>17.2</v>
       </c>
       <c r="D43" s="6" t="s">
         <v>90</v>
       </c>
       <c r="E43" s="37" t="s">
-        <v>115</v>
-      </c>
-      <c r="F43" s="37" t="s">
-        <v>114</v>
+        <v>111</v>
+      </c>
+      <c r="F43" s="6" t="s">
+        <v>92</v>
       </c>
       <c r="G43" s="37" t="s">
-        <v>120</v>
+        <v>93</v>
       </c>
       <c r="H43" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I43" s="37" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="44" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A44" s="58"/>
-      <c r="B44" s="58"/>
+      <c r="A44" s="59"/>
+      <c r="B44" s="59"/>
       <c r="C44" s="5">
-        <v>17.5</v>
+        <v>17.3</v>
       </c>
       <c r="D44" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E44" s="37" t="s">
-        <v>117</v>
+      <c r="E44" s="6" t="s">
+        <v>94</v>
       </c>
       <c r="F44" s="37" t="s">
-        <v>118</v>
+        <v>112</v>
       </c>
       <c r="G44" s="37" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="H44" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I44" s="37" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="45" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="58"/>
-      <c r="B45" s="58"/>
+      <c r="A45" s="59"/>
+      <c r="B45" s="59"/>
       <c r="C45" s="5">
-        <v>17.600000000000001</v>
+        <v>17.399999999999999</v>
       </c>
       <c r="D45" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E45" s="6" t="s">
-        <v>95</v>
+      <c r="E45" s="37" t="s">
+        <v>114</v>
       </c>
       <c r="F45" s="37" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="G45" s="37" t="s">
-        <v>122</v>
+        <v>119</v>
       </c>
       <c r="H45" s="5" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="I45" s="37" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="46" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="58"/>
-      <c r="B46" s="58"/>
+      <c r="A46" s="59"/>
+      <c r="B46" s="59"/>
       <c r="C46" s="5">
-        <v>17.7</v>
+        <v>17.5</v>
       </c>
       <c r="D46" s="6" t="s">
         <v>90</v>
       </c>
-      <c r="E46" s="6" t="s">
+      <c r="E46" s="37" t="s">
+        <v>116</v>
+      </c>
+      <c r="F46" s="37" t="s">
+        <v>117</v>
+      </c>
+      <c r="G46" s="37" t="s">
+        <v>118</v>
+      </c>
+      <c r="H46" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I46" s="37" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A47" s="59"/>
+      <c r="B47" s="59"/>
+      <c r="C47" s="5">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E47" s="6" t="s">
+        <v>95</v>
+      </c>
+      <c r="F47" s="37" t="s">
+        <v>120</v>
+      </c>
+      <c r="G47" s="37" t="s">
+        <v>121</v>
+      </c>
+      <c r="H47" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I47" s="37" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" s="4" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="59"/>
+      <c r="B48" s="59"/>
+      <c r="C48" s="5">
+        <v>17.7</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>90</v>
+      </c>
+      <c r="E48" s="6" t="s">
         <v>96</v>
       </c>
-      <c r="F46" s="37" t="s">
+      <c r="F48" s="37" t="s">
+        <v>122</v>
+      </c>
+      <c r="G48" s="37" t="s">
+        <v>129</v>
+      </c>
+      <c r="H48" s="5" t="s">
+        <v>101</v>
+      </c>
+      <c r="I48" s="37" t="s">
         <v>123</v>
       </c>
-      <c r="G46" s="37" t="s">
-        <v>130</v>
-      </c>
-      <c r="H46" s="5" t="s">
-        <v>102</v>
-      </c>
-      <c r="I46" s="37" t="s">
-        <v>124</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" s="4" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A47" s="68">
+    </row>
+    <row r="49" spans="1:12" s="4" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A49" s="56">
         <v>18</v>
       </c>
-      <c r="B47" s="69" t="s">
+      <c r="B49" s="57" t="s">
+        <v>186</v>
+      </c>
+      <c r="C49" s="53">
+        <v>18.100000000000001</v>
+      </c>
+      <c r="D49" s="49" t="s">
+        <v>187</v>
+      </c>
+      <c r="E49" s="49" t="s">
+        <v>188</v>
+      </c>
+      <c r="F49" s="49" t="s">
         <v>189</v>
       </c>
-      <c r="C47" s="53">
-        <v>18.100000000000001</v>
-      </c>
-      <c r="D47" s="49" t="s">
-        <v>190</v>
-      </c>
-      <c r="E47" s="49" t="s">
-        <v>191</v>
-      </c>
-      <c r="F47" s="49" t="s">
-        <v>192</v>
-      </c>
-      <c r="G47" s="49" t="s">
-        <v>196</v>
-      </c>
-      <c r="H47" s="53"/>
-      <c r="I47" s="54"/>
-    </row>
-    <row r="48" spans="1:9" s="4" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A48" s="68"/>
-      <c r="B48" s="69"/>
-      <c r="C48" s="52">
-        <v>18.2</v>
-      </c>
-      <c r="D48" s="49" t="s">
+      <c r="G49" s="49" t="s">
         <v>193</v>
-      </c>
-      <c r="E48" s="49" t="s">
-        <v>194</v>
-      </c>
-      <c r="F48" s="49" t="s">
-        <v>186</v>
-      </c>
-      <c r="G48" s="49" t="s">
-        <v>195</v>
-      </c>
-      <c r="H48" s="53"/>
-      <c r="I48" s="54"/>
-    </row>
-    <row r="49" spans="1:12" s="4" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A49" s="68">
-        <v>19</v>
-      </c>
-      <c r="B49" s="69" t="s">
-        <v>197</v>
-      </c>
-      <c r="C49" s="53">
-        <v>19.100000000000001</v>
-      </c>
-      <c r="D49" s="49" t="s">
-        <v>198</v>
-      </c>
-      <c r="E49" s="49" t="s">
-        <v>200</v>
-      </c>
-      <c r="F49" s="49" t="s">
-        <v>202</v>
-      </c>
-      <c r="G49" s="49" t="s">
-        <v>203</v>
       </c>
       <c r="H49" s="53"/>
       <c r="I49" s="54"/>
     </row>
     <row r="50" spans="1:12" s="4" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A50" s="68"/>
-      <c r="B50" s="69"/>
+      <c r="A50" s="56"/>
+      <c r="B50" s="57"/>
       <c r="C50" s="52">
-        <v>19.2</v>
+        <v>18.2</v>
       </c>
       <c r="D50" s="49" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="E50" s="49" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="F50" s="49" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G50" s="49" t="s">
-        <v>204</v>
+        <v>192</v>
       </c>
       <c r="H50" s="53"/>
       <c r="I50" s="54"/>
-      <c r="J50" s="3"/>
-      <c r="K50" s="3"/>
-      <c r="L50" s="3"/>
-    </row>
-    <row r="51" spans="1:12" ht="104.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A51" s="68">
-        <v>20</v>
-      </c>
-      <c r="B51" s="69" t="s">
-        <v>205</v>
+    </row>
+    <row r="51" spans="1:12" s="4" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A51" s="56">
+        <v>19</v>
+      </c>
+      <c r="B51" s="57" t="s">
+        <v>194</v>
       </c>
       <c r="C51" s="53">
-        <v>20.100000000000001</v>
+        <v>19.100000000000001</v>
       </c>
       <c r="D51" s="49" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="E51" s="49" t="s">
-        <v>211</v>
+        <v>197</v>
       </c>
       <c r="F51" s="49" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="G51" s="49" t="s">
-        <v>212</v>
+        <v>200</v>
       </c>
       <c r="H51" s="53"/>
       <c r="I51" s="54"/>
     </row>
-    <row r="52" spans="1:12" ht="135" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A52" s="68"/>
-      <c r="B52" s="69"/>
+    <row r="52" spans="1:12" s="4" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A52" s="56"/>
+      <c r="B52" s="57"/>
       <c r="C52" s="52">
-        <v>20.2</v>
+        <v>19.2</v>
       </c>
       <c r="D52" s="49" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="E52" s="49" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="F52" s="49" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G52" s="49" t="s">
-        <v>208</v>
+        <v>201</v>
       </c>
       <c r="H52" s="53"/>
       <c r="I52" s="54"/>
-    </row>
-    <row r="53" spans="1:12" ht="179.4" x14ac:dyDescent="0.3">
-      <c r="A53" s="68">
-        <v>21</v>
-      </c>
-      <c r="B53" s="69" t="s">
-        <v>213</v>
+      <c r="J52" s="3"/>
+      <c r="K52" s="3"/>
+      <c r="L52" s="3"/>
+    </row>
+    <row r="53" spans="1:12" ht="104.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A53" s="56">
+        <v>20</v>
+      </c>
+      <c r="B53" s="57" t="s">
+        <v>202</v>
       </c>
       <c r="C53" s="53">
-        <v>21.1</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="D53" s="49" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="E53" s="49" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="F53" s="49" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="G53" s="49" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="H53" s="53"/>
       <c r="I53" s="54"/>
     </row>
-    <row r="54" spans="1:12" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A54" s="68"/>
-      <c r="B54" s="69"/>
+    <row r="54" spans="1:12" ht="135" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A54" s="56"/>
+      <c r="B54" s="57"/>
       <c r="C54" s="52">
-        <v>21.2</v>
+        <v>20.2</v>
       </c>
       <c r="D54" s="49" t="s">
-        <v>215</v>
-      </c>
-      <c r="E54" s="55" t="s">
-        <v>220</v>
+        <v>204</v>
+      </c>
+      <c r="E54" s="49" t="s">
+        <v>206</v>
       </c>
       <c r="F54" s="49" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="G54" s="49" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="H54" s="53"/>
       <c r="I54" s="54"/>
     </row>
-    <row r="55" spans="1:12" ht="36" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A55" s="2"/>
-      <c r="B55" s="2"/>
-      <c r="C55" s="2"/>
-      <c r="E55" s="49"/>
-      <c r="H55" s="2"/>
-    </row>
-    <row r="56" spans="1:12" ht="31.05" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D56" s="1"/>
-      <c r="F56" s="1"/>
-      <c r="G56" s="1"/>
-      <c r="I56" s="1"/>
-    </row>
-    <row r="57" spans="1:12" ht="34.950000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D57" s="1"/>
-      <c r="F57" s="1"/>
-      <c r="G57" s="1"/>
-      <c r="I57" s="1"/>
-    </row>
-    <row r="58" spans="1:12" ht="31.95" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A58" s="46"/>
-      <c r="B58" s="46"/>
-      <c r="C58" s="46"/>
-      <c r="D58" s="46"/>
-      <c r="E58" s="46"/>
-      <c r="F58" s="46"/>
-      <c r="G58" s="46"/>
-      <c r="H58" s="46"/>
-      <c r="I58" s="46"/>
-    </row>
-    <row r="59" spans="1:12" ht="33.450000000000003" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A59" s="2"/>
-      <c r="B59" s="2"/>
-      <c r="C59" s="2"/>
-      <c r="E59" s="2"/>
-      <c r="H59" s="2"/>
-    </row>
-    <row r="60" spans="1:12" ht="31.5" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="D60" s="1"/>
-      <c r="F60" s="1"/>
-      <c r="G60" s="1"/>
-      <c r="I60" s="1"/>
-    </row>
-    <row r="61" spans="1:12" ht="27.45" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:12" ht="179.4" x14ac:dyDescent="0.3">
+      <c r="A55" s="56">
+        <v>21</v>
+      </c>
+      <c r="B55" s="57" t="s">
+        <v>210</v>
+      </c>
+      <c r="C55" s="53">
+        <v>21.1</v>
+      </c>
+      <c r="D55" s="49" t="s">
+        <v>211</v>
+      </c>
+      <c r="E55" s="49" t="s">
+        <v>214</v>
+      </c>
+      <c r="F55" s="49" t="s">
+        <v>215</v>
+      </c>
+      <c r="G55" s="49" t="s">
+        <v>216</v>
+      </c>
+      <c r="H55" s="53"/>
+      <c r="I55" s="54"/>
+    </row>
+    <row r="56" spans="1:12" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A56" s="56"/>
+      <c r="B56" s="57"/>
+      <c r="C56" s="52">
+        <v>21.2</v>
+      </c>
+      <c r="D56" s="49" t="s">
+        <v>212</v>
+      </c>
+      <c r="E56" s="55" t="s">
+        <v>217</v>
+      </c>
+      <c r="F56" s="49" t="s">
+        <v>183</v>
+      </c>
+      <c r="G56" s="49" t="s">
+        <v>213</v>
+      </c>
+      <c r="H56" s="53"/>
+      <c r="I56" s="54"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A57" s="2"/>
+      <c r="B57" s="2"/>
+      <c r="C57" s="2"/>
+      <c r="E57" s="49"/>
+      <c r="H57" s="2"/>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="D58" s="1"/>
+      <c r="F58" s="1"/>
+      <c r="G58" s="1"/>
+      <c r="I58" s="1"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="D59" s="1"/>
+      <c r="F59" s="1"/>
+      <c r="G59" s="1"/>
+      <c r="I59" s="1"/>
+    </row>
+    <row r="60" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A60" s="46"/>
+      <c r="B60" s="46"/>
+      <c r="C60" s="46"/>
+      <c r="D60" s="46"/>
+      <c r="E60" s="46"/>
+      <c r="F60" s="46"/>
+      <c r="G60" s="46"/>
+      <c r="H60" s="46"/>
+      <c r="I60" s="46"/>
+    </row>
+    <row r="61" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A61" s="2"/>
       <c r="B61" s="2"/>
-      <c r="F61" s="1"/>
-      <c r="G61" s="1"/>
-      <c r="I61" s="1"/>
+      <c r="C61" s="2"/>
+      <c r="E61" s="2"/>
+      <c r="H61" s="2"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="D62" s="1"/>
+      <c r="F62" s="1"/>
+      <c r="G62" s="1"/>
+      <c r="I62" s="1"/>
+    </row>
+    <row r="63" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B63" s="2"/>
+      <c r="F63" s="1"/>
+      <c r="G63" s="1"/>
+      <c r="I63" s="1"/>
     </row>
   </sheetData>
-  <autoFilter ref="I1:I19" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="I1:I21" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="33">
-    <mergeCell ref="A53:A54"/>
-    <mergeCell ref="B53:B54"/>
-    <mergeCell ref="B47:B48"/>
-    <mergeCell ref="A47:A48"/>
-    <mergeCell ref="A49:A50"/>
-    <mergeCell ref="B49:B50"/>
-    <mergeCell ref="A51:A52"/>
-    <mergeCell ref="B51:B52"/>
-    <mergeCell ref="A40:A46"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="B40:B46"/>
-    <mergeCell ref="A10:A12"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B17:B21"/>
-    <mergeCell ref="A17:A21"/>
-    <mergeCell ref="B22:B32"/>
-    <mergeCell ref="B38:B39"/>
+    <mergeCell ref="B8:B11"/>
+    <mergeCell ref="A8:A11"/>
     <mergeCell ref="B5:B6"/>
     <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A33:A37"/>
+    <mergeCell ref="A35:A39"/>
     <mergeCell ref="I1:I2"/>
     <mergeCell ref="D1:F1"/>
-    <mergeCell ref="A13:A16"/>
-    <mergeCell ref="A8:A9"/>
-    <mergeCell ref="B10:B12"/>
+    <mergeCell ref="A15:A18"/>
+    <mergeCell ref="B12:B14"/>
     <mergeCell ref="H1:H2"/>
-    <mergeCell ref="B33:B37"/>
+    <mergeCell ref="B35:B39"/>
     <mergeCell ref="A1:A2"/>
-    <mergeCell ref="A22:A32"/>
+    <mergeCell ref="A24:A34"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="B1:B2"/>
-    <mergeCell ref="B8:B9"/>
+    <mergeCell ref="A42:A48"/>
+    <mergeCell ref="B15:B18"/>
+    <mergeCell ref="B42:B48"/>
+    <mergeCell ref="A12:A14"/>
+    <mergeCell ref="A40:A41"/>
+    <mergeCell ref="B19:B23"/>
+    <mergeCell ref="A19:A23"/>
+    <mergeCell ref="B24:B34"/>
+    <mergeCell ref="B40:B41"/>
+    <mergeCell ref="A55:A56"/>
+    <mergeCell ref="B55:B56"/>
+    <mergeCell ref="B49:B50"/>
+    <mergeCell ref="A49:A50"/>
+    <mergeCell ref="A51:A52"/>
+    <mergeCell ref="B51:B52"/>
+    <mergeCell ref="A53:A54"/>
+    <mergeCell ref="B53:B54"/>
   </mergeCells>
   <phoneticPr fontId="6" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Soubhanik/checkupp_product_backlog_final.xlsx
+++ b/Soubhanik/checkupp_product_backlog_final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Checkupp\CheckUpp\Soubhanik\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Soubhanik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AE628EB5-057C-4A7F-BB1B-802E55CD0742}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0799820-4E7B-4D4D-BCBF-B65CB046B9B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -37,7 +37,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Sayan:</t>
         </r>
@@ -46,7 +46,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Have to check whether it's a compliance green flag to take child's DOB or age for the app</t>
@@ -61,7 +61,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Sayan:</t>
         </r>
@@ -70,7 +70,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Right now "Add New Vaccination" have the option to add custom Travel Vaccine. Should it be made into a distinct tab like "Recommended for you"?</t>
@@ -85,7 +85,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t>Sayan:</t>
         </r>
@@ -94,7 +94,7 @@
             <sz val="9"/>
             <color indexed="81"/>
             <rFont val="Tahoma"/>
-            <charset val="1"/>
+            <family val="2"/>
           </rPr>
           <t xml:space="preserve">
 Right now the app saves documents in cloud buckets. If we let users save them in local device (mobile/pc), do we still need to let them save it in their choice of cloud (gcloud, icloud etc.)?</t>
@@ -106,7 +106,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="497" uniqueCount="315">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="311">
   <si>
     <t>Epic #</t>
   </si>
@@ -1194,49 +1194,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t>Upload Report</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> after saving my custom health check</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I can store supporting medical reports in my </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Document Wallet</t>
-    </r>
-  </si>
-  <si>
-    <t>17.10.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">tap </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t>Add to Calendar</t>
     </r>
     <r>
@@ -1410,6 +1367,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> option for the links in my Document Wallet</t>
@@ -1435,6 +1393,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> option for the links in my Document Wallet</t>
@@ -1690,11 +1649,6 @@
 3. The saved record must appear in Health Check History.</t>
   </si>
   <si>
-    <t>1. Tapping Upload Report must open the Document Wallet.
-2. Users must be able to upload supported medical reports.
-3. Uploaded reports must be linked to the custom health check.</t>
-  </si>
-  <si>
     <t>1. Selecting Add to Calendar must open the calendar sync flow.
 2. Appointment details must be added to the selected calendar.
 3. A confirmation message must be displayed after successful calendar synchronisation.</t>
@@ -1712,6 +1666,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Appointment Details</t>
@@ -1721,6 +1676,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> while creating a custom health check on the </t>
@@ -1731,6 +1687,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Other Ailments</t>
@@ -1740,6 +1697,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> screen</t>
@@ -1757,6 +1715,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> User must be able to enter appointment date, time and location.</t>
@@ -1767,6 +1726,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>2.</t>
@@ -1776,6 +1736,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Appointment details must be linked to the health check.</t>
@@ -1786,6 +1747,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>3.</t>
@@ -1795,6 +1757,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Appointment information must be saved successfully.</t>
@@ -1810,6 +1773,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Save Health Check</t>
@@ -1819,6 +1783,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> on the </t>
@@ -1829,6 +1794,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Other Ailments</t>
@@ -1838,6 +1804,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> screen</t>
@@ -1853,6 +1820,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Add to Calendar</t>
@@ -1862,6 +1830,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> screen</t>
@@ -1876,6 +1845,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> App must display an </t>
@@ -1886,6 +1856,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Add to Calendar</t>
@@ -1895,6 +1866,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> prompt after saving.</t>
@@ -1905,6 +1877,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>2.</t>
@@ -1914,6 +1887,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> User must be able to add or dismiss the prompt.</t>
@@ -1924,6 +1898,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>3.</t>
@@ -1933,6 +1908,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Appointment details must be retained regardless of the user's choice.</t>
@@ -1951,6 +1927,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Allow</t>
@@ -1960,6 +1937,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> on the </t>
@@ -1970,6 +1948,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Calendar Permission</t>
@@ -1979,6 +1958,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> screen after selecting </t>
@@ -1989,6 +1969,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Add to Calendar</t>
@@ -2004,6 +1985,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Select Calendar</t>
@@ -2013,6 +1995,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> screen</t>
@@ -2027,6 +2010,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> App must request calendar permission before the first sync.</t>
@@ -2037,6 +2021,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>2.</t>
@@ -2046,6 +2031,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> User must be able to allow or deny access.</t>
@@ -2056,6 +2042,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>3.</t>
@@ -2065,6 +2052,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Permission request should not appear again once a choice has been made.</t>
@@ -2080,6 +2068,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Select Calendar</t>
@@ -2089,6 +2078,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> screen</t>
@@ -2106,6 +2096,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> User must be able to choose Google Calendar, Apple Calendar/iCal or Outlook (where supported).</t>
@@ -2116,6 +2107,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>2.</t>
@@ -2125,6 +2117,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Selected calendar must be remembered for future syncs.</t>
@@ -2135,6 +2128,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>3.</t>
@@ -2144,6 +2138,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> User must be able to change the selected calendar later.</t>
@@ -2159,6 +2154,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Event Preview</t>
@@ -2168,6 +2164,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> screen</t>
@@ -2185,6 +2182,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Event preview must display title, date, time, location and reminder.</t>
@@ -2195,6 +2193,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>2.</t>
@@ -2204,6 +2203,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> User must be able to edit or cancel before syncing.</t>
@@ -2214,6 +2214,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>3.</t>
@@ -2223,6 +2224,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Calendar event must match the displayed details.</t>
@@ -2238,6 +2240,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Add to Calendar</t>
@@ -2247,6 +2250,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> on the </t>
@@ -2257,6 +2261,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Event Preview</t>
@@ -2266,6 +2271,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> screen</t>
@@ -2281,6 +2287,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Success</t>
@@ -2290,6 +2297,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> screen</t>
@@ -2304,6 +2312,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> App must display a success message after syncing.</t>
@@ -2314,6 +2323,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>2.</t>
@@ -2323,6 +2333,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> User must be able to view the calendar event.</t>
@@ -2333,6 +2344,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>3.</t>
@@ -2342,6 +2354,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Appointment must exist in the selected calendar.</t>
@@ -2357,6 +2370,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>View Upcoming Appointments</t>
@@ -2366,6 +2380,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> on the </t>
@@ -2376,6 +2391,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Success</t>
@@ -2385,6 +2401,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> screen</t>
@@ -2400,6 +2417,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Upcoming Appointments</t>
@@ -2409,6 +2427,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> screen</t>
@@ -2423,6 +2442,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Upcoming Appointments screen must display all synced appointments.</t>
@@ -2433,6 +2453,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>2.</t>
@@ -2442,6 +2463,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Appointments must be grouped by date.</t>
@@ -2452,6 +2474,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>3.</t>
@@ -2461,6 +2484,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> User must be able to open the device calendar from this screen.</t>
@@ -2476,6 +2500,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Calendar</t>
@@ -2485,6 +2510,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> icon on the </t>
@@ -2495,6 +2521,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Screenings</t>
@@ -2504,6 +2531,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> screen</t>
@@ -2519,6 +2547,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Calendar &amp; Sync Settings</t>
@@ -2528,6 +2557,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> screen to manage my calendar preferences</t>
@@ -2542,6 +2572,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Tapping the calendar icon must open Calendar &amp; Sync Settings.</t>
@@ -2552,6 +2583,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>2.</t>
@@ -2561,6 +2593,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Settings must display current sync status.</t>
@@ -2571,6 +2604,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>3.</t>
@@ -2580,6 +2614,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> User must be able to access settings at any time.</t>
@@ -2595,6 +2630,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Calendar Sync</t>
@@ -2604,6 +2640,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> on the </t>
@@ -2614,6 +2651,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Calendar &amp; Sync Settings</t>
@@ -2623,6 +2661,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> screen</t>
@@ -2640,6 +2679,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> User must be able to turn Calendar Sync on or off.</t>
@@ -2650,6 +2690,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>2.</t>
@@ -2659,6 +2700,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Preference must be saved across sessions.</t>
@@ -2669,6 +2711,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>3.</t>
@@ -2678,6 +2721,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Existing calendar events must remain unaffected when sync is disabled.</t>
@@ -2692,6 +2736,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> </t>
@@ -2702,6 +2747,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>(renumbered from the duplicate 14.1)</t>
@@ -2717,6 +2763,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Calendar &amp; Sync Settings</t>
@@ -2726,6 +2773,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> screen</t>
@@ -2743,6 +2791,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> User must be able to enable or disable sync for individual modules.</t>
@@ -2753,6 +2802,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>2.</t>
@@ -2762,6 +2812,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Modules include Screenings, Pregnancy, Midlife Health, Menopause and Other Ailments.</t>
@@ -2772,6 +2823,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>3.</t>
@@ -2781,6 +2833,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Only enabled modules should sync appointments.</t>
@@ -2796,6 +2849,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>Calendar &amp; Sync Settings</t>
@@ -2805,6 +2859,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> screen</t>
@@ -2822,6 +2877,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> User must be able to choose reminder intervals.</t>
@@ -2832,6 +2888,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>2.</t>
@@ -2841,6 +2898,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Reminder settings must apply to newly synced appointments.</t>
@@ -2851,6 +2909,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t>3.</t>
@@ -2860,6 +2919,7 @@
         <sz val="11"/>
         <color theme="1"/>
         <rFont val="Calibri"/>
+        <family val="2"/>
         <scheme val="minor"/>
       </rPr>
       <t xml:space="preserve"> Default reminder must be configurable.</t>
@@ -3363,18 +3423,19 @@
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="9"/>
       <color indexed="81"/>
       <name val="Tahoma"/>
-      <charset val="1"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="8"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3382,6 +3443,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3389,6 +3451,7 @@
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
   </fonts>
@@ -3707,8 +3770,74 @@
     <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="16" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -3731,9 +3860,6 @@
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3752,71 +3878,8 @@
     <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4034,51 +4097,51 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L92"/>
-  <sheetFormatPr defaultColWidth="8.90625" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <dimension ref="A1:L91"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="5.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="22.54296875" style="2" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.08984375" style="2" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="20.90625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="64.90625" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="41.54296875" style="3" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="72.54296875" style="3" customWidth="1"/>
-    <col min="8" max="8" width="11.6328125" style="2" customWidth="1"/>
-    <col min="9" max="9" width="15.36328125" style="3" customWidth="1"/>
-    <col min="10" max="12" width="8.90625" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.90625" style="1"/>
+    <col min="1" max="1" width="5.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="22.5546875" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.109375" style="2" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="20.88671875" style="3" customWidth="1"/>
+    <col min="5" max="5" width="64.88671875" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="41.5546875" style="3" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="72.5546875" style="3" customWidth="1"/>
+    <col min="8" max="8" width="11.6640625" style="2" customWidth="1"/>
+    <col min="9" max="9" width="15.33203125" style="3" customWidth="1"/>
+    <col min="10" max="12" width="8.88671875" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.88671875" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A1" s="49" t="s">
+    <row r="1" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A1" s="71" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="49" t="s">
+      <c r="B1" s="71" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="54" t="s">
+      <c r="C1" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="54" t="s">
+      <c r="D1" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="54" t="s">
+      <c r="E1" s="76"/>
+      <c r="F1" s="76"/>
+      <c r="G1" s="75" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="49" t="s">
+      <c r="H1" s="71" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="49" t="s">
+      <c r="I1" s="71" t="s">
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A2" s="50"/>
-      <c r="B2" s="50"/>
-      <c r="C2" s="55"/>
+    <row r="2" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A2" s="52"/>
+      <c r="B2" s="52"/>
+      <c r="C2" s="76"/>
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
@@ -4088,31 +4151,31 @@
       <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="54"/>
-      <c r="H2" s="50"/>
-      <c r="I2" s="50"/>
-    </row>
-    <row r="3" spans="1:9" s="5" customFormat="1" ht="156" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A3" s="56">
+      <c r="G2" s="75"/>
+      <c r="H2" s="52"/>
+      <c r="I2" s="52"/>
+    </row>
+    <row r="3" spans="1:9" s="5" customFormat="1" ht="156" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="77">
         <v>1</v>
       </c>
-      <c r="B3" s="56" t="s">
+      <c r="B3" s="77" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="30">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F3" s="29" t="s">
+        <v>205</v>
+      </c>
+      <c r="G3" s="30" t="s">
         <v>208</v>
-      </c>
-      <c r="G3" s="30" t="s">
-        <v>211</v>
       </c>
       <c r="H3" s="29" t="s">
         <v>11</v>
@@ -4121,95 +4184,95 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="6" customFormat="1" ht="130" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A4" s="56"/>
-      <c r="B4" s="56"/>
+    <row r="4" spans="1:9" s="6" customFormat="1" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="77"/>
+      <c r="B4" s="77"/>
       <c r="C4" s="30">
         <v>1.2</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="F4" s="29" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="G4" s="30" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
     </row>
-    <row r="5" spans="1:9" s="6" customFormat="1" ht="130" x14ac:dyDescent="0.35">
-      <c r="A5" s="56"/>
-      <c r="B5" s="56"/>
+    <row r="5" spans="1:9" s="6" customFormat="1" ht="138" x14ac:dyDescent="0.3">
+      <c r="A5" s="77"/>
+      <c r="B5" s="77"/>
       <c r="C5" s="30">
         <v>1.3</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="G5" s="30" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H5" s="29"/>
       <c r="I5" s="29"/>
     </row>
-    <row r="6" spans="1:9" s="6" customFormat="1" ht="130" x14ac:dyDescent="0.35">
-      <c r="A6" s="56"/>
-      <c r="B6" s="56"/>
+    <row r="6" spans="1:9" s="6" customFormat="1" ht="138" x14ac:dyDescent="0.3">
+      <c r="A6" s="77"/>
+      <c r="B6" s="77"/>
       <c r="C6" s="30">
         <v>1.4</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="G6" s="30" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H6" s="29"/>
       <c r="I6" s="29"/>
     </row>
-    <row r="7" spans="1:9" s="6" customFormat="1" ht="143" x14ac:dyDescent="0.35">
-      <c r="A7" s="56"/>
-      <c r="B7" s="56"/>
+    <row r="7" spans="1:9" s="6" customFormat="1" ht="165.6" x14ac:dyDescent="0.3">
+      <c r="A7" s="77"/>
+      <c r="B7" s="77"/>
       <c r="C7" s="30">
         <v>1.5</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="G7" s="30" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H7" s="29"/>
       <c r="I7" s="29"/>
     </row>
-    <row r="8" spans="1:9" s="6" customFormat="1" ht="117" x14ac:dyDescent="0.35">
-      <c r="A8" s="51">
+    <row r="8" spans="1:9" s="6" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A8" s="72">
         <v>5</v>
       </c>
-      <c r="B8" s="51" t="s">
+      <c r="B8" s="72" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="8">
@@ -4234,9 +4297,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="6" customFormat="1" ht="117" x14ac:dyDescent="0.35">
-      <c r="A9" s="52"/>
-      <c r="B9" s="52"/>
+    <row r="9" spans="1:9" s="6" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A9" s="73"/>
+      <c r="B9" s="73"/>
       <c r="C9" s="8">
         <v>5.2</v>
       </c>
@@ -4255,9 +4318,9 @@
       <c r="H9" s="9"/>
       <c r="I9" s="7"/>
     </row>
-    <row r="10" spans="1:9" s="6" customFormat="1" ht="195" x14ac:dyDescent="0.35">
-      <c r="A10" s="52"/>
-      <c r="B10" s="52"/>
+    <row r="10" spans="1:9" s="6" customFormat="1" ht="165.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="73"/>
+      <c r="B10" s="73"/>
       <c r="C10" s="8">
         <v>5.3</v>
       </c>
@@ -4276,53 +4339,53 @@
       <c r="H10" s="9"/>
       <c r="I10" s="7"/>
     </row>
-    <row r="11" spans="1:9" s="42" customFormat="1" ht="221" x14ac:dyDescent="0.35">
-      <c r="A11" s="52"/>
-      <c r="B11" s="52"/>
+    <row r="11" spans="1:9" s="78" customFormat="1" ht="207" x14ac:dyDescent="0.3">
+      <c r="A11" s="73"/>
+      <c r="B11" s="73"/>
       <c r="C11" s="39">
         <v>5.4</v>
       </c>
       <c r="D11" s="40" t="s">
+        <v>212</v>
+      </c>
+      <c r="E11" s="40" t="s">
         <v>215</v>
       </c>
-      <c r="E11" s="40" t="s">
-        <v>218</v>
-      </c>
       <c r="F11" s="40" t="s">
-        <v>217</v>
+        <v>214</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H11" s="41"/>
       <c r="I11" s="40"/>
     </row>
-    <row r="12" spans="1:9" s="42" customFormat="1" ht="169" x14ac:dyDescent="0.35">
-      <c r="A12" s="53"/>
-      <c r="B12" s="53"/>
+    <row r="12" spans="1:9" s="78" customFormat="1" ht="151.80000000000001" x14ac:dyDescent="0.3">
+      <c r="A12" s="74"/>
+      <c r="B12" s="74"/>
       <c r="C12" s="39">
         <v>5.5</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F12" s="40" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="H12" s="41"/>
       <c r="I12" s="40"/>
     </row>
-    <row r="13" spans="1:9" s="42" customFormat="1" ht="169" x14ac:dyDescent="0.35">
-      <c r="A13" s="43">
+    <row r="13" spans="1:9" s="78" customFormat="1" ht="151.80000000000001" x14ac:dyDescent="0.3">
+      <c r="A13" s="65">
         <v>6</v>
       </c>
-      <c r="B13" s="43" t="s">
+      <c r="B13" s="65" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="39">
@@ -4347,9 +4410,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="6" customFormat="1" ht="143" x14ac:dyDescent="0.35">
-      <c r="A14" s="44"/>
-      <c r="B14" s="44"/>
+    <row r="14" spans="1:9" s="6" customFormat="1" ht="138" x14ac:dyDescent="0.3">
+      <c r="A14" s="66"/>
+      <c r="B14" s="66"/>
       <c r="C14" s="11">
         <v>6.2</v>
       </c>
@@ -4357,20 +4420,20 @@
         <v>26</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H14" s="12"/>
       <c r="I14" s="10"/>
     </row>
-    <row r="15" spans="1:9" s="6" customFormat="1" ht="182" x14ac:dyDescent="0.35">
-      <c r="A15" s="44"/>
-      <c r="B15" s="44"/>
+    <row r="15" spans="1:9" s="6" customFormat="1" ht="165.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="66"/>
+      <c r="B15" s="66"/>
       <c r="C15" s="11">
         <v>6.3</v>
       </c>
@@ -4389,9 +4452,9 @@
       <c r="H15" s="12"/>
       <c r="I15" s="10"/>
     </row>
-    <row r="16" spans="1:9" s="6" customFormat="1" ht="78" x14ac:dyDescent="0.35">
-      <c r="A16" s="44"/>
-      <c r="B16" s="45"/>
+    <row r="16" spans="1:9" s="6" customFormat="1" ht="69" x14ac:dyDescent="0.3">
+      <c r="A16" s="66"/>
+      <c r="B16" s="67"/>
       <c r="C16" s="35">
         <v>6.4</v>
       </c>
@@ -4414,11 +4477,11 @@
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:9" s="6" customFormat="1" ht="130" x14ac:dyDescent="0.35">
-      <c r="A17" s="46">
+    <row r="17" spans="1:9" s="6" customFormat="1" ht="138" x14ac:dyDescent="0.3">
+      <c r="A17" s="68">
         <v>7</v>
       </c>
-      <c r="B17" s="43" t="s">
+      <c r="B17" s="65" t="s">
         <v>38</v>
       </c>
       <c r="C17" s="11">
@@ -4443,9 +4506,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A18" s="47"/>
-      <c r="B18" s="44"/>
+    <row r="18" spans="1:9" s="6" customFormat="1" ht="69" x14ac:dyDescent="0.3">
+      <c r="A18" s="69"/>
+      <c r="B18" s="66"/>
       <c r="C18" s="11">
         <v>7.2</v>
       </c>
@@ -4466,9 +4529,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="6" customFormat="1" ht="169" x14ac:dyDescent="0.35">
-      <c r="A19" s="47"/>
-      <c r="B19" s="44"/>
+    <row r="19" spans="1:9" s="6" customFormat="1" ht="179.4" x14ac:dyDescent="0.3">
+      <c r="A19" s="69"/>
+      <c r="B19" s="66"/>
       <c r="C19" s="11">
         <v>7.3</v>
       </c>
@@ -4476,7 +4539,7 @@
         <v>39</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>46</v>
@@ -4487,9 +4550,9 @@
       <c r="H19" s="12"/>
       <c r="I19" s="10"/>
     </row>
-    <row r="20" spans="1:9" s="6" customFormat="1" ht="182" x14ac:dyDescent="0.35">
-      <c r="A20" s="48"/>
-      <c r="B20" s="45"/>
+    <row r="20" spans="1:9" s="6" customFormat="1" ht="165.6" x14ac:dyDescent="0.3">
+      <c r="A20" s="70"/>
+      <c r="B20" s="67"/>
       <c r="C20" s="11">
         <v>7.4</v>
       </c>
@@ -4497,7 +4560,7 @@
         <v>39</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>48</v>
@@ -4508,11 +4571,11 @@
       <c r="H20" s="12"/>
       <c r="I20" s="10"/>
     </row>
-    <row r="21" spans="1:9" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A21" s="72">
+    <row r="21" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A21" s="48">
         <v>8</v>
       </c>
-      <c r="B21" s="72" t="s">
+      <c r="B21" s="48" t="s">
         <v>50</v>
       </c>
       <c r="C21" s="14">
@@ -4535,9 +4598,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A22" s="73"/>
-      <c r="B22" s="73"/>
+    <row r="22" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A22" s="49"/>
+      <c r="B22" s="49"/>
       <c r="C22" s="14">
         <v>9.3000000000000007</v>
       </c>
@@ -4558,9 +4621,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="6" customFormat="1" ht="52" x14ac:dyDescent="0.35">
-      <c r="A23" s="74"/>
-      <c r="B23" s="74"/>
+    <row r="23" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A23" s="50"/>
+      <c r="B23" s="50"/>
       <c r="C23" s="14">
         <v>9.4</v>
       </c>
@@ -4581,11 +4644,11 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="6" customFormat="1" ht="52" x14ac:dyDescent="0.35">
-      <c r="A24" s="70">
+    <row r="24" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="46">
         <v>12</v>
       </c>
-      <c r="B24" s="70" t="s">
+      <c r="B24" s="46" t="s">
         <v>64</v>
       </c>
       <c r="C24" s="16">
@@ -4610,9 +4673,9 @@
         <v>70</v>
       </c>
     </row>
-    <row r="25" spans="1:9" s="6" customFormat="1" ht="52" x14ac:dyDescent="0.35">
-      <c r="A25" s="70"/>
-      <c r="B25" s="70"/>
+    <row r="25" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="46"/>
+      <c r="B25" s="46"/>
       <c r="C25" s="16">
         <v>12.2</v>
       </c>
@@ -4635,9 +4698,9 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A26" s="70"/>
-      <c r="B26" s="70"/>
+    <row r="26" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="46"/>
+      <c r="B26" s="46"/>
       <c r="C26" s="16">
         <v>12.3</v>
       </c>
@@ -4660,9 +4723,9 @@
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="6" customFormat="1" ht="130" x14ac:dyDescent="0.35">
-      <c r="A27" s="70"/>
-      <c r="B27" s="70"/>
+    <row r="27" spans="1:9" s="6" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A27" s="46"/>
+      <c r="B27" s="46"/>
       <c r="C27" s="16">
         <v>12.4</v>
       </c>
@@ -4685,9 +4748,9 @@
         <v>70</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="6" customFormat="1" ht="117" x14ac:dyDescent="0.35">
-      <c r="A28" s="70"/>
-      <c r="B28" s="70"/>
+    <row r="28" spans="1:9" s="6" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A28" s="46"/>
+      <c r="B28" s="46"/>
       <c r="C28" s="16">
         <v>12.5</v>
       </c>
@@ -4710,27 +4773,27 @@
         <v>70</v>
       </c>
     </row>
-    <row r="29" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A29" s="71">
+    <row r="29" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A29" s="47">
         <v>14</v>
       </c>
-      <c r="B29" s="71" t="s">
+      <c r="B29" s="47" t="s">
         <v>84</v>
       </c>
       <c r="C29" s="18">
         <v>14.1</v>
       </c>
-      <c r="D29" s="77" t="s">
+      <c r="D29" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="E29" s="77" t="s">
-        <v>288</v>
-      </c>
-      <c r="F29" s="77" t="s">
-        <v>254</v>
-      </c>
-      <c r="G29" s="78" t="s">
-        <v>304</v>
+      <c r="E29" s="44" t="s">
+        <v>284</v>
+      </c>
+      <c r="F29" s="44" t="s">
+        <v>250</v>
+      </c>
+      <c r="G29" s="45" t="s">
+        <v>300</v>
       </c>
       <c r="H29" s="17" t="s">
         <v>86</v>
@@ -4739,23 +4802,23 @@
         <v>87</v>
       </c>
     </row>
-    <row r="30" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A30" s="71"/>
-      <c r="B30" s="71"/>
+    <row r="30" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="47"/>
+      <c r="B30" s="47"/>
       <c r="C30" s="18">
         <v>14.2</v>
       </c>
-      <c r="D30" s="77" t="s">
+      <c r="D30" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="E30" s="77" t="s">
-        <v>289</v>
-      </c>
-      <c r="F30" s="77" t="s">
-        <v>290</v>
-      </c>
-      <c r="G30" s="78" t="s">
-        <v>305</v>
+      <c r="E30" s="44" t="s">
+        <v>285</v>
+      </c>
+      <c r="F30" s="44" t="s">
+        <v>286</v>
+      </c>
+      <c r="G30" s="45" t="s">
+        <v>301</v>
       </c>
       <c r="H30" s="17" t="s">
         <v>86</v>
@@ -4764,23 +4827,23 @@
         <v>87</v>
       </c>
     </row>
-    <row r="31" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A31" s="71"/>
-      <c r="B31" s="71"/>
+    <row r="31" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="47"/>
+      <c r="B31" s="47"/>
       <c r="C31" s="18">
         <v>14.3</v>
       </c>
-      <c r="D31" s="77" t="s">
-        <v>259</v>
-      </c>
-      <c r="E31" s="77" t="s">
-        <v>291</v>
-      </c>
-      <c r="F31" s="77" t="s">
-        <v>292</v>
-      </c>
-      <c r="G31" s="78" t="s">
-        <v>306</v>
+      <c r="D31" s="44" t="s">
+        <v>255</v>
+      </c>
+      <c r="E31" s="44" t="s">
+        <v>287</v>
+      </c>
+      <c r="F31" s="44" t="s">
+        <v>288</v>
+      </c>
+      <c r="G31" s="45" t="s">
+        <v>302</v>
       </c>
       <c r="H31" s="17" t="s">
         <v>86</v>
@@ -4789,23 +4852,23 @@
         <v>87</v>
       </c>
     </row>
-    <row r="32" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A32" s="71"/>
-      <c r="B32" s="71"/>
+    <row r="32" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="47"/>
+      <c r="B32" s="47"/>
       <c r="C32" s="18">
         <v>14.4</v>
       </c>
-      <c r="D32" s="77" t="s">
+      <c r="D32" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="E32" s="77" t="s">
-        <v>293</v>
-      </c>
-      <c r="F32" s="77" t="s">
-        <v>264</v>
-      </c>
-      <c r="G32" s="78" t="s">
-        <v>307</v>
+      <c r="E32" s="44" t="s">
+        <v>289</v>
+      </c>
+      <c r="F32" s="44" t="s">
+        <v>260</v>
+      </c>
+      <c r="G32" s="45" t="s">
+        <v>303</v>
       </c>
       <c r="H32" s="17" t="s">
         <v>86</v>
@@ -4814,23 +4877,23 @@
         <v>87</v>
       </c>
     </row>
-    <row r="33" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A33" s="71"/>
-      <c r="B33" s="71"/>
+    <row r="33" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A33" s="47"/>
+      <c r="B33" s="47"/>
       <c r="C33" s="18">
         <v>14.5</v>
       </c>
-      <c r="D33" s="77" t="s">
+      <c r="D33" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="E33" s="77" t="s">
-        <v>294</v>
-      </c>
-      <c r="F33" s="77" t="s">
-        <v>267</v>
-      </c>
-      <c r="G33" s="78" t="s">
-        <v>308</v>
+      <c r="E33" s="44" t="s">
+        <v>290</v>
+      </c>
+      <c r="F33" s="44" t="s">
+        <v>263</v>
+      </c>
+      <c r="G33" s="45" t="s">
+        <v>304</v>
       </c>
       <c r="H33" s="17" t="s">
         <v>86</v>
@@ -4839,23 +4902,23 @@
         <v>87</v>
       </c>
     </row>
-    <row r="34" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A34" s="71"/>
-      <c r="B34" s="71"/>
+    <row r="34" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A34" s="47"/>
+      <c r="B34" s="47"/>
       <c r="C34" s="18">
         <v>14.6</v>
       </c>
-      <c r="D34" s="77" t="s">
+      <c r="D34" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="E34" s="77" t="s">
-        <v>295</v>
-      </c>
-      <c r="F34" s="77" t="s">
-        <v>296</v>
-      </c>
-      <c r="G34" s="78" t="s">
-        <v>309</v>
+      <c r="E34" s="44" t="s">
+        <v>291</v>
+      </c>
+      <c r="F34" s="44" t="s">
+        <v>292</v>
+      </c>
+      <c r="G34" s="45" t="s">
+        <v>305</v>
       </c>
       <c r="H34" s="17" t="s">
         <v>86</v>
@@ -4864,23 +4927,23 @@
         <v>87</v>
       </c>
     </row>
-    <row r="35" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A35" s="71"/>
-      <c r="B35" s="71"/>
+    <row r="35" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="47"/>
+      <c r="B35" s="47"/>
       <c r="C35" s="18">
         <v>14.7</v>
       </c>
-      <c r="D35" s="77" t="s">
+      <c r="D35" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="E35" s="77" t="s">
-        <v>297</v>
-      </c>
-      <c r="F35" s="77" t="s">
-        <v>298</v>
-      </c>
-      <c r="G35" s="78" t="s">
-        <v>310</v>
+      <c r="E35" s="44" t="s">
+        <v>293</v>
+      </c>
+      <c r="F35" s="44" t="s">
+        <v>294</v>
+      </c>
+      <c r="G35" s="45" t="s">
+        <v>306</v>
       </c>
       <c r="H35" s="17" t="s">
         <v>86</v>
@@ -4889,23 +4952,23 @@
         <v>87</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A36" s="71"/>
-      <c r="B36" s="71"/>
+    <row r="36" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A36" s="47"/>
+      <c r="B36" s="47"/>
       <c r="C36" s="18">
         <v>14.8</v>
       </c>
-      <c r="D36" s="77" t="s">
+      <c r="D36" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="E36" s="77" t="s">
-        <v>299</v>
-      </c>
-      <c r="F36" s="77" t="s">
-        <v>300</v>
-      </c>
-      <c r="G36" s="78" t="s">
-        <v>311</v>
+      <c r="E36" s="44" t="s">
+        <v>295</v>
+      </c>
+      <c r="F36" s="44" t="s">
+        <v>296</v>
+      </c>
+      <c r="G36" s="45" t="s">
+        <v>307</v>
       </c>
       <c r="H36" s="17" t="s">
         <v>88</v>
@@ -4914,23 +4977,23 @@
         <v>87</v>
       </c>
     </row>
-    <row r="37" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A37" s="71"/>
-      <c r="B37" s="71"/>
+    <row r="37" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="47"/>
+      <c r="B37" s="47"/>
       <c r="C37" s="18">
         <v>14.9</v>
       </c>
-      <c r="D37" s="77" t="s">
+      <c r="D37" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="E37" s="77" t="s">
-        <v>301</v>
-      </c>
-      <c r="F37" s="77" t="s">
-        <v>279</v>
-      </c>
-      <c r="G37" s="78" t="s">
-        <v>312</v>
+      <c r="E37" s="44" t="s">
+        <v>297</v>
+      </c>
+      <c r="F37" s="44" t="s">
+        <v>275</v>
+      </c>
+      <c r="G37" s="45" t="s">
+        <v>308</v>
       </c>
       <c r="H37" s="17" t="s">
         <v>88</v>
@@ -4939,23 +5002,23 @@
         <v>87</v>
       </c>
     </row>
-    <row r="38" spans="1:9" s="6" customFormat="1" ht="58" x14ac:dyDescent="0.35">
-      <c r="A38" s="71"/>
-      <c r="B38" s="71"/>
+    <row r="38" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A38" s="47"/>
+      <c r="B38" s="47"/>
       <c r="C38" s="18">
         <v>14.1</v>
       </c>
-      <c r="D38" s="77" t="s">
+      <c r="D38" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="E38" s="77" t="s">
-        <v>302</v>
-      </c>
-      <c r="F38" s="77" t="s">
-        <v>283</v>
-      </c>
-      <c r="G38" s="78" t="s">
-        <v>313</v>
+      <c r="E38" s="44" t="s">
+        <v>298</v>
+      </c>
+      <c r="F38" s="44" t="s">
+        <v>279</v>
+      </c>
+      <c r="G38" s="45" t="s">
+        <v>309</v>
       </c>
       <c r="H38" s="17" t="s">
         <v>88</v>
@@ -4964,23 +5027,23 @@
         <v>87</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="6" customFormat="1" ht="43.5" x14ac:dyDescent="0.35">
-      <c r="A39" s="71"/>
-      <c r="B39" s="71"/>
+    <row r="39" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="47"/>
+      <c r="B39" s="47"/>
       <c r="C39" s="18">
         <v>14.11</v>
       </c>
-      <c r="D39" s="77" t="s">
+      <c r="D39" s="44" t="s">
         <v>137</v>
       </c>
-      <c r="E39" s="77" t="s">
-        <v>303</v>
-      </c>
-      <c r="F39" s="77" t="s">
-        <v>286</v>
-      </c>
-      <c r="G39" s="78" t="s">
-        <v>314</v>
+      <c r="E39" s="44" t="s">
+        <v>299</v>
+      </c>
+      <c r="F39" s="44" t="s">
+        <v>282</v>
+      </c>
+      <c r="G39" s="45" t="s">
+        <v>310</v>
       </c>
       <c r="H39" s="17" t="s">
         <v>88</v>
@@ -4989,11 +5052,11 @@
         <v>87</v>
       </c>
     </row>
-    <row r="40" spans="1:9" s="6" customFormat="1" ht="78" x14ac:dyDescent="0.35">
-      <c r="A40" s="57">
+    <row r="40" spans="1:9" s="6" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="51">
         <v>15</v>
       </c>
-      <c r="B40" s="57" t="s">
+      <c r="B40" s="51" t="s">
         <v>89</v>
       </c>
       <c r="C40" s="20">
@@ -5009,7 +5072,7 @@
         <v>92</v>
       </c>
       <c r="G40" s="20" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="H40" s="19" t="s">
         <v>127</v>
@@ -5018,9 +5081,9 @@
         <v>112</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="6" customFormat="1" ht="52" x14ac:dyDescent="0.35">
-      <c r="A41" s="50"/>
-      <c r="B41" s="50"/>
+    <row r="41" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A41" s="52"/>
+      <c r="B41" s="52"/>
       <c r="C41" s="20">
         <v>15.2</v>
       </c>
@@ -5034,7 +5097,7 @@
         <v>94</v>
       </c>
       <c r="G41" s="20" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="H41" s="19" t="s">
         <v>111</v>
@@ -5043,9 +5106,9 @@
         <v>112</v>
       </c>
     </row>
-    <row r="42" spans="1:9" s="6" customFormat="1" ht="52" x14ac:dyDescent="0.35">
-      <c r="A42" s="50"/>
-      <c r="B42" s="50"/>
+    <row r="42" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A42" s="52"/>
+      <c r="B42" s="52"/>
       <c r="C42" s="20">
         <v>15.3</v>
       </c>
@@ -5059,7 +5122,7 @@
         <v>96</v>
       </c>
       <c r="G42" s="20" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H42" s="19" t="s">
         <v>111</v>
@@ -5068,9 +5131,9 @@
         <v>112</v>
       </c>
     </row>
-    <row r="43" spans="1:9" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A43" s="50"/>
-      <c r="B43" s="50"/>
+    <row r="43" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A43" s="52"/>
+      <c r="B43" s="52"/>
       <c r="C43" s="20">
         <v>15.4</v>
       </c>
@@ -5084,7 +5147,7 @@
         <v>98</v>
       </c>
       <c r="G43" s="20" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="H43" s="19" t="s">
         <v>111</v>
@@ -5093,9 +5156,9 @@
         <v>112</v>
       </c>
     </row>
-    <row r="44" spans="1:9" s="6" customFormat="1" ht="52" x14ac:dyDescent="0.35">
-      <c r="A44" s="50"/>
-      <c r="B44" s="50"/>
+    <row r="44" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A44" s="52"/>
+      <c r="B44" s="52"/>
       <c r="C44" s="20">
         <v>15.5</v>
       </c>
@@ -5109,7 +5172,7 @@
         <v>100</v>
       </c>
       <c r="G44" s="20" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="H44" s="19" t="s">
         <v>111</v>
@@ -5118,9 +5181,9 @@
         <v>112</v>
       </c>
     </row>
-    <row r="45" spans="1:9" s="6" customFormat="1" ht="52" x14ac:dyDescent="0.35">
-      <c r="A45" s="50"/>
-      <c r="B45" s="50"/>
+    <row r="45" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A45" s="52"/>
+      <c r="B45" s="52"/>
       <c r="C45" s="20">
         <v>15.6</v>
       </c>
@@ -5134,7 +5197,7 @@
         <v>102</v>
       </c>
       <c r="G45" s="20" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="H45" s="19" t="s">
         <v>111</v>
@@ -5143,9 +5206,9 @@
         <v>112</v>
       </c>
     </row>
-    <row r="46" spans="1:9" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A46" s="50"/>
-      <c r="B46" s="50"/>
+    <row r="46" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A46" s="52"/>
+      <c r="B46" s="52"/>
       <c r="C46" s="20">
         <v>15.7</v>
       </c>
@@ -5159,7 +5222,7 @@
         <v>104</v>
       </c>
       <c r="G46" s="20" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="H46" s="19" t="s">
         <v>111</v>
@@ -5168,9 +5231,9 @@
         <v>112</v>
       </c>
     </row>
-    <row r="47" spans="1:9" s="6" customFormat="1" ht="52" x14ac:dyDescent="0.35">
-      <c r="A47" s="50"/>
-      <c r="B47" s="50"/>
+    <row r="47" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
+      <c r="A47" s="52"/>
+      <c r="B47" s="52"/>
       <c r="C47" s="20">
         <v>15.8</v>
       </c>
@@ -5184,7 +5247,7 @@
         <v>106</v>
       </c>
       <c r="G47" s="20" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="H47" s="19" t="s">
         <v>111</v>
@@ -5193,11 +5256,11 @@
         <v>112</v>
       </c>
     </row>
-    <row r="48" spans="1:9" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A48" s="64">
+    <row r="48" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A48" s="59">
         <v>16</v>
       </c>
-      <c r="B48" s="64" t="s">
+      <c r="B48" s="59" t="s">
         <v>107</v>
       </c>
       <c r="C48" s="36">
@@ -5213,7 +5276,7 @@
         <v>110</v>
       </c>
       <c r="G48" s="22" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="H48" s="21" t="s">
         <v>111</v>
@@ -5222,9 +5285,9 @@
         <v>112</v>
       </c>
     </row>
-    <row r="49" spans="1:9" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A49" s="64"/>
-      <c r="B49" s="64"/>
+    <row r="49" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A49" s="59"/>
+      <c r="B49" s="59"/>
       <c r="C49" s="36">
         <v>16.2</v>
       </c>
@@ -5238,7 +5301,7 @@
         <v>114</v>
       </c>
       <c r="G49" s="22" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="H49" s="21" t="s">
         <v>111</v>
@@ -5247,9 +5310,9 @@
         <v>112</v>
       </c>
     </row>
-    <row r="50" spans="1:9" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A50" s="64"/>
-      <c r="B50" s="64"/>
+    <row r="50" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A50" s="59"/>
+      <c r="B50" s="59"/>
       <c r="C50" s="36">
         <v>16.3</v>
       </c>
@@ -5263,7 +5326,7 @@
         <v>116</v>
       </c>
       <c r="G50" s="22" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="H50" s="21" t="s">
         <v>111</v>
@@ -5272,9 +5335,9 @@
         <v>112</v>
       </c>
     </row>
-    <row r="51" spans="1:9" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A51" s="64"/>
-      <c r="B51" s="64"/>
+    <row r="51" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A51" s="59"/>
+      <c r="B51" s="59"/>
       <c r="C51" s="36">
         <v>16.399999999999999</v>
       </c>
@@ -5288,7 +5351,7 @@
         <v>118</v>
       </c>
       <c r="G51" s="22" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="H51" s="21" t="s">
         <v>111</v>
@@ -5297,9 +5360,9 @@
         <v>112</v>
       </c>
     </row>
-    <row r="52" spans="1:9" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A52" s="64"/>
-      <c r="B52" s="64"/>
+    <row r="52" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A52" s="59"/>
+      <c r="B52" s="59"/>
       <c r="C52" s="36">
         <v>16.5</v>
       </c>
@@ -5313,7 +5376,7 @@
         <v>120</v>
       </c>
       <c r="G52" s="22" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="H52" s="21" t="s">
         <v>111</v>
@@ -5322,9 +5385,9 @@
         <v>112</v>
       </c>
     </row>
-    <row r="53" spans="1:9" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A53" s="50"/>
-      <c r="B53" s="50"/>
+    <row r="53" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A53" s="52"/>
+      <c r="B53" s="52"/>
       <c r="C53" s="36">
         <v>16.600000000000001</v>
       </c>
@@ -5338,7 +5401,7 @@
         <v>122</v>
       </c>
       <c r="G53" s="22" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="H53" s="21" t="s">
         <v>111</v>
@@ -5347,11 +5410,11 @@
         <v>112</v>
       </c>
     </row>
-    <row r="54" spans="1:9" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A54" s="65">
+    <row r="54" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A54" s="60">
         <v>17</v>
       </c>
-      <c r="B54" s="68" t="s">
+      <c r="B54" s="63" t="s">
         <v>123</v>
       </c>
       <c r="C54" s="24">
@@ -5367,7 +5430,7 @@
         <v>126</v>
       </c>
       <c r="G54" s="24" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="H54" s="23" t="s">
         <v>127</v>
@@ -5376,9 +5439,9 @@
         <v>112</v>
       </c>
     </row>
-    <row r="55" spans="1:9" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A55" s="66"/>
-      <c r="B55" s="68"/>
+    <row r="55" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A55" s="61"/>
+      <c r="B55" s="63"/>
       <c r="C55" s="24">
         <v>17.2</v>
       </c>
@@ -5392,7 +5455,7 @@
         <v>129</v>
       </c>
       <c r="G55" s="24" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="H55" s="23" t="s">
         <v>127</v>
@@ -5401,9 +5464,9 @@
         <v>112</v>
       </c>
     </row>
-    <row r="56" spans="1:9" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A56" s="66"/>
-      <c r="B56" s="68"/>
+    <row r="56" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A56" s="61"/>
+      <c r="B56" s="63"/>
       <c r="C56" s="24">
         <v>17.3</v>
       </c>
@@ -5417,7 +5480,7 @@
         <v>131</v>
       </c>
       <c r="G56" s="24" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="H56" s="23" t="s">
         <v>111</v>
@@ -5426,9 +5489,9 @@
         <v>112</v>
       </c>
     </row>
-    <row r="57" spans="1:9" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A57" s="66"/>
-      <c r="B57" s="68"/>
+    <row r="57" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A57" s="61"/>
+      <c r="B57" s="63"/>
       <c r="C57" s="24">
         <v>17.399999999999999</v>
       </c>
@@ -5442,7 +5505,7 @@
         <v>133</v>
       </c>
       <c r="G57" s="24" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="H57" s="23" t="s">
         <v>127</v>
@@ -5451,9 +5514,9 @@
         <v>112</v>
       </c>
     </row>
-    <row r="58" spans="1:9" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A58" s="67"/>
-      <c r="B58" s="68"/>
+    <row r="58" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A58" s="62"/>
+      <c r="B58" s="63"/>
       <c r="C58" s="24">
         <v>17.5</v>
       </c>
@@ -5467,7 +5530,7 @@
         <v>135</v>
       </c>
       <c r="G58" s="24" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H58" s="23" t="s">
         <v>127</v>
@@ -5476,11 +5539,11 @@
         <v>112</v>
       </c>
     </row>
-    <row r="59" spans="1:9" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A59" s="69">
+    <row r="59" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A59" s="64">
         <v>18</v>
       </c>
-      <c r="B59" s="69" t="s">
+      <c r="B59" s="64" t="s">
         <v>136</v>
       </c>
       <c r="C59" s="8">
@@ -5496,7 +5559,7 @@
         <v>139</v>
       </c>
       <c r="G59" s="8" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="H59" s="7" t="s">
         <v>86</v>
@@ -5505,9 +5568,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="60" spans="1:9" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A60" s="50"/>
-      <c r="B60" s="50"/>
+    <row r="60" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A60" s="52"/>
+      <c r="B60" s="52"/>
       <c r="C60" s="8">
         <v>17.2</v>
       </c>
@@ -5521,7 +5584,7 @@
         <v>142</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="H60" s="7" t="s">
         <v>86</v>
@@ -5530,9 +5593,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="61" spans="1:9" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A61" s="50"/>
-      <c r="B61" s="50"/>
+    <row r="61" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A61" s="52"/>
+      <c r="B61" s="52"/>
       <c r="C61" s="8">
         <v>17.3</v>
       </c>
@@ -5546,7 +5609,7 @@
         <v>144</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="H61" s="7" t="s">
         <v>86</v>
@@ -5555,9 +5618,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="62" spans="1:9" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A62" s="50"/>
-      <c r="B62" s="50"/>
+    <row r="62" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A62" s="52"/>
+      <c r="B62" s="52"/>
       <c r="C62" s="8">
         <v>17.399999999999999</v>
       </c>
@@ -5571,7 +5634,7 @@
         <v>85</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="H62" s="7" t="s">
         <v>86</v>
@@ -5580,9 +5643,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="63" spans="1:9" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A63" s="50"/>
-      <c r="B63" s="50"/>
+    <row r="63" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A63" s="52"/>
+      <c r="B63" s="52"/>
       <c r="C63" s="8">
         <v>17.5</v>
       </c>
@@ -5596,7 +5659,7 @@
         <v>147</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="H63" s="7" t="s">
         <v>86</v>
@@ -5605,9 +5668,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="64" spans="1:9" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A64" s="50"/>
-      <c r="B64" s="50"/>
+    <row r="64" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A64" s="52"/>
+      <c r="B64" s="52"/>
       <c r="C64" s="8">
         <v>17.600000000000001</v>
       </c>
@@ -5621,7 +5684,7 @@
         <v>149</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="H64" s="7" t="s">
         <v>86</v>
@@ -5630,9 +5693,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="65" spans="1:12" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A65" s="50"/>
-      <c r="B65" s="50"/>
+    <row r="65" spans="1:12" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A65" s="52"/>
+      <c r="B65" s="52"/>
       <c r="C65" s="8">
         <v>17.7</v>
       </c>
@@ -5646,7 +5709,7 @@
         <v>151</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="H65" s="7" t="s">
         <v>86</v>
@@ -5655,9 +5718,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="66" spans="1:12" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A66" s="50"/>
-      <c r="B66" s="50"/>
+    <row r="66" spans="1:12" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A66" s="52"/>
+      <c r="B66" s="52"/>
       <c r="C66" s="8">
         <v>17.8</v>
       </c>
@@ -5671,7 +5734,7 @@
         <v>153</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="H66" s="7" t="s">
         <v>86</v>
@@ -5680,9 +5743,9 @@
         <v>140</v>
       </c>
     </row>
-    <row r="67" spans="1:12" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A67" s="50"/>
-      <c r="B67" s="50"/>
+    <row r="67" spans="1:12" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A67" s="52"/>
+      <c r="B67" s="52"/>
       <c r="C67" s="8">
         <v>17.899999999999999</v>
       </c>
@@ -5696,7 +5759,7 @@
         <v>155</v>
       </c>
       <c r="G67" s="8" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="H67" s="7" t="s">
         <v>86</v>
@@ -5705,49 +5768,45 @@
         <v>140</v>
       </c>
     </row>
-    <row r="68" spans="1:12" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A68" s="50"/>
-      <c r="B68" s="50"/>
-      <c r="C68" s="8" t="s">
+    <row r="68" spans="1:12" s="6" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A68" s="53">
+        <v>19</v>
+      </c>
+      <c r="B68" s="56" t="s">
         <v>156</v>
       </c>
-      <c r="D68" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="E68" s="7" t="s">
+      <c r="C68" s="26">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="D68" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="F68" s="7" t="s">
+      <c r="E68" s="33" t="s">
         <v>158</v>
       </c>
-      <c r="G68" s="8" t="s">
-        <v>251</v>
-      </c>
-      <c r="H68" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="I68" s="7" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" s="6" customFormat="1" ht="78" x14ac:dyDescent="0.35">
-      <c r="A69" s="58">
-        <v>19</v>
-      </c>
-      <c r="B69" s="61" t="s">
+      <c r="F68" s="33" t="s">
         <v>159</v>
       </c>
-      <c r="C69" s="26">
-        <v>19.100000000000001</v>
+      <c r="G68" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="H68" s="3"/>
+      <c r="I68" s="32"/>
+    </row>
+    <row r="69" spans="1:12" s="6" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A69" s="54"/>
+      <c r="B69" s="57"/>
+      <c r="C69" s="34">
+        <v>19.2</v>
       </c>
       <c r="D69" s="33" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
       <c r="E69" s="33" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="F69" s="33" t="s">
-        <v>162</v>
+        <v>82</v>
       </c>
       <c r="G69" s="31" t="s">
         <v>163</v>
@@ -5755,133 +5814,133 @@
       <c r="H69" s="3"/>
       <c r="I69" s="32"/>
     </row>
-    <row r="70" spans="1:12" s="6" customFormat="1" ht="117" x14ac:dyDescent="0.35">
-      <c r="A70" s="59"/>
-      <c r="B70" s="62"/>
+    <row r="70" spans="1:12" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A70" s="55"/>
+      <c r="B70" s="58"/>
       <c r="C70" s="34">
-        <v>19.2</v>
+        <v>19.3</v>
       </c>
       <c r="D70" s="33" t="s">
+        <v>157</v>
+      </c>
+      <c r="E70" s="33" t="s">
         <v>164</v>
       </c>
-      <c r="E70" s="33" t="s">
+      <c r="F70" s="33" t="s">
         <v>165</v>
       </c>
-      <c r="F70" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="G70" s="31" t="s">
-        <v>166</v>
-      </c>
+      <c r="G70" s="31"/>
       <c r="H70" s="3"/>
       <c r="I70" s="32"/>
     </row>
-    <row r="71" spans="1:12" s="6" customFormat="1" ht="39" x14ac:dyDescent="0.35">
-      <c r="A71" s="60"/>
-      <c r="B71" s="63"/>
-      <c r="C71" s="34">
-        <v>19.3</v>
+    <row r="71" spans="1:12" s="6" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A71" s="53">
+        <v>20</v>
+      </c>
+      <c r="B71" s="56" t="s">
+        <v>166</v>
+      </c>
+      <c r="C71" s="26">
+        <v>20.100000000000001</v>
       </c>
       <c r="D71" s="33" t="s">
-        <v>160</v>
+        <v>167</v>
       </c>
       <c r="E71" s="33" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="F71" s="33" t="s">
-        <v>168</v>
-      </c>
-      <c r="G71" s="31"/>
+        <v>169</v>
+      </c>
+      <c r="G71" s="31" t="s">
+        <v>170</v>
+      </c>
       <c r="H71" s="3"/>
       <c r="I71" s="32"/>
     </row>
-    <row r="72" spans="1:12" s="6" customFormat="1" ht="78" x14ac:dyDescent="0.35">
-      <c r="A72" s="58">
-        <v>20</v>
-      </c>
-      <c r="B72" s="61" t="s">
-        <v>169</v>
-      </c>
-      <c r="C72" s="26">
-        <v>20.100000000000001</v>
+    <row r="72" spans="1:12" s="6" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A72" s="54"/>
+      <c r="B72" s="57"/>
+      <c r="C72" s="34">
+        <v>20.2</v>
       </c>
       <c r="D72" s="33" t="s">
-        <v>170</v>
+        <v>171</v>
       </c>
       <c r="E72" s="33" t="s">
-        <v>171</v>
+        <v>172</v>
       </c>
       <c r="F72" s="33" t="s">
-        <v>172</v>
+        <v>82</v>
       </c>
       <c r="G72" s="31" t="s">
         <v>173</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="32"/>
-    </row>
-    <row r="73" spans="1:12" s="6" customFormat="1" ht="117" x14ac:dyDescent="0.35">
-      <c r="A73" s="59"/>
-      <c r="B73" s="62"/>
-      <c r="C73" s="34">
-        <v>20.2</v>
+      <c r="J72" s="1"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+    </row>
+    <row r="73" spans="1:12" s="6" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A73" s="55"/>
+      <c r="B73" s="58"/>
+      <c r="C73" s="26">
+        <v>20.3</v>
       </c>
       <c r="D73" s="33" t="s">
-        <v>174</v>
+        <v>167</v>
       </c>
       <c r="E73" s="33" t="s">
-        <v>175</v>
-      </c>
-      <c r="F73" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="G73" s="31" t="s">
-        <v>176</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="F73" s="33"/>
+      <c r="G73" s="31"/>
       <c r="H73" s="3"/>
       <c r="I73" s="32"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
     </row>
-    <row r="74" spans="1:12" s="6" customFormat="1" ht="26" x14ac:dyDescent="0.35">
-      <c r="A74" s="60"/>
-      <c r="B74" s="63"/>
+    <row r="74" spans="1:12" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A74" s="53">
+        <v>21</v>
+      </c>
+      <c r="B74" s="56" t="s">
+        <v>174</v>
+      </c>
       <c r="C74" s="26">
-        <v>20.3</v>
+        <v>21.1</v>
       </c>
       <c r="D74" s="33" t="s">
-        <v>170</v>
+        <v>175</v>
       </c>
       <c r="E74" s="33" t="s">
-        <v>167</v>
-      </c>
-      <c r="F74" s="33"/>
-      <c r="G74" s="31"/>
+        <v>176</v>
+      </c>
+      <c r="F74" s="33" t="s">
+        <v>177</v>
+      </c>
+      <c r="G74" s="31" t="s">
+        <v>178</v>
+      </c>
       <c r="H74" s="3"/>
       <c r="I74" s="32"/>
-      <c r="J74" s="1"/>
-      <c r="K74" s="1"/>
-      <c r="L74" s="1"/>
-    </row>
-    <row r="75" spans="1:12" ht="78" x14ac:dyDescent="0.35">
-      <c r="A75" s="58">
-        <v>21</v>
-      </c>
-      <c r="B75" s="61" t="s">
-        <v>177</v>
-      </c>
-      <c r="C75" s="26">
-        <v>21.1</v>
+    </row>
+    <row r="75" spans="1:12" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A75" s="54"/>
+      <c r="B75" s="57"/>
+      <c r="C75" s="34">
+        <v>21.2</v>
       </c>
       <c r="D75" s="33" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="E75" s="33" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="F75" s="33" t="s">
-        <v>180</v>
+        <v>82</v>
       </c>
       <c r="G75" s="31" t="s">
         <v>181</v>
@@ -5889,62 +5948,62 @@
       <c r="H75" s="3"/>
       <c r="I75" s="32"/>
     </row>
-    <row r="76" spans="1:12" ht="117" x14ac:dyDescent="0.35">
-      <c r="A76" s="59"/>
-      <c r="B76" s="62"/>
-      <c r="C76" s="34">
-        <v>21.2</v>
+    <row r="76" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A76" s="55"/>
+      <c r="B76" s="58"/>
+      <c r="C76" s="26">
+        <v>21.3</v>
       </c>
       <c r="D76" s="33" t="s">
-        <v>182</v>
+        <v>175</v>
       </c>
       <c r="E76" s="33" t="s">
-        <v>183</v>
-      </c>
-      <c r="F76" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="G76" s="31" t="s">
-        <v>184</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="F76" s="33"/>
+      <c r="G76" s="31"/>
       <c r="H76" s="3"/>
       <c r="I76" s="32"/>
     </row>
-    <row r="77" spans="1:12" ht="26" x14ac:dyDescent="0.35">
-      <c r="A77" s="60"/>
-      <c r="B77" s="63"/>
+    <row r="77" spans="1:12" ht="179.4" x14ac:dyDescent="0.3">
+      <c r="A77" s="53">
+        <v>22</v>
+      </c>
+      <c r="B77" s="56" t="s">
+        <v>182</v>
+      </c>
       <c r="C77" s="26">
-        <v>21.3</v>
+        <v>22.1</v>
       </c>
       <c r="D77" s="33" t="s">
-        <v>178</v>
+        <v>183</v>
       </c>
       <c r="E77" s="33" t="s">
-        <v>167</v>
-      </c>
-      <c r="F77" s="33"/>
-      <c r="G77" s="31"/>
+        <v>184</v>
+      </c>
+      <c r="F77" s="33" t="s">
+        <v>185</v>
+      </c>
+      <c r="G77" s="31" t="s">
+        <v>186</v>
+      </c>
       <c r="H77" s="3"/>
       <c r="I77" s="32"/>
     </row>
-    <row r="78" spans="1:12" ht="169" x14ac:dyDescent="0.35">
-      <c r="A78" s="58">
-        <v>22</v>
-      </c>
-      <c r="B78" s="61" t="s">
-        <v>185</v>
-      </c>
-      <c r="C78" s="26">
-        <v>22.1</v>
+    <row r="78" spans="1:12" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A78" s="54"/>
+      <c r="B78" s="57"/>
+      <c r="C78" s="34">
+        <v>22.2</v>
       </c>
       <c r="D78" s="33" t="s">
-        <v>186</v>
-      </c>
-      <c r="E78" s="33" t="s">
         <v>187</v>
       </c>
+      <c r="E78" s="3" t="s">
+        <v>188</v>
+      </c>
       <c r="F78" s="33" t="s">
-        <v>188</v>
+        <v>82</v>
       </c>
       <c r="G78" s="31" t="s">
         <v>189</v>
@@ -5952,78 +6011,65 @@
       <c r="H78" s="3"/>
       <c r="I78" s="32"/>
     </row>
-    <row r="79" spans="1:12" ht="117" x14ac:dyDescent="0.35">
-      <c r="A79" s="59"/>
-      <c r="B79" s="62"/>
-      <c r="C79" s="34">
-        <v>22.2</v>
+    <row r="79" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A79" s="55"/>
+      <c r="B79" s="58"/>
+      <c r="C79" s="26">
+        <v>22.3</v>
       </c>
       <c r="D79" s="33" t="s">
-        <v>190</v>
+        <v>183</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>191</v>
-      </c>
-      <c r="F79" s="33" t="s">
-        <v>82</v>
-      </c>
-      <c r="G79" s="31" t="s">
-        <v>192</v>
-      </c>
+        <v>164</v>
+      </c>
+      <c r="F79" s="33"/>
+      <c r="G79" s="31"/>
       <c r="H79" s="3"/>
       <c r="I79" s="32"/>
     </row>
-    <row r="80" spans="1:12" ht="39" x14ac:dyDescent="0.35">
-      <c r="A80" s="60"/>
-      <c r="B80" s="63"/>
-      <c r="C80" s="26">
-        <v>22.3</v>
-      </c>
-      <c r="D80" s="33" t="s">
-        <v>186</v>
-      </c>
-      <c r="E80" s="3" t="s">
-        <v>167</v>
-      </c>
-      <c r="F80" s="33"/>
-      <c r="G80" s="31"/>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="E80" s="38"/>
       <c r="H80" s="3"/>
-      <c r="I80" s="32"/>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A81" s="3"/>
-      <c r="B81" s="3"/>
-      <c r="C81" s="3"/>
-      <c r="E81" s="38"/>
-      <c r="H81" s="3"/>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.35">
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="I81" s="2"/>
+    </row>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D82" s="2"/>
       <c r="F82" s="2"/>
       <c r="G82" s="2"/>
       <c r="I82" s="2"/>
     </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="D83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="I83" s="2"/>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A84" s="25"/>
-      <c r="B84" s="25"/>
-      <c r="C84" s="25"/>
-      <c r="D84" s="25"/>
-      <c r="E84" s="25"/>
-      <c r="F84" s="25"/>
-      <c r="G84" s="25"/>
-      <c r="H84" s="25"/>
-      <c r="I84" s="25"/>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="A85" s="3"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="3"/>
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A83" s="25"/>
+      <c r="B83" s="25"/>
+      <c r="C83" s="25"/>
+      <c r="D83" s="25"/>
+      <c r="E83" s="25"/>
+      <c r="F83" s="25"/>
+      <c r="G83" s="25"/>
+      <c r="H83" s="25"/>
+      <c r="I83" s="25"/>
+    </row>
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
+      <c r="D84" s="37"/>
+      <c r="E84" s="37"/>
+      <c r="F84" s="37"/>
+      <c r="G84" s="27"/>
+      <c r="H84" s="37"/>
+      <c r="I84" s="37"/>
+    </row>
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D85" s="37"/>
       <c r="E85" s="37"/>
       <c r="F85" s="37"/>
@@ -6031,7 +6077,8 @@
       <c r="H85" s="37"/>
       <c r="I85" s="37"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B86" s="3"/>
       <c r="D86" s="37"/>
       <c r="E86" s="37"/>
       <c r="F86" s="37"/>
@@ -6039,8 +6086,7 @@
       <c r="H86" s="37"/>
       <c r="I86" s="37"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="B87" s="3"/>
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D87" s="37"/>
       <c r="E87" s="37"/>
       <c r="F87" s="37"/>
@@ -6048,7 +6094,7 @@
       <c r="H87" s="37"/>
       <c r="I87" s="37"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D88" s="37"/>
       <c r="E88" s="37"/>
       <c r="F88" s="37"/>
@@ -6056,7 +6102,7 @@
       <c r="H88" s="37"/>
       <c r="I88" s="37"/>
     </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D89" s="37"/>
       <c r="E89" s="37"/>
       <c r="F89" s="37"/>
@@ -6064,7 +6110,7 @@
       <c r="H89" s="37"/>
       <c r="I89" s="37"/>
     </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D90" s="37"/>
       <c r="E90" s="37"/>
       <c r="F90" s="37"/>
@@ -6072,7 +6118,7 @@
       <c r="H90" s="37"/>
       <c r="I90" s="37"/>
     </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.35">
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D91" s="37"/>
       <c r="E91" s="37"/>
       <c r="F91" s="37"/>
@@ -6080,39 +6126,9 @@
       <c r="H91" s="37"/>
       <c r="I91" s="37"/>
     </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.35">
-      <c r="D92" s="37"/>
-      <c r="E92" s="37"/>
-      <c r="F92" s="37"/>
-      <c r="G92" s="27"/>
-      <c r="H92" s="37"/>
-      <c r="I92" s="37"/>
-    </row>
   </sheetData>
   <autoFilter ref="I1:I26" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="37">
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="A29:A39"/>
-    <mergeCell ref="B29:B39"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="A40:A47"/>
-    <mergeCell ref="B40:B47"/>
-    <mergeCell ref="A75:A77"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="A78:A80"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="A48:A53"/>
-    <mergeCell ref="B48:B53"/>
-    <mergeCell ref="A54:A58"/>
-    <mergeCell ref="B54:B58"/>
-    <mergeCell ref="A59:A68"/>
-    <mergeCell ref="B59:B68"/>
-    <mergeCell ref="A69:A71"/>
-    <mergeCell ref="B69:B71"/>
-    <mergeCell ref="A72:A74"/>
-    <mergeCell ref="B72:B74"/>
     <mergeCell ref="A13:A16"/>
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="A17:A20"/>
@@ -6128,6 +6144,28 @@
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="B3:B7"/>
     <mergeCell ref="B17:B20"/>
+    <mergeCell ref="A40:A47"/>
+    <mergeCell ref="B40:B47"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="B74:B76"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="B77:B79"/>
+    <mergeCell ref="A48:A53"/>
+    <mergeCell ref="B48:B53"/>
+    <mergeCell ref="A54:A58"/>
+    <mergeCell ref="B54:B58"/>
+    <mergeCell ref="A59:A67"/>
+    <mergeCell ref="B59:B67"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="B68:B70"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="B71:B73"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="A29:A39"/>
+    <mergeCell ref="B29:B39"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="B21:B23"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6139,15 +6177,15 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:J41"/>
-  <sheetFormatPr defaultColWidth="9.08984375" defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="4" max="4" width="18.1796875" customWidth="1"/>
-    <col min="5" max="5" width="24.90625" customWidth="1"/>
-    <col min="6" max="6" width="27.36328125" customWidth="1"/>
-    <col min="7" max="7" width="36.1796875" customWidth="1"/>
+    <col min="4" max="4" width="18.21875" customWidth="1"/>
+    <col min="5" max="5" width="24.88671875" customWidth="1"/>
+    <col min="6" max="6" width="27.33203125" customWidth="1"/>
+    <col min="7" max="7" width="36.21875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A1" s="28"/>
       <c r="B1" s="28"/>
       <c r="C1" s="28"/>
@@ -6159,7 +6197,7 @@
       <c r="I1" s="28"/>
       <c r="J1" s="28"/>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="28"/>
       <c r="B2" s="28"/>
       <c r="C2" s="28"/>
@@ -6171,295 +6209,295 @@
       <c r="I2" s="28"/>
       <c r="J2" s="28"/>
     </row>
-    <row r="3" spans="1:10" ht="43.5" x14ac:dyDescent="0.35">
+    <row r="3" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
       <c r="A3" s="28"/>
       <c r="B3" s="28"/>
       <c r="C3" s="28"/>
-      <c r="D3" s="75" t="s">
+      <c r="D3" s="42" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="75" t="s">
+      <c r="E3" s="42" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="75" t="s">
+      <c r="F3" s="42" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="75" t="s">
+      <c r="G3" s="42" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="75" t="s">
-        <v>252</v>
-      </c>
-      <c r="I3" s="75" t="s">
+      <c r="H3" s="42" t="s">
+        <v>248</v>
+      </c>
+      <c r="I3" s="42" t="s">
         <v>4</v>
       </c>
       <c r="J3" s="28"/>
     </row>
-    <row r="4" spans="1:10" ht="348" x14ac:dyDescent="0.35">
+    <row r="4" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A4" s="28"/>
       <c r="B4" s="28"/>
       <c r="C4" s="28"/>
-      <c r="D4" s="76" t="s">
+      <c r="D4" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="E4" s="76">
+      <c r="E4" s="43">
         <v>14.1</v>
       </c>
       <c r="F4" s="27" t="s">
         <v>137</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>253</v>
+        <v>249</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>254</v>
-      </c>
-      <c r="I4" s="76" t="s">
-        <v>255</v>
+        <v>250</v>
+      </c>
+      <c r="I4" s="43" t="s">
+        <v>251</v>
       </c>
       <c r="J4" s="28"/>
     </row>
-    <row r="5" spans="1:10" ht="362.5" x14ac:dyDescent="0.35">
+    <row r="5" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A5" s="28"/>
       <c r="B5" s="28"/>
       <c r="C5" s="28"/>
-      <c r="D5" s="76" t="s">
+      <c r="D5" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="E5" s="76">
+      <c r="E5" s="43">
         <v>14.2</v>
       </c>
       <c r="F5" s="27" t="s">
         <v>137</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>256</v>
+        <v>252</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>257</v>
-      </c>
-      <c r="I5" s="76" t="s">
-        <v>258</v>
+        <v>253</v>
+      </c>
+      <c r="I5" s="43" t="s">
+        <v>254</v>
       </c>
       <c r="J5" s="28"/>
     </row>
-    <row r="6" spans="1:10" ht="348" x14ac:dyDescent="0.35">
+    <row r="6" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A6" s="28"/>
       <c r="B6" s="28"/>
       <c r="C6" s="28"/>
-      <c r="D6" s="76" t="s">
+      <c r="D6" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="E6" s="76">
+      <c r="E6" s="43">
         <v>14.3</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>259</v>
+        <v>255</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>260</v>
+        <v>256</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="I6" s="76" t="s">
-        <v>262</v>
+        <v>257</v>
+      </c>
+      <c r="I6" s="43" t="s">
+        <v>258</v>
       </c>
       <c r="J6" s="28"/>
     </row>
-    <row r="7" spans="1:10" ht="406" x14ac:dyDescent="0.35">
+    <row r="7" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
       <c r="A7" s="28"/>
       <c r="B7" s="28"/>
       <c r="C7" s="28"/>
-      <c r="D7" s="76" t="s">
+      <c r="D7" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="E7" s="76">
+      <c r="E7" s="43">
         <v>14.4</v>
       </c>
       <c r="F7" s="27" t="s">
         <v>137</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>263</v>
+        <v>259</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>264</v>
-      </c>
-      <c r="I7" s="76" t="s">
-        <v>265</v>
+        <v>260</v>
+      </c>
+      <c r="I7" s="43" t="s">
+        <v>261</v>
       </c>
       <c r="J7" s="28"/>
     </row>
-    <row r="8" spans="1:10" ht="333.5" x14ac:dyDescent="0.35">
+    <row r="8" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A8" s="28"/>
       <c r="B8" s="28"/>
       <c r="C8" s="28"/>
-      <c r="D8" s="76" t="s">
+      <c r="D8" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="E8" s="76">
+      <c r="E8" s="43">
         <v>14.5</v>
       </c>
       <c r="F8" s="27" t="s">
         <v>137</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>266</v>
+        <v>262</v>
       </c>
       <c r="H8" s="27" t="s">
-        <v>267</v>
-      </c>
-      <c r="I8" s="76" t="s">
-        <v>268</v>
+        <v>263</v>
+      </c>
+      <c r="I8" s="43" t="s">
+        <v>264</v>
       </c>
       <c r="J8" s="28"/>
     </row>
-    <row r="9" spans="1:10" ht="275.5" x14ac:dyDescent="0.35">
+    <row r="9" spans="1:10" ht="273.60000000000002" x14ac:dyDescent="0.3">
       <c r="A9" s="28"/>
       <c r="B9" s="28"/>
       <c r="C9" s="28"/>
-      <c r="D9" s="76" t="s">
+      <c r="D9" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="E9" s="76">
+      <c r="E9" s="43">
         <v>14.6</v>
       </c>
       <c r="F9" s="27" t="s">
         <v>137</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>269</v>
+        <v>265</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>270</v>
-      </c>
-      <c r="I9" s="76" t="s">
-        <v>271</v>
+        <v>266</v>
+      </c>
+      <c r="I9" s="43" t="s">
+        <v>267</v>
       </c>
       <c r="J9" s="28"/>
     </row>
-    <row r="10" spans="1:10" ht="348" x14ac:dyDescent="0.35">
+    <row r="10" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
       <c r="A10" s="28"/>
       <c r="B10" s="28"/>
       <c r="C10" s="28"/>
-      <c r="D10" s="76" t="s">
+      <c r="D10" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="E10" s="76">
+      <c r="E10" s="43">
         <v>14.7</v>
       </c>
       <c r="F10" s="27" t="s">
         <v>137</v>
       </c>
       <c r="G10" s="27" t="s">
-        <v>272</v>
+        <v>268</v>
       </c>
       <c r="H10" s="27" t="s">
-        <v>273</v>
-      </c>
-      <c r="I10" s="76" t="s">
-        <v>274</v>
+        <v>269</v>
+      </c>
+      <c r="I10" s="43" t="s">
+        <v>270</v>
       </c>
       <c r="J10" s="28"/>
     </row>
-    <row r="11" spans="1:10" ht="319" x14ac:dyDescent="0.35">
+    <row r="11" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
       <c r="A11" s="28"/>
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
-      <c r="D11" s="76" t="s">
+      <c r="D11" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="E11" s="76">
+      <c r="E11" s="43">
         <v>14.8</v>
       </c>
       <c r="F11" s="27" t="s">
         <v>137</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>275</v>
+        <v>271</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>276</v>
-      </c>
-      <c r="I11" s="76" t="s">
-        <v>277</v>
+        <v>272</v>
+      </c>
+      <c r="I11" s="43" t="s">
+        <v>273</v>
       </c>
       <c r="J11" s="28"/>
     </row>
-    <row r="12" spans="1:10" ht="304.5" x14ac:dyDescent="0.35">
+    <row r="12" spans="1:10" ht="302.39999999999998" x14ac:dyDescent="0.3">
       <c r="A12" s="28"/>
       <c r="B12" s="28"/>
       <c r="C12" s="28"/>
-      <c r="D12" s="76" t="s">
+      <c r="D12" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="E12" s="76">
+      <c r="E12" s="43">
         <v>14.9</v>
       </c>
       <c r="F12" s="27" t="s">
         <v>137</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>278</v>
+        <v>274</v>
       </c>
       <c r="H12" s="27" t="s">
-        <v>279</v>
-      </c>
-      <c r="I12" s="76" t="s">
-        <v>280</v>
+        <v>275</v>
+      </c>
+      <c r="I12" s="43" t="s">
+        <v>276</v>
       </c>
       <c r="J12" s="28"/>
     </row>
-    <row r="13" spans="1:10" ht="391.5" x14ac:dyDescent="0.35">
+    <row r="13" spans="1:10" ht="388.8" x14ac:dyDescent="0.3">
       <c r="A13" s="28"/>
       <c r="B13" s="28"/>
       <c r="C13" s="28"/>
-      <c r="D13" s="76" t="s">
+      <c r="D13" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="E13" s="76" t="s">
-        <v>281</v>
+      <c r="E13" s="43" t="s">
+        <v>277</v>
       </c>
       <c r="F13" s="27" t="s">
         <v>137</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>282</v>
+        <v>278</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>283</v>
-      </c>
-      <c r="I13" s="76" t="s">
-        <v>284</v>
+        <v>279</v>
+      </c>
+      <c r="I13" s="43" t="s">
+        <v>280</v>
       </c>
       <c r="J13" s="28"/>
     </row>
-    <row r="14" spans="1:10" ht="290" x14ac:dyDescent="0.35">
+    <row r="14" spans="1:10" ht="288" x14ac:dyDescent="0.3">
       <c r="A14" s="28"/>
       <c r="B14" s="28"/>
       <c r="C14" s="28"/>
-      <c r="D14" s="76" t="s">
+      <c r="D14" s="43" t="s">
         <v>84</v>
       </c>
-      <c r="E14" s="76">
+      <c r="E14" s="43">
         <v>14.11</v>
       </c>
       <c r="F14" s="27" t="s">
         <v>137</v>
       </c>
       <c r="G14" s="27" t="s">
-        <v>285</v>
+        <v>281</v>
       </c>
       <c r="H14" s="27" t="s">
-        <v>286</v>
-      </c>
-      <c r="I14" s="76" t="s">
-        <v>287</v>
+        <v>282</v>
+      </c>
+      <c r="I14" s="43" t="s">
+        <v>283</v>
       </c>
       <c r="J14" s="28"/>
     </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A15" s="28"/>
       <c r="B15" s="28"/>
       <c r="C15" s="28"/>
@@ -6471,7 +6509,7 @@
       <c r="I15" s="28"/>
       <c r="J15" s="28"/>
     </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A16" s="28"/>
       <c r="B16" s="28"/>
       <c r="C16" s="28"/>
@@ -6483,7 +6521,7 @@
       <c r="I16" s="28"/>
       <c r="J16" s="28"/>
     </row>
-    <row r="17" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="17" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A17" s="28"/>
       <c r="B17" s="28"/>
       <c r="C17" s="28"/>
@@ -6495,7 +6533,7 @@
       <c r="I17" s="28"/>
       <c r="J17" s="28"/>
     </row>
-    <row r="18" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="18" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A18" s="28"/>
       <c r="B18" s="28"/>
       <c r="C18" s="28"/>
@@ -6507,7 +6545,7 @@
       <c r="I18" s="28"/>
       <c r="J18" s="28"/>
     </row>
-    <row r="19" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="19" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A19" s="28"/>
       <c r="B19" s="28"/>
       <c r="C19" s="28"/>
@@ -6519,7 +6557,7 @@
       <c r="I19" s="28"/>
       <c r="J19" s="28"/>
     </row>
-    <row r="20" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="20" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A20" s="28"/>
       <c r="B20" s="28"/>
       <c r="C20" s="28"/>
@@ -6531,7 +6569,7 @@
       <c r="I20" s="28"/>
       <c r="J20" s="28"/>
     </row>
-    <row r="21" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="21" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A21" s="28"/>
       <c r="B21" s="28"/>
       <c r="C21" s="28"/>
@@ -6543,7 +6581,7 @@
       <c r="I21" s="28"/>
       <c r="J21" s="28"/>
     </row>
-    <row r="22" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="22" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A22" s="28"/>
       <c r="B22" s="28"/>
       <c r="C22" s="28"/>
@@ -6555,7 +6593,7 @@
       <c r="I22" s="28"/>
       <c r="J22" s="28"/>
     </row>
-    <row r="23" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="23" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A23" s="28"/>
       <c r="B23" s="28"/>
       <c r="C23" s="28"/>
@@ -6567,7 +6605,7 @@
       <c r="I23" s="28"/>
       <c r="J23" s="28"/>
     </row>
-    <row r="24" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="24" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A24" s="28"/>
       <c r="B24" s="28"/>
       <c r="C24" s="28"/>
@@ -6579,7 +6617,7 @@
       <c r="I24" s="28"/>
       <c r="J24" s="28"/>
     </row>
-    <row r="25" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="25" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A25" s="28"/>
       <c r="B25" s="28"/>
       <c r="C25" s="28"/>
@@ -6591,7 +6629,7 @@
       <c r="I25" s="28"/>
       <c r="J25" s="28"/>
     </row>
-    <row r="26" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="26" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A26" s="28"/>
       <c r="B26" s="28"/>
       <c r="C26" s="28"/>
@@ -6603,7 +6641,7 @@
       <c r="I26" s="28"/>
       <c r="J26" s="28"/>
     </row>
-    <row r="27" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="27" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A27" s="28"/>
       <c r="B27" s="28"/>
       <c r="C27" s="28"/>
@@ -6615,7 +6653,7 @@
       <c r="I27" s="28"/>
       <c r="J27" s="28"/>
     </row>
-    <row r="28" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="28" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A28" s="28"/>
       <c r="B28" s="28"/>
       <c r="C28" s="28"/>
@@ -6627,7 +6665,7 @@
       <c r="I28" s="28"/>
       <c r="J28" s="28"/>
     </row>
-    <row r="29" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="29" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A29" s="28"/>
       <c r="B29" s="28"/>
       <c r="C29" s="28"/>
@@ -6639,7 +6677,7 @@
       <c r="I29" s="28"/>
       <c r="J29" s="28"/>
     </row>
-    <row r="30" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="30" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A30" s="28"/>
       <c r="B30" s="28"/>
       <c r="C30" s="28"/>
@@ -6651,7 +6689,7 @@
       <c r="I30" s="28"/>
       <c r="J30" s="28"/>
     </row>
-    <row r="31" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="31" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A31" s="28"/>
       <c r="B31" s="28"/>
       <c r="C31" s="28"/>
@@ -6663,7 +6701,7 @@
       <c r="I31" s="28"/>
       <c r="J31" s="28"/>
     </row>
-    <row r="32" spans="1:10" x14ac:dyDescent="0.35">
+    <row r="32" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A32" s="28"/>
       <c r="B32" s="28"/>
       <c r="C32" s="28"/>
@@ -6675,63 +6713,63 @@
       <c r="I32" s="28"/>
       <c r="J32" s="28"/>
     </row>
-    <row r="33" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A33" s="28"/>
       <c r="B33" s="28"/>
       <c r="C33" s="28"/>
       <c r="D33" s="28"/>
       <c r="E33" s="28"/>
     </row>
-    <row r="34" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A34" s="28"/>
       <c r="B34" s="28"/>
       <c r="C34" s="28"/>
       <c r="D34" s="28"/>
       <c r="E34" s="28"/>
     </row>
-    <row r="35" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A35" s="28"/>
       <c r="B35" s="28"/>
       <c r="C35" s="28"/>
       <c r="D35" s="28"/>
       <c r="E35" s="28"/>
     </row>
-    <row r="36" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A36" s="28"/>
       <c r="B36" s="28"/>
       <c r="C36" s="28"/>
       <c r="D36" s="28"/>
       <c r="E36" s="28"/>
     </row>
-    <row r="37" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A37" s="28"/>
       <c r="B37" s="28"/>
       <c r="C37" s="28"/>
       <c r="D37" s="28"/>
       <c r="E37" s="28"/>
     </row>
-    <row r="38" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A38" s="28"/>
       <c r="B38" s="28"/>
       <c r="C38" s="28"/>
       <c r="D38" s="28"/>
       <c r="E38" s="28"/>
     </row>
-    <row r="39" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A39" s="28"/>
       <c r="B39" s="28"/>
       <c r="C39" s="28"/>
       <c r="D39" s="28"/>
       <c r="E39" s="28"/>
     </row>
-    <row r="40" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A40" s="28"/>
       <c r="B40" s="28"/>
       <c r="C40" s="28"/>
       <c r="D40" s="28"/>
       <c r="E40" s="28"/>
     </row>
-    <row r="41" spans="1:5" x14ac:dyDescent="0.35">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A41" s="28"/>
       <c r="B41" s="28"/>
       <c r="C41" s="28"/>

--- a/Soubhanik/checkupp_product_backlog_final.xlsx
+++ b/Soubhanik/checkupp_product_backlog_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Soubhanik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C0799820-4E7B-4D4D-BCBF-B65CB046B9B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBCE050-C94F-4EBD-856F-ED75712EDB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -101,6 +101,135 @@
         </r>
       </text>
     </comment>
+    <comment ref="B24" authorId="0" shapeId="0" xr:uid="{CCB9346B-D6BE-41C8-B44E-B56235F8E7A9}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sayan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Include user story for user taking picture of report for AI assessment, under </t>
+        </r>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Mental Health Assessment</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve"> epic</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G27" authorId="0" shapeId="0" xr:uid="{27A0456B-2583-4AB5-8308-7578F51E35E5}">
+      <text>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sayan:
+Dropdowns with exact name examples from the screen</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G68" authorId="0" shapeId="0" xr:uid="{3283D6CB-61A1-4390-A688-5F4F500D8585}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sayan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Toggles, Dropdowns with exact name examples from the screen</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G71" authorId="0" shapeId="0" xr:uid="{C1521E49-0187-46FC-9D55-A1D99E904DBB}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sayan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Toggles, Dropdowns with exact name examples from the screen</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="G74" authorId="0" shapeId="0" xr:uid="{6311CE01-3810-423E-933D-ACFFBD920BE0}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t>Sayan:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <color indexed="81"/>
+            <rFont val="Tahoma"/>
+            <family val="2"/>
+          </rPr>
+          <t xml:space="preserve">
+Toggles, Dropdowns with exact name examples from the screen</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
@@ -387,20 +516,10 @@
     <t>I don't have to re-enter the data in the fields(K-10 score, DASS-21 Depression, DASS-21 Anxiety, etc.) or re-toggle the switches (difficulty falling asleep and frequent night waking) again</t>
   </si>
   <si>
-    <t xml:space="preserve">1. All entered assessment field values (e.g., K-10 score, DASS-21 Depression, DASS-21 Anxiety) must be automatically saved whenever the user enters or updates them.
-2. All toggle switch states (e.g., Difficulty Falling Asleep, Frequent Night Waking) must be automatically saved whenever they are changed.
-3. All autosaved assessment data must be restored when the user returns to the Mental Health Assessment screen after tapping the Back button.
-4. All autosaved assessment data must be restored when the user reopens the app after it has been closed or removed from the background.
-</t>
-  </si>
-  <si>
     <t>logged in user revisiting the mental health assessment</t>
   </si>
   <si>
     <t>see my previously entered data in available fields(K-10 score, DASS-21 Depression, DASS-21 Anxiety, etc) or the status of the toggle switches (difficulty falling asleep and frequent night waking) restored along with an affirming notification(toast)</t>
-  </si>
-  <si>
-    <t>I am informed that my autosaved data was restored.</t>
   </si>
   <si>
     <t>1. Previously autosaved assessment data must be restored automatically when the logged-in user revisits the Mental Health Assessment screen.
@@ -1223,11 +1342,6 @@
     <t>I don't have to re-enter the data in the fields(systolic, diastolic, heart rate, etc.) again</t>
   </si>
   <si>
-    <t>1. All entered assessment fields(systolic, diastolic, heart rate, etc.) must be automatically saved whenever the user enters or updates them.
-2. All autosaved assessment data must be restored when the user returns to the Cardiovascular Reading screen after tapping the Back button.
-3. All autosaved assessment data must be restored when the user reopens the app after it has been closed or removed from the background.</t>
-  </si>
-  <si>
     <t>logged in user revisiting the Cardiovascular Reading</t>
   </si>
   <si>
@@ -1258,11 +1372,6 @@
     <t>I don't have to re-enter the data in the fields(fasting glucose, random glucose, etc.) again</t>
   </si>
   <si>
-    <t>1. All entered assessment fields(fasting glucose, random glucose, etc.) must be automatically saved whenever the user enters or updates them.
-2. All autosaved assessment data must be restored when the user returns to the Diabetes Test screen after tapping the Back button.
-3. All autosaved assessment data must be restored when the user reopens the app after it has been closed or removed from the background.</t>
-  </si>
-  <si>
     <t>logged in user revisiting the Diabetes Test</t>
   </si>
   <si>
@@ -1287,15 +1396,7 @@
     <t>I don't have to re-enter the data in the fields(Right Eye, Left Eye, etc.) again</t>
   </si>
   <si>
-    <t>1. All entered assessment fields(Right Eye, Left Eye, etc.) must be automatically saved whenever the user enters or updates them.
-2. All autosaved assessment data must be restored when the user returns to the Vision Test screen after tapping the Back button.
-3. All autosaved assessment data must be restored when the user reopens the app after it has been closed or removed from the background.</t>
-  </si>
-  <si>
     <t>logged in user revisiting the Vision Test</t>
-  </si>
-  <si>
-    <t>see my previously entered data in available fields(Right Eye, Left Eye, etc.) restored along with an affirming notification(toast)</t>
   </si>
   <si>
     <t>1. Previously autosaved available data must be restored automatically when the logged-in user revisits the Vision Test screen.
@@ -1311,23 +1412,6 @@
   </si>
   <si>
     <t>have the data I enter in the available fields (cavities, fillings, etc), used the toggle switches (Use mouthwash regularly) and the dropdown options (Brushing frequency and flossing frequency) autosaved in the system if I tap the 'Back' button or close/remove the app from the background</t>
-  </si>
-  <si>
-    <t>I don't have to re-enter the data in the fields (cavities, fillings, etc), re-toggle the switches (Use mouthwash regularly) and the re-use dropdown options (Brushing frequency and flossing frequency)</t>
-  </si>
-  <si>
-    <t>1. All entered dental health field values (e.g., cavities, fillings, etc.) must be automatically saved whenever they are entered or updated.
-2. All toggle switch states (e.g., Use Mouthwash Regularly) must be automatically saved whenever they are changed.
-3. All selected dropdown options (e.g., Brushing Frequency and Flossing Frequency) must be automatically saved whenever they are changed.
-4. All autosaved dental health data must be restored when the user returns to the Dental Health Check screen after tapping the Back button.
-5. All autosaved dental health data must be restored when the user reopens the app after it has been closed or removed from the background.
-6. The most recent values entered in all fields, toggle switches, and dropdown selections must be displayed when the Dental Health Check is resumed, without requiring the user to re-enter or reselect the information.</t>
-  </si>
-  <si>
-    <t>logged in user revisiting the Dental Health Check</t>
-  </si>
-  <si>
-    <t>see my previously entered data in the available fields (e.g., cavities, fillings, etc.), the status of the toggle switch (Use Mouthwash Regularly), and the selected dropdown options (Brushing Frequency and Flossing Frequency) restored along with an affirming notification (toast)</t>
   </si>
   <si>
     <t>1. Previously autosaved available data must be restored automatically when the logged-in user revisits the Dental Health Check screen.
@@ -3351,6 +3435,41 @@
 2. Reminder settings must apply to newly synced appointments.
 3. Default reminder must be configurable.</t>
     </r>
+  </si>
+  <si>
+    <t>I don't have to re-enter the data in the fields (cavities, fillings, etc), re-toggle the switches (Use mouthwash regularly) or re-use the dropdown options (Brushing frequency and flossing frequency) upon revisiting the Dental Health Check screen</t>
+  </si>
+  <si>
+    <t>logged in user revisiting the Dental Health Check screen after tapping back button or closing/removing the app from background</t>
+  </si>
+  <si>
+    <t>see my previously entered data in the available fields (e.g., cavities, fillings, etc.), the status of the toggle switch (Use Mouthwash Regularly), and the selected dropdown options (Brushing Frequency and Flossing Frequency) restored along with an affirming notification</t>
+  </si>
+  <si>
+    <t>1. All entered dental health field values (e.g., cavities, fillings, etc.) must be automatically saved whenever they are entered or updated.
+2. All toggle switch states (e.g., Use Mouthwash Regularly) must be automatically saved whenever they are changed.
+3. All selected dropdown options (e.g., Brushing Frequency and Flossing Frequency) must be automatically saved whenever they are changed.</t>
+  </si>
+  <si>
+    <t>1. All entered assessment fields(Right Eye, Left Eye, etc.) must be automatically saved whenever the user enters or updates them.</t>
+  </si>
+  <si>
+    <t>see my previously entered data in available fields(Right Eye, Left Eye, etc.) restored along with an affirming notification</t>
+  </si>
+  <si>
+    <t>I am informed that my previously entered data progress was restored by the system</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. All entered assessment fields(fasting glucose, random glucose, etc.) must be automatically saved whenever the user enters or updates them.
+</t>
+  </si>
+  <si>
+    <t>1. All entered assessment fields(systolic, diastolic, heart rate, etc.) must be automatically saved whenever the user enters or updates them.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1. All entered assessment field values (e.g., K-10 score, DASS-21 Depression, DASS-21 Anxiety) must be automatically saved whenever the user enters or updates them.
+2. All toggle switch states (e.g., Difficulty Falling Asleep, Frequent Night Waking) must be automatically saved whenever they are changed.
+</t>
   </si>
 </sst>
 </file>
@@ -3645,7 +3764,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="79">
+  <cellXfs count="83">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3782,6 +3901,90 @@
     <xf numFmtId="0" fontId="7" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3797,89 +4000,17 @@
     <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4114,34 +4245,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="71" t="s">
+      <c r="A1" s="53" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="71" t="s">
+      <c r="B1" s="53" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="75" t="s">
+      <c r="C1" s="58" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="75" t="s">
+      <c r="D1" s="58" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="76"/>
-      <c r="F1" s="76"/>
-      <c r="G1" s="75" t="s">
+      <c r="E1" s="59"/>
+      <c r="F1" s="59"/>
+      <c r="G1" s="58" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="71" t="s">
+      <c r="H1" s="53" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="71" t="s">
+      <c r="I1" s="53" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="52"/>
-      <c r="B2" s="52"/>
-      <c r="C2" s="76"/>
+      <c r="A2" s="54"/>
+      <c r="B2" s="54"/>
+      <c r="C2" s="59"/>
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
@@ -4151,31 +4282,31 @@
       <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="75"/>
-      <c r="H2" s="52"/>
-      <c r="I2" s="52"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="54"/>
+      <c r="I2" s="54"/>
     </row>
     <row r="3" spans="1:9" s="5" customFormat="1" ht="156" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="77">
+      <c r="A3" s="60">
         <v>1</v>
       </c>
-      <c r="B3" s="77" t="s">
+      <c r="B3" s="60" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="30">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="29" t="s">
-        <v>197</v>
+        <v>187</v>
       </c>
       <c r="E3" s="29" t="s">
-        <v>196</v>
+        <v>186</v>
       </c>
       <c r="F3" s="29" t="s">
-        <v>205</v>
+        <v>195</v>
       </c>
       <c r="G3" s="30" t="s">
-        <v>208</v>
+        <v>198</v>
       </c>
       <c r="H3" s="29" t="s">
         <v>11</v>
@@ -4185,94 +4316,94 @@
       </c>
     </row>
     <row r="4" spans="1:9" s="6" customFormat="1" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="77"/>
-      <c r="B4" s="77"/>
+      <c r="A4" s="60"/>
+      <c r="B4" s="60"/>
       <c r="C4" s="30">
         <v>1.2</v>
       </c>
       <c r="D4" s="29" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="E4" s="29" t="s">
-        <v>201</v>
+        <v>191</v>
       </c>
       <c r="F4" s="29" t="s">
-        <v>190</v>
+        <v>180</v>
       </c>
       <c r="G4" s="30" t="s">
-        <v>199</v>
+        <v>189</v>
       </c>
       <c r="H4" s="29"/>
       <c r="I4" s="29"/>
     </row>
     <row r="5" spans="1:9" s="6" customFormat="1" ht="138" x14ac:dyDescent="0.3">
-      <c r="A5" s="77"/>
-      <c r="B5" s="77"/>
+      <c r="A5" s="60"/>
+      <c r="B5" s="60"/>
       <c r="C5" s="30">
         <v>1.3</v>
       </c>
       <c r="D5" s="29" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="E5" s="29" t="s">
-        <v>202</v>
+        <v>192</v>
       </c>
       <c r="F5" s="29" t="s">
-        <v>191</v>
+        <v>181</v>
       </c>
       <c r="G5" s="30" t="s">
-        <v>200</v>
+        <v>190</v>
       </c>
       <c r="H5" s="29"/>
       <c r="I5" s="29"/>
     </row>
-    <row r="6" spans="1:9" s="6" customFormat="1" ht="138" x14ac:dyDescent="0.3">
-      <c r="A6" s="77"/>
-      <c r="B6" s="77"/>
+    <row r="6" spans="1:9" s="6" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
+      <c r="A6" s="60"/>
+      <c r="B6" s="60"/>
       <c r="C6" s="30">
         <v>1.4</v>
       </c>
       <c r="D6" s="29" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="E6" s="29" t="s">
-        <v>203</v>
+        <v>193</v>
       </c>
       <c r="F6" s="29" t="s">
-        <v>192</v>
+        <v>182</v>
       </c>
       <c r="G6" s="30" t="s">
-        <v>198</v>
+        <v>188</v>
       </c>
       <c r="H6" s="29"/>
       <c r="I6" s="29"/>
     </row>
-    <row r="7" spans="1:9" s="6" customFormat="1" ht="165.6" x14ac:dyDescent="0.3">
-      <c r="A7" s="77"/>
-      <c r="B7" s="77"/>
+    <row r="7" spans="1:9" s="6" customFormat="1" ht="151.80000000000001" x14ac:dyDescent="0.3">
+      <c r="A7" s="60"/>
+      <c r="B7" s="60"/>
       <c r="C7" s="30">
         <v>1.5</v>
       </c>
       <c r="D7" s="29" t="s">
-        <v>207</v>
+        <v>197</v>
       </c>
       <c r="E7" s="29" t="s">
-        <v>204</v>
+        <v>194</v>
       </c>
       <c r="F7" s="29" t="s">
-        <v>193</v>
+        <v>183</v>
       </c>
       <c r="G7" s="30" t="s">
-        <v>206</v>
+        <v>196</v>
       </c>
       <c r="H7" s="29"/>
       <c r="I7" s="29"/>
     </row>
-    <row r="8" spans="1:9" s="6" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A8" s="72">
+    <row r="8" spans="1:9" s="6" customFormat="1" ht="110.4" x14ac:dyDescent="0.3">
+      <c r="A8" s="55">
         <v>5</v>
       </c>
-      <c r="B8" s="72" t="s">
+      <c r="B8" s="55" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="8">
@@ -4297,9 +4428,9 @@
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="6" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A9" s="73"/>
-      <c r="B9" s="73"/>
+    <row r="9" spans="1:9" s="6" customFormat="1" ht="110.4" x14ac:dyDescent="0.3">
+      <c r="A9" s="56"/>
+      <c r="B9" s="56"/>
       <c r="C9" s="8">
         <v>5.2</v>
       </c>
@@ -4319,8 +4450,8 @@
       <c r="I9" s="7"/>
     </row>
     <row r="10" spans="1:9" s="6" customFormat="1" ht="165.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="73"/>
-      <c r="B10" s="73"/>
+      <c r="A10" s="56"/>
+      <c r="B10" s="56"/>
       <c r="C10" s="8">
         <v>5.3</v>
       </c>
@@ -4339,53 +4470,53 @@
       <c r="H10" s="9"/>
       <c r="I10" s="7"/>
     </row>
-    <row r="11" spans="1:9" s="78" customFormat="1" ht="207" x14ac:dyDescent="0.3">
-      <c r="A11" s="73"/>
-      <c r="B11" s="73"/>
+    <row r="11" spans="1:9" s="46" customFormat="1" ht="207" x14ac:dyDescent="0.3">
+      <c r="A11" s="56"/>
+      <c r="B11" s="56"/>
       <c r="C11" s="39">
         <v>5.4</v>
       </c>
       <c r="D11" s="40" t="s">
-        <v>212</v>
+        <v>202</v>
       </c>
       <c r="E11" s="40" t="s">
-        <v>215</v>
+        <v>205</v>
       </c>
       <c r="F11" s="40" t="s">
-        <v>214</v>
+        <v>204</v>
       </c>
       <c r="G11" s="39" t="s">
-        <v>216</v>
+        <v>206</v>
       </c>
       <c r="H11" s="41"/>
       <c r="I11" s="40"/>
     </row>
-    <row r="12" spans="1:9" s="78" customFormat="1" ht="151.80000000000001" x14ac:dyDescent="0.3">
-      <c r="A12" s="74"/>
-      <c r="B12" s="74"/>
+    <row r="12" spans="1:9" s="46" customFormat="1" ht="151.80000000000001" x14ac:dyDescent="0.3">
+      <c r="A12" s="57"/>
+      <c r="B12" s="57"/>
       <c r="C12" s="39">
         <v>5.5</v>
       </c>
       <c r="D12" s="40" t="s">
-        <v>209</v>
+        <v>199</v>
       </c>
       <c r="E12" s="40" t="s">
-        <v>213</v>
+        <v>203</v>
       </c>
       <c r="F12" s="40" t="s">
-        <v>211</v>
+        <v>201</v>
       </c>
       <c r="G12" s="39" t="s">
-        <v>210</v>
+        <v>200</v>
       </c>
       <c r="H12" s="41"/>
       <c r="I12" s="40"/>
     </row>
-    <row r="13" spans="1:9" s="78" customFormat="1" ht="151.80000000000001" x14ac:dyDescent="0.3">
-      <c r="A13" s="65">
+    <row r="13" spans="1:9" s="46" customFormat="1" ht="151.80000000000001" x14ac:dyDescent="0.3">
+      <c r="A13" s="47">
         <v>6</v>
       </c>
-      <c r="B13" s="65" t="s">
+      <c r="B13" s="47" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="39">
@@ -4410,9 +4541,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="6" customFormat="1" ht="138" x14ac:dyDescent="0.3">
-      <c r="A14" s="66"/>
-      <c r="B14" s="66"/>
+    <row r="14" spans="1:9" s="6" customFormat="1" ht="110.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="48"/>
+      <c r="B14" s="48"/>
       <c r="C14" s="11">
         <v>6.2</v>
       </c>
@@ -4420,20 +4551,20 @@
         <v>26</v>
       </c>
       <c r="E14" s="10" t="s">
-        <v>218</v>
+        <v>208</v>
       </c>
       <c r="F14" s="10" t="s">
-        <v>217</v>
+        <v>207</v>
       </c>
       <c r="G14" s="11" t="s">
-        <v>219</v>
+        <v>209</v>
       </c>
       <c r="H14" s="12"/>
       <c r="I14" s="10"/>
     </row>
-    <row r="15" spans="1:9" s="6" customFormat="1" ht="165.6" x14ac:dyDescent="0.3">
-      <c r="A15" s="66"/>
-      <c r="B15" s="66"/>
+    <row r="15" spans="1:9" s="6" customFormat="1" ht="151.80000000000001" x14ac:dyDescent="0.3">
+      <c r="A15" s="48"/>
+      <c r="B15" s="48"/>
       <c r="C15" s="11">
         <v>6.3</v>
       </c>
@@ -4453,8 +4584,8 @@
       <c r="I15" s="10"/>
     </row>
     <row r="16" spans="1:9" s="6" customFormat="1" ht="69" x14ac:dyDescent="0.3">
-      <c r="A16" s="66"/>
-      <c r="B16" s="67"/>
+      <c r="A16" s="48"/>
+      <c r="B16" s="49"/>
       <c r="C16" s="35">
         <v>6.4</v>
       </c>
@@ -4478,10 +4609,10 @@
       </c>
     </row>
     <row r="17" spans="1:9" s="6" customFormat="1" ht="138" x14ac:dyDescent="0.3">
-      <c r="A17" s="68">
+      <c r="A17" s="50">
         <v>7</v>
       </c>
-      <c r="B17" s="65" t="s">
+      <c r="B17" s="47" t="s">
         <v>38</v>
       </c>
       <c r="C17" s="11">
@@ -4506,9 +4637,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="18" spans="1:9" s="6" customFormat="1" ht="69" x14ac:dyDescent="0.3">
-      <c r="A18" s="69"/>
-      <c r="B18" s="66"/>
+    <row r="18" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A18" s="51"/>
+      <c r="B18" s="48"/>
       <c r="C18" s="11">
         <v>7.2</v>
       </c>
@@ -4529,9 +4660,9 @@
         <v>31</v>
       </c>
     </row>
-    <row r="19" spans="1:9" s="6" customFormat="1" ht="179.4" x14ac:dyDescent="0.3">
-      <c r="A19" s="69"/>
-      <c r="B19" s="66"/>
+    <row r="19" spans="1:9" s="6" customFormat="1" ht="165.6" x14ac:dyDescent="0.3">
+      <c r="A19" s="51"/>
+      <c r="B19" s="48"/>
       <c r="C19" s="11">
         <v>7.3</v>
       </c>
@@ -4539,7 +4670,7 @@
         <v>39</v>
       </c>
       <c r="E19" s="10" t="s">
-        <v>194</v>
+        <v>184</v>
       </c>
       <c r="F19" s="10" t="s">
         <v>46</v>
@@ -4551,8 +4682,8 @@
       <c r="I19" s="10"/>
     </row>
     <row r="20" spans="1:9" s="6" customFormat="1" ht="165.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="70"/>
-      <c r="B20" s="67"/>
+      <c r="A20" s="52"/>
+      <c r="B20" s="49"/>
       <c r="C20" s="11">
         <v>7.4</v>
       </c>
@@ -4560,7 +4691,7 @@
         <v>39</v>
       </c>
       <c r="E20" s="10" t="s">
-        <v>195</v>
+        <v>185</v>
       </c>
       <c r="F20" s="10" t="s">
         <v>48</v>
@@ -4572,10 +4703,10 @@
       <c r="I20" s="10"/>
     </row>
     <row r="21" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="48">
+      <c r="A21" s="76">
         <v>8</v>
       </c>
-      <c r="B21" s="48" t="s">
+      <c r="B21" s="76" t="s">
         <v>50</v>
       </c>
       <c r="C21" s="14">
@@ -4598,9 +4729,9 @@
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A22" s="49"/>
-      <c r="B22" s="49"/>
+    <row r="22" spans="1:9" s="6" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A22" s="77"/>
+      <c r="B22" s="77"/>
       <c r="C22" s="14">
         <v>9.3000000000000007</v>
       </c>
@@ -4622,8 +4753,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="50"/>
-      <c r="B23" s="50"/>
+      <c r="A23" s="78"/>
+      <c r="B23" s="78"/>
       <c r="C23" s="14">
         <v>9.4</v>
       </c>
@@ -4644,11 +4775,11 @@
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A24" s="46">
+    <row r="24" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A24" s="74">
         <v>12</v>
       </c>
-      <c r="B24" s="46" t="s">
+      <c r="B24" s="74" t="s">
         <v>64</v>
       </c>
       <c r="C24" s="16">
@@ -4674,8 +4805,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A25" s="46"/>
-      <c r="B25" s="46"/>
+      <c r="A25" s="74"/>
+      <c r="B25" s="74"/>
       <c r="C25" s="16">
         <v>12.2</v>
       </c>
@@ -4698,9 +4829,9 @@
         <v>70</v>
       </c>
     </row>
-    <row r="26" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A26" s="46"/>
-      <c r="B26" s="46"/>
+    <row r="26" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A26" s="74"/>
+      <c r="B26" s="74"/>
       <c r="C26" s="16">
         <v>12.3</v>
       </c>
@@ -4723,9 +4854,9 @@
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="1:9" s="6" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A27" s="46"/>
-      <c r="B27" s="46"/>
+    <row r="27" spans="1:9" s="6" customFormat="1" ht="69" x14ac:dyDescent="0.3">
+      <c r="A27" s="74"/>
+      <c r="B27" s="74"/>
       <c r="C27" s="16">
         <v>12.4</v>
       </c>
@@ -4738,8 +4869,8 @@
       <c r="F27" s="15" t="s">
         <v>78</v>
       </c>
-      <c r="G27" s="16" t="s">
-        <v>79</v>
+      <c r="G27" s="39" t="s">
+        <v>310</v>
       </c>
       <c r="H27" s="15" t="s">
         <v>69</v>
@@ -4749,22 +4880,22 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="6" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A28" s="46"/>
-      <c r="B28" s="46"/>
+      <c r="A28" s="74"/>
+      <c r="B28" s="74"/>
       <c r="C28" s="16">
         <v>12.5</v>
       </c>
       <c r="D28" s="15" t="s">
+        <v>79</v>
+      </c>
+      <c r="E28" s="15" t="s">
         <v>80</v>
       </c>
-      <c r="E28" s="15" t="s">
+      <c r="F28" s="15" t="s">
+        <v>307</v>
+      </c>
+      <c r="G28" s="16" t="s">
         <v>81</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>82</v>
-      </c>
-      <c r="G28" s="16" t="s">
-        <v>83</v>
       </c>
       <c r="H28" s="15" t="s">
         <v>69</v>
@@ -4774,1107 +4905,1107 @@
       </c>
     </row>
     <row r="29" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A29" s="47">
+      <c r="A29" s="75">
         <v>14</v>
       </c>
-      <c r="B29" s="47" t="s">
-        <v>84</v>
+      <c r="B29" s="75" t="s">
+        <v>82</v>
       </c>
       <c r="C29" s="18">
         <v>14.1</v>
       </c>
       <c r="D29" s="44" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E29" s="44" t="s">
-        <v>284</v>
+        <v>274</v>
       </c>
       <c r="F29" s="44" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="G29" s="45" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="H29" s="17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I29" s="17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="30" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="47"/>
-      <c r="B30" s="47"/>
+      <c r="A30" s="75"/>
+      <c r="B30" s="75"/>
       <c r="C30" s="18">
         <v>14.2</v>
       </c>
       <c r="D30" s="44" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E30" s="44" t="s">
-        <v>285</v>
+        <v>275</v>
       </c>
       <c r="F30" s="44" t="s">
-        <v>286</v>
+        <v>276</v>
       </c>
       <c r="G30" s="45" t="s">
-        <v>301</v>
+        <v>291</v>
       </c>
       <c r="H30" s="17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I30" s="17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="47"/>
-      <c r="B31" s="47"/>
+      <c r="A31" s="75"/>
+      <c r="B31" s="75"/>
       <c r="C31" s="18">
         <v>14.3</v>
       </c>
       <c r="D31" s="44" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="E31" s="44" t="s">
-        <v>287</v>
+        <v>277</v>
       </c>
       <c r="F31" s="44" t="s">
-        <v>288</v>
+        <v>278</v>
       </c>
       <c r="G31" s="45" t="s">
-        <v>302</v>
+        <v>292</v>
       </c>
       <c r="H31" s="17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I31" s="17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="32" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="47"/>
-      <c r="B32" s="47"/>
+      <c r="A32" s="75"/>
+      <c r="B32" s="75"/>
       <c r="C32" s="18">
         <v>14.4</v>
       </c>
       <c r="D32" s="44" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E32" s="44" t="s">
-        <v>289</v>
+        <v>279</v>
       </c>
       <c r="F32" s="44" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="G32" s="45" t="s">
-        <v>303</v>
+        <v>293</v>
       </c>
       <c r="H32" s="17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I32" s="17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="33" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A33" s="47"/>
-      <c r="B33" s="47"/>
+      <c r="A33" s="75"/>
+      <c r="B33" s="75"/>
       <c r="C33" s="18">
         <v>14.5</v>
       </c>
       <c r="D33" s="44" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E33" s="44" t="s">
-        <v>290</v>
+        <v>280</v>
       </c>
       <c r="F33" s="44" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="G33" s="45" t="s">
-        <v>304</v>
+        <v>294</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I33" s="17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="34" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="47"/>
-      <c r="B34" s="47"/>
+      <c r="A34" s="75"/>
+      <c r="B34" s="75"/>
       <c r="C34" s="18">
         <v>14.6</v>
       </c>
       <c r="D34" s="44" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E34" s="44" t="s">
-        <v>291</v>
+        <v>281</v>
       </c>
       <c r="F34" s="44" t="s">
-        <v>292</v>
+        <v>282</v>
       </c>
       <c r="G34" s="45" t="s">
-        <v>305</v>
+        <v>295</v>
       </c>
       <c r="H34" s="17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I34" s="17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="35" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="47"/>
-      <c r="B35" s="47"/>
+      <c r="A35" s="75"/>
+      <c r="B35" s="75"/>
       <c r="C35" s="18">
         <v>14.7</v>
       </c>
       <c r="D35" s="44" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E35" s="44" t="s">
-        <v>293</v>
+        <v>283</v>
       </c>
       <c r="F35" s="44" t="s">
-        <v>294</v>
+        <v>284</v>
       </c>
       <c r="G35" s="45" t="s">
-        <v>306</v>
+        <v>296</v>
       </c>
       <c r="H35" s="17" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I35" s="17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="36" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="47"/>
-      <c r="B36" s="47"/>
+      <c r="A36" s="75"/>
+      <c r="B36" s="75"/>
       <c r="C36" s="18">
         <v>14.8</v>
       </c>
       <c r="D36" s="44" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E36" s="44" t="s">
-        <v>295</v>
+        <v>285</v>
       </c>
       <c r="F36" s="44" t="s">
-        <v>296</v>
+        <v>286</v>
       </c>
       <c r="G36" s="45" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="H36" s="17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I36" s="17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="37" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="47"/>
-      <c r="B37" s="47"/>
+      <c r="A37" s="75"/>
+      <c r="B37" s="75"/>
       <c r="C37" s="18">
         <v>14.9</v>
       </c>
       <c r="D37" s="44" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E37" s="44" t="s">
-        <v>297</v>
+        <v>287</v>
       </c>
       <c r="F37" s="44" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="G37" s="45" t="s">
-        <v>308</v>
+        <v>298</v>
       </c>
       <c r="H37" s="17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I37" s="17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="38" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="47"/>
-      <c r="B38" s="47"/>
+      <c r="A38" s="75"/>
+      <c r="B38" s="75"/>
       <c r="C38" s="18">
         <v>14.1</v>
       </c>
       <c r="D38" s="44" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E38" s="44" t="s">
-        <v>298</v>
+        <v>288</v>
       </c>
       <c r="F38" s="44" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="G38" s="45" t="s">
-        <v>309</v>
+        <v>299</v>
       </c>
       <c r="H38" s="17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I38" s="17" t="s">
-        <v>87</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="47"/>
-      <c r="B39" s="47"/>
+      <c r="A39" s="75"/>
+      <c r="B39" s="75"/>
       <c r="C39" s="18">
         <v>14.11</v>
       </c>
       <c r="D39" s="44" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E39" s="44" t="s">
-        <v>299</v>
+        <v>289</v>
       </c>
       <c r="F39" s="44" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="G39" s="45" t="s">
-        <v>310</v>
+        <v>300</v>
       </c>
       <c r="H39" s="17" t="s">
-        <v>88</v>
+        <v>86</v>
       </c>
       <c r="I39" s="17" t="s">
+        <v>85</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="6" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A40" s="61">
+        <v>15</v>
+      </c>
+      <c r="B40" s="61" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" s="6" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="51">
-        <v>15</v>
-      </c>
-      <c r="B40" s="51" t="s">
-        <v>89</v>
       </c>
       <c r="C40" s="20">
         <v>15.1</v>
       </c>
       <c r="D40" s="19" t="s">
+        <v>88</v>
+      </c>
+      <c r="E40" s="19" t="s">
+        <v>89</v>
+      </c>
+      <c r="F40" s="19" t="s">
         <v>90</v>
       </c>
-      <c r="E40" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="F40" s="19" t="s">
-        <v>92</v>
-      </c>
       <c r="G40" s="20" t="s">
-        <v>220</v>
+        <v>210</v>
       </c>
       <c r="H40" s="19" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I40" s="19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="41" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A41" s="52"/>
-      <c r="B41" s="52"/>
+      <c r="A41" s="54"/>
+      <c r="B41" s="54"/>
       <c r="C41" s="20">
         <v>15.2</v>
       </c>
       <c r="D41" s="19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E41" s="19" t="s">
-        <v>93</v>
+        <v>91</v>
       </c>
       <c r="F41" s="19" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
       <c r="G41" s="20" t="s">
-        <v>221</v>
+        <v>211</v>
       </c>
       <c r="H41" s="19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I41" s="19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="42" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A42" s="52"/>
-      <c r="B42" s="52"/>
+      <c r="A42" s="54"/>
+      <c r="B42" s="54"/>
       <c r="C42" s="20">
         <v>15.3</v>
       </c>
       <c r="D42" s="19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E42" s="19" t="s">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="F42" s="19" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="G42" s="20" t="s">
-        <v>222</v>
+        <v>212</v>
       </c>
       <c r="H42" s="19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I42" s="19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="43" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A43" s="52"/>
-      <c r="B43" s="52"/>
+      <c r="A43" s="54"/>
+      <c r="B43" s="54"/>
       <c r="C43" s="20">
         <v>15.4</v>
       </c>
       <c r="D43" s="19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E43" s="19" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="F43" s="19" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
       <c r="G43" s="20" t="s">
-        <v>223</v>
+        <v>213</v>
       </c>
       <c r="H43" s="19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I43" s="19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="44" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A44" s="52"/>
-      <c r="B44" s="52"/>
+      <c r="A44" s="54"/>
+      <c r="B44" s="54"/>
       <c r="C44" s="20">
         <v>15.5</v>
       </c>
       <c r="D44" s="19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E44" s="19" t="s">
-        <v>99</v>
+        <v>97</v>
       </c>
       <c r="F44" s="19" t="s">
-        <v>100</v>
+        <v>98</v>
       </c>
       <c r="G44" s="20" t="s">
-        <v>224</v>
+        <v>214</v>
       </c>
       <c r="H44" s="19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I44" s="19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="45" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A45" s="52"/>
-      <c r="B45" s="52"/>
+      <c r="A45" s="54"/>
+      <c r="B45" s="54"/>
       <c r="C45" s="20">
         <v>15.6</v>
       </c>
       <c r="D45" s="19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E45" s="19" t="s">
-        <v>101</v>
+        <v>99</v>
       </c>
       <c r="F45" s="19" t="s">
-        <v>102</v>
+        <v>100</v>
       </c>
       <c r="G45" s="20" t="s">
-        <v>225</v>
+        <v>215</v>
       </c>
       <c r="H45" s="19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I45" s="19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="46" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="52"/>
-      <c r="B46" s="52"/>
+      <c r="A46" s="54"/>
+      <c r="B46" s="54"/>
       <c r="C46" s="20">
         <v>15.7</v>
       </c>
       <c r="D46" s="19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E46" s="19" t="s">
-        <v>103</v>
+        <v>101</v>
       </c>
       <c r="F46" s="19" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
       <c r="G46" s="20" t="s">
-        <v>226</v>
+        <v>216</v>
       </c>
       <c r="H46" s="19" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I46" s="19" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="47" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A47" s="52"/>
-      <c r="B47" s="52"/>
+      <c r="A47" s="54"/>
+      <c r="B47" s="54"/>
       <c r="C47" s="20">
         <v>15.8</v>
       </c>
       <c r="D47" s="19" t="s">
-        <v>90</v>
+        <v>88</v>
       </c>
       <c r="E47" s="19" t="s">
+        <v>103</v>
+      </c>
+      <c r="F47" s="19" t="s">
+        <v>104</v>
+      </c>
+      <c r="G47" s="20" t="s">
+        <v>217</v>
+      </c>
+      <c r="H47" s="19" t="s">
+        <v>109</v>
+      </c>
+      <c r="I47" s="19" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A48" s="68">
+        <v>16</v>
+      </c>
+      <c r="B48" s="68" t="s">
         <v>105</v>
-      </c>
-      <c r="F47" s="19" t="s">
-        <v>106</v>
-      </c>
-      <c r="G47" s="20" t="s">
-        <v>227</v>
-      </c>
-      <c r="H47" s="19" t="s">
-        <v>111</v>
-      </c>
-      <c r="I47" s="19" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A48" s="59">
-        <v>16</v>
-      </c>
-      <c r="B48" s="59" t="s">
-        <v>107</v>
       </c>
       <c r="C48" s="36">
         <v>16.100000000000001</v>
       </c>
       <c r="D48" s="21" t="s">
+        <v>106</v>
+      </c>
+      <c r="E48" s="21" t="s">
+        <v>107</v>
+      </c>
+      <c r="F48" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="E48" s="21" t="s">
+      <c r="G48" s="22" t="s">
+        <v>218</v>
+      </c>
+      <c r="H48" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="F48" s="21" t="s">
+      <c r="I48" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="G48" s="22" t="s">
-        <v>228</v>
-      </c>
-      <c r="H48" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="I48" s="21" t="s">
-        <v>112</v>
-      </c>
     </row>
     <row r="49" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A49" s="59"/>
-      <c r="B49" s="59"/>
+      <c r="A49" s="68"/>
+      <c r="B49" s="68"/>
       <c r="C49" s="36">
         <v>16.2</v>
       </c>
       <c r="D49" s="21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E49" s="21" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="F49" s="21" t="s">
-        <v>114</v>
+        <v>112</v>
       </c>
       <c r="G49" s="22" t="s">
-        <v>229</v>
+        <v>219</v>
       </c>
       <c r="H49" s="21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I49" s="21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="50" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A50" s="59"/>
-      <c r="B50" s="59"/>
+      <c r="A50" s="68"/>
+      <c r="B50" s="68"/>
       <c r="C50" s="36">
         <v>16.3</v>
       </c>
       <c r="D50" s="21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E50" s="21" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="F50" s="21" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="G50" s="22" t="s">
-        <v>230</v>
+        <v>220</v>
       </c>
       <c r="H50" s="21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I50" s="21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="51" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A51" s="59"/>
-      <c r="B51" s="59"/>
+      <c r="A51" s="68"/>
+      <c r="B51" s="68"/>
       <c r="C51" s="36">
         <v>16.399999999999999</v>
       </c>
       <c r="D51" s="21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E51" s="21" t="s">
-        <v>117</v>
+        <v>115</v>
       </c>
       <c r="F51" s="21" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="G51" s="22" t="s">
-        <v>231</v>
+        <v>221</v>
       </c>
       <c r="H51" s="21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I51" s="21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="52" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A52" s="59"/>
-      <c r="B52" s="59"/>
+      <c r="A52" s="68"/>
+      <c r="B52" s="68"/>
       <c r="C52" s="36">
         <v>16.5</v>
       </c>
       <c r="D52" s="21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E52" s="21" t="s">
-        <v>119</v>
+        <v>117</v>
       </c>
       <c r="F52" s="21" t="s">
-        <v>120</v>
+        <v>118</v>
       </c>
       <c r="G52" s="22" t="s">
-        <v>232</v>
+        <v>222</v>
       </c>
       <c r="H52" s="21" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I52" s="21" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="53" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A53" s="52"/>
-      <c r="B53" s="52"/>
+      <c r="A53" s="54"/>
+      <c r="B53" s="54"/>
       <c r="C53" s="36">
         <v>16.600000000000001</v>
       </c>
       <c r="D53" s="21" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
       <c r="E53" s="21" t="s">
+        <v>119</v>
+      </c>
+      <c r="F53" s="21" t="s">
+        <v>120</v>
+      </c>
+      <c r="G53" s="22" t="s">
+        <v>223</v>
+      </c>
+      <c r="H53" s="21" t="s">
+        <v>109</v>
+      </c>
+      <c r="I53" s="21" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A54" s="69">
+        <v>17</v>
+      </c>
+      <c r="B54" s="72" t="s">
         <v>121</v>
-      </c>
-      <c r="F53" s="21" t="s">
-        <v>122</v>
-      </c>
-      <c r="G53" s="22" t="s">
-        <v>233</v>
-      </c>
-      <c r="H53" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="I53" s="21" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A54" s="60">
-        <v>17</v>
-      </c>
-      <c r="B54" s="63" t="s">
-        <v>123</v>
       </c>
       <c r="C54" s="24">
         <v>17.100000000000001</v>
       </c>
       <c r="D54" s="23" t="s">
+        <v>122</v>
+      </c>
+      <c r="E54" s="23" t="s">
+        <v>123</v>
+      </c>
+      <c r="F54" s="23" t="s">
         <v>124</v>
       </c>
-      <c r="E54" s="23" t="s">
+      <c r="G54" s="24" t="s">
+        <v>224</v>
+      </c>
+      <c r="H54" s="23" t="s">
         <v>125</v>
       </c>
-      <c r="F54" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="G54" s="24" t="s">
-        <v>234</v>
-      </c>
-      <c r="H54" s="23" t="s">
-        <v>127</v>
-      </c>
       <c r="I54" s="23" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="55" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A55" s="61"/>
-      <c r="B55" s="63"/>
+      <c r="A55" s="70"/>
+      <c r="B55" s="72"/>
       <c r="C55" s="24">
         <v>17.2</v>
       </c>
       <c r="D55" s="23" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E55" s="23" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="F55" s="23" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="G55" s="24" t="s">
-        <v>235</v>
+        <v>225</v>
       </c>
       <c r="H55" s="23" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I55" s="23" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="56" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A56" s="61"/>
-      <c r="B56" s="63"/>
+      <c r="A56" s="70"/>
+      <c r="B56" s="72"/>
       <c r="C56" s="24">
         <v>17.3</v>
       </c>
       <c r="D56" s="23" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E56" s="23" t="s">
-        <v>130</v>
+        <v>128</v>
       </c>
       <c r="F56" s="23" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="G56" s="24" t="s">
-        <v>236</v>
+        <v>226</v>
       </c>
       <c r="H56" s="23" t="s">
-        <v>111</v>
+        <v>109</v>
       </c>
       <c r="I56" s="23" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="57" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A57" s="61"/>
-      <c r="B57" s="63"/>
+      <c r="A57" s="70"/>
+      <c r="B57" s="72"/>
       <c r="C57" s="24">
         <v>17.399999999999999</v>
       </c>
       <c r="D57" s="23" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E57" s="23" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="F57" s="23" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="G57" s="24" t="s">
-        <v>237</v>
+        <v>227</v>
       </c>
       <c r="H57" s="23" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="I57" s="23" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
     </row>
     <row r="58" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A58" s="62"/>
-      <c r="B58" s="63"/>
+      <c r="A58" s="71"/>
+      <c r="B58" s="72"/>
       <c r="C58" s="24">
         <v>17.5</v>
       </c>
       <c r="D58" s="23" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="E58" s="23" t="s">
+        <v>132</v>
+      </c>
+      <c r="F58" s="23" t="s">
+        <v>133</v>
+      </c>
+      <c r="G58" s="24" t="s">
+        <v>228</v>
+      </c>
+      <c r="H58" s="23" t="s">
+        <v>125</v>
+      </c>
+      <c r="I58" s="23" t="s">
+        <v>110</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A59" s="73">
+        <v>18</v>
+      </c>
+      <c r="B59" s="73" t="s">
         <v>134</v>
-      </c>
-      <c r="F58" s="23" t="s">
-        <v>135</v>
-      </c>
-      <c r="G58" s="24" t="s">
-        <v>238</v>
-      </c>
-      <c r="H58" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="I58" s="23" t="s">
-        <v>112</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A59" s="64">
-        <v>18</v>
-      </c>
-      <c r="B59" s="64" t="s">
-        <v>136</v>
       </c>
       <c r="C59" s="8">
         <v>17.100000000000001</v>
       </c>
       <c r="D59" s="7" t="s">
+        <v>135</v>
+      </c>
+      <c r="E59" s="7" t="s">
+        <v>136</v>
+      </c>
+      <c r="F59" s="7" t="s">
         <v>137</v>
       </c>
-      <c r="E59" s="7" t="s">
+      <c r="G59" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="H59" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I59" s="7" t="s">
         <v>138</v>
       </c>
-      <c r="F59" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="G59" s="8" t="s">
-        <v>239</v>
-      </c>
-      <c r="H59" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="I59" s="7" t="s">
-        <v>140</v>
-      </c>
     </row>
     <row r="60" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A60" s="52"/>
-      <c r="B60" s="52"/>
+      <c r="A60" s="54"/>
+      <c r="B60" s="54"/>
       <c r="C60" s="8">
         <v>17.2</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E60" s="7" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
       <c r="F60" s="7" t="s">
-        <v>142</v>
+        <v>140</v>
       </c>
       <c r="G60" s="8" t="s">
-        <v>240</v>
+        <v>230</v>
       </c>
       <c r="H60" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I60" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="61" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A61" s="52"/>
-      <c r="B61" s="52"/>
+      <c r="A61" s="54"/>
+      <c r="B61" s="54"/>
       <c r="C61" s="8">
         <v>17.3</v>
       </c>
       <c r="D61" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E61" s="7" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="F61" s="7" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="G61" s="8" t="s">
-        <v>241</v>
+        <v>231</v>
       </c>
       <c r="H61" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I61" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="62" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A62" s="52"/>
-      <c r="B62" s="52"/>
+      <c r="A62" s="54"/>
+      <c r="B62" s="54"/>
       <c r="C62" s="8">
         <v>17.399999999999999</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E62" s="7" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="F62" s="7" t="s">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="G62" s="8" t="s">
-        <v>242</v>
+        <v>232</v>
       </c>
       <c r="H62" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I62" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="63" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A63" s="52"/>
-      <c r="B63" s="52"/>
+      <c r="A63" s="54"/>
+      <c r="B63" s="54"/>
       <c r="C63" s="8">
         <v>17.5</v>
       </c>
       <c r="D63" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E63" s="7" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F63" s="7" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="G63" s="8" t="s">
-        <v>243</v>
+        <v>233</v>
       </c>
       <c r="H63" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I63" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="64" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A64" s="52"/>
-      <c r="B64" s="52"/>
+      <c r="A64" s="54"/>
+      <c r="B64" s="54"/>
       <c r="C64" s="8">
         <v>17.600000000000001</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E64" s="7" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="F64" s="7" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="G64" s="8" t="s">
-        <v>244</v>
+        <v>234</v>
       </c>
       <c r="H64" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I64" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="65" spans="1:12" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A65" s="52"/>
-      <c r="B65" s="52"/>
+      <c r="A65" s="54"/>
+      <c r="B65" s="54"/>
       <c r="C65" s="8">
         <v>17.7</v>
       </c>
       <c r="D65" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E65" s="7" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="F65" s="7" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="G65" s="8" t="s">
-        <v>245</v>
+        <v>235</v>
       </c>
       <c r="H65" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I65" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="66" spans="1:12" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A66" s="52"/>
-      <c r="B66" s="52"/>
+      <c r="A66" s="54"/>
+      <c r="B66" s="54"/>
       <c r="C66" s="8">
         <v>17.8</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E66" s="7" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="F66" s="7" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="G66" s="8" t="s">
-        <v>246</v>
+        <v>236</v>
       </c>
       <c r="H66" s="7" t="s">
-        <v>86</v>
+        <v>84</v>
       </c>
       <c r="I66" s="7" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
     </row>
     <row r="67" spans="1:12" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A67" s="52"/>
-      <c r="B67" s="52"/>
+      <c r="A67" s="54"/>
+      <c r="B67" s="54"/>
       <c r="C67" s="8">
         <v>17.899999999999999</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="E67" s="7" t="s">
+        <v>152</v>
+      </c>
+      <c r="F67" s="7" t="s">
+        <v>153</v>
+      </c>
+      <c r="G67" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="H67" s="7" t="s">
+        <v>84</v>
+      </c>
+      <c r="I67" s="7" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A68" s="62">
+        <v>19</v>
+      </c>
+      <c r="B68" s="65" t="s">
         <v>154</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>155</v>
-      </c>
-      <c r="G67" s="8" t="s">
-        <v>247</v>
-      </c>
-      <c r="H67" s="7" t="s">
-        <v>86</v>
-      </c>
-      <c r="I67" s="7" t="s">
-        <v>140</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" s="6" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A68" s="53">
-        <v>19</v>
-      </c>
-      <c r="B68" s="56" t="s">
-        <v>156</v>
       </c>
       <c r="C68" s="26">
         <v>19.100000000000001</v>
       </c>
       <c r="D68" s="33" t="s">
+        <v>155</v>
+      </c>
+      <c r="E68" s="33" t="s">
+        <v>156</v>
+      </c>
+      <c r="F68" s="33" t="s">
         <v>157</v>
       </c>
-      <c r="E68" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="F68" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="G68" s="31" t="s">
-        <v>160</v>
+      <c r="G68" s="39" t="s">
+        <v>309</v>
       </c>
       <c r="H68" s="3"/>
       <c r="I68" s="32"/>
     </row>
     <row r="69" spans="1:12" s="6" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A69" s="54"/>
-      <c r="B69" s="57"/>
+      <c r="A69" s="63"/>
+      <c r="B69" s="66"/>
       <c r="C69" s="34">
         <v>19.2</v>
       </c>
       <c r="D69" s="33" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="E69" s="33" t="s">
-        <v>162</v>
+        <v>159</v>
       </c>
       <c r="F69" s="33" t="s">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="G69" s="31" t="s">
-        <v>163</v>
+        <v>160</v>
       </c>
       <c r="H69" s="3"/>
       <c r="I69" s="32"/>
     </row>
     <row r="70" spans="1:12" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A70" s="55"/>
-      <c r="B70" s="58"/>
-      <c r="C70" s="34">
+      <c r="A70" s="64"/>
+      <c r="B70" s="67"/>
+      <c r="C70" s="82">
         <v>19.3</v>
       </c>
-      <c r="D70" s="33" t="s">
-        <v>157</v>
-      </c>
-      <c r="E70" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="F70" s="33" t="s">
-        <v>165</v>
-      </c>
-      <c r="G70" s="31"/>
-      <c r="H70" s="3"/>
-      <c r="I70" s="32"/>
-    </row>
-    <row r="71" spans="1:12" s="6" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A71" s="53">
+      <c r="D70" s="29" t="s">
+        <v>155</v>
+      </c>
+      <c r="E70" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="F70" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="G70" s="30"/>
+      <c r="H70" s="80"/>
+      <c r="I70" s="81"/>
+    </row>
+    <row r="71" spans="1:12" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A71" s="62">
         <v>20</v>
       </c>
-      <c r="B71" s="56" t="s">
-        <v>166</v>
+      <c r="B71" s="65" t="s">
+        <v>163</v>
       </c>
       <c r="C71" s="26">
         <v>20.100000000000001</v>
       </c>
       <c r="D71" s="33" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="E71" s="33" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="F71" s="33" t="s">
-        <v>169</v>
-      </c>
-      <c r="G71" s="31" t="s">
-        <v>170</v>
+        <v>166</v>
+      </c>
+      <c r="G71" s="39" t="s">
+        <v>308</v>
       </c>
       <c r="H71" s="3"/>
       <c r="I71" s="32"/>
     </row>
     <row r="72" spans="1:12" s="6" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A72" s="54"/>
-      <c r="B72" s="57"/>
+      <c r="A72" s="63"/>
+      <c r="B72" s="66"/>
       <c r="C72" s="34">
         <v>20.2</v>
       </c>
       <c r="D72" s="33" t="s">
-        <v>171</v>
+        <v>167</v>
       </c>
       <c r="E72" s="33" t="s">
-        <v>172</v>
+        <v>168</v>
       </c>
       <c r="F72" s="33" t="s">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="G72" s="31" t="s">
-        <v>173</v>
+        <v>169</v>
       </c>
       <c r="H72" s="3"/>
       <c r="I72" s="32"/>
@@ -5883,150 +6014,150 @@
       <c r="L72" s="1"/>
     </row>
     <row r="73" spans="1:12" s="6" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="55"/>
-      <c r="B73" s="58"/>
-      <c r="C73" s="26">
+      <c r="A73" s="64"/>
+      <c r="B73" s="67"/>
+      <c r="C73" s="79">
         <v>20.3</v>
       </c>
-      <c r="D73" s="33" t="s">
-        <v>167</v>
-      </c>
-      <c r="E73" s="33" t="s">
+      <c r="D73" s="29" t="s">
         <v>164</v>
       </c>
-      <c r="F73" s="33"/>
-      <c r="G73" s="31"/>
-      <c r="H73" s="3"/>
-      <c r="I73" s="32"/>
+      <c r="E73" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="F73" s="29"/>
+      <c r="G73" s="30"/>
+      <c r="H73" s="80"/>
+      <c r="I73" s="81"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
     </row>
-    <row r="74" spans="1:12" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A74" s="53">
+    <row r="74" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
+      <c r="A74" s="62">
         <v>21</v>
       </c>
-      <c r="B74" s="56" t="s">
-        <v>174</v>
+      <c r="B74" s="65" t="s">
+        <v>170</v>
       </c>
       <c r="C74" s="26">
         <v>21.1</v>
       </c>
       <c r="D74" s="33" t="s">
-        <v>175</v>
+        <v>171</v>
       </c>
       <c r="E74" s="33" t="s">
-        <v>176</v>
+        <v>172</v>
       </c>
       <c r="F74" s="33" t="s">
-        <v>177</v>
-      </c>
-      <c r="G74" s="31" t="s">
-        <v>178</v>
+        <v>173</v>
+      </c>
+      <c r="G74" s="39" t="s">
+        <v>305</v>
       </c>
       <c r="H74" s="3"/>
       <c r="I74" s="32"/>
     </row>
     <row r="75" spans="1:12" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A75" s="54"/>
-      <c r="B75" s="57"/>
+      <c r="A75" s="63"/>
+      <c r="B75" s="66"/>
       <c r="C75" s="34">
         <v>21.2</v>
       </c>
       <c r="D75" s="33" t="s">
-        <v>179</v>
+        <v>174</v>
       </c>
       <c r="E75" s="33" t="s">
-        <v>180</v>
+        <v>306</v>
       </c>
       <c r="F75" s="33" t="s">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="G75" s="31" t="s">
-        <v>181</v>
+        <v>175</v>
       </c>
       <c r="H75" s="3"/>
       <c r="I75" s="32"/>
     </row>
     <row r="76" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="55"/>
-      <c r="B76" s="58"/>
-      <c r="C76" s="26">
+      <c r="A76" s="64"/>
+      <c r="B76" s="67"/>
+      <c r="C76" s="79">
         <v>21.3</v>
       </c>
-      <c r="D76" s="33" t="s">
-        <v>175</v>
-      </c>
-      <c r="E76" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="F76" s="33"/>
-      <c r="G76" s="31"/>
-      <c r="H76" s="3"/>
-      <c r="I76" s="32"/>
-    </row>
-    <row r="77" spans="1:12" ht="179.4" x14ac:dyDescent="0.3">
-      <c r="A77" s="53">
+      <c r="D76" s="29" t="s">
+        <v>171</v>
+      </c>
+      <c r="E76" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="F76" s="29"/>
+      <c r="G76" s="30"/>
+      <c r="H76" s="80"/>
+      <c r="I76" s="81"/>
+    </row>
+    <row r="77" spans="1:12" ht="82.8" x14ac:dyDescent="0.3">
+      <c r="A77" s="62">
         <v>22</v>
       </c>
-      <c r="B77" s="56" t="s">
-        <v>182</v>
+      <c r="B77" s="65" t="s">
+        <v>176</v>
       </c>
       <c r="C77" s="26">
         <v>22.1</v>
       </c>
       <c r="D77" s="33" t="s">
-        <v>183</v>
+        <v>177</v>
       </c>
       <c r="E77" s="33" t="s">
-        <v>184</v>
+        <v>178</v>
       </c>
       <c r="F77" s="33" t="s">
-        <v>185</v>
+        <v>301</v>
       </c>
       <c r="G77" s="31" t="s">
-        <v>186</v>
+        <v>304</v>
       </c>
       <c r="H77" s="3"/>
       <c r="I77" s="32"/>
     </row>
     <row r="78" spans="1:12" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A78" s="54"/>
-      <c r="B78" s="57"/>
+      <c r="A78" s="63"/>
+      <c r="B78" s="66"/>
       <c r="C78" s="34">
         <v>22.2</v>
       </c>
       <c r="D78" s="33" t="s">
-        <v>187</v>
+        <v>302</v>
       </c>
       <c r="E78" s="3" t="s">
-        <v>188</v>
+        <v>303</v>
       </c>
       <c r="F78" s="33" t="s">
-        <v>82</v>
+        <v>307</v>
       </c>
       <c r="G78" s="31" t="s">
-        <v>189</v>
+        <v>179</v>
       </c>
       <c r="H78" s="3"/>
       <c r="I78" s="32"/>
     </row>
     <row r="79" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A79" s="55"/>
-      <c r="B79" s="58"/>
-      <c r="C79" s="26">
+      <c r="A79" s="64"/>
+      <c r="B79" s="67"/>
+      <c r="C79" s="79">
         <v>22.3</v>
       </c>
-      <c r="D79" s="33" t="s">
-        <v>183</v>
-      </c>
-      <c r="E79" s="3" t="s">
-        <v>164</v>
-      </c>
-      <c r="F79" s="33"/>
-      <c r="G79" s="31"/>
-      <c r="H79" s="3"/>
-      <c r="I79" s="32"/>
+      <c r="D79" s="29" t="s">
+        <v>177</v>
+      </c>
+      <c r="E79" s="80" t="s">
+        <v>161</v>
+      </c>
+      <c r="F79" s="29"/>
+      <c r="G79" s="30"/>
+      <c r="H79" s="80"/>
+      <c r="I79" s="81"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A80" s="3"/>
@@ -6129,21 +6260,12 @@
   </sheetData>
   <autoFilter ref="I1:I26" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="37">
-    <mergeCell ref="A13:A16"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="A17:A20"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="A29:A39"/>
+    <mergeCell ref="B29:B39"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="B21:B23"/>
     <mergeCell ref="A40:A47"/>
     <mergeCell ref="B40:B47"/>
     <mergeCell ref="A74:A76"/>
@@ -6160,12 +6282,21 @@
     <mergeCell ref="B68:B70"/>
     <mergeCell ref="A71:A73"/>
     <mergeCell ref="B71:B73"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="A29:A39"/>
-    <mergeCell ref="B29:B39"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B17:B20"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6226,7 +6357,7 @@
         <v>8</v>
       </c>
       <c r="H3" s="42" t="s">
-        <v>248</v>
+        <v>238</v>
       </c>
       <c r="I3" s="42" t="s">
         <v>4</v>
@@ -6238,22 +6369,22 @@
       <c r="B4" s="28"/>
       <c r="C4" s="28"/>
       <c r="D4" s="43" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E4" s="43">
         <v>14.1</v>
       </c>
       <c r="F4" s="27" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G4" s="27" t="s">
-        <v>249</v>
+        <v>239</v>
       </c>
       <c r="H4" s="27" t="s">
-        <v>250</v>
+        <v>240</v>
       </c>
       <c r="I4" s="43" t="s">
-        <v>251</v>
+        <v>241</v>
       </c>
       <c r="J4" s="28"/>
     </row>
@@ -6262,22 +6393,22 @@
       <c r="B5" s="28"/>
       <c r="C5" s="28"/>
       <c r="D5" s="43" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E5" s="43">
         <v>14.2</v>
       </c>
       <c r="F5" s="27" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G5" s="27" t="s">
-        <v>252</v>
+        <v>242</v>
       </c>
       <c r="H5" s="27" t="s">
-        <v>253</v>
+        <v>243</v>
       </c>
       <c r="I5" s="43" t="s">
-        <v>254</v>
+        <v>244</v>
       </c>
       <c r="J5" s="28"/>
     </row>
@@ -6286,22 +6417,22 @@
       <c r="B6" s="28"/>
       <c r="C6" s="28"/>
       <c r="D6" s="43" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E6" s="43">
         <v>14.3</v>
       </c>
       <c r="F6" s="27" t="s">
-        <v>255</v>
+        <v>245</v>
       </c>
       <c r="G6" s="27" t="s">
-        <v>256</v>
+        <v>246</v>
       </c>
       <c r="H6" s="27" t="s">
-        <v>257</v>
+        <v>247</v>
       </c>
       <c r="I6" s="43" t="s">
-        <v>258</v>
+        <v>248</v>
       </c>
       <c r="J6" s="28"/>
     </row>
@@ -6310,22 +6441,22 @@
       <c r="B7" s="28"/>
       <c r="C7" s="28"/>
       <c r="D7" s="43" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E7" s="43">
         <v>14.4</v>
       </c>
       <c r="F7" s="27" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G7" s="27" t="s">
-        <v>259</v>
+        <v>249</v>
       </c>
       <c r="H7" s="27" t="s">
-        <v>260</v>
+        <v>250</v>
       </c>
       <c r="I7" s="43" t="s">
-        <v>261</v>
+        <v>251</v>
       </c>
       <c r="J7" s="28"/>
     </row>
@@ -6334,22 +6465,22 @@
       <c r="B8" s="28"/>
       <c r="C8" s="28"/>
       <c r="D8" s="43" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E8" s="43">
         <v>14.5</v>
       </c>
       <c r="F8" s="27" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G8" s="27" t="s">
-        <v>262</v>
+        <v>252</v>
       </c>
       <c r="H8" s="27" t="s">
-        <v>263</v>
+        <v>253</v>
       </c>
       <c r="I8" s="43" t="s">
-        <v>264</v>
+        <v>254</v>
       </c>
       <c r="J8" s="28"/>
     </row>
@@ -6358,22 +6489,22 @@
       <c r="B9" s="28"/>
       <c r="C9" s="28"/>
       <c r="D9" s="43" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E9" s="43">
         <v>14.6</v>
       </c>
       <c r="F9" s="27" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G9" s="27" t="s">
-        <v>265</v>
+        <v>255</v>
       </c>
       <c r="H9" s="27" t="s">
-        <v>266</v>
+        <v>256</v>
       </c>
       <c r="I9" s="43" t="s">
-        <v>267</v>
+        <v>257</v>
       </c>
       <c r="J9" s="28"/>
     </row>
@@ -6382,22 +6513,22 @@
       <c r="B10" s="28"/>
       <c r="C10" s="28"/>
       <c r="D10" s="43" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E10" s="43">
         <v>14.7</v>
       </c>
       <c r="F10" s="27" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G10" s="27" t="s">
-        <v>268</v>
+        <v>258</v>
       </c>
       <c r="H10" s="27" t="s">
-        <v>269</v>
+        <v>259</v>
       </c>
       <c r="I10" s="43" t="s">
-        <v>270</v>
+        <v>260</v>
       </c>
       <c r="J10" s="28"/>
     </row>
@@ -6406,22 +6537,22 @@
       <c r="B11" s="28"/>
       <c r="C11" s="28"/>
       <c r="D11" s="43" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E11" s="43">
         <v>14.8</v>
       </c>
       <c r="F11" s="27" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G11" s="27" t="s">
-        <v>271</v>
+        <v>261</v>
       </c>
       <c r="H11" s="27" t="s">
-        <v>272</v>
+        <v>262</v>
       </c>
       <c r="I11" s="43" t="s">
-        <v>273</v>
+        <v>263</v>
       </c>
       <c r="J11" s="28"/>
     </row>
@@ -6430,22 +6561,22 @@
       <c r="B12" s="28"/>
       <c r="C12" s="28"/>
       <c r="D12" s="43" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E12" s="43">
         <v>14.9</v>
       </c>
       <c r="F12" s="27" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G12" s="27" t="s">
-        <v>274</v>
+        <v>264</v>
       </c>
       <c r="H12" s="27" t="s">
-        <v>275</v>
+        <v>265</v>
       </c>
       <c r="I12" s="43" t="s">
-        <v>276</v>
+        <v>266</v>
       </c>
       <c r="J12" s="28"/>
     </row>
@@ -6454,22 +6585,22 @@
       <c r="B13" s="28"/>
       <c r="C13" s="28"/>
       <c r="D13" s="43" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E13" s="43" t="s">
-        <v>277</v>
+        <v>267</v>
       </c>
       <c r="F13" s="27" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G13" s="27" t="s">
-        <v>278</v>
+        <v>268</v>
       </c>
       <c r="H13" s="27" t="s">
-        <v>279</v>
+        <v>269</v>
       </c>
       <c r="I13" s="43" t="s">
-        <v>280</v>
+        <v>270</v>
       </c>
       <c r="J13" s="28"/>
     </row>
@@ -6478,22 +6609,22 @@
       <c r="B14" s="28"/>
       <c r="C14" s="28"/>
       <c r="D14" s="43" t="s">
-        <v>84</v>
+        <v>82</v>
       </c>
       <c r="E14" s="43">
         <v>14.11</v>
       </c>
       <c r="F14" s="27" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="G14" s="27" t="s">
-        <v>281</v>
+        <v>271</v>
       </c>
       <c r="H14" s="27" t="s">
-        <v>282</v>
+        <v>272</v>
       </c>
       <c r="I14" s="43" t="s">
-        <v>283</v>
+        <v>273</v>
       </c>
       <c r="J14" s="28"/>
     </row>

--- a/Soubhanik/checkupp_product_backlog_final.xlsx
+++ b/Soubhanik/checkupp_product_backlog_final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Soubhanik\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anodiam\2026\CheckUpp_Parent\CheckUpp\Soubhanik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DBCE050-C94F-4EBD-856F-ED75712EDB8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43CB0B16-3146-438B-94C7-AFE204B96F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -101,64 +101,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="B24" authorId="0" shapeId="0" xr:uid="{CCB9346B-D6BE-41C8-B44E-B56235F8E7A9}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Sayan:</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve">
-Include user story for user taking picture of report for AI assessment, under </t>
-        </r>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Mental Health Assessment</t>
-        </r>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t xml:space="preserve"> epic</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G27" authorId="0" shapeId="0" xr:uid="{27A0456B-2583-4AB5-8308-7578F51E35E5}">
-      <text>
-        <r>
-          <rPr>
-            <sz val="9"/>
-            <color indexed="81"/>
-            <rFont val="Tahoma"/>
-            <family val="2"/>
-          </rPr>
-          <t>Sayan:
-Dropdowns with exact name examples from the screen</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="G68" authorId="0" shapeId="0" xr:uid="{3283D6CB-61A1-4390-A688-5F4F500D8585}">
+    <comment ref="G69" authorId="0" shapeId="0" xr:uid="{3283D6CB-61A1-4390-A688-5F4F500D8585}">
       <text>
         <r>
           <rPr>
@@ -182,7 +125,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G71" authorId="0" shapeId="0" xr:uid="{C1521E49-0187-46FC-9D55-A1D99E904DBB}">
+    <comment ref="G72" authorId="0" shapeId="0" xr:uid="{C1521E49-0187-46FC-9D55-A1D99E904DBB}">
       <text>
         <r>
           <rPr>
@@ -206,7 +149,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G74" authorId="0" shapeId="0" xr:uid="{6311CE01-3810-423E-933D-ACFFBD920BE0}">
+    <comment ref="G75" authorId="0" shapeId="0" xr:uid="{6311CE01-3810-423E-933D-ACFFBD920BE0}">
       <text>
         <r>
           <rPr>
@@ -235,7 +178,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="490" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="311">
   <si>
     <t>Epic #</t>
   </si>
@@ -510,12 +453,6 @@
 3. Screen must be accessible from the Mental Health Check screen</t>
   </si>
   <si>
-    <t>have the data I enter in the available fields(K-10 score, DASS-21 Depression, DASS-21 Anxiety, etc) or used the toggle switches (difficulty falling asleep and frequent night waking) autosaved in the system if I tap the 'Back' button or close/remove the app from the background</t>
-  </si>
-  <si>
-    <t>I don't have to re-enter the data in the fields(K-10 score, DASS-21 Depression, DASS-21 Anxiety, etc.) or re-toggle the switches (difficulty falling asleep and frequent night waking) again</t>
-  </si>
-  <si>
     <t>logged in user revisiting the mental health assessment</t>
   </si>
   <si>
@@ -966,328 +903,28 @@
     <t>Logged-in User</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">tap </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Other Ailments</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> from the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Available Health Checks</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen in the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Screenings</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tab</t>
-    </r>
-  </si>
-  <si>
     <t>I can create a custom health check for conditions not currently supported by CheckUpp</t>
   </si>
   <si>
     <t>Discussion #4 – TANVI</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">select a predefined condition or enter a custom condition name on the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Other Ailments</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
     <t>I can document any medical condition or test</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">enter a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Test Date</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> on the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Other Ailments</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
     <t>my health record is accurately timestamped</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">enter appointment details on the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Other Ailments</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">tap </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Add Field</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> on the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Other Ailments</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
     <t>I can create custom sections relevant to my condition</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">tap </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Add Subfield</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> under a custom field</t>
-    </r>
-  </si>
-  <si>
     <t>I can record detailed measurements</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">review my entered information before saving on the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Review Your Entries</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
     <t>I can verify all information before creating the health check</t>
   </si>
   <si>
     <r>
-      <t xml:space="preserve">tap </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Save Health Check</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> on the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Review Your Entries</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">my custom health check is stored in my </t>
     </r>
     <r>
@@ -1302,31 +939,6 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">tap </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Add to Calendar</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> after saving a health check with appointment details</t>
-    </r>
-  </si>
-  <si>
     <t>I can sync my appointment with my device calendar and receive reminders</t>
   </si>
   <si>
@@ -1334,12 +946,6 @@
   </si>
   <si>
     <t>logged in user navigating the Cardiovascular Reading screen</t>
-  </si>
-  <si>
-    <t>have the data I enter in the available fields(systolic, diastolic, heart rate, etc.)  autosaved in the system if I tap the 'Back' button or close/remove the app from the background</t>
-  </si>
-  <si>
-    <t>I don't have to re-enter the data in the fields(systolic, diastolic, heart rate, etc.) again</t>
   </si>
   <si>
     <t>logged in user revisiting the Cardiovascular Reading</t>
@@ -1366,34 +972,13 @@
     <t>logged in user navigating the Diabetes Test screen</t>
   </si>
   <si>
-    <t>have the data I enter in the available fields(fasting glucose, random glucose, etc.)  autosaved in the system if I tap the 'Back' button or close/remove the app from the background</t>
-  </si>
-  <si>
-    <t>I don't have to re-enter the data in the fields(fasting glucose, random glucose, etc.) again</t>
-  </si>
-  <si>
     <t>logged in user revisiting the Diabetes Test</t>
   </si>
   <si>
-    <t>see my previously entered data in available fields(fasting glucose, random glucose, etc.) restored along with an affirming notification(toast)</t>
-  </si>
-  <si>
-    <t>1. Previously autosaved available data must be restored automatically when the logged-in user revisits the Diabetes Test screen.
-2. An affirming notification (toast) saying 'Data restored', indicating that the autosaved data has been restored must be displayed after the assessment data is successfully loaded and must not appear if no saved data exists.
-3. The restored values for all available fields must be identical to the most recently autosaved data. 
-4. The restored data and affirming notification must be visible without requiring any additional action from the user.</t>
-  </si>
-  <si>
     <t>Vision Test</t>
   </si>
   <si>
     <t>logged in user navigating the Vision Test screen</t>
-  </si>
-  <si>
-    <t>have the data I enter in the available fields(Right Eye, Left Eye, etc.)  autosaved in the system if I tap the 'Back' button or close/remove the app from the background</t>
-  </si>
-  <si>
-    <t>I don't have to re-enter the data in the fields(Right Eye, Left Eye, etc.) again</t>
   </si>
   <si>
     <t>logged in user revisiting the Vision Test</t>
@@ -1409,15 +994,6 @@
   </si>
   <si>
     <t>logged in user navigating the Dental Health Check screen</t>
-  </si>
-  <si>
-    <t>have the data I enter in the available fields (cavities, fillings, etc), used the toggle switches (Use mouthwash regularly) and the dropdown options (Brushing frequency and flossing frequency) autosaved in the system if I tap the 'Back' button or close/remove the app from the background</t>
-  </si>
-  <si>
-    <t>1. Previously autosaved available data must be restored automatically when the logged-in user revisits the Dental Health Check screen.
-2. An affirming notification (toast) saying 'Data restored', indicating that the autosaved data has been restored must be displayed after the assessment data is successfully loaded and must not appear if no saved data exists.
-3. The restored values for all available fields must be identical to the most recently autosaved data. 
-4. The restored data and affirming notification must be visible without requiring any additional action from the user.</t>
   </si>
   <si>
     <t>I can keep track of my scheduled healthcare appointments.</t>
@@ -3437,46 +3013,235 @@
     </r>
   </si>
   <si>
-    <t>I don't have to re-enter the data in the fields (cavities, fillings, etc), re-toggle the switches (Use mouthwash regularly) or re-use the dropdown options (Brushing frequency and flossing frequency) upon revisiting the Dental Health Check screen</t>
-  </si>
-  <si>
     <t>logged in user revisiting the Dental Health Check screen after tapping back button or closing/removing the app from background</t>
   </si>
   <si>
-    <t>see my previously entered data in the available fields (e.g., cavities, fillings, etc.), the status of the toggle switch (Use Mouthwash Regularly), and the selected dropdown options (Brushing Frequency and Flossing Frequency) restored along with an affirming notification</t>
-  </si>
-  <si>
-    <t>1. All entered dental health field values (e.g., cavities, fillings, etc.) must be automatically saved whenever they are entered or updated.
-2. All toggle switch states (e.g., Use Mouthwash Regularly) must be automatically saved whenever they are changed.
-3. All selected dropdown options (e.g., Brushing Frequency and Flossing Frequency) must be automatically saved whenever they are changed.</t>
-  </si>
-  <si>
-    <t>1. All entered assessment fields(Right Eye, Left Eye, etc.) must be automatically saved whenever the user enters or updates them.</t>
-  </si>
-  <si>
     <t>see my previously entered data in available fields(Right Eye, Left Eye, etc.) restored along with an affirming notification</t>
   </si>
   <si>
     <t>I am informed that my previously entered data progress was restored by the system</t>
   </si>
   <si>
-    <t xml:space="preserve">1. All entered assessment fields(fasting glucose, random glucose, etc.) must be automatically saved whenever the user enters or updates them.
-</t>
-  </si>
-  <si>
-    <t>1. All entered assessment fields(systolic, diastolic, heart rate, etc.) must be automatically saved whenever the user enters or updates them.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1. All entered assessment field values (e.g., K-10 score, DASS-21 Depression, DASS-21 Anxiety) must be automatically saved whenever the user enters or updates them.
-2. All toggle switch states (e.g., Difficulty Falling Asleep, Frequent Night Waking) must be automatically saved whenever they are changed.
-</t>
+    <t>have the data I enter in the available fields(K-10 score, DASS-21 Depression, DASS-21 Anxiety, etc) or used the toggle switches (difficulty falling asleep and frequent night waking) or text field (Notes) autosaved in the system if I tap the 'Back' button or close/remove the app from the background</t>
+  </si>
+  <si>
+    <t>I don't have to re-enter the data in the fields(K-10 score, DASS-21 Depression, DASS-21 Anxiety, etc.) or re-toggle the switches (difficulty falling asleep and frequent night waking) or text field(Notes) again</t>
+  </si>
+  <si>
+    <t>1. All entered assessment field values (e.g., K-10 score, DASS-21 Depression, DASS-21 Anxiety) must be automatically saved whenever the user enters or updates them.
+2. All toggle switch states (e.g., Difficulty Falling Asleep, Frequent Night Waking, Substance Use(alcohol, drugs, etc.), Persistent sadness or depressed mood, Loss of interest in activities, Anxious or worried feelings, Irritability or mood swings, Concentration or memory problems, Fatigue or low energy) must be automatically saved whenever they are changed.
+3. All dropdowns (Exercise frequence. Social Support, Work/Life Stress)must be automatically saved whenever they are changed/added.</t>
+  </si>
+  <si>
+    <t>I don't have to re-enter the data in the fields(systolic, diastolic, heart rate, etc.) , ECG Result status (Normal, Abnormal, Not Done) and Cholesterol Levels fields(Total, LDL, HDL, Triglycerides) again</t>
+  </si>
+  <si>
+    <t>have the data I enter in the available fields(systolic, diastolic, heart rate, etc.), ECG Result status (Normal, Abnormal, Not Done) and Cholesterol Levels fields(Total, LDL, HDL, Triglycerides) autosaved in the system if I tap the 'Back' button or close/remove the app from the background</t>
+  </si>
+  <si>
+    <t>1. All entered Blood Pressure fields(systolic, diastolic, heart rate) must be automatically saved whenever the user enters or updates them.
+2. ECG Result status must be automatically saved whenever the user enters or updates it.
+3. All entered Cholesterol Levels fields(Total, LDL, HDL, Triglycerides) must be automatically saved whenever the user enters or updates them.</t>
+  </si>
+  <si>
+    <t>see my previously entered data in available fields(fasting glucose, random glucose, Post-meal Glucose, HbA1c, Ketones, Systolic BP, Diastolic BP, Weight, Height) restored along with an affirming notification(toast) or text field (Notes)</t>
+  </si>
+  <si>
+    <t>1. Previously autosaved available data must be restored automatically when the logged-in user revisits the Diabetes Test screen.
+2. An affirming notification (toast) saying 'Data restored', indicating that the autosaved data has been restored must be displayed after the assessment data is successfully loaded and must not appear if no saved data exists.
+3. The restored values for all available fields(fasting glucose, random glucose, Post-meal Glucose, HbA1c, Ketones, Systolic BP, Diastolic BP, Weight, Height) restored along with an affirming notification(toast) or text field (Notes) must be identical to the most recently autosaved data. 
+4. The restored data and affirming notification must be visible without requiring any additional action from the user.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">tap </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Other Ailments from the Available Health Checks screen in the Screenings tab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">select a predefined condition or enter a custom condition name on the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Other Ailments screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">enter a </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Test Date on the Other Ailments screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">enter appointment details on the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Other Ailments screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">tap </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Add Field on the Other Ailments screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">tap </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Add Subfield under a custom field</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">review my entered information before saving on the </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Review Your Entries screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">tap </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Save Health Check on the Review Your Entries screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">tap </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Add to Calendar after saving a health check with appointment details</t>
+    </r>
+  </si>
+  <si>
+    <t>have the data I enter in the Visual Acuity dropdowns(Right Eye, Left Eye, Both Eyes), Specialised Vision tests fields (Color Vision Test (Normal, Abnormal) and Peripheral Vision Test(Normal, Abnormal), Eye Pressure fields(Right Eye, Left Eye), Vision Correction dropdown(Do you wear glasses or contacts?), Vision Symptoms (Blurred vision, Eye strain or fatigue, Headaches, Dry eyes, poor night vision, Double vision) and Addition Notes text field autosaved in the system if I tap the 'Back' button or close/remove the app from the background</t>
+  </si>
+  <si>
+    <t>I don't have to re-enter the data again</t>
+  </si>
+  <si>
+    <t>1. All selected values in the Visual Acuity dropdowns (Right Eye, Left Eye, and Both Eyes), Vision Correction dropdown, Specialised Vision Test fields, Eye Pressure fields, Vision Symptoms, and Additional Notes field must be automatically saved whenever they are entered or updated.
+2. All autosaved Vision Test data must be restored when the user returns to the Vision Test screen after tapping the Back button.
+3. All autosaved Vision Test data must be restored when the user reopens the app after it has been closed or removed from the background.
+4. The most recent values entered in all dropdowns, fields, symptom selections, and the Additional Notes field must be displayed when the Vision Test is resumed, without requiring the user to re-enter the information.
+5. Only the autosaved Vision Test data associated with the logged-in user's account must be restored when the Vision Test screen is reopened.</t>
+  </si>
+  <si>
+    <t>see my previously entered data in the available in the Check Date field, Oral Hygiene Habits dropdowns (Brushing Frequency and Flossing Frequency), Use Mouthwash Regularly toggle, Current Dental Condition fields (Cavities, Fillings, Missing Teeth, Crowns and Implants), Gum Health toggles (Bleeding Gums, Swollen Gums, Gum Recession and Gum Sensitivity), Current Symptoms toggles (Toothache, Jaw Pain or TMJ, Bad Breath (Halitosis), Dry Mouth, Teeth Grinding (Bruxism) and Tooth Sensitivity), Professional Care fields (Last Dental Cleaning and Last X-ray), Additional Information dropdowns (Orthodontic Treatment and Smoking Status) and Additional Notes text field) restored along with an affirming notification</t>
+  </si>
+  <si>
+    <t>1. Previously autosaved data in the Check Date field, Oral Hygiene Habits dropdowns (Brushing Frequency and Flossing Frequency), Use Mouthwash Regularly toggle, Current Dental Condition fields (Cavities, Fillings, Missing Teeth, Crowns and Implants), Gum Health toggles, Current Symptoms toggles, Professional Care fields (Last Dental Cleaning and Last X-ray), Additional Information dropdowns (Orthodontic Treatment and Smoking Status), and Additional Notes field must be restored automatically when the logged-in user revisits the Dental Health Check screen after tapping the Back button or reopening the app.
+2. An affirming notification (toast) indicating that the previously entered Dental Health Check data has been restored must be displayed after the data is successfully loaded.
+3. The restored values for all fields, dropdowns, toggle switches, date fields, and the Additional Notes field must be identical to the most recently autosaved data.
+4. The restored data and affirming notification must be visible without requiring any additional action from the user.
+5. The affirming notification must be displayed only when previously autosaved Dental Health Check data has been successfully restored and must not appear if no saved data exists.</t>
+  </si>
+  <si>
+    <t>Have the data I enter in the Check Date field, Oral Hygiene Habits dropdowns (Brushing Frequency and Flossing Frequency), Use Mouthwash Regularly toggle, Current Dental Condition fields (Cavities, Fillings, Missing Teeth, Crowns and Implants), Gum Health toggles (Bleeding Gums, Swollen Gums, Gum Recession and Gum Sensitivity), Current Symptoms toggles (Toothache, Jaw Pain or TMJ, Bad Breath (Halitosis), Dry Mouth, Teeth Grinding (Bruxism) and Tooth Sensitivity), Professional Care fields (Last Dental Cleaning and Last X-ray), Additional Information dropdowns (Orthodontic Treatment and Smoking Status), and Additional Notes text field automatically saved in the system if I tap the 'Back' button or close/remove the app from the background</t>
+  </si>
+  <si>
+    <t>I don't have to re-enter the previously entered data when I revisit the Dental Health Check screen.</t>
+  </si>
+  <si>
+    <t>1. All selected values in the Check Date field, Oral Hygiene Habits dropdowns (Brushing Frequency and Flossing Frequency), Use Mouthwash Regularly toggle, Current Dental Condition fields (Cavities, Fillings, Missing Teeth, Crowns and Implants), Gum Health toggles (Bleeding Gums, Swollen Gums, Gum Recession and Gum Sensitivity), Current Symptoms toggles (Toothache, Jaw Pain or TMJ, Bad Breath (Halitosis), Dry Mouth, Teeth Grinding (Bruxism) and Tooth Sensitivity), Professional Care fields (Last Dental Cleaning and Last X-ray), Additional Information dropdowns (Orthodontic Treatment and Smoking Status), and Additional Notes field must be automatically saved whenever they are entered, selected, or updated.
+2. All autosaved Dental Health Check data must be restored when the user returns to the Dental Health Check screen after tapping the Back button.
+3. All autosaved Dental Health Check data must be restored when the user reopens the app after it has been closed or removed from the background.
+4. The most recent values entered in all date fields, dropdowns, numeric fields, toggle switches, and the Additional Notes field must be displayed when the Dental Health Check is resumed, without requiring the user to re-enter the information.
+5. Only the autosaved Dental Health Check data associated with the logged-in user's account must be restored when the Dental Health Check screen is reopened.</t>
+  </si>
+  <si>
+    <t>Have the data I enter in the Test Date field, Blood Glucose Levels fields (Fasting Glucose, Random Glucose and Post-Meal Glucose), Long-term Indicators fields (HbA1c and Ketones), Additional Measurements fields (Systolic Blood Pressure, Diastolic Blood Pressure, Weight and Height), and Additional Notes text field automatically saved in the system if I tap the 'Back' button or close/remove the app from the background</t>
+  </si>
+  <si>
+    <t>I don't have to re-enter the previously entered data when I revisit the Diabetes Test screen.</t>
+  </si>
+  <si>
+    <t>1. All selected values in the Test Date field, Blood Glucose Levels fields (Fasting Glucose, Random Glucose and Post-Meal Glucose), Long-term Indicators fields (HbA1c and Ketones), Additional Measurements fields (Systolic Blood Pressure, Diastolic Blood Pressure, Weight and Height), and Additional Notes field must be automatically saved whenever they are entered or updated.
+2. All autosaved Diabetes Test data must be restored when the user returns to the Diabetes Test screen after tapping the Back button.
+3. All autosaved Diabetes Test data must be restored when the user reopens the app after it has been closed or removed from the background.
+4. The most recent values entered in all date fields, measurement fields, and the Additional Notes field must be displayed when the Diabetes Test is resumed, without requiring the user to re-enter the information.
+5. Only the autosaved Diabetes Test data associated with the logged-in user's account must be restored when the Diabetes Test screen is reopened.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="14" x14ac:knownFonts="1">
+  <fonts count="15" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -3518,12 +3283,6 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="10"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
@@ -3572,6 +3331,17 @@
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
     </font>
   </fonts>
   <fills count="18">
@@ -3764,7 +3534,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="83">
+  <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3784,233 +3554,224 @@
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="15" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="2" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="3" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="13" borderId="4" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="14" borderId="1" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -4228,7 +3989,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L91"/>
+  <dimension ref="A1:L92"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.88671875" style="2" bestFit="1" customWidth="1"/>
@@ -4245,34 +4006,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="53" t="s">
+      <c r="A1" s="15" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="53" t="s">
+      <c r="B1" s="15" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="58" t="s">
+      <c r="C1" s="15" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="58" t="s">
+      <c r="D1" s="15" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="59"/>
-      <c r="F1" s="59"/>
-      <c r="G1" s="58" t="s">
+      <c r="E1" s="17"/>
+      <c r="F1" s="17"/>
+      <c r="G1" s="16" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="53" t="s">
+      <c r="H1" s="15" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="53" t="s">
+      <c r="I1" s="15" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="54"/>
-      <c r="B2" s="54"/>
-      <c r="C2" s="59"/>
+      <c r="A2" s="17"/>
+      <c r="B2" s="17"/>
+      <c r="C2" s="17"/>
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
@@ -4282,1895 +4043,1906 @@
       <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="58"/>
-      <c r="H2" s="54"/>
-      <c r="I2" s="54"/>
+      <c r="G2" s="16"/>
+      <c r="H2" s="17"/>
+      <c r="I2" s="17"/>
     </row>
     <row r="3" spans="1:9" s="5" customFormat="1" ht="156" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="60">
+      <c r="A3" s="18">
         <v>1</v>
       </c>
-      <c r="B3" s="60" t="s">
+      <c r="B3" s="18" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="30">
+      <c r="C3" s="19">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D3" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="E3" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="F3" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="G3" s="20" t="s">
+        <v>177</v>
+      </c>
+      <c r="H3" s="19" t="s">
+        <v>11</v>
+      </c>
+      <c r="I3" s="19" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" s="6" customFormat="1" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="18"/>
+      <c r="B4" s="18"/>
+      <c r="C4" s="19">
+        <v>1.2</v>
+      </c>
+      <c r="D4" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="E4" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="F4" s="19" t="s">
+        <v>159</v>
+      </c>
+      <c r="G4" s="20" t="s">
+        <v>168</v>
+      </c>
+      <c r="H4" s="19"/>
+      <c r="I4" s="19"/>
+    </row>
+    <row r="5" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
+      <c r="A5" s="18"/>
+      <c r="B5" s="18"/>
+      <c r="C5" s="19">
+        <v>1.3</v>
+      </c>
+      <c r="D5" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="E5" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="F5" s="19" t="s">
+        <v>160</v>
+      </c>
+      <c r="G5" s="20" t="s">
+        <v>169</v>
+      </c>
+      <c r="H5" s="19"/>
+      <c r="I5" s="19"/>
+    </row>
+    <row r="6" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
+      <c r="A6" s="18"/>
+      <c r="B6" s="18"/>
+      <c r="C6" s="19">
+        <v>1.4</v>
+      </c>
+      <c r="D6" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="E6" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="F6" s="19" t="s">
+        <v>161</v>
+      </c>
+      <c r="G6" s="20" t="s">
+        <v>167</v>
+      </c>
+      <c r="H6" s="19"/>
+      <c r="I6" s="19"/>
+    </row>
+    <row r="7" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A7" s="18"/>
+      <c r="B7" s="18"/>
+      <c r="C7" s="19">
+        <v>1.5</v>
+      </c>
+      <c r="D7" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="E7" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="F7" s="19" t="s">
+        <v>162</v>
+      </c>
+      <c r="G7" s="20" t="s">
+        <v>175</v>
+      </c>
+      <c r="H7" s="19"/>
+      <c r="I7" s="19"/>
+    </row>
+    <row r="8" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="21">
+        <v>5</v>
+      </c>
+      <c r="B8" s="21" t="s">
+        <v>13</v>
+      </c>
+      <c r="C8" s="22">
+        <v>5.0999999999999996</v>
+      </c>
+      <c r="D8" s="22" t="s">
+        <v>14</v>
+      </c>
+      <c r="E8" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F8" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G8" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="H8" s="24" t="s">
+        <v>18</v>
+      </c>
+      <c r="I8" s="22" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A9" s="25"/>
+      <c r="B9" s="25"/>
+      <c r="C9" s="22">
+        <v>5.2</v>
+      </c>
+      <c r="D9" s="22" t="s">
+        <v>20</v>
+      </c>
+      <c r="E9" s="22" t="s">
+        <v>15</v>
+      </c>
+      <c r="F9" s="22" t="s">
+        <v>16</v>
+      </c>
+      <c r="G9" s="23" t="s">
+        <v>17</v>
+      </c>
+      <c r="H9" s="24"/>
+      <c r="I9" s="22"/>
+    </row>
+    <row r="10" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A10" s="25"/>
+      <c r="B10" s="25"/>
+      <c r="C10" s="22">
+        <v>5.3</v>
+      </c>
+      <c r="D10" s="22" t="s">
+        <v>21</v>
+      </c>
+      <c r="E10" s="22" t="s">
+        <v>22</v>
+      </c>
+      <c r="F10" s="22" t="s">
+        <v>23</v>
+      </c>
+      <c r="G10" s="23" t="s">
+        <v>24</v>
+      </c>
+      <c r="H10" s="24"/>
+      <c r="I10" s="22"/>
+    </row>
+    <row r="11" spans="1:9" s="14" customFormat="1" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A11" s="25"/>
+      <c r="B11" s="25"/>
+      <c r="C11" s="26">
+        <v>5.4</v>
+      </c>
+      <c r="D11" s="26" t="s">
+        <v>181</v>
+      </c>
+      <c r="E11" s="26" t="s">
+        <v>184</v>
+      </c>
+      <c r="F11" s="26" t="s">
+        <v>183</v>
+      </c>
+      <c r="G11" s="27" t="s">
+        <v>185</v>
+      </c>
+      <c r="H11" s="28"/>
+      <c r="I11" s="26"/>
+    </row>
+    <row r="12" spans="1:9" s="14" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A12" s="29"/>
+      <c r="B12" s="29"/>
+      <c r="C12" s="26">
+        <v>5.5</v>
+      </c>
+      <c r="D12" s="26" t="s">
+        <v>178</v>
+      </c>
+      <c r="E12" s="26" t="s">
+        <v>182</v>
+      </c>
+      <c r="F12" s="26" t="s">
+        <v>180</v>
+      </c>
+      <c r="G12" s="27" t="s">
+        <v>179</v>
+      </c>
+      <c r="H12" s="28"/>
+      <c r="I12" s="26"/>
+    </row>
+    <row r="13" spans="1:9" s="14" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="30">
+        <v>6</v>
+      </c>
+      <c r="B13" s="30" t="s">
+        <v>25</v>
+      </c>
+      <c r="C13" s="26">
+        <v>6.1</v>
+      </c>
+      <c r="D13" s="26" t="s">
+        <v>26</v>
+      </c>
+      <c r="E13" s="26" t="s">
+        <v>27</v>
+      </c>
+      <c r="F13" s="26" t="s">
+        <v>28</v>
+      </c>
+      <c r="G13" s="27" t="s">
+        <v>29</v>
+      </c>
+      <c r="H13" s="28" t="s">
+        <v>30</v>
+      </c>
+      <c r="I13" s="26" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="14" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
+      <c r="A14" s="31"/>
+      <c r="B14" s="31"/>
+      <c r="C14" s="32">
+        <v>6.2</v>
+      </c>
+      <c r="D14" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="E14" s="32" t="s">
         <v>187</v>
       </c>
-      <c r="E3" s="29" t="s">
+      <c r="F14" s="32" t="s">
         <v>186</v>
       </c>
-      <c r="F3" s="29" t="s">
+      <c r="G14" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="H14" s="34"/>
+      <c r="I14" s="32"/>
+    </row>
+    <row r="15" spans="1:9" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="31"/>
+      <c r="B15" s="31"/>
+      <c r="C15" s="32">
+        <v>6.3</v>
+      </c>
+      <c r="D15" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="E15" s="32" t="s">
+        <v>32</v>
+      </c>
+      <c r="F15" s="32" t="s">
+        <v>33</v>
+      </c>
+      <c r="G15" s="33" t="s">
+        <v>34</v>
+      </c>
+      <c r="H15" s="34"/>
+      <c r="I15" s="32"/>
+    </row>
+    <row r="16" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A16" s="31"/>
+      <c r="B16" s="35"/>
+      <c r="C16" s="36">
+        <v>6.4</v>
+      </c>
+      <c r="D16" s="32" t="s">
+        <v>26</v>
+      </c>
+      <c r="E16" s="32" t="s">
+        <v>35</v>
+      </c>
+      <c r="F16" s="32" t="s">
+        <v>36</v>
+      </c>
+      <c r="G16" s="33" t="s">
+        <v>37</v>
+      </c>
+      <c r="H16" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="I16" s="32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="17" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
+      <c r="A17" s="37">
+        <v>7</v>
+      </c>
+      <c r="B17" s="30" t="s">
+        <v>38</v>
+      </c>
+      <c r="C17" s="32">
+        <v>7.1</v>
+      </c>
+      <c r="D17" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E17" s="32" t="s">
+        <v>40</v>
+      </c>
+      <c r="F17" s="32" t="s">
+        <v>41</v>
+      </c>
+      <c r="G17" s="33" t="s">
+        <v>42</v>
+      </c>
+      <c r="H17" s="34" t="s">
+        <v>30</v>
+      </c>
+      <c r="I17" s="32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A18" s="38"/>
+      <c r="B18" s="31"/>
+      <c r="C18" s="32">
+        <v>7.2</v>
+      </c>
+      <c r="D18" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E18" s="32" t="s">
+        <v>43</v>
+      </c>
+      <c r="F18" s="32" t="s">
+        <v>44</v>
+      </c>
+      <c r="G18" s="33" t="s">
+        <v>45</v>
+      </c>
+      <c r="H18" s="34"/>
+      <c r="I18" s="32" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" s="6" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A19" s="38"/>
+      <c r="B19" s="31"/>
+      <c r="C19" s="32">
+        <v>7.3</v>
+      </c>
+      <c r="D19" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E19" s="32" t="s">
+        <v>163</v>
+      </c>
+      <c r="F19" s="32" t="s">
+        <v>46</v>
+      </c>
+      <c r="G19" s="33" t="s">
+        <v>47</v>
+      </c>
+      <c r="H19" s="34"/>
+      <c r="I19" s="32"/>
+    </row>
+    <row r="20" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A20" s="39"/>
+      <c r="B20" s="35"/>
+      <c r="C20" s="32">
+        <v>7.4</v>
+      </c>
+      <c r="D20" s="32" t="s">
+        <v>39</v>
+      </c>
+      <c r="E20" s="32" t="s">
+        <v>164</v>
+      </c>
+      <c r="F20" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="G20" s="33" t="s">
+        <v>49</v>
+      </c>
+      <c r="H20" s="34"/>
+      <c r="I20" s="32"/>
+    </row>
+    <row r="21" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A21" s="40">
+        <v>8</v>
+      </c>
+      <c r="B21" s="40" t="s">
+        <v>50</v>
+      </c>
+      <c r="C21" s="41">
+        <v>9.1999999999999993</v>
+      </c>
+      <c r="D21" s="41" t="s">
+        <v>51</v>
+      </c>
+      <c r="E21" s="41" t="s">
+        <v>52</v>
+      </c>
+      <c r="F21" s="41" t="s">
+        <v>53</v>
+      </c>
+      <c r="G21" s="42" t="s">
+        <v>54</v>
+      </c>
+      <c r="H21" s="41"/>
+      <c r="I21" s="41" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="43"/>
+      <c r="B22" s="43"/>
+      <c r="C22" s="41">
+        <v>9.3000000000000007</v>
+      </c>
+      <c r="D22" s="41" t="s">
+        <v>56</v>
+      </c>
+      <c r="E22" s="41" t="s">
+        <v>57</v>
+      </c>
+      <c r="F22" s="41" t="s">
+        <v>58</v>
+      </c>
+      <c r="G22" s="42" t="s">
+        <v>59</v>
+      </c>
+      <c r="H22" s="41"/>
+      <c r="I22" s="41" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="23" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A23" s="44"/>
+      <c r="B23" s="44"/>
+      <c r="C23" s="41">
+        <v>9.4</v>
+      </c>
+      <c r="D23" s="41" t="s">
+        <v>60</v>
+      </c>
+      <c r="E23" s="41" t="s">
+        <v>61</v>
+      </c>
+      <c r="F23" s="41" t="s">
+        <v>62</v>
+      </c>
+      <c r="G23" s="42" t="s">
+        <v>63</v>
+      </c>
+      <c r="H23" s="41"/>
+      <c r="I23" s="41" t="s">
+        <v>55</v>
+      </c>
+    </row>
+    <row r="24" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A24" s="45">
+        <v>12</v>
+      </c>
+      <c r="B24" s="45" t="s">
+        <v>64</v>
+      </c>
+      <c r="C24" s="46">
+        <v>12.1</v>
+      </c>
+      <c r="D24" s="46" t="s">
+        <v>65</v>
+      </c>
+      <c r="E24" s="46" t="s">
+        <v>66</v>
+      </c>
+      <c r="F24" s="46" t="s">
+        <v>67</v>
+      </c>
+      <c r="G24" s="47" t="s">
+        <v>68</v>
+      </c>
+      <c r="H24" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="I24" s="46" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="25" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A25" s="45"/>
+      <c r="B25" s="45"/>
+      <c r="C25" s="46">
+        <v>12.2</v>
+      </c>
+      <c r="D25" s="46" t="s">
+        <v>65</v>
+      </c>
+      <c r="E25" s="46" t="s">
+        <v>71</v>
+      </c>
+      <c r="F25" s="46" t="s">
+        <v>72</v>
+      </c>
+      <c r="G25" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="H25" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="I25" s="46" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="26" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A26" s="45"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="46">
+        <v>12.3</v>
+      </c>
+      <c r="D26" s="46" t="s">
+        <v>65</v>
+      </c>
+      <c r="E26" s="46" t="s">
+        <v>74</v>
+      </c>
+      <c r="F26" s="46" t="s">
+        <v>75</v>
+      </c>
+      <c r="G26" s="47" t="s">
+        <v>76</v>
+      </c>
+      <c r="H26" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="I26" s="46" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="27" spans="1:9" s="6" customFormat="1" ht="123.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="45"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="46">
+        <v>12.4</v>
+      </c>
+      <c r="D27" s="46" t="s">
+        <v>65</v>
+      </c>
+      <c r="E27" s="46" t="s">
+        <v>283</v>
+      </c>
+      <c r="F27" s="46" t="s">
+        <v>284</v>
+      </c>
+      <c r="G27" s="47" t="s">
+        <v>285</v>
+      </c>
+      <c r="H27" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="I27" s="46" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="28" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="45"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="46">
+        <v>12.5</v>
+      </c>
+      <c r="D28" s="46" t="s">
+        <v>77</v>
+      </c>
+      <c r="E28" s="46" t="s">
+        <v>78</v>
+      </c>
+      <c r="F28" s="46" t="s">
+        <v>282</v>
+      </c>
+      <c r="G28" s="47" t="s">
+        <v>79</v>
+      </c>
+      <c r="H28" s="46" t="s">
+        <v>69</v>
+      </c>
+      <c r="I28" s="46" t="s">
+        <v>70</v>
+      </c>
+    </row>
+    <row r="29" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A29" s="48"/>
+      <c r="B29" s="48"/>
+      <c r="C29" s="19">
+        <v>12.6</v>
+      </c>
+      <c r="D29" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="E29" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F29" s="19"/>
+      <c r="G29" s="20"/>
+      <c r="H29" s="49"/>
+      <c r="I29" s="50"/>
+    </row>
+    <row r="30" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A30" s="51">
+        <v>14</v>
+      </c>
+      <c r="B30" s="51" t="s">
+        <v>80</v>
+      </c>
+      <c r="C30" s="52">
+        <v>14.1</v>
+      </c>
+      <c r="D30" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="E30" s="53" t="s">
+        <v>253</v>
+      </c>
+      <c r="F30" s="53" t="s">
+        <v>219</v>
+      </c>
+      <c r="G30" s="54" t="s">
+        <v>269</v>
+      </c>
+      <c r="H30" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="I30" s="52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A31" s="51"/>
+      <c r="B31" s="51"/>
+      <c r="C31" s="52">
+        <v>14.2</v>
+      </c>
+      <c r="D31" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="E31" s="53" t="s">
+        <v>254</v>
+      </c>
+      <c r="F31" s="53" t="s">
+        <v>255</v>
+      </c>
+      <c r="G31" s="54" t="s">
+        <v>270</v>
+      </c>
+      <c r="H31" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="I31" s="52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A32" s="51"/>
+      <c r="B32" s="51"/>
+      <c r="C32" s="52">
+        <v>14.3</v>
+      </c>
+      <c r="D32" s="53" t="s">
+        <v>224</v>
+      </c>
+      <c r="E32" s="53" t="s">
+        <v>256</v>
+      </c>
+      <c r="F32" s="53" t="s">
+        <v>257</v>
+      </c>
+      <c r="G32" s="54" t="s">
+        <v>271</v>
+      </c>
+      <c r="H32" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="I32" s="52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="33" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A33" s="51"/>
+      <c r="B33" s="51"/>
+      <c r="C33" s="52">
+        <v>14.4</v>
+      </c>
+      <c r="D33" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="E33" s="53" t="s">
+        <v>258</v>
+      </c>
+      <c r="F33" s="53" t="s">
+        <v>229</v>
+      </c>
+      <c r="G33" s="54" t="s">
+        <v>272</v>
+      </c>
+      <c r="H33" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="I33" s="52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="34" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A34" s="51"/>
+      <c r="B34" s="51"/>
+      <c r="C34" s="52">
+        <v>14.5</v>
+      </c>
+      <c r="D34" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="E34" s="53" t="s">
+        <v>259</v>
+      </c>
+      <c r="F34" s="53" t="s">
+        <v>232</v>
+      </c>
+      <c r="G34" s="54" t="s">
+        <v>273</v>
+      </c>
+      <c r="H34" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="I34" s="52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="35" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A35" s="51"/>
+      <c r="B35" s="51"/>
+      <c r="C35" s="52">
+        <v>14.6</v>
+      </c>
+      <c r="D35" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="E35" s="53" t="s">
+        <v>260</v>
+      </c>
+      <c r="F35" s="53" t="s">
+        <v>261</v>
+      </c>
+      <c r="G35" s="54" t="s">
+        <v>274</v>
+      </c>
+      <c r="H35" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="I35" s="52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="36" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A36" s="51"/>
+      <c r="B36" s="51"/>
+      <c r="C36" s="52">
+        <v>14.7</v>
+      </c>
+      <c r="D36" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="E36" s="53" t="s">
+        <v>262</v>
+      </c>
+      <c r="F36" s="53" t="s">
+        <v>263</v>
+      </c>
+      <c r="G36" s="54" t="s">
+        <v>275</v>
+      </c>
+      <c r="H36" s="52" t="s">
+        <v>82</v>
+      </c>
+      <c r="I36" s="52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="37" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A37" s="51"/>
+      <c r="B37" s="51"/>
+      <c r="C37" s="52">
+        <v>14.8</v>
+      </c>
+      <c r="D37" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="E37" s="53" t="s">
+        <v>264</v>
+      </c>
+      <c r="F37" s="53" t="s">
+        <v>265</v>
+      </c>
+      <c r="G37" s="54" t="s">
+        <v>276</v>
+      </c>
+      <c r="H37" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="I37" s="52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="38" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A38" s="51"/>
+      <c r="B38" s="51"/>
+      <c r="C38" s="52">
+        <v>14.9</v>
+      </c>
+      <c r="D38" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="E38" s="53" t="s">
+        <v>266</v>
+      </c>
+      <c r="F38" s="53" t="s">
+        <v>244</v>
+      </c>
+      <c r="G38" s="54" t="s">
+        <v>277</v>
+      </c>
+      <c r="H38" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="I38" s="52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="39" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A39" s="51"/>
+      <c r="B39" s="51"/>
+      <c r="C39" s="52">
+        <v>14.1</v>
+      </c>
+      <c r="D39" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="E39" s="53" t="s">
+        <v>267</v>
+      </c>
+      <c r="F39" s="53" t="s">
+        <v>248</v>
+      </c>
+      <c r="G39" s="54" t="s">
+        <v>278</v>
+      </c>
+      <c r="H39" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="I39" s="52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="40" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A40" s="51"/>
+      <c r="B40" s="51"/>
+      <c r="C40" s="52">
+        <v>14.11</v>
+      </c>
+      <c r="D40" s="53" t="s">
+        <v>133</v>
+      </c>
+      <c r="E40" s="53" t="s">
+        <v>268</v>
+      </c>
+      <c r="F40" s="53" t="s">
+        <v>251</v>
+      </c>
+      <c r="G40" s="54" t="s">
+        <v>279</v>
+      </c>
+      <c r="H40" s="52" t="s">
+        <v>84</v>
+      </c>
+      <c r="I40" s="52" t="s">
+        <v>83</v>
+      </c>
+    </row>
+    <row r="41" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A41" s="55">
+        <v>15</v>
+      </c>
+      <c r="B41" s="55" t="s">
+        <v>85</v>
+      </c>
+      <c r="C41" s="56">
+        <v>15.1</v>
+      </c>
+      <c r="D41" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="E41" s="56" t="s">
+        <v>87</v>
+      </c>
+      <c r="F41" s="56" t="s">
+        <v>88</v>
+      </c>
+      <c r="G41" s="57" t="s">
+        <v>189</v>
+      </c>
+      <c r="H41" s="56" t="s">
+        <v>123</v>
+      </c>
+      <c r="I41" s="56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="17"/>
+      <c r="B42" s="17"/>
+      <c r="C42" s="56">
+        <v>15.2</v>
+      </c>
+      <c r="D42" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="E42" s="56" t="s">
+        <v>89</v>
+      </c>
+      <c r="F42" s="56" t="s">
+        <v>90</v>
+      </c>
+      <c r="G42" s="57" t="s">
+        <v>190</v>
+      </c>
+      <c r="H42" s="56" t="s">
+        <v>107</v>
+      </c>
+      <c r="I42" s="56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A43" s="17"/>
+      <c r="B43" s="17"/>
+      <c r="C43" s="56">
+        <v>15.3</v>
+      </c>
+      <c r="D43" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="E43" s="56" t="s">
+        <v>91</v>
+      </c>
+      <c r="F43" s="56" t="s">
+        <v>92</v>
+      </c>
+      <c r="G43" s="57" t="s">
+        <v>191</v>
+      </c>
+      <c r="H43" s="56" t="s">
+        <v>107</v>
+      </c>
+      <c r="I43" s="56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A44" s="17"/>
+      <c r="B44" s="17"/>
+      <c r="C44" s="56">
+        <v>15.4</v>
+      </c>
+      <c r="D44" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="E44" s="56" t="s">
+        <v>93</v>
+      </c>
+      <c r="F44" s="56" t="s">
+        <v>94</v>
+      </c>
+      <c r="G44" s="57" t="s">
+        <v>192</v>
+      </c>
+      <c r="H44" s="56" t="s">
+        <v>107</v>
+      </c>
+      <c r="I44" s="56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="45" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A45" s="17"/>
+      <c r="B45" s="17"/>
+      <c r="C45" s="56">
+        <v>15.5</v>
+      </c>
+      <c r="D45" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="E45" s="56" t="s">
+        <v>95</v>
+      </c>
+      <c r="F45" s="56" t="s">
+        <v>96</v>
+      </c>
+      <c r="G45" s="57" t="s">
+        <v>193</v>
+      </c>
+      <c r="H45" s="56" t="s">
+        <v>107</v>
+      </c>
+      <c r="I45" s="56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="46" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A46" s="17"/>
+      <c r="B46" s="17"/>
+      <c r="C46" s="56">
+        <v>15.6</v>
+      </c>
+      <c r="D46" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="E46" s="56" t="s">
+        <v>97</v>
+      </c>
+      <c r="F46" s="56" t="s">
+        <v>98</v>
+      </c>
+      <c r="G46" s="57" t="s">
+        <v>194</v>
+      </c>
+      <c r="H46" s="56" t="s">
+        <v>107</v>
+      </c>
+      <c r="I46" s="56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="47" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A47" s="17"/>
+      <c r="B47" s="17"/>
+      <c r="C47" s="56">
+        <v>15.7</v>
+      </c>
+      <c r="D47" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="E47" s="56" t="s">
+        <v>99</v>
+      </c>
+      <c r="F47" s="56" t="s">
+        <v>100</v>
+      </c>
+      <c r="G47" s="57" t="s">
         <v>195</v>
       </c>
-      <c r="G3" s="30" t="s">
+      <c r="H47" s="56" t="s">
+        <v>107</v>
+      </c>
+      <c r="I47" s="56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="48" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A48" s="17"/>
+      <c r="B48" s="17"/>
+      <c r="C48" s="56">
+        <v>15.8</v>
+      </c>
+      <c r="D48" s="56" t="s">
+        <v>86</v>
+      </c>
+      <c r="E48" s="56" t="s">
+        <v>101</v>
+      </c>
+      <c r="F48" s="56" t="s">
+        <v>102</v>
+      </c>
+      <c r="G48" s="57" t="s">
+        <v>196</v>
+      </c>
+      <c r="H48" s="56" t="s">
+        <v>107</v>
+      </c>
+      <c r="I48" s="56" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="49" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A49" s="58">
+        <v>16</v>
+      </c>
+      <c r="B49" s="58" t="s">
+        <v>103</v>
+      </c>
+      <c r="C49" s="59">
+        <v>16.100000000000001</v>
+      </c>
+      <c r="D49" s="60" t="s">
+        <v>104</v>
+      </c>
+      <c r="E49" s="60" t="s">
+        <v>105</v>
+      </c>
+      <c r="F49" s="60" t="s">
+        <v>106</v>
+      </c>
+      <c r="G49" s="61" t="s">
+        <v>197</v>
+      </c>
+      <c r="H49" s="60" t="s">
+        <v>107</v>
+      </c>
+      <c r="I49" s="60" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A50" s="58"/>
+      <c r="B50" s="58"/>
+      <c r="C50" s="59">
+        <v>16.2</v>
+      </c>
+      <c r="D50" s="60" t="s">
+        <v>104</v>
+      </c>
+      <c r="E50" s="60" t="s">
+        <v>109</v>
+      </c>
+      <c r="F50" s="60" t="s">
+        <v>110</v>
+      </c>
+      <c r="G50" s="61" t="s">
         <v>198</v>
       </c>
-      <c r="H3" s="29" t="s">
-        <v>11</v>
-      </c>
-      <c r="I3" s="29" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="4" spans="1:9" s="6" customFormat="1" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="60"/>
-      <c r="B4" s="60"/>
-      <c r="C4" s="30">
-        <v>1.2</v>
-      </c>
-      <c r="D4" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="E4" s="29" t="s">
-        <v>191</v>
-      </c>
-      <c r="F4" s="29" t="s">
-        <v>180</v>
-      </c>
-      <c r="G4" s="30" t="s">
-        <v>189</v>
-      </c>
-      <c r="H4" s="29"/>
-      <c r="I4" s="29"/>
-    </row>
-    <row r="5" spans="1:9" s="6" customFormat="1" ht="138" x14ac:dyDescent="0.3">
-      <c r="A5" s="60"/>
-      <c r="B5" s="60"/>
-      <c r="C5" s="30">
-        <v>1.3</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="E5" s="29" t="s">
-        <v>192</v>
-      </c>
-      <c r="F5" s="29" t="s">
-        <v>181</v>
-      </c>
-      <c r="G5" s="30" t="s">
-        <v>190</v>
-      </c>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-    </row>
-    <row r="6" spans="1:9" s="6" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A6" s="60"/>
-      <c r="B6" s="60"/>
-      <c r="C6" s="30">
-        <v>1.4</v>
-      </c>
-      <c r="D6" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="E6" s="29" t="s">
-        <v>193</v>
-      </c>
-      <c r="F6" s="29" t="s">
-        <v>182</v>
-      </c>
-      <c r="G6" s="30" t="s">
-        <v>188</v>
-      </c>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-    </row>
-    <row r="7" spans="1:9" s="6" customFormat="1" ht="151.80000000000001" x14ac:dyDescent="0.3">
-      <c r="A7" s="60"/>
-      <c r="B7" s="60"/>
-      <c r="C7" s="30">
-        <v>1.5</v>
-      </c>
-      <c r="D7" s="29" t="s">
-        <v>197</v>
-      </c>
-      <c r="E7" s="29" t="s">
-        <v>194</v>
-      </c>
-      <c r="F7" s="29" t="s">
-        <v>183</v>
-      </c>
-      <c r="G7" s="30" t="s">
-        <v>196</v>
-      </c>
-      <c r="H7" s="29"/>
-      <c r="I7" s="29"/>
-    </row>
-    <row r="8" spans="1:9" s="6" customFormat="1" ht="110.4" x14ac:dyDescent="0.3">
-      <c r="A8" s="55">
-        <v>5</v>
-      </c>
-      <c r="B8" s="55" t="s">
-        <v>13</v>
-      </c>
-      <c r="C8" s="8">
-        <v>5.0999999999999996</v>
-      </c>
-      <c r="D8" s="7" t="s">
-        <v>14</v>
-      </c>
-      <c r="E8" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F8" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G8" s="8" t="s">
+      <c r="H50" s="60" t="s">
+        <v>107</v>
+      </c>
+      <c r="I50" s="60" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A51" s="58"/>
+      <c r="B51" s="58"/>
+      <c r="C51" s="59">
+        <v>16.3</v>
+      </c>
+      <c r="D51" s="60" t="s">
+        <v>104</v>
+      </c>
+      <c r="E51" s="60" t="s">
+        <v>111</v>
+      </c>
+      <c r="F51" s="60" t="s">
+        <v>112</v>
+      </c>
+      <c r="G51" s="61" t="s">
+        <v>199</v>
+      </c>
+      <c r="H51" s="60" t="s">
+        <v>107</v>
+      </c>
+      <c r="I51" s="60" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A52" s="58"/>
+      <c r="B52" s="58"/>
+      <c r="C52" s="59">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="D52" s="60" t="s">
+        <v>104</v>
+      </c>
+      <c r="E52" s="60" t="s">
+        <v>113</v>
+      </c>
+      <c r="F52" s="60" t="s">
+        <v>114</v>
+      </c>
+      <c r="G52" s="61" t="s">
+        <v>200</v>
+      </c>
+      <c r="H52" s="60" t="s">
+        <v>107</v>
+      </c>
+      <c r="I52" s="60" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="53" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A53" s="58"/>
+      <c r="B53" s="58"/>
+      <c r="C53" s="59">
+        <v>16.5</v>
+      </c>
+      <c r="D53" s="60" t="s">
+        <v>104</v>
+      </c>
+      <c r="E53" s="60" t="s">
+        <v>115</v>
+      </c>
+      <c r="F53" s="60" t="s">
+        <v>116</v>
+      </c>
+      <c r="G53" s="61" t="s">
+        <v>201</v>
+      </c>
+      <c r="H53" s="60" t="s">
+        <v>107</v>
+      </c>
+      <c r="I53" s="60" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="54" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A54" s="17"/>
+      <c r="B54" s="17"/>
+      <c r="C54" s="59">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="D54" s="60" t="s">
+        <v>104</v>
+      </c>
+      <c r="E54" s="60" t="s">
+        <v>117</v>
+      </c>
+      <c r="F54" s="60" t="s">
+        <v>118</v>
+      </c>
+      <c r="G54" s="61" t="s">
+        <v>202</v>
+      </c>
+      <c r="H54" s="60" t="s">
+        <v>107</v>
+      </c>
+      <c r="I54" s="60" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="55" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A55" s="62">
         <v>17</v>
       </c>
-      <c r="H8" s="9" t="s">
+      <c r="B55" s="63" t="s">
+        <v>119</v>
+      </c>
+      <c r="C55" s="64">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="D55" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="E55" s="64" t="s">
+        <v>121</v>
+      </c>
+      <c r="F55" s="64" t="s">
+        <v>122</v>
+      </c>
+      <c r="G55" s="65" t="s">
+        <v>203</v>
+      </c>
+      <c r="H55" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="I55" s="64" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A56" s="66"/>
+      <c r="B56" s="63"/>
+      <c r="C56" s="64">
+        <v>17.2</v>
+      </c>
+      <c r="D56" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="E56" s="64" t="s">
+        <v>124</v>
+      </c>
+      <c r="F56" s="64" t="s">
+        <v>125</v>
+      </c>
+      <c r="G56" s="65" t="s">
+        <v>204</v>
+      </c>
+      <c r="H56" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="I56" s="64" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A57" s="66"/>
+      <c r="B57" s="63"/>
+      <c r="C57" s="64">
+        <v>17.3</v>
+      </c>
+      <c r="D57" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="E57" s="64" t="s">
+        <v>126</v>
+      </c>
+      <c r="F57" s="64" t="s">
+        <v>127</v>
+      </c>
+      <c r="G57" s="65" t="s">
+        <v>205</v>
+      </c>
+      <c r="H57" s="64" t="s">
+        <v>107</v>
+      </c>
+      <c r="I57" s="64" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A58" s="66"/>
+      <c r="B58" s="63"/>
+      <c r="C58" s="64">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="D58" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="E58" s="64" t="s">
+        <v>128</v>
+      </c>
+      <c r="F58" s="64" t="s">
+        <v>129</v>
+      </c>
+      <c r="G58" s="65" t="s">
+        <v>206</v>
+      </c>
+      <c r="H58" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="I58" s="64" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="59" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A59" s="67"/>
+      <c r="B59" s="63"/>
+      <c r="C59" s="64">
+        <v>17.5</v>
+      </c>
+      <c r="D59" s="64" t="s">
+        <v>120</v>
+      </c>
+      <c r="E59" s="64" t="s">
+        <v>130</v>
+      </c>
+      <c r="F59" s="64" t="s">
+        <v>131</v>
+      </c>
+      <c r="G59" s="65" t="s">
+        <v>207</v>
+      </c>
+      <c r="H59" s="64" t="s">
+        <v>123</v>
+      </c>
+      <c r="I59" s="64" t="s">
+        <v>108</v>
+      </c>
+    </row>
+    <row r="60" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A60" s="68">
         <v>18</v>
       </c>
-      <c r="I8" s="7" t="s">
+      <c r="B60" s="68" t="s">
+        <v>132</v>
+      </c>
+      <c r="C60" s="22">
+        <v>17.100000000000001</v>
+      </c>
+      <c r="D60" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E60" s="22" t="s">
+        <v>291</v>
+      </c>
+      <c r="F60" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="G60" s="23" t="s">
+        <v>208</v>
+      </c>
+      <c r="H60" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="I60" s="22" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A61" s="17"/>
+      <c r="B61" s="17"/>
+      <c r="C61" s="22">
+        <v>17.2</v>
+      </c>
+      <c r="D61" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E61" s="22" t="s">
+        <v>292</v>
+      </c>
+      <c r="F61" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="G61" s="23" t="s">
+        <v>209</v>
+      </c>
+      <c r="H61" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="I61" s="22" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A62" s="17"/>
+      <c r="B62" s="17"/>
+      <c r="C62" s="22">
+        <v>17.3</v>
+      </c>
+      <c r="D62" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E62" s="22" t="s">
+        <v>293</v>
+      </c>
+      <c r="F62" s="22" t="s">
+        <v>137</v>
+      </c>
+      <c r="G62" s="23" t="s">
+        <v>210</v>
+      </c>
+      <c r="H62" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="I62" s="22" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A63" s="17"/>
+      <c r="B63" s="17"/>
+      <c r="C63" s="22">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="D63" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E63" s="22" t="s">
+        <v>294</v>
+      </c>
+      <c r="F63" s="22" t="s">
+        <v>81</v>
+      </c>
+      <c r="G63" s="23" t="s">
+        <v>211</v>
+      </c>
+      <c r="H63" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="I63" s="22" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A64" s="17"/>
+      <c r="B64" s="17"/>
+      <c r="C64" s="22">
+        <v>17.5</v>
+      </c>
+      <c r="D64" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E64" s="22" t="s">
+        <v>295</v>
+      </c>
+      <c r="F64" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="G64" s="23" t="s">
+        <v>212</v>
+      </c>
+      <c r="H64" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="I64" s="22" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A65" s="17"/>
+      <c r="B65" s="17"/>
+      <c r="C65" s="22">
+        <v>17.600000000000001</v>
+      </c>
+      <c r="D65" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E65" s="22" t="s">
+        <v>296</v>
+      </c>
+      <c r="F65" s="22" t="s">
+        <v>139</v>
+      </c>
+      <c r="G65" s="23" t="s">
+        <v>213</v>
+      </c>
+      <c r="H65" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="I65" s="22" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A66" s="17"/>
+      <c r="B66" s="17"/>
+      <c r="C66" s="22">
+        <v>17.7</v>
+      </c>
+      <c r="D66" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E66" s="22" t="s">
+        <v>297</v>
+      </c>
+      <c r="F66" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="G66" s="23" t="s">
+        <v>214</v>
+      </c>
+      <c r="H66" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="I66" s="22" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A67" s="17"/>
+      <c r="B67" s="17"/>
+      <c r="C67" s="22">
+        <v>17.8</v>
+      </c>
+      <c r="D67" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E67" s="22" t="s">
+        <v>298</v>
+      </c>
+      <c r="F67" s="22" t="s">
+        <v>141</v>
+      </c>
+      <c r="G67" s="23" t="s">
+        <v>215</v>
+      </c>
+      <c r="H67" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="I67" s="22" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="68" spans="1:12" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A68" s="17"/>
+      <c r="B68" s="17"/>
+      <c r="C68" s="22">
+        <v>17.899999999999999</v>
+      </c>
+      <c r="D68" s="22" t="s">
+        <v>133</v>
+      </c>
+      <c r="E68" s="22" t="s">
+        <v>299</v>
+      </c>
+      <c r="F68" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="G68" s="23" t="s">
+        <v>216</v>
+      </c>
+      <c r="H68" s="22" t="s">
+        <v>82</v>
+      </c>
+      <c r="I68" s="22" t="s">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="69" spans="1:12" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A69" s="69">
         <v>19</v>
       </c>
-    </row>
-    <row r="9" spans="1:9" s="6" customFormat="1" ht="110.4" x14ac:dyDescent="0.3">
-      <c r="A9" s="56"/>
-      <c r="B9" s="56"/>
-      <c r="C9" s="8">
-        <v>5.2</v>
-      </c>
-      <c r="D9" s="7" t="s">
+      <c r="B69" s="70" t="s">
+        <v>143</v>
+      </c>
+      <c r="C69" s="71">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="D69" s="72" t="s">
+        <v>144</v>
+      </c>
+      <c r="E69" s="72" t="s">
+        <v>287</v>
+      </c>
+      <c r="F69" s="72" t="s">
+        <v>286</v>
+      </c>
+      <c r="G69" s="73" t="s">
+        <v>288</v>
+      </c>
+      <c r="H69" s="71"/>
+      <c r="I69" s="74"/>
+    </row>
+    <row r="70" spans="1:12" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A70" s="75"/>
+      <c r="B70" s="76"/>
+      <c r="C70" s="77">
+        <v>19.2</v>
+      </c>
+      <c r="D70" s="72" t="s">
+        <v>145</v>
+      </c>
+      <c r="E70" s="72" t="s">
+        <v>146</v>
+      </c>
+      <c r="F70" s="72" t="s">
+        <v>282</v>
+      </c>
+      <c r="G70" s="73" t="s">
+        <v>147</v>
+      </c>
+      <c r="H70" s="71"/>
+      <c r="I70" s="74"/>
+    </row>
+    <row r="71" spans="1:12" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="78"/>
+      <c r="B71" s="79"/>
+      <c r="C71" s="50">
+        <v>19.3</v>
+      </c>
+      <c r="D71" s="19" t="s">
+        <v>144</v>
+      </c>
+      <c r="E71" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F71" s="19" t="s">
+        <v>149</v>
+      </c>
+      <c r="G71" s="20"/>
+      <c r="H71" s="49"/>
+      <c r="I71" s="50"/>
+    </row>
+    <row r="72" spans="1:12" s="6" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A72" s="69">
         <v>20</v>
       </c>
-      <c r="E9" s="7" t="s">
-        <v>15</v>
-      </c>
-      <c r="F9" s="7" t="s">
-        <v>16</v>
-      </c>
-      <c r="G9" s="8" t="s">
-        <v>17</v>
-      </c>
-      <c r="H9" s="9"/>
-      <c r="I9" s="7"/>
-    </row>
-    <row r="10" spans="1:9" s="6" customFormat="1" ht="165.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="56"/>
-      <c r="B10" s="56"/>
-      <c r="C10" s="8">
-        <v>5.3</v>
-      </c>
-      <c r="D10" s="7" t="s">
-        <v>21</v>
-      </c>
-      <c r="E10" s="7" t="s">
-        <v>22</v>
-      </c>
-      <c r="F10" s="7" t="s">
-        <v>23</v>
-      </c>
-      <c r="G10" s="8" t="s">
-        <v>24</v>
-      </c>
-      <c r="H10" s="9"/>
-      <c r="I10" s="7"/>
-    </row>
-    <row r="11" spans="1:9" s="46" customFormat="1" ht="207" x14ac:dyDescent="0.3">
-      <c r="A11" s="56"/>
-      <c r="B11" s="56"/>
-      <c r="C11" s="39">
-        <v>5.4</v>
-      </c>
-      <c r="D11" s="40" t="s">
-        <v>202</v>
-      </c>
-      <c r="E11" s="40" t="s">
-        <v>205</v>
-      </c>
-      <c r="F11" s="40" t="s">
-        <v>204</v>
-      </c>
-      <c r="G11" s="39" t="s">
-        <v>206</v>
-      </c>
-      <c r="H11" s="41"/>
-      <c r="I11" s="40"/>
-    </row>
-    <row r="12" spans="1:9" s="46" customFormat="1" ht="151.80000000000001" x14ac:dyDescent="0.3">
-      <c r="A12" s="57"/>
-      <c r="B12" s="57"/>
-      <c r="C12" s="39">
-        <v>5.5</v>
-      </c>
-      <c r="D12" s="40" t="s">
-        <v>199</v>
-      </c>
-      <c r="E12" s="40" t="s">
-        <v>203</v>
-      </c>
-      <c r="F12" s="40" t="s">
-        <v>201</v>
-      </c>
-      <c r="G12" s="39" t="s">
-        <v>200</v>
-      </c>
-      <c r="H12" s="41"/>
-      <c r="I12" s="40"/>
-    </row>
-    <row r="13" spans="1:9" s="46" customFormat="1" ht="151.80000000000001" x14ac:dyDescent="0.3">
-      <c r="A13" s="47">
-        <v>6</v>
-      </c>
-      <c r="B13" s="47" t="s">
-        <v>25</v>
-      </c>
-      <c r="C13" s="39">
-        <v>6.1</v>
-      </c>
-      <c r="D13" s="40" t="s">
-        <v>26</v>
-      </c>
-      <c r="E13" s="40" t="s">
-        <v>27</v>
-      </c>
-      <c r="F13" s="40" t="s">
-        <v>28</v>
-      </c>
-      <c r="G13" s="39" t="s">
-        <v>29</v>
-      </c>
-      <c r="H13" s="41" t="s">
-        <v>30</v>
-      </c>
-      <c r="I13" s="40" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="14" spans="1:9" s="6" customFormat="1" ht="110.4" x14ac:dyDescent="0.3">
-      <c r="A14" s="48"/>
-      <c r="B14" s="48"/>
-      <c r="C14" s="11">
-        <v>6.2</v>
-      </c>
-      <c r="D14" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E14" s="10" t="s">
-        <v>208</v>
-      </c>
-      <c r="F14" s="10" t="s">
-        <v>207</v>
-      </c>
-      <c r="G14" s="11" t="s">
-        <v>209</v>
-      </c>
-      <c r="H14" s="12"/>
-      <c r="I14" s="10"/>
-    </row>
-    <row r="15" spans="1:9" s="6" customFormat="1" ht="151.80000000000001" x14ac:dyDescent="0.3">
-      <c r="A15" s="48"/>
-      <c r="B15" s="48"/>
-      <c r="C15" s="11">
-        <v>6.3</v>
-      </c>
-      <c r="D15" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E15" s="10" t="s">
-        <v>32</v>
-      </c>
-      <c r="F15" s="10" t="s">
-        <v>33</v>
-      </c>
-      <c r="G15" s="11" t="s">
-        <v>34</v>
-      </c>
-      <c r="H15" s="12"/>
-      <c r="I15" s="10"/>
-    </row>
-    <row r="16" spans="1:9" s="6" customFormat="1" ht="69" x14ac:dyDescent="0.3">
-      <c r="A16" s="48"/>
-      <c r="B16" s="49"/>
-      <c r="C16" s="35">
-        <v>6.4</v>
-      </c>
-      <c r="D16" s="10" t="s">
-        <v>26</v>
-      </c>
-      <c r="E16" s="10" t="s">
-        <v>35</v>
-      </c>
-      <c r="F16" s="10" t="s">
-        <v>36</v>
-      </c>
-      <c r="G16" s="11" t="s">
-        <v>37</v>
-      </c>
-      <c r="H16" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="I16" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="17" spans="1:9" s="6" customFormat="1" ht="138" x14ac:dyDescent="0.3">
-      <c r="A17" s="50">
-        <v>7</v>
-      </c>
-      <c r="B17" s="47" t="s">
-        <v>38</v>
-      </c>
-      <c r="C17" s="11">
-        <v>7.1</v>
-      </c>
-      <c r="D17" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" s="10" t="s">
-        <v>40</v>
-      </c>
-      <c r="F17" s="10" t="s">
-        <v>41</v>
-      </c>
-      <c r="G17" s="11" t="s">
-        <v>42</v>
-      </c>
-      <c r="H17" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A18" s="51"/>
-      <c r="B18" s="48"/>
-      <c r="C18" s="11">
-        <v>7.2</v>
-      </c>
-      <c r="D18" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" s="10" t="s">
-        <v>43</v>
-      </c>
-      <c r="F18" s="10" t="s">
-        <v>44</v>
-      </c>
-      <c r="G18" s="11" t="s">
-        <v>45</v>
-      </c>
-      <c r="H18" s="12"/>
-      <c r="I18" s="10" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" s="6" customFormat="1" ht="165.6" x14ac:dyDescent="0.3">
-      <c r="A19" s="51"/>
-      <c r="B19" s="48"/>
-      <c r="C19" s="11">
-        <v>7.3</v>
-      </c>
-      <c r="D19" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="10" t="s">
-        <v>184</v>
-      </c>
-      <c r="F19" s="10" t="s">
-        <v>46</v>
-      </c>
-      <c r="G19" s="11" t="s">
-        <v>47</v>
-      </c>
-      <c r="H19" s="12"/>
-      <c r="I19" s="10"/>
-    </row>
-    <row r="20" spans="1:9" s="6" customFormat="1" ht="165.6" x14ac:dyDescent="0.3">
-      <c r="A20" s="52"/>
-      <c r="B20" s="49"/>
-      <c r="C20" s="11">
-        <v>7.4</v>
-      </c>
-      <c r="D20" s="10" t="s">
-        <v>39</v>
-      </c>
-      <c r="E20" s="10" t="s">
-        <v>185</v>
-      </c>
-      <c r="F20" s="10" t="s">
-        <v>48</v>
-      </c>
-      <c r="G20" s="11" t="s">
-        <v>49</v>
-      </c>
-      <c r="H20" s="12"/>
-      <c r="I20" s="10"/>
-    </row>
-    <row r="21" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A21" s="76">
-        <v>8</v>
-      </c>
-      <c r="B21" s="76" t="s">
-        <v>50</v>
-      </c>
-      <c r="C21" s="14">
-        <v>9.1999999999999993</v>
-      </c>
-      <c r="D21" s="13" t="s">
-        <v>51</v>
-      </c>
-      <c r="E21" s="13" t="s">
-        <v>52</v>
-      </c>
-      <c r="F21" s="13" t="s">
-        <v>53</v>
-      </c>
-      <c r="G21" s="14" t="s">
-        <v>54</v>
-      </c>
-      <c r="H21" s="13"/>
-      <c r="I21" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="22" spans="1:9" s="6" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A22" s="77"/>
-      <c r="B22" s="77"/>
-      <c r="C22" s="14">
-        <v>9.3000000000000007</v>
-      </c>
-      <c r="D22" s="13" t="s">
-        <v>56</v>
-      </c>
-      <c r="E22" s="13" t="s">
-        <v>57</v>
-      </c>
-      <c r="F22" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="G22" s="14" t="s">
-        <v>59</v>
-      </c>
-      <c r="H22" s="13"/>
-      <c r="I22" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="23" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A23" s="78"/>
-      <c r="B23" s="78"/>
-      <c r="C23" s="14">
-        <v>9.4</v>
-      </c>
-      <c r="D23" s="13" t="s">
-        <v>60</v>
-      </c>
-      <c r="E23" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="F23" s="13" t="s">
-        <v>62</v>
-      </c>
-      <c r="G23" s="14" t="s">
-        <v>63</v>
-      </c>
-      <c r="H23" s="13"/>
-      <c r="I23" s="13" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="24" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A24" s="74">
-        <v>12</v>
-      </c>
-      <c r="B24" s="74" t="s">
-        <v>64</v>
-      </c>
-      <c r="C24" s="16">
-        <v>12.1</v>
-      </c>
-      <c r="D24" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="E24" s="15" t="s">
-        <v>66</v>
-      </c>
-      <c r="F24" s="15" t="s">
-        <v>67</v>
-      </c>
-      <c r="G24" s="16" t="s">
-        <v>68</v>
-      </c>
-      <c r="H24" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="I24" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A25" s="74"/>
-      <c r="B25" s="74"/>
-      <c r="C25" s="16">
-        <v>12.2</v>
-      </c>
-      <c r="D25" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="E25" s="15" t="s">
-        <v>71</v>
-      </c>
-      <c r="F25" s="15" t="s">
-        <v>72</v>
-      </c>
-      <c r="G25" s="16" t="s">
-        <v>73</v>
-      </c>
-      <c r="H25" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="I25" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A26" s="74"/>
-      <c r="B26" s="74"/>
-      <c r="C26" s="16">
-        <v>12.3</v>
-      </c>
-      <c r="D26" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="E26" s="15" t="s">
-        <v>74</v>
-      </c>
-      <c r="F26" s="15" t="s">
-        <v>75</v>
-      </c>
-      <c r="G26" s="16" t="s">
-        <v>76</v>
-      </c>
-      <c r="H26" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="I26" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" s="6" customFormat="1" ht="69" x14ac:dyDescent="0.3">
-      <c r="A27" s="74"/>
-      <c r="B27" s="74"/>
-      <c r="C27" s="16">
-        <v>12.4</v>
-      </c>
-      <c r="D27" s="15" t="s">
-        <v>65</v>
-      </c>
-      <c r="E27" s="15" t="s">
-        <v>77</v>
-      </c>
-      <c r="F27" s="15" t="s">
-        <v>78</v>
-      </c>
-      <c r="G27" s="39" t="s">
+      <c r="B72" s="70" t="s">
+        <v>150</v>
+      </c>
+      <c r="C72" s="71">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="D72" s="72" t="s">
+        <v>151</v>
+      </c>
+      <c r="E72" s="72" t="s">
+        <v>308</v>
+      </c>
+      <c r="F72" s="72" t="s">
+        <v>309</v>
+      </c>
+      <c r="G72" s="73" t="s">
         <v>310</v>
       </c>
-      <c r="H27" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="I27" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="28" spans="1:9" s="6" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A28" s="74"/>
-      <c r="B28" s="74"/>
-      <c r="C28" s="16">
-        <v>12.5</v>
-      </c>
-      <c r="D28" s="15" t="s">
-        <v>79</v>
-      </c>
-      <c r="E28" s="15" t="s">
-        <v>80</v>
-      </c>
-      <c r="F28" s="15" t="s">
-        <v>307</v>
-      </c>
-      <c r="G28" s="16" t="s">
-        <v>81</v>
-      </c>
-      <c r="H28" s="15" t="s">
-        <v>69</v>
-      </c>
-      <c r="I28" s="15" t="s">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="29" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A29" s="75">
-        <v>14</v>
-      </c>
-      <c r="B29" s="75" t="s">
-        <v>82</v>
-      </c>
-      <c r="C29" s="18">
-        <v>14.1</v>
-      </c>
-      <c r="D29" s="44" t="s">
-        <v>135</v>
-      </c>
-      <c r="E29" s="44" t="s">
-        <v>274</v>
-      </c>
-      <c r="F29" s="44" t="s">
-        <v>240</v>
-      </c>
-      <c r="G29" s="45" t="s">
+      <c r="H72" s="71"/>
+      <c r="I72" s="74"/>
+    </row>
+    <row r="73" spans="1:12" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A73" s="75"/>
+      <c r="B73" s="76"/>
+      <c r="C73" s="77">
+        <v>20.2</v>
+      </c>
+      <c r="D73" s="72" t="s">
+        <v>152</v>
+      </c>
+      <c r="E73" s="72" t="s">
+        <v>289</v>
+      </c>
+      <c r="F73" s="72" t="s">
+        <v>282</v>
+      </c>
+      <c r="G73" s="73" t="s">
         <v>290</v>
       </c>
-      <c r="H29" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="I29" s="17" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="30" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="75"/>
-      <c r="B30" s="75"/>
-      <c r="C30" s="18">
-        <v>14.2</v>
-      </c>
-      <c r="D30" s="44" t="s">
-        <v>135</v>
-      </c>
-      <c r="E30" s="44" t="s">
-        <v>275</v>
-      </c>
-      <c r="F30" s="44" t="s">
-        <v>276</v>
-      </c>
-      <c r="G30" s="45" t="s">
-        <v>291</v>
-      </c>
-      <c r="H30" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="I30" s="17" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="75"/>
-      <c r="B31" s="75"/>
-      <c r="C31" s="18">
-        <v>14.3</v>
-      </c>
-      <c r="D31" s="44" t="s">
-        <v>245</v>
-      </c>
-      <c r="E31" s="44" t="s">
-        <v>277</v>
-      </c>
-      <c r="F31" s="44" t="s">
-        <v>278</v>
-      </c>
-      <c r="G31" s="45" t="s">
-        <v>292</v>
-      </c>
-      <c r="H31" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="I31" s="17" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A32" s="75"/>
-      <c r="B32" s="75"/>
-      <c r="C32" s="18">
-        <v>14.4</v>
-      </c>
-      <c r="D32" s="44" t="s">
-        <v>135</v>
-      </c>
-      <c r="E32" s="44" t="s">
-        <v>279</v>
-      </c>
-      <c r="F32" s="44" t="s">
-        <v>250</v>
-      </c>
-      <c r="G32" s="45" t="s">
-        <v>293</v>
-      </c>
-      <c r="H32" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="I32" s="17" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A33" s="75"/>
-      <c r="B33" s="75"/>
-      <c r="C33" s="18">
-        <v>14.5</v>
-      </c>
-      <c r="D33" s="44" t="s">
-        <v>135</v>
-      </c>
-      <c r="E33" s="44" t="s">
-        <v>280</v>
-      </c>
-      <c r="F33" s="44" t="s">
-        <v>253</v>
-      </c>
-      <c r="G33" s="45" t="s">
-        <v>294</v>
-      </c>
-      <c r="H33" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="I33" s="17" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="34" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="75"/>
-      <c r="B34" s="75"/>
-      <c r="C34" s="18">
-        <v>14.6</v>
-      </c>
-      <c r="D34" s="44" t="s">
-        <v>135</v>
-      </c>
-      <c r="E34" s="44" t="s">
-        <v>281</v>
-      </c>
-      <c r="F34" s="44" t="s">
-        <v>282</v>
-      </c>
-      <c r="G34" s="45" t="s">
-        <v>295</v>
-      </c>
-      <c r="H34" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="I34" s="17" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="35" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="75"/>
-      <c r="B35" s="75"/>
-      <c r="C35" s="18">
-        <v>14.7</v>
-      </c>
-      <c r="D35" s="44" t="s">
-        <v>135</v>
-      </c>
-      <c r="E35" s="44" t="s">
-        <v>283</v>
-      </c>
-      <c r="F35" s="44" t="s">
-        <v>284</v>
-      </c>
-      <c r="G35" s="45" t="s">
-        <v>296</v>
-      </c>
-      <c r="H35" s="17" t="s">
-        <v>84</v>
-      </c>
-      <c r="I35" s="17" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="36" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="75"/>
-      <c r="B36" s="75"/>
-      <c r="C36" s="18">
-        <v>14.8</v>
-      </c>
-      <c r="D36" s="44" t="s">
-        <v>135</v>
-      </c>
-      <c r="E36" s="44" t="s">
-        <v>285</v>
-      </c>
-      <c r="F36" s="44" t="s">
-        <v>286</v>
-      </c>
-      <c r="G36" s="45" t="s">
-        <v>297</v>
-      </c>
-      <c r="H36" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="I36" s="17" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="37" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="75"/>
-      <c r="B37" s="75"/>
-      <c r="C37" s="18">
-        <v>14.9</v>
-      </c>
-      <c r="D37" s="44" t="s">
-        <v>135</v>
-      </c>
-      <c r="E37" s="44" t="s">
-        <v>287</v>
-      </c>
-      <c r="F37" s="44" t="s">
-        <v>265</v>
-      </c>
-      <c r="G37" s="45" t="s">
-        <v>298</v>
-      </c>
-      <c r="H37" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="I37" s="17" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="38" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A38" s="75"/>
-      <c r="B38" s="75"/>
-      <c r="C38" s="18">
-        <v>14.1</v>
-      </c>
-      <c r="D38" s="44" t="s">
-        <v>135</v>
-      </c>
-      <c r="E38" s="44" t="s">
-        <v>288</v>
-      </c>
-      <c r="F38" s="44" t="s">
-        <v>269</v>
-      </c>
-      <c r="G38" s="45" t="s">
-        <v>299</v>
-      </c>
-      <c r="H38" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="I38" s="17" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="39" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A39" s="75"/>
-      <c r="B39" s="75"/>
-      <c r="C39" s="18">
-        <v>14.11</v>
-      </c>
-      <c r="D39" s="44" t="s">
-        <v>135</v>
-      </c>
-      <c r="E39" s="44" t="s">
-        <v>289</v>
-      </c>
-      <c r="F39" s="44" t="s">
-        <v>272</v>
-      </c>
-      <c r="G39" s="45" t="s">
-        <v>300</v>
-      </c>
-      <c r="H39" s="17" t="s">
-        <v>86</v>
-      </c>
-      <c r="I39" s="17" t="s">
-        <v>85</v>
-      </c>
-    </row>
-    <row r="40" spans="1:9" s="6" customFormat="1" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A40" s="61">
-        <v>15</v>
-      </c>
-      <c r="B40" s="61" t="s">
-        <v>87</v>
-      </c>
-      <c r="C40" s="20">
-        <v>15.1</v>
-      </c>
-      <c r="D40" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="E40" s="19" t="s">
-        <v>89</v>
-      </c>
-      <c r="F40" s="19" t="s">
-        <v>90</v>
-      </c>
-      <c r="G40" s="20" t="s">
-        <v>210</v>
-      </c>
-      <c r="H40" s="19" t="s">
-        <v>125</v>
-      </c>
-      <c r="I40" s="19" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="41" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A41" s="54"/>
-      <c r="B41" s="54"/>
-      <c r="C41" s="20">
-        <v>15.2</v>
-      </c>
-      <c r="D41" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="E41" s="19" t="s">
-        <v>91</v>
-      </c>
-      <c r="F41" s="19" t="s">
-        <v>92</v>
-      </c>
-      <c r="G41" s="20" t="s">
-        <v>211</v>
-      </c>
-      <c r="H41" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="I41" s="19" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A42" s="54"/>
-      <c r="B42" s="54"/>
-      <c r="C42" s="20">
-        <v>15.3</v>
-      </c>
-      <c r="D42" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="E42" s="19" t="s">
-        <v>93</v>
-      </c>
-      <c r="F42" s="19" t="s">
-        <v>94</v>
-      </c>
-      <c r="G42" s="20" t="s">
-        <v>212</v>
-      </c>
-      <c r="H42" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="I42" s="19" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A43" s="54"/>
-      <c r="B43" s="54"/>
-      <c r="C43" s="20">
-        <v>15.4</v>
-      </c>
-      <c r="D43" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="E43" s="19" t="s">
-        <v>95</v>
-      </c>
-      <c r="F43" s="19" t="s">
-        <v>96</v>
-      </c>
-      <c r="G43" s="20" t="s">
-        <v>213</v>
-      </c>
-      <c r="H43" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="I43" s="19" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A44" s="54"/>
-      <c r="B44" s="54"/>
-      <c r="C44" s="20">
-        <v>15.5</v>
-      </c>
-      <c r="D44" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="E44" s="19" t="s">
-        <v>97</v>
-      </c>
-      <c r="F44" s="19" t="s">
-        <v>98</v>
-      </c>
-      <c r="G44" s="20" t="s">
-        <v>214</v>
-      </c>
-      <c r="H44" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="I44" s="19" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="45" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A45" s="54"/>
-      <c r="B45" s="54"/>
-      <c r="C45" s="20">
-        <v>15.6</v>
-      </c>
-      <c r="D45" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="E45" s="19" t="s">
-        <v>99</v>
-      </c>
-      <c r="F45" s="19" t="s">
-        <v>100</v>
-      </c>
-      <c r="G45" s="20" t="s">
-        <v>215</v>
-      </c>
-      <c r="H45" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="I45" s="19" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="46" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A46" s="54"/>
-      <c r="B46" s="54"/>
-      <c r="C46" s="20">
-        <v>15.7</v>
-      </c>
-      <c r="D46" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="E46" s="19" t="s">
-        <v>101</v>
-      </c>
-      <c r="F46" s="19" t="s">
-        <v>102</v>
-      </c>
-      <c r="G46" s="20" t="s">
-        <v>216</v>
-      </c>
-      <c r="H46" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="I46" s="19" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="47" spans="1:9" s="6" customFormat="1" ht="55.2" x14ac:dyDescent="0.3">
-      <c r="A47" s="54"/>
-      <c r="B47" s="54"/>
-      <c r="C47" s="20">
-        <v>15.8</v>
-      </c>
-      <c r="D47" s="19" t="s">
-        <v>88</v>
-      </c>
-      <c r="E47" s="19" t="s">
-        <v>103</v>
-      </c>
-      <c r="F47" s="19" t="s">
-        <v>104</v>
-      </c>
-      <c r="G47" s="20" t="s">
-        <v>217</v>
-      </c>
-      <c r="H47" s="19" t="s">
-        <v>109</v>
-      </c>
-      <c r="I47" s="19" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="48" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A48" s="68">
-        <v>16</v>
-      </c>
-      <c r="B48" s="68" t="s">
-        <v>105</v>
-      </c>
-      <c r="C48" s="36">
-        <v>16.100000000000001</v>
-      </c>
-      <c r="D48" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="E48" s="21" t="s">
-        <v>107</v>
-      </c>
-      <c r="F48" s="21" t="s">
-        <v>108</v>
-      </c>
-      <c r="G48" s="22" t="s">
-        <v>218</v>
-      </c>
-      <c r="H48" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="I48" s="21" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="49" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A49" s="68"/>
-      <c r="B49" s="68"/>
-      <c r="C49" s="36">
-        <v>16.2</v>
-      </c>
-      <c r="D49" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="E49" s="21" t="s">
-        <v>111</v>
-      </c>
-      <c r="F49" s="21" t="s">
-        <v>112</v>
-      </c>
-      <c r="G49" s="22" t="s">
-        <v>219</v>
-      </c>
-      <c r="H49" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="I49" s="21" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A50" s="68"/>
-      <c r="B50" s="68"/>
-      <c r="C50" s="36">
-        <v>16.3</v>
-      </c>
-      <c r="D50" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="E50" s="21" t="s">
-        <v>113</v>
-      </c>
-      <c r="F50" s="21" t="s">
-        <v>114</v>
-      </c>
-      <c r="G50" s="22" t="s">
-        <v>220</v>
-      </c>
-      <c r="H50" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="I50" s="21" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A51" s="68"/>
-      <c r="B51" s="68"/>
-      <c r="C51" s="36">
-        <v>16.399999999999999</v>
-      </c>
-      <c r="D51" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="E51" s="21" t="s">
-        <v>115</v>
-      </c>
-      <c r="F51" s="21" t="s">
-        <v>116</v>
-      </c>
-      <c r="G51" s="22" t="s">
-        <v>221</v>
-      </c>
-      <c r="H51" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="I51" s="21" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A52" s="68"/>
-      <c r="B52" s="68"/>
-      <c r="C52" s="36">
-        <v>16.5</v>
-      </c>
-      <c r="D52" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="E52" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="F52" s="21" t="s">
-        <v>118</v>
-      </c>
-      <c r="G52" s="22" t="s">
-        <v>222</v>
-      </c>
-      <c r="H52" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="I52" s="21" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="53" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A53" s="54"/>
-      <c r="B53" s="54"/>
-      <c r="C53" s="36">
-        <v>16.600000000000001</v>
-      </c>
-      <c r="D53" s="21" t="s">
-        <v>106</v>
-      </c>
-      <c r="E53" s="21" t="s">
-        <v>119</v>
-      </c>
-      <c r="F53" s="21" t="s">
-        <v>120</v>
-      </c>
-      <c r="G53" s="22" t="s">
-        <v>223</v>
-      </c>
-      <c r="H53" s="21" t="s">
-        <v>109</v>
-      </c>
-      <c r="I53" s="21" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="54" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A54" s="69">
-        <v>17</v>
-      </c>
-      <c r="B54" s="72" t="s">
-        <v>121</v>
-      </c>
-      <c r="C54" s="24">
-        <v>17.100000000000001</v>
-      </c>
-      <c r="D54" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="E54" s="23" t="s">
-        <v>123</v>
-      </c>
-      <c r="F54" s="23" t="s">
-        <v>124</v>
-      </c>
-      <c r="G54" s="24" t="s">
-        <v>224</v>
-      </c>
-      <c r="H54" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="I54" s="23" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="55" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A55" s="70"/>
-      <c r="B55" s="72"/>
-      <c r="C55" s="24">
-        <v>17.2</v>
-      </c>
-      <c r="D55" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="E55" s="23" t="s">
-        <v>126</v>
-      </c>
-      <c r="F55" s="23" t="s">
-        <v>127</v>
-      </c>
-      <c r="G55" s="24" t="s">
-        <v>225</v>
-      </c>
-      <c r="H55" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="I55" s="23" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A56" s="70"/>
-      <c r="B56" s="72"/>
-      <c r="C56" s="24">
-        <v>17.3</v>
-      </c>
-      <c r="D56" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="E56" s="23" t="s">
-        <v>128</v>
-      </c>
-      <c r="F56" s="23" t="s">
-        <v>129</v>
-      </c>
-      <c r="G56" s="24" t="s">
-        <v>226</v>
-      </c>
-      <c r="H56" s="23" t="s">
-        <v>109</v>
-      </c>
-      <c r="I56" s="23" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A57" s="70"/>
-      <c r="B57" s="72"/>
-      <c r="C57" s="24">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="D57" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="E57" s="23" t="s">
-        <v>130</v>
-      </c>
-      <c r="F57" s="23" t="s">
-        <v>131</v>
-      </c>
-      <c r="G57" s="24" t="s">
-        <v>227</v>
-      </c>
-      <c r="H57" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="I57" s="23" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A58" s="71"/>
-      <c r="B58" s="72"/>
-      <c r="C58" s="24">
-        <v>17.5</v>
-      </c>
-      <c r="D58" s="23" t="s">
-        <v>122</v>
-      </c>
-      <c r="E58" s="23" t="s">
-        <v>132</v>
-      </c>
-      <c r="F58" s="23" t="s">
-        <v>133</v>
-      </c>
-      <c r="G58" s="24" t="s">
-        <v>228</v>
-      </c>
-      <c r="H58" s="23" t="s">
-        <v>125</v>
-      </c>
-      <c r="I58" s="23" t="s">
-        <v>110</v>
-      </c>
-    </row>
-    <row r="59" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A59" s="73">
-        <v>18</v>
-      </c>
-      <c r="B59" s="73" t="s">
-        <v>134</v>
-      </c>
-      <c r="C59" s="8">
-        <v>17.100000000000001</v>
-      </c>
-      <c r="D59" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E59" s="7" t="s">
-        <v>136</v>
-      </c>
-      <c r="F59" s="7" t="s">
-        <v>137</v>
-      </c>
-      <c r="G59" s="8" t="s">
-        <v>229</v>
-      </c>
-      <c r="H59" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="I59" s="7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="60" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A60" s="54"/>
-      <c r="B60" s="54"/>
-      <c r="C60" s="8">
-        <v>17.2</v>
-      </c>
-      <c r="D60" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E60" s="7" t="s">
-        <v>139</v>
-      </c>
-      <c r="F60" s="7" t="s">
-        <v>140</v>
-      </c>
-      <c r="G60" s="8" t="s">
-        <v>230</v>
-      </c>
-      <c r="H60" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="I60" s="7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A61" s="54"/>
-      <c r="B61" s="54"/>
-      <c r="C61" s="8">
-        <v>17.3</v>
-      </c>
-      <c r="D61" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E61" s="7" t="s">
-        <v>141</v>
-      </c>
-      <c r="F61" s="7" t="s">
-        <v>142</v>
-      </c>
-      <c r="G61" s="8" t="s">
-        <v>231</v>
-      </c>
-      <c r="H61" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="I61" s="7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A62" s="54"/>
-      <c r="B62" s="54"/>
-      <c r="C62" s="8">
-        <v>17.399999999999999</v>
-      </c>
-      <c r="D62" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E62" s="7" t="s">
-        <v>143</v>
-      </c>
-      <c r="F62" s="7" t="s">
-        <v>83</v>
-      </c>
-      <c r="G62" s="8" t="s">
-        <v>232</v>
-      </c>
-      <c r="H62" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="I62" s="7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A63" s="54"/>
-      <c r="B63" s="54"/>
-      <c r="C63" s="8">
-        <v>17.5</v>
-      </c>
-      <c r="D63" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E63" s="7" t="s">
-        <v>144</v>
-      </c>
-      <c r="F63" s="7" t="s">
-        <v>145</v>
-      </c>
-      <c r="G63" s="8" t="s">
-        <v>233</v>
-      </c>
-      <c r="H63" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="I63" s="7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="64" spans="1:9" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A64" s="54"/>
-      <c r="B64" s="54"/>
-      <c r="C64" s="8">
-        <v>17.600000000000001</v>
-      </c>
-      <c r="D64" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E64" s="7" t="s">
-        <v>146</v>
-      </c>
-      <c r="F64" s="7" t="s">
-        <v>147</v>
-      </c>
-      <c r="G64" s="8" t="s">
-        <v>234</v>
-      </c>
-      <c r="H64" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="I64" s="7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="65" spans="1:12" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A65" s="54"/>
-      <c r="B65" s="54"/>
-      <c r="C65" s="8">
-        <v>17.7</v>
-      </c>
-      <c r="D65" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E65" s="7" t="s">
-        <v>148</v>
-      </c>
-      <c r="F65" s="7" t="s">
-        <v>149</v>
-      </c>
-      <c r="G65" s="8" t="s">
-        <v>235</v>
-      </c>
-      <c r="H65" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="I65" s="7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A66" s="54"/>
-      <c r="B66" s="54"/>
-      <c r="C66" s="8">
-        <v>17.8</v>
-      </c>
-      <c r="D66" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E66" s="7" t="s">
-        <v>150</v>
-      </c>
-      <c r="F66" s="7" t="s">
-        <v>151</v>
-      </c>
-      <c r="G66" s="8" t="s">
-        <v>236</v>
-      </c>
-      <c r="H66" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="I66" s="7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A67" s="54"/>
-      <c r="B67" s="54"/>
-      <c r="C67" s="8">
-        <v>17.899999999999999</v>
-      </c>
-      <c r="D67" s="7" t="s">
-        <v>135</v>
-      </c>
-      <c r="E67" s="7" t="s">
-        <v>152</v>
-      </c>
-      <c r="F67" s="7" t="s">
-        <v>153</v>
-      </c>
-      <c r="G67" s="8" t="s">
-        <v>237</v>
-      </c>
-      <c r="H67" s="7" t="s">
-        <v>84</v>
-      </c>
-      <c r="I67" s="7" t="s">
-        <v>138</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A68" s="62">
-        <v>19</v>
-      </c>
-      <c r="B68" s="65" t="s">
-        <v>154</v>
-      </c>
-      <c r="C68" s="26">
-        <v>19.100000000000001</v>
-      </c>
-      <c r="D68" s="33" t="s">
-        <v>155</v>
-      </c>
-      <c r="E68" s="33" t="s">
-        <v>156</v>
-      </c>
-      <c r="F68" s="33" t="s">
-        <v>157</v>
-      </c>
-      <c r="G68" s="39" t="s">
-        <v>309</v>
-      </c>
-      <c r="H68" s="3"/>
-      <c r="I68" s="32"/>
-    </row>
-    <row r="69" spans="1:12" s="6" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A69" s="63"/>
-      <c r="B69" s="66"/>
-      <c r="C69" s="34">
-        <v>19.2</v>
-      </c>
-      <c r="D69" s="33" t="s">
-        <v>158</v>
-      </c>
-      <c r="E69" s="33" t="s">
-        <v>159</v>
-      </c>
-      <c r="F69" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="G69" s="31" t="s">
-        <v>160</v>
-      </c>
-      <c r="H69" s="3"/>
-      <c r="I69" s="32"/>
-    </row>
-    <row r="70" spans="1:12" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A70" s="64"/>
-      <c r="B70" s="67"/>
-      <c r="C70" s="82">
-        <v>19.3</v>
-      </c>
-      <c r="D70" s="29" t="s">
-        <v>155</v>
-      </c>
-      <c r="E70" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="F70" s="29" t="s">
-        <v>162</v>
-      </c>
-      <c r="G70" s="30"/>
-      <c r="H70" s="80"/>
-      <c r="I70" s="81"/>
-    </row>
-    <row r="71" spans="1:12" s="6" customFormat="1" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A71" s="62">
-        <v>20</v>
-      </c>
-      <c r="B71" s="65" t="s">
-        <v>163</v>
-      </c>
-      <c r="C71" s="26">
-        <v>20.100000000000001</v>
-      </c>
-      <c r="D71" s="33" t="s">
-        <v>164</v>
-      </c>
-      <c r="E71" s="33" t="s">
-        <v>165</v>
-      </c>
-      <c r="F71" s="33" t="s">
-        <v>166</v>
-      </c>
-      <c r="G71" s="39" t="s">
-        <v>308</v>
-      </c>
-      <c r="H71" s="3"/>
-      <c r="I71" s="32"/>
-    </row>
-    <row r="72" spans="1:12" s="6" customFormat="1" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A72" s="63"/>
-      <c r="B72" s="66"/>
-      <c r="C72" s="34">
-        <v>20.2</v>
-      </c>
-      <c r="D72" s="33" t="s">
-        <v>167</v>
-      </c>
-      <c r="E72" s="33" t="s">
-        <v>168</v>
-      </c>
-      <c r="F72" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="G72" s="31" t="s">
-        <v>169</v>
-      </c>
-      <c r="H72" s="3"/>
-      <c r="I72" s="32"/>
-      <c r="J72" s="1"/>
-      <c r="K72" s="1"/>
-      <c r="L72" s="1"/>
-    </row>
-    <row r="73" spans="1:12" s="6" customFormat="1" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A73" s="64"/>
-      <c r="B73" s="67"/>
-      <c r="C73" s="79">
-        <v>20.3</v>
-      </c>
-      <c r="D73" s="29" t="s">
-        <v>164</v>
-      </c>
-      <c r="E73" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="F73" s="29"/>
-      <c r="G73" s="30"/>
-      <c r="H73" s="80"/>
-      <c r="I73" s="81"/>
+      <c r="H73" s="71"/>
+      <c r="I73" s="74"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
     </row>
-    <row r="74" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A74" s="62">
+    <row r="74" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A74" s="78"/>
+      <c r="B74" s="79"/>
+      <c r="C74" s="49">
+        <v>20.3</v>
+      </c>
+      <c r="D74" s="19" t="s">
+        <v>151</v>
+      </c>
+      <c r="E74" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F74" s="19"/>
+      <c r="G74" s="20"/>
+      <c r="H74" s="49"/>
+      <c r="I74" s="50"/>
+      <c r="J74" s="1"/>
+      <c r="K74" s="1"/>
+      <c r="L74" s="1"/>
+    </row>
+    <row r="75" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A75" s="69">
         <v>21</v>
       </c>
-      <c r="B74" s="65" t="s">
-        <v>170</v>
-      </c>
-      <c r="C74" s="26">
+      <c r="B75" s="70" t="s">
+        <v>153</v>
+      </c>
+      <c r="C75" s="71">
         <v>21.1</v>
       </c>
-      <c r="D74" s="33" t="s">
-        <v>171</v>
-      </c>
-      <c r="E74" s="33" t="s">
-        <v>172</v>
-      </c>
-      <c r="F74" s="33" t="s">
-        <v>173</v>
-      </c>
-      <c r="G74" s="39" t="s">
+      <c r="D75" s="72" t="s">
+        <v>154</v>
+      </c>
+      <c r="E75" s="72" t="s">
+        <v>300</v>
+      </c>
+      <c r="F75" s="72" t="s">
+        <v>301</v>
+      </c>
+      <c r="G75" s="73" t="s">
+        <v>302</v>
+      </c>
+      <c r="H75" s="71"/>
+      <c r="I75" s="74"/>
+    </row>
+    <row r="76" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A76" s="75"/>
+      <c r="B76" s="76"/>
+      <c r="C76" s="77">
+        <v>21.2</v>
+      </c>
+      <c r="D76" s="72" t="s">
+        <v>155</v>
+      </c>
+      <c r="E76" s="72" t="s">
+        <v>281</v>
+      </c>
+      <c r="F76" s="72" t="s">
+        <v>282</v>
+      </c>
+      <c r="G76" s="73" t="s">
+        <v>156</v>
+      </c>
+      <c r="H76" s="71"/>
+      <c r="I76" s="74"/>
+    </row>
+    <row r="77" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A77" s="78"/>
+      <c r="B77" s="79"/>
+      <c r="C77" s="49">
+        <v>21.3</v>
+      </c>
+      <c r="D77" s="19" t="s">
+        <v>154</v>
+      </c>
+      <c r="E77" s="19" t="s">
+        <v>148</v>
+      </c>
+      <c r="F77" s="19"/>
+      <c r="G77" s="20"/>
+      <c r="H77" s="49"/>
+      <c r="I77" s="50"/>
+    </row>
+    <row r="78" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A78" s="69">
+        <v>22</v>
+      </c>
+      <c r="B78" s="70" t="s">
+        <v>157</v>
+      </c>
+      <c r="C78" s="71">
+        <v>22.1</v>
+      </c>
+      <c r="D78" s="72" t="s">
+        <v>158</v>
+      </c>
+      <c r="E78" s="72" t="s">
         <v>305</v>
       </c>
-      <c r="H74" s="3"/>
-      <c r="I74" s="32"/>
-    </row>
-    <row r="75" spans="1:12" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A75" s="63"/>
-      <c r="B75" s="66"/>
-      <c r="C75" s="34">
-        <v>21.2</v>
-      </c>
-      <c r="D75" s="33" t="s">
-        <v>174</v>
-      </c>
-      <c r="E75" s="33" t="s">
+      <c r="F78" s="72" t="s">
         <v>306</v>
       </c>
-      <c r="F75" s="33" t="s">
+      <c r="G78" s="73" t="s">
         <v>307</v>
       </c>
-      <c r="G75" s="31" t="s">
-        <v>175</v>
-      </c>
-      <c r="H75" s="3"/>
-      <c r="I75" s="32"/>
-    </row>
-    <row r="76" spans="1:12" ht="27.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="64"/>
-      <c r="B76" s="67"/>
-      <c r="C76" s="79">
-        <v>21.3</v>
-      </c>
-      <c r="D76" s="29" t="s">
-        <v>171</v>
-      </c>
-      <c r="E76" s="29" t="s">
-        <v>161</v>
-      </c>
-      <c r="F76" s="29"/>
-      <c r="G76" s="30"/>
-      <c r="H76" s="80"/>
-      <c r="I76" s="81"/>
-    </row>
-    <row r="77" spans="1:12" ht="82.8" x14ac:dyDescent="0.3">
-      <c r="A77" s="62">
-        <v>22</v>
-      </c>
-      <c r="B77" s="65" t="s">
-        <v>176</v>
-      </c>
-      <c r="C77" s="26">
-        <v>22.1</v>
-      </c>
-      <c r="D77" s="33" t="s">
-        <v>177</v>
-      </c>
-      <c r="E77" s="33" t="s">
-        <v>178</v>
-      </c>
-      <c r="F77" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="G77" s="31" t="s">
+      <c r="H78" s="71"/>
+      <c r="I78" s="74"/>
+    </row>
+    <row r="79" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A79" s="75"/>
+      <c r="B79" s="76"/>
+      <c r="C79" s="77">
+        <v>22.2</v>
+      </c>
+      <c r="D79" s="72" t="s">
+        <v>280</v>
+      </c>
+      <c r="E79" s="71" t="s">
+        <v>303</v>
+      </c>
+      <c r="F79" s="72" t="s">
+        <v>282</v>
+      </c>
+      <c r="G79" s="73" t="s">
         <v>304</v>
       </c>
-      <c r="H77" s="3"/>
-      <c r="I77" s="32"/>
-    </row>
-    <row r="78" spans="1:12" ht="124.2" x14ac:dyDescent="0.3">
-      <c r="A78" s="63"/>
-      <c r="B78" s="66"/>
-      <c r="C78" s="34">
-        <v>22.2</v>
-      </c>
-      <c r="D78" s="33" t="s">
-        <v>302</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>303</v>
-      </c>
-      <c r="F78" s="33" t="s">
-        <v>307</v>
-      </c>
-      <c r="G78" s="31" t="s">
-        <v>179</v>
-      </c>
-      <c r="H78" s="3"/>
-      <c r="I78" s="32"/>
-    </row>
-    <row r="79" spans="1:12" ht="41.4" x14ac:dyDescent="0.3">
-      <c r="A79" s="64"/>
-      <c r="B79" s="67"/>
-      <c r="C79" s="79">
+      <c r="H79" s="71"/>
+      <c r="I79" s="74"/>
+    </row>
+    <row r="80" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A80" s="78"/>
+      <c r="B80" s="79"/>
+      <c r="C80" s="49">
         <v>22.3</v>
       </c>
-      <c r="D79" s="29" t="s">
-        <v>177</v>
-      </c>
-      <c r="E79" s="80" t="s">
-        <v>161</v>
-      </c>
-      <c r="F79" s="29"/>
-      <c r="G79" s="30"/>
-      <c r="H79" s="80"/>
-      <c r="I79" s="81"/>
-    </row>
-    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A80" s="3"/>
-      <c r="B80" s="3"/>
-      <c r="C80" s="3"/>
-      <c r="E80" s="38"/>
-      <c r="H80" s="3"/>
+      <c r="D80" s="19" t="s">
+        <v>158</v>
+      </c>
+      <c r="E80" s="49" t="s">
+        <v>148</v>
+      </c>
+      <c r="F80" s="19"/>
+      <c r="G80" s="20"/>
+      <c r="H80" s="49"/>
+      <c r="I80" s="50"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D81" s="2"/>
-      <c r="F81" s="2"/>
-      <c r="G81" s="2"/>
-      <c r="I81" s="2"/>
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
+      <c r="E81" s="11"/>
+      <c r="H81" s="3"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D82" s="2"/>
@@ -6179,109 +5951,93 @@
       <c r="I82" s="2"/>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A83" s="25"/>
-      <c r="B83" s="25"/>
-      <c r="C83" s="25"/>
-      <c r="D83" s="25"/>
-      <c r="E83" s="25"/>
-      <c r="F83" s="25"/>
-      <c r="G83" s="25"/>
-      <c r="H83" s="25"/>
-      <c r="I83" s="25"/>
+      <c r="D83" s="2"/>
+      <c r="F83" s="2"/>
+      <c r="G83" s="2"/>
+      <c r="I83" s="2"/>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A84" s="3"/>
-      <c r="B84" s="3"/>
-      <c r="C84" s="3"/>
-      <c r="D84" s="37"/>
-      <c r="E84" s="37"/>
-      <c r="F84" s="37"/>
-      <c r="G84" s="27"/>
-      <c r="H84" s="37"/>
-      <c r="I84" s="37"/>
+      <c r="A84" s="7"/>
+      <c r="B84" s="7"/>
+      <c r="C84" s="7"/>
+      <c r="D84" s="7"/>
+      <c r="E84" s="7"/>
+      <c r="F84" s="7"/>
+      <c r="G84" s="7"/>
+      <c r="H84" s="7"/>
+      <c r="I84" s="7"/>
     </row>
     <row r="85" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D85" s="37"/>
-      <c r="E85" s="37"/>
-      <c r="F85" s="37"/>
-      <c r="G85" s="27"/>
-      <c r="H85" s="37"/>
-      <c r="I85" s="37"/>
+      <c r="A85" s="3"/>
+      <c r="B85" s="3"/>
+      <c r="C85" s="3"/>
+      <c r="D85" s="10"/>
+      <c r="E85" s="10"/>
+      <c r="F85" s="10"/>
+      <c r="G85" s="8"/>
+      <c r="H85" s="10"/>
+      <c r="I85" s="10"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B86" s="3"/>
-      <c r="D86" s="37"/>
-      <c r="E86" s="37"/>
-      <c r="F86" s="37"/>
-      <c r="G86" s="27"/>
-      <c r="H86" s="37"/>
-      <c r="I86" s="37"/>
+      <c r="D86" s="10"/>
+      <c r="E86" s="10"/>
+      <c r="F86" s="10"/>
+      <c r="G86" s="8"/>
+      <c r="H86" s="10"/>
+      <c r="I86" s="10"/>
     </row>
     <row r="87" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D87" s="37"/>
-      <c r="E87" s="37"/>
-      <c r="F87" s="37"/>
-      <c r="G87" s="27"/>
-      <c r="H87" s="37"/>
-      <c r="I87" s="37"/>
+      <c r="B87" s="3"/>
+      <c r="D87" s="10"/>
+      <c r="E87" s="10"/>
+      <c r="F87" s="10"/>
+      <c r="G87" s="8"/>
+      <c r="H87" s="10"/>
+      <c r="I87" s="10"/>
     </row>
     <row r="88" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D88" s="37"/>
-      <c r="E88" s="37"/>
-      <c r="F88" s="37"/>
-      <c r="G88" s="27"/>
-      <c r="H88" s="37"/>
-      <c r="I88" s="37"/>
+      <c r="D88" s="10"/>
+      <c r="E88" s="10"/>
+      <c r="F88" s="10"/>
+      <c r="G88" s="8"/>
+      <c r="H88" s="10"/>
+      <c r="I88" s="10"/>
     </row>
     <row r="89" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D89" s="37"/>
-      <c r="E89" s="37"/>
-      <c r="F89" s="37"/>
-      <c r="G89" s="27"/>
-      <c r="H89" s="37"/>
-      <c r="I89" s="37"/>
+      <c r="D89" s="10"/>
+      <c r="E89" s="10"/>
+      <c r="F89" s="10"/>
+      <c r="G89" s="8"/>
+      <c r="H89" s="10"/>
+      <c r="I89" s="10"/>
     </row>
     <row r="90" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D90" s="37"/>
-      <c r="E90" s="37"/>
-      <c r="F90" s="37"/>
-      <c r="G90" s="27"/>
-      <c r="H90" s="37"/>
-      <c r="I90" s="37"/>
+      <c r="D90" s="10"/>
+      <c r="E90" s="10"/>
+      <c r="F90" s="10"/>
+      <c r="G90" s="8"/>
+      <c r="H90" s="10"/>
+      <c r="I90" s="10"/>
     </row>
     <row r="91" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D91" s="37"/>
-      <c r="E91" s="37"/>
-      <c r="F91" s="37"/>
-      <c r="G91" s="27"/>
-      <c r="H91" s="37"/>
-      <c r="I91" s="37"/>
+      <c r="D91" s="10"/>
+      <c r="E91" s="10"/>
+      <c r="F91" s="10"/>
+      <c r="G91" s="8"/>
+      <c r="H91" s="10"/>
+      <c r="I91" s="10"/>
+    </row>
+    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D92" s="10"/>
+      <c r="E92" s="10"/>
+      <c r="F92" s="10"/>
+      <c r="G92" s="8"/>
+      <c r="H92" s="10"/>
+      <c r="I92" s="10"/>
     </row>
   </sheetData>
   <autoFilter ref="I1:I26" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="37">
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="A29:A39"/>
-    <mergeCell ref="B29:B39"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="A40:A47"/>
-    <mergeCell ref="B40:B47"/>
-    <mergeCell ref="A74:A76"/>
-    <mergeCell ref="B74:B76"/>
-    <mergeCell ref="A77:A79"/>
-    <mergeCell ref="B77:B79"/>
-    <mergeCell ref="A48:A53"/>
-    <mergeCell ref="B48:B53"/>
-    <mergeCell ref="A54:A58"/>
-    <mergeCell ref="B54:B58"/>
-    <mergeCell ref="A59:A67"/>
-    <mergeCell ref="B59:B67"/>
-    <mergeCell ref="A68:A70"/>
-    <mergeCell ref="B68:B70"/>
-    <mergeCell ref="A71:A73"/>
-    <mergeCell ref="B71:B73"/>
     <mergeCell ref="A13:A16"/>
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="A17:A20"/>
@@ -6297,8 +6053,30 @@
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="B3:B7"/>
     <mergeCell ref="B17:B20"/>
+    <mergeCell ref="A41:A48"/>
+    <mergeCell ref="B41:B48"/>
+    <mergeCell ref="A75:A77"/>
+    <mergeCell ref="B75:B77"/>
+    <mergeCell ref="A78:A80"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="A49:A54"/>
+    <mergeCell ref="B49:B54"/>
+    <mergeCell ref="A55:A59"/>
+    <mergeCell ref="B55:B59"/>
+    <mergeCell ref="A60:A68"/>
+    <mergeCell ref="B60:B68"/>
+    <mergeCell ref="A69:A71"/>
+    <mergeCell ref="B69:B71"/>
+    <mergeCell ref="A72:A74"/>
+    <mergeCell ref="B72:B74"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="A30:A40"/>
+    <mergeCell ref="B30:B40"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="B21:B23"/>
   </mergeCells>
-  <phoneticPr fontId="11" type="noConversion"/>
+  <phoneticPr fontId="10" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <legacyDrawing r:id="rId1"/>
@@ -6317,595 +6095,595 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A1" s="28"/>
-      <c r="B1" s="28"/>
-      <c r="C1" s="28"/>
-      <c r="D1" s="28"/>
-      <c r="E1" s="28"/>
-      <c r="F1" s="28"/>
-      <c r="G1" s="28"/>
-      <c r="H1" s="28"/>
-      <c r="I1" s="28"/>
-      <c r="J1" s="28"/>
+      <c r="A1" s="9"/>
+      <c r="B1" s="9"/>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+      <c r="J1" s="9"/>
     </row>
     <row r="2" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A2" s="28"/>
-      <c r="B2" s="28"/>
-      <c r="C2" s="28"/>
-      <c r="D2" s="28"/>
-      <c r="E2" s="28"/>
-      <c r="F2" s="28"/>
-      <c r="G2" s="28"/>
-      <c r="H2" s="28"/>
-      <c r="I2" s="28"/>
-      <c r="J2" s="28"/>
+      <c r="A2" s="9"/>
+      <c r="B2" s="9"/>
+      <c r="C2" s="9"/>
+      <c r="D2" s="9"/>
+      <c r="E2" s="9"/>
+      <c r="F2" s="9"/>
+      <c r="G2" s="9"/>
+      <c r="H2" s="9"/>
+      <c r="I2" s="9"/>
+      <c r="J2" s="9"/>
     </row>
     <row r="3" spans="1:10" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A3" s="28"/>
-      <c r="B3" s="28"/>
-      <c r="C3" s="28"/>
-      <c r="D3" s="42" t="s">
+      <c r="A3" s="9"/>
+      <c r="B3" s="9"/>
+      <c r="C3" s="9"/>
+      <c r="D3" s="12" t="s">
         <v>1</v>
       </c>
-      <c r="E3" s="42" t="s">
+      <c r="E3" s="12" t="s">
         <v>2</v>
       </c>
-      <c r="F3" s="42" t="s">
+      <c r="F3" s="12" t="s">
         <v>7</v>
       </c>
-      <c r="G3" s="42" t="s">
+      <c r="G3" s="12" t="s">
         <v>8</v>
       </c>
-      <c r="H3" s="42" t="s">
+      <c r="H3" s="12" t="s">
+        <v>217</v>
+      </c>
+      <c r="I3" s="12" t="s">
+        <v>4</v>
+      </c>
+      <c r="J3" s="9"/>
+    </row>
+    <row r="4" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
+      <c r="A4" s="9"/>
+      <c r="B4" s="9"/>
+      <c r="C4" s="9"/>
+      <c r="D4" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E4" s="13">
+        <v>14.1</v>
+      </c>
+      <c r="F4" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G4" s="8" t="s">
+        <v>218</v>
+      </c>
+      <c r="H4" s="8" t="s">
+        <v>219</v>
+      </c>
+      <c r="I4" s="13" t="s">
+        <v>220</v>
+      </c>
+      <c r="J4" s="9"/>
+    </row>
+    <row r="5" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="9"/>
+      <c r="B5" s="9"/>
+      <c r="C5" s="9"/>
+      <c r="D5" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E5" s="13">
+        <v>14.2</v>
+      </c>
+      <c r="F5" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G5" s="8" t="s">
+        <v>221</v>
+      </c>
+      <c r="H5" s="8" t="s">
+        <v>222</v>
+      </c>
+      <c r="I5" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="J5" s="9"/>
+    </row>
+    <row r="6" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
+      <c r="A6" s="9"/>
+      <c r="B6" s="9"/>
+      <c r="C6" s="9"/>
+      <c r="D6" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E6" s="13">
+        <v>14.3</v>
+      </c>
+      <c r="F6" s="8" t="s">
+        <v>224</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>225</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="I6" s="13" t="s">
+        <v>227</v>
+      </c>
+      <c r="J6" s="9"/>
+    </row>
+    <row r="7" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="9"/>
+      <c r="B7" s="9"/>
+      <c r="C7" s="9"/>
+      <c r="D7" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E7" s="13">
+        <v>14.4</v>
+      </c>
+      <c r="F7" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G7" s="8" t="s">
+        <v>228</v>
+      </c>
+      <c r="H7" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="I7" s="13" t="s">
+        <v>230</v>
+      </c>
+      <c r="J7" s="9"/>
+    </row>
+    <row r="8" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="9"/>
+      <c r="B8" s="9"/>
+      <c r="C8" s="9"/>
+      <c r="D8" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E8" s="13">
+        <v>14.5</v>
+      </c>
+      <c r="F8" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G8" s="8" t="s">
+        <v>231</v>
+      </c>
+      <c r="H8" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="I8" s="13" t="s">
+        <v>233</v>
+      </c>
+      <c r="J8" s="9"/>
+    </row>
+    <row r="9" spans="1:10" ht="273.60000000000002" x14ac:dyDescent="0.3">
+      <c r="A9" s="9"/>
+      <c r="B9" s="9"/>
+      <c r="C9" s="9"/>
+      <c r="D9" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E9" s="13">
+        <v>14.6</v>
+      </c>
+      <c r="F9" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G9" s="8" t="s">
+        <v>234</v>
+      </c>
+      <c r="H9" s="8" t="s">
+        <v>235</v>
+      </c>
+      <c r="I9" s="13" t="s">
+        <v>236</v>
+      </c>
+      <c r="J9" s="9"/>
+    </row>
+    <row r="10" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
+      <c r="A10" s="9"/>
+      <c r="B10" s="9"/>
+      <c r="C10" s="9"/>
+      <c r="D10" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E10" s="13">
+        <v>14.7</v>
+      </c>
+      <c r="F10" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G10" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="H10" s="8" t="s">
         <v>238</v>
       </c>
-      <c r="I3" s="42" t="s">
-        <v>4</v>
-      </c>
-      <c r="J3" s="28"/>
-    </row>
-    <row r="4" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A4" s="28"/>
-      <c r="B4" s="28"/>
-      <c r="C4" s="28"/>
-      <c r="D4" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="E4" s="43">
-        <v>14.1</v>
-      </c>
-      <c r="F4" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="G4" s="27" t="s">
+      <c r="I10" s="13" t="s">
         <v>239</v>
       </c>
-      <c r="H4" s="27" t="s">
+      <c r="J10" s="9"/>
+    </row>
+    <row r="11" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
+      <c r="A11" s="9"/>
+      <c r="B11" s="9"/>
+      <c r="C11" s="9"/>
+      <c r="D11" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E11" s="13">
+        <v>14.8</v>
+      </c>
+      <c r="F11" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G11" s="8" t="s">
         <v>240</v>
       </c>
-      <c r="I4" s="43" t="s">
+      <c r="H11" s="8" t="s">
         <v>241</v>
       </c>
-      <c r="J4" s="28"/>
-    </row>
-    <row r="5" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="28"/>
-      <c r="B5" s="28"/>
-      <c r="C5" s="28"/>
-      <c r="D5" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="E5" s="43">
-        <v>14.2</v>
-      </c>
-      <c r="F5" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="G5" s="27" t="s">
+      <c r="I11" s="13" t="s">
         <v>242</v>
       </c>
-      <c r="H5" s="27" t="s">
+      <c r="J11" s="9"/>
+    </row>
+    <row r="12" spans="1:10" ht="302.39999999999998" x14ac:dyDescent="0.3">
+      <c r="A12" s="9"/>
+      <c r="B12" s="9"/>
+      <c r="C12" s="9"/>
+      <c r="D12" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E12" s="13">
+        <v>14.9</v>
+      </c>
+      <c r="F12" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G12" s="8" t="s">
         <v>243</v>
       </c>
-      <c r="I5" s="43" t="s">
+      <c r="H12" s="8" t="s">
         <v>244</v>
       </c>
-      <c r="J5" s="28"/>
-    </row>
-    <row r="6" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A6" s="28"/>
-      <c r="B6" s="28"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="E6" s="43">
-        <v>14.3</v>
-      </c>
-      <c r="F6" s="27" t="s">
+      <c r="I12" s="13" t="s">
         <v>245</v>
       </c>
-      <c r="G6" s="27" t="s">
+      <c r="J12" s="9"/>
+    </row>
+    <row r="13" spans="1:10" ht="388.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="9"/>
+      <c r="B13" s="9"/>
+      <c r="C13" s="9"/>
+      <c r="D13" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E13" s="13" t="s">
         <v>246</v>
       </c>
-      <c r="H6" s="27" t="s">
+      <c r="F13" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G13" s="8" t="s">
         <v>247</v>
       </c>
-      <c r="I6" s="43" t="s">
+      <c r="H13" s="8" t="s">
         <v>248</v>
       </c>
-      <c r="J6" s="28"/>
-    </row>
-    <row r="7" spans="1:10" ht="403.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="28"/>
-      <c r="B7" s="28"/>
-      <c r="C7" s="28"/>
-      <c r="D7" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="E7" s="43">
-        <v>14.4</v>
-      </c>
-      <c r="F7" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="G7" s="27" t="s">
+      <c r="I13" s="13" t="s">
         <v>249</v>
       </c>
-      <c r="H7" s="27" t="s">
+      <c r="J13" s="9"/>
+    </row>
+    <row r="14" spans="1:10" ht="288" x14ac:dyDescent="0.3">
+      <c r="A14" s="9"/>
+      <c r="B14" s="9"/>
+      <c r="C14" s="9"/>
+      <c r="D14" s="13" t="s">
+        <v>80</v>
+      </c>
+      <c r="E14" s="13">
+        <v>14.11</v>
+      </c>
+      <c r="F14" s="8" t="s">
+        <v>133</v>
+      </c>
+      <c r="G14" s="8" t="s">
         <v>250</v>
       </c>
-      <c r="I7" s="43" t="s">
+      <c r="H14" s="8" t="s">
         <v>251</v>
       </c>
-      <c r="J7" s="28"/>
-    </row>
-    <row r="8" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="28"/>
-      <c r="B8" s="28"/>
-      <c r="C8" s="28"/>
-      <c r="D8" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="E8" s="43">
-        <v>14.5</v>
-      </c>
-      <c r="F8" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="G8" s="27" t="s">
+      <c r="I14" s="13" t="s">
         <v>252</v>
       </c>
-      <c r="H8" s="27" t="s">
-        <v>253</v>
-      </c>
-      <c r="I8" s="43" t="s">
-        <v>254</v>
-      </c>
-      <c r="J8" s="28"/>
-    </row>
-    <row r="9" spans="1:10" ht="273.60000000000002" x14ac:dyDescent="0.3">
-      <c r="A9" s="28"/>
-      <c r="B9" s="28"/>
-      <c r="C9" s="28"/>
-      <c r="D9" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="E9" s="43">
-        <v>14.6</v>
-      </c>
-      <c r="F9" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="G9" s="27" t="s">
-        <v>255</v>
-      </c>
-      <c r="H9" s="27" t="s">
-        <v>256</v>
-      </c>
-      <c r="I9" s="43" t="s">
-        <v>257</v>
-      </c>
-      <c r="J9" s="28"/>
-    </row>
-    <row r="10" spans="1:10" ht="345.6" x14ac:dyDescent="0.3">
-      <c r="A10" s="28"/>
-      <c r="B10" s="28"/>
-      <c r="C10" s="28"/>
-      <c r="D10" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="E10" s="43">
-        <v>14.7</v>
-      </c>
-      <c r="F10" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="G10" s="27" t="s">
-        <v>258</v>
-      </c>
-      <c r="H10" s="27" t="s">
-        <v>259</v>
-      </c>
-      <c r="I10" s="43" t="s">
-        <v>260</v>
-      </c>
-      <c r="J10" s="28"/>
-    </row>
-    <row r="11" spans="1:10" ht="316.8" x14ac:dyDescent="0.3">
-      <c r="A11" s="28"/>
-      <c r="B11" s="28"/>
-      <c r="C11" s="28"/>
-      <c r="D11" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="E11" s="43">
-        <v>14.8</v>
-      </c>
-      <c r="F11" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="G11" s="27" t="s">
-        <v>261</v>
-      </c>
-      <c r="H11" s="27" t="s">
-        <v>262</v>
-      </c>
-      <c r="I11" s="43" t="s">
-        <v>263</v>
-      </c>
-      <c r="J11" s="28"/>
-    </row>
-    <row r="12" spans="1:10" ht="302.39999999999998" x14ac:dyDescent="0.3">
-      <c r="A12" s="28"/>
-      <c r="B12" s="28"/>
-      <c r="C12" s="28"/>
-      <c r="D12" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="E12" s="43">
-        <v>14.9</v>
-      </c>
-      <c r="F12" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="G12" s="27" t="s">
-        <v>264</v>
-      </c>
-      <c r="H12" s="27" t="s">
-        <v>265</v>
-      </c>
-      <c r="I12" s="43" t="s">
-        <v>266</v>
-      </c>
-      <c r="J12" s="28"/>
-    </row>
-    <row r="13" spans="1:10" ht="388.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="28"/>
-      <c r="B13" s="28"/>
-      <c r="C13" s="28"/>
-      <c r="D13" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="E13" s="43" t="s">
-        <v>267</v>
-      </c>
-      <c r="F13" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="G13" s="27" t="s">
-        <v>268</v>
-      </c>
-      <c r="H13" s="27" t="s">
-        <v>269</v>
-      </c>
-      <c r="I13" s="43" t="s">
-        <v>270</v>
-      </c>
-      <c r="J13" s="28"/>
-    </row>
-    <row r="14" spans="1:10" ht="288" x14ac:dyDescent="0.3">
-      <c r="A14" s="28"/>
-      <c r="B14" s="28"/>
-      <c r="C14" s="28"/>
-      <c r="D14" s="43" t="s">
-        <v>82</v>
-      </c>
-      <c r="E14" s="43">
-        <v>14.11</v>
-      </c>
-      <c r="F14" s="27" t="s">
-        <v>135</v>
-      </c>
-      <c r="G14" s="27" t="s">
-        <v>271</v>
-      </c>
-      <c r="H14" s="27" t="s">
-        <v>272</v>
-      </c>
-      <c r="I14" s="43" t="s">
-        <v>273</v>
-      </c>
-      <c r="J14" s="28"/>
+      <c r="J14" s="9"/>
     </row>
     <row r="15" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A15" s="28"/>
-      <c r="B15" s="28"/>
-      <c r="C15" s="28"/>
-      <c r="D15" s="28"/>
-      <c r="E15" s="28"/>
-      <c r="F15" s="28"/>
-      <c r="G15" s="28"/>
-      <c r="H15" s="28"/>
-      <c r="I15" s="28"/>
-      <c r="J15" s="28"/>
+      <c r="A15" s="9"/>
+      <c r="B15" s="9"/>
+      <c r="C15" s="9"/>
+      <c r="D15" s="9"/>
+      <c r="E15" s="9"/>
+      <c r="F15" s="9"/>
+      <c r="G15" s="9"/>
+      <c r="H15" s="9"/>
+      <c r="I15" s="9"/>
+      <c r="J15" s="9"/>
     </row>
     <row r="16" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A16" s="28"/>
-      <c r="B16" s="28"/>
-      <c r="C16" s="28"/>
-      <c r="D16" s="28"/>
-      <c r="E16" s="28"/>
-      <c r="F16" s="28"/>
-      <c r="G16" s="28"/>
-      <c r="H16" s="28"/>
-      <c r="I16" s="28"/>
-      <c r="J16" s="28"/>
+      <c r="A16" s="9"/>
+      <c r="B16" s="9"/>
+      <c r="C16" s="9"/>
+      <c r="D16" s="9"/>
+      <c r="E16" s="9"/>
+      <c r="F16" s="9"/>
+      <c r="G16" s="9"/>
+      <c r="H16" s="9"/>
+      <c r="I16" s="9"/>
+      <c r="J16" s="9"/>
     </row>
     <row r="17" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A17" s="28"/>
-      <c r="B17" s="28"/>
-      <c r="C17" s="28"/>
-      <c r="D17" s="28"/>
-      <c r="E17" s="28"/>
-      <c r="F17" s="28"/>
-      <c r="G17" s="28"/>
-      <c r="H17" s="28"/>
-      <c r="I17" s="28"/>
-      <c r="J17" s="28"/>
+      <c r="A17" s="9"/>
+      <c r="B17" s="9"/>
+      <c r="C17" s="9"/>
+      <c r="D17" s="9"/>
+      <c r="E17" s="9"/>
+      <c r="F17" s="9"/>
+      <c r="G17" s="9"/>
+      <c r="H17" s="9"/>
+      <c r="I17" s="9"/>
+      <c r="J17" s="9"/>
     </row>
     <row r="18" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A18" s="28"/>
-      <c r="B18" s="28"/>
-      <c r="C18" s="28"/>
-      <c r="D18" s="28"/>
-      <c r="E18" s="28"/>
-      <c r="F18" s="28"/>
-      <c r="G18" s="28"/>
-      <c r="H18" s="28"/>
-      <c r="I18" s="28"/>
-      <c r="J18" s="28"/>
+      <c r="A18" s="9"/>
+      <c r="B18" s="9"/>
+      <c r="C18" s="9"/>
+      <c r="D18" s="9"/>
+      <c r="E18" s="9"/>
+      <c r="F18" s="9"/>
+      <c r="G18" s="9"/>
+      <c r="H18" s="9"/>
+      <c r="I18" s="9"/>
+      <c r="J18" s="9"/>
     </row>
     <row r="19" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A19" s="28"/>
-      <c r="B19" s="28"/>
-      <c r="C19" s="28"/>
-      <c r="D19" s="28"/>
-      <c r="E19" s="28"/>
-      <c r="F19" s="28"/>
-      <c r="G19" s="28"/>
-      <c r="H19" s="28"/>
-      <c r="I19" s="28"/>
-      <c r="J19" s="28"/>
+      <c r="A19" s="9"/>
+      <c r="B19" s="9"/>
+      <c r="C19" s="9"/>
+      <c r="D19" s="9"/>
+      <c r="E19" s="9"/>
+      <c r="F19" s="9"/>
+      <c r="G19" s="9"/>
+      <c r="H19" s="9"/>
+      <c r="I19" s="9"/>
+      <c r="J19" s="9"/>
     </row>
     <row r="20" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A20" s="28"/>
-      <c r="B20" s="28"/>
-      <c r="C20" s="28"/>
-      <c r="D20" s="28"/>
-      <c r="E20" s="28"/>
-      <c r="F20" s="28"/>
-      <c r="G20" s="28"/>
-      <c r="H20" s="28"/>
-      <c r="I20" s="28"/>
-      <c r="J20" s="28"/>
+      <c r="A20" s="9"/>
+      <c r="B20" s="9"/>
+      <c r="C20" s="9"/>
+      <c r="D20" s="9"/>
+      <c r="E20" s="9"/>
+      <c r="F20" s="9"/>
+      <c r="G20" s="9"/>
+      <c r="H20" s="9"/>
+      <c r="I20" s="9"/>
+      <c r="J20" s="9"/>
     </row>
     <row r="21" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A21" s="28"/>
-      <c r="B21" s="28"/>
-      <c r="C21" s="28"/>
-      <c r="D21" s="28"/>
-      <c r="E21" s="28"/>
-      <c r="F21" s="28"/>
-      <c r="G21" s="28"/>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28"/>
-      <c r="J21" s="28"/>
+      <c r="A21" s="9"/>
+      <c r="B21" s="9"/>
+      <c r="C21" s="9"/>
+      <c r="D21" s="9"/>
+      <c r="E21" s="9"/>
+      <c r="F21" s="9"/>
+      <c r="G21" s="9"/>
+      <c r="H21" s="9"/>
+      <c r="I21" s="9"/>
+      <c r="J21" s="9"/>
     </row>
     <row r="22" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A22" s="28"/>
-      <c r="B22" s="28"/>
-      <c r="C22" s="28"/>
-      <c r="D22" s="28"/>
-      <c r="E22" s="28"/>
-      <c r="F22" s="28"/>
-      <c r="G22" s="28"/>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28"/>
-      <c r="J22" s="28"/>
+      <c r="A22" s="9"/>
+      <c r="B22" s="9"/>
+      <c r="C22" s="9"/>
+      <c r="D22" s="9"/>
+      <c r="E22" s="9"/>
+      <c r="F22" s="9"/>
+      <c r="G22" s="9"/>
+      <c r="H22" s="9"/>
+      <c r="I22" s="9"/>
+      <c r="J22" s="9"/>
     </row>
     <row r="23" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A23" s="28"/>
-      <c r="B23" s="28"/>
-      <c r="C23" s="28"/>
-      <c r="D23" s="28"/>
-      <c r="E23" s="28"/>
-      <c r="F23" s="28"/>
-      <c r="G23" s="28"/>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28"/>
-      <c r="J23" s="28"/>
+      <c r="A23" s="9"/>
+      <c r="B23" s="9"/>
+      <c r="C23" s="9"/>
+      <c r="D23" s="9"/>
+      <c r="E23" s="9"/>
+      <c r="F23" s="9"/>
+      <c r="G23" s="9"/>
+      <c r="H23" s="9"/>
+      <c r="I23" s="9"/>
+      <c r="J23" s="9"/>
     </row>
     <row r="24" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A24" s="28"/>
-      <c r="B24" s="28"/>
-      <c r="C24" s="28"/>
-      <c r="D24" s="28"/>
-      <c r="E24" s="28"/>
-      <c r="F24" s="28"/>
-      <c r="G24" s="28"/>
-      <c r="H24" s="28"/>
-      <c r="I24" s="28"/>
-      <c r="J24" s="28"/>
+      <c r="A24" s="9"/>
+      <c r="B24" s="9"/>
+      <c r="C24" s="9"/>
+      <c r="D24" s="9"/>
+      <c r="E24" s="9"/>
+      <c r="F24" s="9"/>
+      <c r="G24" s="9"/>
+      <c r="H24" s="9"/>
+      <c r="I24" s="9"/>
+      <c r="J24" s="9"/>
     </row>
     <row r="25" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A25" s="28"/>
-      <c r="B25" s="28"/>
-      <c r="C25" s="28"/>
-      <c r="D25" s="28"/>
-      <c r="E25" s="28"/>
-      <c r="F25" s="28"/>
-      <c r="G25" s="28"/>
-      <c r="H25" s="28"/>
-      <c r="I25" s="28"/>
-      <c r="J25" s="28"/>
+      <c r="A25" s="9"/>
+      <c r="B25" s="9"/>
+      <c r="C25" s="9"/>
+      <c r="D25" s="9"/>
+      <c r="E25" s="9"/>
+      <c r="F25" s="9"/>
+      <c r="G25" s="9"/>
+      <c r="H25" s="9"/>
+      <c r="I25" s="9"/>
+      <c r="J25" s="9"/>
     </row>
     <row r="26" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A26" s="28"/>
-      <c r="B26" s="28"/>
-      <c r="C26" s="28"/>
-      <c r="D26" s="28"/>
-      <c r="E26" s="28"/>
-      <c r="F26" s="28"/>
-      <c r="G26" s="28"/>
-      <c r="H26" s="28"/>
-      <c r="I26" s="28"/>
-      <c r="J26" s="28"/>
+      <c r="A26" s="9"/>
+      <c r="B26" s="9"/>
+      <c r="C26" s="9"/>
+      <c r="D26" s="9"/>
+      <c r="E26" s="9"/>
+      <c r="F26" s="9"/>
+      <c r="G26" s="9"/>
+      <c r="H26" s="9"/>
+      <c r="I26" s="9"/>
+      <c r="J26" s="9"/>
     </row>
     <row r="27" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A27" s="28"/>
-      <c r="B27" s="28"/>
-      <c r="C27" s="28"/>
-      <c r="D27" s="28"/>
-      <c r="E27" s="28"/>
-      <c r="F27" s="28"/>
-      <c r="G27" s="28"/>
-      <c r="H27" s="28"/>
-      <c r="I27" s="28"/>
-      <c r="J27" s="28"/>
+      <c r="A27" s="9"/>
+      <c r="B27" s="9"/>
+      <c r="C27" s="9"/>
+      <c r="D27" s="9"/>
+      <c r="E27" s="9"/>
+      <c r="F27" s="9"/>
+      <c r="G27" s="9"/>
+      <c r="H27" s="9"/>
+      <c r="I27" s="9"/>
+      <c r="J27" s="9"/>
     </row>
     <row r="28" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A28" s="28"/>
-      <c r="B28" s="28"/>
-      <c r="C28" s="28"/>
-      <c r="D28" s="28"/>
-      <c r="E28" s="28"/>
-      <c r="F28" s="28"/>
-      <c r="G28" s="28"/>
-      <c r="H28" s="28"/>
-      <c r="I28" s="28"/>
-      <c r="J28" s="28"/>
+      <c r="A28" s="9"/>
+      <c r="B28" s="9"/>
+      <c r="C28" s="9"/>
+      <c r="D28" s="9"/>
+      <c r="E28" s="9"/>
+      <c r="F28" s="9"/>
+      <c r="G28" s="9"/>
+      <c r="H28" s="9"/>
+      <c r="I28" s="9"/>
+      <c r="J28" s="9"/>
     </row>
     <row r="29" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A29" s="28"/>
-      <c r="B29" s="28"/>
-      <c r="C29" s="28"/>
-      <c r="D29" s="28"/>
-      <c r="E29" s="28"/>
-      <c r="F29" s="28"/>
-      <c r="G29" s="28"/>
-      <c r="H29" s="28"/>
-      <c r="I29" s="28"/>
-      <c r="J29" s="28"/>
+      <c r="A29" s="9"/>
+      <c r="B29" s="9"/>
+      <c r="C29" s="9"/>
+      <c r="D29" s="9"/>
+      <c r="E29" s="9"/>
+      <c r="F29" s="9"/>
+      <c r="G29" s="9"/>
+      <c r="H29" s="9"/>
+      <c r="I29" s="9"/>
+      <c r="J29" s="9"/>
     </row>
     <row r="30" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A30" s="28"/>
-      <c r="B30" s="28"/>
-      <c r="C30" s="28"/>
-      <c r="D30" s="28"/>
-      <c r="E30" s="28"/>
-      <c r="F30" s="28"/>
-      <c r="G30" s="28"/>
-      <c r="H30" s="28"/>
-      <c r="I30" s="28"/>
-      <c r="J30" s="28"/>
+      <c r="A30" s="9"/>
+      <c r="B30" s="9"/>
+      <c r="C30" s="9"/>
+      <c r="D30" s="9"/>
+      <c r="E30" s="9"/>
+      <c r="F30" s="9"/>
+      <c r="G30" s="9"/>
+      <c r="H30" s="9"/>
+      <c r="I30" s="9"/>
+      <c r="J30" s="9"/>
     </row>
     <row r="31" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A31" s="28"/>
-      <c r="B31" s="28"/>
-      <c r="C31" s="28"/>
-      <c r="D31" s="28"/>
-      <c r="E31" s="28"/>
-      <c r="F31" s="28"/>
-      <c r="G31" s="28"/>
-      <c r="H31" s="28"/>
-      <c r="I31" s="28"/>
-      <c r="J31" s="28"/>
+      <c r="A31" s="9"/>
+      <c r="B31" s="9"/>
+      <c r="C31" s="9"/>
+      <c r="D31" s="9"/>
+      <c r="E31" s="9"/>
+      <c r="F31" s="9"/>
+      <c r="G31" s="9"/>
+      <c r="H31" s="9"/>
+      <c r="I31" s="9"/>
+      <c r="J31" s="9"/>
     </row>
     <row r="32" spans="1:10" x14ac:dyDescent="0.3">
-      <c r="A32" s="28"/>
-      <c r="B32" s="28"/>
-      <c r="C32" s="28"/>
-      <c r="D32" s="28"/>
-      <c r="E32" s="28"/>
-      <c r="F32" s="28"/>
-      <c r="G32" s="28"/>
-      <c r="H32" s="28"/>
-      <c r="I32" s="28"/>
-      <c r="J32" s="28"/>
+      <c r="A32" s="9"/>
+      <c r="B32" s="9"/>
+      <c r="C32" s="9"/>
+      <c r="D32" s="9"/>
+      <c r="E32" s="9"/>
+      <c r="F32" s="9"/>
+      <c r="G32" s="9"/>
+      <c r="H32" s="9"/>
+      <c r="I32" s="9"/>
+      <c r="J32" s="9"/>
     </row>
     <row r="33" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A33" s="28"/>
-      <c r="B33" s="28"/>
-      <c r="C33" s="28"/>
-      <c r="D33" s="28"/>
-      <c r="E33" s="28"/>
+      <c r="A33" s="9"/>
+      <c r="B33" s="9"/>
+      <c r="C33" s="9"/>
+      <c r="D33" s="9"/>
+      <c r="E33" s="9"/>
     </row>
     <row r="34" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A34" s="28"/>
-      <c r="B34" s="28"/>
-      <c r="C34" s="28"/>
-      <c r="D34" s="28"/>
-      <c r="E34" s="28"/>
+      <c r="A34" s="9"/>
+      <c r="B34" s="9"/>
+      <c r="C34" s="9"/>
+      <c r="D34" s="9"/>
+      <c r="E34" s="9"/>
     </row>
     <row r="35" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A35" s="28"/>
-      <c r="B35" s="28"/>
-      <c r="C35" s="28"/>
-      <c r="D35" s="28"/>
-      <c r="E35" s="28"/>
+      <c r="A35" s="9"/>
+      <c r="B35" s="9"/>
+      <c r="C35" s="9"/>
+      <c r="D35" s="9"/>
+      <c r="E35" s="9"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A36" s="28"/>
-      <c r="B36" s="28"/>
-      <c r="C36" s="28"/>
-      <c r="D36" s="28"/>
-      <c r="E36" s="28"/>
+      <c r="A36" s="9"/>
+      <c r="B36" s="9"/>
+      <c r="C36" s="9"/>
+      <c r="D36" s="9"/>
+      <c r="E36" s="9"/>
     </row>
     <row r="37" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A37" s="28"/>
-      <c r="B37" s="28"/>
-      <c r="C37" s="28"/>
-      <c r="D37" s="28"/>
-      <c r="E37" s="28"/>
+      <c r="A37" s="9"/>
+      <c r="B37" s="9"/>
+      <c r="C37" s="9"/>
+      <c r="D37" s="9"/>
+      <c r="E37" s="9"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A38" s="28"/>
-      <c r="B38" s="28"/>
-      <c r="C38" s="28"/>
-      <c r="D38" s="28"/>
-      <c r="E38" s="28"/>
+      <c r="A38" s="9"/>
+      <c r="B38" s="9"/>
+      <c r="C38" s="9"/>
+      <c r="D38" s="9"/>
+      <c r="E38" s="9"/>
     </row>
     <row r="39" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A39" s="28"/>
-      <c r="B39" s="28"/>
-      <c r="C39" s="28"/>
-      <c r="D39" s="28"/>
-      <c r="E39" s="28"/>
+      <c r="A39" s="9"/>
+      <c r="B39" s="9"/>
+      <c r="C39" s="9"/>
+      <c r="D39" s="9"/>
+      <c r="E39" s="9"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A40" s="28"/>
-      <c r="B40" s="28"/>
-      <c r="C40" s="28"/>
-      <c r="D40" s="28"/>
-      <c r="E40" s="28"/>
+      <c r="A40" s="9"/>
+      <c r="B40" s="9"/>
+      <c r="C40" s="9"/>
+      <c r="D40" s="9"/>
+      <c r="E40" s="9"/>
     </row>
     <row r="41" spans="1:5" x14ac:dyDescent="0.3">
-      <c r="A41" s="28"/>
-      <c r="B41" s="28"/>
-      <c r="C41" s="28"/>
-      <c r="D41" s="28"/>
-      <c r="E41" s="28"/>
+      <c r="A41" s="9"/>
+      <c r="B41" s="9"/>
+      <c r="C41" s="9"/>
+      <c r="D41" s="9"/>
+      <c r="E41" s="9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Soubhanik/checkupp_product_backlog_final.xlsx
+++ b/Soubhanik/checkupp_product_backlog_final.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\Anodiam\2026\CheckUpp_Parent\CheckUpp\Soubhanik\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Soubhanik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{43CB0B16-3146-438B-94C7-AFE204B96F65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E4E8CF-3396-47EF-8A96-4CC709A97038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -3241,11 +3241,18 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -3532,7 +3539,7 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="80">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
@@ -3545,10 +3552,10 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="6" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
@@ -3566,211 +3573,211 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="15" borderId="0" xfId="0" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="16" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="17" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="12" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4006,34 +4013,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="15" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="15" t="s">
+      <c r="B1" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="15" t="s">
+      <c r="C1" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="15" t="s">
+      <c r="D1" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="17"/>
-      <c r="F1" s="17"/>
-      <c r="G1" s="16" t="s">
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="15" t="s">
+      <c r="H1" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="15" t="s">
+      <c r="I1" s="55" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="17"/>
-      <c r="B2" s="17"/>
-      <c r="C2" s="17"/>
+      <c r="A2" s="56"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
@@ -4043,1899 +4050,1899 @@
       <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="16"/>
-      <c r="H2" s="17"/>
-      <c r="I2" s="17"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
     </row>
     <row r="3" spans="1:9" s="5" customFormat="1" ht="156" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="18">
+      <c r="A3" s="61">
         <v>1</v>
       </c>
-      <c r="B3" s="18" t="s">
+      <c r="B3" s="61" t="s">
         <v>10</v>
       </c>
-      <c r="C3" s="19">
+      <c r="C3" s="16">
         <v>1.1000000000000001</v>
       </c>
-      <c r="D3" s="19" t="s">
+      <c r="D3" s="16" t="s">
         <v>166</v>
       </c>
-      <c r="E3" s="19" t="s">
+      <c r="E3" s="16" t="s">
         <v>165</v>
       </c>
-      <c r="F3" s="19" t="s">
+      <c r="F3" s="16" t="s">
         <v>174</v>
       </c>
-      <c r="G3" s="20" t="s">
+      <c r="G3" s="17" t="s">
         <v>177</v>
       </c>
-      <c r="H3" s="19" t="s">
+      <c r="H3" s="16" t="s">
         <v>11</v>
       </c>
-      <c r="I3" s="19" t="s">
+      <c r="I3" s="16" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="6" customFormat="1" ht="130.05000000000001" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A4" s="18"/>
-      <c r="B4" s="18"/>
-      <c r="C4" s="19">
+    <row r="4" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
+      <c r="A4" s="61"/>
+      <c r="B4" s="61"/>
+      <c r="C4" s="16">
         <v>1.2</v>
       </c>
-      <c r="D4" s="19" t="s">
+      <c r="D4" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="E4" s="19" t="s">
+      <c r="E4" s="16" t="s">
         <v>170</v>
       </c>
-      <c r="F4" s="19" t="s">
+      <c r="F4" s="16" t="s">
         <v>159</v>
       </c>
-      <c r="G4" s="20" t="s">
+      <c r="G4" s="17" t="s">
         <v>168</v>
       </c>
-      <c r="H4" s="19"/>
-      <c r="I4" s="19"/>
+      <c r="H4" s="16"/>
+      <c r="I4" s="16"/>
     </row>
     <row r="5" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A5" s="18"/>
-      <c r="B5" s="18"/>
-      <c r="C5" s="19">
+      <c r="A5" s="61"/>
+      <c r="B5" s="61"/>
+      <c r="C5" s="16">
         <v>1.3</v>
       </c>
-      <c r="D5" s="19" t="s">
+      <c r="D5" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="E5" s="19" t="s">
+      <c r="E5" s="16" t="s">
         <v>171</v>
       </c>
-      <c r="F5" s="19" t="s">
+      <c r="F5" s="16" t="s">
         <v>160</v>
       </c>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="17" t="s">
         <v>169</v>
       </c>
-      <c r="H5" s="19"/>
-      <c r="I5" s="19"/>
+      <c r="H5" s="16"/>
+      <c r="I5" s="16"/>
     </row>
     <row r="6" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A6" s="18"/>
-      <c r="B6" s="18"/>
-      <c r="C6" s="19">
+      <c r="A6" s="61"/>
+      <c r="B6" s="61"/>
+      <c r="C6" s="16">
         <v>1.4</v>
       </c>
-      <c r="D6" s="19" t="s">
+      <c r="D6" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="E6" s="19" t="s">
+      <c r="E6" s="16" t="s">
         <v>172</v>
       </c>
-      <c r="F6" s="19" t="s">
+      <c r="F6" s="16" t="s">
         <v>161</v>
       </c>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="17" t="s">
         <v>167</v>
       </c>
-      <c r="H6" s="19"/>
-      <c r="I6" s="19"/>
+      <c r="H6" s="16"/>
+      <c r="I6" s="16"/>
     </row>
     <row r="7" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="18"/>
-      <c r="B7" s="18"/>
-      <c r="C7" s="19">
+      <c r="A7" s="61"/>
+      <c r="B7" s="61"/>
+      <c r="C7" s="16">
         <v>1.5</v>
       </c>
-      <c r="D7" s="19" t="s">
+      <c r="D7" s="16" t="s">
         <v>176</v>
       </c>
-      <c r="E7" s="19" t="s">
+      <c r="E7" s="16" t="s">
         <v>173</v>
       </c>
-      <c r="F7" s="19" t="s">
+      <c r="F7" s="16" t="s">
         <v>162</v>
       </c>
-      <c r="G7" s="20" t="s">
+      <c r="G7" s="17" t="s">
         <v>175</v>
       </c>
-      <c r="H7" s="19"/>
-      <c r="I7" s="19"/>
+      <c r="H7" s="16"/>
+      <c r="I7" s="16"/>
     </row>
     <row r="8" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="21">
+      <c r="A8" s="57">
         <v>5</v>
       </c>
-      <c r="B8" s="21" t="s">
+      <c r="B8" s="57" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="22">
+      <c r="C8" s="18">
         <v>5.0999999999999996</v>
       </c>
-      <c r="D8" s="22" t="s">
+      <c r="D8" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="22" t="s">
+      <c r="E8" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="22" t="s">
+      <c r="F8" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="23" t="s">
+      <c r="G8" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="24" t="s">
+      <c r="H8" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="22" t="s">
+      <c r="I8" s="18" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="9" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="25"/>
-      <c r="B9" s="25"/>
-      <c r="C9" s="22">
+      <c r="A9" s="58"/>
+      <c r="B9" s="58"/>
+      <c r="C9" s="18">
         <v>5.2</v>
       </c>
-      <c r="D9" s="22" t="s">
+      <c r="D9" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="22" t="s">
+      <c r="E9" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="22" t="s">
+      <c r="F9" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="23" t="s">
+      <c r="G9" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="24"/>
-      <c r="I9" s="22"/>
+      <c r="H9" s="20"/>
+      <c r="I9" s="18"/>
     </row>
     <row r="10" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="25"/>
-      <c r="B10" s="25"/>
-      <c r="C10" s="22">
+      <c r="A10" s="58"/>
+      <c r="B10" s="58"/>
+      <c r="C10" s="18">
         <v>5.3</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="22" t="s">
+      <c r="F10" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="23" t="s">
+      <c r="G10" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="24"/>
-      <c r="I10" s="22"/>
+      <c r="H10" s="20"/>
+      <c r="I10" s="18"/>
     </row>
     <row r="11" spans="1:9" s="14" customFormat="1" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="25"/>
-      <c r="B11" s="25"/>
-      <c r="C11" s="26">
+      <c r="A11" s="58"/>
+      <c r="B11" s="58"/>
+      <c r="C11" s="21">
         <v>5.4</v>
       </c>
-      <c r="D11" s="26" t="s">
+      <c r="D11" s="21" t="s">
         <v>181</v>
       </c>
-      <c r="E11" s="26" t="s">
+      <c r="E11" s="21" t="s">
         <v>184</v>
       </c>
-      <c r="F11" s="26" t="s">
+      <c r="F11" s="21" t="s">
         <v>183</v>
       </c>
-      <c r="G11" s="27" t="s">
+      <c r="G11" s="22" t="s">
         <v>185</v>
       </c>
-      <c r="H11" s="28"/>
-      <c r="I11" s="26"/>
+      <c r="H11" s="23"/>
+      <c r="I11" s="21"/>
     </row>
     <row r="12" spans="1:9" s="14" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="29"/>
-      <c r="B12" s="29"/>
-      <c r="C12" s="26">
+      <c r="A12" s="59"/>
+      <c r="B12" s="59"/>
+      <c r="C12" s="21">
         <v>5.5</v>
       </c>
-      <c r="D12" s="26" t="s">
+      <c r="D12" s="21" t="s">
         <v>178</v>
       </c>
-      <c r="E12" s="26" t="s">
+      <c r="E12" s="21" t="s">
         <v>182</v>
       </c>
-      <c r="F12" s="26" t="s">
+      <c r="F12" s="21" t="s">
         <v>180</v>
       </c>
-      <c r="G12" s="27" t="s">
+      <c r="G12" s="22" t="s">
         <v>179</v>
       </c>
-      <c r="H12" s="28"/>
-      <c r="I12" s="26"/>
+      <c r="H12" s="23"/>
+      <c r="I12" s="21"/>
     </row>
     <row r="13" spans="1:9" s="14" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="30">
+      <c r="A13" s="49">
         <v>6</v>
       </c>
-      <c r="B13" s="30" t="s">
+      <c r="B13" s="49" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="26">
+      <c r="C13" s="21">
         <v>6.1</v>
       </c>
-      <c r="D13" s="26" t="s">
+      <c r="D13" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="26" t="s">
+      <c r="E13" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="26" t="s">
+      <c r="F13" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="27" t="s">
+      <c r="G13" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="28" t="s">
+      <c r="H13" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="I13" s="26" t="s">
+      <c r="I13" s="21" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="14" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A14" s="31"/>
-      <c r="B14" s="31"/>
-      <c r="C14" s="32">
+      <c r="A14" s="50"/>
+      <c r="B14" s="50"/>
+      <c r="C14" s="24">
         <v>6.2</v>
       </c>
-      <c r="D14" s="32" t="s">
+      <c r="D14" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="32" t="s">
+      <c r="E14" s="24" t="s">
         <v>187</v>
       </c>
-      <c r="F14" s="32" t="s">
+      <c r="F14" s="24" t="s">
         <v>186</v>
       </c>
-      <c r="G14" s="33" t="s">
+      <c r="G14" s="25" t="s">
         <v>188</v>
       </c>
-      <c r="H14" s="34"/>
-      <c r="I14" s="32"/>
-    </row>
-    <row r="15" spans="1:9" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A15" s="31"/>
-      <c r="B15" s="31"/>
-      <c r="C15" s="32">
+      <c r="H14" s="26"/>
+      <c r="I14" s="24"/>
+    </row>
+    <row r="15" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A15" s="50"/>
+      <c r="B15" s="50"/>
+      <c r="C15" s="24">
         <v>6.3</v>
       </c>
-      <c r="D15" s="32" t="s">
+      <c r="D15" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="32" t="s">
+      <c r="E15" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="F15" s="32" t="s">
+      <c r="F15" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="G15" s="33" t="s">
+      <c r="G15" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="34"/>
-      <c r="I15" s="32"/>
+      <c r="H15" s="26"/>
+      <c r="I15" s="24"/>
     </row>
     <row r="16" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A16" s="31"/>
-      <c r="B16" s="35"/>
-      <c r="C16" s="36">
+      <c r="A16" s="50"/>
+      <c r="B16" s="51"/>
+      <c r="C16" s="27">
         <v>6.4</v>
       </c>
-      <c r="D16" s="32" t="s">
+      <c r="D16" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="32" t="s">
+      <c r="E16" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="32" t="s">
+      <c r="F16" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="G16" s="33" t="s">
+      <c r="G16" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="H16" s="34" t="s">
+      <c r="H16" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="I16" s="32" t="s">
+      <c r="I16" s="24" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="17" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A17" s="37">
+      <c r="A17" s="52">
         <v>7</v>
       </c>
-      <c r="B17" s="30" t="s">
+      <c r="B17" s="49" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="32">
+      <c r="C17" s="24">
         <v>7.1</v>
       </c>
-      <c r="D17" s="32" t="s">
+      <c r="D17" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E17" s="32" t="s">
+      <c r="E17" s="24" t="s">
         <v>40</v>
       </c>
-      <c r="F17" s="32" t="s">
+      <c r="F17" s="24" t="s">
         <v>41</v>
       </c>
-      <c r="G17" s="33" t="s">
+      <c r="G17" s="25" t="s">
         <v>42</v>
       </c>
-      <c r="H17" s="34" t="s">
+      <c r="H17" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="I17" s="32" t="s">
+      <c r="I17" s="24" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="18" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A18" s="38"/>
-      <c r="B18" s="31"/>
-      <c r="C18" s="32">
+      <c r="A18" s="53"/>
+      <c r="B18" s="50"/>
+      <c r="C18" s="24">
         <v>7.2</v>
       </c>
-      <c r="D18" s="32" t="s">
+      <c r="D18" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E18" s="32" t="s">
+      <c r="E18" s="24" t="s">
         <v>43</v>
       </c>
-      <c r="F18" s="32" t="s">
+      <c r="F18" s="24" t="s">
         <v>44</v>
       </c>
-      <c r="G18" s="33" t="s">
+      <c r="G18" s="25" t="s">
         <v>45</v>
       </c>
-      <c r="H18" s="34"/>
-      <c r="I18" s="32" t="s">
+      <c r="H18" s="26"/>
+      <c r="I18" s="24" t="s">
         <v>31</v>
       </c>
     </row>
     <row r="19" spans="1:9" s="6" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="38"/>
-      <c r="B19" s="31"/>
-      <c r="C19" s="32">
+      <c r="A19" s="53"/>
+      <c r="B19" s="50"/>
+      <c r="C19" s="24">
         <v>7.3</v>
       </c>
-      <c r="D19" s="32" t="s">
+      <c r="D19" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E19" s="32" t="s">
+      <c r="E19" s="24" t="s">
         <v>163</v>
       </c>
-      <c r="F19" s="32" t="s">
+      <c r="F19" s="24" t="s">
         <v>46</v>
       </c>
-      <c r="G19" s="33" t="s">
+      <c r="G19" s="25" t="s">
         <v>47</v>
       </c>
-      <c r="H19" s="34"/>
-      <c r="I19" s="32"/>
+      <c r="H19" s="26"/>
+      <c r="I19" s="24"/>
     </row>
     <row r="20" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="39"/>
-      <c r="B20" s="35"/>
-      <c r="C20" s="32">
+      <c r="A20" s="54"/>
+      <c r="B20" s="51"/>
+      <c r="C20" s="24">
         <v>7.4</v>
       </c>
-      <c r="D20" s="32" t="s">
+      <c r="D20" s="24" t="s">
         <v>39</v>
       </c>
-      <c r="E20" s="32" t="s">
+      <c r="E20" s="24" t="s">
         <v>164</v>
       </c>
-      <c r="F20" s="32" t="s">
+      <c r="F20" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="G20" s="33" t="s">
+      <c r="G20" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="H20" s="34"/>
-      <c r="I20" s="32"/>
+      <c r="H20" s="26"/>
+      <c r="I20" s="24"/>
     </row>
     <row r="21" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="40">
+      <c r="A21" s="77">
         <v>8</v>
       </c>
-      <c r="B21" s="40" t="s">
+      <c r="B21" s="77" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="41">
+      <c r="C21" s="28">
         <v>9.1999999999999993</v>
       </c>
-      <c r="D21" s="41" t="s">
+      <c r="D21" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="41" t="s">
+      <c r="E21" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="F21" s="41" t="s">
+      <c r="F21" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="G21" s="42" t="s">
+      <c r="G21" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="H21" s="41"/>
-      <c r="I21" s="41" t="s">
+      <c r="H21" s="28"/>
+      <c r="I21" s="28" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="43"/>
-      <c r="B22" s="43"/>
-      <c r="C22" s="41">
+      <c r="A22" s="78"/>
+      <c r="B22" s="78"/>
+      <c r="C22" s="28">
         <v>9.3000000000000007</v>
       </c>
-      <c r="D22" s="41" t="s">
+      <c r="D22" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="E22" s="41" t="s">
+      <c r="E22" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="F22" s="41" t="s">
+      <c r="F22" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="G22" s="42" t="s">
+      <c r="G22" s="29" t="s">
         <v>59</v>
       </c>
-      <c r="H22" s="41"/>
-      <c r="I22" s="41" t="s">
+      <c r="H22" s="28"/>
+      <c r="I22" s="28" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="44"/>
-      <c r="B23" s="44"/>
-      <c r="C23" s="41">
+      <c r="A23" s="79"/>
+      <c r="B23" s="79"/>
+      <c r="C23" s="28">
         <v>9.4</v>
       </c>
-      <c r="D23" s="41" t="s">
+      <c r="D23" s="28" t="s">
         <v>60</v>
       </c>
-      <c r="E23" s="41" t="s">
+      <c r="E23" s="28" t="s">
         <v>61</v>
       </c>
-      <c r="F23" s="41" t="s">
+      <c r="F23" s="28" t="s">
         <v>62</v>
       </c>
-      <c r="G23" s="42" t="s">
+      <c r="G23" s="29" t="s">
         <v>63</v>
       </c>
-      <c r="H23" s="41"/>
-      <c r="I23" s="41" t="s">
+      <c r="H23" s="28"/>
+      <c r="I23" s="28" t="s">
         <v>55</v>
       </c>
     </row>
     <row r="24" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="45">
+      <c r="A24" s="75">
         <v>12</v>
       </c>
-      <c r="B24" s="45" t="s">
+      <c r="B24" s="75" t="s">
         <v>64</v>
       </c>
-      <c r="C24" s="46">
+      <c r="C24" s="31">
         <v>12.1</v>
       </c>
-      <c r="D24" s="46" t="s">
+      <c r="D24" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="E24" s="46" t="s">
+      <c r="E24" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="F24" s="46" t="s">
+      <c r="F24" s="31" t="s">
         <v>67</v>
       </c>
-      <c r="G24" s="47" t="s">
+      <c r="G24" s="32" t="s">
         <v>68</v>
       </c>
-      <c r="H24" s="46" t="s">
+      <c r="H24" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="I24" s="46" t="s">
+      <c r="I24" s="31" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="25" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="45"/>
-      <c r="B25" s="45"/>
-      <c r="C25" s="46">
+      <c r="A25" s="75"/>
+      <c r="B25" s="75"/>
+      <c r="C25" s="31">
         <v>12.2</v>
       </c>
-      <c r="D25" s="46" t="s">
+      <c r="D25" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="E25" s="46" t="s">
+      <c r="E25" s="31" t="s">
         <v>71</v>
       </c>
-      <c r="F25" s="46" t="s">
+      <c r="F25" s="31" t="s">
         <v>72</v>
       </c>
-      <c r="G25" s="47" t="s">
+      <c r="G25" s="32" t="s">
         <v>73</v>
       </c>
-      <c r="H25" s="46" t="s">
+      <c r="H25" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="I25" s="46" t="s">
+      <c r="I25" s="31" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="26" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="45"/>
-      <c r="B26" s="45"/>
-      <c r="C26" s="46">
+      <c r="A26" s="75"/>
+      <c r="B26" s="75"/>
+      <c r="C26" s="31">
         <v>12.3</v>
       </c>
-      <c r="D26" s="46" t="s">
+      <c r="D26" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="E26" s="46" t="s">
+      <c r="E26" s="31" t="s">
         <v>74</v>
       </c>
-      <c r="F26" s="46" t="s">
+      <c r="F26" s="31" t="s">
         <v>75</v>
       </c>
-      <c r="G26" s="47" t="s">
+      <c r="G26" s="32" t="s">
         <v>76</v>
       </c>
-      <c r="H26" s="46" t="s">
+      <c r="H26" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="I26" s="46" t="s">
+      <c r="I26" s="31" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="27" spans="1:9" s="6" customFormat="1" ht="123.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="45"/>
-      <c r="B27" s="45"/>
-      <c r="C27" s="46">
+      <c r="A27" s="75"/>
+      <c r="B27" s="75"/>
+      <c r="C27" s="31">
         <v>12.4</v>
       </c>
-      <c r="D27" s="46" t="s">
+      <c r="D27" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="E27" s="46" t="s">
+      <c r="E27" s="31" t="s">
         <v>283</v>
       </c>
-      <c r="F27" s="46" t="s">
+      <c r="F27" s="31" t="s">
         <v>284</v>
       </c>
-      <c r="G27" s="47" t="s">
+      <c r="G27" s="32" t="s">
         <v>285</v>
       </c>
-      <c r="H27" s="46" t="s">
+      <c r="H27" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="I27" s="46" t="s">
+      <c r="I27" s="31" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="28" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="45"/>
-      <c r="B28" s="45"/>
-      <c r="C28" s="46">
+      <c r="A28" s="75"/>
+      <c r="B28" s="75"/>
+      <c r="C28" s="31">
         <v>12.5</v>
       </c>
-      <c r="D28" s="46" t="s">
+      <c r="D28" s="31" t="s">
         <v>77</v>
       </c>
-      <c r="E28" s="46" t="s">
+      <c r="E28" s="31" t="s">
         <v>78</v>
       </c>
-      <c r="F28" s="46" t="s">
+      <c r="F28" s="31" t="s">
         <v>282</v>
       </c>
-      <c r="G28" s="47" t="s">
+      <c r="G28" s="32" t="s">
         <v>79</v>
       </c>
-      <c r="H28" s="46" t="s">
+      <c r="H28" s="31" t="s">
         <v>69</v>
       </c>
-      <c r="I28" s="46" t="s">
+      <c r="I28" s="31" t="s">
         <v>70</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="48"/>
-      <c r="B29" s="48"/>
-      <c r="C29" s="19">
+      <c r="A29" s="30"/>
+      <c r="B29" s="30"/>
+      <c r="C29" s="16">
         <v>12.6</v>
       </c>
-      <c r="D29" s="19" t="s">
+      <c r="D29" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="E29" s="19" t="s">
+      <c r="E29" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="F29" s="19"/>
-      <c r="G29" s="20"/>
-      <c r="H29" s="49"/>
-      <c r="I29" s="50"/>
+      <c r="F29" s="16"/>
+      <c r="G29" s="17"/>
+      <c r="H29" s="33"/>
+      <c r="I29" s="34"/>
     </row>
     <row r="30" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="51">
+      <c r="A30" s="76">
         <v>14</v>
       </c>
-      <c r="B30" s="51" t="s">
+      <c r="B30" s="76" t="s">
         <v>80</v>
       </c>
-      <c r="C30" s="52">
+      <c r="C30" s="35">
         <v>14.1</v>
       </c>
-      <c r="D30" s="53" t="s">
+      <c r="D30" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="E30" s="53" t="s">
+      <c r="E30" s="36" t="s">
         <v>253</v>
       </c>
-      <c r="F30" s="53" t="s">
+      <c r="F30" s="36" t="s">
         <v>219</v>
       </c>
-      <c r="G30" s="54" t="s">
+      <c r="G30" s="37" t="s">
         <v>269</v>
       </c>
-      <c r="H30" s="52" t="s">
+      <c r="H30" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="I30" s="52" t="s">
+      <c r="I30" s="35" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="51"/>
-      <c r="B31" s="51"/>
-      <c r="C31" s="52">
+      <c r="A31" s="76"/>
+      <c r="B31" s="76"/>
+      <c r="C31" s="35">
         <v>14.2</v>
       </c>
-      <c r="D31" s="53" t="s">
+      <c r="D31" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="E31" s="53" t="s">
+      <c r="E31" s="36" t="s">
         <v>254</v>
       </c>
-      <c r="F31" s="53" t="s">
+      <c r="F31" s="36" t="s">
         <v>255</v>
       </c>
-      <c r="G31" s="54" t="s">
+      <c r="G31" s="37" t="s">
         <v>270</v>
       </c>
-      <c r="H31" s="52" t="s">
+      <c r="H31" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="I31" s="52" t="s">
+      <c r="I31" s="35" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="32" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="51"/>
-      <c r="B32" s="51"/>
-      <c r="C32" s="52">
+      <c r="A32" s="76"/>
+      <c r="B32" s="76"/>
+      <c r="C32" s="35">
         <v>14.3</v>
       </c>
-      <c r="D32" s="53" t="s">
+      <c r="D32" s="36" t="s">
         <v>224</v>
       </c>
-      <c r="E32" s="53" t="s">
+      <c r="E32" s="36" t="s">
         <v>256</v>
       </c>
-      <c r="F32" s="53" t="s">
+      <c r="F32" s="36" t="s">
         <v>257</v>
       </c>
-      <c r="G32" s="54" t="s">
+      <c r="G32" s="37" t="s">
         <v>271</v>
       </c>
-      <c r="H32" s="52" t="s">
+      <c r="H32" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="I32" s="52" t="s">
+      <c r="I32" s="35" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="33" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="51"/>
-      <c r="B33" s="51"/>
-      <c r="C33" s="52">
+      <c r="A33" s="76"/>
+      <c r="B33" s="76"/>
+      <c r="C33" s="35">
         <v>14.4</v>
       </c>
-      <c r="D33" s="53" t="s">
+      <c r="D33" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="E33" s="53" t="s">
+      <c r="E33" s="36" t="s">
         <v>258</v>
       </c>
-      <c r="F33" s="53" t="s">
+      <c r="F33" s="36" t="s">
         <v>229</v>
       </c>
-      <c r="G33" s="54" t="s">
+      <c r="G33" s="37" t="s">
         <v>272</v>
       </c>
-      <c r="H33" s="52" t="s">
+      <c r="H33" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="I33" s="52" t="s">
+      <c r="I33" s="35" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="34" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="51"/>
-      <c r="B34" s="51"/>
-      <c r="C34" s="52">
+      <c r="A34" s="76"/>
+      <c r="B34" s="76"/>
+      <c r="C34" s="35">
         <v>14.5</v>
       </c>
-      <c r="D34" s="53" t="s">
+      <c r="D34" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="E34" s="53" t="s">
+      <c r="E34" s="36" t="s">
         <v>259</v>
       </c>
-      <c r="F34" s="53" t="s">
+      <c r="F34" s="36" t="s">
         <v>232</v>
       </c>
-      <c r="G34" s="54" t="s">
+      <c r="G34" s="37" t="s">
         <v>273</v>
       </c>
-      <c r="H34" s="52" t="s">
+      <c r="H34" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="I34" s="52" t="s">
+      <c r="I34" s="35" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="35" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="51"/>
-      <c r="B35" s="51"/>
-      <c r="C35" s="52">
+      <c r="A35" s="76"/>
+      <c r="B35" s="76"/>
+      <c r="C35" s="35">
         <v>14.6</v>
       </c>
-      <c r="D35" s="53" t="s">
+      <c r="D35" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="E35" s="53" t="s">
+      <c r="E35" s="36" t="s">
         <v>260</v>
       </c>
-      <c r="F35" s="53" t="s">
+      <c r="F35" s="36" t="s">
         <v>261</v>
       </c>
-      <c r="G35" s="54" t="s">
+      <c r="G35" s="37" t="s">
         <v>274</v>
       </c>
-      <c r="H35" s="52" t="s">
+      <c r="H35" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="I35" s="52" t="s">
+      <c r="I35" s="35" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="36" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="51"/>
-      <c r="B36" s="51"/>
-      <c r="C36" s="52">
+      <c r="A36" s="76"/>
+      <c r="B36" s="76"/>
+      <c r="C36" s="35">
         <v>14.7</v>
       </c>
-      <c r="D36" s="53" t="s">
+      <c r="D36" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="E36" s="53" t="s">
+      <c r="E36" s="36" t="s">
         <v>262</v>
       </c>
-      <c r="F36" s="53" t="s">
+      <c r="F36" s="36" t="s">
         <v>263</v>
       </c>
-      <c r="G36" s="54" t="s">
+      <c r="G36" s="37" t="s">
         <v>275</v>
       </c>
-      <c r="H36" s="52" t="s">
+      <c r="H36" s="35" t="s">
         <v>82</v>
       </c>
-      <c r="I36" s="52" t="s">
+      <c r="I36" s="35" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="37" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="51"/>
-      <c r="B37" s="51"/>
-      <c r="C37" s="52">
+      <c r="A37" s="76"/>
+      <c r="B37" s="76"/>
+      <c r="C37" s="35">
         <v>14.8</v>
       </c>
-      <c r="D37" s="53" t="s">
+      <c r="D37" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="E37" s="53" t="s">
+      <c r="E37" s="36" t="s">
         <v>264</v>
       </c>
-      <c r="F37" s="53" t="s">
+      <c r="F37" s="36" t="s">
         <v>265</v>
       </c>
-      <c r="G37" s="54" t="s">
+      <c r="G37" s="37" t="s">
         <v>276</v>
       </c>
-      <c r="H37" s="52" t="s">
+      <c r="H37" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="I37" s="52" t="s">
+      <c r="I37" s="35" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="38" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A38" s="51"/>
-      <c r="B38" s="51"/>
-      <c r="C38" s="52">
+      <c r="A38" s="76"/>
+      <c r="B38" s="76"/>
+      <c r="C38" s="35">
         <v>14.9</v>
       </c>
-      <c r="D38" s="53" t="s">
+      <c r="D38" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="E38" s="53" t="s">
+      <c r="E38" s="36" t="s">
         <v>266</v>
       </c>
-      <c r="F38" s="53" t="s">
+      <c r="F38" s="36" t="s">
         <v>244</v>
       </c>
-      <c r="G38" s="54" t="s">
+      <c r="G38" s="37" t="s">
         <v>277</v>
       </c>
-      <c r="H38" s="52" t="s">
+      <c r="H38" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="I38" s="52" t="s">
+      <c r="I38" s="35" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="39" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="51"/>
-      <c r="B39" s="51"/>
-      <c r="C39" s="52">
+      <c r="A39" s="76"/>
+      <c r="B39" s="76"/>
+      <c r="C39" s="35">
         <v>14.1</v>
       </c>
-      <c r="D39" s="53" t="s">
+      <c r="D39" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="E39" s="53" t="s">
+      <c r="E39" s="36" t="s">
         <v>267</v>
       </c>
-      <c r="F39" s="53" t="s">
+      <c r="F39" s="36" t="s">
         <v>248</v>
       </c>
-      <c r="G39" s="54" t="s">
+      <c r="G39" s="37" t="s">
         <v>278</v>
       </c>
-      <c r="H39" s="52" t="s">
+      <c r="H39" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="I39" s="52" t="s">
+      <c r="I39" s="35" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="40" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="51"/>
-      <c r="B40" s="51"/>
-      <c r="C40" s="52">
+      <c r="A40" s="76"/>
+      <c r="B40" s="76"/>
+      <c r="C40" s="35">
         <v>14.11</v>
       </c>
-      <c r="D40" s="53" t="s">
+      <c r="D40" s="36" t="s">
         <v>133</v>
       </c>
-      <c r="E40" s="53" t="s">
+      <c r="E40" s="36" t="s">
         <v>268</v>
       </c>
-      <c r="F40" s="53" t="s">
+      <c r="F40" s="36" t="s">
         <v>251</v>
       </c>
-      <c r="G40" s="54" t="s">
+      <c r="G40" s="37" t="s">
         <v>279</v>
       </c>
-      <c r="H40" s="52" t="s">
+      <c r="H40" s="35" t="s">
         <v>84</v>
       </c>
-      <c r="I40" s="52" t="s">
+      <c r="I40" s="35" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="41" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A41" s="55">
+      <c r="A41" s="62">
         <v>15</v>
       </c>
-      <c r="B41" s="55" t="s">
+      <c r="B41" s="62" t="s">
         <v>85</v>
       </c>
-      <c r="C41" s="56">
+      <c r="C41" s="38">
         <v>15.1</v>
       </c>
-      <c r="D41" s="56" t="s">
+      <c r="D41" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="E41" s="56" t="s">
+      <c r="E41" s="38" t="s">
         <v>87</v>
       </c>
-      <c r="F41" s="56" t="s">
+      <c r="F41" s="38" t="s">
         <v>88</v>
       </c>
-      <c r="G41" s="57" t="s">
+      <c r="G41" s="39" t="s">
         <v>189</v>
       </c>
-      <c r="H41" s="56" t="s">
+      <c r="H41" s="38" t="s">
         <v>123</v>
       </c>
-      <c r="I41" s="56" t="s">
+      <c r="I41" s="38" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="42" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="17"/>
-      <c r="B42" s="17"/>
-      <c r="C42" s="56">
+      <c r="A42" s="56"/>
+      <c r="B42" s="56"/>
+      <c r="C42" s="38">
         <v>15.2</v>
       </c>
-      <c r="D42" s="56" t="s">
+      <c r="D42" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="E42" s="56" t="s">
+      <c r="E42" s="38" t="s">
         <v>89</v>
       </c>
-      <c r="F42" s="56" t="s">
+      <c r="F42" s="38" t="s">
         <v>90</v>
       </c>
-      <c r="G42" s="57" t="s">
+      <c r="G42" s="39" t="s">
         <v>190</v>
       </c>
-      <c r="H42" s="56" t="s">
+      <c r="H42" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="I42" s="56" t="s">
+      <c r="I42" s="38" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="43" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="17"/>
-      <c r="B43" s="17"/>
-      <c r="C43" s="56">
+      <c r="A43" s="56"/>
+      <c r="B43" s="56"/>
+      <c r="C43" s="38">
         <v>15.3</v>
       </c>
-      <c r="D43" s="56" t="s">
+      <c r="D43" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="E43" s="56" t="s">
+      <c r="E43" s="38" t="s">
         <v>91</v>
       </c>
-      <c r="F43" s="56" t="s">
+      <c r="F43" s="38" t="s">
         <v>92</v>
       </c>
-      <c r="G43" s="57" t="s">
+      <c r="G43" s="39" t="s">
         <v>191</v>
       </c>
-      <c r="H43" s="56" t="s">
+      <c r="H43" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="I43" s="56" t="s">
+      <c r="I43" s="38" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="44" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A44" s="17"/>
-      <c r="B44" s="17"/>
-      <c r="C44" s="56">
+      <c r="A44" s="56"/>
+      <c r="B44" s="56"/>
+      <c r="C44" s="38">
         <v>15.4</v>
       </c>
-      <c r="D44" s="56" t="s">
+      <c r="D44" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="E44" s="56" t="s">
+      <c r="E44" s="38" t="s">
         <v>93</v>
       </c>
-      <c r="F44" s="56" t="s">
+      <c r="F44" s="38" t="s">
         <v>94</v>
       </c>
-      <c r="G44" s="57" t="s">
+      <c r="G44" s="39" t="s">
         <v>192</v>
       </c>
-      <c r="H44" s="56" t="s">
+      <c r="H44" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="I44" s="56" t="s">
+      <c r="I44" s="38" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="45" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="17"/>
-      <c r="B45" s="17"/>
-      <c r="C45" s="56">
+      <c r="A45" s="56"/>
+      <c r="B45" s="56"/>
+      <c r="C45" s="38">
         <v>15.5</v>
       </c>
-      <c r="D45" s="56" t="s">
+      <c r="D45" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="E45" s="56" t="s">
+      <c r="E45" s="38" t="s">
         <v>95</v>
       </c>
-      <c r="F45" s="56" t="s">
+      <c r="F45" s="38" t="s">
         <v>96</v>
       </c>
-      <c r="G45" s="57" t="s">
+      <c r="G45" s="39" t="s">
         <v>193</v>
       </c>
-      <c r="H45" s="56" t="s">
+      <c r="H45" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="I45" s="56" t="s">
+      <c r="I45" s="38" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="46" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="17"/>
-      <c r="B46" s="17"/>
-      <c r="C46" s="56">
+      <c r="A46" s="56"/>
+      <c r="B46" s="56"/>
+      <c r="C46" s="38">
         <v>15.6</v>
       </c>
-      <c r="D46" s="56" t="s">
+      <c r="D46" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="E46" s="56" t="s">
+      <c r="E46" s="38" t="s">
         <v>97</v>
       </c>
-      <c r="F46" s="56" t="s">
+      <c r="F46" s="38" t="s">
         <v>98</v>
       </c>
-      <c r="G46" s="57" t="s">
+      <c r="G46" s="39" t="s">
         <v>194</v>
       </c>
-      <c r="H46" s="56" t="s">
+      <c r="H46" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="I46" s="56" t="s">
+      <c r="I46" s="38" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="47" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A47" s="17"/>
-      <c r="B47" s="17"/>
-      <c r="C47" s="56">
+      <c r="A47" s="56"/>
+      <c r="B47" s="56"/>
+      <c r="C47" s="38">
         <v>15.7</v>
       </c>
-      <c r="D47" s="56" t="s">
+      <c r="D47" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="E47" s="56" t="s">
+      <c r="E47" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="F47" s="56" t="s">
+      <c r="F47" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="G47" s="57" t="s">
+      <c r="G47" s="39" t="s">
         <v>195</v>
       </c>
-      <c r="H47" s="56" t="s">
+      <c r="H47" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="I47" s="56" t="s">
+      <c r="I47" s="38" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="48" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="17"/>
-      <c r="B48" s="17"/>
-      <c r="C48" s="56">
+      <c r="A48" s="56"/>
+      <c r="B48" s="56"/>
+      <c r="C48" s="38">
         <v>15.8</v>
       </c>
-      <c r="D48" s="56" t="s">
+      <c r="D48" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="E48" s="56" t="s">
+      <c r="E48" s="38" t="s">
         <v>101</v>
       </c>
-      <c r="F48" s="56" t="s">
+      <c r="F48" s="38" t="s">
         <v>102</v>
       </c>
-      <c r="G48" s="57" t="s">
+      <c r="G48" s="39" t="s">
         <v>196</v>
       </c>
-      <c r="H48" s="56" t="s">
+      <c r="H48" s="38" t="s">
         <v>107</v>
       </c>
-      <c r="I48" s="56" t="s">
+      <c r="I48" s="38" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="49" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A49" s="58">
+      <c r="A49" s="69">
         <v>16</v>
       </c>
-      <c r="B49" s="58" t="s">
+      <c r="B49" s="69" t="s">
         <v>103</v>
       </c>
-      <c r="C49" s="59">
+      <c r="C49" s="40">
         <v>16.100000000000001</v>
       </c>
-      <c r="D49" s="60" t="s">
+      <c r="D49" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="E49" s="60" t="s">
+      <c r="E49" s="41" t="s">
         <v>105</v>
       </c>
-      <c r="F49" s="60" t="s">
+      <c r="F49" s="41" t="s">
         <v>106</v>
       </c>
-      <c r="G49" s="61" t="s">
+      <c r="G49" s="42" t="s">
         <v>197</v>
       </c>
-      <c r="H49" s="60" t="s">
+      <c r="H49" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="I49" s="60" t="s">
+      <c r="I49" s="41" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="50" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A50" s="58"/>
-      <c r="B50" s="58"/>
-      <c r="C50" s="59">
+      <c r="A50" s="69"/>
+      <c r="B50" s="69"/>
+      <c r="C50" s="40">
         <v>16.2</v>
       </c>
-      <c r="D50" s="60" t="s">
+      <c r="D50" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="E50" s="60" t="s">
+      <c r="E50" s="41" t="s">
         <v>109</v>
       </c>
-      <c r="F50" s="60" t="s">
+      <c r="F50" s="41" t="s">
         <v>110</v>
       </c>
-      <c r="G50" s="61" t="s">
+      <c r="G50" s="42" t="s">
         <v>198</v>
       </c>
-      <c r="H50" s="60" t="s">
+      <c r="H50" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="I50" s="60" t="s">
+      <c r="I50" s="41" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="51" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="58"/>
-      <c r="B51" s="58"/>
-      <c r="C51" s="59">
+      <c r="A51" s="69"/>
+      <c r="B51" s="69"/>
+      <c r="C51" s="40">
         <v>16.3</v>
       </c>
-      <c r="D51" s="60" t="s">
+      <c r="D51" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="E51" s="60" t="s">
+      <c r="E51" s="41" t="s">
         <v>111</v>
       </c>
-      <c r="F51" s="60" t="s">
+      <c r="F51" s="41" t="s">
         <v>112</v>
       </c>
-      <c r="G51" s="61" t="s">
+      <c r="G51" s="42" t="s">
         <v>199</v>
       </c>
-      <c r="H51" s="60" t="s">
+      <c r="H51" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="I51" s="60" t="s">
+      <c r="I51" s="41" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="52" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A52" s="58"/>
-      <c r="B52" s="58"/>
-      <c r="C52" s="59">
+      <c r="A52" s="69"/>
+      <c r="B52" s="69"/>
+      <c r="C52" s="40">
         <v>16.399999999999999</v>
       </c>
-      <c r="D52" s="60" t="s">
+      <c r="D52" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="E52" s="60" t="s">
+      <c r="E52" s="41" t="s">
         <v>113</v>
       </c>
-      <c r="F52" s="60" t="s">
+      <c r="F52" s="41" t="s">
         <v>114</v>
       </c>
-      <c r="G52" s="61" t="s">
+      <c r="G52" s="42" t="s">
         <v>200</v>
       </c>
-      <c r="H52" s="60" t="s">
+      <c r="H52" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="I52" s="60" t="s">
+      <c r="I52" s="41" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="53" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A53" s="58"/>
-      <c r="B53" s="58"/>
-      <c r="C53" s="59">
+      <c r="A53" s="69"/>
+      <c r="B53" s="69"/>
+      <c r="C53" s="40">
         <v>16.5</v>
       </c>
-      <c r="D53" s="60" t="s">
+      <c r="D53" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="E53" s="60" t="s">
+      <c r="E53" s="41" t="s">
         <v>115</v>
       </c>
-      <c r="F53" s="60" t="s">
+      <c r="F53" s="41" t="s">
         <v>116</v>
       </c>
-      <c r="G53" s="61" t="s">
+      <c r="G53" s="42" t="s">
         <v>201</v>
       </c>
-      <c r="H53" s="60" t="s">
+      <c r="H53" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="I53" s="60" t="s">
+      <c r="I53" s="41" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="54" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A54" s="17"/>
-      <c r="B54" s="17"/>
-      <c r="C54" s="59">
+      <c r="A54" s="56"/>
+      <c r="B54" s="56"/>
+      <c r="C54" s="40">
         <v>16.600000000000001</v>
       </c>
-      <c r="D54" s="60" t="s">
+      <c r="D54" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="E54" s="60" t="s">
+      <c r="E54" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="F54" s="60" t="s">
+      <c r="F54" s="41" t="s">
         <v>118</v>
       </c>
-      <c r="G54" s="61" t="s">
+      <c r="G54" s="42" t="s">
         <v>202</v>
       </c>
-      <c r="H54" s="60" t="s">
+      <c r="H54" s="41" t="s">
         <v>107</v>
       </c>
-      <c r="I54" s="60" t="s">
+      <c r="I54" s="41" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="55" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A55" s="62">
+      <c r="A55" s="70">
         <v>17</v>
       </c>
-      <c r="B55" s="63" t="s">
+      <c r="B55" s="73" t="s">
         <v>119</v>
       </c>
-      <c r="C55" s="64">
+      <c r="C55" s="43">
         <v>17.100000000000001</v>
       </c>
-      <c r="D55" s="64" t="s">
+      <c r="D55" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="E55" s="64" t="s">
+      <c r="E55" s="43" t="s">
         <v>121</v>
       </c>
-      <c r="F55" s="64" t="s">
+      <c r="F55" s="43" t="s">
         <v>122</v>
       </c>
-      <c r="G55" s="65" t="s">
+      <c r="G55" s="44" t="s">
         <v>203</v>
       </c>
-      <c r="H55" s="64" t="s">
+      <c r="H55" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="I55" s="64" t="s">
+      <c r="I55" s="43" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="56" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A56" s="66"/>
-      <c r="B56" s="63"/>
-      <c r="C56" s="64">
+      <c r="A56" s="71"/>
+      <c r="B56" s="73"/>
+      <c r="C56" s="43">
         <v>17.2</v>
       </c>
-      <c r="D56" s="64" t="s">
+      <c r="D56" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="E56" s="64" t="s">
+      <c r="E56" s="43" t="s">
         <v>124</v>
       </c>
-      <c r="F56" s="64" t="s">
+      <c r="F56" s="43" t="s">
         <v>125</v>
       </c>
-      <c r="G56" s="65" t="s">
+      <c r="G56" s="44" t="s">
         <v>204</v>
       </c>
-      <c r="H56" s="64" t="s">
+      <c r="H56" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="I56" s="64" t="s">
+      <c r="I56" s="43" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="57" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A57" s="66"/>
-      <c r="B57" s="63"/>
-      <c r="C57" s="64">
+      <c r="A57" s="71"/>
+      <c r="B57" s="73"/>
+      <c r="C57" s="43">
         <v>17.3</v>
       </c>
-      <c r="D57" s="64" t="s">
+      <c r="D57" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="E57" s="64" t="s">
+      <c r="E57" s="43" t="s">
         <v>126</v>
       </c>
-      <c r="F57" s="64" t="s">
+      <c r="F57" s="43" t="s">
         <v>127</v>
       </c>
-      <c r="G57" s="65" t="s">
+      <c r="G57" s="44" t="s">
         <v>205</v>
       </c>
-      <c r="H57" s="64" t="s">
+      <c r="H57" s="43" t="s">
         <v>107</v>
       </c>
-      <c r="I57" s="64" t="s">
+      <c r="I57" s="43" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="58" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A58" s="66"/>
-      <c r="B58" s="63"/>
-      <c r="C58" s="64">
+      <c r="A58" s="71"/>
+      <c r="B58" s="73"/>
+      <c r="C58" s="43">
         <v>17.399999999999999</v>
       </c>
-      <c r="D58" s="64" t="s">
+      <c r="D58" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="E58" s="64" t="s">
+      <c r="E58" s="43" t="s">
         <v>128</v>
       </c>
-      <c r="F58" s="64" t="s">
+      <c r="F58" s="43" t="s">
         <v>129</v>
       </c>
-      <c r="G58" s="65" t="s">
+      <c r="G58" s="44" t="s">
         <v>206</v>
       </c>
-      <c r="H58" s="64" t="s">
+      <c r="H58" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="I58" s="64" t="s">
+      <c r="I58" s="43" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="59" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A59" s="67"/>
-      <c r="B59" s="63"/>
-      <c r="C59" s="64">
+      <c r="A59" s="72"/>
+      <c r="B59" s="73"/>
+      <c r="C59" s="43">
         <v>17.5</v>
       </c>
-      <c r="D59" s="64" t="s">
+      <c r="D59" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="E59" s="64" t="s">
+      <c r="E59" s="43" t="s">
         <v>130</v>
       </c>
-      <c r="F59" s="64" t="s">
+      <c r="F59" s="43" t="s">
         <v>131</v>
       </c>
-      <c r="G59" s="65" t="s">
+      <c r="G59" s="44" t="s">
         <v>207</v>
       </c>
-      <c r="H59" s="64" t="s">
+      <c r="H59" s="43" t="s">
         <v>123</v>
       </c>
-      <c r="I59" s="64" t="s">
+      <c r="I59" s="43" t="s">
         <v>108</v>
       </c>
     </row>
     <row r="60" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A60" s="68">
+      <c r="A60" s="74">
         <v>18</v>
       </c>
-      <c r="B60" s="68" t="s">
+      <c r="B60" s="74" t="s">
         <v>132</v>
       </c>
-      <c r="C60" s="22">
+      <c r="C60" s="18">
         <v>17.100000000000001</v>
       </c>
-      <c r="D60" s="22" t="s">
+      <c r="D60" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="E60" s="22" t="s">
+      <c r="E60" s="18" t="s">
         <v>291</v>
       </c>
-      <c r="F60" s="22" t="s">
+      <c r="F60" s="18" t="s">
         <v>134</v>
       </c>
-      <c r="G60" s="23" t="s">
+      <c r="G60" s="19" t="s">
         <v>208</v>
       </c>
-      <c r="H60" s="22" t="s">
+      <c r="H60" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="I60" s="22" t="s">
+      <c r="I60" s="18" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="61" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A61" s="17"/>
-      <c r="B61" s="17"/>
-      <c r="C61" s="22">
+      <c r="A61" s="56"/>
+      <c r="B61" s="56"/>
+      <c r="C61" s="18">
         <v>17.2</v>
       </c>
-      <c r="D61" s="22" t="s">
+      <c r="D61" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="E61" s="22" t="s">
+      <c r="E61" s="18" t="s">
         <v>292</v>
       </c>
-      <c r="F61" s="22" t="s">
+      <c r="F61" s="18" t="s">
         <v>136</v>
       </c>
-      <c r="G61" s="23" t="s">
+      <c r="G61" s="19" t="s">
         <v>209</v>
       </c>
-      <c r="H61" s="22" t="s">
+      <c r="H61" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="I61" s="22" t="s">
+      <c r="I61" s="18" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="62" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A62" s="17"/>
-      <c r="B62" s="17"/>
-      <c r="C62" s="22">
+      <c r="A62" s="56"/>
+      <c r="B62" s="56"/>
+      <c r="C62" s="18">
         <v>17.3</v>
       </c>
-      <c r="D62" s="22" t="s">
+      <c r="D62" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="E62" s="22" t="s">
+      <c r="E62" s="18" t="s">
         <v>293</v>
       </c>
-      <c r="F62" s="22" t="s">
+      <c r="F62" s="18" t="s">
         <v>137</v>
       </c>
-      <c r="G62" s="23" t="s">
+      <c r="G62" s="19" t="s">
         <v>210</v>
       </c>
-      <c r="H62" s="22" t="s">
+      <c r="H62" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="I62" s="22" t="s">
+      <c r="I62" s="18" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="63" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A63" s="17"/>
-      <c r="B63" s="17"/>
-      <c r="C63" s="22">
+      <c r="A63" s="56"/>
+      <c r="B63" s="56"/>
+      <c r="C63" s="18">
         <v>17.399999999999999</v>
       </c>
-      <c r="D63" s="22" t="s">
+      <c r="D63" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="E63" s="22" t="s">
+      <c r="E63" s="18" t="s">
         <v>294</v>
       </c>
-      <c r="F63" s="22" t="s">
+      <c r="F63" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="G63" s="23" t="s">
+      <c r="G63" s="19" t="s">
         <v>211</v>
       </c>
-      <c r="H63" s="22" t="s">
+      <c r="H63" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="I63" s="22" t="s">
+      <c r="I63" s="18" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="64" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A64" s="17"/>
-      <c r="B64" s="17"/>
-      <c r="C64" s="22">
+      <c r="A64" s="56"/>
+      <c r="B64" s="56"/>
+      <c r="C64" s="18">
         <v>17.5</v>
       </c>
-      <c r="D64" s="22" t="s">
+      <c r="D64" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="E64" s="22" t="s">
+      <c r="E64" s="18" t="s">
         <v>295</v>
       </c>
-      <c r="F64" s="22" t="s">
+      <c r="F64" s="18" t="s">
         <v>138</v>
       </c>
-      <c r="G64" s="23" t="s">
+      <c r="G64" s="19" t="s">
         <v>212</v>
       </c>
-      <c r="H64" s="22" t="s">
+      <c r="H64" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="I64" s="22" t="s">
+      <c r="I64" s="18" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="65" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A65" s="17"/>
-      <c r="B65" s="17"/>
-      <c r="C65" s="22">
+      <c r="A65" s="56"/>
+      <c r="B65" s="56"/>
+      <c r="C65" s="18">
         <v>17.600000000000001</v>
       </c>
-      <c r="D65" s="22" t="s">
+      <c r="D65" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="E65" s="22" t="s">
+      <c r="E65" s="18" t="s">
         <v>296</v>
       </c>
-      <c r="F65" s="22" t="s">
+      <c r="F65" s="18" t="s">
         <v>139</v>
       </c>
-      <c r="G65" s="23" t="s">
+      <c r="G65" s="19" t="s">
         <v>213</v>
       </c>
-      <c r="H65" s="22" t="s">
+      <c r="H65" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="I65" s="22" t="s">
+      <c r="I65" s="18" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="66" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A66" s="17"/>
-      <c r="B66" s="17"/>
-      <c r="C66" s="22">
+      <c r="A66" s="56"/>
+      <c r="B66" s="56"/>
+      <c r="C66" s="18">
         <v>17.7</v>
       </c>
-      <c r="D66" s="22" t="s">
+      <c r="D66" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="E66" s="22" t="s">
+      <c r="E66" s="18" t="s">
         <v>297</v>
       </c>
-      <c r="F66" s="22" t="s">
+      <c r="F66" s="18" t="s">
         <v>140</v>
       </c>
-      <c r="G66" s="23" t="s">
+      <c r="G66" s="19" t="s">
         <v>214</v>
       </c>
-      <c r="H66" s="22" t="s">
+      <c r="H66" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="I66" s="22" t="s">
+      <c r="I66" s="18" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="67" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A67" s="17"/>
-      <c r="B67" s="17"/>
-      <c r="C67" s="22">
+      <c r="A67" s="56"/>
+      <c r="B67" s="56"/>
+      <c r="C67" s="18">
         <v>17.8</v>
       </c>
-      <c r="D67" s="22" t="s">
+      <c r="D67" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="E67" s="22" t="s">
+      <c r="E67" s="18" t="s">
         <v>298</v>
       </c>
-      <c r="F67" s="22" t="s">
+      <c r="F67" s="18" t="s">
         <v>141</v>
       </c>
-      <c r="G67" s="23" t="s">
+      <c r="G67" s="19" t="s">
         <v>215</v>
       </c>
-      <c r="H67" s="22" t="s">
+      <c r="H67" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="I67" s="22" t="s">
+      <c r="I67" s="18" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="68" spans="1:12" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="17"/>
-      <c r="B68" s="17"/>
-      <c r="C68" s="22">
+      <c r="A68" s="56"/>
+      <c r="B68" s="56"/>
+      <c r="C68" s="18">
         <v>17.899999999999999</v>
       </c>
-      <c r="D68" s="22" t="s">
+      <c r="D68" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="E68" s="22" t="s">
+      <c r="E68" s="18" t="s">
         <v>299</v>
       </c>
-      <c r="F68" s="22" t="s">
+      <c r="F68" s="18" t="s">
         <v>142</v>
       </c>
-      <c r="G68" s="23" t="s">
+      <c r="G68" s="19" t="s">
         <v>216</v>
       </c>
-      <c r="H68" s="22" t="s">
+      <c r="H68" s="18" t="s">
         <v>82</v>
       </c>
-      <c r="I68" s="22" t="s">
+      <c r="I68" s="18" t="s">
         <v>135</v>
       </c>
     </row>
     <row r="69" spans="1:12" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A69" s="69">
+      <c r="A69" s="63">
         <v>19</v>
       </c>
-      <c r="B69" s="70" t="s">
+      <c r="B69" s="66" t="s">
         <v>143</v>
       </c>
-      <c r="C69" s="71">
+      <c r="C69" s="45">
         <v>19.100000000000001</v>
       </c>
-      <c r="D69" s="72" t="s">
+      <c r="D69" s="46" t="s">
         <v>144</v>
       </c>
-      <c r="E69" s="72" t="s">
+      <c r="E69" s="46" t="s">
         <v>287</v>
       </c>
-      <c r="F69" s="72" t="s">
+      <c r="F69" s="46" t="s">
         <v>286</v>
       </c>
-      <c r="G69" s="73" t="s">
+      <c r="G69" s="47" t="s">
         <v>288</v>
       </c>
-      <c r="H69" s="71"/>
-      <c r="I69" s="74"/>
+      <c r="H69" s="45"/>
+      <c r="I69" s="48"/>
     </row>
     <row r="70" spans="1:12" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="75"/>
-      <c r="B70" s="76"/>
-      <c r="C70" s="77">
+      <c r="A70" s="64"/>
+      <c r="B70" s="67"/>
+      <c r="C70" s="15">
         <v>19.2</v>
       </c>
-      <c r="D70" s="72" t="s">
+      <c r="D70" s="46" t="s">
         <v>145</v>
       </c>
-      <c r="E70" s="72" t="s">
+      <c r="E70" s="46" t="s">
         <v>146</v>
       </c>
-      <c r="F70" s="72" t="s">
+      <c r="F70" s="46" t="s">
         <v>282</v>
       </c>
-      <c r="G70" s="73" t="s">
+      <c r="G70" s="47" t="s">
         <v>147</v>
       </c>
-      <c r="H70" s="71"/>
-      <c r="I70" s="74"/>
+      <c r="H70" s="45"/>
+      <c r="I70" s="48"/>
     </row>
     <row r="71" spans="1:12" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="78"/>
-      <c r="B71" s="79"/>
-      <c r="C71" s="50">
+      <c r="A71" s="65"/>
+      <c r="B71" s="68"/>
+      <c r="C71" s="34">
         <v>19.3</v>
       </c>
-      <c r="D71" s="19" t="s">
+      <c r="D71" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="E71" s="19" t="s">
+      <c r="E71" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="F71" s="19" t="s">
+      <c r="F71" s="16" t="s">
         <v>149</v>
       </c>
-      <c r="G71" s="20"/>
-      <c r="H71" s="49"/>
-      <c r="I71" s="50"/>
+      <c r="G71" s="17"/>
+      <c r="H71" s="33"/>
+      <c r="I71" s="34"/>
     </row>
     <row r="72" spans="1:12" s="6" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="69">
+      <c r="A72" s="63">
         <v>20</v>
       </c>
-      <c r="B72" s="70" t="s">
+      <c r="B72" s="66" t="s">
         <v>150</v>
       </c>
-      <c r="C72" s="71">
+      <c r="C72" s="45">
         <v>20.100000000000001</v>
       </c>
-      <c r="D72" s="72" t="s">
+      <c r="D72" s="46" t="s">
         <v>151</v>
       </c>
-      <c r="E72" s="72" t="s">
+      <c r="E72" s="46" t="s">
         <v>308</v>
       </c>
-      <c r="F72" s="72" t="s">
+      <c r="F72" s="46" t="s">
         <v>309</v>
       </c>
-      <c r="G72" s="73" t="s">
+      <c r="G72" s="47" t="s">
         <v>310</v>
       </c>
-      <c r="H72" s="71"/>
-      <c r="I72" s="74"/>
+      <c r="H72" s="45"/>
+      <c r="I72" s="48"/>
     </row>
     <row r="73" spans="1:12" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A73" s="75"/>
-      <c r="B73" s="76"/>
-      <c r="C73" s="77">
+      <c r="A73" s="64"/>
+      <c r="B73" s="67"/>
+      <c r="C73" s="15">
         <v>20.2</v>
       </c>
-      <c r="D73" s="72" t="s">
+      <c r="D73" s="46" t="s">
         <v>152</v>
       </c>
-      <c r="E73" s="72" t="s">
+      <c r="E73" s="46" t="s">
         <v>289</v>
       </c>
-      <c r="F73" s="72" t="s">
+      <c r="F73" s="46" t="s">
         <v>282</v>
       </c>
-      <c r="G73" s="73" t="s">
+      <c r="G73" s="47" t="s">
         <v>290</v>
       </c>
-      <c r="H73" s="71"/>
-      <c r="I73" s="74"/>
+      <c r="H73" s="45"/>
+      <c r="I73" s="48"/>
       <c r="J73" s="1"/>
       <c r="K73" s="1"/>
       <c r="L73" s="1"/>
     </row>
     <row r="74" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A74" s="78"/>
-      <c r="B74" s="79"/>
-      <c r="C74" s="49">
+      <c r="A74" s="65"/>
+      <c r="B74" s="68"/>
+      <c r="C74" s="33">
         <v>20.3</v>
       </c>
-      <c r="D74" s="19" t="s">
+      <c r="D74" s="16" t="s">
         <v>151</v>
       </c>
-      <c r="E74" s="19" t="s">
+      <c r="E74" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="F74" s="19"/>
-      <c r="G74" s="20"/>
-      <c r="H74" s="49"/>
-      <c r="I74" s="50"/>
+      <c r="F74" s="16"/>
+      <c r="G74" s="17"/>
+      <c r="H74" s="33"/>
+      <c r="I74" s="34"/>
       <c r="J74" s="1"/>
       <c r="K74" s="1"/>
       <c r="L74" s="1"/>
     </row>
     <row r="75" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A75" s="69">
+      <c r="A75" s="63">
         <v>21</v>
       </c>
-      <c r="B75" s="70" t="s">
+      <c r="B75" s="66" t="s">
         <v>153</v>
       </c>
-      <c r="C75" s="71">
+      <c r="C75" s="45">
         <v>21.1</v>
       </c>
-      <c r="D75" s="72" t="s">
+      <c r="D75" s="46" t="s">
         <v>154</v>
       </c>
-      <c r="E75" s="72" t="s">
+      <c r="E75" s="46" t="s">
         <v>300</v>
       </c>
-      <c r="F75" s="72" t="s">
+      <c r="F75" s="46" t="s">
         <v>301</v>
       </c>
-      <c r="G75" s="73" t="s">
+      <c r="G75" s="47" t="s">
         <v>302</v>
       </c>
-      <c r="H75" s="71"/>
-      <c r="I75" s="74"/>
+      <c r="H75" s="45"/>
+      <c r="I75" s="48"/>
     </row>
     <row r="76" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="75"/>
-      <c r="B76" s="76"/>
-      <c r="C76" s="77">
+      <c r="A76" s="64"/>
+      <c r="B76" s="67"/>
+      <c r="C76" s="15">
         <v>21.2</v>
       </c>
-      <c r="D76" s="72" t="s">
+      <c r="D76" s="46" t="s">
         <v>155</v>
       </c>
-      <c r="E76" s="72" t="s">
+      <c r="E76" s="46" t="s">
         <v>281</v>
       </c>
-      <c r="F76" s="72" t="s">
+      <c r="F76" s="46" t="s">
         <v>282</v>
       </c>
-      <c r="G76" s="73" t="s">
+      <c r="G76" s="47" t="s">
         <v>156</v>
       </c>
-      <c r="H76" s="71"/>
-      <c r="I76" s="74"/>
+      <c r="H76" s="45"/>
+      <c r="I76" s="48"/>
     </row>
     <row r="77" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A77" s="78"/>
-      <c r="B77" s="79"/>
-      <c r="C77" s="49">
+      <c r="A77" s="65"/>
+      <c r="B77" s="68"/>
+      <c r="C77" s="33">
         <v>21.3</v>
       </c>
-      <c r="D77" s="19" t="s">
+      <c r="D77" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="E77" s="19" t="s">
+      <c r="E77" s="16" t="s">
         <v>148</v>
       </c>
-      <c r="F77" s="19"/>
-      <c r="G77" s="20"/>
-      <c r="H77" s="49"/>
-      <c r="I77" s="50"/>
+      <c r="F77" s="16"/>
+      <c r="G77" s="17"/>
+      <c r="H77" s="33"/>
+      <c r="I77" s="34"/>
     </row>
     <row r="78" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A78" s="69">
+      <c r="A78" s="63">
         <v>22</v>
       </c>
-      <c r="B78" s="70" t="s">
+      <c r="B78" s="66" t="s">
         <v>157</v>
       </c>
-      <c r="C78" s="71">
+      <c r="C78" s="45">
         <v>22.1</v>
       </c>
-      <c r="D78" s="72" t="s">
+      <c r="D78" s="46" t="s">
         <v>158</v>
       </c>
-      <c r="E78" s="72" t="s">
+      <c r="E78" s="46" t="s">
         <v>305</v>
       </c>
-      <c r="F78" s="72" t="s">
+      <c r="F78" s="46" t="s">
         <v>306</v>
       </c>
-      <c r="G78" s="73" t="s">
+      <c r="G78" s="47" t="s">
         <v>307</v>
       </c>
-      <c r="H78" s="71"/>
-      <c r="I78" s="74"/>
+      <c r="H78" s="45"/>
+      <c r="I78" s="48"/>
     </row>
     <row r="79" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A79" s="75"/>
-      <c r="B79" s="76"/>
-      <c r="C79" s="77">
+      <c r="A79" s="64"/>
+      <c r="B79" s="67"/>
+      <c r="C79" s="15">
         <v>22.2</v>
       </c>
-      <c r="D79" s="72" t="s">
+      <c r="D79" s="46" t="s">
         <v>280</v>
       </c>
-      <c r="E79" s="71" t="s">
+      <c r="E79" s="45" t="s">
         <v>303</v>
       </c>
-      <c r="F79" s="72" t="s">
+      <c r="F79" s="46" t="s">
         <v>282</v>
       </c>
-      <c r="G79" s="73" t="s">
+      <c r="G79" s="47" t="s">
         <v>304</v>
       </c>
-      <c r="H79" s="71"/>
-      <c r="I79" s="74"/>
+      <c r="H79" s="45"/>
+      <c r="I79" s="48"/>
     </row>
     <row r="80" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A80" s="78"/>
-      <c r="B80" s="79"/>
-      <c r="C80" s="49">
+      <c r="A80" s="65"/>
+      <c r="B80" s="68"/>
+      <c r="C80" s="33">
         <v>22.3</v>
       </c>
-      <c r="D80" s="19" t="s">
+      <c r="D80" s="16" t="s">
         <v>158</v>
       </c>
-      <c r="E80" s="49" t="s">
+      <c r="E80" s="33" t="s">
         <v>148</v>
       </c>
-      <c r="F80" s="19"/>
-      <c r="G80" s="20"/>
-      <c r="H80" s="49"/>
-      <c r="I80" s="50"/>
+      <c r="F80" s="16"/>
+      <c r="G80" s="17"/>
+      <c r="H80" s="33"/>
+      <c r="I80" s="34"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A81" s="3"/>
@@ -6038,21 +6045,12 @@
   </sheetData>
   <autoFilter ref="I1:I26" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="37">
-    <mergeCell ref="A13:A16"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="A17:A20"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="A30:A40"/>
+    <mergeCell ref="B30:B40"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="B21:B23"/>
     <mergeCell ref="A41:A48"/>
     <mergeCell ref="B41:B48"/>
     <mergeCell ref="A75:A77"/>
@@ -6069,14 +6067,23 @@
     <mergeCell ref="B69:B71"/>
     <mergeCell ref="A72:A74"/>
     <mergeCell ref="B72:B74"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="A30:A40"/>
-    <mergeCell ref="B30:B40"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B17:B20"/>
   </mergeCells>
-  <phoneticPr fontId="10" type="noConversion"/>
+  <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
   <legacyDrawing r:id="rId1"/>

--- a/Soubhanik/checkupp_product_backlog_final.xlsx
+++ b/Soubhanik/checkupp_product_backlog_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Soubhanik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F7E4E8CF-3396-47EF-8A96-4CC709A97038}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1122256-98C8-479E-A2D3-58B281786993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -19,7 +19,18 @@
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$I$1:$I$26</definedName>
   </definedNames>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -3687,6 +3698,63 @@
     <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3708,9 +3776,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3724,60 +3789,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4013,34 +4024,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="55" t="s">
+      <c r="C1" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="55" t="s">
+      <c r="D1" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="60" t="s">
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="55" t="s">
+      <c r="H1" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="55" t="s">
+      <c r="I1" s="74" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="56"/>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
+      <c r="A2" s="55"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
@@ -4050,15 +4061,15 @@
       <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="60"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
     </row>
     <row r="3" spans="1:9" s="5" customFormat="1" ht="156" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="61">
+      <c r="A3" s="79">
         <v>1</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="79" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="16">
@@ -4084,8 +4095,8 @@
       </c>
     </row>
     <row r="4" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A4" s="61"/>
-      <c r="B4" s="61"/>
+      <c r="A4" s="79"/>
+      <c r="B4" s="79"/>
       <c r="C4" s="16">
         <v>1.2</v>
       </c>
@@ -4105,8 +4116,8 @@
       <c r="I4" s="16"/>
     </row>
     <row r="5" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A5" s="61"/>
-      <c r="B5" s="61"/>
+      <c r="A5" s="79"/>
+      <c r="B5" s="79"/>
       <c r="C5" s="16">
         <v>1.3</v>
       </c>
@@ -4126,8 +4137,8 @@
       <c r="I5" s="16"/>
     </row>
     <row r="6" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A6" s="61"/>
-      <c r="B6" s="61"/>
+      <c r="A6" s="79"/>
+      <c r="B6" s="79"/>
       <c r="C6" s="16">
         <v>1.4</v>
       </c>
@@ -4147,8 +4158,8 @@
       <c r="I6" s="16"/>
     </row>
     <row r="7" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="61"/>
-      <c r="B7" s="61"/>
+      <c r="A7" s="79"/>
+      <c r="B7" s="79"/>
       <c r="C7" s="16">
         <v>1.5</v>
       </c>
@@ -4168,10 +4179,10 @@
       <c r="I7" s="16"/>
     </row>
     <row r="8" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="57">
+      <c r="A8" s="75">
         <v>5</v>
       </c>
-      <c r="B8" s="57" t="s">
+      <c r="B8" s="75" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="18">
@@ -4197,8 +4208,8 @@
       </c>
     </row>
     <row r="9" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="58"/>
-      <c r="B9" s="58"/>
+      <c r="A9" s="76"/>
+      <c r="B9" s="76"/>
       <c r="C9" s="18">
         <v>5.2</v>
       </c>
@@ -4218,8 +4229,8 @@
       <c r="I9" s="18"/>
     </row>
     <row r="10" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="58"/>
-      <c r="B10" s="58"/>
+      <c r="A10" s="76"/>
+      <c r="B10" s="76"/>
       <c r="C10" s="18">
         <v>5.3</v>
       </c>
@@ -4239,8 +4250,8 @@
       <c r="I10" s="18"/>
     </row>
     <row r="11" spans="1:9" s="14" customFormat="1" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="58"/>
-      <c r="B11" s="58"/>
+      <c r="A11" s="76"/>
+      <c r="B11" s="76"/>
       <c r="C11" s="21">
         <v>5.4</v>
       </c>
@@ -4260,8 +4271,8 @@
       <c r="I11" s="21"/>
     </row>
     <row r="12" spans="1:9" s="14" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="59"/>
-      <c r="B12" s="59"/>
+      <c r="A12" s="77"/>
+      <c r="B12" s="77"/>
       <c r="C12" s="21">
         <v>5.5</v>
       </c>
@@ -4281,10 +4292,10 @@
       <c r="I12" s="21"/>
     </row>
     <row r="13" spans="1:9" s="14" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="49">
+      <c r="A13" s="68">
         <v>6</v>
       </c>
-      <c r="B13" s="49" t="s">
+      <c r="B13" s="68" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="21">
@@ -4310,8 +4321,8 @@
       </c>
     </row>
     <row r="14" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A14" s="50"/>
-      <c r="B14" s="50"/>
+      <c r="A14" s="69"/>
+      <c r="B14" s="69"/>
       <c r="C14" s="24">
         <v>6.2</v>
       </c>
@@ -4331,8 +4342,8 @@
       <c r="I14" s="24"/>
     </row>
     <row r="15" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="50"/>
-      <c r="B15" s="50"/>
+      <c r="A15" s="69"/>
+      <c r="B15" s="69"/>
       <c r="C15" s="24">
         <v>6.3</v>
       </c>
@@ -4352,8 +4363,8 @@
       <c r="I15" s="24"/>
     </row>
     <row r="16" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A16" s="50"/>
-      <c r="B16" s="51"/>
+      <c r="A16" s="69"/>
+      <c r="B16" s="70"/>
       <c r="C16" s="27">
         <v>6.4</v>
       </c>
@@ -4377,10 +4388,10 @@
       </c>
     </row>
     <row r="17" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A17" s="52">
+      <c r="A17" s="71">
         <v>7</v>
       </c>
-      <c r="B17" s="49" t="s">
+      <c r="B17" s="68" t="s">
         <v>38</v>
       </c>
       <c r="C17" s="24">
@@ -4406,8 +4417,8 @@
       </c>
     </row>
     <row r="18" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A18" s="53"/>
-      <c r="B18" s="50"/>
+      <c r="A18" s="72"/>
+      <c r="B18" s="69"/>
       <c r="C18" s="24">
         <v>7.2</v>
       </c>
@@ -4429,8 +4440,8 @@
       </c>
     </row>
     <row r="19" spans="1:9" s="6" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="53"/>
-      <c r="B19" s="50"/>
+      <c r="A19" s="72"/>
+      <c r="B19" s="69"/>
       <c r="C19" s="24">
         <v>7.3</v>
       </c>
@@ -4450,8 +4461,8 @@
       <c r="I19" s="24"/>
     </row>
     <row r="20" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="54"/>
-      <c r="B20" s="51"/>
+      <c r="A20" s="73"/>
+      <c r="B20" s="70"/>
       <c r="C20" s="24">
         <v>7.4</v>
       </c>
@@ -4471,10 +4482,10 @@
       <c r="I20" s="24"/>
     </row>
     <row r="21" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="77">
+      <c r="A21" s="51">
         <v>8</v>
       </c>
-      <c r="B21" s="77" t="s">
+      <c r="B21" s="51" t="s">
         <v>50</v>
       </c>
       <c r="C21" s="28">
@@ -4498,8 +4509,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="78"/>
-      <c r="B22" s="78"/>
+      <c r="A22" s="52"/>
+      <c r="B22" s="52"/>
       <c r="C22" s="28">
         <v>9.3000000000000007</v>
       </c>
@@ -4521,8 +4532,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="79"/>
-      <c r="B23" s="79"/>
+      <c r="A23" s="53"/>
+      <c r="B23" s="53"/>
       <c r="C23" s="28">
         <v>9.4</v>
       </c>
@@ -4544,10 +4555,10 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="75">
+      <c r="A24" s="49">
         <v>12</v>
       </c>
-      <c r="B24" s="75" t="s">
+      <c r="B24" s="49" t="s">
         <v>64</v>
       </c>
       <c r="C24" s="31">
@@ -4573,8 +4584,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="75"/>
-      <c r="B25" s="75"/>
+      <c r="A25" s="49"/>
+      <c r="B25" s="49"/>
       <c r="C25" s="31">
         <v>12.2</v>
       </c>
@@ -4598,8 +4609,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="75"/>
-      <c r="B26" s="75"/>
+      <c r="A26" s="49"/>
+      <c r="B26" s="49"/>
       <c r="C26" s="31">
         <v>12.3</v>
       </c>
@@ -4623,8 +4634,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" s="6" customFormat="1" ht="123.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="75"/>
-      <c r="B27" s="75"/>
+      <c r="A27" s="49"/>
+      <c r="B27" s="49"/>
       <c r="C27" s="31">
         <v>12.4</v>
       </c>
@@ -4648,8 +4659,8 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="75"/>
-      <c r="B28" s="75"/>
+      <c r="A28" s="49"/>
+      <c r="B28" s="49"/>
       <c r="C28" s="31">
         <v>12.5</v>
       </c>
@@ -4690,10 +4701,10 @@
       <c r="I29" s="34"/>
     </row>
     <row r="30" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="76">
+      <c r="A30" s="50">
         <v>14</v>
       </c>
-      <c r="B30" s="76" t="s">
+      <c r="B30" s="50" t="s">
         <v>80</v>
       </c>
       <c r="C30" s="35">
@@ -4719,8 +4730,8 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="76"/>
-      <c r="B31" s="76"/>
+      <c r="A31" s="50"/>
+      <c r="B31" s="50"/>
       <c r="C31" s="35">
         <v>14.2</v>
       </c>
@@ -4744,8 +4755,8 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="76"/>
-      <c r="B32" s="76"/>
+      <c r="A32" s="50"/>
+      <c r="B32" s="50"/>
       <c r="C32" s="35">
         <v>14.3</v>
       </c>
@@ -4769,8 +4780,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="76"/>
-      <c r="B33" s="76"/>
+      <c r="A33" s="50"/>
+      <c r="B33" s="50"/>
       <c r="C33" s="35">
         <v>14.4</v>
       </c>
@@ -4794,8 +4805,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="76"/>
-      <c r="B34" s="76"/>
+      <c r="A34" s="50"/>
+      <c r="B34" s="50"/>
       <c r="C34" s="35">
         <v>14.5</v>
       </c>
@@ -4819,8 +4830,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="76"/>
-      <c r="B35" s="76"/>
+      <c r="A35" s="50"/>
+      <c r="B35" s="50"/>
       <c r="C35" s="35">
         <v>14.6</v>
       </c>
@@ -4844,8 +4855,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="76"/>
-      <c r="B36" s="76"/>
+      <c r="A36" s="50"/>
+      <c r="B36" s="50"/>
       <c r="C36" s="35">
         <v>14.7</v>
       </c>
@@ -4869,8 +4880,8 @@
       </c>
     </row>
     <row r="37" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="76"/>
-      <c r="B37" s="76"/>
+      <c r="A37" s="50"/>
+      <c r="B37" s="50"/>
       <c r="C37" s="35">
         <v>14.8</v>
       </c>
@@ -4894,8 +4905,8 @@
       </c>
     </row>
     <row r="38" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A38" s="76"/>
-      <c r="B38" s="76"/>
+      <c r="A38" s="50"/>
+      <c r="B38" s="50"/>
       <c r="C38" s="35">
         <v>14.9</v>
       </c>
@@ -4919,8 +4930,8 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="76"/>
-      <c r="B39" s="76"/>
+      <c r="A39" s="50"/>
+      <c r="B39" s="50"/>
       <c r="C39" s="35">
         <v>14.1</v>
       </c>
@@ -4944,8 +4955,8 @@
       </c>
     </row>
     <row r="40" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="76"/>
-      <c r="B40" s="76"/>
+      <c r="A40" s="50"/>
+      <c r="B40" s="50"/>
       <c r="C40" s="35">
         <v>14.11</v>
       </c>
@@ -4969,10 +4980,10 @@
       </c>
     </row>
     <row r="41" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A41" s="62">
+      <c r="A41" s="54">
         <v>15</v>
       </c>
-      <c r="B41" s="62" t="s">
+      <c r="B41" s="54" t="s">
         <v>85</v>
       </c>
       <c r="C41" s="38">
@@ -4998,8 +5009,8 @@
       </c>
     </row>
     <row r="42" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="56"/>
-      <c r="B42" s="56"/>
+      <c r="A42" s="55"/>
+      <c r="B42" s="55"/>
       <c r="C42" s="38">
         <v>15.2</v>
       </c>
@@ -5023,8 +5034,8 @@
       </c>
     </row>
     <row r="43" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="56"/>
-      <c r="B43" s="56"/>
+      <c r="A43" s="55"/>
+      <c r="B43" s="55"/>
       <c r="C43" s="38">
         <v>15.3</v>
       </c>
@@ -5048,8 +5059,8 @@
       </c>
     </row>
     <row r="44" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A44" s="56"/>
-      <c r="B44" s="56"/>
+      <c r="A44" s="55"/>
+      <c r="B44" s="55"/>
       <c r="C44" s="38">
         <v>15.4</v>
       </c>
@@ -5073,8 +5084,8 @@
       </c>
     </row>
     <row r="45" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="56"/>
-      <c r="B45" s="56"/>
+      <c r="A45" s="55"/>
+      <c r="B45" s="55"/>
       <c r="C45" s="38">
         <v>15.5</v>
       </c>
@@ -5098,8 +5109,8 @@
       </c>
     </row>
     <row r="46" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="56"/>
-      <c r="B46" s="56"/>
+      <c r="A46" s="55"/>
+      <c r="B46" s="55"/>
       <c r="C46" s="38">
         <v>15.6</v>
       </c>
@@ -5123,8 +5134,8 @@
       </c>
     </row>
     <row r="47" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A47" s="56"/>
-      <c r="B47" s="56"/>
+      <c r="A47" s="55"/>
+      <c r="B47" s="55"/>
       <c r="C47" s="38">
         <v>15.7</v>
       </c>
@@ -5148,8 +5159,8 @@
       </c>
     </row>
     <row r="48" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="56"/>
-      <c r="B48" s="56"/>
+      <c r="A48" s="55"/>
+      <c r="B48" s="55"/>
       <c r="C48" s="38">
         <v>15.8</v>
       </c>
@@ -5173,10 +5184,10 @@
       </c>
     </row>
     <row r="49" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A49" s="69">
+      <c r="A49" s="62">
         <v>16</v>
       </c>
-      <c r="B49" s="69" t="s">
+      <c r="B49" s="62" t="s">
         <v>103</v>
       </c>
       <c r="C49" s="40">
@@ -5202,8 +5213,8 @@
       </c>
     </row>
     <row r="50" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A50" s="69"/>
-      <c r="B50" s="69"/>
+      <c r="A50" s="62"/>
+      <c r="B50" s="62"/>
       <c r="C50" s="40">
         <v>16.2</v>
       </c>
@@ -5227,8 +5238,8 @@
       </c>
     </row>
     <row r="51" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="69"/>
-      <c r="B51" s="69"/>
+      <c r="A51" s="62"/>
+      <c r="B51" s="62"/>
       <c r="C51" s="40">
         <v>16.3</v>
       </c>
@@ -5252,8 +5263,8 @@
       </c>
     </row>
     <row r="52" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A52" s="69"/>
-      <c r="B52" s="69"/>
+      <c r="A52" s="62"/>
+      <c r="B52" s="62"/>
       <c r="C52" s="40">
         <v>16.399999999999999</v>
       </c>
@@ -5277,8 +5288,8 @@
       </c>
     </row>
     <row r="53" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A53" s="69"/>
-      <c r="B53" s="69"/>
+      <c r="A53" s="62"/>
+      <c r="B53" s="62"/>
       <c r="C53" s="40">
         <v>16.5</v>
       </c>
@@ -5302,8 +5313,8 @@
       </c>
     </row>
     <row r="54" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A54" s="56"/>
-      <c r="B54" s="56"/>
+      <c r="A54" s="55"/>
+      <c r="B54" s="55"/>
       <c r="C54" s="40">
         <v>16.600000000000001</v>
       </c>
@@ -5327,10 +5338,10 @@
       </c>
     </row>
     <row r="55" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A55" s="70">
+      <c r="A55" s="63">
         <v>17</v>
       </c>
-      <c r="B55" s="73" t="s">
+      <c r="B55" s="66" t="s">
         <v>119</v>
       </c>
       <c r="C55" s="43">
@@ -5356,8 +5367,8 @@
       </c>
     </row>
     <row r="56" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A56" s="71"/>
-      <c r="B56" s="73"/>
+      <c r="A56" s="64"/>
+      <c r="B56" s="66"/>
       <c r="C56" s="43">
         <v>17.2</v>
       </c>
@@ -5381,8 +5392,8 @@
       </c>
     </row>
     <row r="57" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A57" s="71"/>
-      <c r="B57" s="73"/>
+      <c r="A57" s="64"/>
+      <c r="B57" s="66"/>
       <c r="C57" s="43">
         <v>17.3</v>
       </c>
@@ -5406,8 +5417,8 @@
       </c>
     </row>
     <row r="58" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A58" s="71"/>
-      <c r="B58" s="73"/>
+      <c r="A58" s="64"/>
+      <c r="B58" s="66"/>
       <c r="C58" s="43">
         <v>17.399999999999999</v>
       </c>
@@ -5431,8 +5442,8 @@
       </c>
     </row>
     <row r="59" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A59" s="72"/>
-      <c r="B59" s="73"/>
+      <c r="A59" s="65"/>
+      <c r="B59" s="66"/>
       <c r="C59" s="43">
         <v>17.5</v>
       </c>
@@ -5456,14 +5467,14 @@
       </c>
     </row>
     <row r="60" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A60" s="74">
+      <c r="A60" s="67">
         <v>18</v>
       </c>
-      <c r="B60" s="74" t="s">
+      <c r="B60" s="67" t="s">
         <v>132</v>
       </c>
       <c r="C60" s="18">
-        <v>17.100000000000001</v>
+        <v>18.100000000000001</v>
       </c>
       <c r="D60" s="18" t="s">
         <v>133</v>
@@ -5485,10 +5496,10 @@
       </c>
     </row>
     <row r="61" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A61" s="56"/>
-      <c r="B61" s="56"/>
+      <c r="A61" s="55"/>
+      <c r="B61" s="55"/>
       <c r="C61" s="18">
-        <v>17.2</v>
+        <v>18.2</v>
       </c>
       <c r="D61" s="18" t="s">
         <v>133</v>
@@ -5510,10 +5521,10 @@
       </c>
     </row>
     <row r="62" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A62" s="56"/>
-      <c r="B62" s="56"/>
+      <c r="A62" s="55"/>
+      <c r="B62" s="55"/>
       <c r="C62" s="18">
-        <v>17.3</v>
+        <v>18.3</v>
       </c>
       <c r="D62" s="18" t="s">
         <v>133</v>
@@ -5535,10 +5546,10 @@
       </c>
     </row>
     <row r="63" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A63" s="56"/>
-      <c r="B63" s="56"/>
+      <c r="A63" s="55"/>
+      <c r="B63" s="55"/>
       <c r="C63" s="18">
-        <v>17.399999999999999</v>
+        <v>18.399999999999999</v>
       </c>
       <c r="D63" s="18" t="s">
         <v>133</v>
@@ -5560,10 +5571,10 @@
       </c>
     </row>
     <row r="64" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A64" s="56"/>
-      <c r="B64" s="56"/>
+      <c r="A64" s="55"/>
+      <c r="B64" s="55"/>
       <c r="C64" s="18">
-        <v>17.5</v>
+        <v>18.5</v>
       </c>
       <c r="D64" s="18" t="s">
         <v>133</v>
@@ -5585,10 +5596,10 @@
       </c>
     </row>
     <row r="65" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A65" s="56"/>
-      <c r="B65" s="56"/>
+      <c r="A65" s="55"/>
+      <c r="B65" s="55"/>
       <c r="C65" s="18">
-        <v>17.600000000000001</v>
+        <v>18.600000000000001</v>
       </c>
       <c r="D65" s="18" t="s">
         <v>133</v>
@@ -5610,10 +5621,10 @@
       </c>
     </row>
     <row r="66" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A66" s="56"/>
-      <c r="B66" s="56"/>
+      <c r="A66" s="55"/>
+      <c r="B66" s="55"/>
       <c r="C66" s="18">
-        <v>17.7</v>
+        <v>18.7</v>
       </c>
       <c r="D66" s="18" t="s">
         <v>133</v>
@@ -5635,10 +5646,10 @@
       </c>
     </row>
     <row r="67" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A67" s="56"/>
-      <c r="B67" s="56"/>
+      <c r="A67" s="55"/>
+      <c r="B67" s="55"/>
       <c r="C67" s="18">
-        <v>17.8</v>
+        <v>18.8</v>
       </c>
       <c r="D67" s="18" t="s">
         <v>133</v>
@@ -5660,10 +5671,10 @@
       </c>
     </row>
     <row r="68" spans="1:12" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="56"/>
-      <c r="B68" s="56"/>
+      <c r="A68" s="55"/>
+      <c r="B68" s="55"/>
       <c r="C68" s="18">
-        <v>17.899999999999999</v>
+        <v>18.899999999999999</v>
       </c>
       <c r="D68" s="18" t="s">
         <v>133</v>
@@ -5685,10 +5696,10 @@
       </c>
     </row>
     <row r="69" spans="1:12" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A69" s="63">
+      <c r="A69" s="56">
         <v>19</v>
       </c>
-      <c r="B69" s="66" t="s">
+      <c r="B69" s="59" t="s">
         <v>143</v>
       </c>
       <c r="C69" s="45">
@@ -5710,8 +5721,8 @@
       <c r="I69" s="48"/>
     </row>
     <row r="70" spans="1:12" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="64"/>
-      <c r="B70" s="67"/>
+      <c r="A70" s="57"/>
+      <c r="B70" s="60"/>
       <c r="C70" s="15">
         <v>19.2</v>
       </c>
@@ -5731,8 +5742,8 @@
       <c r="I70" s="48"/>
     </row>
     <row r="71" spans="1:12" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="65"/>
-      <c r="B71" s="68"/>
+      <c r="A71" s="58"/>
+      <c r="B71" s="61"/>
       <c r="C71" s="34">
         <v>19.3</v>
       </c>
@@ -5750,10 +5761,10 @@
       <c r="I71" s="34"/>
     </row>
     <row r="72" spans="1:12" s="6" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="63">
+      <c r="A72" s="56">
         <v>20</v>
       </c>
-      <c r="B72" s="66" t="s">
+      <c r="B72" s="59" t="s">
         <v>150</v>
       </c>
       <c r="C72" s="45">
@@ -5775,8 +5786,8 @@
       <c r="I72" s="48"/>
     </row>
     <row r="73" spans="1:12" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A73" s="64"/>
-      <c r="B73" s="67"/>
+      <c r="A73" s="57"/>
+      <c r="B73" s="60"/>
       <c r="C73" s="15">
         <v>20.2</v>
       </c>
@@ -5799,8 +5810,8 @@
       <c r="L73" s="1"/>
     </row>
     <row r="74" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A74" s="65"/>
-      <c r="B74" s="68"/>
+      <c r="A74" s="58"/>
+      <c r="B74" s="61"/>
       <c r="C74" s="33">
         <v>20.3</v>
       </c>
@@ -5819,10 +5830,10 @@
       <c r="L74" s="1"/>
     </row>
     <row r="75" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A75" s="63">
+      <c r="A75" s="56">
         <v>21</v>
       </c>
-      <c r="B75" s="66" t="s">
+      <c r="B75" s="59" t="s">
         <v>153</v>
       </c>
       <c r="C75" s="45">
@@ -5844,8 +5855,8 @@
       <c r="I75" s="48"/>
     </row>
     <row r="76" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="64"/>
-      <c r="B76" s="67"/>
+      <c r="A76" s="57"/>
+      <c r="B76" s="60"/>
       <c r="C76" s="15">
         <v>21.2</v>
       </c>
@@ -5865,8 +5876,8 @@
       <c r="I76" s="48"/>
     </row>
     <row r="77" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A77" s="65"/>
-      <c r="B77" s="68"/>
+      <c r="A77" s="58"/>
+      <c r="B77" s="61"/>
       <c r="C77" s="33">
         <v>21.3</v>
       </c>
@@ -5882,10 +5893,10 @@
       <c r="I77" s="34"/>
     </row>
     <row r="78" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A78" s="63">
+      <c r="A78" s="56">
         <v>22</v>
       </c>
-      <c r="B78" s="66" t="s">
+      <c r="B78" s="59" t="s">
         <v>157</v>
       </c>
       <c r="C78" s="45">
@@ -5907,8 +5918,8 @@
       <c r="I78" s="48"/>
     </row>
     <row r="79" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A79" s="64"/>
-      <c r="B79" s="67"/>
+      <c r="A79" s="57"/>
+      <c r="B79" s="60"/>
       <c r="C79" s="15">
         <v>22.2</v>
       </c>
@@ -5928,8 +5939,8 @@
       <c r="I79" s="48"/>
     </row>
     <row r="80" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A80" s="65"/>
-      <c r="B80" s="68"/>
+      <c r="A80" s="58"/>
+      <c r="B80" s="61"/>
       <c r="C80" s="33">
         <v>22.3</v>
       </c>
@@ -6045,12 +6056,21 @@
   </sheetData>
   <autoFilter ref="I1:I26" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="37">
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="A30:A40"/>
-    <mergeCell ref="B30:B40"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B17:B20"/>
     <mergeCell ref="A41:A48"/>
     <mergeCell ref="B41:B48"/>
     <mergeCell ref="A75:A77"/>
@@ -6067,21 +6087,12 @@
     <mergeCell ref="B69:B71"/>
     <mergeCell ref="A72:A74"/>
     <mergeCell ref="B72:B74"/>
-    <mergeCell ref="A13:A16"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="A17:A20"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="A30:A40"/>
+    <mergeCell ref="B30:B40"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="B21:B23"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Soubhanik/checkupp_product_backlog_final.xlsx
+++ b/Soubhanik/checkupp_product_backlog_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Soubhanik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E1122256-98C8-479E-A2D3-58B281786993}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303B43DF-6A2A-4839-9905-224C3A45929B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1013,12 +1013,6 @@
     <t>I can keep track of appointments that have been rescheduled.</t>
   </si>
   <si>
-    <t>I can review my previously completed healthcare appointments.</t>
-  </si>
-  <si>
-    <t>I can view the detailed information (Appointment Date and time, medical facility, facility address, Lead physician) for the selected appointment.</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Tap on the </t>
     </r>
@@ -1098,37 +1092,7 @@
 5. If no Rescheduled appointments exist, an appropriate message (e.g.- No Rescheduled appointments) must be displayed.</t>
   </si>
   <si>
-    <t>View my Upcoming appointments in Your Appointments section</t>
-  </si>
-  <si>
-    <t>View my Rescheduled appointments in Your Appointments section</t>
-  </si>
-  <si>
-    <t>View my Completed appointments in Your Appointments section</t>
-  </si>
-  <si>
-    <t>Tap an appointment from the appointment list in Your Appointments section</t>
-  </si>
-  <si>
-    <t>I can view my Upcoming, Rescheduled and Completed appointments in Your Appointments section</t>
-  </si>
-  <si>
-    <t>1. The logged-in user must be able to open the Appointment Details screen by selecting an appointment from the appointment list.
-2. The appointment date and time must be displayed on the Appointment Details screen.
-3. The medical facility name and facility address must be displayed on the Appointment Details screen.
-4. The Doctor's/Medical Professional's name (optional field) must be displayed on the Appointment Details screen, where available.
-5. If any appointment details are unavailable, an appropriate message (e.g.- N/A) must be displayed while the remaining available information continues to be shown.
-6. Tapping the back button must navigate the user back to the Your Appointments section.</t>
-  </si>
-  <si>
     <t>Logged-in user</t>
-  </si>
-  <si>
-    <t>1. The User must be able to access the Your Appointments section by tapping the Your Health Overview section on the Home Screen.
-2. The user's Upcoming, Rescheduled, and Completed appointment categories filter must be displayed in the Your Appointments section.
-3. The total number of appointments in each category must be displayed at the top of the screen, in Your Appointments section.
-4. Only appointments associated with the logged-in user's account must be displayed.
-5. If no appointments are available in a category, an appropriate message (e.g.- You don't have any appointments scheduled right now) must be displayed indicating that no appointments are available, in the Your Appointments section.</t>
   </si>
   <si>
     <t>logged in user navigating the immunisation screen</t>
@@ -3246,6 +3210,498 @@
 3. All autosaved Diabetes Test data must be restored when the user reopens the app after it has been closed or removed from the background.
 4. The most recent values entered in all date fields, measurement fields, and the Additional Notes field must be displayed when the Diabetes Test is resumed, without requiring the user to re-enter the information.
 5. Only the autosaved Diabetes Test data associated with the logged-in user's account must be restored when the Diabetes Test screen is reopened.</t>
+  </si>
+  <si>
+    <t>I can view my Upcoming, Due and Completed appointments in Your Appointments section</t>
+  </si>
+  <si>
+    <t>1. The User must be able to access the Your Appointments section by tapping the Your Health Overview section on the Home Screen.
+2. The user's Upcoming, Due, and Completed appointment categories filter (top tabs) must be displayed in the Your Appointments section.
+3. The total number of appointments in each category must be displayed in the Upccoming, Due and Completed top tabs.
+4. Only appointments associated with the logged-in user's account must be displayed.
+5. If no appointments are available in a category (upcoming/due/completed), an appropriate message (e.g.- "You don't have any upcoming/due/completed appointments right now") must be displayed indicating that no appointments are available, in the Your Appointments section.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">View my </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> appointments in Your Appointments section</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">View my </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Upcoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> appointments in Your Appointments section</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">View my </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Completed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> appointments in Your Appointments section</t>
+    </r>
+  </si>
+  <si>
+    <t>I can view my previously completed healthcare appointments.</t>
+  </si>
+  <si>
+    <t>I can view the detailed information (Appointment Date and time, medical facility, facility address, Lead physician) for the selected appointment and manage them.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tap an appointment from the appointment list in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Your Appointments</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. The logged-in user must be able to open the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Appointment Details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> bottom sheet by tapping any appointment card from the appointment list.
+2. The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Appointment Details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> bottom sheet must show the following appointment details: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Appointment Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Date </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(MM DD, YYYY and ), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Time </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(e.g. 12:00 pm), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Healthcare Provider</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Location </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(Facility name and Address).
+5. If any appointment details are unavailable inside the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Appointment Details </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">bottom sheet, an appropriate message (e.g.- N/A) must be displayed while the available information is kept intact.
+6. Upcoming cards' </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Appointment Details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> bottom sheet must have the following CTA buttons: Primary type - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Reschedule</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, Secondary type- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Cancel
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>-</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Reschedule </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">action: Opens the app's existing appointment booking modal pop up
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Cancel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> action: Cancels the appointment (removes the synced appointment from device's calendar and removes it from the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Upcoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab)</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">7. Due cards' </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Appointment Details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> bottom sheet must have the following CTA buttons: Primary type - </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Reschedule</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, Secondary type- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Dismiss
+</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Reschedule</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> action: Opens the app's existing appointment booking modal pop up
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Dismiss</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> action: Dismisses the appointment (removes it from the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab)
+8. Closing the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Appointment Details</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> bottom sheet must send the user back to the previous screen (where they opened the bottom sheet).</t>
+    </r>
   </si>
 </sst>
 </file>
@@ -3698,6 +4154,84 @@
     <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -3711,84 +4245,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4024,34 +4480,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="74" t="s">
+      <c r="C1" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="74" t="s">
+      <c r="D1" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="78" t="s">
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="74" t="s">
+      <c r="H1" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="74" t="s">
+      <c r="I1" s="55" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="55"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
+      <c r="A2" s="56"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
@@ -4061,31 +4517,31 @@
       <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
-    </row>
-    <row r="3" spans="1:9" s="5" customFormat="1" ht="156" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A3" s="79">
+      <c r="G2" s="60"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+    </row>
+    <row r="3" spans="1:9" s="5" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A3" s="61">
         <v>1</v>
       </c>
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="61" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="16">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>174</v>
+        <v>302</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>177</v>
+        <v>303</v>
       </c>
       <c r="H3" s="16" t="s">
         <v>11</v>
@@ -4095,94 +4551,94 @@
       </c>
     </row>
     <row r="4" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A4" s="79"/>
-      <c r="B4" s="79"/>
+      <c r="A4" s="61"/>
+      <c r="B4" s="61"/>
       <c r="C4" s="16">
         <v>1.2</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>170</v>
+        <v>305</v>
       </c>
       <c r="F4" s="16" t="s">
         <v>159</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="H4" s="16"/>
       <c r="I4" s="16"/>
     </row>
     <row r="5" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A5" s="79"/>
-      <c r="B5" s="79"/>
+      <c r="A5" s="61"/>
+      <c r="B5" s="61"/>
       <c r="C5" s="16">
         <v>1.3</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>171</v>
+        <v>304</v>
       </c>
       <c r="F5" s="16" t="s">
         <v>160</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="H5" s="16"/>
       <c r="I5" s="16"/>
     </row>
     <row r="6" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A6" s="79"/>
-      <c r="B6" s="79"/>
+      <c r="A6" s="61"/>
+      <c r="B6" s="61"/>
       <c r="C6" s="16">
         <v>1.4</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>172</v>
+        <v>306</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>161</v>
+        <v>307</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="H6" s="16"/>
       <c r="I6" s="16"/>
     </row>
-    <row r="7" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A7" s="79"/>
-      <c r="B7" s="79"/>
+    <row r="7" spans="1:9" s="6" customFormat="1" ht="282" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A7" s="61"/>
+      <c r="B7" s="61"/>
       <c r="C7" s="16">
         <v>1.5</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>173</v>
+        <v>309</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>162</v>
+        <v>308</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>175</v>
+        <v>310</v>
       </c>
       <c r="H7" s="16"/>
       <c r="I7" s="16"/>
     </row>
     <row r="8" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="75">
+      <c r="A8" s="57">
         <v>5</v>
       </c>
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="57" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="18">
@@ -4208,8 +4664,8 @@
       </c>
     </row>
     <row r="9" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="76"/>
-      <c r="B9" s="76"/>
+      <c r="A9" s="58"/>
+      <c r="B9" s="58"/>
       <c r="C9" s="18">
         <v>5.2</v>
       </c>
@@ -4229,8 +4685,8 @@
       <c r="I9" s="18"/>
     </row>
     <row r="10" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="76"/>
-      <c r="B10" s="76"/>
+      <c r="A10" s="58"/>
+      <c r="B10" s="58"/>
       <c r="C10" s="18">
         <v>5.3</v>
       </c>
@@ -4250,52 +4706,52 @@
       <c r="I10" s="18"/>
     </row>
     <row r="11" spans="1:9" s="14" customFormat="1" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="76"/>
-      <c r="B11" s="76"/>
+      <c r="A11" s="58"/>
+      <c r="B11" s="58"/>
       <c r="C11" s="21">
         <v>5.4</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>181</v>
+        <v>172</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>184</v>
+        <v>175</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>183</v>
+        <v>174</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>185</v>
+        <v>176</v>
       </c>
       <c r="H11" s="23"/>
       <c r="I11" s="21"/>
     </row>
     <row r="12" spans="1:9" s="14" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="77"/>
-      <c r="B12" s="77"/>
+      <c r="A12" s="59"/>
+      <c r="B12" s="59"/>
       <c r="C12" s="21">
         <v>5.5</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>178</v>
+        <v>169</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>182</v>
+        <v>173</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>180</v>
+        <v>171</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>179</v>
+        <v>170</v>
       </c>
       <c r="H12" s="23"/>
       <c r="I12" s="21"/>
     </row>
     <row r="13" spans="1:9" s="14" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="68">
+      <c r="A13" s="49">
         <v>6</v>
       </c>
-      <c r="B13" s="68" t="s">
+      <c r="B13" s="49" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="21">
@@ -4321,8 +4777,8 @@
       </c>
     </row>
     <row r="14" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A14" s="69"/>
-      <c r="B14" s="69"/>
+      <c r="A14" s="50"/>
+      <c r="B14" s="50"/>
       <c r="C14" s="24">
         <v>6.2</v>
       </c>
@@ -4330,20 +4786,20 @@
         <v>26</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>187</v>
+        <v>178</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>186</v>
+        <v>177</v>
       </c>
       <c r="G14" s="25" t="s">
-        <v>188</v>
+        <v>179</v>
       </c>
       <c r="H14" s="26"/>
       <c r="I14" s="24"/>
     </row>
     <row r="15" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="69"/>
-      <c r="B15" s="69"/>
+      <c r="A15" s="50"/>
+      <c r="B15" s="50"/>
       <c r="C15" s="24">
         <v>6.3</v>
       </c>
@@ -4363,8 +4819,8 @@
       <c r="I15" s="24"/>
     </row>
     <row r="16" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A16" s="69"/>
-      <c r="B16" s="70"/>
+      <c r="A16" s="50"/>
+      <c r="B16" s="51"/>
       <c r="C16" s="27">
         <v>6.4</v>
       </c>
@@ -4388,10 +4844,10 @@
       </c>
     </row>
     <row r="17" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A17" s="71">
+      <c r="A17" s="52">
         <v>7</v>
       </c>
-      <c r="B17" s="68" t="s">
+      <c r="B17" s="49" t="s">
         <v>38</v>
       </c>
       <c r="C17" s="24">
@@ -4417,8 +4873,8 @@
       </c>
     </row>
     <row r="18" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A18" s="72"/>
-      <c r="B18" s="69"/>
+      <c r="A18" s="53"/>
+      <c r="B18" s="50"/>
       <c r="C18" s="24">
         <v>7.2</v>
       </c>
@@ -4440,8 +4896,8 @@
       </c>
     </row>
     <row r="19" spans="1:9" s="6" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="72"/>
-      <c r="B19" s="69"/>
+      <c r="A19" s="53"/>
+      <c r="B19" s="50"/>
       <c r="C19" s="24">
         <v>7.3</v>
       </c>
@@ -4449,7 +4905,7 @@
         <v>39</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="F19" s="24" t="s">
         <v>46</v>
@@ -4461,8 +4917,8 @@
       <c r="I19" s="24"/>
     </row>
     <row r="20" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="73"/>
-      <c r="B20" s="70"/>
+      <c r="A20" s="54"/>
+      <c r="B20" s="51"/>
       <c r="C20" s="24">
         <v>7.4</v>
       </c>
@@ -4470,7 +4926,7 @@
         <v>39</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="F20" s="24" t="s">
         <v>48</v>
@@ -4482,10 +4938,10 @@
       <c r="I20" s="24"/>
     </row>
     <row r="21" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="51">
+      <c r="A21" s="77">
         <v>8</v>
       </c>
-      <c r="B21" s="51" t="s">
+      <c r="B21" s="77" t="s">
         <v>50</v>
       </c>
       <c r="C21" s="28">
@@ -4509,8 +4965,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="52"/>
-      <c r="B22" s="52"/>
+      <c r="A22" s="78"/>
+      <c r="B22" s="78"/>
       <c r="C22" s="28">
         <v>9.3000000000000007</v>
       </c>
@@ -4532,8 +4988,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="53"/>
-      <c r="B23" s="53"/>
+      <c r="A23" s="79"/>
+      <c r="B23" s="79"/>
       <c r="C23" s="28">
         <v>9.4</v>
       </c>
@@ -4555,10 +5011,10 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="49">
+      <c r="A24" s="75">
         <v>12</v>
       </c>
-      <c r="B24" s="49" t="s">
+      <c r="B24" s="75" t="s">
         <v>64</v>
       </c>
       <c r="C24" s="31">
@@ -4584,8 +5040,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="49"/>
-      <c r="B25" s="49"/>
+      <c r="A25" s="75"/>
+      <c r="B25" s="75"/>
       <c r="C25" s="31">
         <v>12.2</v>
       </c>
@@ -4609,8 +5065,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="49"/>
-      <c r="B26" s="49"/>
+      <c r="A26" s="75"/>
+      <c r="B26" s="75"/>
       <c r="C26" s="31">
         <v>12.3</v>
       </c>
@@ -4634,8 +5090,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" s="6" customFormat="1" ht="123.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="49"/>
-      <c r="B27" s="49"/>
+      <c r="A27" s="75"/>
+      <c r="B27" s="75"/>
       <c r="C27" s="31">
         <v>12.4</v>
       </c>
@@ -4643,13 +5099,13 @@
         <v>65</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>283</v>
+        <v>274</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>284</v>
+        <v>275</v>
       </c>
       <c r="G27" s="32" t="s">
-        <v>285</v>
+        <v>276</v>
       </c>
       <c r="H27" s="31" t="s">
         <v>69</v>
@@ -4659,8 +5115,8 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="49"/>
-      <c r="B28" s="49"/>
+      <c r="A28" s="75"/>
+      <c r="B28" s="75"/>
       <c r="C28" s="31">
         <v>12.5</v>
       </c>
@@ -4671,7 +5127,7 @@
         <v>78</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="G28" s="32" t="s">
         <v>79</v>
@@ -4701,10 +5157,10 @@
       <c r="I29" s="34"/>
     </row>
     <row r="30" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="50">
+      <c r="A30" s="76">
         <v>14</v>
       </c>
-      <c r="B30" s="50" t="s">
+      <c r="B30" s="76" t="s">
         <v>80</v>
       </c>
       <c r="C30" s="35">
@@ -4714,13 +5170,13 @@
         <v>133</v>
       </c>
       <c r="E30" s="36" t="s">
-        <v>253</v>
+        <v>244</v>
       </c>
       <c r="F30" s="36" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>269</v>
+        <v>260</v>
       </c>
       <c r="H30" s="35" t="s">
         <v>82</v>
@@ -4730,8 +5186,8 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="50"/>
-      <c r="B31" s="50"/>
+      <c r="A31" s="76"/>
+      <c r="B31" s="76"/>
       <c r="C31" s="35">
         <v>14.2</v>
       </c>
@@ -4739,13 +5195,13 @@
         <v>133</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>254</v>
+        <v>245</v>
       </c>
       <c r="F31" s="36" t="s">
-        <v>255</v>
+        <v>246</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>270</v>
+        <v>261</v>
       </c>
       <c r="H31" s="35" t="s">
         <v>82</v>
@@ -4755,22 +5211,22 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="50"/>
-      <c r="B32" s="50"/>
+      <c r="A32" s="76"/>
+      <c r="B32" s="76"/>
       <c r="C32" s="35">
         <v>14.3</v>
       </c>
       <c r="D32" s="36" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>256</v>
+        <v>247</v>
       </c>
       <c r="F32" s="36" t="s">
-        <v>257</v>
+        <v>248</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>271</v>
+        <v>262</v>
       </c>
       <c r="H32" s="35" t="s">
         <v>82</v>
@@ -4780,8 +5236,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="50"/>
-      <c r="B33" s="50"/>
+      <c r="A33" s="76"/>
+      <c r="B33" s="76"/>
       <c r="C33" s="35">
         <v>14.4</v>
       </c>
@@ -4789,13 +5245,13 @@
         <v>133</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>258</v>
+        <v>249</v>
       </c>
       <c r="F33" s="36" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>272</v>
+        <v>263</v>
       </c>
       <c r="H33" s="35" t="s">
         <v>82</v>
@@ -4805,8 +5261,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="50"/>
-      <c r="B34" s="50"/>
+      <c r="A34" s="76"/>
+      <c r="B34" s="76"/>
       <c r="C34" s="35">
         <v>14.5</v>
       </c>
@@ -4814,13 +5270,13 @@
         <v>133</v>
       </c>
       <c r="E34" s="36" t="s">
-        <v>259</v>
+        <v>250</v>
       </c>
       <c r="F34" s="36" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>273</v>
+        <v>264</v>
       </c>
       <c r="H34" s="35" t="s">
         <v>82</v>
@@ -4830,8 +5286,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="50"/>
-      <c r="B35" s="50"/>
+      <c r="A35" s="76"/>
+      <c r="B35" s="76"/>
       <c r="C35" s="35">
         <v>14.6</v>
       </c>
@@ -4839,13 +5295,13 @@
         <v>133</v>
       </c>
       <c r="E35" s="36" t="s">
-        <v>260</v>
+        <v>251</v>
       </c>
       <c r="F35" s="36" t="s">
-        <v>261</v>
+        <v>252</v>
       </c>
       <c r="G35" s="37" t="s">
-        <v>274</v>
+        <v>265</v>
       </c>
       <c r="H35" s="35" t="s">
         <v>82</v>
@@ -4855,8 +5311,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="50"/>
-      <c r="B36" s="50"/>
+      <c r="A36" s="76"/>
+      <c r="B36" s="76"/>
       <c r="C36" s="35">
         <v>14.7</v>
       </c>
@@ -4864,13 +5320,13 @@
         <v>133</v>
       </c>
       <c r="E36" s="36" t="s">
-        <v>262</v>
+        <v>253</v>
       </c>
       <c r="F36" s="36" t="s">
-        <v>263</v>
+        <v>254</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>275</v>
+        <v>266</v>
       </c>
       <c r="H36" s="35" t="s">
         <v>82</v>
@@ -4880,8 +5336,8 @@
       </c>
     </row>
     <row r="37" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="50"/>
-      <c r="B37" s="50"/>
+      <c r="A37" s="76"/>
+      <c r="B37" s="76"/>
       <c r="C37" s="35">
         <v>14.8</v>
       </c>
@@ -4889,13 +5345,13 @@
         <v>133</v>
       </c>
       <c r="E37" s="36" t="s">
-        <v>264</v>
+        <v>255</v>
       </c>
       <c r="F37" s="36" t="s">
-        <v>265</v>
+        <v>256</v>
       </c>
       <c r="G37" s="37" t="s">
-        <v>276</v>
+        <v>267</v>
       </c>
       <c r="H37" s="35" t="s">
         <v>84</v>
@@ -4905,8 +5361,8 @@
       </c>
     </row>
     <row r="38" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A38" s="50"/>
-      <c r="B38" s="50"/>
+      <c r="A38" s="76"/>
+      <c r="B38" s="76"/>
       <c r="C38" s="35">
         <v>14.9</v>
       </c>
@@ -4914,13 +5370,13 @@
         <v>133</v>
       </c>
       <c r="E38" s="36" t="s">
-        <v>266</v>
+        <v>257</v>
       </c>
       <c r="F38" s="36" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>277</v>
+        <v>268</v>
       </c>
       <c r="H38" s="35" t="s">
         <v>84</v>
@@ -4930,8 +5386,8 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="50"/>
-      <c r="B39" s="50"/>
+      <c r="A39" s="76"/>
+      <c r="B39" s="76"/>
       <c r="C39" s="35">
         <v>14.1</v>
       </c>
@@ -4939,13 +5395,13 @@
         <v>133</v>
       </c>
       <c r="E39" s="36" t="s">
-        <v>267</v>
+        <v>258</v>
       </c>
       <c r="F39" s="36" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>278</v>
+        <v>269</v>
       </c>
       <c r="H39" s="35" t="s">
         <v>84</v>
@@ -4955,8 +5411,8 @@
       </c>
     </row>
     <row r="40" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="50"/>
-      <c r="B40" s="50"/>
+      <c r="A40" s="76"/>
+      <c r="B40" s="76"/>
       <c r="C40" s="35">
         <v>14.11</v>
       </c>
@@ -4964,13 +5420,13 @@
         <v>133</v>
       </c>
       <c r="E40" s="36" t="s">
-        <v>268</v>
+        <v>259</v>
       </c>
       <c r="F40" s="36" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>279</v>
+        <v>270</v>
       </c>
       <c r="H40" s="35" t="s">
         <v>84</v>
@@ -4980,10 +5436,10 @@
       </c>
     </row>
     <row r="41" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A41" s="54">
+      <c r="A41" s="62">
         <v>15</v>
       </c>
-      <c r="B41" s="54" t="s">
+      <c r="B41" s="62" t="s">
         <v>85</v>
       </c>
       <c r="C41" s="38">
@@ -4999,7 +5455,7 @@
         <v>88</v>
       </c>
       <c r="G41" s="39" t="s">
-        <v>189</v>
+        <v>180</v>
       </c>
       <c r="H41" s="38" t="s">
         <v>123</v>
@@ -5009,8 +5465,8 @@
       </c>
     </row>
     <row r="42" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="55"/>
-      <c r="B42" s="55"/>
+      <c r="A42" s="56"/>
+      <c r="B42" s="56"/>
       <c r="C42" s="38">
         <v>15.2</v>
       </c>
@@ -5024,7 +5480,7 @@
         <v>90</v>
       </c>
       <c r="G42" s="39" t="s">
-        <v>190</v>
+        <v>181</v>
       </c>
       <c r="H42" s="38" t="s">
         <v>107</v>
@@ -5034,8 +5490,8 @@
       </c>
     </row>
     <row r="43" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="55"/>
-      <c r="B43" s="55"/>
+      <c r="A43" s="56"/>
+      <c r="B43" s="56"/>
       <c r="C43" s="38">
         <v>15.3</v>
       </c>
@@ -5049,7 +5505,7 @@
         <v>92</v>
       </c>
       <c r="G43" s="39" t="s">
-        <v>191</v>
+        <v>182</v>
       </c>
       <c r="H43" s="38" t="s">
         <v>107</v>
@@ -5059,8 +5515,8 @@
       </c>
     </row>
     <row r="44" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A44" s="55"/>
-      <c r="B44" s="55"/>
+      <c r="A44" s="56"/>
+      <c r="B44" s="56"/>
       <c r="C44" s="38">
         <v>15.4</v>
       </c>
@@ -5074,7 +5530,7 @@
         <v>94</v>
       </c>
       <c r="G44" s="39" t="s">
-        <v>192</v>
+        <v>183</v>
       </c>
       <c r="H44" s="38" t="s">
         <v>107</v>
@@ -5084,8 +5540,8 @@
       </c>
     </row>
     <row r="45" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="55"/>
-      <c r="B45" s="55"/>
+      <c r="A45" s="56"/>
+      <c r="B45" s="56"/>
       <c r="C45" s="38">
         <v>15.5</v>
       </c>
@@ -5099,7 +5555,7 @@
         <v>96</v>
       </c>
       <c r="G45" s="39" t="s">
-        <v>193</v>
+        <v>184</v>
       </c>
       <c r="H45" s="38" t="s">
         <v>107</v>
@@ -5109,8 +5565,8 @@
       </c>
     </row>
     <row r="46" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="55"/>
-      <c r="B46" s="55"/>
+      <c r="A46" s="56"/>
+      <c r="B46" s="56"/>
       <c r="C46" s="38">
         <v>15.6</v>
       </c>
@@ -5124,7 +5580,7 @@
         <v>98</v>
       </c>
       <c r="G46" s="39" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="H46" s="38" t="s">
         <v>107</v>
@@ -5134,8 +5590,8 @@
       </c>
     </row>
     <row r="47" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A47" s="55"/>
-      <c r="B47" s="55"/>
+      <c r="A47" s="56"/>
+      <c r="B47" s="56"/>
       <c r="C47" s="38">
         <v>15.7</v>
       </c>
@@ -5149,7 +5605,7 @@
         <v>100</v>
       </c>
       <c r="G47" s="39" t="s">
-        <v>195</v>
+        <v>186</v>
       </c>
       <c r="H47" s="38" t="s">
         <v>107</v>
@@ -5159,8 +5615,8 @@
       </c>
     </row>
     <row r="48" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="55"/>
-      <c r="B48" s="55"/>
+      <c r="A48" s="56"/>
+      <c r="B48" s="56"/>
       <c r="C48" s="38">
         <v>15.8</v>
       </c>
@@ -5174,7 +5630,7 @@
         <v>102</v>
       </c>
       <c r="G48" s="39" t="s">
-        <v>196</v>
+        <v>187</v>
       </c>
       <c r="H48" s="38" t="s">
         <v>107</v>
@@ -5184,10 +5640,10 @@
       </c>
     </row>
     <row r="49" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A49" s="62">
+      <c r="A49" s="69">
         <v>16</v>
       </c>
-      <c r="B49" s="62" t="s">
+      <c r="B49" s="69" t="s">
         <v>103</v>
       </c>
       <c r="C49" s="40">
@@ -5203,7 +5659,7 @@
         <v>106</v>
       </c>
       <c r="G49" s="42" t="s">
-        <v>197</v>
+        <v>188</v>
       </c>
       <c r="H49" s="41" t="s">
         <v>107</v>
@@ -5213,8 +5669,8 @@
       </c>
     </row>
     <row r="50" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A50" s="62"/>
-      <c r="B50" s="62"/>
+      <c r="A50" s="69"/>
+      <c r="B50" s="69"/>
       <c r="C50" s="40">
         <v>16.2</v>
       </c>
@@ -5228,7 +5684,7 @@
         <v>110</v>
       </c>
       <c r="G50" s="42" t="s">
-        <v>198</v>
+        <v>189</v>
       </c>
       <c r="H50" s="41" t="s">
         <v>107</v>
@@ -5238,8 +5694,8 @@
       </c>
     </row>
     <row r="51" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="62"/>
-      <c r="B51" s="62"/>
+      <c r="A51" s="69"/>
+      <c r="B51" s="69"/>
       <c r="C51" s="40">
         <v>16.3</v>
       </c>
@@ -5253,7 +5709,7 @@
         <v>112</v>
       </c>
       <c r="G51" s="42" t="s">
-        <v>199</v>
+        <v>190</v>
       </c>
       <c r="H51" s="41" t="s">
         <v>107</v>
@@ -5263,8 +5719,8 @@
       </c>
     </row>
     <row r="52" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A52" s="62"/>
-      <c r="B52" s="62"/>
+      <c r="A52" s="69"/>
+      <c r="B52" s="69"/>
       <c r="C52" s="40">
         <v>16.399999999999999</v>
       </c>
@@ -5278,7 +5734,7 @@
         <v>114</v>
       </c>
       <c r="G52" s="42" t="s">
-        <v>200</v>
+        <v>191</v>
       </c>
       <c r="H52" s="41" t="s">
         <v>107</v>
@@ -5288,8 +5744,8 @@
       </c>
     </row>
     <row r="53" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A53" s="62"/>
-      <c r="B53" s="62"/>
+      <c r="A53" s="69"/>
+      <c r="B53" s="69"/>
       <c r="C53" s="40">
         <v>16.5</v>
       </c>
@@ -5303,7 +5759,7 @@
         <v>116</v>
       </c>
       <c r="G53" s="42" t="s">
-        <v>201</v>
+        <v>192</v>
       </c>
       <c r="H53" s="41" t="s">
         <v>107</v>
@@ -5313,8 +5769,8 @@
       </c>
     </row>
     <row r="54" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A54" s="55"/>
-      <c r="B54" s="55"/>
+      <c r="A54" s="56"/>
+      <c r="B54" s="56"/>
       <c r="C54" s="40">
         <v>16.600000000000001</v>
       </c>
@@ -5328,7 +5784,7 @@
         <v>118</v>
       </c>
       <c r="G54" s="42" t="s">
-        <v>202</v>
+        <v>193</v>
       </c>
       <c r="H54" s="41" t="s">
         <v>107</v>
@@ -5338,10 +5794,10 @@
       </c>
     </row>
     <row r="55" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A55" s="63">
+      <c r="A55" s="70">
         <v>17</v>
       </c>
-      <c r="B55" s="66" t="s">
+      <c r="B55" s="73" t="s">
         <v>119</v>
       </c>
       <c r="C55" s="43">
@@ -5357,7 +5813,7 @@
         <v>122</v>
       </c>
       <c r="G55" s="44" t="s">
-        <v>203</v>
+        <v>194</v>
       </c>
       <c r="H55" s="43" t="s">
         <v>123</v>
@@ -5367,8 +5823,8 @@
       </c>
     </row>
     <row r="56" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A56" s="64"/>
-      <c r="B56" s="66"/>
+      <c r="A56" s="71"/>
+      <c r="B56" s="73"/>
       <c r="C56" s="43">
         <v>17.2</v>
       </c>
@@ -5382,7 +5838,7 @@
         <v>125</v>
       </c>
       <c r="G56" s="44" t="s">
-        <v>204</v>
+        <v>195</v>
       </c>
       <c r="H56" s="43" t="s">
         <v>123</v>
@@ -5392,8 +5848,8 @@
       </c>
     </row>
     <row r="57" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A57" s="64"/>
-      <c r="B57" s="66"/>
+      <c r="A57" s="71"/>
+      <c r="B57" s="73"/>
       <c r="C57" s="43">
         <v>17.3</v>
       </c>
@@ -5407,7 +5863,7 @@
         <v>127</v>
       </c>
       <c r="G57" s="44" t="s">
-        <v>205</v>
+        <v>196</v>
       </c>
       <c r="H57" s="43" t="s">
         <v>107</v>
@@ -5417,8 +5873,8 @@
       </c>
     </row>
     <row r="58" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A58" s="64"/>
-      <c r="B58" s="66"/>
+      <c r="A58" s="71"/>
+      <c r="B58" s="73"/>
       <c r="C58" s="43">
         <v>17.399999999999999</v>
       </c>
@@ -5432,7 +5888,7 @@
         <v>129</v>
       </c>
       <c r="G58" s="44" t="s">
-        <v>206</v>
+        <v>197</v>
       </c>
       <c r="H58" s="43" t="s">
         <v>123</v>
@@ -5442,8 +5898,8 @@
       </c>
     </row>
     <row r="59" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A59" s="65"/>
-      <c r="B59" s="66"/>
+      <c r="A59" s="72"/>
+      <c r="B59" s="73"/>
       <c r="C59" s="43">
         <v>17.5</v>
       </c>
@@ -5457,7 +5913,7 @@
         <v>131</v>
       </c>
       <c r="G59" s="44" t="s">
-        <v>207</v>
+        <v>198</v>
       </c>
       <c r="H59" s="43" t="s">
         <v>123</v>
@@ -5467,10 +5923,10 @@
       </c>
     </row>
     <row r="60" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A60" s="67">
+      <c r="A60" s="74">
         <v>18</v>
       </c>
-      <c r="B60" s="67" t="s">
+      <c r="B60" s="74" t="s">
         <v>132</v>
       </c>
       <c r="C60" s="18">
@@ -5480,13 +5936,13 @@
         <v>133</v>
       </c>
       <c r="E60" s="18" t="s">
-        <v>291</v>
+        <v>282</v>
       </c>
       <c r="F60" s="18" t="s">
         <v>134</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>208</v>
+        <v>199</v>
       </c>
       <c r="H60" s="18" t="s">
         <v>82</v>
@@ -5496,8 +5952,8 @@
       </c>
     </row>
     <row r="61" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A61" s="55"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="56"/>
+      <c r="B61" s="56"/>
       <c r="C61" s="18">
         <v>18.2</v>
       </c>
@@ -5505,13 +5961,13 @@
         <v>133</v>
       </c>
       <c r="E61" s="18" t="s">
-        <v>292</v>
+        <v>283</v>
       </c>
       <c r="F61" s="18" t="s">
         <v>136</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>209</v>
+        <v>200</v>
       </c>
       <c r="H61" s="18" t="s">
         <v>82</v>
@@ -5521,8 +5977,8 @@
       </c>
     </row>
     <row r="62" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A62" s="55"/>
-      <c r="B62" s="55"/>
+      <c r="A62" s="56"/>
+      <c r="B62" s="56"/>
       <c r="C62" s="18">
         <v>18.3</v>
       </c>
@@ -5530,13 +5986,13 @@
         <v>133</v>
       </c>
       <c r="E62" s="18" t="s">
-        <v>293</v>
+        <v>284</v>
       </c>
       <c r="F62" s="18" t="s">
         <v>137</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>210</v>
+        <v>201</v>
       </c>
       <c r="H62" s="18" t="s">
         <v>82</v>
@@ -5546,8 +6002,8 @@
       </c>
     </row>
     <row r="63" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A63" s="55"/>
-      <c r="B63" s="55"/>
+      <c r="A63" s="56"/>
+      <c r="B63" s="56"/>
       <c r="C63" s="18">
         <v>18.399999999999999</v>
       </c>
@@ -5555,13 +6011,13 @@
         <v>133</v>
       </c>
       <c r="E63" s="18" t="s">
-        <v>294</v>
+        <v>285</v>
       </c>
       <c r="F63" s="18" t="s">
         <v>81</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>211</v>
+        <v>202</v>
       </c>
       <c r="H63" s="18" t="s">
         <v>82</v>
@@ -5571,8 +6027,8 @@
       </c>
     </row>
     <row r="64" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A64" s="55"/>
-      <c r="B64" s="55"/>
+      <c r="A64" s="56"/>
+      <c r="B64" s="56"/>
       <c r="C64" s="18">
         <v>18.5</v>
       </c>
@@ -5580,13 +6036,13 @@
         <v>133</v>
       </c>
       <c r="E64" s="18" t="s">
-        <v>295</v>
+        <v>286</v>
       </c>
       <c r="F64" s="18" t="s">
         <v>138</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>212</v>
+        <v>203</v>
       </c>
       <c r="H64" s="18" t="s">
         <v>82</v>
@@ -5596,8 +6052,8 @@
       </c>
     </row>
     <row r="65" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A65" s="55"/>
-      <c r="B65" s="55"/>
+      <c r="A65" s="56"/>
+      <c r="B65" s="56"/>
       <c r="C65" s="18">
         <v>18.600000000000001</v>
       </c>
@@ -5605,13 +6061,13 @@
         <v>133</v>
       </c>
       <c r="E65" s="18" t="s">
-        <v>296</v>
+        <v>287</v>
       </c>
       <c r="F65" s="18" t="s">
         <v>139</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>213</v>
+        <v>204</v>
       </c>
       <c r="H65" s="18" t="s">
         <v>82</v>
@@ -5621,8 +6077,8 @@
       </c>
     </row>
     <row r="66" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A66" s="55"/>
-      <c r="B66" s="55"/>
+      <c r="A66" s="56"/>
+      <c r="B66" s="56"/>
       <c r="C66" s="18">
         <v>18.7</v>
       </c>
@@ -5630,13 +6086,13 @@
         <v>133</v>
       </c>
       <c r="E66" s="18" t="s">
-        <v>297</v>
+        <v>288</v>
       </c>
       <c r="F66" s="18" t="s">
         <v>140</v>
       </c>
       <c r="G66" s="19" t="s">
-        <v>214</v>
+        <v>205</v>
       </c>
       <c r="H66" s="18" t="s">
         <v>82</v>
@@ -5646,8 +6102,8 @@
       </c>
     </row>
     <row r="67" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A67" s="55"/>
-      <c r="B67" s="55"/>
+      <c r="A67" s="56"/>
+      <c r="B67" s="56"/>
       <c r="C67" s="18">
         <v>18.8</v>
       </c>
@@ -5655,13 +6111,13 @@
         <v>133</v>
       </c>
       <c r="E67" s="18" t="s">
-        <v>298</v>
+        <v>289</v>
       </c>
       <c r="F67" s="18" t="s">
         <v>141</v>
       </c>
       <c r="G67" s="19" t="s">
-        <v>215</v>
+        <v>206</v>
       </c>
       <c r="H67" s="18" t="s">
         <v>82</v>
@@ -5671,8 +6127,8 @@
       </c>
     </row>
     <row r="68" spans="1:12" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="55"/>
-      <c r="B68" s="55"/>
+      <c r="A68" s="56"/>
+      <c r="B68" s="56"/>
       <c r="C68" s="18">
         <v>18.899999999999999</v>
       </c>
@@ -5680,13 +6136,13 @@
         <v>133</v>
       </c>
       <c r="E68" s="18" t="s">
-        <v>299</v>
+        <v>290</v>
       </c>
       <c r="F68" s="18" t="s">
         <v>142</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>216</v>
+        <v>207</v>
       </c>
       <c r="H68" s="18" t="s">
         <v>82</v>
@@ -5696,10 +6152,10 @@
       </c>
     </row>
     <row r="69" spans="1:12" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A69" s="56">
+      <c r="A69" s="63">
         <v>19</v>
       </c>
-      <c r="B69" s="59" t="s">
+      <c r="B69" s="66" t="s">
         <v>143</v>
       </c>
       <c r="C69" s="45">
@@ -5709,20 +6165,20 @@
         <v>144</v>
       </c>
       <c r="E69" s="46" t="s">
-        <v>287</v>
+        <v>278</v>
       </c>
       <c r="F69" s="46" t="s">
-        <v>286</v>
+        <v>277</v>
       </c>
       <c r="G69" s="47" t="s">
-        <v>288</v>
+        <v>279</v>
       </c>
       <c r="H69" s="45"/>
       <c r="I69" s="48"/>
     </row>
     <row r="70" spans="1:12" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="57"/>
-      <c r="B70" s="60"/>
+      <c r="A70" s="64"/>
+      <c r="B70" s="67"/>
       <c r="C70" s="15">
         <v>19.2</v>
       </c>
@@ -5733,7 +6189,7 @@
         <v>146</v>
       </c>
       <c r="F70" s="46" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="G70" s="47" t="s">
         <v>147</v>
@@ -5742,8 +6198,8 @@
       <c r="I70" s="48"/>
     </row>
     <row r="71" spans="1:12" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="58"/>
-      <c r="B71" s="61"/>
+      <c r="A71" s="65"/>
+      <c r="B71" s="68"/>
       <c r="C71" s="34">
         <v>19.3</v>
       </c>
@@ -5761,10 +6217,10 @@
       <c r="I71" s="34"/>
     </row>
     <row r="72" spans="1:12" s="6" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="56">
+      <c r="A72" s="63">
         <v>20</v>
       </c>
-      <c r="B72" s="59" t="s">
+      <c r="B72" s="66" t="s">
         <v>150</v>
       </c>
       <c r="C72" s="45">
@@ -5774,20 +6230,20 @@
         <v>151</v>
       </c>
       <c r="E72" s="46" t="s">
-        <v>308</v>
+        <v>299</v>
       </c>
       <c r="F72" s="46" t="s">
-        <v>309</v>
+        <v>300</v>
       </c>
       <c r="G72" s="47" t="s">
-        <v>310</v>
+        <v>301</v>
       </c>
       <c r="H72" s="45"/>
       <c r="I72" s="48"/>
     </row>
     <row r="73" spans="1:12" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A73" s="57"/>
-      <c r="B73" s="60"/>
+      <c r="A73" s="64"/>
+      <c r="B73" s="67"/>
       <c r="C73" s="15">
         <v>20.2</v>
       </c>
@@ -5795,13 +6251,13 @@
         <v>152</v>
       </c>
       <c r="E73" s="46" t="s">
-        <v>289</v>
+        <v>280</v>
       </c>
       <c r="F73" s="46" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="G73" s="47" t="s">
-        <v>290</v>
+        <v>281</v>
       </c>
       <c r="H73" s="45"/>
       <c r="I73" s="48"/>
@@ -5810,8 +6266,8 @@
       <c r="L73" s="1"/>
     </row>
     <row r="74" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A74" s="58"/>
-      <c r="B74" s="61"/>
+      <c r="A74" s="65"/>
+      <c r="B74" s="68"/>
       <c r="C74" s="33">
         <v>20.3</v>
       </c>
@@ -5830,10 +6286,10 @@
       <c r="L74" s="1"/>
     </row>
     <row r="75" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A75" s="56">
+      <c r="A75" s="63">
         <v>21</v>
       </c>
-      <c r="B75" s="59" t="s">
+      <c r="B75" s="66" t="s">
         <v>153</v>
       </c>
       <c r="C75" s="45">
@@ -5843,20 +6299,20 @@
         <v>154</v>
       </c>
       <c r="E75" s="46" t="s">
-        <v>300</v>
+        <v>291</v>
       </c>
       <c r="F75" s="46" t="s">
-        <v>301</v>
+        <v>292</v>
       </c>
       <c r="G75" s="47" t="s">
-        <v>302</v>
+        <v>293</v>
       </c>
       <c r="H75" s="45"/>
       <c r="I75" s="48"/>
     </row>
     <row r="76" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="57"/>
-      <c r="B76" s="60"/>
+      <c r="A76" s="64"/>
+      <c r="B76" s="67"/>
       <c r="C76" s="15">
         <v>21.2</v>
       </c>
@@ -5864,10 +6320,10 @@
         <v>155</v>
       </c>
       <c r="E76" s="46" t="s">
-        <v>281</v>
+        <v>272</v>
       </c>
       <c r="F76" s="46" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="G76" s="47" t="s">
         <v>156</v>
@@ -5876,8 +6332,8 @@
       <c r="I76" s="48"/>
     </row>
     <row r="77" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A77" s="58"/>
-      <c r="B77" s="61"/>
+      <c r="A77" s="65"/>
+      <c r="B77" s="68"/>
       <c r="C77" s="33">
         <v>21.3</v>
       </c>
@@ -5893,10 +6349,10 @@
       <c r="I77" s="34"/>
     </row>
     <row r="78" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A78" s="56">
+      <c r="A78" s="63">
         <v>22</v>
       </c>
-      <c r="B78" s="59" t="s">
+      <c r="B78" s="66" t="s">
         <v>157</v>
       </c>
       <c r="C78" s="45">
@@ -5906,41 +6362,41 @@
         <v>158</v>
       </c>
       <c r="E78" s="46" t="s">
-        <v>305</v>
+        <v>296</v>
       </c>
       <c r="F78" s="46" t="s">
-        <v>306</v>
+        <v>297</v>
       </c>
       <c r="G78" s="47" t="s">
-        <v>307</v>
+        <v>298</v>
       </c>
       <c r="H78" s="45"/>
       <c r="I78" s="48"/>
     </row>
-    <row r="79" spans="1:12" ht="244.8" x14ac:dyDescent="0.3">
-      <c r="A79" s="57"/>
-      <c r="B79" s="60"/>
+    <row r="79" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A79" s="64"/>
+      <c r="B79" s="67"/>
       <c r="C79" s="15">
         <v>22.2</v>
       </c>
       <c r="D79" s="46" t="s">
-        <v>280</v>
+        <v>271</v>
       </c>
       <c r="E79" s="45" t="s">
-        <v>303</v>
+        <v>294</v>
       </c>
       <c r="F79" s="46" t="s">
-        <v>282</v>
+        <v>273</v>
       </c>
       <c r="G79" s="47" t="s">
-        <v>304</v>
+        <v>295</v>
       </c>
       <c r="H79" s="45"/>
       <c r="I79" s="48"/>
     </row>
     <row r="80" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A80" s="58"/>
-      <c r="B80" s="61"/>
+      <c r="A80" s="65"/>
+      <c r="B80" s="68"/>
       <c r="C80" s="33">
         <v>22.3</v>
       </c>
@@ -6056,21 +6512,12 @@
   </sheetData>
   <autoFilter ref="I1:I26" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="37">
-    <mergeCell ref="A13:A16"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="A17:A20"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="A30:A40"/>
+    <mergeCell ref="B30:B40"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="B21:B23"/>
     <mergeCell ref="A41:A48"/>
     <mergeCell ref="B41:B48"/>
     <mergeCell ref="A75:A77"/>
@@ -6087,12 +6534,21 @@
     <mergeCell ref="B69:B71"/>
     <mergeCell ref="A72:A74"/>
     <mergeCell ref="B72:B74"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="A30:A40"/>
-    <mergeCell ref="B30:B40"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B17:B20"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6153,7 +6609,7 @@
         <v>8</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>217</v>
+        <v>208</v>
       </c>
       <c r="I3" s="12" t="s">
         <v>4</v>
@@ -6174,13 +6630,13 @@
         <v>133</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>218</v>
+        <v>209</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>219</v>
+        <v>210</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>220</v>
+        <v>211</v>
       </c>
       <c r="J4" s="9"/>
     </row>
@@ -6198,13 +6654,13 @@
         <v>133</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>221</v>
+        <v>212</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>222</v>
+        <v>213</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>223</v>
+        <v>214</v>
       </c>
       <c r="J5" s="9"/>
     </row>
@@ -6219,16 +6675,16 @@
         <v>14.3</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>224</v>
+        <v>215</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>225</v>
+        <v>216</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>226</v>
+        <v>217</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>227</v>
+        <v>218</v>
       </c>
       <c r="J6" s="9"/>
     </row>
@@ -6246,13 +6702,13 @@
         <v>133</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>228</v>
+        <v>219</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>229</v>
+        <v>220</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>230</v>
+        <v>221</v>
       </c>
       <c r="J7" s="9"/>
     </row>
@@ -6270,13 +6726,13 @@
         <v>133</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>231</v>
+        <v>222</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>232</v>
+        <v>223</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>233</v>
+        <v>224</v>
       </c>
       <c r="J8" s="9"/>
     </row>
@@ -6294,13 +6750,13 @@
         <v>133</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>234</v>
+        <v>225</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>235</v>
+        <v>226</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>236</v>
+        <v>227</v>
       </c>
       <c r="J9" s="9"/>
     </row>
@@ -6318,13 +6774,13 @@
         <v>133</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>237</v>
+        <v>228</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>238</v>
+        <v>229</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>239</v>
+        <v>230</v>
       </c>
       <c r="J10" s="9"/>
     </row>
@@ -6342,13 +6798,13 @@
         <v>133</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>240</v>
+        <v>231</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>241</v>
+        <v>232</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>242</v>
+        <v>233</v>
       </c>
       <c r="J11" s="9"/>
     </row>
@@ -6366,13 +6822,13 @@
         <v>133</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>243</v>
+        <v>234</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>244</v>
+        <v>235</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>245</v>
+        <v>236</v>
       </c>
       <c r="J12" s="9"/>
     </row>
@@ -6384,19 +6840,19 @@
         <v>80</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>246</v>
+        <v>237</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>133</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>247</v>
+        <v>238</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>248</v>
+        <v>239</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>249</v>
+        <v>240</v>
       </c>
       <c r="J13" s="9"/>
     </row>
@@ -6414,13 +6870,13 @@
         <v>133</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>250</v>
+        <v>241</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>251</v>
+        <v>242</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>252</v>
+        <v>243</v>
       </c>
       <c r="J14" s="9"/>
     </row>

--- a/Soubhanik/checkupp_product_backlog_final.xlsx
+++ b/Soubhanik/checkupp_product_backlog_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Soubhanik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{303B43DF-6A2A-4839-9905-224C3A45929B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC212EFE-3A18-44FF-AB50-E204DB1FF9D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1071,27 +1071,6 @@
     <t>logged-in user</t>
   </si>
   <si>
-    <t>1. All appointments with a Completed status must be displayed under the Completed tab.
-2. Each completed appointment must display its appointment name, completed appointment date, and completed appointment time.
-3. The logged-in user must be able to tap any Completed appointment from the list to view its details.
-4. Only appointments associated with the logged-in user's account must be displayed under the Completed tab.
-5. If no Completed appointments exist, an appropriate message (e.g.- No completed appointments).</t>
-  </si>
-  <si>
-    <t>1. All appointments with an Upcoming status must be displayed under the Upcoming tab.
-2. Each upcoming appointment must display its appointment name, scheduled date, and scheduled time.
-3. The logged-in user must be able to tap any Upcoming appointment from the list to view its details.
-4. Only appointments associated with the logged-in user's account must be displayed under the Upcoming tab.
-5. If no Upcoming appointments exist, an appropriate message (e.g.- No upcoming appointments) must be displayed.</t>
-  </si>
-  <si>
-    <t>1. All appointments with a Rescheduled status must be displayed under the Rescheduled tab.
-2. Each rescheduled appointment must display its appointment name, updated date, and updated time.
-3. The logged-in user must be able to tap any Rescheduled appointment from the list to see details.
-4. Only appointments associated with the logged-in user's account must be displayed under the Rescheduled tab.
-5. If no Rescheduled appointments exist, an appropriate message (e.g.- No Rescheduled appointments) must be displayed.</t>
-  </si>
-  <si>
     <t>Logged-in user</t>
   </si>
   <si>
@@ -3215,13 +3194,6 @@
     <t>I can view my Upcoming, Due and Completed appointments in Your Appointments section</t>
   </si>
   <si>
-    <t>1. The User must be able to access the Your Appointments section by tapping the Your Health Overview section on the Home Screen.
-2. The user's Upcoming, Due, and Completed appointment categories filter (top tabs) must be displayed in the Your Appointments section.
-3. The total number of appointments in each category must be displayed in the Upccoming, Due and Completed top tabs.
-4. Only appointments associated with the logged-in user's account must be displayed.
-5. If no appointments are available in a category (upcoming/due/completed), an appropriate message (e.g.- "You don't have any upcoming/due/completed appointments right now") must be displayed indicating that no appointments are available, in the Your Appointments section.</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">View my </t>
     </r>
@@ -3701,6 +3673,245 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> bottom sheet must send the user back to the previous screen (where they opened the bottom sheet).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. The User must be able to access the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Your Appointments</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> screen by tapping the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Your Health Overview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> section on the Home Screen.
+2. The user's </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Upcoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Completed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> appointment categories filter (top tabs) must be displayed in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Your Appointments</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> screen.
+3. The total number of appointments in each category must be displayed in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Upccoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Completed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> top tabs.
+4. Only appointments associated with the logged-in user's account must be displayed.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. All appointments with an Upcoming status must be displayed under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Upcoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab.
+2. Each upcoming appointment must display its appointment name, scheduled date, and scheduled time.
+3. The logged-in user must be able to tap any Upcoming appointment from the list to view its details.
+4. Only appointments associated with the logged-in user's account must be displayed under the Upcoming tab.
+5. If no Upcoming appointments exist, an appropriate message: "You don't have any upcoming appointments" must be displayed.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. All appointments with a Due status must be displayed under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab.
+2. Each due appointment must display its appointment name, updated date, and updated time.
+3. The logged-in user must be able to tap any due appointment from the list to see details.
+4. Only appointments associated with the logged-in user's account must be displayed under the Rescheduled tab.
+5. If no due appointments exist, an appropriate message: "You don't have any upcoming appointments" must be displayed.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. All appointments with a Completed status must be displayed under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Completed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab.
+2. Each completed appointment must display its appointment name, completed appointment date, and completed appointment time.
+3. The logged-in user must be able to tap any Completed appointment from the list to view its details.
+4. Only appointments associated with the logged-in user's account must be displayed under the Completed tab.
+5. If no Completed appointments exist, an appropriate message: "You don't have any upcoming appointments" must be displayed.</t>
     </r>
   </si>
 </sst>
@@ -4154,6 +4365,63 @@
     <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4175,9 +4443,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4191,60 +4456,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4480,34 +4691,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="55" t="s">
+      <c r="C1" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="55" t="s">
+      <c r="D1" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="60" t="s">
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="55" t="s">
+      <c r="H1" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="55" t="s">
+      <c r="I1" s="74" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="56"/>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
+      <c r="A2" s="55"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
@@ -4517,15 +4728,15 @@
       <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="60"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
-    </row>
-    <row r="3" spans="1:9" s="5" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A3" s="61">
+      <c r="G2" s="78"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
+    </row>
+    <row r="3" spans="1:9" s="5" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A3" s="79">
         <v>1</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="79" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="16">
@@ -4538,10 +4749,10 @@
         <v>163</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>302</v>
+        <v>299</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="H3" s="16" t="s">
         <v>11</v>
@@ -4551,94 +4762,94 @@
       </c>
     </row>
     <row r="4" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A4" s="61"/>
-      <c r="B4" s="61"/>
+      <c r="A4" s="79"/>
+      <c r="B4" s="79"/>
       <c r="C4" s="16">
         <v>1.2</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>305</v>
+        <v>301</v>
       </c>
       <c r="F4" s="16" t="s">
         <v>159</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>166</v>
+        <v>308</v>
       </c>
       <c r="H4" s="16"/>
       <c r="I4" s="16"/>
     </row>
-    <row r="5" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A5" s="61"/>
-      <c r="B5" s="61"/>
+    <row r="5" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A5" s="79"/>
+      <c r="B5" s="79"/>
       <c r="C5" s="16">
         <v>1.3</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>304</v>
+        <v>300</v>
       </c>
       <c r="F5" s="16" t="s">
         <v>160</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>167</v>
+        <v>309</v>
       </c>
       <c r="H5" s="16"/>
       <c r="I5" s="16"/>
     </row>
     <row r="6" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A6" s="61"/>
-      <c r="B6" s="61"/>
+      <c r="A6" s="79"/>
+      <c r="B6" s="79"/>
       <c r="C6" s="16">
         <v>1.4</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>306</v>
+        <v>302</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>307</v>
+        <v>303</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>165</v>
+        <v>310</v>
       </c>
       <c r="H6" s="16"/>
       <c r="I6" s="16"/>
     </row>
     <row r="7" spans="1:9" s="6" customFormat="1" ht="282" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="61"/>
-      <c r="B7" s="61"/>
+      <c r="A7" s="79"/>
+      <c r="B7" s="79"/>
       <c r="C7" s="16">
         <v>1.5</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>168</v>
+        <v>165</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>309</v>
+        <v>305</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>308</v>
+        <v>304</v>
       </c>
       <c r="G7" s="17" t="s">
-        <v>310</v>
+        <v>306</v>
       </c>
       <c r="H7" s="16"/>
       <c r="I7" s="16"/>
     </row>
     <row r="8" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="57">
+      <c r="A8" s="75">
         <v>5</v>
       </c>
-      <c r="B8" s="57" t="s">
+      <c r="B8" s="75" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="18">
@@ -4664,8 +4875,8 @@
       </c>
     </row>
     <row r="9" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="58"/>
-      <c r="B9" s="58"/>
+      <c r="A9" s="76"/>
+      <c r="B9" s="76"/>
       <c r="C9" s="18">
         <v>5.2</v>
       </c>
@@ -4685,8 +4896,8 @@
       <c r="I9" s="18"/>
     </row>
     <row r="10" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="58"/>
-      <c r="B10" s="58"/>
+      <c r="A10" s="76"/>
+      <c r="B10" s="76"/>
       <c r="C10" s="18">
         <v>5.3</v>
       </c>
@@ -4706,52 +4917,52 @@
       <c r="I10" s="18"/>
     </row>
     <row r="11" spans="1:9" s="14" customFormat="1" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="58"/>
-      <c r="B11" s="58"/>
+      <c r="A11" s="76"/>
+      <c r="B11" s="76"/>
       <c r="C11" s="21">
         <v>5.4</v>
       </c>
       <c r="D11" s="21" t="s">
+        <v>169</v>
+      </c>
+      <c r="E11" s="21" t="s">
         <v>172</v>
       </c>
-      <c r="E11" s="21" t="s">
-        <v>175</v>
-      </c>
       <c r="F11" s="21" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>176</v>
+        <v>173</v>
       </c>
       <c r="H11" s="23"/>
       <c r="I11" s="21"/>
     </row>
     <row r="12" spans="1:9" s="14" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="59"/>
-      <c r="B12" s="59"/>
+      <c r="A12" s="77"/>
+      <c r="B12" s="77"/>
       <c r="C12" s="21">
         <v>5.5</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="H12" s="23"/>
       <c r="I12" s="21"/>
     </row>
     <row r="13" spans="1:9" s="14" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="49">
+      <c r="A13" s="68">
         <v>6</v>
       </c>
-      <c r="B13" s="49" t="s">
+      <c r="B13" s="68" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="21">
@@ -4777,8 +4988,8 @@
       </c>
     </row>
     <row r="14" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A14" s="50"/>
-      <c r="B14" s="50"/>
+      <c r="A14" s="69"/>
+      <c r="B14" s="69"/>
       <c r="C14" s="24">
         <v>6.2</v>
       </c>
@@ -4786,20 +4997,20 @@
         <v>26</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>178</v>
+        <v>175</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>177</v>
+        <v>174</v>
       </c>
       <c r="G14" s="25" t="s">
-        <v>179</v>
+        <v>176</v>
       </c>
       <c r="H14" s="26"/>
       <c r="I14" s="24"/>
     </row>
     <row r="15" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="50"/>
-      <c r="B15" s="50"/>
+      <c r="A15" s="69"/>
+      <c r="B15" s="69"/>
       <c r="C15" s="24">
         <v>6.3</v>
       </c>
@@ -4819,8 +5030,8 @@
       <c r="I15" s="24"/>
     </row>
     <row r="16" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A16" s="50"/>
-      <c r="B16" s="51"/>
+      <c r="A16" s="69"/>
+      <c r="B16" s="70"/>
       <c r="C16" s="27">
         <v>6.4</v>
       </c>
@@ -4844,10 +5055,10 @@
       </c>
     </row>
     <row r="17" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A17" s="52">
+      <c r="A17" s="71">
         <v>7</v>
       </c>
-      <c r="B17" s="49" t="s">
+      <c r="B17" s="68" t="s">
         <v>38</v>
       </c>
       <c r="C17" s="24">
@@ -4873,8 +5084,8 @@
       </c>
     </row>
     <row r="18" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A18" s="53"/>
-      <c r="B18" s="50"/>
+      <c r="A18" s="72"/>
+      <c r="B18" s="69"/>
       <c r="C18" s="24">
         <v>7.2</v>
       </c>
@@ -4896,8 +5107,8 @@
       </c>
     </row>
     <row r="19" spans="1:9" s="6" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="53"/>
-      <c r="B19" s="50"/>
+      <c r="A19" s="72"/>
+      <c r="B19" s="69"/>
       <c r="C19" s="24">
         <v>7.3</v>
       </c>
@@ -4917,8 +5128,8 @@
       <c r="I19" s="24"/>
     </row>
     <row r="20" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="54"/>
-      <c r="B20" s="51"/>
+      <c r="A20" s="73"/>
+      <c r="B20" s="70"/>
       <c r="C20" s="24">
         <v>7.4</v>
       </c>
@@ -4938,10 +5149,10 @@
       <c r="I20" s="24"/>
     </row>
     <row r="21" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="77">
+      <c r="A21" s="51">
         <v>8</v>
       </c>
-      <c r="B21" s="77" t="s">
+      <c r="B21" s="51" t="s">
         <v>50</v>
       </c>
       <c r="C21" s="28">
@@ -4965,8 +5176,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="78"/>
-      <c r="B22" s="78"/>
+      <c r="A22" s="52"/>
+      <c r="B22" s="52"/>
       <c r="C22" s="28">
         <v>9.3000000000000007</v>
       </c>
@@ -4988,8 +5199,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="79"/>
-      <c r="B23" s="79"/>
+      <c r="A23" s="53"/>
+      <c r="B23" s="53"/>
       <c r="C23" s="28">
         <v>9.4</v>
       </c>
@@ -5011,10 +5222,10 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="75">
+      <c r="A24" s="49">
         <v>12</v>
       </c>
-      <c r="B24" s="75" t="s">
+      <c r="B24" s="49" t="s">
         <v>64</v>
       </c>
       <c r="C24" s="31">
@@ -5040,8 +5251,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="75"/>
-      <c r="B25" s="75"/>
+      <c r="A25" s="49"/>
+      <c r="B25" s="49"/>
       <c r="C25" s="31">
         <v>12.2</v>
       </c>
@@ -5065,8 +5276,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="75"/>
-      <c r="B26" s="75"/>
+      <c r="A26" s="49"/>
+      <c r="B26" s="49"/>
       <c r="C26" s="31">
         <v>12.3</v>
       </c>
@@ -5090,8 +5301,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" s="6" customFormat="1" ht="123.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="75"/>
-      <c r="B27" s="75"/>
+      <c r="A27" s="49"/>
+      <c r="B27" s="49"/>
       <c r="C27" s="31">
         <v>12.4</v>
       </c>
@@ -5099,13 +5310,13 @@
         <v>65</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>275</v>
+        <v>272</v>
       </c>
       <c r="G27" s="32" t="s">
-        <v>276</v>
+        <v>273</v>
       </c>
       <c r="H27" s="31" t="s">
         <v>69</v>
@@ -5115,8 +5326,8 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="75"/>
-      <c r="B28" s="75"/>
+      <c r="A28" s="49"/>
+      <c r="B28" s="49"/>
       <c r="C28" s="31">
         <v>12.5</v>
       </c>
@@ -5127,7 +5338,7 @@
         <v>78</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G28" s="32" t="s">
         <v>79</v>
@@ -5157,10 +5368,10 @@
       <c r="I29" s="34"/>
     </row>
     <row r="30" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="76">
+      <c r="A30" s="50">
         <v>14</v>
       </c>
-      <c r="B30" s="76" t="s">
+      <c r="B30" s="50" t="s">
         <v>80</v>
       </c>
       <c r="C30" s="35">
@@ -5170,13 +5381,13 @@
         <v>133</v>
       </c>
       <c r="E30" s="36" t="s">
-        <v>244</v>
+        <v>241</v>
       </c>
       <c r="F30" s="36" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>260</v>
+        <v>257</v>
       </c>
       <c r="H30" s="35" t="s">
         <v>82</v>
@@ -5186,8 +5397,8 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="76"/>
-      <c r="B31" s="76"/>
+      <c r="A31" s="50"/>
+      <c r="B31" s="50"/>
       <c r="C31" s="35">
         <v>14.2</v>
       </c>
@@ -5195,13 +5406,13 @@
         <v>133</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>245</v>
+        <v>242</v>
       </c>
       <c r="F31" s="36" t="s">
-        <v>246</v>
+        <v>243</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>261</v>
+        <v>258</v>
       </c>
       <c r="H31" s="35" t="s">
         <v>82</v>
@@ -5211,22 +5422,22 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="76"/>
-      <c r="B32" s="76"/>
+      <c r="A32" s="50"/>
+      <c r="B32" s="50"/>
       <c r="C32" s="35">
         <v>14.3</v>
       </c>
       <c r="D32" s="36" t="s">
-        <v>215</v>
+        <v>212</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>247</v>
+        <v>244</v>
       </c>
       <c r="F32" s="36" t="s">
-        <v>248</v>
+        <v>245</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>262</v>
+        <v>259</v>
       </c>
       <c r="H32" s="35" t="s">
         <v>82</v>
@@ -5236,8 +5447,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="76"/>
-      <c r="B33" s="76"/>
+      <c r="A33" s="50"/>
+      <c r="B33" s="50"/>
       <c r="C33" s="35">
         <v>14.4</v>
       </c>
@@ -5245,13 +5456,13 @@
         <v>133</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>249</v>
+        <v>246</v>
       </c>
       <c r="F33" s="36" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>263</v>
+        <v>260</v>
       </c>
       <c r="H33" s="35" t="s">
         <v>82</v>
@@ -5261,8 +5472,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="76"/>
-      <c r="B34" s="76"/>
+      <c r="A34" s="50"/>
+      <c r="B34" s="50"/>
       <c r="C34" s="35">
         <v>14.5</v>
       </c>
@@ -5270,13 +5481,13 @@
         <v>133</v>
       </c>
       <c r="E34" s="36" t="s">
-        <v>250</v>
+        <v>247</v>
       </c>
       <c r="F34" s="36" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="H34" s="35" t="s">
         <v>82</v>
@@ -5286,8 +5497,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="76"/>
-      <c r="B35" s="76"/>
+      <c r="A35" s="50"/>
+      <c r="B35" s="50"/>
       <c r="C35" s="35">
         <v>14.6</v>
       </c>
@@ -5295,13 +5506,13 @@
         <v>133</v>
       </c>
       <c r="E35" s="36" t="s">
-        <v>251</v>
+        <v>248</v>
       </c>
       <c r="F35" s="36" t="s">
-        <v>252</v>
+        <v>249</v>
       </c>
       <c r="G35" s="37" t="s">
-        <v>265</v>
+        <v>262</v>
       </c>
       <c r="H35" s="35" t="s">
         <v>82</v>
@@ -5311,8 +5522,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="76"/>
-      <c r="B36" s="76"/>
+      <c r="A36" s="50"/>
+      <c r="B36" s="50"/>
       <c r="C36" s="35">
         <v>14.7</v>
       </c>
@@ -5320,13 +5531,13 @@
         <v>133</v>
       </c>
       <c r="E36" s="36" t="s">
-        <v>253</v>
+        <v>250</v>
       </c>
       <c r="F36" s="36" t="s">
-        <v>254</v>
+        <v>251</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>266</v>
+        <v>263</v>
       </c>
       <c r="H36" s="35" t="s">
         <v>82</v>
@@ -5336,8 +5547,8 @@
       </c>
     </row>
     <row r="37" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="76"/>
-      <c r="B37" s="76"/>
+      <c r="A37" s="50"/>
+      <c r="B37" s="50"/>
       <c r="C37" s="35">
         <v>14.8</v>
       </c>
@@ -5345,13 +5556,13 @@
         <v>133</v>
       </c>
       <c r="E37" s="36" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="F37" s="36" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="G37" s="37" t="s">
-        <v>267</v>
+        <v>264</v>
       </c>
       <c r="H37" s="35" t="s">
         <v>84</v>
@@ -5361,8 +5572,8 @@
       </c>
     </row>
     <row r="38" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A38" s="76"/>
-      <c r="B38" s="76"/>
+      <c r="A38" s="50"/>
+      <c r="B38" s="50"/>
       <c r="C38" s="35">
         <v>14.9</v>
       </c>
@@ -5370,13 +5581,13 @@
         <v>133</v>
       </c>
       <c r="E38" s="36" t="s">
-        <v>257</v>
+        <v>254</v>
       </c>
       <c r="F38" s="36" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>268</v>
+        <v>265</v>
       </c>
       <c r="H38" s="35" t="s">
         <v>84</v>
@@ -5386,8 +5597,8 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="76"/>
-      <c r="B39" s="76"/>
+      <c r="A39" s="50"/>
+      <c r="B39" s="50"/>
       <c r="C39" s="35">
         <v>14.1</v>
       </c>
@@ -5395,13 +5606,13 @@
         <v>133</v>
       </c>
       <c r="E39" s="36" t="s">
-        <v>258</v>
+        <v>255</v>
       </c>
       <c r="F39" s="36" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>269</v>
+        <v>266</v>
       </c>
       <c r="H39" s="35" t="s">
         <v>84</v>
@@ -5411,8 +5622,8 @@
       </c>
     </row>
     <row r="40" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="76"/>
-      <c r="B40" s="76"/>
+      <c r="A40" s="50"/>
+      <c r="B40" s="50"/>
       <c r="C40" s="35">
         <v>14.11</v>
       </c>
@@ -5420,13 +5631,13 @@
         <v>133</v>
       </c>
       <c r="E40" s="36" t="s">
-        <v>259</v>
+        <v>256</v>
       </c>
       <c r="F40" s="36" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>270</v>
+        <v>267</v>
       </c>
       <c r="H40" s="35" t="s">
         <v>84</v>
@@ -5436,10 +5647,10 @@
       </c>
     </row>
     <row r="41" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A41" s="62">
+      <c r="A41" s="54">
         <v>15</v>
       </c>
-      <c r="B41" s="62" t="s">
+      <c r="B41" s="54" t="s">
         <v>85</v>
       </c>
       <c r="C41" s="38">
@@ -5455,7 +5666,7 @@
         <v>88</v>
       </c>
       <c r="G41" s="39" t="s">
-        <v>180</v>
+        <v>177</v>
       </c>
       <c r="H41" s="38" t="s">
         <v>123</v>
@@ -5465,8 +5676,8 @@
       </c>
     </row>
     <row r="42" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="56"/>
-      <c r="B42" s="56"/>
+      <c r="A42" s="55"/>
+      <c r="B42" s="55"/>
       <c r="C42" s="38">
         <v>15.2</v>
       </c>
@@ -5480,7 +5691,7 @@
         <v>90</v>
       </c>
       <c r="G42" s="39" t="s">
-        <v>181</v>
+        <v>178</v>
       </c>
       <c r="H42" s="38" t="s">
         <v>107</v>
@@ -5490,8 +5701,8 @@
       </c>
     </row>
     <row r="43" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="56"/>
-      <c r="B43" s="56"/>
+      <c r="A43" s="55"/>
+      <c r="B43" s="55"/>
       <c r="C43" s="38">
         <v>15.3</v>
       </c>
@@ -5505,7 +5716,7 @@
         <v>92</v>
       </c>
       <c r="G43" s="39" t="s">
-        <v>182</v>
+        <v>179</v>
       </c>
       <c r="H43" s="38" t="s">
         <v>107</v>
@@ -5515,8 +5726,8 @@
       </c>
     </row>
     <row r="44" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A44" s="56"/>
-      <c r="B44" s="56"/>
+      <c r="A44" s="55"/>
+      <c r="B44" s="55"/>
       <c r="C44" s="38">
         <v>15.4</v>
       </c>
@@ -5530,7 +5741,7 @@
         <v>94</v>
       </c>
       <c r="G44" s="39" t="s">
-        <v>183</v>
+        <v>180</v>
       </c>
       <c r="H44" s="38" t="s">
         <v>107</v>
@@ -5540,8 +5751,8 @@
       </c>
     </row>
     <row r="45" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="56"/>
-      <c r="B45" s="56"/>
+      <c r="A45" s="55"/>
+      <c r="B45" s="55"/>
       <c r="C45" s="38">
         <v>15.5</v>
       </c>
@@ -5555,7 +5766,7 @@
         <v>96</v>
       </c>
       <c r="G45" s="39" t="s">
-        <v>184</v>
+        <v>181</v>
       </c>
       <c r="H45" s="38" t="s">
         <v>107</v>
@@ -5565,8 +5776,8 @@
       </c>
     </row>
     <row r="46" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="56"/>
-      <c r="B46" s="56"/>
+      <c r="A46" s="55"/>
+      <c r="B46" s="55"/>
       <c r="C46" s="38">
         <v>15.6</v>
       </c>
@@ -5580,7 +5791,7 @@
         <v>98</v>
       </c>
       <c r="G46" s="39" t="s">
-        <v>185</v>
+        <v>182</v>
       </c>
       <c r="H46" s="38" t="s">
         <v>107</v>
@@ -5590,8 +5801,8 @@
       </c>
     </row>
     <row r="47" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A47" s="56"/>
-      <c r="B47" s="56"/>
+      <c r="A47" s="55"/>
+      <c r="B47" s="55"/>
       <c r="C47" s="38">
         <v>15.7</v>
       </c>
@@ -5605,7 +5816,7 @@
         <v>100</v>
       </c>
       <c r="G47" s="39" t="s">
-        <v>186</v>
+        <v>183</v>
       </c>
       <c r="H47" s="38" t="s">
         <v>107</v>
@@ -5615,8 +5826,8 @@
       </c>
     </row>
     <row r="48" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="56"/>
-      <c r="B48" s="56"/>
+      <c r="A48" s="55"/>
+      <c r="B48" s="55"/>
       <c r="C48" s="38">
         <v>15.8</v>
       </c>
@@ -5630,7 +5841,7 @@
         <v>102</v>
       </c>
       <c r="G48" s="39" t="s">
-        <v>187</v>
+        <v>184</v>
       </c>
       <c r="H48" s="38" t="s">
         <v>107</v>
@@ -5640,10 +5851,10 @@
       </c>
     </row>
     <row r="49" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A49" s="69">
+      <c r="A49" s="62">
         <v>16</v>
       </c>
-      <c r="B49" s="69" t="s">
+      <c r="B49" s="62" t="s">
         <v>103</v>
       </c>
       <c r="C49" s="40">
@@ -5659,7 +5870,7 @@
         <v>106</v>
       </c>
       <c r="G49" s="42" t="s">
-        <v>188</v>
+        <v>185</v>
       </c>
       <c r="H49" s="41" t="s">
         <v>107</v>
@@ -5669,8 +5880,8 @@
       </c>
     </row>
     <row r="50" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A50" s="69"/>
-      <c r="B50" s="69"/>
+      <c r="A50" s="62"/>
+      <c r="B50" s="62"/>
       <c r="C50" s="40">
         <v>16.2</v>
       </c>
@@ -5684,7 +5895,7 @@
         <v>110</v>
       </c>
       <c r="G50" s="42" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
       <c r="H50" s="41" t="s">
         <v>107</v>
@@ -5694,8 +5905,8 @@
       </c>
     </row>
     <row r="51" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="69"/>
-      <c r="B51" s="69"/>
+      <c r="A51" s="62"/>
+      <c r="B51" s="62"/>
       <c r="C51" s="40">
         <v>16.3</v>
       </c>
@@ -5709,7 +5920,7 @@
         <v>112</v>
       </c>
       <c r="G51" s="42" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="H51" s="41" t="s">
         <v>107</v>
@@ -5719,8 +5930,8 @@
       </c>
     </row>
     <row r="52" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A52" s="69"/>
-      <c r="B52" s="69"/>
+      <c r="A52" s="62"/>
+      <c r="B52" s="62"/>
       <c r="C52" s="40">
         <v>16.399999999999999</v>
       </c>
@@ -5734,7 +5945,7 @@
         <v>114</v>
       </c>
       <c r="G52" s="42" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="H52" s="41" t="s">
         <v>107</v>
@@ -5744,8 +5955,8 @@
       </c>
     </row>
     <row r="53" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A53" s="69"/>
-      <c r="B53" s="69"/>
+      <c r="A53" s="62"/>
+      <c r="B53" s="62"/>
       <c r="C53" s="40">
         <v>16.5</v>
       </c>
@@ -5759,7 +5970,7 @@
         <v>116</v>
       </c>
       <c r="G53" s="42" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
       <c r="H53" s="41" t="s">
         <v>107</v>
@@ -5769,8 +5980,8 @@
       </c>
     </row>
     <row r="54" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A54" s="56"/>
-      <c r="B54" s="56"/>
+      <c r="A54" s="55"/>
+      <c r="B54" s="55"/>
       <c r="C54" s="40">
         <v>16.600000000000001</v>
       </c>
@@ -5784,7 +5995,7 @@
         <v>118</v>
       </c>
       <c r="G54" s="42" t="s">
-        <v>193</v>
+        <v>190</v>
       </c>
       <c r="H54" s="41" t="s">
         <v>107</v>
@@ -5794,10 +6005,10 @@
       </c>
     </row>
     <row r="55" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A55" s="70">
+      <c r="A55" s="63">
         <v>17</v>
       </c>
-      <c r="B55" s="73" t="s">
+      <c r="B55" s="66" t="s">
         <v>119</v>
       </c>
       <c r="C55" s="43">
@@ -5813,7 +6024,7 @@
         <v>122</v>
       </c>
       <c r="G55" s="44" t="s">
-        <v>194</v>
+        <v>191</v>
       </c>
       <c r="H55" s="43" t="s">
         <v>123</v>
@@ -5823,8 +6034,8 @@
       </c>
     </row>
     <row r="56" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A56" s="71"/>
-      <c r="B56" s="73"/>
+      <c r="A56" s="64"/>
+      <c r="B56" s="66"/>
       <c r="C56" s="43">
         <v>17.2</v>
       </c>
@@ -5838,7 +6049,7 @@
         <v>125</v>
       </c>
       <c r="G56" s="44" t="s">
-        <v>195</v>
+        <v>192</v>
       </c>
       <c r="H56" s="43" t="s">
         <v>123</v>
@@ -5848,8 +6059,8 @@
       </c>
     </row>
     <row r="57" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A57" s="71"/>
-      <c r="B57" s="73"/>
+      <c r="A57" s="64"/>
+      <c r="B57" s="66"/>
       <c r="C57" s="43">
         <v>17.3</v>
       </c>
@@ -5863,7 +6074,7 @@
         <v>127</v>
       </c>
       <c r="G57" s="44" t="s">
-        <v>196</v>
+        <v>193</v>
       </c>
       <c r="H57" s="43" t="s">
         <v>107</v>
@@ -5873,8 +6084,8 @@
       </c>
     </row>
     <row r="58" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A58" s="71"/>
-      <c r="B58" s="73"/>
+      <c r="A58" s="64"/>
+      <c r="B58" s="66"/>
       <c r="C58" s="43">
         <v>17.399999999999999</v>
       </c>
@@ -5888,7 +6099,7 @@
         <v>129</v>
       </c>
       <c r="G58" s="44" t="s">
-        <v>197</v>
+        <v>194</v>
       </c>
       <c r="H58" s="43" t="s">
         <v>123</v>
@@ -5898,8 +6109,8 @@
       </c>
     </row>
     <row r="59" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A59" s="72"/>
-      <c r="B59" s="73"/>
+      <c r="A59" s="65"/>
+      <c r="B59" s="66"/>
       <c r="C59" s="43">
         <v>17.5</v>
       </c>
@@ -5913,7 +6124,7 @@
         <v>131</v>
       </c>
       <c r="G59" s="44" t="s">
-        <v>198</v>
+        <v>195</v>
       </c>
       <c r="H59" s="43" t="s">
         <v>123</v>
@@ -5923,10 +6134,10 @@
       </c>
     </row>
     <row r="60" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A60" s="74">
+      <c r="A60" s="67">
         <v>18</v>
       </c>
-      <c r="B60" s="74" t="s">
+      <c r="B60" s="67" t="s">
         <v>132</v>
       </c>
       <c r="C60" s="18">
@@ -5936,13 +6147,13 @@
         <v>133</v>
       </c>
       <c r="E60" s="18" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="F60" s="18" t="s">
         <v>134</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="H60" s="18" t="s">
         <v>82</v>
@@ -5952,8 +6163,8 @@
       </c>
     </row>
     <row r="61" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A61" s="56"/>
-      <c r="B61" s="56"/>
+      <c r="A61" s="55"/>
+      <c r="B61" s="55"/>
       <c r="C61" s="18">
         <v>18.2</v>
       </c>
@@ -5961,13 +6172,13 @@
         <v>133</v>
       </c>
       <c r="E61" s="18" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
       <c r="F61" s="18" t="s">
         <v>136</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>200</v>
+        <v>197</v>
       </c>
       <c r="H61" s="18" t="s">
         <v>82</v>
@@ -5977,8 +6188,8 @@
       </c>
     </row>
     <row r="62" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A62" s="56"/>
-      <c r="B62" s="56"/>
+      <c r="A62" s="55"/>
+      <c r="B62" s="55"/>
       <c r="C62" s="18">
         <v>18.3</v>
       </c>
@@ -5986,13 +6197,13 @@
         <v>133</v>
       </c>
       <c r="E62" s="18" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="F62" s="18" t="s">
         <v>137</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>201</v>
+        <v>198</v>
       </c>
       <c r="H62" s="18" t="s">
         <v>82</v>
@@ -6002,8 +6213,8 @@
       </c>
     </row>
     <row r="63" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A63" s="56"/>
-      <c r="B63" s="56"/>
+      <c r="A63" s="55"/>
+      <c r="B63" s="55"/>
       <c r="C63" s="18">
         <v>18.399999999999999</v>
       </c>
@@ -6011,13 +6222,13 @@
         <v>133</v>
       </c>
       <c r="E63" s="18" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
       <c r="F63" s="18" t="s">
         <v>81</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="H63" s="18" t="s">
         <v>82</v>
@@ -6027,8 +6238,8 @@
       </c>
     </row>
     <row r="64" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A64" s="56"/>
-      <c r="B64" s="56"/>
+      <c r="A64" s="55"/>
+      <c r="B64" s="55"/>
       <c r="C64" s="18">
         <v>18.5</v>
       </c>
@@ -6036,13 +6247,13 @@
         <v>133</v>
       </c>
       <c r="E64" s="18" t="s">
-        <v>286</v>
+        <v>283</v>
       </c>
       <c r="F64" s="18" t="s">
         <v>138</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="H64" s="18" t="s">
         <v>82</v>
@@ -6052,8 +6263,8 @@
       </c>
     </row>
     <row r="65" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A65" s="56"/>
-      <c r="B65" s="56"/>
+      <c r="A65" s="55"/>
+      <c r="B65" s="55"/>
       <c r="C65" s="18">
         <v>18.600000000000001</v>
       </c>
@@ -6061,13 +6272,13 @@
         <v>133</v>
       </c>
       <c r="E65" s="18" t="s">
-        <v>287</v>
+        <v>284</v>
       </c>
       <c r="F65" s="18" t="s">
         <v>139</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="H65" s="18" t="s">
         <v>82</v>
@@ -6077,8 +6288,8 @@
       </c>
     </row>
     <row r="66" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A66" s="56"/>
-      <c r="B66" s="56"/>
+      <c r="A66" s="55"/>
+      <c r="B66" s="55"/>
       <c r="C66" s="18">
         <v>18.7</v>
       </c>
@@ -6086,13 +6297,13 @@
         <v>133</v>
       </c>
       <c r="E66" s="18" t="s">
-        <v>288</v>
+        <v>285</v>
       </c>
       <c r="F66" s="18" t="s">
         <v>140</v>
       </c>
       <c r="G66" s="19" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="H66" s="18" t="s">
         <v>82</v>
@@ -6102,8 +6313,8 @@
       </c>
     </row>
     <row r="67" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A67" s="56"/>
-      <c r="B67" s="56"/>
+      <c r="A67" s="55"/>
+      <c r="B67" s="55"/>
       <c r="C67" s="18">
         <v>18.8</v>
       </c>
@@ -6111,13 +6322,13 @@
         <v>133</v>
       </c>
       <c r="E67" s="18" t="s">
-        <v>289</v>
+        <v>286</v>
       </c>
       <c r="F67" s="18" t="s">
         <v>141</v>
       </c>
       <c r="G67" s="19" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="H67" s="18" t="s">
         <v>82</v>
@@ -6127,8 +6338,8 @@
       </c>
     </row>
     <row r="68" spans="1:12" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="56"/>
-      <c r="B68" s="56"/>
+      <c r="A68" s="55"/>
+      <c r="B68" s="55"/>
       <c r="C68" s="18">
         <v>18.899999999999999</v>
       </c>
@@ -6136,13 +6347,13 @@
         <v>133</v>
       </c>
       <c r="E68" s="18" t="s">
-        <v>290</v>
+        <v>287</v>
       </c>
       <c r="F68" s="18" t="s">
         <v>142</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>207</v>
+        <v>204</v>
       </c>
       <c r="H68" s="18" t="s">
         <v>82</v>
@@ -6152,10 +6363,10 @@
       </c>
     </row>
     <row r="69" spans="1:12" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A69" s="63">
+      <c r="A69" s="56">
         <v>19</v>
       </c>
-      <c r="B69" s="66" t="s">
+      <c r="B69" s="59" t="s">
         <v>143</v>
       </c>
       <c r="C69" s="45">
@@ -6165,20 +6376,20 @@
         <v>144</v>
       </c>
       <c r="E69" s="46" t="s">
-        <v>278</v>
+        <v>275</v>
       </c>
       <c r="F69" s="46" t="s">
-        <v>277</v>
+        <v>274</v>
       </c>
       <c r="G69" s="47" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
       <c r="H69" s="45"/>
       <c r="I69" s="48"/>
     </row>
     <row r="70" spans="1:12" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="64"/>
-      <c r="B70" s="67"/>
+      <c r="A70" s="57"/>
+      <c r="B70" s="60"/>
       <c r="C70" s="15">
         <v>19.2</v>
       </c>
@@ -6189,7 +6400,7 @@
         <v>146</v>
       </c>
       <c r="F70" s="46" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G70" s="47" t="s">
         <v>147</v>
@@ -6198,8 +6409,8 @@
       <c r="I70" s="48"/>
     </row>
     <row r="71" spans="1:12" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="65"/>
-      <c r="B71" s="68"/>
+      <c r="A71" s="58"/>
+      <c r="B71" s="61"/>
       <c r="C71" s="34">
         <v>19.3</v>
       </c>
@@ -6217,10 +6428,10 @@
       <c r="I71" s="34"/>
     </row>
     <row r="72" spans="1:12" s="6" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="63">
+      <c r="A72" s="56">
         <v>20</v>
       </c>
-      <c r="B72" s="66" t="s">
+      <c r="B72" s="59" t="s">
         <v>150</v>
       </c>
       <c r="C72" s="45">
@@ -6230,20 +6441,20 @@
         <v>151</v>
       </c>
       <c r="E72" s="46" t="s">
-        <v>299</v>
+        <v>296</v>
       </c>
       <c r="F72" s="46" t="s">
-        <v>300</v>
+        <v>297</v>
       </c>
       <c r="G72" s="47" t="s">
-        <v>301</v>
+        <v>298</v>
       </c>
       <c r="H72" s="45"/>
       <c r="I72" s="48"/>
     </row>
     <row r="73" spans="1:12" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A73" s="64"/>
-      <c r="B73" s="67"/>
+      <c r="A73" s="57"/>
+      <c r="B73" s="60"/>
       <c r="C73" s="15">
         <v>20.2</v>
       </c>
@@ -6251,13 +6462,13 @@
         <v>152</v>
       </c>
       <c r="E73" s="46" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="F73" s="46" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G73" s="47" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
       <c r="H73" s="45"/>
       <c r="I73" s="48"/>
@@ -6266,8 +6477,8 @@
       <c r="L73" s="1"/>
     </row>
     <row r="74" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A74" s="65"/>
-      <c r="B74" s="68"/>
+      <c r="A74" s="58"/>
+      <c r="B74" s="61"/>
       <c r="C74" s="33">
         <v>20.3</v>
       </c>
@@ -6286,10 +6497,10 @@
       <c r="L74" s="1"/>
     </row>
     <row r="75" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A75" s="63">
+      <c r="A75" s="56">
         <v>21</v>
       </c>
-      <c r="B75" s="66" t="s">
+      <c r="B75" s="59" t="s">
         <v>153</v>
       </c>
       <c r="C75" s="45">
@@ -6299,20 +6510,20 @@
         <v>154</v>
       </c>
       <c r="E75" s="46" t="s">
-        <v>291</v>
+        <v>288</v>
       </c>
       <c r="F75" s="46" t="s">
-        <v>292</v>
+        <v>289</v>
       </c>
       <c r="G75" s="47" t="s">
-        <v>293</v>
+        <v>290</v>
       </c>
       <c r="H75" s="45"/>
       <c r="I75" s="48"/>
     </row>
     <row r="76" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="64"/>
-      <c r="B76" s="67"/>
+      <c r="A76" s="57"/>
+      <c r="B76" s="60"/>
       <c r="C76" s="15">
         <v>21.2</v>
       </c>
@@ -6320,10 +6531,10 @@
         <v>155</v>
       </c>
       <c r="E76" s="46" t="s">
-        <v>272</v>
+        <v>269</v>
       </c>
       <c r="F76" s="46" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G76" s="47" t="s">
         <v>156</v>
@@ -6332,8 +6543,8 @@
       <c r="I76" s="48"/>
     </row>
     <row r="77" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A77" s="65"/>
-      <c r="B77" s="68"/>
+      <c r="A77" s="58"/>
+      <c r="B77" s="61"/>
       <c r="C77" s="33">
         <v>21.3</v>
       </c>
@@ -6349,10 +6560,10 @@
       <c r="I77" s="34"/>
     </row>
     <row r="78" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A78" s="63">
+      <c r="A78" s="56">
         <v>22</v>
       </c>
-      <c r="B78" s="66" t="s">
+      <c r="B78" s="59" t="s">
         <v>157</v>
       </c>
       <c r="C78" s="45">
@@ -6362,41 +6573,41 @@
         <v>158</v>
       </c>
       <c r="E78" s="46" t="s">
-        <v>296</v>
+        <v>293</v>
       </c>
       <c r="F78" s="46" t="s">
-        <v>297</v>
+        <v>294</v>
       </c>
       <c r="G78" s="47" t="s">
-        <v>298</v>
+        <v>295</v>
       </c>
       <c r="H78" s="45"/>
       <c r="I78" s="48"/>
     </row>
     <row r="79" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A79" s="64"/>
-      <c r="B79" s="67"/>
+      <c r="A79" s="57"/>
+      <c r="B79" s="60"/>
       <c r="C79" s="15">
         <v>22.2</v>
       </c>
       <c r="D79" s="46" t="s">
-        <v>271</v>
+        <v>268</v>
       </c>
       <c r="E79" s="45" t="s">
-        <v>294</v>
+        <v>291</v>
       </c>
       <c r="F79" s="46" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="G79" s="47" t="s">
-        <v>295</v>
+        <v>292</v>
       </c>
       <c r="H79" s="45"/>
       <c r="I79" s="48"/>
     </row>
     <row r="80" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A80" s="65"/>
-      <c r="B80" s="68"/>
+      <c r="A80" s="58"/>
+      <c r="B80" s="61"/>
       <c r="C80" s="33">
         <v>22.3</v>
       </c>
@@ -6512,12 +6723,21 @@
   </sheetData>
   <autoFilter ref="I1:I26" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="37">
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="A30:A40"/>
-    <mergeCell ref="B30:B40"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B17:B20"/>
     <mergeCell ref="A41:A48"/>
     <mergeCell ref="B41:B48"/>
     <mergeCell ref="A75:A77"/>
@@ -6534,21 +6754,12 @@
     <mergeCell ref="B69:B71"/>
     <mergeCell ref="A72:A74"/>
     <mergeCell ref="B72:B74"/>
-    <mergeCell ref="A13:A16"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="A17:A20"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="A30:A40"/>
+    <mergeCell ref="B30:B40"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="B21:B23"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6609,7 +6820,7 @@
         <v>8</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>208</v>
+        <v>205</v>
       </c>
       <c r="I3" s="12" t="s">
         <v>4</v>
@@ -6630,13 +6841,13 @@
         <v>133</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="J4" s="9"/>
     </row>
@@ -6654,13 +6865,13 @@
         <v>133</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>212</v>
+        <v>209</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>214</v>
+        <v>211</v>
       </c>
       <c r="J5" s="9"/>
     </row>
@@ -6675,16 +6886,16 @@
         <v>14.3</v>
       </c>
       <c r="F6" s="8" t="s">
+        <v>212</v>
+      </c>
+      <c r="G6" s="8" t="s">
+        <v>213</v>
+      </c>
+      <c r="H6" s="8" t="s">
+        <v>214</v>
+      </c>
+      <c r="I6" s="13" t="s">
         <v>215</v>
-      </c>
-      <c r="G6" s="8" t="s">
-        <v>216</v>
-      </c>
-      <c r="H6" s="8" t="s">
-        <v>217</v>
-      </c>
-      <c r="I6" s="13" t="s">
-        <v>218</v>
       </c>
       <c r="J6" s="9"/>
     </row>
@@ -6702,13 +6913,13 @@
         <v>133</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>219</v>
+        <v>216</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>220</v>
+        <v>217</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>221</v>
+        <v>218</v>
       </c>
       <c r="J7" s="9"/>
     </row>
@@ -6726,13 +6937,13 @@
         <v>133</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>222</v>
+        <v>219</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>223</v>
+        <v>220</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>224</v>
+        <v>221</v>
       </c>
       <c r="J8" s="9"/>
     </row>
@@ -6750,13 +6961,13 @@
         <v>133</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>225</v>
+        <v>222</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>226</v>
+        <v>223</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
       <c r="J9" s="9"/>
     </row>
@@ -6774,13 +6985,13 @@
         <v>133</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>230</v>
+        <v>227</v>
       </c>
       <c r="J10" s="9"/>
     </row>
@@ -6798,13 +7009,13 @@
         <v>133</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>231</v>
+        <v>228</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>232</v>
+        <v>229</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>233</v>
+        <v>230</v>
       </c>
       <c r="J11" s="9"/>
     </row>
@@ -6822,13 +7033,13 @@
         <v>133</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>234</v>
+        <v>231</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>235</v>
+        <v>232</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>236</v>
+        <v>233</v>
       </c>
       <c r="J12" s="9"/>
     </row>
@@ -6840,19 +7051,19 @@
         <v>80</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>237</v>
+        <v>234</v>
       </c>
       <c r="F13" s="8" t="s">
         <v>133</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>238</v>
+        <v>235</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>239</v>
+        <v>236</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>240</v>
+        <v>237</v>
       </c>
       <c r="J13" s="9"/>
     </row>
@@ -6870,13 +7081,13 @@
         <v>133</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>241</v>
+        <v>238</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>242</v>
+        <v>239</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>243</v>
+        <v>240</v>
       </c>
       <c r="J14" s="9"/>
     </row>

--- a/Soubhanik/checkupp_product_backlog_final.xlsx
+++ b/Soubhanik/checkupp_product_backlog_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Soubhanik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{CC212EFE-3A18-44FF-AB50-E204DB1FF9D3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7C2148-AF37-4B48-840E-CB1FDC0E937A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -189,7 +189,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="492" uniqueCount="311">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="316">
   <si>
     <t>Epic #</t>
   </si>
@@ -397,25 +397,10 @@
     <t>tap a health check and indicate I haven't done it</t>
   </si>
   <si>
-    <t>I am taken to the booking/appointment screen</t>
-  </si>
-  <si>
-    <t>1. 'No' on health check confirmation must lead to the Book Appointment screen
-2. Booking flow must be initiated</t>
-  </si>
-  <si>
     <t>user</t>
   </si>
   <si>
-    <t>book a health check appointment from within the app</t>
-  </si>
-  <si>
     <t>I can schedule a required screening without leaving the app</t>
-  </si>
-  <si>
-    <t>1. Book Appointment screen must be accessible after selecting 'No' on a health check
-2. Integration with HotDocs API via Railway must be in place
-3. Booking confirmation must be displayed on success</t>
   </si>
   <si>
     <t>Mental Health Assessment</t>
@@ -479,9 +464,6 @@
     <t>Screenings Schedule</t>
   </si>
   <si>
-    <t>I can schedule future health appointments</t>
-  </si>
-  <si>
     <t>Slide 24</t>
   </si>
   <si>
@@ -563,21 +545,6 @@
     <t>I can view trimester-specific blood tests, ultrasounds and doctor visits</t>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">mark a prenatal appointment or test as completed on the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Prenatal Checklist screen</t>
-    </r>
-  </si>
-  <si>
     <t>I can monitor my completed pregnancy checks</t>
   </si>
   <si>
@@ -626,9 +593,6 @@
     </r>
   </si>
   <si>
-    <t>I can view and manage my scheduled pregnancy appointments</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">view reminder cards on the </t>
     </r>
@@ -644,9 +608,6 @@
     </r>
   </si>
   <si>
-    <t>I receive timely reminders for upcoming prenatal appointments and tests</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">view my pregnancy summary on the </t>
     </r>
@@ -948,9 +909,6 @@
       </rPr>
       <t>Health Check History</t>
     </r>
-  </si>
-  <si>
-    <t>I can sync my appointment with my device calendar and receive reminders</t>
   </si>
   <si>
     <t>Cardiovascular Reading</t>
@@ -1007,12 +965,6 @@
     <t>logged in user navigating the Dental Health Check screen</t>
   </si>
   <si>
-    <t>I can keep track of my scheduled healthcare appointments.</t>
-  </si>
-  <si>
-    <t>I can keep track of appointments that have been rescheduled.</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">Tap on the </t>
     </r>
@@ -1063,9 +1015,6 @@
       </rPr>
       <t xml:space="preserve"> option for the links in my Document Wallet</t>
     </r>
-  </si>
-  <si>
-    <t>tap Your Health Overview section on the Home Screen</t>
   </si>
   <si>
     <t>logged-in user</t>
@@ -1140,28 +1089,12 @@
 4. Each checklist item must display its completion status.</t>
   </si>
   <si>
-    <t>1. Users must be able to mark prenatal appointments and tests as completed.
-2. Completed checklist items must be visually distinguished.
-3. Completion status must be saved to the user's pregnancy record.</t>
-  </si>
-  <si>
     <t>1. Tapping Upload Documents must open the Document Wallet.
 2. Users must be able to upload supported document types.
 3. Uploaded documents must be linked to the pregnancy record.
 4. The system must display a successful upload confirmation.</t>
   </si>
   <si>
-    <t>1. Tapping Hospital Visits must open the Hospital Visits screen.
-2. Upcoming appointments must be displayed.
-3. Appointment details must be accessible.
-4. Users must be able to add future hospital visits.</t>
-  </si>
-  <si>
-    <t>1. Reminder cards must display upcoming prenatal appointments and tests.
-2. Reminder dates must be accurate.
-3. Push notifications must be scheduled before appointment due dates.</t>
-  </si>
-  <si>
     <t>1. The Pregnancy Dashboard must display a pregnancy summary.
 2. The current trimester must be displayed.
 3. The estimated due date must be displayed.
@@ -1238,11 +1171,6 @@
 3. The selected date must be saved with the health check.</t>
   </si>
   <si>
-    <t>1. Appointment Details must include appointment date, time and location.
-2. Appointment information must be saved with the health check.
-3. Calendar Sync must be available for appointments.</t>
-  </si>
-  <si>
     <t>1. Users must be able to create multiple custom fields.
 2. Each custom field must allow a name and description.
 3. Custom fields must remain editable before saving.</t>
@@ -1263,11 +1191,6 @@
 3. The saved record must appear in Health Check History.</t>
   </si>
   <si>
-    <t>1. Selecting Add to Calendar must open the calendar sync flow.
-2. Appointment details must be added to the selected calendar.
-3. A confirmation message must be displayed after successful calendar synchronisation.</t>
-  </si>
-  <si>
     <t>So that</t>
   </si>
   <si>
@@ -2541,21 +2464,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">enter </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Appointment Details while creating a custom health check on the Other Ailments screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">tap </t>
     </r>
     <r>
@@ -2571,21 +2479,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">I can choose to sync my appointment on the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Add to Calendar screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">tap </t>
     </r>
     <r>
@@ -2631,21 +2524,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">review my appointment details on the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Event Preview screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">tap </t>
     </r>
     <r>
@@ -2661,51 +2539,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">I receive confirmation that my appointment has been successfully added to my device calendar on the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Success screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">tap </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>View Upcoming Appointments on the Success screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">I can manage all my upcoming health appointments from the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Upcoming Appointments screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">tap the </t>
     </r>
     <r>
@@ -2777,40 +2610,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>Calendar &amp; Sync Settings screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> User must be able to enter appointment date, time and location.
-2. Appointment details must be linked to the health check.
-3. Appointment information must be saved successfully.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> App must display an Add to Calendar prompt after saving.
-2. User must be able to add or dismiss the prompt.
-3. Appointment details must be retained regardless of the user's choice.</t>
     </r>
   </si>
   <si>
@@ -2876,40 +2675,6 @@
         <family val="2"/>
         <scheme val="minor"/>
       </rPr>
-      <t xml:space="preserve"> App must display a success message after syncing.
-2. User must be able to view the calendar event.
-3. Appointment must exist in the selected calendar.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> Upcoming Appointments screen must display all synced appointments.
-2. Appointments must be grouped by date.
-3. User must be able to open the device calendar from this screen.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
       <t xml:space="preserve"> Tapping the calendar icon must open Calendar &amp; Sync Settings.
 2. Settings must display current sync status.
 3. User must be able to access settings at any time.</t>
@@ -2930,40 +2695,6 @@
       <t xml:space="preserve"> User must be able to turn Calendar Sync on or off.
 2. Preference must be saved across sessions.
 3. Existing calendar events must remain unaffected when sync is disabled.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> User must be able to enable or disable sync for individual modules.
-2. Modules include Screenings, Pregnancy, Midlife Health, Menopause and Other Ailments.
-3. Only enabled modules should sync appointments.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t>1.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> User must be able to choose reminder intervals.
-2. Reminder settings must apply to newly synced appointments.
-3. Default reminder must be configurable.</t>
     </r>
   </si>
   <si>
@@ -3053,21 +2784,6 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">enter appointment details on the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Other Ailments screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
       <t xml:space="preserve">tap </t>
     </r>
     <r>
@@ -3124,21 +2840,6 @@
         <scheme val="minor"/>
       </rPr>
       <t>Save Health Check on the Review Your Entries screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">tap </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Add to Calendar after saving a health check with appointment details</t>
     </r>
   </si>
   <si>
@@ -3191,7 +2892,209 @@
 5. Only the autosaved Diabetes Test data associated with the logged-in user's account must be restored when the Diabetes Test screen is reopened.</t>
   </si>
   <si>
-    <t>I can view my Upcoming, Due and Completed appointments in Your Appointments section</t>
+    <r>
+      <t xml:space="preserve">tap </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Your Health Overview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab on the Home Screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">I can view my Upcoming, Due and Completed screenings in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Your Health Overview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. The User must be able to access the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Your Health Overview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> screen by tapping the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Your Health Overview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab on the Home Screen.
+2. The user's </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Upcoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Completed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> screening categories filter (top tabs) must be displayed in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Your Health Overview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> screen.
+3. The total number (count) of screenings in each category must be displayed in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Upccoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Completed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> top tabs, next to the tab title.
+4. Only screenings associated with the logged-in user's account must be displayed.</t>
+    </r>
   </si>
   <si>
     <r>
@@ -3204,6 +3107,89 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
+      <t>Upcoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> screenings in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Your Health Overview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <t>my health Screenings are synced to my preferred calendar application</t>
+  </si>
+  <si>
+    <t>tap View Upcoming Screenings on the Success screen</t>
+  </si>
+  <si>
+    <t>I can manage all my upcoming health Screenings from the Upcoming Screenings screen</t>
+  </si>
+  <si>
+    <t>1. Upcoming Screenings screen must display all synced Screenings.
+2. Screenings must be grouped by date.
+3. User must be able to open the device calendar from this screen.</t>
+  </si>
+  <si>
+    <t>I can control whether my health Screenings are automatically synced to my device calendar</t>
+  </si>
+  <si>
+    <t>only Screenings from my selected health modules appear in my device calendar</t>
+  </si>
+  <si>
+    <t>1. User must be able to enable or disable sync for individual modules.
+2. Modules include Screenings, Pregnancy, Midlife Health, Menopause and Other Ailments.
+3. Only enabled modules should sync Screenings.</t>
+  </si>
+  <si>
+    <t>1. User must be able to choose reminder intervals.
+2. Reminder settings must apply to newly synced Screenings.
+3. Default reminder must be configurable.</t>
+  </si>
+  <si>
+    <t>1. Users must be able to mark prenatal Screenings and tests as completed.
+2. Completed checklist items must be visually distinguished.
+3. Completion status must be saved to the user's pregnancy record.</t>
+  </si>
+  <si>
+    <t>I can view and manage my scheduled pregnancy Screenings</t>
+  </si>
+  <si>
+    <t>I receive timely reminders for upcoming prenatal Screenings and tests</t>
+  </si>
+  <si>
+    <t>I can schedule future health Screenings</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">View my </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
       <t>Due</t>
     </r>
     <r>
@@ -3212,7 +3198,24 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> appointments in Your Appointments section</t>
+      <t xml:space="preserve"> screenings in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Your Health overview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
     </r>
   </si>
   <si>
@@ -3226,6 +3229,167 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
+      <t>Completed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> screenings in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Your Health overview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <t>I can view my previously completed screenings.</t>
+  </si>
+  <si>
+    <t>1. The logged-in user must be able to open the screening Details bottom sheet by tapping any screening card from the screening list.
+2. The screening Details bottom sheet must show the following screening details: screening Name, Date (MM DD, YYYY and ), Time (e.g. 12:00 pm), Healthcare Provider, Location (Facility name and Address).
+5. If any screening details are unavailable inside the screening Details bottom sheet, an appropriate message (e.g.- N/A) must be displayed while the available information is kept intact.
+6. Upcoming cards' screening Details bottom sheet must have the following CTA buttons: Primary type - Reschedule, Secondary type- Cancel
+- Reschedule action: Opens the app's existing screening booking modal pop up
+- Cancel action: Cancels the screening (removes the synced screening from device's calendar and removes it from the Upcoming tab)
+7. Due cards' screening Details bottom sheet must have the following CTA buttons: Primary type - Reschedule, Secondary type- Dismiss
+- Reschedule action: Opens the app's existing screening booking modal pop up
+- Dismiss action: Dismisses the screening (removes it from the Due tab)
+8. Closing the screening Details bottom sheet must send the user back to the previous screen (where they opened the bottom sheet).</t>
+  </si>
+  <si>
+    <t>I am taken to the booking/screening screen</t>
+  </si>
+  <si>
+    <t>1. 'No' on health check confirmation must lead to the Book screening screen
+2. Booking flow must be initiated</t>
+  </si>
+  <si>
+    <t>book a health check screening from within the app</t>
+  </si>
+  <si>
+    <t>1. Book screening screen must be accessible after selecting 'No' on a health check
+2. Integration with HotDocs API via Railway must be in place
+3. Booking confirmation must be displayed on success</t>
+  </si>
+  <si>
+    <t>enter screening Details while creating a custom health check on the Other Ailments screen</t>
+  </si>
+  <si>
+    <t>I can schedule a future health screening before saving my custom health check</t>
+  </si>
+  <si>
+    <t>1. User must be able to enter screening date, time and location.
+2. screening details must be linked to the health check.
+3. screening information must be saved successfully.</t>
+  </si>
+  <si>
+    <t>I can choose to sync my screening on the Add to Calendar screen</t>
+  </si>
+  <si>
+    <t>1. App must display an Add to Calendar prompt after saving.
+2. User must be able to add or dismiss the prompt.
+3. screening details must be retained regardless of the user's choice.</t>
+  </si>
+  <si>
+    <t>review my screening details on the Event Preview screen</t>
+  </si>
+  <si>
+    <t>I can verify the screening information before adding it to my calendar</t>
+  </si>
+  <si>
+    <t>I receive confirmation that my screening has been successfully added to my device calendar on the Success screen</t>
+  </si>
+  <si>
+    <t>1. App must display a success message after syncing.
+2. User must be able to view the calendar event.
+3. screening must exist in the selected calendar.</t>
+  </si>
+  <si>
+    <t>I receive screening reminders at my preferred time</t>
+  </si>
+  <si>
+    <t>mark a prenatal screening or test as completed on the Prenatal Checklist screen</t>
+  </si>
+  <si>
+    <t>1. Tapping Hospital Visits must open the Hospital Visits screen.
+2. Upcoming Screenings must be displayed.
+3. screening details must be accessible.
+4. Users must be able to add future hospital visits.</t>
+  </si>
+  <si>
+    <t>1. Reminder cards must display upcoming prenatal Screenings and tests.
+2. Reminder dates must be accurate.
+3. Push notifications must be scheduled before screening due dates.</t>
+  </si>
+  <si>
+    <t>enter screening details on the Other Ailments screen</t>
+  </si>
+  <si>
+    <t>1. screening Details must include screening date, time and location.
+2. screening information must be saved with the health check.
+3. Calendar Sync must be available for Screenings.</t>
+  </si>
+  <si>
+    <t>tap Add to Calendar after saving a health check with screening details</t>
+  </si>
+  <si>
+    <t>I can sync my screening with my device calendar and receive reminders</t>
+  </si>
+  <si>
+    <t>1. Selecting Add to Calendar must open the calendar sync flow.
+2. screening details must be added to the selected calendar.
+3. A confirmation message must be displayed after successful calendar synchronisation.</t>
+  </si>
+  <si>
+    <t>I can keep track of my screenings, due in 90 days or less.</t>
+  </si>
+  <si>
+    <t>I can keep track of my screenings, due in 365 days or less as well as the overdue ones.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. All screenings </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>due in 90 days or less</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must be displayed under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
       <t>Upcoming</t>
     </r>
     <r>
@@ -3234,49 +3398,127 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> appointments in Your Appointments section</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">View my </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Completed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> appointments in Your Appointments section</t>
-    </r>
-  </si>
-  <si>
-    <t>I can view my previously completed healthcare appointments.</t>
-  </si>
-  <si>
-    <t>I can view the detailed information (Appointment Date and time, medical facility, facility address, Lead physician) for the selected appointment and manage them.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Tap an appointment from the appointment list in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Your Appointments</t>
+      <t xml:space="preserve"> tab.
+2. Each upcoming screening must display its name and scheduled date.
+3. The logged-in user must be able to tap/press any upcoming screening from the list.
+4. Only screenings associated with the logged-in user's account must be displayed under the Upcoming tab.
+5. If no upcoming screenings exist, an appropriate message: "You don't have any upcoming screenings." must be displayed.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. All screenings </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>due in 365 days or less</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>not less than 90 days</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, must be displayed under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab.
+2. All </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>overdue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> screenings (screening date missed), must be displayed under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab distinctively,highlighted in red color.
+3. Each due and overdue screening must display its screening name and scheduled date.
+3. The logged-in user must be able to tap/press any due or overdue screening.
+4. Only screenings associated with the logged-in user's account must be displayed under the Rescheduled tab.
+5. If no due or overdue screenings exist, an appropriate message: "You don't have any due screenings." must be displayed.</t>
+    </r>
+  </si>
+  <si>
+    <t>1. All screenings with a Completed status must be displayed under the Completed tab.
+2. Each completed screening must display its screening name and completed screening date.
+3. The logged-in user must be able to tap/press any Completed screening from the list.
+4. Only Screenings associated with the logged-in user's account must be displayed under the Completed tab.
+5. If no completed screenings exist, an appropriate message: "You don't have any completed screenings." must be displayed.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">Tap a screening from the screening list in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Your Health overview</t>
     </r>
     <r>
       <rPr>
@@ -3285,633 +3527,6 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. The logged-in user must be able to open the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Appointment Details</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> bottom sheet by tapping any appointment card from the appointment list.
-2. The </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Appointment Details</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> bottom sheet must show the following appointment details: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Appointment Name</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Date </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(MM DD, YYYY and ), </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Time </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(e.g. 12:00 pm), </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Healthcare Provider</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Location </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(Facility name and Address).
-5. If any appointment details are unavailable inside the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Appointment Details </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">bottom sheet, an appropriate message (e.g.- N/A) must be displayed while the available information is kept intact.
-6. Upcoming cards' </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Appointment Details</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> bottom sheet must have the following CTA buttons: Primary type - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Reschedule</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, Secondary type- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Cancel
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>-</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Reschedule </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">action: Opens the app's existing appointment booking modal pop up
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Cancel</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> action: Cancels the appointment (removes the synced appointment from device's calendar and removes it from the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Upcoming</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> tab)</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">7. Due cards' </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Appointment Details</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> bottom sheet must have the following CTA buttons: Primary type - </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Reschedule</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, Secondary type- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Dismiss
-</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Reschedule</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> action: Opens the app's existing appointment booking modal pop up
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Dismiss</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> action: Dismisses the appointment (removes it from the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Due</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> tab)
-8. Closing the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Appointment Details</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> bottom sheet must send the user back to the previous screen (where they opened the bottom sheet).</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. The User must be able to access the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Your Appointments</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> screen by tapping the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Your Health Overview</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> section on the Home Screen.
-2. The user's </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Upcoming</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Due</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Completed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> appointment categories filter (top tabs) must be displayed in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Your Appointments</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> screen.
-3. The total number of appointments in each category must be displayed in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Upccoming</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Due</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Completed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> top tabs.
-4. Only appointments associated with the logged-in user's account must be displayed.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. All appointments with an Upcoming status must be displayed under the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Upcoming</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> tab.
-2. Each upcoming appointment must display its appointment name, scheduled date, and scheduled time.
-3. The logged-in user must be able to tap any Upcoming appointment from the list to view its details.
-4. Only appointments associated with the logged-in user's account must be displayed under the Upcoming tab.
-5. If no Upcoming appointments exist, an appropriate message: "You don't have any upcoming appointments" must be displayed.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. All appointments with a Due status must be displayed under the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Due</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> tab.
-2. Each due appointment must display its appointment name, updated date, and updated time.
-3. The logged-in user must be able to tap any due appointment from the list to see details.
-4. Only appointments associated with the logged-in user's account must be displayed under the Rescheduled tab.
-5. If no due appointments exist, an appropriate message: "You don't have any upcoming appointments" must be displayed.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. All appointments with a Completed status must be displayed under the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Completed</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> tab.
-2. Each completed appointment must display its appointment name, completed appointment date, and completed appointment time.
-3. The logged-in user must be able to tap any Completed appointment from the list to view its details.
-4. Only appointments associated with the logged-in user's account must be displayed under the Completed tab.
-5. If no Completed appointments exist, an appropriate message: "You don't have any upcoming appointments" must be displayed.</t>
     </r>
   </si>
 </sst>
@@ -4365,6 +3980,84 @@
     <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4378,84 +4071,6 @@
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4691,34 +4306,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="55" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="55" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="74" t="s">
+      <c r="C1" s="55" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="74" t="s">
+      <c r="D1" s="55" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="78" t="s">
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="60" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="74" t="s">
+      <c r="H1" s="55" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="74" t="s">
+      <c r="I1" s="55" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="55"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
+      <c r="A2" s="56"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
@@ -4728,31 +4343,31 @@
       <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
+      <c r="G2" s="60"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
     </row>
     <row r="3" spans="1:9" s="5" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="79">
+      <c r="A3" s="61">
         <v>1</v>
       </c>
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="61" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="16">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>164</v>
+        <v>152</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>163</v>
+        <v>268</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>299</v>
+        <v>269</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>307</v>
+        <v>270</v>
       </c>
       <c r="H3" s="16" t="s">
         <v>11</v>
@@ -4761,95 +4376,93 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A4" s="79"/>
-      <c r="B4" s="79"/>
+    <row r="4" spans="1:9" s="6" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
+      <c r="A4" s="61"/>
+      <c r="B4" s="61"/>
       <c r="C4" s="16">
         <v>1.2</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>301</v>
+        <v>271</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>159</v>
+        <v>310</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="H4" s="16"/>
       <c r="I4" s="16"/>
     </row>
-    <row r="5" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A5" s="79"/>
-      <c r="B5" s="79"/>
+    <row r="5" spans="1:9" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A5" s="61"/>
+      <c r="B5" s="61"/>
       <c r="C5" s="16">
         <v>1.3</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>300</v>
+        <v>284</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>160</v>
+        <v>311</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="H5" s="16"/>
       <c r="I5" s="16"/>
     </row>
-    <row r="6" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A6" s="79"/>
-      <c r="B6" s="79"/>
+    <row r="6" spans="1:9" s="6" customFormat="1" ht="154.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A6" s="61"/>
+      <c r="B6" s="61"/>
       <c r="C6" s="16">
         <v>1.4</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>302</v>
+        <v>285</v>
       </c>
       <c r="F6" s="16" t="s">
-        <v>303</v>
+        <v>286</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="H6" s="16"/>
       <c r="I6" s="16"/>
     </row>
     <row r="7" spans="1:9" s="6" customFormat="1" ht="282" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="79"/>
-      <c r="B7" s="79"/>
+      <c r="A7" s="61"/>
+      <c r="B7" s="61"/>
       <c r="C7" s="16">
         <v>1.5</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>165</v>
+        <v>153</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>305</v>
-      </c>
-      <c r="F7" s="16" t="s">
-        <v>304</v>
-      </c>
+        <v>315</v>
+      </c>
+      <c r="F7" s="16"/>
       <c r="G7" s="17" t="s">
-        <v>306</v>
+        <v>287</v>
       </c>
       <c r="H7" s="16"/>
       <c r="I7" s="16"/>
     </row>
     <row r="8" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="75">
+      <c r="A8" s="57">
         <v>5</v>
       </c>
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="57" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="18">
@@ -4875,8 +4488,8 @@
       </c>
     </row>
     <row r="9" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="76"/>
-      <c r="B9" s="76"/>
+      <c r="A9" s="58"/>
+      <c r="B9" s="58"/>
       <c r="C9" s="18">
         <v>5.2</v>
       </c>
@@ -4896,8 +4509,8 @@
       <c r="I9" s="18"/>
     </row>
     <row r="10" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="76"/>
-      <c r="B10" s="76"/>
+      <c r="A10" s="58"/>
+      <c r="B10" s="58"/>
       <c r="C10" s="18">
         <v>5.3</v>
       </c>
@@ -4917,52 +4530,52 @@
       <c r="I10" s="18"/>
     </row>
     <row r="11" spans="1:9" s="14" customFormat="1" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="76"/>
-      <c r="B11" s="76"/>
+      <c r="A11" s="58"/>
+      <c r="B11" s="58"/>
       <c r="C11" s="21">
         <v>5.4</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>169</v>
+        <v>157</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>172</v>
+        <v>160</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>171</v>
+        <v>159</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>173</v>
+        <v>161</v>
       </c>
       <c r="H11" s="23"/>
       <c r="I11" s="21"/>
     </row>
     <row r="12" spans="1:9" s="14" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="77"/>
-      <c r="B12" s="77"/>
+      <c r="A12" s="59"/>
+      <c r="B12" s="59"/>
       <c r="C12" s="21">
         <v>5.5</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>166</v>
+        <v>154</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>170</v>
+        <v>158</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>168</v>
+        <v>156</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>167</v>
+        <v>155</v>
       </c>
       <c r="H12" s="23"/>
       <c r="I12" s="21"/>
     </row>
     <row r="13" spans="1:9" s="14" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="68">
+      <c r="A13" s="49">
         <v>6</v>
       </c>
-      <c r="B13" s="68" t="s">
+      <c r="B13" s="49" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="21">
@@ -4988,8 +4601,8 @@
       </c>
     </row>
     <row r="14" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A14" s="69"/>
-      <c r="B14" s="69"/>
+      <c r="A14" s="50"/>
+      <c r="B14" s="50"/>
       <c r="C14" s="24">
         <v>6.2</v>
       </c>
@@ -4997,20 +4610,20 @@
         <v>26</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>175</v>
+        <v>163</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>174</v>
+        <v>162</v>
       </c>
       <c r="G14" s="25" t="s">
-        <v>176</v>
+        <v>164</v>
       </c>
       <c r="H14" s="26"/>
       <c r="I14" s="24"/>
     </row>
     <row r="15" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="69"/>
-      <c r="B15" s="69"/>
+      <c r="A15" s="50"/>
+      <c r="B15" s="50"/>
       <c r="C15" s="24">
         <v>6.3</v>
       </c>
@@ -5030,8 +4643,8 @@
       <c r="I15" s="24"/>
     </row>
     <row r="16" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A16" s="69"/>
-      <c r="B16" s="70"/>
+      <c r="A16" s="50"/>
+      <c r="B16" s="51"/>
       <c r="C16" s="27">
         <v>6.4</v>
       </c>
@@ -5055,10 +4668,10 @@
       </c>
     </row>
     <row r="17" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A17" s="71">
+      <c r="A17" s="52">
         <v>7</v>
       </c>
-      <c r="B17" s="68" t="s">
+      <c r="B17" s="49" t="s">
         <v>38</v>
       </c>
       <c r="C17" s="24">
@@ -5084,8 +4697,8 @@
       </c>
     </row>
     <row r="18" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A18" s="72"/>
-      <c r="B18" s="69"/>
+      <c r="A18" s="53"/>
+      <c r="B18" s="50"/>
       <c r="C18" s="24">
         <v>7.2</v>
       </c>
@@ -5107,8 +4720,8 @@
       </c>
     </row>
     <row r="19" spans="1:9" s="6" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="72"/>
-      <c r="B19" s="69"/>
+      <c r="A19" s="53"/>
+      <c r="B19" s="50"/>
       <c r="C19" s="24">
         <v>7.3</v>
       </c>
@@ -5116,7 +4729,7 @@
         <v>39</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="F19" s="24" t="s">
         <v>46</v>
@@ -5128,8 +4741,8 @@
       <c r="I19" s="24"/>
     </row>
     <row r="20" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="73"/>
-      <c r="B20" s="70"/>
+      <c r="A20" s="54"/>
+      <c r="B20" s="51"/>
       <c r="C20" s="24">
         <v>7.4</v>
       </c>
@@ -5137,7 +4750,7 @@
         <v>39</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="F20" s="24" t="s">
         <v>48</v>
@@ -5149,10 +4762,10 @@
       <c r="I20" s="24"/>
     </row>
     <row r="21" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="51">
+      <c r="A21" s="77">
         <v>8</v>
       </c>
-      <c r="B21" s="51" t="s">
+      <c r="B21" s="77" t="s">
         <v>50</v>
       </c>
       <c r="C21" s="28">
@@ -5176,8 +4789,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="52"/>
-      <c r="B22" s="52"/>
+      <c r="A22" s="78"/>
+      <c r="B22" s="78"/>
       <c r="C22" s="28">
         <v>9.3000000000000007</v>
       </c>
@@ -5188,10 +4801,10 @@
         <v>57</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>58</v>
+        <v>288</v>
       </c>
       <c r="G22" s="29" t="s">
-        <v>59</v>
+        <v>289</v>
       </c>
       <c r="H22" s="28"/>
       <c r="I22" s="28" t="s">
@@ -5199,22 +4812,22 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="53"/>
-      <c r="B23" s="53"/>
+      <c r="A23" s="79"/>
+      <c r="B23" s="79"/>
       <c r="C23" s="28">
         <v>9.4</v>
       </c>
       <c r="D23" s="28" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>61</v>
+        <v>290</v>
       </c>
       <c r="F23" s="28" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="G23" s="29" t="s">
-        <v>63</v>
+        <v>291</v>
       </c>
       <c r="H23" s="28"/>
       <c r="I23" s="28" t="s">
@@ -5222,132 +4835,132 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="49">
+      <c r="A24" s="75">
         <v>12</v>
       </c>
-      <c r="B24" s="49" t="s">
-        <v>64</v>
+      <c r="B24" s="75" t="s">
+        <v>60</v>
       </c>
       <c r="C24" s="31">
         <v>12.1</v>
       </c>
       <c r="D24" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E24" s="31" t="s">
+        <v>62</v>
+      </c>
+      <c r="F24" s="31" t="s">
+        <v>63</v>
+      </c>
+      <c r="G24" s="32" t="s">
+        <v>64</v>
+      </c>
+      <c r="H24" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="E24" s="31" t="s">
+      <c r="I24" s="31" t="s">
         <v>66</v>
       </c>
-      <c r="F24" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="G24" s="32" t="s">
-        <v>68</v>
-      </c>
-      <c r="H24" s="31" t="s">
-        <v>69</v>
-      </c>
-      <c r="I24" s="31" t="s">
-        <v>70</v>
-      </c>
     </row>
     <row r="25" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="49"/>
-      <c r="B25" s="49"/>
+      <c r="A25" s="75"/>
+      <c r="B25" s="75"/>
       <c r="C25" s="31">
         <v>12.2</v>
       </c>
       <c r="D25" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E25" s="31" t="s">
+        <v>67</v>
+      </c>
+      <c r="F25" s="31" t="s">
+        <v>68</v>
+      </c>
+      <c r="G25" s="32" t="s">
+        <v>69</v>
+      </c>
+      <c r="H25" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="E25" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="F25" s="31" t="s">
-        <v>72</v>
-      </c>
-      <c r="G25" s="32" t="s">
-        <v>73</v>
-      </c>
-      <c r="H25" s="31" t="s">
-        <v>69</v>
-      </c>
       <c r="I25" s="31" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="26" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="49"/>
-      <c r="B26" s="49"/>
+      <c r="A26" s="75"/>
+      <c r="B26" s="75"/>
       <c r="C26" s="31">
         <v>12.3</v>
       </c>
       <c r="D26" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E26" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="F26" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="G26" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="H26" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="E26" s="31" t="s">
-        <v>74</v>
-      </c>
-      <c r="F26" s="31" t="s">
-        <v>75</v>
-      </c>
-      <c r="G26" s="32" t="s">
-        <v>76</v>
-      </c>
-      <c r="H26" s="31" t="s">
-        <v>69</v>
-      </c>
       <c r="I26" s="31" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="27" spans="1:9" s="6" customFormat="1" ht="123.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="49"/>
-      <c r="B27" s="49"/>
+      <c r="A27" s="75"/>
+      <c r="B27" s="75"/>
       <c r="C27" s="31">
         <v>12.4</v>
       </c>
       <c r="D27" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E27" s="31" t="s">
+        <v>242</v>
+      </c>
+      <c r="F27" s="31" t="s">
+        <v>243</v>
+      </c>
+      <c r="G27" s="32" t="s">
+        <v>244</v>
+      </c>
+      <c r="H27" s="31" t="s">
         <v>65</v>
       </c>
-      <c r="E27" s="31" t="s">
-        <v>271</v>
-      </c>
-      <c r="F27" s="31" t="s">
-        <v>272</v>
-      </c>
-      <c r="G27" s="32" t="s">
-        <v>273</v>
-      </c>
-      <c r="H27" s="31" t="s">
-        <v>69</v>
-      </c>
       <c r="I27" s="31" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="28" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="49"/>
-      <c r="B28" s="49"/>
+      <c r="A28" s="75"/>
+      <c r="B28" s="75"/>
       <c r="C28" s="31">
         <v>12.5</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="E28" s="31" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="G28" s="32" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="H28" s="31" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
       <c r="I28" s="31" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
     </row>
     <row r="29" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
@@ -5357,10 +4970,10 @@
         <v>12.6</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="F29" s="16"/>
       <c r="G29" s="17"/>
@@ -5368,1107 +4981,1107 @@
       <c r="I29" s="34"/>
     </row>
     <row r="30" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="50">
+      <c r="A30" s="76">
         <v>14</v>
       </c>
-      <c r="B30" s="50" t="s">
-        <v>80</v>
+      <c r="B30" s="76" t="s">
+        <v>76</v>
       </c>
       <c r="C30" s="35">
         <v>14.1</v>
       </c>
       <c r="D30" s="36" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E30" s="36" t="s">
-        <v>241</v>
+        <v>292</v>
       </c>
       <c r="F30" s="36" t="s">
-        <v>207</v>
+        <v>293</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>257</v>
+        <v>294</v>
       </c>
       <c r="H30" s="35" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I30" s="35" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="31" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="50"/>
-      <c r="B31" s="50"/>
+      <c r="A31" s="76"/>
+      <c r="B31" s="76"/>
       <c r="C31" s="35">
         <v>14.2</v>
       </c>
       <c r="D31" s="36" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>242</v>
+        <v>224</v>
       </c>
       <c r="F31" s="36" t="s">
-        <v>243</v>
+        <v>295</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>258</v>
+        <v>296</v>
       </c>
       <c r="H31" s="35" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I31" s="35" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="32" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="50"/>
-      <c r="B32" s="50"/>
+      <c r="A32" s="76"/>
+      <c r="B32" s="76"/>
       <c r="C32" s="35">
         <v>14.3</v>
       </c>
       <c r="D32" s="36" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>244</v>
+        <v>225</v>
       </c>
       <c r="F32" s="36" t="s">
-        <v>245</v>
+        <v>226</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>259</v>
+        <v>234</v>
       </c>
       <c r="H32" s="35" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I32" s="35" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="33" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="50"/>
-      <c r="B33" s="50"/>
+      <c r="A33" s="76"/>
+      <c r="B33" s="76"/>
       <c r="C33" s="35">
         <v>14.4</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>246</v>
+        <v>227</v>
       </c>
       <c r="F33" s="36" t="s">
-        <v>217</v>
+        <v>272</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>260</v>
+        <v>235</v>
       </c>
       <c r="H33" s="35" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I33" s="35" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="34" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="50"/>
-      <c r="B34" s="50"/>
+      <c r="A34" s="76"/>
+      <c r="B34" s="76"/>
       <c r="C34" s="35">
         <v>14.5</v>
       </c>
       <c r="D34" s="36" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E34" s="36" t="s">
-        <v>247</v>
+        <v>297</v>
       </c>
       <c r="F34" s="36" t="s">
-        <v>220</v>
+        <v>298</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>261</v>
+        <v>236</v>
       </c>
       <c r="H34" s="35" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I34" s="35" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="35" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="50"/>
-      <c r="B35" s="50"/>
+      <c r="A35" s="76"/>
+      <c r="B35" s="76"/>
       <c r="C35" s="35">
         <v>14.6</v>
       </c>
       <c r="D35" s="36" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E35" s="36" t="s">
-        <v>248</v>
+        <v>228</v>
       </c>
       <c r="F35" s="36" t="s">
-        <v>249</v>
+        <v>299</v>
       </c>
       <c r="G35" s="37" t="s">
-        <v>262</v>
+        <v>300</v>
       </c>
       <c r="H35" s="35" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I35" s="35" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="36" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="50"/>
-      <c r="B36" s="50"/>
+      <c r="A36" s="76"/>
+      <c r="B36" s="76"/>
       <c r="C36" s="35">
         <v>14.7</v>
       </c>
       <c r="D36" s="36" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E36" s="36" t="s">
-        <v>250</v>
+        <v>273</v>
       </c>
       <c r="F36" s="36" t="s">
-        <v>251</v>
+        <v>274</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>263</v>
+        <v>275</v>
       </c>
       <c r="H36" s="35" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I36" s="35" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="37" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="50"/>
-      <c r="B37" s="50"/>
+      <c r="A37" s="76"/>
+      <c r="B37" s="76"/>
       <c r="C37" s="35">
         <v>14.8</v>
       </c>
       <c r="D37" s="36" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E37" s="36" t="s">
-        <v>252</v>
+        <v>229</v>
       </c>
       <c r="F37" s="36" t="s">
-        <v>253</v>
+        <v>230</v>
       </c>
       <c r="G37" s="37" t="s">
-        <v>264</v>
+        <v>237</v>
       </c>
       <c r="H37" s="35" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="I37" s="35" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A38" s="50"/>
-      <c r="B38" s="50"/>
+      <c r="A38" s="76"/>
+      <c r="B38" s="76"/>
       <c r="C38" s="35">
         <v>14.9</v>
       </c>
       <c r="D38" s="36" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E38" s="36" t="s">
-        <v>254</v>
+        <v>231</v>
       </c>
       <c r="F38" s="36" t="s">
-        <v>232</v>
+        <v>276</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>265</v>
+        <v>238</v>
       </c>
       <c r="H38" s="35" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="I38" s="35" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="39" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="50"/>
-      <c r="B39" s="50"/>
+      <c r="A39" s="76"/>
+      <c r="B39" s="76"/>
       <c r="C39" s="35">
         <v>14.1</v>
       </c>
       <c r="D39" s="36" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E39" s="36" t="s">
-        <v>255</v>
+        <v>232</v>
       </c>
       <c r="F39" s="36" t="s">
-        <v>236</v>
+        <v>277</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>266</v>
+        <v>278</v>
       </c>
       <c r="H39" s="35" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="I39" s="35" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="50"/>
-      <c r="B40" s="50"/>
+      <c r="A40" s="76"/>
+      <c r="B40" s="76"/>
       <c r="C40" s="35">
         <v>14.11</v>
       </c>
       <c r="D40" s="36" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E40" s="36" t="s">
-        <v>256</v>
+        <v>233</v>
       </c>
       <c r="F40" s="36" t="s">
-        <v>239</v>
+        <v>301</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>267</v>
+        <v>279</v>
       </c>
       <c r="H40" s="35" t="s">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="I40" s="35" t="s">
-        <v>83</v>
+        <v>78</v>
       </c>
     </row>
     <row r="41" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A41" s="54">
+      <c r="A41" s="62">
         <v>15</v>
       </c>
-      <c r="B41" s="54" t="s">
-        <v>85</v>
+      <c r="B41" s="62" t="s">
+        <v>80</v>
       </c>
       <c r="C41" s="38">
         <v>15.1</v>
       </c>
       <c r="D41" s="38" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E41" s="38" t="s">
-        <v>87</v>
+        <v>82</v>
       </c>
       <c r="F41" s="38" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G41" s="39" t="s">
-        <v>177</v>
+        <v>165</v>
       </c>
       <c r="H41" s="38" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="I41" s="38" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="42" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="55"/>
-      <c r="B42" s="55"/>
+      <c r="A42" s="56"/>
+      <c r="B42" s="56"/>
       <c r="C42" s="38">
         <v>15.2</v>
       </c>
       <c r="D42" s="38" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E42" s="38" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F42" s="38" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G42" s="39" t="s">
-        <v>178</v>
+        <v>166</v>
       </c>
       <c r="H42" s="38" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="I42" s="38" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="43" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="55"/>
-      <c r="B43" s="55"/>
+      <c r="A43" s="56"/>
+      <c r="B43" s="56"/>
       <c r="C43" s="38">
         <v>15.3</v>
       </c>
       <c r="D43" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="E43" s="38" t="s">
         <v>86</v>
       </c>
-      <c r="E43" s="38" t="s">
-        <v>91</v>
-      </c>
       <c r="F43" s="38" t="s">
-        <v>92</v>
+        <v>87</v>
       </c>
       <c r="G43" s="39" t="s">
-        <v>179</v>
+        <v>167</v>
       </c>
       <c r="H43" s="38" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="I43" s="38" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="44" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A44" s="55"/>
-      <c r="B44" s="55"/>
+      <c r="A44" s="56"/>
+      <c r="B44" s="56"/>
       <c r="C44" s="38">
         <v>15.4</v>
       </c>
       <c r="D44" s="38" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E44" s="38" t="s">
-        <v>93</v>
+        <v>302</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="G44" s="39" t="s">
-        <v>180</v>
+        <v>280</v>
       </c>
       <c r="H44" s="38" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="I44" s="38" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="55"/>
-      <c r="B45" s="55"/>
+      <c r="A45" s="56"/>
+      <c r="B45" s="56"/>
       <c r="C45" s="38">
         <v>15.5</v>
       </c>
       <c r="D45" s="38" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E45" s="38" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
       <c r="F45" s="38" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
       <c r="G45" s="39" t="s">
-        <v>181</v>
+        <v>168</v>
       </c>
       <c r="H45" s="38" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="I45" s="38" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="46" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="55"/>
-      <c r="B46" s="55"/>
+      <c r="A46" s="56"/>
+      <c r="B46" s="56"/>
       <c r="C46" s="38">
         <v>15.6</v>
       </c>
       <c r="D46" s="38" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E46" s="38" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>98</v>
+        <v>281</v>
       </c>
       <c r="G46" s="39" t="s">
-        <v>182</v>
+        <v>303</v>
       </c>
       <c r="H46" s="38" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="I46" s="38" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="47" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A47" s="55"/>
-      <c r="B47" s="55"/>
+      <c r="A47" s="56"/>
+      <c r="B47" s="56"/>
       <c r="C47" s="38">
         <v>15.7</v>
       </c>
       <c r="D47" s="38" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E47" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="F47" s="38" t="s">
+        <v>282</v>
+      </c>
+      <c r="G47" s="39" t="s">
+        <v>304</v>
+      </c>
+      <c r="H47" s="38" t="s">
         <v>99</v>
       </c>
-      <c r="F47" s="38" t="s">
+      <c r="I47" s="38" t="s">
         <v>100</v>
       </c>
-      <c r="G47" s="39" t="s">
-        <v>183</v>
-      </c>
-      <c r="H47" s="38" t="s">
-        <v>107</v>
-      </c>
-      <c r="I47" s="38" t="s">
-        <v>108</v>
-      </c>
     </row>
     <row r="48" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="55"/>
-      <c r="B48" s="55"/>
+      <c r="A48" s="56"/>
+      <c r="B48" s="56"/>
       <c r="C48" s="38">
         <v>15.8</v>
       </c>
       <c r="D48" s="38" t="s">
-        <v>86</v>
+        <v>81</v>
       </c>
       <c r="E48" s="38" t="s">
-        <v>101</v>
+        <v>93</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>102</v>
+        <v>94</v>
       </c>
       <c r="G48" s="39" t="s">
-        <v>184</v>
+        <v>169</v>
       </c>
       <c r="H48" s="38" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="I48" s="38" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A49" s="62">
+      <c r="A49" s="69">
         <v>16</v>
       </c>
-      <c r="B49" s="62" t="s">
-        <v>103</v>
+      <c r="B49" s="69" t="s">
+        <v>95</v>
       </c>
       <c r="C49" s="40">
         <v>16.100000000000001</v>
       </c>
       <c r="D49" s="41" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E49" s="41" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F49" s="41" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G49" s="42" t="s">
-        <v>185</v>
+        <v>170</v>
       </c>
       <c r="H49" s="41" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="I49" s="41" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="50" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A50" s="62"/>
-      <c r="B50" s="62"/>
+      <c r="A50" s="69"/>
+      <c r="B50" s="69"/>
       <c r="C50" s="40">
         <v>16.2</v>
       </c>
       <c r="D50" s="41" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E50" s="41" t="s">
-        <v>109</v>
+        <v>101</v>
       </c>
       <c r="F50" s="41" t="s">
-        <v>110</v>
+        <v>102</v>
       </c>
       <c r="G50" s="42" t="s">
-        <v>186</v>
+        <v>171</v>
       </c>
       <c r="H50" s="41" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="I50" s="41" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="62"/>
-      <c r="B51" s="62"/>
+      <c r="A51" s="69"/>
+      <c r="B51" s="69"/>
       <c r="C51" s="40">
         <v>16.3</v>
       </c>
       <c r="D51" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="E51" s="41" t="s">
+        <v>103</v>
+      </c>
+      <c r="F51" s="41" t="s">
         <v>104</v>
       </c>
-      <c r="E51" s="41" t="s">
-        <v>111</v>
-      </c>
-      <c r="F51" s="41" t="s">
-        <v>112</v>
-      </c>
       <c r="G51" s="42" t="s">
-        <v>187</v>
+        <v>172</v>
       </c>
       <c r="H51" s="41" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="I51" s="41" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A52" s="62"/>
-      <c r="B52" s="62"/>
+      <c r="A52" s="69"/>
+      <c r="B52" s="69"/>
       <c r="C52" s="40">
         <v>16.399999999999999</v>
       </c>
       <c r="D52" s="41" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E52" s="41" t="s">
-        <v>113</v>
+        <v>105</v>
       </c>
       <c r="F52" s="41" t="s">
-        <v>114</v>
+        <v>106</v>
       </c>
       <c r="G52" s="42" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="H52" s="41" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="I52" s="41" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A53" s="62"/>
-      <c r="B53" s="62"/>
+      <c r="A53" s="69"/>
+      <c r="B53" s="69"/>
       <c r="C53" s="40">
         <v>16.5</v>
       </c>
       <c r="D53" s="41" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E53" s="41" t="s">
-        <v>115</v>
+        <v>107</v>
       </c>
       <c r="F53" s="41" t="s">
-        <v>116</v>
+        <v>108</v>
       </c>
       <c r="G53" s="42" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="H53" s="41" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="I53" s="41" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="54" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A54" s="55"/>
-      <c r="B54" s="55"/>
+      <c r="A54" s="56"/>
+      <c r="B54" s="56"/>
       <c r="C54" s="40">
         <v>16.600000000000001</v>
       </c>
       <c r="D54" s="41" t="s">
-        <v>104</v>
+        <v>96</v>
       </c>
       <c r="E54" s="41" t="s">
-        <v>117</v>
+        <v>109</v>
       </c>
       <c r="F54" s="41" t="s">
-        <v>118</v>
+        <v>110</v>
       </c>
       <c r="G54" s="42" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="H54" s="41" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="I54" s="41" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="55" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A55" s="63">
+      <c r="A55" s="70">
         <v>17</v>
       </c>
-      <c r="B55" s="66" t="s">
-        <v>119</v>
+      <c r="B55" s="73" t="s">
+        <v>111</v>
       </c>
       <c r="C55" s="43">
         <v>17.100000000000001</v>
       </c>
       <c r="D55" s="43" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E55" s="43" t="s">
-        <v>121</v>
+        <v>113</v>
       </c>
       <c r="F55" s="43" t="s">
-        <v>122</v>
+        <v>114</v>
       </c>
       <c r="G55" s="44" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="H55" s="43" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="I55" s="43" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="56" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A56" s="64"/>
-      <c r="B56" s="66"/>
+      <c r="A56" s="71"/>
+      <c r="B56" s="73"/>
       <c r="C56" s="43">
         <v>17.2</v>
       </c>
       <c r="D56" s="43" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E56" s="43" t="s">
-        <v>124</v>
+        <v>116</v>
       </c>
       <c r="F56" s="43" t="s">
-        <v>125</v>
+        <v>117</v>
       </c>
       <c r="G56" s="44" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="H56" s="43" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="I56" s="43" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A57" s="64"/>
-      <c r="B57" s="66"/>
+      <c r="A57" s="71"/>
+      <c r="B57" s="73"/>
       <c r="C57" s="43">
         <v>17.3</v>
       </c>
       <c r="D57" s="43" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E57" s="43" t="s">
-        <v>126</v>
+        <v>118</v>
       </c>
       <c r="F57" s="43" t="s">
-        <v>127</v>
+        <v>119</v>
       </c>
       <c r="G57" s="44" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="H57" s="43" t="s">
-        <v>107</v>
+        <v>99</v>
       </c>
       <c r="I57" s="43" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="58" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A58" s="64"/>
-      <c r="B58" s="66"/>
+      <c r="A58" s="71"/>
+      <c r="B58" s="73"/>
       <c r="C58" s="43">
         <v>17.399999999999999</v>
       </c>
       <c r="D58" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="E58" s="43" t="s">
         <v>120</v>
       </c>
-      <c r="E58" s="43" t="s">
-        <v>128</v>
-      </c>
       <c r="F58" s="43" t="s">
-        <v>129</v>
+        <v>121</v>
       </c>
       <c r="G58" s="44" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="H58" s="43" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="I58" s="43" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="59" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A59" s="65"/>
-      <c r="B59" s="66"/>
+      <c r="A59" s="72"/>
+      <c r="B59" s="73"/>
       <c r="C59" s="43">
         <v>17.5</v>
       </c>
       <c r="D59" s="43" t="s">
-        <v>120</v>
+        <v>112</v>
       </c>
       <c r="E59" s="43" t="s">
-        <v>130</v>
+        <v>122</v>
       </c>
       <c r="F59" s="43" t="s">
-        <v>131</v>
+        <v>123</v>
       </c>
       <c r="G59" s="44" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="H59" s="43" t="s">
-        <v>123</v>
+        <v>115</v>
       </c>
       <c r="I59" s="43" t="s">
-        <v>108</v>
+        <v>100</v>
       </c>
     </row>
     <row r="60" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A60" s="67">
+      <c r="A60" s="74">
         <v>18</v>
       </c>
-      <c r="B60" s="67" t="s">
-        <v>132</v>
+      <c r="B60" s="74" t="s">
+        <v>124</v>
       </c>
       <c r="C60" s="18">
         <v>18.100000000000001</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E60" s="18" t="s">
-        <v>279</v>
+        <v>250</v>
       </c>
       <c r="F60" s="18" t="s">
-        <v>134</v>
+        <v>126</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="H60" s="18" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I60" s="18" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="61" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A61" s="55"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="56"/>
+      <c r="B61" s="56"/>
       <c r="C61" s="18">
         <v>18.2</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E61" s="18" t="s">
-        <v>280</v>
+        <v>251</v>
       </c>
       <c r="F61" s="18" t="s">
-        <v>136</v>
+        <v>128</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="H61" s="18" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I61" s="18" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="62" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A62" s="55"/>
-      <c r="B62" s="55"/>
+      <c r="A62" s="56"/>
+      <c r="B62" s="56"/>
       <c r="C62" s="18">
         <v>18.3</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E62" s="18" t="s">
-        <v>281</v>
+        <v>252</v>
       </c>
       <c r="F62" s="18" t="s">
-        <v>137</v>
+        <v>129</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="H62" s="18" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I62" s="18" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="63" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A63" s="55"/>
-      <c r="B63" s="55"/>
+      <c r="A63" s="56"/>
+      <c r="B63" s="56"/>
       <c r="C63" s="18">
         <v>18.399999999999999</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E63" s="18" t="s">
-        <v>282</v>
+        <v>305</v>
       </c>
       <c r="F63" s="18" t="s">
-        <v>81</v>
+        <v>283</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>199</v>
+        <v>306</v>
       </c>
       <c r="H63" s="18" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I63" s="18" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="64" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A64" s="55"/>
-      <c r="B64" s="55"/>
+      <c r="A64" s="56"/>
+      <c r="B64" s="56"/>
       <c r="C64" s="18">
         <v>18.5</v>
       </c>
       <c r="D64" s="18" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E64" s="18" t="s">
-        <v>283</v>
+        <v>253</v>
       </c>
       <c r="F64" s="18" t="s">
-        <v>138</v>
+        <v>130</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>200</v>
+        <v>184</v>
       </c>
       <c r="H64" s="18" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I64" s="18" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="65" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A65" s="55"/>
-      <c r="B65" s="55"/>
+      <c r="A65" s="56"/>
+      <c r="B65" s="56"/>
       <c r="C65" s="18">
         <v>18.600000000000001</v>
       </c>
       <c r="D65" s="18" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E65" s="18" t="s">
-        <v>284</v>
+        <v>254</v>
       </c>
       <c r="F65" s="18" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="G65" s="19" t="s">
-        <v>201</v>
+        <v>185</v>
       </c>
       <c r="H65" s="18" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I65" s="18" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="66" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A66" s="55"/>
-      <c r="B66" s="55"/>
+      <c r="A66" s="56"/>
+      <c r="B66" s="56"/>
       <c r="C66" s="18">
         <v>18.7</v>
       </c>
       <c r="D66" s="18" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E66" s="18" t="s">
-        <v>285</v>
+        <v>255</v>
       </c>
       <c r="F66" s="18" t="s">
-        <v>140</v>
+        <v>132</v>
       </c>
       <c r="G66" s="19" t="s">
-        <v>202</v>
+        <v>186</v>
       </c>
       <c r="H66" s="18" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I66" s="18" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="67" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A67" s="55"/>
-      <c r="B67" s="55"/>
+      <c r="A67" s="56"/>
+      <c r="B67" s="56"/>
       <c r="C67" s="18">
         <v>18.8</v>
       </c>
       <c r="D67" s="18" t="s">
+        <v>125</v>
+      </c>
+      <c r="E67" s="18" t="s">
+        <v>256</v>
+      </c>
+      <c r="F67" s="18" t="s">
         <v>133</v>
       </c>
-      <c r="E67" s="18" t="s">
-        <v>286</v>
-      </c>
-      <c r="F67" s="18" t="s">
-        <v>141</v>
-      </c>
       <c r="G67" s="19" t="s">
-        <v>203</v>
+        <v>187</v>
       </c>
       <c r="H67" s="18" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I67" s="18" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="68" spans="1:12" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="55"/>
-      <c r="B68" s="55"/>
+      <c r="A68" s="56"/>
+      <c r="B68" s="56"/>
       <c r="C68" s="18">
         <v>18.899999999999999</v>
       </c>
       <c r="D68" s="18" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="E68" s="18" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="F68" s="18" t="s">
-        <v>142</v>
+        <v>308</v>
       </c>
       <c r="G68" s="19" t="s">
-        <v>204</v>
+        <v>309</v>
       </c>
       <c r="H68" s="18" t="s">
-        <v>82</v>
+        <v>77</v>
       </c>
       <c r="I68" s="18" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
     </row>
     <row r="69" spans="1:12" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A69" s="56">
+      <c r="A69" s="63">
         <v>19</v>
       </c>
-      <c r="B69" s="59" t="s">
-        <v>143</v>
+      <c r="B69" s="66" t="s">
+        <v>134</v>
       </c>
       <c r="C69" s="45">
         <v>19.100000000000001</v>
       </c>
       <c r="D69" s="46" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="E69" s="46" t="s">
-        <v>275</v>
+        <v>246</v>
       </c>
       <c r="F69" s="46" t="s">
-        <v>274</v>
+        <v>245</v>
       </c>
       <c r="G69" s="47" t="s">
-        <v>276</v>
+        <v>247</v>
       </c>
       <c r="H69" s="45"/>
       <c r="I69" s="48"/>
     </row>
     <row r="70" spans="1:12" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="57"/>
-      <c r="B70" s="60"/>
+      <c r="A70" s="64"/>
+      <c r="B70" s="67"/>
       <c r="C70" s="15">
         <v>19.2</v>
       </c>
       <c r="D70" s="46" t="s">
-        <v>145</v>
+        <v>136</v>
       </c>
       <c r="E70" s="46" t="s">
-        <v>146</v>
+        <v>137</v>
       </c>
       <c r="F70" s="46" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="G70" s="47" t="s">
-        <v>147</v>
+        <v>138</v>
       </c>
       <c r="H70" s="45"/>
       <c r="I70" s="48"/>
     </row>
     <row r="71" spans="1:12" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="58"/>
-      <c r="B71" s="61"/>
+      <c r="A71" s="65"/>
+      <c r="B71" s="68"/>
       <c r="C71" s="34">
         <v>19.3</v>
       </c>
       <c r="D71" s="16" t="s">
-        <v>144</v>
+        <v>135</v>
       </c>
       <c r="E71" s="16" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="F71" s="16" t="s">
-        <v>149</v>
+        <v>140</v>
       </c>
       <c r="G71" s="17"/>
       <c r="H71" s="33"/>
       <c r="I71" s="34"/>
     </row>
     <row r="72" spans="1:12" s="6" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="56">
+      <c r="A72" s="63">
         <v>20</v>
       </c>
-      <c r="B72" s="59" t="s">
-        <v>150</v>
+      <c r="B72" s="66" t="s">
+        <v>141</v>
       </c>
       <c r="C72" s="45">
         <v>20.100000000000001</v>
       </c>
       <c r="D72" s="46" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="E72" s="46" t="s">
-        <v>296</v>
+        <v>265</v>
       </c>
       <c r="F72" s="46" t="s">
-        <v>297</v>
+        <v>266</v>
       </c>
       <c r="G72" s="47" t="s">
-        <v>298</v>
+        <v>267</v>
       </c>
       <c r="H72" s="45"/>
       <c r="I72" s="48"/>
     </row>
     <row r="73" spans="1:12" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A73" s="57"/>
-      <c r="B73" s="60"/>
+      <c r="A73" s="64"/>
+      <c r="B73" s="67"/>
       <c r="C73" s="15">
         <v>20.2</v>
       </c>
       <c r="D73" s="46" t="s">
-        <v>152</v>
+        <v>143</v>
       </c>
       <c r="E73" s="46" t="s">
-        <v>277</v>
+        <v>248</v>
       </c>
       <c r="F73" s="46" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="G73" s="47" t="s">
-        <v>278</v>
+        <v>249</v>
       </c>
       <c r="H73" s="45"/>
       <c r="I73" s="48"/>
@@ -6477,16 +6090,16 @@
       <c r="L73" s="1"/>
     </row>
     <row r="74" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A74" s="58"/>
-      <c r="B74" s="61"/>
+      <c r="A74" s="65"/>
+      <c r="B74" s="68"/>
       <c r="C74" s="33">
         <v>20.3</v>
       </c>
       <c r="D74" s="16" t="s">
-        <v>151</v>
+        <v>142</v>
       </c>
       <c r="E74" s="16" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="F74" s="16"/>
       <c r="G74" s="17"/>
@@ -6497,62 +6110,62 @@
       <c r="L74" s="1"/>
     </row>
     <row r="75" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A75" s="56">
+      <c r="A75" s="63">
         <v>21</v>
       </c>
-      <c r="B75" s="59" t="s">
-        <v>153</v>
+      <c r="B75" s="66" t="s">
+        <v>144</v>
       </c>
       <c r="C75" s="45">
         <v>21.1</v>
       </c>
       <c r="D75" s="46" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="E75" s="46" t="s">
-        <v>288</v>
+        <v>257</v>
       </c>
       <c r="F75" s="46" t="s">
-        <v>289</v>
+        <v>258</v>
       </c>
       <c r="G75" s="47" t="s">
-        <v>290</v>
+        <v>259</v>
       </c>
       <c r="H75" s="45"/>
       <c r="I75" s="48"/>
     </row>
     <row r="76" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="57"/>
-      <c r="B76" s="60"/>
+      <c r="A76" s="64"/>
+      <c r="B76" s="67"/>
       <c r="C76" s="15">
         <v>21.2</v>
       </c>
       <c r="D76" s="46" t="s">
-        <v>155</v>
+        <v>146</v>
       </c>
       <c r="E76" s="46" t="s">
-        <v>269</v>
+        <v>240</v>
       </c>
       <c r="F76" s="46" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="G76" s="47" t="s">
-        <v>156</v>
+        <v>147</v>
       </c>
       <c r="H76" s="45"/>
       <c r="I76" s="48"/>
     </row>
     <row r="77" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A77" s="58"/>
-      <c r="B77" s="61"/>
+      <c r="A77" s="65"/>
+      <c r="B77" s="68"/>
       <c r="C77" s="33">
         <v>21.3</v>
       </c>
       <c r="D77" s="16" t="s">
-        <v>154</v>
+        <v>145</v>
       </c>
       <c r="E77" s="16" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="F77" s="16"/>
       <c r="G77" s="17"/>
@@ -6560,62 +6173,62 @@
       <c r="I77" s="34"/>
     </row>
     <row r="78" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A78" s="56">
+      <c r="A78" s="63">
         <v>22</v>
       </c>
-      <c r="B78" s="59" t="s">
-        <v>157</v>
+      <c r="B78" s="66" t="s">
+        <v>148</v>
       </c>
       <c r="C78" s="45">
         <v>22.1</v>
       </c>
       <c r="D78" s="46" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="E78" s="46" t="s">
-        <v>293</v>
+        <v>262</v>
       </c>
       <c r="F78" s="46" t="s">
-        <v>294</v>
+        <v>263</v>
       </c>
       <c r="G78" s="47" t="s">
-        <v>295</v>
+        <v>264</v>
       </c>
       <c r="H78" s="45"/>
       <c r="I78" s="48"/>
     </row>
     <row r="79" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A79" s="57"/>
-      <c r="B79" s="60"/>
+      <c r="A79" s="64"/>
+      <c r="B79" s="67"/>
       <c r="C79" s="15">
         <v>22.2</v>
       </c>
       <c r="D79" s="46" t="s">
-        <v>268</v>
+        <v>239</v>
       </c>
       <c r="E79" s="45" t="s">
-        <v>291</v>
+        <v>260</v>
       </c>
       <c r="F79" s="46" t="s">
-        <v>270</v>
+        <v>241</v>
       </c>
       <c r="G79" s="47" t="s">
-        <v>292</v>
+        <v>261</v>
       </c>
       <c r="H79" s="45"/>
       <c r="I79" s="48"/>
     </row>
     <row r="80" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A80" s="58"/>
-      <c r="B80" s="61"/>
+      <c r="A80" s="65"/>
+      <c r="B80" s="68"/>
       <c r="C80" s="33">
         <v>22.3</v>
       </c>
       <c r="D80" s="16" t="s">
-        <v>158</v>
+        <v>149</v>
       </c>
       <c r="E80" s="33" t="s">
-        <v>148</v>
+        <v>139</v>
       </c>
       <c r="F80" s="16"/>
       <c r="G80" s="17"/>
@@ -6723,21 +6336,12 @@
   </sheetData>
   <autoFilter ref="I1:I26" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="37">
-    <mergeCell ref="A13:A16"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="A17:A20"/>
-    <mergeCell ref="H1:H2"/>
-    <mergeCell ref="I1:I2"/>
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="B8:B12"/>
-    <mergeCell ref="A1:A2"/>
-    <mergeCell ref="B1:B2"/>
-    <mergeCell ref="C1:C2"/>
-    <mergeCell ref="D1:F1"/>
-    <mergeCell ref="G1:G2"/>
-    <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="A30:A40"/>
+    <mergeCell ref="B30:B40"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="B21:B23"/>
     <mergeCell ref="A41:A48"/>
     <mergeCell ref="B41:B48"/>
     <mergeCell ref="A75:A77"/>
@@ -6754,12 +6358,21 @@
     <mergeCell ref="B69:B71"/>
     <mergeCell ref="A72:A74"/>
     <mergeCell ref="B72:B74"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="A30:A40"/>
-    <mergeCell ref="B30:B40"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="A13:A16"/>
+    <mergeCell ref="B13:B16"/>
+    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="H1:H2"/>
+    <mergeCell ref="I1:I2"/>
+    <mergeCell ref="A8:A12"/>
+    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="A1:A2"/>
+    <mergeCell ref="B1:B2"/>
+    <mergeCell ref="C1:C2"/>
+    <mergeCell ref="D1:F1"/>
+    <mergeCell ref="G1:G2"/>
+    <mergeCell ref="A3:A7"/>
+    <mergeCell ref="B3:B7"/>
+    <mergeCell ref="B17:B20"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6820,7 +6433,7 @@
         <v>8</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>205</v>
+        <v>188</v>
       </c>
       <c r="I3" s="12" t="s">
         <v>4</v>
@@ -6832,22 +6445,22 @@
       <c r="B4" s="9"/>
       <c r="C4" s="9"/>
       <c r="D4" s="13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E4" s="13">
         <v>14.1</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>206</v>
+        <v>189</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>207</v>
+        <v>190</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>208</v>
+        <v>191</v>
       </c>
       <c r="J4" s="9"/>
     </row>
@@ -6856,22 +6469,22 @@
       <c r="B5" s="9"/>
       <c r="C5" s="9"/>
       <c r="D5" s="13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E5" s="13">
         <v>14.2</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>209</v>
+        <v>192</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>210</v>
+        <v>193</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>211</v>
+        <v>194</v>
       </c>
       <c r="J5" s="9"/>
     </row>
@@ -6880,22 +6493,22 @@
       <c r="B6" s="9"/>
       <c r="C6" s="9"/>
       <c r="D6" s="13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E6" s="13">
         <v>14.3</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>212</v>
+        <v>195</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>213</v>
+        <v>196</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>214</v>
+        <v>197</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>215</v>
+        <v>198</v>
       </c>
       <c r="J6" s="9"/>
     </row>
@@ -6904,22 +6517,22 @@
       <c r="B7" s="9"/>
       <c r="C7" s="9"/>
       <c r="D7" s="13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E7" s="13">
         <v>14.4</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>216</v>
+        <v>199</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>217</v>
+        <v>200</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>218</v>
+        <v>201</v>
       </c>
       <c r="J7" s="9"/>
     </row>
@@ -6928,22 +6541,22 @@
       <c r="B8" s="9"/>
       <c r="C8" s="9"/>
       <c r="D8" s="13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E8" s="13">
         <v>14.5</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>219</v>
+        <v>202</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>220</v>
+        <v>203</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>221</v>
+        <v>204</v>
       </c>
       <c r="J8" s="9"/>
     </row>
@@ -6952,22 +6565,22 @@
       <c r="B9" s="9"/>
       <c r="C9" s="9"/>
       <c r="D9" s="13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E9" s="13">
         <v>14.6</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>222</v>
+        <v>205</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>223</v>
+        <v>206</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>224</v>
+        <v>207</v>
       </c>
       <c r="J9" s="9"/>
     </row>
@@ -6976,22 +6589,22 @@
       <c r="B10" s="9"/>
       <c r="C10" s="9"/>
       <c r="D10" s="13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E10" s="13">
         <v>14.7</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>225</v>
+        <v>208</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>226</v>
+        <v>209</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>227</v>
+        <v>210</v>
       </c>
       <c r="J10" s="9"/>
     </row>
@@ -7000,22 +6613,22 @@
       <c r="B11" s="9"/>
       <c r="C11" s="9"/>
       <c r="D11" s="13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E11" s="13">
         <v>14.8</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>228</v>
+        <v>211</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>229</v>
+        <v>212</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>230</v>
+        <v>213</v>
       </c>
       <c r="J11" s="9"/>
     </row>
@@ -7024,22 +6637,22 @@
       <c r="B12" s="9"/>
       <c r="C12" s="9"/>
       <c r="D12" s="13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E12" s="13">
         <v>14.9</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>231</v>
+        <v>214</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>232</v>
+        <v>215</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>233</v>
+        <v>216</v>
       </c>
       <c r="J12" s="9"/>
     </row>
@@ -7048,22 +6661,22 @@
       <c r="B13" s="9"/>
       <c r="C13" s="9"/>
       <c r="D13" s="13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>234</v>
+        <v>217</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>235</v>
+        <v>218</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>236</v>
+        <v>219</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>237</v>
+        <v>220</v>
       </c>
       <c r="J13" s="9"/>
     </row>
@@ -7072,22 +6685,22 @@
       <c r="B14" s="9"/>
       <c r="C14" s="9"/>
       <c r="D14" s="13" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="E14" s="13">
         <v>14.11</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>133</v>
+        <v>125</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>238</v>
+        <v>221</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>239</v>
+        <v>222</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>240</v>
+        <v>223</v>
       </c>
       <c r="J14" s="9"/>
     </row>

--- a/Soubhanik/checkupp_product_backlog_final.xlsx
+++ b/Soubhanik/checkupp_product_backlog_final.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30131"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Soubhanik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D7C2148-AF37-4B48-840E-CB1FDC0E937A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF03BF71-B7C3-42C7-908E-80AD1F2DE1FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -112,7 +112,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G69" authorId="0" shapeId="0" xr:uid="{3283D6CB-61A1-4390-A688-5F4F500D8585}">
+    <comment ref="G64" authorId="0" shapeId="0" xr:uid="{3283D6CB-61A1-4390-A688-5F4F500D8585}">
       <text>
         <r>
           <rPr>
@@ -136,7 +136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G72" authorId="0" shapeId="0" xr:uid="{C1521E49-0187-46FC-9D55-A1D99E904DBB}">
+    <comment ref="G67" authorId="0" shapeId="0" xr:uid="{C1521E49-0187-46FC-9D55-A1D99E904DBB}">
       <text>
         <r>
           <rPr>
@@ -160,7 +160,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G75" authorId="0" shapeId="0" xr:uid="{6311CE01-3810-423E-933D-ACFFBD920BE0}">
+    <comment ref="G70" authorId="0" shapeId="0" xr:uid="{6311CE01-3810-423E-933D-ACFFBD920BE0}">
       <text>
         <r>
           <rPr>
@@ -189,7 +189,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="491" uniqueCount="316">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="301">
   <si>
     <t>Epic #</t>
   </si>
@@ -869,46 +869,10 @@
     <t>I can access personalised lifestyle guidance</t>
   </si>
   <si>
-    <t>Other Ailments</t>
-  </si>
-  <si>
     <t>Logged-in User</t>
   </si>
   <si>
-    <t>I can create a custom health check for conditions not currently supported by CheckUpp</t>
-  </si>
-  <si>
     <t>Discussion #4 – TANVI</t>
-  </si>
-  <si>
-    <t>I can document any medical condition or test</t>
-  </si>
-  <si>
-    <t>my health record is accurately timestamped</t>
-  </si>
-  <si>
-    <t>I can create custom sections relevant to my condition</t>
-  </si>
-  <si>
-    <t>I can record detailed measurements</t>
-  </si>
-  <si>
-    <t>I can verify all information before creating the health check</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">my custom health check is stored in my </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Health Check History</t>
-    </r>
   </si>
   <si>
     <t>Cardiovascular Reading</t>
@@ -1156,41 +1120,6 @@
 3. Users must be able to navigate between wellness categories.</t>
   </si>
   <si>
-    <t>1. Tapping Other Ailments must open the Other Ailments screen.
-2. The screen must display Condition Name and Test Date fields.
-3. The Save Health Check button must be available.</t>
-  </si>
-  <si>
-    <t>1. Users must be able to select a predefined condition.
-2. Users must be able to enter a custom condition name.
-3. The selected or entered condition must be saved.</t>
-  </si>
-  <si>
-    <t>1. The Test Date field must use a calendar date picker.
-2. Only valid dates must be accepted.
-3. The selected date must be saved with the health check.</t>
-  </si>
-  <si>
-    <t>1. Users must be able to create multiple custom fields.
-2. Each custom field must allow a name and description.
-3. Custom fields must remain editable before saving.</t>
-  </si>
-  <si>
-    <t>1. Users must be able to create multiple subfields.
-2. Each subfield must support a name, value, unit and description.
-3. Subfields must remain linked to their parent field.</t>
-  </si>
-  <si>
-    <t>1. The Review Your Entries screen must display all entered information.
-2. Users must be able to edit any section before saving.
-3. Validation must occur before the health check is saved.</t>
-  </si>
-  <si>
-    <t>1. Saving the health check must store all entered information.
-2. A confirmation message must be displayed after saving.
-3. The saved record must appear in Health Check History.</t>
-  </si>
-  <si>
     <t>So that</t>
   </si>
   <si>
@@ -2736,111 +2665,6 @@
 2. An affirming notification (toast) saying 'Data restored', indicating that the autosaved data has been restored must be displayed after the assessment data is successfully loaded and must not appear if no saved data exists.
 3. The restored values for all available fields(fasting glucose, random glucose, Post-meal Glucose, HbA1c, Ketones, Systolic BP, Diastolic BP, Weight, Height) restored along with an affirming notification(toast) or text field (Notes) must be identical to the most recently autosaved data. 
 4. The restored data and affirming notification must be visible without requiring any additional action from the user.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">tap </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Other Ailments from the Available Health Checks screen in the Screenings tab</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">select a predefined condition or enter a custom condition name on the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Other Ailments screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">enter a </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Test Date on the Other Ailments screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">tap </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Add Field on the Other Ailments screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">tap </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Add Subfield under a custom field</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">review my entered information before saving on the </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Review Your Entries screen</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">tap </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Save Health Check on the Review Your Entries screen</t>
-    </r>
   </si>
   <si>
     <t>have the data I enter in the Visual Acuity dropdowns(Right Eye, Left Eye, Both Eyes), Specialised Vision tests fields (Color Vision Test (Normal, Abnormal) and Peripheral Vision Test(Normal, Abnormal), Eye Pressure fields(Right Eye, Left Eye), Vision Correction dropdown(Do you wear glasses or contacts?), Vision Symptoms (Blurred vision, Eye strain or fatigue, Headaches, Dry eyes, poor night vision, Double vision) and Addition Notes text field autosaved in the system if I tap the 'Back' button or close/remove the app from the background</t>
@@ -3177,9 +3001,6 @@
     <t>I receive timely reminders for upcoming prenatal Screenings and tests</t>
   </si>
   <si>
-    <t>I can schedule future health Screenings</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">View my </t>
     </r>
@@ -3259,18 +3080,6 @@
   </si>
   <si>
     <t>I can view my previously completed screenings.</t>
-  </si>
-  <si>
-    <t>1. The logged-in user must be able to open the screening Details bottom sheet by tapping any screening card from the screening list.
-2. The screening Details bottom sheet must show the following screening details: screening Name, Date (MM DD, YYYY and ), Time (e.g. 12:00 pm), Healthcare Provider, Location (Facility name and Address).
-5. If any screening details are unavailable inside the screening Details bottom sheet, an appropriate message (e.g.- N/A) must be displayed while the available information is kept intact.
-6. Upcoming cards' screening Details bottom sheet must have the following CTA buttons: Primary type - Reschedule, Secondary type- Cancel
-- Reschedule action: Opens the app's existing screening booking modal pop up
-- Cancel action: Cancels the screening (removes the synced screening from device's calendar and removes it from the Upcoming tab)
-7. Due cards' screening Details bottom sheet must have the following CTA buttons: Primary type - Reschedule, Secondary type- Dismiss
-- Reschedule action: Opens the app's existing screening booking modal pop up
-- Dismiss action: Dismisses the screening (removes it from the Due tab)
-8. Closing the screening Details bottom sheet must send the user back to the previous screen (where they opened the bottom sheet).</t>
   </si>
   <si>
     <t>I am taken to the booking/screening screen</t>
@@ -3338,25 +3147,6 @@
 3. Push notifications must be scheduled before screening due dates.</t>
   </si>
   <si>
-    <t>enter screening details on the Other Ailments screen</t>
-  </si>
-  <si>
-    <t>1. screening Details must include screening date, time and location.
-2. screening information must be saved with the health check.
-3. Calendar Sync must be available for Screenings.</t>
-  </si>
-  <si>
-    <t>tap Add to Calendar after saving a health check with screening details</t>
-  </si>
-  <si>
-    <t>I can sync my screening with my device calendar and receive reminders</t>
-  </si>
-  <si>
-    <t>1. Selecting Add to Calendar must open the calendar sync flow.
-2. screening details must be added to the selected calendar.
-3. A confirmation message must be displayed after successful calendar synchronisation.</t>
-  </si>
-  <si>
     <t>I can keep track of my screenings, due in 90 days or less.</t>
   </si>
   <si>
@@ -3364,33 +3154,204 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">1. All screenings </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>due in 90 days or less</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must be displayed under the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Upcoming</t>
+      <t xml:space="preserve">Tap a screening from the screening list in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Your Health overview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> screen</t>
+    </r>
+  </si>
+  <si>
+    <t>I can record my screening results if I had that screening or book an appointment if I had not</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Tapping on any screening card must open the app's </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>existing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> modal that contains:
+- Corresponding screening name (e.g. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Cardiovascular Health</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>"Have you had this screening?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">"
+- Two CTA buttons: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Yes </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>No</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+2. Tapping on the "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Yes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">" button must open the app's </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>existing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> data entry form for that corresponding screening.
+3. Tapping on the "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>No</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">" button must open the app's </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>exisiting</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Appointment Booking modal</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. All screenings with a Completed status must be displayed under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Completed</t>
     </r>
     <r>
       <rPr>
@@ -3399,10 +3360,44 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> tab.
-2. Each upcoming screening must display its name and scheduled date.
-3. The logged-in user must be able to tap/press any upcoming screening from the list.
-4. Only screenings associated with the logged-in user's account must be displayed under the Upcoming tab.
-5. If no upcoming screenings exist, an appropriate message: "You don't have any upcoming screenings." must be displayed.</t>
+2. Each completed screening must display its screening name and completed screening date.
+3. The logged-in user must be able to tap/press any Completed screening from the list.
+4. Only Screenings associated with the logged-in user's account must be displayed under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Completed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab.
+5. If no completed screenings exist, an appropriate </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>message: "You don't have any completed screenings.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>" must be displayed.</t>
     </r>
   </si>
   <si>
@@ -3494,39 +3489,916 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve"> tab distinctively,highlighted in red color.
-3. Each due and overdue screening must display its screening name and scheduled date.
+3. Each due and overdue screening must display its screening name and date.
 3. The logged-in user must be able to tap/press any due or overdue screening.
-4. Only screenings associated with the logged-in user's account must be displayed under the Rescheduled tab.
-5. If no due or overdue screenings exist, an appropriate message: "You don't have any due screenings." must be displayed.</t>
-    </r>
-  </si>
-  <si>
-    <t>1. All screenings with a Completed status must be displayed under the Completed tab.
-2. Each completed screening must display its screening name and completed screening date.
-3. The logged-in user must be able to tap/press any Completed screening from the list.
-4. Only Screenings associated with the logged-in user's account must be displayed under the Completed tab.
-5. If no completed screenings exist, an appropriate message: "You don't have any completed screenings." must be displayed.</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">Tap a screening from the screening list in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Your Health overview</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> screen</t>
+4. Only screenings associated with the logged-in user's account must be displayed under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab.
+5. If no due or overdue screenings exist, an appropriate message: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>You don't have any due screenings.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>" must be displayed.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. All screenings </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>due in 90 days or less</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> must be displayed under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Upcoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab.
+2. Each upcoming screening must display its name and date.
+3. The logged-in user must be able to tap/press any upcoming screening from the list.
+4. Only screenings associated with the logged-in user's account must be displayed under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Upcoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab.
+5. If no upcoming screenings exist, an appropriate message: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>You don't have any upcoming screenings.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>" must be displayed.</t>
+    </r>
+  </si>
+  <si>
+    <t>Specific Conditions</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">tap </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Specific Conditions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button from the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Available Health Checks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Screenings</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab</t>
+    </r>
+  </si>
+  <si>
+    <t>I can create a custom health check for conditions specifc to me</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">enter my condition's </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Monitioring Type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Screening, Imaging, Blood Test etc.), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>How Often</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Doctor visit frequency) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Doctor or Care Provider</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (name)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Tapping </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Specific Conditions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> button must open the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Add Specific Conditions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> bottom sheet.
+2. The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Specific Conditions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab/button must display this sub text: "Uncommon, rare and specific conditions to me"
+3. The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Specific Conditions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab/button must display an add icon (+) to indicate that it is a tappable action component.</t>
+    </r>
+  </si>
+  <si>
+    <t>I can save my specific condition in the system</t>
+  </si>
+  <si>
+    <t>I can edit if I made mistake or continue to final submission</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Confirm Adding Condtion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> modal must pop up upon tapping of the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Save</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> button, in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Add Specific Condition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> bottom sheet.
+2. The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Confirm Adding Condtion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> modal must contain the following:
+- Summary of the data entered in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Add Specific Condition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> bottom sheet
+- Primary Button: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Submit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- Secondary Button: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Back to Editing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+3. Tapping the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Submit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> button must close the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Confirm Adding Condtion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> modal, add the condition to system database and to the user's screen.
+4. Tapping the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Back to Editing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> button must close the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Confirm Adding Condtion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> modal and keep user on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Add Specific Condition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> bottom sheet, where they could edit the data.</t>
+    </r>
+  </si>
+  <si>
+    <t>view a summary of the specific condition data I entered and choose between editing or continuing with it</t>
+  </si>
+  <si>
+    <r>
+      <t>View my specific condition listed as an interactive screening in the</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Available Health Checks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> list, inside </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Screenings - Health Checks tab</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. The specifc condition must be visually different than the default screenings in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Avalaibvle Health checks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> list, to indicated it was a custom addition, exclusive to the user who added it
+2. The specific condition card must display the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Frequency</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (How Often?).
+3. The specific condition card must contain a chevronright icon to indicate it is tappable.
+4. Tapping on the specific condition card must open the app's existing modal that contains:
+- Corresponding screening name (e.g. Hashimoto's Thyroiditis)
+- "Have you had this screening?"
+- Two CTA buttons: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Yes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>No</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+5. Tapping on the "Yes" button must open the app's existing data entry form for that corresponding screening.
+6. Tapping on the "No" button must open the app's exisiting Appointment Booking modal
+</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Add Specific Condtion </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">bottom sheet must contain the following:
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Condition or Diagnosis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (free text field)
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Monitoring Type </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(Dropdown: Blood test, Imaging/ Radiology, Doctor Review, Endoscopy and Other...)
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">How Often? </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(multiple choice chips: Monthly, Every 3 Months, Ever 6 Months, Annually and Custom…)
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Doctor or Care Provider </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(free text field)
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Primary button</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Save
+2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. Tapping "Other" option in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Monitoring Type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> field must render a free text field for user to type.
+3. Tapping the "Custom..." option in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>How Often?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> field must render the following:
+- Numeric text input with engraved stepper control (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Chevron up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Chevron down</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+- Dropdown (Days, Weeks, Months, Years)
+4. The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Save</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> button must stay disabled (untappable) until all the mandatory fields have data entry.</t>
     </r>
   </si>
 </sst>
@@ -3980,6 +4852,63 @@
     <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4001,9 +4930,6 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -4017,60 +4943,6 @@
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="11" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -4289,7 +5161,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L92"/>
+  <dimension ref="A1:L87"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.88671875" style="2" bestFit="1" customWidth="1"/>
@@ -4306,34 +5178,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="55" t="s">
+      <c r="A1" s="74" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="55" t="s">
+      <c r="B1" s="74" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="55" t="s">
+      <c r="C1" s="74" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="55" t="s">
+      <c r="D1" s="74" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="56"/>
-      <c r="F1" s="56"/>
-      <c r="G1" s="60" t="s">
+      <c r="E1" s="55"/>
+      <c r="F1" s="55"/>
+      <c r="G1" s="78" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="55" t="s">
+      <c r="H1" s="74" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="55" t="s">
+      <c r="I1" s="74" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="56"/>
-      <c r="B2" s="56"/>
-      <c r="C2" s="56"/>
+      <c r="A2" s="55"/>
+      <c r="B2" s="55"/>
+      <c r="C2" s="55"/>
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
@@ -4343,31 +5215,31 @@
       <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="60"/>
-      <c r="H2" s="56"/>
-      <c r="I2" s="56"/>
+      <c r="G2" s="78"/>
+      <c r="H2" s="55"/>
+      <c r="I2" s="55"/>
     </row>
     <row r="3" spans="1:9" s="5" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="61">
+      <c r="A3" s="79">
         <v>1</v>
       </c>
-      <c r="B3" s="61" t="s">
+      <c r="B3" s="79" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="16">
         <v>1.1000000000000001</v>
       </c>
       <c r="D3" s="16" t="s">
-        <v>152</v>
+        <v>144</v>
       </c>
       <c r="E3" s="16" t="s">
-        <v>268</v>
+        <v>246</v>
       </c>
       <c r="F3" s="16" t="s">
-        <v>269</v>
+        <v>247</v>
       </c>
       <c r="G3" s="17" t="s">
-        <v>270</v>
+        <v>248</v>
       </c>
       <c r="H3" s="16" t="s">
         <v>11</v>
@@ -4377,92 +5249,94 @@
       </c>
     </row>
     <row r="4" spans="1:9" s="6" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="61"/>
-      <c r="B4" s="61"/>
+      <c r="A4" s="79"/>
+      <c r="B4" s="79"/>
       <c r="C4" s="16">
         <v>1.2</v>
       </c>
       <c r="D4" s="16" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E4" s="16" t="s">
-        <v>271</v>
+        <v>249</v>
       </c>
       <c r="F4" s="16" t="s">
-        <v>310</v>
+        <v>281</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>312</v>
+        <v>288</v>
       </c>
       <c r="H4" s="16"/>
       <c r="I4" s="16"/>
     </row>
-    <row r="5" spans="1:9" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A5" s="61"/>
-      <c r="B5" s="61"/>
+    <row r="5" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
+      <c r="A5" s="79"/>
+      <c r="B5" s="79"/>
       <c r="C5" s="16">
         <v>1.3</v>
       </c>
       <c r="D5" s="16" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E5" s="16" t="s">
-        <v>284</v>
+        <v>261</v>
       </c>
       <c r="F5" s="16" t="s">
-        <v>311</v>
+        <v>282</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>313</v>
+        <v>287</v>
       </c>
       <c r="H5" s="16"/>
       <c r="I5" s="16"/>
     </row>
     <row r="6" spans="1:9" s="6" customFormat="1" ht="154.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="61"/>
-      <c r="B6" s="61"/>
+      <c r="A6" s="79"/>
+      <c r="B6" s="79"/>
       <c r="C6" s="16">
         <v>1.4</v>
       </c>
       <c r="D6" s="16" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E6" s="16" t="s">
-        <v>285</v>
+        <v>262</v>
       </c>
       <c r="F6" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="G6" s="17" t="s">
         <v>286</v>
-      </c>
-      <c r="G6" s="17" t="s">
-        <v>314</v>
       </c>
       <c r="H6" s="16"/>
       <c r="I6" s="16"/>
     </row>
-    <row r="7" spans="1:9" s="6" customFormat="1" ht="282" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A7" s="61"/>
-      <c r="B7" s="61"/>
+    <row r="7" spans="1:9" s="6" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
+      <c r="A7" s="79"/>
+      <c r="B7" s="79"/>
       <c r="C7" s="16">
         <v>1.5</v>
       </c>
       <c r="D7" s="16" t="s">
-        <v>153</v>
+        <v>145</v>
       </c>
       <c r="E7" s="16" t="s">
-        <v>315</v>
-      </c>
-      <c r="F7" s="16"/>
+        <v>283</v>
+      </c>
+      <c r="F7" s="16" t="s">
+        <v>284</v>
+      </c>
       <c r="G7" s="17" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="H7" s="16"/>
       <c r="I7" s="16"/>
     </row>
     <row r="8" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="57">
+      <c r="A8" s="75">
         <v>5</v>
       </c>
-      <c r="B8" s="57" t="s">
+      <c r="B8" s="75" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="18">
@@ -4488,8 +5362,8 @@
       </c>
     </row>
     <row r="9" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="58"/>
-      <c r="B9" s="58"/>
+      <c r="A9" s="76"/>
+      <c r="B9" s="76"/>
       <c r="C9" s="18">
         <v>5.2</v>
       </c>
@@ -4509,8 +5383,8 @@
       <c r="I9" s="18"/>
     </row>
     <row r="10" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="58"/>
-      <c r="B10" s="58"/>
+      <c r="A10" s="76"/>
+      <c r="B10" s="76"/>
       <c r="C10" s="18">
         <v>5.3</v>
       </c>
@@ -4530,52 +5404,52 @@
       <c r="I10" s="18"/>
     </row>
     <row r="11" spans="1:9" s="14" customFormat="1" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="58"/>
-      <c r="B11" s="58"/>
+      <c r="A11" s="76"/>
+      <c r="B11" s="76"/>
       <c r="C11" s="21">
         <v>5.4</v>
       </c>
       <c r="D11" s="21" t="s">
-        <v>157</v>
+        <v>149</v>
       </c>
       <c r="E11" s="21" t="s">
-        <v>160</v>
+        <v>152</v>
       </c>
       <c r="F11" s="21" t="s">
-        <v>159</v>
+        <v>151</v>
       </c>
       <c r="G11" s="22" t="s">
-        <v>161</v>
+        <v>153</v>
       </c>
       <c r="H11" s="23"/>
       <c r="I11" s="21"/>
     </row>
     <row r="12" spans="1:9" s="14" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="59"/>
-      <c r="B12" s="59"/>
+      <c r="A12" s="77"/>
+      <c r="B12" s="77"/>
       <c r="C12" s="21">
         <v>5.5</v>
       </c>
       <c r="D12" s="21" t="s">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="E12" s="21" t="s">
-        <v>158</v>
+        <v>150</v>
       </c>
       <c r="F12" s="21" t="s">
-        <v>156</v>
+        <v>148</v>
       </c>
       <c r="G12" s="22" t="s">
-        <v>155</v>
+        <v>147</v>
       </c>
       <c r="H12" s="23"/>
       <c r="I12" s="21"/>
     </row>
     <row r="13" spans="1:9" s="14" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="49">
+      <c r="A13" s="68">
         <v>6</v>
       </c>
-      <c r="B13" s="49" t="s">
+      <c r="B13" s="68" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="21">
@@ -4601,8 +5475,8 @@
       </c>
     </row>
     <row r="14" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A14" s="50"/>
-      <c r="B14" s="50"/>
+      <c r="A14" s="69"/>
+      <c r="B14" s="69"/>
       <c r="C14" s="24">
         <v>6.2</v>
       </c>
@@ -4610,20 +5484,20 @@
         <v>26</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>163</v>
+        <v>155</v>
       </c>
       <c r="F14" s="24" t="s">
-        <v>162</v>
+        <v>154</v>
       </c>
       <c r="G14" s="25" t="s">
-        <v>164</v>
+        <v>156</v>
       </c>
       <c r="H14" s="26"/>
       <c r="I14" s="24"/>
     </row>
     <row r="15" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="50"/>
-      <c r="B15" s="50"/>
+      <c r="A15" s="69"/>
+      <c r="B15" s="69"/>
       <c r="C15" s="24">
         <v>6.3</v>
       </c>
@@ -4643,8 +5517,8 @@
       <c r="I15" s="24"/>
     </row>
     <row r="16" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A16" s="50"/>
-      <c r="B16" s="51"/>
+      <c r="A16" s="69"/>
+      <c r="B16" s="70"/>
       <c r="C16" s="27">
         <v>6.4</v>
       </c>
@@ -4668,10 +5542,10 @@
       </c>
     </row>
     <row r="17" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A17" s="52">
+      <c r="A17" s="71">
         <v>7</v>
       </c>
-      <c r="B17" s="49" t="s">
+      <c r="B17" s="68" t="s">
         <v>38</v>
       </c>
       <c r="C17" s="24">
@@ -4697,8 +5571,8 @@
       </c>
     </row>
     <row r="18" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A18" s="53"/>
-      <c r="B18" s="50"/>
+      <c r="A18" s="72"/>
+      <c r="B18" s="69"/>
       <c r="C18" s="24">
         <v>7.2</v>
       </c>
@@ -4720,8 +5594,8 @@
       </c>
     </row>
     <row r="19" spans="1:9" s="6" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="53"/>
-      <c r="B19" s="50"/>
+      <c r="A19" s="72"/>
+      <c r="B19" s="69"/>
       <c r="C19" s="24">
         <v>7.3</v>
       </c>
@@ -4729,7 +5603,7 @@
         <v>39</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>150</v>
+        <v>142</v>
       </c>
       <c r="F19" s="24" t="s">
         <v>46</v>
@@ -4741,8 +5615,8 @@
       <c r="I19" s="24"/>
     </row>
     <row r="20" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="54"/>
-      <c r="B20" s="51"/>
+      <c r="A20" s="73"/>
+      <c r="B20" s="70"/>
       <c r="C20" s="24">
         <v>7.4</v>
       </c>
@@ -4750,7 +5624,7 @@
         <v>39</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>151</v>
+        <v>143</v>
       </c>
       <c r="F20" s="24" t="s">
         <v>48</v>
@@ -4762,10 +5636,10 @@
       <c r="I20" s="24"/>
     </row>
     <row r="21" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="77">
+      <c r="A21" s="51">
         <v>8</v>
       </c>
-      <c r="B21" s="77" t="s">
+      <c r="B21" s="51" t="s">
         <v>50</v>
       </c>
       <c r="C21" s="28">
@@ -4789,8 +5663,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="78"/>
-      <c r="B22" s="78"/>
+      <c r="A22" s="52"/>
+      <c r="B22" s="52"/>
       <c r="C22" s="28">
         <v>9.3000000000000007</v>
       </c>
@@ -4801,10 +5675,10 @@
         <v>57</v>
       </c>
       <c r="F22" s="28" t="s">
-        <v>288</v>
+        <v>264</v>
       </c>
       <c r="G22" s="29" t="s">
-        <v>289</v>
+        <v>265</v>
       </c>
       <c r="H22" s="28"/>
       <c r="I22" s="28" t="s">
@@ -4812,8 +5686,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="79"/>
-      <c r="B23" s="79"/>
+      <c r="A23" s="53"/>
+      <c r="B23" s="53"/>
       <c r="C23" s="28">
         <v>9.4</v>
       </c>
@@ -4821,13 +5695,13 @@
         <v>58</v>
       </c>
       <c r="E23" s="28" t="s">
-        <v>290</v>
+        <v>266</v>
       </c>
       <c r="F23" s="28" t="s">
         <v>59</v>
       </c>
       <c r="G23" s="29" t="s">
-        <v>291</v>
+        <v>267</v>
       </c>
       <c r="H23" s="28"/>
       <c r="I23" s="28" t="s">
@@ -4835,10 +5709,10 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="75">
+      <c r="A24" s="49">
         <v>12</v>
       </c>
-      <c r="B24" s="75" t="s">
+      <c r="B24" s="49" t="s">
         <v>60</v>
       </c>
       <c r="C24" s="31">
@@ -4864,8 +5738,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="75"/>
-      <c r="B25" s="75"/>
+      <c r="A25" s="49"/>
+      <c r="B25" s="49"/>
       <c r="C25" s="31">
         <v>12.2</v>
       </c>
@@ -4889,8 +5763,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="75"/>
-      <c r="B26" s="75"/>
+      <c r="A26" s="49"/>
+      <c r="B26" s="49"/>
       <c r="C26" s="31">
         <v>12.3</v>
       </c>
@@ -4914,8 +5788,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" s="6" customFormat="1" ht="123.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="75"/>
-      <c r="B27" s="75"/>
+      <c r="A27" s="49"/>
+      <c r="B27" s="49"/>
       <c r="C27" s="31">
         <v>12.4</v>
       </c>
@@ -4923,13 +5797,13 @@
         <v>61</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>242</v>
+        <v>227</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>243</v>
+        <v>228</v>
       </c>
       <c r="G27" s="32" t="s">
-        <v>244</v>
+        <v>229</v>
       </c>
       <c r="H27" s="31" t="s">
         <v>65</v>
@@ -4939,8 +5813,8 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="75"/>
-      <c r="B28" s="75"/>
+      <c r="A28" s="49"/>
+      <c r="B28" s="49"/>
       <c r="C28" s="31">
         <v>12.5</v>
       </c>
@@ -4951,7 +5825,7 @@
         <v>74</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>241</v>
+        <v>226</v>
       </c>
       <c r="G28" s="32" t="s">
         <v>75</v>
@@ -4970,10 +5844,10 @@
         <v>12.6</v>
       </c>
       <c r="D29" s="16" t="s">
-        <v>135</v>
+        <v>127</v>
       </c>
       <c r="E29" s="16" t="s">
-        <v>139</v>
+        <v>131</v>
       </c>
       <c r="F29" s="16"/>
       <c r="G29" s="17"/>
@@ -4981,26 +5855,26 @@
       <c r="I29" s="34"/>
     </row>
     <row r="30" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="76">
+      <c r="A30" s="50">
         <v>14</v>
       </c>
-      <c r="B30" s="76" t="s">
+      <c r="B30" s="50" t="s">
         <v>76</v>
       </c>
       <c r="C30" s="35">
         <v>14.1</v>
       </c>
       <c r="D30" s="36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E30" s="36" t="s">
-        <v>292</v>
+        <v>268</v>
       </c>
       <c r="F30" s="36" t="s">
-        <v>293</v>
+        <v>269</v>
       </c>
       <c r="G30" s="37" t="s">
-        <v>294</v>
+        <v>270</v>
       </c>
       <c r="H30" s="35" t="s">
         <v>77</v>
@@ -5010,22 +5884,22 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="76"/>
-      <c r="B31" s="76"/>
+      <c r="A31" s="50"/>
+      <c r="B31" s="50"/>
       <c r="C31" s="35">
         <v>14.2</v>
       </c>
       <c r="D31" s="36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E31" s="36" t="s">
-        <v>224</v>
+        <v>209</v>
       </c>
       <c r="F31" s="36" t="s">
-        <v>295</v>
+        <v>271</v>
       </c>
       <c r="G31" s="37" t="s">
-        <v>296</v>
+        <v>272</v>
       </c>
       <c r="H31" s="35" t="s">
         <v>77</v>
@@ -5035,22 +5909,22 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="76"/>
-      <c r="B32" s="76"/>
+      <c r="A32" s="50"/>
+      <c r="B32" s="50"/>
       <c r="C32" s="35">
         <v>14.3</v>
       </c>
       <c r="D32" s="36" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="E32" s="36" t="s">
-        <v>225</v>
+        <v>210</v>
       </c>
       <c r="F32" s="36" t="s">
-        <v>226</v>
+        <v>211</v>
       </c>
       <c r="G32" s="37" t="s">
-        <v>234</v>
+        <v>219</v>
       </c>
       <c r="H32" s="35" t="s">
         <v>77</v>
@@ -5060,22 +5934,22 @@
       </c>
     </row>
     <row r="33" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="76"/>
-      <c r="B33" s="76"/>
+      <c r="A33" s="50"/>
+      <c r="B33" s="50"/>
       <c r="C33" s="35">
         <v>14.4</v>
       </c>
       <c r="D33" s="36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>227</v>
+        <v>212</v>
       </c>
       <c r="F33" s="36" t="s">
-        <v>272</v>
+        <v>250</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>235</v>
+        <v>220</v>
       </c>
       <c r="H33" s="35" t="s">
         <v>77</v>
@@ -5085,22 +5959,22 @@
       </c>
     </row>
     <row r="34" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="76"/>
-      <c r="B34" s="76"/>
+      <c r="A34" s="50"/>
+      <c r="B34" s="50"/>
       <c r="C34" s="35">
         <v>14.5</v>
       </c>
       <c r="D34" s="36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E34" s="36" t="s">
-        <v>297</v>
+        <v>273</v>
       </c>
       <c r="F34" s="36" t="s">
-        <v>298</v>
+        <v>274</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>236</v>
+        <v>221</v>
       </c>
       <c r="H34" s="35" t="s">
         <v>77</v>
@@ -5110,22 +5984,22 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="76"/>
-      <c r="B35" s="76"/>
+      <c r="A35" s="50"/>
+      <c r="B35" s="50"/>
       <c r="C35" s="35">
         <v>14.6</v>
       </c>
       <c r="D35" s="36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E35" s="36" t="s">
-        <v>228</v>
+        <v>213</v>
       </c>
       <c r="F35" s="36" t="s">
-        <v>299</v>
+        <v>275</v>
       </c>
       <c r="G35" s="37" t="s">
-        <v>300</v>
+        <v>276</v>
       </c>
       <c r="H35" s="35" t="s">
         <v>77</v>
@@ -5135,22 +6009,22 @@
       </c>
     </row>
     <row r="36" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="76"/>
-      <c r="B36" s="76"/>
+      <c r="A36" s="50"/>
+      <c r="B36" s="50"/>
       <c r="C36" s="35">
         <v>14.7</v>
       </c>
       <c r="D36" s="36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E36" s="36" t="s">
-        <v>273</v>
+        <v>251</v>
       </c>
       <c r="F36" s="36" t="s">
-        <v>274</v>
+        <v>252</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>275</v>
+        <v>253</v>
       </c>
       <c r="H36" s="35" t="s">
         <v>77</v>
@@ -5160,22 +6034,22 @@
       </c>
     </row>
     <row r="37" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="76"/>
-      <c r="B37" s="76"/>
+      <c r="A37" s="50"/>
+      <c r="B37" s="50"/>
       <c r="C37" s="35">
         <v>14.8</v>
       </c>
       <c r="D37" s="36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E37" s="36" t="s">
-        <v>229</v>
+        <v>214</v>
       </c>
       <c r="F37" s="36" t="s">
-        <v>230</v>
+        <v>215</v>
       </c>
       <c r="G37" s="37" t="s">
-        <v>237</v>
+        <v>222</v>
       </c>
       <c r="H37" s="35" t="s">
         <v>79</v>
@@ -5185,22 +6059,22 @@
       </c>
     </row>
     <row r="38" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A38" s="76"/>
-      <c r="B38" s="76"/>
+      <c r="A38" s="50"/>
+      <c r="B38" s="50"/>
       <c r="C38" s="35">
         <v>14.9</v>
       </c>
       <c r="D38" s="36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E38" s="36" t="s">
-        <v>231</v>
+        <v>216</v>
       </c>
       <c r="F38" s="36" t="s">
-        <v>276</v>
+        <v>254</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>238</v>
+        <v>223</v>
       </c>
       <c r="H38" s="35" t="s">
         <v>79</v>
@@ -5210,22 +6084,22 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="76"/>
-      <c r="B39" s="76"/>
+      <c r="A39" s="50"/>
+      <c r="B39" s="50"/>
       <c r="C39" s="35">
         <v>14.1</v>
       </c>
       <c r="D39" s="36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E39" s="36" t="s">
-        <v>232</v>
+        <v>217</v>
       </c>
       <c r="F39" s="36" t="s">
-        <v>277</v>
+        <v>255</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>278</v>
+        <v>256</v>
       </c>
       <c r="H39" s="35" t="s">
         <v>79</v>
@@ -5235,22 +6109,22 @@
       </c>
     </row>
     <row r="40" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="76"/>
-      <c r="B40" s="76"/>
+      <c r="A40" s="50"/>
+      <c r="B40" s="50"/>
       <c r="C40" s="35">
         <v>14.11</v>
       </c>
       <c r="D40" s="36" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E40" s="36" t="s">
-        <v>233</v>
+        <v>218</v>
       </c>
       <c r="F40" s="36" t="s">
-        <v>301</v>
+        <v>277</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>279</v>
+        <v>257</v>
       </c>
       <c r="H40" s="35" t="s">
         <v>79</v>
@@ -5260,10 +6134,10 @@
       </c>
     </row>
     <row r="41" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A41" s="62">
+      <c r="A41" s="54">
         <v>15</v>
       </c>
-      <c r="B41" s="62" t="s">
+      <c r="B41" s="54" t="s">
         <v>80</v>
       </c>
       <c r="C41" s="38">
@@ -5279,7 +6153,7 @@
         <v>83</v>
       </c>
       <c r="G41" s="39" t="s">
-        <v>165</v>
+        <v>157</v>
       </c>
       <c r="H41" s="38" t="s">
         <v>115</v>
@@ -5289,8 +6163,8 @@
       </c>
     </row>
     <row r="42" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="56"/>
-      <c r="B42" s="56"/>
+      <c r="A42" s="55"/>
+      <c r="B42" s="55"/>
       <c r="C42" s="38">
         <v>15.2</v>
       </c>
@@ -5304,7 +6178,7 @@
         <v>85</v>
       </c>
       <c r="G42" s="39" t="s">
-        <v>166</v>
+        <v>158</v>
       </c>
       <c r="H42" s="38" t="s">
         <v>99</v>
@@ -5314,8 +6188,8 @@
       </c>
     </row>
     <row r="43" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="56"/>
-      <c r="B43" s="56"/>
+      <c r="A43" s="55"/>
+      <c r="B43" s="55"/>
       <c r="C43" s="38">
         <v>15.3</v>
       </c>
@@ -5329,7 +6203,7 @@
         <v>87</v>
       </c>
       <c r="G43" s="39" t="s">
-        <v>167</v>
+        <v>159</v>
       </c>
       <c r="H43" s="38" t="s">
         <v>99</v>
@@ -5339,8 +6213,8 @@
       </c>
     </row>
     <row r="44" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A44" s="56"/>
-      <c r="B44" s="56"/>
+      <c r="A44" s="55"/>
+      <c r="B44" s="55"/>
       <c r="C44" s="38">
         <v>15.4</v>
       </c>
@@ -5348,13 +6222,13 @@
         <v>81</v>
       </c>
       <c r="E44" s="38" t="s">
-        <v>302</v>
+        <v>278</v>
       </c>
       <c r="F44" s="38" t="s">
         <v>88</v>
       </c>
       <c r="G44" s="39" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="H44" s="38" t="s">
         <v>99</v>
@@ -5364,8 +6238,8 @@
       </c>
     </row>
     <row r="45" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="56"/>
-      <c r="B45" s="56"/>
+      <c r="A45" s="55"/>
+      <c r="B45" s="55"/>
       <c r="C45" s="38">
         <v>15.5</v>
       </c>
@@ -5379,7 +6253,7 @@
         <v>90</v>
       </c>
       <c r="G45" s="39" t="s">
-        <v>168</v>
+        <v>160</v>
       </c>
       <c r="H45" s="38" t="s">
         <v>99</v>
@@ -5389,8 +6263,8 @@
       </c>
     </row>
     <row r="46" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="56"/>
-      <c r="B46" s="56"/>
+      <c r="A46" s="55"/>
+      <c r="B46" s="55"/>
       <c r="C46" s="38">
         <v>15.6</v>
       </c>
@@ -5401,10 +6275,10 @@
         <v>91</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>281</v>
+        <v>259</v>
       </c>
       <c r="G46" s="39" t="s">
-        <v>303</v>
+        <v>279</v>
       </c>
       <c r="H46" s="38" t="s">
         <v>99</v>
@@ -5414,8 +6288,8 @@
       </c>
     </row>
     <row r="47" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A47" s="56"/>
-      <c r="B47" s="56"/>
+      <c r="A47" s="55"/>
+      <c r="B47" s="55"/>
       <c r="C47" s="38">
         <v>15.7</v>
       </c>
@@ -5426,10 +6300,10 @@
         <v>92</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>282</v>
+        <v>260</v>
       </c>
       <c r="G47" s="39" t="s">
-        <v>304</v>
+        <v>280</v>
       </c>
       <c r="H47" s="38" t="s">
         <v>99</v>
@@ -5439,8 +6313,8 @@
       </c>
     </row>
     <row r="48" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="56"/>
-      <c r="B48" s="56"/>
+      <c r="A48" s="55"/>
+      <c r="B48" s="55"/>
       <c r="C48" s="38">
         <v>15.8</v>
       </c>
@@ -5454,7 +6328,7 @@
         <v>94</v>
       </c>
       <c r="G48" s="39" t="s">
-        <v>169</v>
+        <v>161</v>
       </c>
       <c r="H48" s="38" t="s">
         <v>99</v>
@@ -5464,10 +6338,10 @@
       </c>
     </row>
     <row r="49" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A49" s="69">
+      <c r="A49" s="62">
         <v>16</v>
       </c>
-      <c r="B49" s="69" t="s">
+      <c r="B49" s="62" t="s">
         <v>95</v>
       </c>
       <c r="C49" s="40">
@@ -5483,7 +6357,7 @@
         <v>98</v>
       </c>
       <c r="G49" s="42" t="s">
-        <v>170</v>
+        <v>162</v>
       </c>
       <c r="H49" s="41" t="s">
         <v>99</v>
@@ -5493,8 +6367,8 @@
       </c>
     </row>
     <row r="50" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A50" s="69"/>
-      <c r="B50" s="69"/>
+      <c r="A50" s="62"/>
+      <c r="B50" s="62"/>
       <c r="C50" s="40">
         <v>16.2</v>
       </c>
@@ -5508,7 +6382,7 @@
         <v>102</v>
       </c>
       <c r="G50" s="42" t="s">
-        <v>171</v>
+        <v>163</v>
       </c>
       <c r="H50" s="41" t="s">
         <v>99</v>
@@ -5518,8 +6392,8 @@
       </c>
     </row>
     <row r="51" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="69"/>
-      <c r="B51" s="69"/>
+      <c r="A51" s="62"/>
+      <c r="B51" s="62"/>
       <c r="C51" s="40">
         <v>16.3</v>
       </c>
@@ -5533,7 +6407,7 @@
         <v>104</v>
       </c>
       <c r="G51" s="42" t="s">
-        <v>172</v>
+        <v>164</v>
       </c>
       <c r="H51" s="41" t="s">
         <v>99</v>
@@ -5543,8 +6417,8 @@
       </c>
     </row>
     <row r="52" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A52" s="69"/>
-      <c r="B52" s="69"/>
+      <c r="A52" s="62"/>
+      <c r="B52" s="62"/>
       <c r="C52" s="40">
         <v>16.399999999999999</v>
       </c>
@@ -5558,7 +6432,7 @@
         <v>106</v>
       </c>
       <c r="G52" s="42" t="s">
-        <v>173</v>
+        <v>165</v>
       </c>
       <c r="H52" s="41" t="s">
         <v>99</v>
@@ -5568,8 +6442,8 @@
       </c>
     </row>
     <row r="53" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A53" s="69"/>
-      <c r="B53" s="69"/>
+      <c r="A53" s="62"/>
+      <c r="B53" s="62"/>
       <c r="C53" s="40">
         <v>16.5</v>
       </c>
@@ -5583,7 +6457,7 @@
         <v>108</v>
       </c>
       <c r="G53" s="42" t="s">
-        <v>174</v>
+        <v>166</v>
       </c>
       <c r="H53" s="41" t="s">
         <v>99</v>
@@ -5593,8 +6467,8 @@
       </c>
     </row>
     <row r="54" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A54" s="56"/>
-      <c r="B54" s="56"/>
+      <c r="A54" s="55"/>
+      <c r="B54" s="55"/>
       <c r="C54" s="40">
         <v>16.600000000000001</v>
       </c>
@@ -5608,7 +6482,7 @@
         <v>110</v>
       </c>
       <c r="G54" s="42" t="s">
-        <v>175</v>
+        <v>167</v>
       </c>
       <c r="H54" s="41" t="s">
         <v>99</v>
@@ -5618,10 +6492,10 @@
       </c>
     </row>
     <row r="55" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A55" s="70">
+      <c r="A55" s="63">
         <v>17</v>
       </c>
-      <c r="B55" s="73" t="s">
+      <c r="B55" s="66" t="s">
         <v>111</v>
       </c>
       <c r="C55" s="43">
@@ -5637,7 +6511,7 @@
         <v>114</v>
       </c>
       <c r="G55" s="44" t="s">
-        <v>176</v>
+        <v>168</v>
       </c>
       <c r="H55" s="43" t="s">
         <v>115</v>
@@ -5647,8 +6521,8 @@
       </c>
     </row>
     <row r="56" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A56" s="71"/>
-      <c r="B56" s="73"/>
+      <c r="A56" s="64"/>
+      <c r="B56" s="66"/>
       <c r="C56" s="43">
         <v>17.2</v>
       </c>
@@ -5662,7 +6536,7 @@
         <v>117</v>
       </c>
       <c r="G56" s="44" t="s">
-        <v>177</v>
+        <v>169</v>
       </c>
       <c r="H56" s="43" t="s">
         <v>115</v>
@@ -5672,8 +6546,8 @@
       </c>
     </row>
     <row r="57" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A57" s="71"/>
-      <c r="B57" s="73"/>
+      <c r="A57" s="64"/>
+      <c r="B57" s="66"/>
       <c r="C57" s="43">
         <v>17.3</v>
       </c>
@@ -5687,7 +6561,7 @@
         <v>119</v>
       </c>
       <c r="G57" s="44" t="s">
-        <v>178</v>
+        <v>170</v>
       </c>
       <c r="H57" s="43" t="s">
         <v>99</v>
@@ -5697,8 +6571,8 @@
       </c>
     </row>
     <row r="58" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A58" s="71"/>
-      <c r="B58" s="73"/>
+      <c r="A58" s="64"/>
+      <c r="B58" s="66"/>
       <c r="C58" s="43">
         <v>17.399999999999999</v>
       </c>
@@ -5712,7 +6586,7 @@
         <v>121</v>
       </c>
       <c r="G58" s="44" t="s">
-        <v>179</v>
+        <v>171</v>
       </c>
       <c r="H58" s="43" t="s">
         <v>115</v>
@@ -5722,8 +6596,8 @@
       </c>
     </row>
     <row r="59" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A59" s="72"/>
-      <c r="B59" s="73"/>
+      <c r="A59" s="65"/>
+      <c r="B59" s="66"/>
       <c r="C59" s="43">
         <v>17.5</v>
       </c>
@@ -5737,7 +6611,7 @@
         <v>123</v>
       </c>
       <c r="G59" s="44" t="s">
-        <v>180</v>
+        <v>172</v>
       </c>
       <c r="H59" s="43" t="s">
         <v>115</v>
@@ -5746,529 +6620,445 @@
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A60" s="74">
+    <row r="60" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A60" s="67">
         <v>18</v>
       </c>
-      <c r="B60" s="74" t="s">
-        <v>124</v>
+      <c r="B60" s="67" t="s">
+        <v>289</v>
       </c>
       <c r="C60" s="18">
         <v>18.100000000000001</v>
       </c>
       <c r="D60" s="18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E60" s="18" t="s">
-        <v>250</v>
+        <v>290</v>
       </c>
       <c r="F60" s="18" t="s">
-        <v>126</v>
+        <v>291</v>
       </c>
       <c r="G60" s="19" t="s">
-        <v>181</v>
+        <v>293</v>
       </c>
       <c r="H60" s="18" t="s">
         <v>77</v>
       </c>
       <c r="I60" s="18" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A61" s="56"/>
-      <c r="B61" s="56"/>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" s="6" customFormat="1" ht="199.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A61" s="55"/>
+      <c r="B61" s="55"/>
       <c r="C61" s="18">
         <v>18.2</v>
       </c>
       <c r="D61" s="18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E61" s="18" t="s">
-        <v>251</v>
+        <v>292</v>
       </c>
       <c r="F61" s="18" t="s">
-        <v>128</v>
+        <v>294</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>182</v>
+        <v>300</v>
       </c>
       <c r="H61" s="18" t="s">
         <v>77</v>
       </c>
       <c r="I61" s="18" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A62" s="56"/>
-      <c r="B62" s="56"/>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" s="6" customFormat="1" ht="167.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A62" s="55"/>
+      <c r="B62" s="55"/>
       <c r="C62" s="18">
         <v>18.3</v>
       </c>
       <c r="D62" s="18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E62" s="18" t="s">
-        <v>252</v>
+        <v>297</v>
       </c>
       <c r="F62" s="18" t="s">
-        <v>129</v>
+        <v>295</v>
       </c>
       <c r="G62" s="19" t="s">
-        <v>183</v>
+        <v>296</v>
       </c>
       <c r="H62" s="18" t="s">
         <v>77</v>
       </c>
       <c r="I62" s="18" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A63" s="56"/>
-      <c r="B63" s="56"/>
+        <v>125</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" s="6" customFormat="1" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A63" s="55"/>
+      <c r="B63" s="55"/>
       <c r="C63" s="18">
         <v>18.399999999999999</v>
       </c>
       <c r="D63" s="18" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="E63" s="18" t="s">
-        <v>305</v>
+        <v>298</v>
       </c>
       <c r="F63" s="18" t="s">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>306</v>
+        <v>299</v>
       </c>
       <c r="H63" s="18" t="s">
         <v>77</v>
       </c>
       <c r="I63" s="18" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="64" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A64" s="56">
+        <v>19</v>
+      </c>
+      <c r="B64" s="59" t="s">
+        <v>126</v>
+      </c>
+      <c r="C64" s="45">
+        <v>19.100000000000001</v>
+      </c>
+      <c r="D64" s="46" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="64" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A64" s="56"/>
-      <c r="B64" s="56"/>
-      <c r="C64" s="18">
-        <v>18.5</v>
-      </c>
-      <c r="D64" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="E64" s="18" t="s">
-        <v>253</v>
-      </c>
-      <c r="F64" s="18" t="s">
+      <c r="E64" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="F64" s="46" t="s">
+        <v>230</v>
+      </c>
+      <c r="G64" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="H64" s="45"/>
+      <c r="I64" s="48"/>
+    </row>
+    <row r="65" spans="1:12" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A65" s="57"/>
+      <c r="B65" s="60"/>
+      <c r="C65" s="15">
+        <v>19.2</v>
+      </c>
+      <c r="D65" s="46" t="s">
+        <v>128</v>
+      </c>
+      <c r="E65" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="F65" s="46" t="s">
+        <v>226</v>
+      </c>
+      <c r="G65" s="47" t="s">
         <v>130</v>
       </c>
-      <c r="G64" s="19" t="s">
-        <v>184</v>
-      </c>
-      <c r="H64" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="I64" s="18" t="s">
+      <c r="H65" s="45"/>
+      <c r="I65" s="48"/>
+    </row>
+    <row r="66" spans="1:12" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A66" s="58"/>
+      <c r="B66" s="61"/>
+      <c r="C66" s="34">
+        <v>19.3</v>
+      </c>
+      <c r="D66" s="16" t="s">
         <v>127</v>
       </c>
-    </row>
-    <row r="65" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A65" s="56"/>
-      <c r="B65" s="56"/>
-      <c r="C65" s="18">
-        <v>18.600000000000001</v>
-      </c>
-      <c r="D65" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="E65" s="18" t="s">
-        <v>254</v>
-      </c>
-      <c r="F65" s="18" t="s">
+      <c r="E66" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="G65" s="19" t="s">
-        <v>185</v>
-      </c>
-      <c r="H65" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="I65" s="18" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="66" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A66" s="56"/>
-      <c r="B66" s="56"/>
-      <c r="C66" s="18">
-        <v>18.7</v>
-      </c>
-      <c r="D66" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="E66" s="18" t="s">
-        <v>255</v>
-      </c>
-      <c r="F66" s="18" t="s">
+      <c r="F66" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="G66" s="19" t="s">
-        <v>186</v>
-      </c>
-      <c r="H66" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="I66" s="18" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="67" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A67" s="56"/>
-      <c r="B67" s="56"/>
-      <c r="C67" s="18">
-        <v>18.8</v>
-      </c>
-      <c r="D67" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="E67" s="18" t="s">
-        <v>256</v>
-      </c>
-      <c r="F67" s="18" t="s">
+      <c r="G66" s="17"/>
+      <c r="H66" s="33"/>
+      <c r="I66" s="34"/>
+    </row>
+    <row r="67" spans="1:12" s="6" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A67" s="56">
+        <v>20</v>
+      </c>
+      <c r="B67" s="59" t="s">
         <v>133</v>
       </c>
-      <c r="G67" s="19" t="s">
-        <v>187</v>
-      </c>
-      <c r="H67" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="I67" s="18" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="68" spans="1:12" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="56"/>
-      <c r="B68" s="56"/>
-      <c r="C68" s="18">
-        <v>18.899999999999999</v>
-      </c>
-      <c r="D68" s="18" t="s">
-        <v>125</v>
-      </c>
-      <c r="E68" s="18" t="s">
-        <v>307</v>
-      </c>
-      <c r="F68" s="18" t="s">
-        <v>308</v>
-      </c>
-      <c r="G68" s="19" t="s">
-        <v>309</v>
-      </c>
-      <c r="H68" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="I68" s="18" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="69" spans="1:12" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A69" s="63">
-        <v>19</v>
-      </c>
-      <c r="B69" s="66" t="s">
+      <c r="C67" s="45">
+        <v>20.100000000000001</v>
+      </c>
+      <c r="D67" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="C69" s="45">
-        <v>19.100000000000001</v>
-      </c>
-      <c r="D69" s="46" t="s">
+      <c r="E67" s="46" t="s">
+        <v>243</v>
+      </c>
+      <c r="F67" s="46" t="s">
+        <v>244</v>
+      </c>
+      <c r="G67" s="47" t="s">
+        <v>245</v>
+      </c>
+      <c r="H67" s="45"/>
+      <c r="I67" s="48"/>
+    </row>
+    <row r="68" spans="1:12" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A68" s="57"/>
+      <c r="B68" s="60"/>
+      <c r="C68" s="15">
+        <v>20.2</v>
+      </c>
+      <c r="D68" s="46" t="s">
         <v>135</v>
       </c>
-      <c r="E69" s="46" t="s">
-        <v>246</v>
-      </c>
-      <c r="F69" s="46" t="s">
-        <v>245</v>
-      </c>
-      <c r="G69" s="47" t="s">
-        <v>247</v>
-      </c>
-      <c r="H69" s="45"/>
-      <c r="I69" s="48"/>
-    </row>
-    <row r="70" spans="1:12" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A70" s="64"/>
-      <c r="B70" s="67"/>
-      <c r="C70" s="15">
-        <v>19.2</v>
+      <c r="E68" s="46" t="s">
+        <v>233</v>
+      </c>
+      <c r="F68" s="46" t="s">
+        <v>226</v>
+      </c>
+      <c r="G68" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="H68" s="45"/>
+      <c r="I68" s="48"/>
+      <c r="J68" s="1"/>
+      <c r="K68" s="1"/>
+      <c r="L68" s="1"/>
+    </row>
+    <row r="69" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A69" s="58"/>
+      <c r="B69" s="61"/>
+      <c r="C69" s="33">
+        <v>20.3</v>
+      </c>
+      <c r="D69" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="E69" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="F69" s="16"/>
+      <c r="G69" s="17"/>
+      <c r="H69" s="33"/>
+      <c r="I69" s="34"/>
+      <c r="J69" s="1"/>
+      <c r="K69" s="1"/>
+      <c r="L69" s="1"/>
+    </row>
+    <row r="70" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A70" s="56">
+        <v>21</v>
+      </c>
+      <c r="B70" s="59" t="s">
+        <v>136</v>
+      </c>
+      <c r="C70" s="45">
+        <v>21.1</v>
       </c>
       <c r="D70" s="46" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
       <c r="E70" s="46" t="s">
-        <v>137</v>
+        <v>235</v>
       </c>
       <c r="F70" s="46" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="G70" s="47" t="s">
-        <v>138</v>
+        <v>237</v>
       </c>
       <c r="H70" s="45"/>
       <c r="I70" s="48"/>
     </row>
-    <row r="71" spans="1:12" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="65"/>
-      <c r="B71" s="68"/>
-      <c r="C71" s="34">
-        <v>19.3</v>
-      </c>
-      <c r="D71" s="16" t="s">
-        <v>135</v>
-      </c>
-      <c r="E71" s="16" t="s">
+    <row r="71" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="57"/>
+      <c r="B71" s="60"/>
+      <c r="C71" s="15">
+        <v>21.2</v>
+      </c>
+      <c r="D71" s="46" t="s">
+        <v>138</v>
+      </c>
+      <c r="E71" s="46" t="s">
+        <v>225</v>
+      </c>
+      <c r="F71" s="46" t="s">
+        <v>226</v>
+      </c>
+      <c r="G71" s="47" t="s">
         <v>139</v>
       </c>
-      <c r="F71" s="16" t="s">
+      <c r="H71" s="45"/>
+      <c r="I71" s="48"/>
+    </row>
+    <row r="72" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A72" s="58"/>
+      <c r="B72" s="61"/>
+      <c r="C72" s="33">
+        <v>21.3</v>
+      </c>
+      <c r="D72" s="16" t="s">
+        <v>137</v>
+      </c>
+      <c r="E72" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="F72" s="16"/>
+      <c r="G72" s="17"/>
+      <c r="H72" s="33"/>
+      <c r="I72" s="34"/>
+    </row>
+    <row r="73" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A73" s="56">
+        <v>22</v>
+      </c>
+      <c r="B73" s="59" t="s">
         <v>140</v>
       </c>
-      <c r="G71" s="17"/>
-      <c r="H71" s="33"/>
-      <c r="I71" s="34"/>
-    </row>
-    <row r="72" spans="1:12" s="6" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="63">
-        <v>20</v>
-      </c>
-      <c r="B72" s="66" t="s">
+      <c r="C73" s="45">
+        <v>22.1</v>
+      </c>
+      <c r="D73" s="46" t="s">
         <v>141</v>
       </c>
-      <c r="C72" s="45">
-        <v>20.100000000000001</v>
-      </c>
-      <c r="D72" s="46" t="s">
-        <v>142</v>
-      </c>
-      <c r="E72" s="46" t="s">
-        <v>265</v>
-      </c>
-      <c r="F72" s="46" t="s">
-        <v>266</v>
-      </c>
-      <c r="G72" s="47" t="s">
-        <v>267</v>
-      </c>
-      <c r="H72" s="45"/>
-      <c r="I72" s="48"/>
-    </row>
-    <row r="73" spans="1:12" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A73" s="64"/>
-      <c r="B73" s="67"/>
-      <c r="C73" s="15">
-        <v>20.2</v>
-      </c>
-      <c r="D73" s="46" t="s">
-        <v>143</v>
-      </c>
       <c r="E73" s="46" t="s">
-        <v>248</v>
+        <v>240</v>
       </c>
       <c r="F73" s="46" t="s">
         <v>241</v>
       </c>
       <c r="G73" s="47" t="s">
-        <v>249</v>
+        <v>242</v>
       </c>
       <c r="H73" s="45"/>
       <c r="I73" s="48"/>
-      <c r="J73" s="1"/>
-      <c r="K73" s="1"/>
-      <c r="L73" s="1"/>
-    </row>
-    <row r="74" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A74" s="65"/>
-      <c r="B74" s="68"/>
-      <c r="C74" s="33">
-        <v>20.3</v>
-      </c>
-      <c r="D74" s="16" t="s">
-        <v>142</v>
-      </c>
-      <c r="E74" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="F74" s="16"/>
-      <c r="G74" s="17"/>
-      <c r="H74" s="33"/>
-      <c r="I74" s="34"/>
-      <c r="J74" s="1"/>
-      <c r="K74" s="1"/>
-      <c r="L74" s="1"/>
-    </row>
-    <row r="75" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A75" s="63">
-        <v>21</v>
-      </c>
-      <c r="B75" s="66" t="s">
-        <v>144</v>
-      </c>
-      <c r="C75" s="45">
-        <v>21.1</v>
-      </c>
-      <c r="D75" s="46" t="s">
-        <v>145</v>
-      </c>
-      <c r="E75" s="46" t="s">
-        <v>257</v>
-      </c>
-      <c r="F75" s="46" t="s">
-        <v>258</v>
-      </c>
-      <c r="G75" s="47" t="s">
-        <v>259</v>
-      </c>
-      <c r="H75" s="45"/>
-      <c r="I75" s="48"/>
-    </row>
-    <row r="76" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A76" s="64"/>
-      <c r="B76" s="67"/>
-      <c r="C76" s="15">
-        <v>21.2</v>
-      </c>
-      <c r="D76" s="46" t="s">
-        <v>146</v>
-      </c>
-      <c r="E76" s="46" t="s">
-        <v>240</v>
-      </c>
-      <c r="F76" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="G76" s="47" t="s">
-        <v>147</v>
-      </c>
-      <c r="H76" s="45"/>
-      <c r="I76" s="48"/>
-    </row>
-    <row r="77" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A77" s="65"/>
-      <c r="B77" s="68"/>
-      <c r="C77" s="33">
-        <v>21.3</v>
-      </c>
-      <c r="D77" s="16" t="s">
-        <v>145</v>
-      </c>
-      <c r="E77" s="16" t="s">
-        <v>139</v>
-      </c>
-      <c r="F77" s="16"/>
-      <c r="G77" s="17"/>
-      <c r="H77" s="33"/>
-      <c r="I77" s="34"/>
-    </row>
-    <row r="78" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A78" s="63">
-        <v>22</v>
-      </c>
-      <c r="B78" s="66" t="s">
-        <v>148</v>
-      </c>
-      <c r="C78" s="45">
-        <v>22.1</v>
-      </c>
-      <c r="D78" s="46" t="s">
-        <v>149</v>
-      </c>
-      <c r="E78" s="46" t="s">
-        <v>262</v>
-      </c>
-      <c r="F78" s="46" t="s">
-        <v>263</v>
-      </c>
-      <c r="G78" s="47" t="s">
-        <v>264</v>
-      </c>
-      <c r="H78" s="45"/>
-      <c r="I78" s="48"/>
-    </row>
-    <row r="79" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A79" s="64"/>
-      <c r="B79" s="67"/>
-      <c r="C79" s="15">
+    </row>
+    <row r="74" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A74" s="57"/>
+      <c r="B74" s="60"/>
+      <c r="C74" s="15">
         <v>22.2</v>
       </c>
-      <c r="D79" s="46" t="s">
+      <c r="D74" s="46" t="s">
+        <v>224</v>
+      </c>
+      <c r="E74" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="F74" s="46" t="s">
+        <v>226</v>
+      </c>
+      <c r="G74" s="47" t="s">
         <v>239</v>
       </c>
-      <c r="E79" s="45" t="s">
-        <v>260</v>
-      </c>
-      <c r="F79" s="46" t="s">
-        <v>241</v>
-      </c>
-      <c r="G79" s="47" t="s">
-        <v>261</v>
-      </c>
-      <c r="H79" s="45"/>
-      <c r="I79" s="48"/>
-    </row>
-    <row r="80" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A80" s="65"/>
-      <c r="B80" s="68"/>
-      <c r="C80" s="33">
+      <c r="H74" s="45"/>
+      <c r="I74" s="48"/>
+    </row>
+    <row r="75" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A75" s="58"/>
+      <c r="B75" s="61"/>
+      <c r="C75" s="33">
         <v>22.3</v>
       </c>
-      <c r="D80" s="16" t="s">
-        <v>149</v>
-      </c>
-      <c r="E80" s="33" t="s">
-        <v>139</v>
-      </c>
-      <c r="F80" s="16"/>
-      <c r="G80" s="17"/>
-      <c r="H80" s="33"/>
-      <c r="I80" s="34"/>
-    </row>
-    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A81" s="3"/>
-      <c r="B81" s="3"/>
-      <c r="C81" s="3"/>
-      <c r="E81" s="11"/>
-      <c r="H81" s="3"/>
-    </row>
-    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D82" s="2"/>
-      <c r="F82" s="2"/>
-      <c r="G82" s="2"/>
-      <c r="I82" s="2"/>
-    </row>
-    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D83" s="2"/>
-      <c r="F83" s="2"/>
-      <c r="G83" s="2"/>
-      <c r="I83" s="2"/>
-    </row>
-    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A84" s="7"/>
-      <c r="B84" s="7"/>
-      <c r="C84" s="7"/>
-      <c r="D84" s="7"/>
-      <c r="E84" s="7"/>
-      <c r="F84" s="7"/>
-      <c r="G84" s="7"/>
-      <c r="H84" s="7"/>
-      <c r="I84" s="7"/>
-    </row>
-    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A85" s="3"/>
-      <c r="B85" s="3"/>
-      <c r="C85" s="3"/>
+      <c r="D75" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="E75" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="F75" s="16"/>
+      <c r="G75" s="17"/>
+      <c r="H75" s="33"/>
+      <c r="I75" s="34"/>
+    </row>
+    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A76" s="3"/>
+      <c r="B76" s="3"/>
+      <c r="C76" s="3"/>
+      <c r="E76" s="11"/>
+      <c r="H76" s="3"/>
+    </row>
+    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="D77" s="2"/>
+      <c r="F77" s="2"/>
+      <c r="G77" s="2"/>
+      <c r="I77" s="2"/>
+    </row>
+    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="D78" s="2"/>
+      <c r="F78" s="2"/>
+      <c r="G78" s="2"/>
+      <c r="I78" s="2"/>
+    </row>
+    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A79" s="7"/>
+      <c r="B79" s="7"/>
+      <c r="C79" s="7"/>
+      <c r="D79" s="7"/>
+      <c r="E79" s="7"/>
+      <c r="F79" s="7"/>
+      <c r="G79" s="7"/>
+      <c r="H79" s="7"/>
+      <c r="I79" s="7"/>
+    </row>
+    <row r="80" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="D80" s="10"/>
+      <c r="E80" s="10"/>
+      <c r="F80" s="10"/>
+      <c r="G80" s="8"/>
+      <c r="H80" s="10"/>
+      <c r="I80" s="10"/>
+    </row>
+    <row r="81" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D81" s="10"/>
+      <c r="E81" s="10"/>
+      <c r="F81" s="10"/>
+      <c r="G81" s="8"/>
+      <c r="H81" s="10"/>
+      <c r="I81" s="10"/>
+    </row>
+    <row r="82" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="B82" s="3"/>
+      <c r="D82" s="10"/>
+      <c r="E82" s="10"/>
+      <c r="F82" s="10"/>
+      <c r="G82" s="8"/>
+      <c r="H82" s="10"/>
+      <c r="I82" s="10"/>
+    </row>
+    <row r="83" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D83" s="10"/>
+      <c r="E83" s="10"/>
+      <c r="F83" s="10"/>
+      <c r="G83" s="8"/>
+      <c r="H83" s="10"/>
+      <c r="I83" s="10"/>
+    </row>
+    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="D84" s="10"/>
+      <c r="E84" s="10"/>
+      <c r="F84" s="10"/>
+      <c r="G84" s="8"/>
+      <c r="H84" s="10"/>
+      <c r="I84" s="10"/>
+    </row>
+    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D85" s="10"/>
       <c r="E85" s="10"/>
       <c r="F85" s="10"/>
@@ -6276,7 +7066,7 @@
       <c r="H85" s="10"/>
       <c r="I85" s="10"/>
     </row>
-    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D86" s="10"/>
       <c r="E86" s="10"/>
       <c r="F86" s="10"/>
@@ -6284,8 +7074,7 @@
       <c r="H86" s="10"/>
       <c r="I86" s="10"/>
     </row>
-    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B87" s="3"/>
+    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
       <c r="D87" s="10"/>
       <c r="E87" s="10"/>
       <c r="F87" s="10"/>
@@ -6293,71 +7082,9 @@
       <c r="H87" s="10"/>
       <c r="I87" s="10"/>
     </row>
-    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D88" s="10"/>
-      <c r="E88" s="10"/>
-      <c r="F88" s="10"/>
-      <c r="G88" s="8"/>
-      <c r="H88" s="10"/>
-      <c r="I88" s="10"/>
-    </row>
-    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D89" s="10"/>
-      <c r="E89" s="10"/>
-      <c r="F89" s="10"/>
-      <c r="G89" s="8"/>
-      <c r="H89" s="10"/>
-      <c r="I89" s="10"/>
-    </row>
-    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D90" s="10"/>
-      <c r="E90" s="10"/>
-      <c r="F90" s="10"/>
-      <c r="G90" s="8"/>
-      <c r="H90" s="10"/>
-      <c r="I90" s="10"/>
-    </row>
-    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D91" s="10"/>
-      <c r="E91" s="10"/>
-      <c r="F91" s="10"/>
-      <c r="G91" s="8"/>
-      <c r="H91" s="10"/>
-      <c r="I91" s="10"/>
-    </row>
-    <row r="92" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D92" s="10"/>
-      <c r="E92" s="10"/>
-      <c r="F92" s="10"/>
-      <c r="G92" s="8"/>
-      <c r="H92" s="10"/>
-      <c r="I92" s="10"/>
-    </row>
   </sheetData>
   <autoFilter ref="I1:I26" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="37">
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="A30:A40"/>
-    <mergeCell ref="B30:B40"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="A41:A48"/>
-    <mergeCell ref="B41:B48"/>
-    <mergeCell ref="A75:A77"/>
-    <mergeCell ref="B75:B77"/>
-    <mergeCell ref="A78:A80"/>
-    <mergeCell ref="B78:B80"/>
-    <mergeCell ref="A49:A54"/>
-    <mergeCell ref="B49:B54"/>
-    <mergeCell ref="A55:A59"/>
-    <mergeCell ref="B55:B59"/>
-    <mergeCell ref="A60:A68"/>
-    <mergeCell ref="B60:B68"/>
-    <mergeCell ref="A69:A71"/>
-    <mergeCell ref="B69:B71"/>
-    <mergeCell ref="A72:A74"/>
-    <mergeCell ref="B72:B74"/>
     <mergeCell ref="A13:A16"/>
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="A17:A20"/>
@@ -6373,6 +7100,28 @@
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="B3:B7"/>
     <mergeCell ref="B17:B20"/>
+    <mergeCell ref="A41:A48"/>
+    <mergeCell ref="B41:B48"/>
+    <mergeCell ref="A70:A72"/>
+    <mergeCell ref="B70:B72"/>
+    <mergeCell ref="A73:A75"/>
+    <mergeCell ref="B73:B75"/>
+    <mergeCell ref="A49:A54"/>
+    <mergeCell ref="B49:B54"/>
+    <mergeCell ref="A55:A59"/>
+    <mergeCell ref="B55:B59"/>
+    <mergeCell ref="A60:A63"/>
+    <mergeCell ref="B60:B63"/>
+    <mergeCell ref="A64:A66"/>
+    <mergeCell ref="B64:B66"/>
+    <mergeCell ref="A67:A69"/>
+    <mergeCell ref="B67:B69"/>
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="A30:A40"/>
+    <mergeCell ref="B30:B40"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="B21:B23"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -6433,7 +7182,7 @@
         <v>8</v>
       </c>
       <c r="H3" s="12" t="s">
-        <v>188</v>
+        <v>173</v>
       </c>
       <c r="I3" s="12" t="s">
         <v>4</v>
@@ -6451,16 +7200,16 @@
         <v>14.1</v>
       </c>
       <c r="F4" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G4" s="8" t="s">
-        <v>189</v>
+        <v>174</v>
       </c>
       <c r="H4" s="8" t="s">
-        <v>190</v>
+        <v>175</v>
       </c>
       <c r="I4" s="13" t="s">
-        <v>191</v>
+        <v>176</v>
       </c>
       <c r="J4" s="9"/>
     </row>
@@ -6475,16 +7224,16 @@
         <v>14.2</v>
       </c>
       <c r="F5" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G5" s="8" t="s">
-        <v>192</v>
+        <v>177</v>
       </c>
       <c r="H5" s="8" t="s">
-        <v>193</v>
+        <v>178</v>
       </c>
       <c r="I5" s="13" t="s">
-        <v>194</v>
+        <v>179</v>
       </c>
       <c r="J5" s="9"/>
     </row>
@@ -6499,16 +7248,16 @@
         <v>14.3</v>
       </c>
       <c r="F6" s="8" t="s">
-        <v>195</v>
+        <v>180</v>
       </c>
       <c r="G6" s="8" t="s">
-        <v>196</v>
+        <v>181</v>
       </c>
       <c r="H6" s="8" t="s">
-        <v>197</v>
+        <v>182</v>
       </c>
       <c r="I6" s="13" t="s">
-        <v>198</v>
+        <v>183</v>
       </c>
       <c r="J6" s="9"/>
     </row>
@@ -6523,16 +7272,16 @@
         <v>14.4</v>
       </c>
       <c r="F7" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G7" s="8" t="s">
-        <v>199</v>
+        <v>184</v>
       </c>
       <c r="H7" s="8" t="s">
-        <v>200</v>
+        <v>185</v>
       </c>
       <c r="I7" s="13" t="s">
-        <v>201</v>
+        <v>186</v>
       </c>
       <c r="J7" s="9"/>
     </row>
@@ -6547,16 +7296,16 @@
         <v>14.5</v>
       </c>
       <c r="F8" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G8" s="8" t="s">
-        <v>202</v>
+        <v>187</v>
       </c>
       <c r="H8" s="8" t="s">
-        <v>203</v>
+        <v>188</v>
       </c>
       <c r="I8" s="13" t="s">
-        <v>204</v>
+        <v>189</v>
       </c>
       <c r="J8" s="9"/>
     </row>
@@ -6571,16 +7320,16 @@
         <v>14.6</v>
       </c>
       <c r="F9" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G9" s="8" t="s">
-        <v>205</v>
+        <v>190</v>
       </c>
       <c r="H9" s="8" t="s">
-        <v>206</v>
+        <v>191</v>
       </c>
       <c r="I9" s="13" t="s">
-        <v>207</v>
+        <v>192</v>
       </c>
       <c r="J9" s="9"/>
     </row>
@@ -6595,16 +7344,16 @@
         <v>14.7</v>
       </c>
       <c r="F10" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G10" s="8" t="s">
-        <v>208</v>
+        <v>193</v>
       </c>
       <c r="H10" s="8" t="s">
-        <v>209</v>
+        <v>194</v>
       </c>
       <c r="I10" s="13" t="s">
-        <v>210</v>
+        <v>195</v>
       </c>
       <c r="J10" s="9"/>
     </row>
@@ -6619,16 +7368,16 @@
         <v>14.8</v>
       </c>
       <c r="F11" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G11" s="8" t="s">
-        <v>211</v>
+        <v>196</v>
       </c>
       <c r="H11" s="8" t="s">
-        <v>212</v>
+        <v>197</v>
       </c>
       <c r="I11" s="13" t="s">
-        <v>213</v>
+        <v>198</v>
       </c>
       <c r="J11" s="9"/>
     </row>
@@ -6643,16 +7392,16 @@
         <v>14.9</v>
       </c>
       <c r="F12" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G12" s="8" t="s">
-        <v>214</v>
+        <v>199</v>
       </c>
       <c r="H12" s="8" t="s">
-        <v>215</v>
+        <v>200</v>
       </c>
       <c r="I12" s="13" t="s">
-        <v>216</v>
+        <v>201</v>
       </c>
       <c r="J12" s="9"/>
     </row>
@@ -6664,19 +7413,19 @@
         <v>76</v>
       </c>
       <c r="E13" s="13" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="F13" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G13" s="8" t="s">
-        <v>218</v>
+        <v>203</v>
       </c>
       <c r="H13" s="8" t="s">
-        <v>219</v>
+        <v>204</v>
       </c>
       <c r="I13" s="13" t="s">
-        <v>220</v>
+        <v>205</v>
       </c>
       <c r="J13" s="9"/>
     </row>
@@ -6691,16 +7440,16 @@
         <v>14.11</v>
       </c>
       <c r="F14" s="8" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="G14" s="8" t="s">
-        <v>221</v>
+        <v>206</v>
       </c>
       <c r="H14" s="8" t="s">
-        <v>222</v>
+        <v>207</v>
       </c>
       <c r="I14" s="13" t="s">
-        <v>223</v>
+        <v>208</v>
       </c>
       <c r="J14" s="9"/>
     </row>

--- a/Soubhanik/checkupp_product_backlog_final.xlsx
+++ b/Soubhanik/checkupp_product_backlog_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Soubhanik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BF03BF71-B7C3-42C7-908E-80AD1F2DE1FB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4AD2BF9-54DE-4898-B0A7-E560789929EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -112,7 +112,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G64" authorId="0" shapeId="0" xr:uid="{3283D6CB-61A1-4390-A688-5F4F500D8585}">
+    <comment ref="G65" authorId="0" shapeId="0" xr:uid="{3283D6CB-61A1-4390-A688-5F4F500D8585}">
       <text>
         <r>
           <rPr>
@@ -136,7 +136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G67" authorId="0" shapeId="0" xr:uid="{C1521E49-0187-46FC-9D55-A1D99E904DBB}">
+    <comment ref="G68" authorId="0" shapeId="0" xr:uid="{C1521E49-0187-46FC-9D55-A1D99E904DBB}">
       <text>
         <r>
           <rPr>
@@ -160,7 +160,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G70" authorId="0" shapeId="0" xr:uid="{6311CE01-3810-423E-933D-ACFFBD920BE0}">
+    <comment ref="G71" authorId="0" shapeId="0" xr:uid="{6311CE01-3810-423E-933D-ACFFBD920BE0}">
       <text>
         <r>
           <rPr>
@@ -189,7 +189,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="462" uniqueCount="301">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="304">
   <si>
     <t>Epic #</t>
   </si>
@@ -4085,6 +4085,225 @@
   </si>
   <si>
     <r>
+      <t xml:space="preserve">1. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Add Specific Condtion </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">bottom sheet must contain the following:
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Condition or Diagnosis</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (free text field)
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Monitoring Type </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(Dropdown: Blood test, Imaging/ Radiology, Doctor Review, Endoscopy and Other...)
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">How Often? </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(multiple choice chips: Monthly, Every 3 Months, Ever 6 Months, Annually and Custom…)
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Doctor or Care Provider </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(free text field)
+- </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Primary button</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Save
+2</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">. Tapping "Other" option in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Monitoring Type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> field must render a free text field for user to type.
+3. Tapping the "Custom..." option in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>How Often?</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> field must render the following:
+- Numeric text input with engraved stepper control (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Chevron up</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Chevron down</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">)
+- Dropdown (Days, Weeks, Months, Years)
+4. The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Save</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> button must stay disabled (untappable) until all the mandatory fields have data entry.</t>
+    </r>
+  </si>
+  <si>
+    <r>
       <t xml:space="preserve">1. The specifc condition must be visually different than the default screenings in the </t>
     </r>
     <r>
@@ -4177,211 +4396,142 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">
-5. Tapping on the "Yes" button must open the app's existing data entry form for that corresponding screening.
-6. Tapping on the "No" button must open the app's exisiting Appointment Booking modal
+5. Tapping on the "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Yes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>" button must open the app's existing data entry form for that corresponding screening.
+6. Tapping on the "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>No</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">" button must open the app's exisiting Appointment Booking modal
 </t>
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">1. </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Add Specific Condtion </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">bottom sheet must contain the following:
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Condition or Diagnosis</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (free text field)
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Monitoring Type </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(Dropdown: Blood test, Imaging/ Radiology, Doctor Review, Endoscopy and Other...)
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">How Often? </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(multiple choice chips: Monthly, Every 3 Months, Ever 6 Months, Annually and Custom…)
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">Doctor or Care Provider </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">(free text field)
-- </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Primary button</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Save
-2</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">. Tapping "Other" option in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Monitoring Type</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> field must render a free text field for user to type.
-3. Tapping the "Custom..." option in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>How Often?</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> field must render the following:
-- Numeric text input with engraved stepper control (</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Chevron up</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Chevron down</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">)
-- Dropdown (Days, Weeks, Months, Years)
-4. The </t>
+    <t>Log the screening result for my specific condition</t>
+  </si>
+  <si>
+    <t>I can track my future screenings and have my health record in the app</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. The data entry form </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Log Specific Conditions </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">(full screen modal) must show the following info: condition name, monitoring type, frequency and care provider.
+2. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Date of Check</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> date picker must show the current date by default and let user pick a desired date.
+3. User must be able to type the outcome in a free text field </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Outcome or Clinical Notes</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Log Specific Conditions </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">form must have two CTA buttons: Secondary: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Cancel</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and Primary: </t>
     </r>
     <r>
       <rPr>
@@ -4398,7 +4548,111 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t xml:space="preserve"> button must stay disabled (untappable) until all the mandatory fields have data entry.</t>
+      <t xml:space="preserve">
+5. Tapping </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Cancel </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">button must close the modal and send user back to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Available Health Checks - Health Checks top tab - Screenings bottom tab</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+6. Tapping </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">Save </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">button must save the record in system, close the modal and send user to to </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Available Health Checks - Health Checks top tab - Screenings bottom tab</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>, showing a green pill displaying "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>current date</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">" on the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>specific condition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> screening card.</t>
     </r>
   </si>
 </sst>
@@ -4706,7 +4960,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="80">
+  <cellXfs count="81">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4852,26 +5106,50 @@
     <xf numFmtId="0" fontId="2" fillId="15" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -4909,40 +5187,19 @@
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5161,7 +5418,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L87"/>
+  <dimension ref="A1:L88"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.88671875" style="2" bestFit="1" customWidth="1"/>
@@ -5178,34 +5435,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="74" t="s">
+      <c r="A1" s="56" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="74" t="s">
+      <c r="B1" s="56" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="74" t="s">
+      <c r="C1" s="56" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="74" t="s">
+      <c r="D1" s="56" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="55"/>
-      <c r="F1" s="55"/>
-      <c r="G1" s="78" t="s">
+      <c r="E1" s="57"/>
+      <c r="F1" s="57"/>
+      <c r="G1" s="61" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="74" t="s">
+      <c r="H1" s="56" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="74" t="s">
+      <c r="I1" s="56" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="55"/>
-      <c r="B2" s="55"/>
-      <c r="C2" s="55"/>
+      <c r="A2" s="57"/>
+      <c r="B2" s="57"/>
+      <c r="C2" s="57"/>
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
@@ -5215,15 +5472,15 @@
       <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="78"/>
-      <c r="H2" s="55"/>
-      <c r="I2" s="55"/>
+      <c r="G2" s="61"/>
+      <c r="H2" s="57"/>
+      <c r="I2" s="57"/>
     </row>
     <row r="3" spans="1:9" s="5" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="79">
+      <c r="A3" s="62">
         <v>1</v>
       </c>
-      <c r="B3" s="79" t="s">
+      <c r="B3" s="62" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="16">
@@ -5249,8 +5506,8 @@
       </c>
     </row>
     <row r="4" spans="1:9" s="6" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="79"/>
-      <c r="B4" s="79"/>
+      <c r="A4" s="62"/>
+      <c r="B4" s="62"/>
       <c r="C4" s="16">
         <v>1.2</v>
       </c>
@@ -5270,8 +5527,8 @@
       <c r="I4" s="16"/>
     </row>
     <row r="5" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A5" s="79"/>
-      <c r="B5" s="79"/>
+      <c r="A5" s="62"/>
+      <c r="B5" s="62"/>
       <c r="C5" s="16">
         <v>1.3</v>
       </c>
@@ -5291,8 +5548,8 @@
       <c r="I5" s="16"/>
     </row>
     <row r="6" spans="1:9" s="6" customFormat="1" ht="154.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="79"/>
-      <c r="B6" s="79"/>
+      <c r="A6" s="62"/>
+      <c r="B6" s="62"/>
       <c r="C6" s="16">
         <v>1.4</v>
       </c>
@@ -5312,8 +5569,8 @@
       <c r="I6" s="16"/>
     </row>
     <row r="7" spans="1:9" s="6" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="79"/>
-      <c r="B7" s="79"/>
+      <c r="A7" s="62"/>
+      <c r="B7" s="62"/>
       <c r="C7" s="16">
         <v>1.5</v>
       </c>
@@ -5333,10 +5590,10 @@
       <c r="I7" s="16"/>
     </row>
     <row r="8" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="75">
+      <c r="A8" s="58">
         <v>5</v>
       </c>
-      <c r="B8" s="75" t="s">
+      <c r="B8" s="58" t="s">
         <v>13</v>
       </c>
       <c r="C8" s="18">
@@ -5362,8 +5619,8 @@
       </c>
     </row>
     <row r="9" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="76"/>
-      <c r="B9" s="76"/>
+      <c r="A9" s="59"/>
+      <c r="B9" s="59"/>
       <c r="C9" s="18">
         <v>5.2</v>
       </c>
@@ -5383,8 +5640,8 @@
       <c r="I9" s="18"/>
     </row>
     <row r="10" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="76"/>
-      <c r="B10" s="76"/>
+      <c r="A10" s="59"/>
+      <c r="B10" s="59"/>
       <c r="C10" s="18">
         <v>5.3</v>
       </c>
@@ -5404,8 +5661,8 @@
       <c r="I10" s="18"/>
     </row>
     <row r="11" spans="1:9" s="14" customFormat="1" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="76"/>
-      <c r="B11" s="76"/>
+      <c r="A11" s="59"/>
+      <c r="B11" s="59"/>
       <c r="C11" s="21">
         <v>5.4</v>
       </c>
@@ -5425,8 +5682,8 @@
       <c r="I11" s="21"/>
     </row>
     <row r="12" spans="1:9" s="14" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="77"/>
-      <c r="B12" s="77"/>
+      <c r="A12" s="60"/>
+      <c r="B12" s="60"/>
       <c r="C12" s="21">
         <v>5.5</v>
       </c>
@@ -5446,10 +5703,10 @@
       <c r="I12" s="21"/>
     </row>
     <row r="13" spans="1:9" s="14" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="68">
+      <c r="A13" s="50">
         <v>6</v>
       </c>
-      <c r="B13" s="68" t="s">
+      <c r="B13" s="50" t="s">
         <v>25</v>
       </c>
       <c r="C13" s="21">
@@ -5475,8 +5732,8 @@
       </c>
     </row>
     <row r="14" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A14" s="69"/>
-      <c r="B14" s="69"/>
+      <c r="A14" s="51"/>
+      <c r="B14" s="51"/>
       <c r="C14" s="24">
         <v>6.2</v>
       </c>
@@ -5496,8 +5753,8 @@
       <c r="I14" s="24"/>
     </row>
     <row r="15" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="69"/>
-      <c r="B15" s="69"/>
+      <c r="A15" s="51"/>
+      <c r="B15" s="51"/>
       <c r="C15" s="24">
         <v>6.3</v>
       </c>
@@ -5517,8 +5774,8 @@
       <c r="I15" s="24"/>
     </row>
     <row r="16" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A16" s="69"/>
-      <c r="B16" s="70"/>
+      <c r="A16" s="51"/>
+      <c r="B16" s="52"/>
       <c r="C16" s="27">
         <v>6.4</v>
       </c>
@@ -5542,10 +5799,10 @@
       </c>
     </row>
     <row r="17" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A17" s="71">
+      <c r="A17" s="53">
         <v>7</v>
       </c>
-      <c r="B17" s="68" t="s">
+      <c r="B17" s="50" t="s">
         <v>38</v>
       </c>
       <c r="C17" s="24">
@@ -5571,8 +5828,8 @@
       </c>
     </row>
     <row r="18" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A18" s="72"/>
-      <c r="B18" s="69"/>
+      <c r="A18" s="54"/>
+      <c r="B18" s="51"/>
       <c r="C18" s="24">
         <v>7.2</v>
       </c>
@@ -5594,8 +5851,8 @@
       </c>
     </row>
     <row r="19" spans="1:9" s="6" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="72"/>
-      <c r="B19" s="69"/>
+      <c r="A19" s="54"/>
+      <c r="B19" s="51"/>
       <c r="C19" s="24">
         <v>7.3</v>
       </c>
@@ -5615,8 +5872,8 @@
       <c r="I19" s="24"/>
     </row>
     <row r="20" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="73"/>
-      <c r="B20" s="70"/>
+      <c r="A20" s="55"/>
+      <c r="B20" s="52"/>
       <c r="C20" s="24">
         <v>7.4</v>
       </c>
@@ -5636,10 +5893,10 @@
       <c r="I20" s="24"/>
     </row>
     <row r="21" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="51">
+      <c r="A21" s="78">
         <v>8</v>
       </c>
-      <c r="B21" s="51" t="s">
+      <c r="B21" s="78" t="s">
         <v>50</v>
       </c>
       <c r="C21" s="28">
@@ -5663,8 +5920,8 @@
       </c>
     </row>
     <row r="22" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="52"/>
-      <c r="B22" s="52"/>
+      <c r="A22" s="79"/>
+      <c r="B22" s="79"/>
       <c r="C22" s="28">
         <v>9.3000000000000007</v>
       </c>
@@ -5686,8 +5943,8 @@
       </c>
     </row>
     <row r="23" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="53"/>
-      <c r="B23" s="53"/>
+      <c r="A23" s="80"/>
+      <c r="B23" s="80"/>
       <c r="C23" s="28">
         <v>9.4</v>
       </c>
@@ -5709,10 +5966,10 @@
       </c>
     </row>
     <row r="24" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="49">
+      <c r="A24" s="76">
         <v>12</v>
       </c>
-      <c r="B24" s="49" t="s">
+      <c r="B24" s="76" t="s">
         <v>60</v>
       </c>
       <c r="C24" s="31">
@@ -5738,8 +5995,8 @@
       </c>
     </row>
     <row r="25" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="49"/>
-      <c r="B25" s="49"/>
+      <c r="A25" s="76"/>
+      <c r="B25" s="76"/>
       <c r="C25" s="31">
         <v>12.2</v>
       </c>
@@ -5763,8 +6020,8 @@
       </c>
     </row>
     <row r="26" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="49"/>
-      <c r="B26" s="49"/>
+      <c r="A26" s="76"/>
+      <c r="B26" s="76"/>
       <c r="C26" s="31">
         <v>12.3</v>
       </c>
@@ -5788,8 +6045,8 @@
       </c>
     </row>
     <row r="27" spans="1:9" s="6" customFormat="1" ht="123.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="49"/>
-      <c r="B27" s="49"/>
+      <c r="A27" s="76"/>
+      <c r="B27" s="76"/>
       <c r="C27" s="31">
         <v>12.4</v>
       </c>
@@ -5813,8 +6070,8 @@
       </c>
     </row>
     <row r="28" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="49"/>
-      <c r="B28" s="49"/>
+      <c r="A28" s="76"/>
+      <c r="B28" s="76"/>
       <c r="C28" s="31">
         <v>12.5</v>
       </c>
@@ -5855,10 +6112,10 @@
       <c r="I29" s="34"/>
     </row>
     <row r="30" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="50">
+      <c r="A30" s="77">
         <v>14</v>
       </c>
-      <c r="B30" s="50" t="s">
+      <c r="B30" s="77" t="s">
         <v>76</v>
       </c>
       <c r="C30" s="35">
@@ -5884,8 +6141,8 @@
       </c>
     </row>
     <row r="31" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="50"/>
-      <c r="B31" s="50"/>
+      <c r="A31" s="77"/>
+      <c r="B31" s="77"/>
       <c r="C31" s="35">
         <v>14.2</v>
       </c>
@@ -5909,8 +6166,8 @@
       </c>
     </row>
     <row r="32" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="50"/>
-      <c r="B32" s="50"/>
+      <c r="A32" s="77"/>
+      <c r="B32" s="77"/>
       <c r="C32" s="35">
         <v>14.3</v>
       </c>
@@ -5934,8 +6191,8 @@
       </c>
     </row>
     <row r="33" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="50"/>
-      <c r="B33" s="50"/>
+      <c r="A33" s="77"/>
+      <c r="B33" s="77"/>
       <c r="C33" s="35">
         <v>14.4</v>
       </c>
@@ -5959,8 +6216,8 @@
       </c>
     </row>
     <row r="34" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="50"/>
-      <c r="B34" s="50"/>
+      <c r="A34" s="77"/>
+      <c r="B34" s="77"/>
       <c r="C34" s="35">
         <v>14.5</v>
       </c>
@@ -5984,8 +6241,8 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="50"/>
-      <c r="B35" s="50"/>
+      <c r="A35" s="77"/>
+      <c r="B35" s="77"/>
       <c r="C35" s="35">
         <v>14.6</v>
       </c>
@@ -6009,8 +6266,8 @@
       </c>
     </row>
     <row r="36" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="50"/>
-      <c r="B36" s="50"/>
+      <c r="A36" s="77"/>
+      <c r="B36" s="77"/>
       <c r="C36" s="35">
         <v>14.7</v>
       </c>
@@ -6034,8 +6291,8 @@
       </c>
     </row>
     <row r="37" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="50"/>
-      <c r="B37" s="50"/>
+      <c r="A37" s="77"/>
+      <c r="B37" s="77"/>
       <c r="C37" s="35">
         <v>14.8</v>
       </c>
@@ -6059,8 +6316,8 @@
       </c>
     </row>
     <row r="38" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A38" s="50"/>
-      <c r="B38" s="50"/>
+      <c r="A38" s="77"/>
+      <c r="B38" s="77"/>
       <c r="C38" s="35">
         <v>14.9</v>
       </c>
@@ -6084,8 +6341,8 @@
       </c>
     </row>
     <row r="39" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="50"/>
-      <c r="B39" s="50"/>
+      <c r="A39" s="77"/>
+      <c r="B39" s="77"/>
       <c r="C39" s="35">
         <v>14.1</v>
       </c>
@@ -6109,8 +6366,8 @@
       </c>
     </row>
     <row r="40" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="50"/>
-      <c r="B40" s="50"/>
+      <c r="A40" s="77"/>
+      <c r="B40" s="77"/>
       <c r="C40" s="35">
         <v>14.11</v>
       </c>
@@ -6134,10 +6391,10 @@
       </c>
     </row>
     <row r="41" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A41" s="54">
+      <c r="A41" s="63">
         <v>15</v>
       </c>
-      <c r="B41" s="54" t="s">
+      <c r="B41" s="63" t="s">
         <v>80</v>
       </c>
       <c r="C41" s="38">
@@ -6163,8 +6420,8 @@
       </c>
     </row>
     <row r="42" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="55"/>
-      <c r="B42" s="55"/>
+      <c r="A42" s="57"/>
+      <c r="B42" s="57"/>
       <c r="C42" s="38">
         <v>15.2</v>
       </c>
@@ -6188,8 +6445,8 @@
       </c>
     </row>
     <row r="43" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="55"/>
-      <c r="B43" s="55"/>
+      <c r="A43" s="57"/>
+      <c r="B43" s="57"/>
       <c r="C43" s="38">
         <v>15.3</v>
       </c>
@@ -6213,8 +6470,8 @@
       </c>
     </row>
     <row r="44" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A44" s="55"/>
-      <c r="B44" s="55"/>
+      <c r="A44" s="57"/>
+      <c r="B44" s="57"/>
       <c r="C44" s="38">
         <v>15.4</v>
       </c>
@@ -6238,8 +6495,8 @@
       </c>
     </row>
     <row r="45" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="55"/>
-      <c r="B45" s="55"/>
+      <c r="A45" s="57"/>
+      <c r="B45" s="57"/>
       <c r="C45" s="38">
         <v>15.5</v>
       </c>
@@ -6263,8 +6520,8 @@
       </c>
     </row>
     <row r="46" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="55"/>
-      <c r="B46" s="55"/>
+      <c r="A46" s="57"/>
+      <c r="B46" s="57"/>
       <c r="C46" s="38">
         <v>15.6</v>
       </c>
@@ -6288,8 +6545,8 @@
       </c>
     </row>
     <row r="47" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A47" s="55"/>
-      <c r="B47" s="55"/>
+      <c r="A47" s="57"/>
+      <c r="B47" s="57"/>
       <c r="C47" s="38">
         <v>15.7</v>
       </c>
@@ -6313,8 +6570,8 @@
       </c>
     </row>
     <row r="48" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="55"/>
-      <c r="B48" s="55"/>
+      <c r="A48" s="57"/>
+      <c r="B48" s="57"/>
       <c r="C48" s="38">
         <v>15.8</v>
       </c>
@@ -6338,10 +6595,10 @@
       </c>
     </row>
     <row r="49" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A49" s="62">
+      <c r="A49" s="70">
         <v>16</v>
       </c>
-      <c r="B49" s="62" t="s">
+      <c r="B49" s="70" t="s">
         <v>95</v>
       </c>
       <c r="C49" s="40">
@@ -6367,8 +6624,8 @@
       </c>
     </row>
     <row r="50" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A50" s="62"/>
-      <c r="B50" s="62"/>
+      <c r="A50" s="70"/>
+      <c r="B50" s="70"/>
       <c r="C50" s="40">
         <v>16.2</v>
       </c>
@@ -6392,8 +6649,8 @@
       </c>
     </row>
     <row r="51" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="62"/>
-      <c r="B51" s="62"/>
+      <c r="A51" s="70"/>
+      <c r="B51" s="70"/>
       <c r="C51" s="40">
         <v>16.3</v>
       </c>
@@ -6417,8 +6674,8 @@
       </c>
     </row>
     <row r="52" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A52" s="62"/>
-      <c r="B52" s="62"/>
+      <c r="A52" s="70"/>
+      <c r="B52" s="70"/>
       <c r="C52" s="40">
         <v>16.399999999999999</v>
       </c>
@@ -6442,8 +6699,8 @@
       </c>
     </row>
     <row r="53" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A53" s="62"/>
-      <c r="B53" s="62"/>
+      <c r="A53" s="70"/>
+      <c r="B53" s="70"/>
       <c r="C53" s="40">
         <v>16.5</v>
       </c>
@@ -6467,8 +6724,8 @@
       </c>
     </row>
     <row r="54" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A54" s="55"/>
-      <c r="B54" s="55"/>
+      <c r="A54" s="57"/>
+      <c r="B54" s="57"/>
       <c r="C54" s="40">
         <v>16.600000000000001</v>
       </c>
@@ -6492,10 +6749,10 @@
       </c>
     </row>
     <row r="55" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A55" s="63">
+      <c r="A55" s="71">
         <v>17</v>
       </c>
-      <c r="B55" s="66" t="s">
+      <c r="B55" s="74" t="s">
         <v>111</v>
       </c>
       <c r="C55" s="43">
@@ -6521,8 +6778,8 @@
       </c>
     </row>
     <row r="56" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A56" s="64"/>
-      <c r="B56" s="66"/>
+      <c r="A56" s="72"/>
+      <c r="B56" s="74"/>
       <c r="C56" s="43">
         <v>17.2</v>
       </c>
@@ -6546,8 +6803,8 @@
       </c>
     </row>
     <row r="57" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A57" s="64"/>
-      <c r="B57" s="66"/>
+      <c r="A57" s="72"/>
+      <c r="B57" s="74"/>
       <c r="C57" s="43">
         <v>17.3</v>
       </c>
@@ -6571,8 +6828,8 @@
       </c>
     </row>
     <row r="58" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A58" s="64"/>
-      <c r="B58" s="66"/>
+      <c r="A58" s="72"/>
+      <c r="B58" s="74"/>
       <c r="C58" s="43">
         <v>17.399999999999999</v>
       </c>
@@ -6596,8 +6853,8 @@
       </c>
     </row>
     <row r="59" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A59" s="65"/>
-      <c r="B59" s="66"/>
+      <c r="A59" s="73"/>
+      <c r="B59" s="74"/>
       <c r="C59" s="43">
         <v>17.5</v>
       </c>
@@ -6621,10 +6878,10 @@
       </c>
     </row>
     <row r="60" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A60" s="67">
+      <c r="A60" s="75">
         <v>18</v>
       </c>
-      <c r="B60" s="67" t="s">
+      <c r="B60" s="75" t="s">
         <v>289</v>
       </c>
       <c r="C60" s="18">
@@ -6650,8 +6907,8 @@
       </c>
     </row>
     <row r="61" spans="1:9" s="6" customFormat="1" ht="199.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="55"/>
-      <c r="B61" s="55"/>
+      <c r="A61" s="57"/>
+      <c r="B61" s="57"/>
       <c r="C61" s="18">
         <v>18.2</v>
       </c>
@@ -6665,7 +6922,7 @@
         <v>294</v>
       </c>
       <c r="G61" s="19" t="s">
-        <v>300</v>
+        <v>299</v>
       </c>
       <c r="H61" s="18" t="s">
         <v>77</v>
@@ -6675,8 +6932,8 @@
       </c>
     </row>
     <row r="62" spans="1:9" s="6" customFormat="1" ht="167.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="55"/>
-      <c r="B62" s="55"/>
+      <c r="A62" s="57"/>
+      <c r="B62" s="57"/>
       <c r="C62" s="18">
         <v>18.3</v>
       </c>
@@ -6700,8 +6957,8 @@
       </c>
     </row>
     <row r="63" spans="1:9" s="6" customFormat="1" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A63" s="55"/>
-      <c r="B63" s="55"/>
+      <c r="A63" s="57"/>
+      <c r="B63" s="57"/>
       <c r="C63" s="18">
         <v>18.399999999999999</v>
       </c>
@@ -6715,7 +6972,7 @@
         <v>284</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="H63" s="18" t="s">
         <v>77</v>
@@ -6724,278 +6981,291 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A64" s="56">
+    <row r="64" spans="1:9" s="6" customFormat="1" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="49"/>
+      <c r="B64" s="49"/>
+      <c r="C64" s="18"/>
+      <c r="D64" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="E64" s="18" t="s">
+        <v>301</v>
+      </c>
+      <c r="F64" s="18" t="s">
+        <v>302</v>
+      </c>
+      <c r="G64" s="19" t="s">
+        <v>303</v>
+      </c>
+      <c r="H64" s="18"/>
+      <c r="I64" s="18"/>
+    </row>
+    <row r="65" spans="1:12" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A65" s="64">
         <v>19</v>
       </c>
-      <c r="B64" s="59" t="s">
+      <c r="B65" s="67" t="s">
         <v>126</v>
       </c>
-      <c r="C64" s="45">
+      <c r="C65" s="45">
         <v>19.100000000000001</v>
       </c>
-      <c r="D64" s="46" t="s">
+      <c r="D65" s="46" t="s">
         <v>127</v>
       </c>
-      <c r="E64" s="46" t="s">
+      <c r="E65" s="46" t="s">
         <v>231</v>
       </c>
-      <c r="F64" s="46" t="s">
+      <c r="F65" s="46" t="s">
         <v>230</v>
       </c>
-      <c r="G64" s="47" t="s">
+      <c r="G65" s="47" t="s">
         <v>232</v>
-      </c>
-      <c r="H64" s="45"/>
-      <c r="I64" s="48"/>
-    </row>
-    <row r="65" spans="1:12" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A65" s="57"/>
-      <c r="B65" s="60"/>
-      <c r="C65" s="15">
-        <v>19.2</v>
-      </c>
-      <c r="D65" s="46" t="s">
-        <v>128</v>
-      </c>
-      <c r="E65" s="46" t="s">
-        <v>129</v>
-      </c>
-      <c r="F65" s="46" t="s">
-        <v>226</v>
-      </c>
-      <c r="G65" s="47" t="s">
-        <v>130</v>
       </c>
       <c r="H65" s="45"/>
       <c r="I65" s="48"/>
     </row>
-    <row r="66" spans="1:12" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="58"/>
-      <c r="B66" s="61"/>
-      <c r="C66" s="34">
+    <row r="66" spans="1:12" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A66" s="65"/>
+      <c r="B66" s="68"/>
+      <c r="C66" s="15">
+        <v>19.2</v>
+      </c>
+      <c r="D66" s="46" t="s">
+        <v>128</v>
+      </c>
+      <c r="E66" s="46" t="s">
+        <v>129</v>
+      </c>
+      <c r="F66" s="46" t="s">
+        <v>226</v>
+      </c>
+      <c r="G66" s="47" t="s">
+        <v>130</v>
+      </c>
+      <c r="H66" s="45"/>
+      <c r="I66" s="48"/>
+    </row>
+    <row r="67" spans="1:12" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A67" s="66"/>
+      <c r="B67" s="69"/>
+      <c r="C67" s="34">
         <v>19.3</v>
       </c>
-      <c r="D66" s="16" t="s">
+      <c r="D67" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="E66" s="16" t="s">
+      <c r="E67" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="F66" s="16" t="s">
+      <c r="F67" s="16" t="s">
         <v>132</v>
       </c>
-      <c r="G66" s="17"/>
-      <c r="H66" s="33"/>
-      <c r="I66" s="34"/>
-    </row>
-    <row r="67" spans="1:12" s="6" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="56">
+      <c r="G67" s="17"/>
+      <c r="H67" s="33"/>
+      <c r="I67" s="34"/>
+    </row>
+    <row r="68" spans="1:12" s="6" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A68" s="64">
         <v>20</v>
       </c>
-      <c r="B67" s="59" t="s">
+      <c r="B68" s="67" t="s">
         <v>133</v>
       </c>
-      <c r="C67" s="45">
+      <c r="C68" s="45">
         <v>20.100000000000001</v>
       </c>
-      <c r="D67" s="46" t="s">
+      <c r="D68" s="46" t="s">
         <v>134</v>
       </c>
-      <c r="E67" s="46" t="s">
+      <c r="E68" s="46" t="s">
         <v>243</v>
       </c>
-      <c r="F67" s="46" t="s">
+      <c r="F68" s="46" t="s">
         <v>244</v>
       </c>
-      <c r="G67" s="47" t="s">
+      <c r="G68" s="47" t="s">
         <v>245</v>
-      </c>
-      <c r="H67" s="45"/>
-      <c r="I67" s="48"/>
-    </row>
-    <row r="68" spans="1:12" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A68" s="57"/>
-      <c r="B68" s="60"/>
-      <c r="C68" s="15">
-        <v>20.2</v>
-      </c>
-      <c r="D68" s="46" t="s">
-        <v>135</v>
-      </c>
-      <c r="E68" s="46" t="s">
-        <v>233</v>
-      </c>
-      <c r="F68" s="46" t="s">
-        <v>226</v>
-      </c>
-      <c r="G68" s="47" t="s">
-        <v>234</v>
       </c>
       <c r="H68" s="45"/>
       <c r="I68" s="48"/>
-      <c r="J68" s="1"/>
-      <c r="K68" s="1"/>
-      <c r="L68" s="1"/>
-    </row>
-    <row r="69" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A69" s="58"/>
-      <c r="B69" s="61"/>
-      <c r="C69" s="33">
-        <v>20.3</v>
-      </c>
-      <c r="D69" s="16" t="s">
-        <v>134</v>
-      </c>
-      <c r="E69" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="F69" s="16"/>
-      <c r="G69" s="17"/>
-      <c r="H69" s="33"/>
-      <c r="I69" s="34"/>
+    </row>
+    <row r="69" spans="1:12" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A69" s="65"/>
+      <c r="B69" s="68"/>
+      <c r="C69" s="15">
+        <v>20.2</v>
+      </c>
+      <c r="D69" s="46" t="s">
+        <v>135</v>
+      </c>
+      <c r="E69" s="46" t="s">
+        <v>233</v>
+      </c>
+      <c r="F69" s="46" t="s">
+        <v>226</v>
+      </c>
+      <c r="G69" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="H69" s="45"/>
+      <c r="I69" s="48"/>
       <c r="J69" s="1"/>
       <c r="K69" s="1"/>
       <c r="L69" s="1"/>
     </row>
-    <row r="70" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A70" s="56">
+    <row r="70" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A70" s="66"/>
+      <c r="B70" s="69"/>
+      <c r="C70" s="33">
+        <v>20.3</v>
+      </c>
+      <c r="D70" s="16" t="s">
+        <v>134</v>
+      </c>
+      <c r="E70" s="16" t="s">
+        <v>131</v>
+      </c>
+      <c r="F70" s="16"/>
+      <c r="G70" s="17"/>
+      <c r="H70" s="33"/>
+      <c r="I70" s="34"/>
+      <c r="J70" s="1"/>
+      <c r="K70" s="1"/>
+      <c r="L70" s="1"/>
+    </row>
+    <row r="71" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A71" s="64">
         <v>21</v>
       </c>
-      <c r="B70" s="59" t="s">
+      <c r="B71" s="67" t="s">
         <v>136</v>
       </c>
-      <c r="C70" s="45">
+      <c r="C71" s="45">
         <v>21.1</v>
       </c>
-      <c r="D70" s="46" t="s">
+      <c r="D71" s="46" t="s">
         <v>137</v>
       </c>
-      <c r="E70" s="46" t="s">
+      <c r="E71" s="46" t="s">
         <v>235</v>
       </c>
-      <c r="F70" s="46" t="s">
+      <c r="F71" s="46" t="s">
         <v>236</v>
       </c>
-      <c r="G70" s="47" t="s">
+      <c r="G71" s="47" t="s">
         <v>237</v>
-      </c>
-      <c r="H70" s="45"/>
-      <c r="I70" s="48"/>
-    </row>
-    <row r="71" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A71" s="57"/>
-      <c r="B71" s="60"/>
-      <c r="C71" s="15">
-        <v>21.2</v>
-      </c>
-      <c r="D71" s="46" t="s">
-        <v>138</v>
-      </c>
-      <c r="E71" s="46" t="s">
-        <v>225</v>
-      </c>
-      <c r="F71" s="46" t="s">
-        <v>226</v>
-      </c>
-      <c r="G71" s="47" t="s">
-        <v>139</v>
       </c>
       <c r="H71" s="45"/>
       <c r="I71" s="48"/>
     </row>
-    <row r="72" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A72" s="58"/>
-      <c r="B72" s="61"/>
-      <c r="C72" s="33">
+    <row r="72" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A72" s="65"/>
+      <c r="B72" s="68"/>
+      <c r="C72" s="15">
+        <v>21.2</v>
+      </c>
+      <c r="D72" s="46" t="s">
+        <v>138</v>
+      </c>
+      <c r="E72" s="46" t="s">
+        <v>225</v>
+      </c>
+      <c r="F72" s="46" t="s">
+        <v>226</v>
+      </c>
+      <c r="G72" s="47" t="s">
+        <v>139</v>
+      </c>
+      <c r="H72" s="45"/>
+      <c r="I72" s="48"/>
+    </row>
+    <row r="73" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A73" s="66"/>
+      <c r="B73" s="69"/>
+      <c r="C73" s="33">
         <v>21.3</v>
       </c>
-      <c r="D72" s="16" t="s">
+      <c r="D73" s="16" t="s">
         <v>137</v>
       </c>
-      <c r="E72" s="16" t="s">
+      <c r="E73" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="F72" s="16"/>
-      <c r="G72" s="17"/>
-      <c r="H72" s="33"/>
-      <c r="I72" s="34"/>
-    </row>
-    <row r="73" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A73" s="56">
+      <c r="F73" s="16"/>
+      <c r="G73" s="17"/>
+      <c r="H73" s="33"/>
+      <c r="I73" s="34"/>
+    </row>
+    <row r="74" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A74" s="64">
         <v>22</v>
       </c>
-      <c r="B73" s="59" t="s">
+      <c r="B74" s="67" t="s">
         <v>140</v>
       </c>
-      <c r="C73" s="45">
+      <c r="C74" s="45">
         <v>22.1</v>
       </c>
-      <c r="D73" s="46" t="s">
+      <c r="D74" s="46" t="s">
         <v>141</v>
       </c>
-      <c r="E73" s="46" t="s">
+      <c r="E74" s="46" t="s">
         <v>240</v>
       </c>
-      <c r="F73" s="46" t="s">
+      <c r="F74" s="46" t="s">
         <v>241</v>
       </c>
-      <c r="G73" s="47" t="s">
+      <c r="G74" s="47" t="s">
         <v>242</v>
-      </c>
-      <c r="H73" s="45"/>
-      <c r="I73" s="48"/>
-    </row>
-    <row r="74" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A74" s="57"/>
-      <c r="B74" s="60"/>
-      <c r="C74" s="15">
-        <v>22.2</v>
-      </c>
-      <c r="D74" s="46" t="s">
-        <v>224</v>
-      </c>
-      <c r="E74" s="45" t="s">
-        <v>238</v>
-      </c>
-      <c r="F74" s="46" t="s">
-        <v>226</v>
-      </c>
-      <c r="G74" s="47" t="s">
-        <v>239</v>
       </c>
       <c r="H74" s="45"/>
       <c r="I74" s="48"/>
     </row>
-    <row r="75" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A75" s="58"/>
-      <c r="B75" s="61"/>
-      <c r="C75" s="33">
+    <row r="75" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A75" s="65"/>
+      <c r="B75" s="68"/>
+      <c r="C75" s="15">
+        <v>22.2</v>
+      </c>
+      <c r="D75" s="46" t="s">
+        <v>224</v>
+      </c>
+      <c r="E75" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="F75" s="46" t="s">
+        <v>226</v>
+      </c>
+      <c r="G75" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="H75" s="45"/>
+      <c r="I75" s="48"/>
+    </row>
+    <row r="76" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A76" s="66"/>
+      <c r="B76" s="69"/>
+      <c r="C76" s="33">
         <v>22.3</v>
       </c>
-      <c r="D75" s="16" t="s">
+      <c r="D76" s="16" t="s">
         <v>141</v>
       </c>
-      <c r="E75" s="33" t="s">
+      <c r="E76" s="33" t="s">
         <v>131</v>
       </c>
-      <c r="F75" s="16"/>
-      <c r="G75" s="17"/>
-      <c r="H75" s="33"/>
-      <c r="I75" s="34"/>
-    </row>
-    <row r="76" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A76" s="3"/>
-      <c r="B76" s="3"/>
-      <c r="C76" s="3"/>
-      <c r="E76" s="11"/>
-      <c r="H76" s="3"/>
+      <c r="F76" s="16"/>
+      <c r="G76" s="17"/>
+      <c r="H76" s="33"/>
+      <c r="I76" s="34"/>
     </row>
     <row r="77" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D77" s="2"/>
-      <c r="F77" s="2"/>
-      <c r="G77" s="2"/>
-      <c r="I77" s="2"/>
+      <c r="A77" s="3"/>
+      <c r="B77" s="3"/>
+      <c r="C77" s="3"/>
+      <c r="E77" s="11"/>
+      <c r="H77" s="3"/>
     </row>
     <row r="78" spans="1:12" x14ac:dyDescent="0.3">
       <c r="D78" s="2"/>
@@ -7004,28 +7274,26 @@
       <c r="I78" s="2"/>
     </row>
     <row r="79" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A79" s="7"/>
-      <c r="B79" s="7"/>
-      <c r="C79" s="7"/>
-      <c r="D79" s="7"/>
-      <c r="E79" s="7"/>
-      <c r="F79" s="7"/>
-      <c r="G79" s="7"/>
-      <c r="H79" s="7"/>
-      <c r="I79" s="7"/>
+      <c r="D79" s="2"/>
+      <c r="F79" s="2"/>
+      <c r="G79" s="2"/>
+      <c r="I79" s="2"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A80" s="3"/>
-      <c r="B80" s="3"/>
-      <c r="C80" s="3"/>
-      <c r="D80" s="10"/>
-      <c r="E80" s="10"/>
-      <c r="F80" s="10"/>
-      <c r="G80" s="8"/>
-      <c r="H80" s="10"/>
-      <c r="I80" s="10"/>
-    </row>
-    <row r="81" spans="2:9" x14ac:dyDescent="0.3">
+      <c r="A80" s="7"/>
+      <c r="B80" s="7"/>
+      <c r="C80" s="7"/>
+      <c r="D80" s="7"/>
+      <c r="E80" s="7"/>
+      <c r="F80" s="7"/>
+      <c r="G80" s="7"/>
+      <c r="H80" s="7"/>
+      <c r="I80" s="7"/>
+    </row>
+    <row r="81" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A81" s="3"/>
+      <c r="B81" s="3"/>
+      <c r="C81" s="3"/>
       <c r="D81" s="10"/>
       <c r="E81" s="10"/>
       <c r="F81" s="10"/>
@@ -7033,8 +7301,7 @@
       <c r="H81" s="10"/>
       <c r="I81" s="10"/>
     </row>
-    <row r="82" spans="2:9" x14ac:dyDescent="0.3">
-      <c r="B82" s="3"/>
+    <row r="82" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D82" s="10"/>
       <c r="E82" s="10"/>
       <c r="F82" s="10"/>
@@ -7042,7 +7309,8 @@
       <c r="H82" s="10"/>
       <c r="I82" s="10"/>
     </row>
-    <row r="83" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B83" s="3"/>
       <c r="D83" s="10"/>
       <c r="E83" s="10"/>
       <c r="F83" s="10"/>
@@ -7050,7 +7318,7 @@
       <c r="H83" s="10"/>
       <c r="I83" s="10"/>
     </row>
-    <row r="84" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D84" s="10"/>
       <c r="E84" s="10"/>
       <c r="F84" s="10"/>
@@ -7058,7 +7326,7 @@
       <c r="H84" s="10"/>
       <c r="I84" s="10"/>
     </row>
-    <row r="85" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D85" s="10"/>
       <c r="E85" s="10"/>
       <c r="F85" s="10"/>
@@ -7066,7 +7334,7 @@
       <c r="H85" s="10"/>
       <c r="I85" s="10"/>
     </row>
-    <row r="86" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D86" s="10"/>
       <c r="E86" s="10"/>
       <c r="F86" s="10"/>
@@ -7074,7 +7342,7 @@
       <c r="H86" s="10"/>
       <c r="I86" s="10"/>
     </row>
-    <row r="87" spans="2:9" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:9" x14ac:dyDescent="0.3">
       <c r="D87" s="10"/>
       <c r="E87" s="10"/>
       <c r="F87" s="10"/>
@@ -7082,9 +7350,39 @@
       <c r="H87" s="10"/>
       <c r="I87" s="10"/>
     </row>
+    <row r="88" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D88" s="10"/>
+      <c r="E88" s="10"/>
+      <c r="F88" s="10"/>
+      <c r="G88" s="8"/>
+      <c r="H88" s="10"/>
+      <c r="I88" s="10"/>
+    </row>
   </sheetData>
   <autoFilter ref="I1:I26" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="37">
+    <mergeCell ref="A24:A28"/>
+    <mergeCell ref="B24:B28"/>
+    <mergeCell ref="A30:A40"/>
+    <mergeCell ref="B30:B40"/>
+    <mergeCell ref="A21:A23"/>
+    <mergeCell ref="B21:B23"/>
+    <mergeCell ref="A41:A48"/>
+    <mergeCell ref="B41:B48"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="B71:B73"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="B74:B76"/>
+    <mergeCell ref="A49:A54"/>
+    <mergeCell ref="B49:B54"/>
+    <mergeCell ref="A55:A59"/>
+    <mergeCell ref="B55:B59"/>
+    <mergeCell ref="A60:A63"/>
+    <mergeCell ref="B60:B63"/>
+    <mergeCell ref="A65:A67"/>
+    <mergeCell ref="B65:B67"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="B68:B70"/>
     <mergeCell ref="A13:A16"/>
     <mergeCell ref="B13:B16"/>
     <mergeCell ref="A17:A20"/>
@@ -7100,28 +7398,6 @@
     <mergeCell ref="A3:A7"/>
     <mergeCell ref="B3:B7"/>
     <mergeCell ref="B17:B20"/>
-    <mergeCell ref="A41:A48"/>
-    <mergeCell ref="B41:B48"/>
-    <mergeCell ref="A70:A72"/>
-    <mergeCell ref="B70:B72"/>
-    <mergeCell ref="A73:A75"/>
-    <mergeCell ref="B73:B75"/>
-    <mergeCell ref="A49:A54"/>
-    <mergeCell ref="B49:B54"/>
-    <mergeCell ref="A55:A59"/>
-    <mergeCell ref="B55:B59"/>
-    <mergeCell ref="A60:A63"/>
-    <mergeCell ref="B60:B63"/>
-    <mergeCell ref="A64:A66"/>
-    <mergeCell ref="B64:B66"/>
-    <mergeCell ref="A67:A69"/>
-    <mergeCell ref="B67:B69"/>
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="A30:A40"/>
-    <mergeCell ref="B30:B40"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="B21:B23"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>

--- a/Soubhanik/checkupp_product_backlog_final.xlsx
+++ b/Soubhanik/checkupp_product_backlog_final.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\GitHub\CheckUpp\Soubhanik\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A4AD2BF9-54DE-4898-B0A7-E560789929EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3882B033-71BD-4562-97C9-9D1442EAEB87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -17,7 +17,7 @@
     <sheet name="Sheet2" sheetId="2" r:id="rId2"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$I$1:$I$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$I$1:$I$29</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -40,7 +40,7 @@
     <author>HP</author>
   </authors>
   <commentList>
-    <comment ref="F11" authorId="0" shapeId="0" xr:uid="{19C9952F-A312-497A-B805-86D2AF987FB6}">
+    <comment ref="F14" authorId="0" shapeId="0" xr:uid="{19C9952F-A312-497A-B805-86D2AF987FB6}">
       <text>
         <r>
           <rPr>
@@ -64,7 +64,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F12" authorId="0" shapeId="0" xr:uid="{0C139348-C773-4A3A-9EFF-28FD018E1F38}">
+    <comment ref="F15" authorId="0" shapeId="0" xr:uid="{0C139348-C773-4A3A-9EFF-28FD018E1F38}">
       <text>
         <r>
           <rPr>
@@ -88,7 +88,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="E13" authorId="0" shapeId="0" xr:uid="{5F9CCF78-5F65-427E-9141-163B695DF126}">
+    <comment ref="E16" authorId="0" shapeId="0" xr:uid="{5F9CCF78-5F65-427E-9141-163B695DF126}">
       <text>
         <r>
           <rPr>
@@ -112,7 +112,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G65" authorId="0" shapeId="0" xr:uid="{3283D6CB-61A1-4390-A688-5F4F500D8585}">
+    <comment ref="G68" authorId="0" shapeId="0" xr:uid="{3283D6CB-61A1-4390-A688-5F4F500D8585}">
       <text>
         <r>
           <rPr>
@@ -136,7 +136,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G68" authorId="0" shapeId="0" xr:uid="{C1521E49-0187-46FC-9D55-A1D99E904DBB}">
+    <comment ref="G71" authorId="0" shapeId="0" xr:uid="{C1521E49-0187-46FC-9D55-A1D99E904DBB}">
       <text>
         <r>
           <rPr>
@@ -160,7 +160,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="G71" authorId="0" shapeId="0" xr:uid="{6311CE01-3810-423E-933D-ACFFBD920BE0}">
+    <comment ref="G74" authorId="0" shapeId="0" xr:uid="{6311CE01-3810-423E-933D-ACFFBD920BE0}">
       <text>
         <r>
           <rPr>
@@ -189,7 +189,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="466" uniqueCount="304">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="478" uniqueCount="314">
   <si>
     <t>Epic #</t>
   </si>
@@ -3341,8 +3341,1090 @@
     </r>
   </si>
   <si>
-    <r>
-      <t xml:space="preserve">1. All screenings with a Completed status must be displayed under the </t>
+    <t>Specific Conditions</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">tap </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Specific Conditions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> button from the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Available Health Checks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> screen in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t>Screenings</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </rPr>
+      <t xml:space="preserve"> tab</t>
+    </r>
+  </si>
+  <si>
+    <t>I can create a custom health check for conditions specifc to me</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">enter my condition's </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Name</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Monitioring Type</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Screening, Imaging, Blood Test etc.), </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>How Often</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (Doctor visit frequency) and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Doctor or Care Provider</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (name)</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Tapping </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Specific Conditions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> button must open the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Add Specific Conditions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> bottom sheet.
+2. The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Specific Conditions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab/button must display this sub text: "Uncommon, rare and specific conditions to me"
+3. The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Specific Conditions</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab/button must display an add icon (+) to indicate that it is a tappable action component.</t>
+    </r>
+  </si>
+  <si>
+    <t>I can save my specific condition in the system</t>
+  </si>
+  <si>
+    <t>I can edit if I made mistake or continue to final submission</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Confirm Adding Condtion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> modal must pop up upon tapping of the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Save</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> button, in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Add Specific Condition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> bottom sheet.
+2. The </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Confirm Adding Condtion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> modal must contain the following:
+- Summary of the data entered in </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Add Specific Condition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> bottom sheet
+- Primary Button: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Submit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+- Secondary Button: </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Back to Editing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">
+3. Tapping the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Submit</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> button must close the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Confirm Adding Condtion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> modal, add the condition to system database and to the user's screen.
+4. Tapping the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Back to Editing</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> button must close the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Confirm Adding Condtion</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> modal and keep user on </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Add Specific Condition</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> bottom sheet, where they could edit the data.</t>
+    </r>
+  </si>
+  <si>
+    <t>view a summary of the specific condition data I entered and choose between editing or continuing with it</t>
+  </si>
+  <si>
+    <t>Log the screening result for my specific condition</t>
+  </si>
+  <si>
+    <t>I can track my future screenings and have my health record in the app</t>
+  </si>
+  <si>
+    <r>
+      <t>View my specific condition listed as an interactive screening card in the</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> Available Health Checks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> list, inside </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Screenings - Health Checks tab</t>
+    </r>
+  </si>
+  <si>
+    <t>I can record my screening results if I had that screening or book an appointment if I had not.</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. When a user successfully saves a screening result via the data entry form, the corresponding card must immediately transition from the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Upcoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> or </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab to the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Completed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab.
+2. The item count badges for all 3 tabs (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Upcoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Completed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) in the top navigation bar must dynamically increment/decrement to reflect the updated state.
+3. The system must recalculate the next due date in the background and schedule the next cycle's card under Upcoming or Due according to the clinical guideline interval (e.g. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Every 2 Years</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Every 3 Months</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> etc.).</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">have my screening cards to automatically update their status and move between </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Upcoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Completed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tabs after I log a result or book an appointment by the system</t>
+    </r>
+  </si>
+  <si>
+    <t>view the screenings within each tab to be sorted in a chronological order</t>
+  </si>
+  <si>
+    <t>I can easily prioritize my most urgent health tasks</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. Under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Upcoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (due date between 0 to 90 days) tab, screening cards must be sorted chronologically </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ascending</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> by due date (earliest upcoming screening displayed at the top of the list).
+2. Under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Overdue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (screening date missed) screenings must always be pinned to the top of the list (sorted by </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>most overdue first</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">), followed by standard </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (due date between 91 days to 365 days) screenings sorted chronologically </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>ascending</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> by due date.
+3. Under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Completed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab, screening cards must be sorted chronologically </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>descending</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> by completion date (most recently completed screening displayed at the top of the list).</t>
+    </r>
+  </si>
+  <si>
+    <t>I can manually sync my schedule and still view my health tasks when offline</t>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">pull-to-refresh </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Your Health Overview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> screen and see clear loading, offline, and error states</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. All screenings </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>due in 90 days or less</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (0 to 90 days) must be displayed under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Upcoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab.
+2. Each upcoming screening must display its name and date.
+3. The logged-in user must be able to tap/press any upcoming screening from the list.
+4. Only screenings associated with the logged-in user's account must be displayed under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Upcoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab.
+5. If no upcoming screenings exist, an appropriate message: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>You don't have any upcoming screenings.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>" must be displayed.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. All screenings </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>due in 365 days or less</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> and </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>not less than 90 days</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (91 to 365 days), must be displayed under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab.
+2. All </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>overdue</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> screenings (screening date missed), must be displayed under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab distinctively,highlighted in red color.
+3. Each due and overdue screening must display its screening name and date.
+3. The logged-in user must be able to tap/press any due or overdue screening.
+4. Only screenings associated with the logged-in user's account must be displayed under the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> tab.
+5. If no due or overdue screenings exist, an appropriate message: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>You don't have any due screenings.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>" must be displayed.</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t xml:space="preserve">1. All screenings with a Completed status (record entered in the forms and saved) must be displayed under the </t>
     </r>
     <r>
       <rPr>
@@ -3402,685 +4484,21 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">1. All screenings </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>due in 365 days or less</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>not less than 90 days</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, must be displayed under the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Due</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> tab.
-2. All </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>overdue</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> screenings (screening date missed), must be displayed under the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Due</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> tab distinctively,highlighted in red color.
-3. Each due and overdue screening must display its screening name and date.
-3. The logged-in user must be able to tap/press any due or overdue screening.
-4. Only screenings associated with the logged-in user's account must be displayed under the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Due</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> tab.
-5. If no due or overdue screenings exist, an appropriate message: "</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>You don't have any due screenings.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>" must be displayed.</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. All screenings </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>due in 90 days or less</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> must be displayed under the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Upcoming</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> tab.
-2. Each upcoming screening must display its name and date.
-3. The logged-in user must be able to tap/press any upcoming screening from the list.
-4. Only screenings associated with the logged-in user's account must be displayed under the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Upcoming</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> tab.
-5. If no upcoming screenings exist, an appropriate message: "</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>You don't have any upcoming screenings.</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>" must be displayed.</t>
-    </r>
-  </si>
-  <si>
-    <t>Specific Conditions</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">tap </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Specific Conditions</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> button from the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Available Health Checks</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> screen in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t>Screenings</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <color theme="1"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </rPr>
-      <t xml:space="preserve"> tab</t>
-    </r>
-  </si>
-  <si>
-    <t>I can create a custom health check for conditions specifc to me</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">enter my condition's </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Name</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">, </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Monitioring Type</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (Screening, Imaging, Blood Test etc.), </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>How Often</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (Doctor visit frequency) and </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Doctor or Care Provider</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> (name)</t>
-    </r>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. Tapping </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Specific Conditions</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> button must open the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Add Specific Conditions</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> bottom sheet.
-2. The </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Specific Conditions</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> tab/button must display this sub text: "Uncommon, rare and specific conditions to me"
-3. The </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Specific Conditions</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> tab/button must display an add icon (+) to indicate that it is a tappable action component.</t>
-    </r>
-  </si>
-  <si>
-    <t>I can save my specific condition in the system</t>
-  </si>
-  <si>
-    <t>I can edit if I made mistake or continue to final submission</t>
-  </si>
-  <si>
-    <r>
-      <t xml:space="preserve">1. The </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Confirm Adding Condtion</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> modal must pop up upon tapping of the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Save</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> button, in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Add Specific Condition</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> bottom sheet.
-2. The </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Confirm Adding Condtion</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> modal must contain the following:
-- Summary of the data entered in </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Add Specific Condition</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> bottom sheet
-- Primary Button: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Submit</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-- Secondary Button: </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Back to Editing</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">
-3. Tapping the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Submit</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> button must close the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Confirm Adding Condtion</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> modal, add the condition to system database and to the user's screen.
-4. Tapping the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Back to Editing</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> button must close the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Confirm Adding Condtion</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> modal and keep user on </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Add Specific Condition</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> bottom sheet, where they could edit the data.</t>
-    </r>
-  </si>
-  <si>
-    <t>view a summary of the specific condition data I entered and choose between editing or continuing with it</t>
-  </si>
-  <si>
-    <r>
-      <t>View my specific condition listed as an interactive screening in the</t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> Available Health Checks</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> list, inside </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Screenings - Health Checks tab</t>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Your Health Overview</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> screen always reflects my current health schedule without requiring a manual app restart.</t>
     </r>
   </si>
   <si>
@@ -4281,7 +4699,7 @@
         <family val="2"/>
       </rPr>
       <t xml:space="preserve">)
-- Dropdown (Days, Weeks, Months, Years)
+- Dropdown (Days, Months, Years)
 4. The </t>
     </r>
     <r>
@@ -4304,24 +4722,24 @@
   </si>
   <si>
     <r>
-      <t xml:space="preserve">1. The specifc condition must be visually different than the default screenings in the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>Avalaibvle Health checks</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> list, to indicated it was a custom addition, exclusive to the user who added it
+      <t xml:space="preserve">1. The specifc condition must be visually different (refer to wireframe) than the default screenings in the </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Avalaible Health checks</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> list, to indicate it was a custom addition, exclusive to the user who added it but behave exactly like the default screening cards.
 2. The specific condition card must display the </t>
     </r>
     <r>
@@ -4436,12 +4854,6 @@
     </r>
   </si>
   <si>
-    <t>Log the screening result for my specific condition</t>
-  </si>
-  <si>
-    <t>I can track my future screenings and have my health record in the app</t>
-  </si>
-  <si>
     <r>
       <t xml:space="preserve">1. The data entry form </t>
     </r>
@@ -4627,32 +5039,181 @@
         <rFont val="Calibri"/>
         <family val="2"/>
       </rPr>
-      <t>current date</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve">" on the </t>
-    </r>
-    <r>
-      <rPr>
-        <b/>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t>specific condition</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="11"/>
-        <rFont val="Calibri"/>
-        <family val="2"/>
-      </rPr>
-      <t xml:space="preserve"> screening card.</t>
+      <t>Last: [Today's Logging Date]</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>" (e.g., Last: 02 Aug 2026) on the specific condition screening card."</t>
+    </r>
+  </si>
+  <si>
+    <r>
+      <t>1. The user must be able to perform a downward swipe gesture (Pull-to-Refresh) on the screening list to trigger a background re-fetch of their screening schedule, in any tab (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Upcoming</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Due</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">, </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Completed</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>)
+2. While data is being fetched on initial screen load, lightweight placeholder cards (</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>skeleton loaders</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">) must be displayed.
+3. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Offline Refresh</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (With Cached Data): If the user pulls to refresh while offline and cached schedule data exists:
+   - The previously cached screening cards must remain visible on screen without disruption.
+   - The refresh spinner must dismiss within 3 seconds.
+   - A temporary, non-intrusive toast/snackbar must display: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>No internet connection. Showing your last saved schedule.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">"
+4. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Offline Cold Start</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve"> (No Cached Data): If the user opens the screen offline with zero cached data available:
+   - An offline empty-state card must be displayed with the text: "</t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>You're offline. Connect to the internet to load your screenings.</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">" and an interactive [Retry] button.
+5. </t>
+    </r>
+    <r>
+      <rPr>
+        <b/>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>Error Handling</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+      </rPr>
+      <t>: If the server returns an error (e.g., 500 Internal Server Error), the app must not crash; it must retain cached data and display a retryable error banner.</t>
     </r>
   </si>
 </sst>
@@ -4660,7 +5221,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="16" x14ac:knownFonts="1">
+  <fonts count="17" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -4766,6 +5327,13 @@
     </font>
     <font>
       <sz val="11"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="22"/>
+      <color rgb="FFFF0000"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -4960,7 +5528,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="81">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5109,47 +5677,26 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="10" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -5187,19 +5734,55 @@
     <xf numFmtId="0" fontId="14" fillId="5" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="8" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="7" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="5" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="14" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="14" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5418,7 +6001,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:L88"/>
+  <dimension ref="A1:L91"/>
   <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="5.88671875" style="2" bestFit="1" customWidth="1"/>
@@ -5435,34 +6018,34 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="75" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="56" t="s">
+      <c r="B1" s="75" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="56" t="s">
+      <c r="C1" s="75" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="56" t="s">
+      <c r="D1" s="75" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="57"/>
-      <c r="F1" s="57"/>
-      <c r="G1" s="61" t="s">
+      <c r="E1" s="56"/>
+      <c r="F1" s="56"/>
+      <c r="G1" s="79" t="s">
         <v>4</v>
       </c>
-      <c r="H1" s="56" t="s">
+      <c r="H1" s="75" t="s">
         <v>5</v>
       </c>
-      <c r="I1" s="56" t="s">
+      <c r="I1" s="75" t="s">
         <v>6</v>
       </c>
     </row>
     <row r="2" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A2" s="57"/>
-      <c r="B2" s="57"/>
-      <c r="C2" s="57"/>
+      <c r="A2" s="56"/>
+      <c r="B2" s="56"/>
+      <c r="C2" s="56"/>
       <c r="D2" s="4" t="s">
         <v>7</v>
       </c>
@@ -5472,15 +6055,15 @@
       <c r="F2" s="4" t="s">
         <v>9</v>
       </c>
-      <c r="G2" s="61"/>
-      <c r="H2" s="57"/>
-      <c r="I2" s="57"/>
-    </row>
-    <row r="3" spans="1:9" s="5" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A3" s="62">
+      <c r="G2" s="79"/>
+      <c r="H2" s="56"/>
+      <c r="I2" s="56"/>
+    </row>
+    <row r="3" spans="1:9" s="5" customFormat="1" ht="108" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A3" s="80">
         <v>1</v>
       </c>
-      <c r="B3" s="62" t="s">
+      <c r="B3" s="82" t="s">
         <v>10</v>
       </c>
       <c r="C3" s="16">
@@ -5505,9 +6088,9 @@
         <v>12</v>
       </c>
     </row>
-    <row r="4" spans="1:9" s="6" customFormat="1" ht="100.8" x14ac:dyDescent="0.3">
-      <c r="A4" s="62"/>
-      <c r="B4" s="62"/>
+    <row r="4" spans="1:9" s="6" customFormat="1" ht="124.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A4" s="80"/>
+      <c r="B4" s="83"/>
       <c r="C4" s="16">
         <v>1.2</v>
       </c>
@@ -5521,14 +6104,14 @@
         <v>281</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>288</v>
+        <v>306</v>
       </c>
       <c r="H4" s="16"/>
       <c r="I4" s="16"/>
     </row>
-    <row r="5" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A5" s="62"/>
-      <c r="B5" s="62"/>
+    <row r="5" spans="1:9" s="6" customFormat="1" ht="160.80000000000001" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A5" s="80"/>
+      <c r="B5" s="83"/>
       <c r="C5" s="16">
         <v>1.3</v>
       </c>
@@ -5542,14 +6125,14 @@
         <v>282</v>
       </c>
       <c r="G5" s="17" t="s">
-        <v>287</v>
+        <v>307</v>
       </c>
       <c r="H5" s="16"/>
       <c r="I5" s="16"/>
     </row>
     <row r="6" spans="1:9" s="6" customFormat="1" ht="154.19999999999999" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A6" s="62"/>
-      <c r="B6" s="62"/>
+      <c r="A6" s="80"/>
+      <c r="B6" s="83"/>
       <c r="C6" s="16">
         <v>1.4</v>
       </c>
@@ -5563,14 +6146,14 @@
         <v>263</v>
       </c>
       <c r="G6" s="17" t="s">
-        <v>286</v>
+        <v>308</v>
       </c>
       <c r="H6" s="16"/>
       <c r="I6" s="16"/>
     </row>
     <row r="7" spans="1:9" s="6" customFormat="1" ht="115.2" x14ac:dyDescent="0.3">
-      <c r="A7" s="62"/>
-      <c r="B7" s="62"/>
+      <c r="A7" s="80"/>
+      <c r="B7" s="83"/>
       <c r="C7" s="16">
         <v>1.5</v>
       </c>
@@ -5581,7 +6164,7 @@
         <v>283</v>
       </c>
       <c r="F7" s="16" t="s">
-        <v>284</v>
+        <v>298</v>
       </c>
       <c r="G7" s="17" t="s">
         <v>285</v>
@@ -5589,478 +6172,466 @@
       <c r="H7" s="16"/>
       <c r="I7" s="16"/>
     </row>
-    <row r="8" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A8" s="58">
+    <row r="8" spans="1:9" s="6" customFormat="1" ht="124.2" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A8" s="81"/>
+      <c r="B8" s="83"/>
+      <c r="C8" s="16">
+        <v>1.6</v>
+      </c>
+      <c r="D8" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="E8" s="16" t="s">
+        <v>300</v>
+      </c>
+      <c r="F8" s="16" t="s">
+        <v>309</v>
+      </c>
+      <c r="G8" s="17" t="s">
+        <v>299</v>
+      </c>
+      <c r="H8" s="16"/>
+      <c r="I8" s="16"/>
+    </row>
+    <row r="9" spans="1:9" s="6" customFormat="1" ht="152.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="81"/>
+      <c r="B9" s="83"/>
+      <c r="C9" s="16">
+        <v>1.7</v>
+      </c>
+      <c r="D9" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="E9" s="16" t="s">
+        <v>301</v>
+      </c>
+      <c r="F9" s="16" t="s">
+        <v>302</v>
+      </c>
+      <c r="G9" s="17" t="s">
+        <v>303</v>
+      </c>
+      <c r="H9" s="16"/>
+      <c r="I9" s="16"/>
+    </row>
+    <row r="10" spans="1:9" s="6" customFormat="1" ht="295.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="81"/>
+      <c r="B10" s="84"/>
+      <c r="C10" s="16">
+        <v>1.8</v>
+      </c>
+      <c r="D10" s="16" t="s">
+        <v>145</v>
+      </c>
+      <c r="E10" s="16" t="s">
+        <v>305</v>
+      </c>
+      <c r="F10" s="16" t="s">
+        <v>304</v>
+      </c>
+      <c r="G10" s="17" t="s">
+        <v>313</v>
+      </c>
+      <c r="H10" s="16"/>
+      <c r="I10" s="85"/>
+    </row>
+    <row r="11" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="76">
         <v>5</v>
       </c>
-      <c r="B8" s="58" t="s">
+      <c r="B11" s="76" t="s">
         <v>13</v>
       </c>
-      <c r="C8" s="18">
+      <c r="C11" s="18">
         <v>5.0999999999999996</v>
       </c>
-      <c r="D8" s="18" t="s">
+      <c r="D11" s="18" t="s">
         <v>14</v>
       </c>
-      <c r="E8" s="18" t="s">
+      <c r="E11" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F8" s="18" t="s">
+      <c r="F11" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G8" s="19" t="s">
+      <c r="G11" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H8" s="20" t="s">
+      <c r="H11" s="20" t="s">
         <v>18</v>
       </c>
-      <c r="I8" s="18" t="s">
+      <c r="I11" s="18" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="9" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A9" s="59"/>
-      <c r="B9" s="59"/>
-      <c r="C9" s="18">
+    <row r="12" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A12" s="77"/>
+      <c r="B12" s="77"/>
+      <c r="C12" s="18">
         <v>5.2</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D12" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E12" s="18" t="s">
         <v>15</v>
       </c>
-      <c r="F9" s="18" t="s">
+      <c r="F12" s="18" t="s">
         <v>16</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="G12" s="19" t="s">
         <v>17</v>
       </c>
-      <c r="H9" s="20"/>
-      <c r="I9" s="18"/>
-    </row>
-    <row r="10" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A10" s="59"/>
-      <c r="B10" s="59"/>
-      <c r="C10" s="18">
+      <c r="H12" s="20"/>
+      <c r="I12" s="18"/>
+    </row>
+    <row r="13" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A13" s="77"/>
+      <c r="B13" s="77"/>
+      <c r="C13" s="18">
         <v>5.3</v>
       </c>
-      <c r="D10" s="18" t="s">
+      <c r="D13" s="18" t="s">
         <v>21</v>
       </c>
-      <c r="E10" s="18" t="s">
+      <c r="E13" s="18" t="s">
         <v>22</v>
       </c>
-      <c r="F10" s="18" t="s">
+      <c r="F13" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="G10" s="19" t="s">
+      <c r="G13" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="H10" s="20"/>
-      <c r="I10" s="18"/>
-    </row>
-    <row r="11" spans="1:9" s="14" customFormat="1" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A11" s="59"/>
-      <c r="B11" s="59"/>
-      <c r="C11" s="21">
+      <c r="H13" s="20"/>
+      <c r="I13" s="18"/>
+    </row>
+    <row r="14" spans="1:9" s="14" customFormat="1" ht="230.4" x14ac:dyDescent="0.3">
+      <c r="A14" s="77"/>
+      <c r="B14" s="77"/>
+      <c r="C14" s="21">
         <v>5.4</v>
       </c>
-      <c r="D11" s="21" t="s">
+      <c r="D14" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="E11" s="21" t="s">
+      <c r="E14" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="F11" s="21" t="s">
+      <c r="F14" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="G11" s="22" t="s">
+      <c r="G14" s="22" t="s">
         <v>153</v>
       </c>
-      <c r="H11" s="23"/>
-      <c r="I11" s="21"/>
-    </row>
-    <row r="12" spans="1:9" s="14" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A12" s="60"/>
-      <c r="B12" s="60"/>
-      <c r="C12" s="21">
+      <c r="H14" s="23"/>
+      <c r="I14" s="21"/>
+    </row>
+    <row r="15" spans="1:9" s="14" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A15" s="78"/>
+      <c r="B15" s="78"/>
+      <c r="C15" s="21">
         <v>5.5</v>
       </c>
-      <c r="D12" s="21" t="s">
+      <c r="D15" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="E12" s="21" t="s">
+      <c r="E15" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="F12" s="21" t="s">
+      <c r="F15" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="G12" s="22" t="s">
+      <c r="G15" s="22" t="s">
         <v>147</v>
       </c>
-      <c r="H12" s="23"/>
-      <c r="I12" s="21"/>
-    </row>
-    <row r="13" spans="1:9" s="14" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A13" s="50">
+      <c r="H15" s="23"/>
+      <c r="I15" s="21"/>
+    </row>
+    <row r="16" spans="1:9" s="14" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A16" s="69">
         <v>6</v>
       </c>
-      <c r="B13" s="50" t="s">
+      <c r="B16" s="69" t="s">
         <v>25</v>
       </c>
-      <c r="C13" s="21">
+      <c r="C16" s="21">
         <v>6.1</v>
       </c>
-      <c r="D13" s="21" t="s">
+      <c r="D16" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="E13" s="21" t="s">
+      <c r="E16" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="F13" s="21" t="s">
+      <c r="F16" s="21" t="s">
         <v>28</v>
       </c>
-      <c r="G13" s="22" t="s">
+      <c r="G16" s="22" t="s">
         <v>29</v>
       </c>
-      <c r="H13" s="23" t="s">
+      <c r="H16" s="23" t="s">
         <v>30</v>
       </c>
-      <c r="I13" s="21" t="s">
+      <c r="I16" s="21" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="14" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A14" s="51"/>
-      <c r="B14" s="51"/>
-      <c r="C14" s="24">
+    <row r="17" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
+      <c r="A17" s="70"/>
+      <c r="B17" s="70"/>
+      <c r="C17" s="24">
         <v>6.2</v>
       </c>
-      <c r="D14" s="24" t="s">
+      <c r="D17" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E14" s="24" t="s">
+      <c r="E17" s="24" t="s">
         <v>155</v>
       </c>
-      <c r="F14" s="24" t="s">
+      <c r="F17" s="24" t="s">
         <v>154</v>
       </c>
-      <c r="G14" s="25" t="s">
+      <c r="G17" s="25" t="s">
         <v>156</v>
       </c>
-      <c r="H14" s="26"/>
-      <c r="I14" s="24"/>
-    </row>
-    <row r="15" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A15" s="51"/>
-      <c r="B15" s="51"/>
-      <c r="C15" s="24">
+      <c r="H17" s="26"/>
+      <c r="I17" s="24"/>
+    </row>
+    <row r="18" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A18" s="70"/>
+      <c r="B18" s="70"/>
+      <c r="C18" s="24">
         <v>6.3</v>
       </c>
-      <c r="D15" s="24" t="s">
+      <c r="D18" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E15" s="24" t="s">
+      <c r="E18" s="24" t="s">
         <v>32</v>
       </c>
-      <c r="F15" s="24" t="s">
+      <c r="F18" s="24" t="s">
         <v>33</v>
       </c>
-      <c r="G15" s="25" t="s">
+      <c r="G18" s="25" t="s">
         <v>34</v>
       </c>
-      <c r="H15" s="26"/>
-      <c r="I15" s="24"/>
-    </row>
-    <row r="16" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A16" s="51"/>
-      <c r="B16" s="52"/>
-      <c r="C16" s="27">
+      <c r="H18" s="26"/>
+      <c r="I18" s="24"/>
+    </row>
+    <row r="19" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A19" s="70"/>
+      <c r="B19" s="71"/>
+      <c r="C19" s="27">
         <v>6.4</v>
       </c>
-      <c r="D16" s="24" t="s">
+      <c r="D19" s="24" t="s">
         <v>26</v>
       </c>
-      <c r="E16" s="24" t="s">
+      <c r="E19" s="24" t="s">
         <v>35</v>
       </c>
-      <c r="F16" s="24" t="s">
+      <c r="F19" s="24" t="s">
         <v>36</v>
       </c>
-      <c r="G16" s="25" t="s">
+      <c r="G19" s="25" t="s">
         <v>37</v>
       </c>
-      <c r="H16" s="26" t="s">
+      <c r="H19" s="26" t="s">
         <v>30</v>
       </c>
-      <c r="I16" s="24" t="s">
+      <c r="I19" s="24" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="17" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
-      <c r="A17" s="53">
+    <row r="20" spans="1:9" s="6" customFormat="1" ht="144" x14ac:dyDescent="0.3">
+      <c r="A20" s="72">
         <v>7</v>
       </c>
-      <c r="B17" s="50" t="s">
+      <c r="B20" s="69" t="s">
         <v>38</v>
       </c>
-      <c r="C17" s="24">
+      <c r="C20" s="24">
         <v>7.1</v>
-      </c>
-      <c r="D17" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="E17" s="24" t="s">
-        <v>40</v>
-      </c>
-      <c r="F17" s="24" t="s">
-        <v>41</v>
-      </c>
-      <c r="G17" s="25" t="s">
-        <v>42</v>
-      </c>
-      <c r="H17" s="26" t="s">
-        <v>30</v>
-      </c>
-      <c r="I17" s="24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="18" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
-      <c r="A18" s="54"/>
-      <c r="B18" s="51"/>
-      <c r="C18" s="24">
-        <v>7.2</v>
-      </c>
-      <c r="D18" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="E18" s="24" t="s">
-        <v>43</v>
-      </c>
-      <c r="F18" s="24" t="s">
-        <v>44</v>
-      </c>
-      <c r="G18" s="25" t="s">
-        <v>45</v>
-      </c>
-      <c r="H18" s="26"/>
-      <c r="I18" s="24" t="s">
-        <v>31</v>
-      </c>
-    </row>
-    <row r="19" spans="1:9" s="6" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A19" s="54"/>
-      <c r="B19" s="51"/>
-      <c r="C19" s="24">
-        <v>7.3</v>
-      </c>
-      <c r="D19" s="24" t="s">
-        <v>39</v>
-      </c>
-      <c r="E19" s="24" t="s">
-        <v>142</v>
-      </c>
-      <c r="F19" s="24" t="s">
-        <v>46</v>
-      </c>
-      <c r="G19" s="25" t="s">
-        <v>47</v>
-      </c>
-      <c r="H19" s="26"/>
-      <c r="I19" s="24"/>
-    </row>
-    <row r="20" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
-      <c r="A20" s="55"/>
-      <c r="B20" s="52"/>
-      <c r="C20" s="24">
-        <v>7.4</v>
       </c>
       <c r="D20" s="24" t="s">
         <v>39</v>
       </c>
       <c r="E20" s="24" t="s">
+        <v>40</v>
+      </c>
+      <c r="F20" s="24" t="s">
+        <v>41</v>
+      </c>
+      <c r="G20" s="25" t="s">
+        <v>42</v>
+      </c>
+      <c r="H20" s="26" t="s">
+        <v>30</v>
+      </c>
+      <c r="I20" s="24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="21" spans="1:9" s="6" customFormat="1" ht="72" x14ac:dyDescent="0.3">
+      <c r="A21" s="73"/>
+      <c r="B21" s="70"/>
+      <c r="C21" s="24">
+        <v>7.2</v>
+      </c>
+      <c r="D21" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="E21" s="24" t="s">
+        <v>43</v>
+      </c>
+      <c r="F21" s="24" t="s">
+        <v>44</v>
+      </c>
+      <c r="G21" s="25" t="s">
+        <v>45</v>
+      </c>
+      <c r="H21" s="26"/>
+      <c r="I21" s="24" t="s">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" s="6" customFormat="1" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A22" s="73"/>
+      <c r="B22" s="70"/>
+      <c r="C22" s="24">
+        <v>7.3</v>
+      </c>
+      <c r="D22" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="E22" s="24" t="s">
+        <v>142</v>
+      </c>
+      <c r="F22" s="24" t="s">
+        <v>46</v>
+      </c>
+      <c r="G22" s="25" t="s">
+        <v>47</v>
+      </c>
+      <c r="H22" s="26"/>
+      <c r="I22" s="24"/>
+    </row>
+    <row r="23" spans="1:9" s="6" customFormat="1" ht="172.8" x14ac:dyDescent="0.3">
+      <c r="A23" s="74"/>
+      <c r="B23" s="71"/>
+      <c r="C23" s="24">
+        <v>7.4</v>
+      </c>
+      <c r="D23" s="24" t="s">
+        <v>39</v>
+      </c>
+      <c r="E23" s="24" t="s">
         <v>143</v>
       </c>
-      <c r="F20" s="24" t="s">
+      <c r="F23" s="24" t="s">
         <v>48</v>
       </c>
-      <c r="G20" s="25" t="s">
+      <c r="G23" s="25" t="s">
         <v>49</v>
       </c>
-      <c r="H20" s="26"/>
-      <c r="I20" s="24"/>
-    </row>
-    <row r="21" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A21" s="78">
+      <c r="H23" s="26"/>
+      <c r="I23" s="24"/>
+    </row>
+    <row r="24" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A24" s="52">
         <v>8</v>
       </c>
-      <c r="B21" s="78" t="s">
+      <c r="B24" s="52" t="s">
         <v>50</v>
       </c>
-      <c r="C21" s="28">
+      <c r="C24" s="28">
         <v>9.1999999999999993</v>
       </c>
-      <c r="D21" s="28" t="s">
+      <c r="D24" s="28" t="s">
         <v>51</v>
       </c>
-      <c r="E21" s="28" t="s">
+      <c r="E24" s="28" t="s">
         <v>52</v>
       </c>
-      <c r="F21" s="28" t="s">
+      <c r="F24" s="28" t="s">
         <v>53</v>
       </c>
-      <c r="G21" s="29" t="s">
+      <c r="G24" s="29" t="s">
         <v>54</v>
       </c>
-      <c r="H21" s="28"/>
-      <c r="I21" s="28" t="s">
+      <c r="H24" s="28"/>
+      <c r="I24" s="28" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="22" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A22" s="79"/>
-      <c r="B22" s="79"/>
-      <c r="C22" s="28">
+    <row r="25" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A25" s="53"/>
+      <c r="B25" s="53"/>
+      <c r="C25" s="28">
         <v>9.3000000000000007</v>
       </c>
-      <c r="D22" s="28" t="s">
+      <c r="D25" s="28" t="s">
         <v>56</v>
       </c>
-      <c r="E22" s="28" t="s">
+      <c r="E25" s="28" t="s">
         <v>57</v>
       </c>
-      <c r="F22" s="28" t="s">
+      <c r="F25" s="28" t="s">
         <v>264</v>
       </c>
-      <c r="G22" s="29" t="s">
+      <c r="G25" s="29" t="s">
         <v>265</v>
       </c>
-      <c r="H22" s="28"/>
-      <c r="I22" s="28" t="s">
+      <c r="H25" s="28"/>
+      <c r="I25" s="28" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="23" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A23" s="80"/>
-      <c r="B23" s="80"/>
-      <c r="C23" s="28">
+    <row r="26" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A26" s="54"/>
+      <c r="B26" s="54"/>
+      <c r="C26" s="28">
         <v>9.4</v>
       </c>
-      <c r="D23" s="28" t="s">
+      <c r="D26" s="28" t="s">
         <v>58</v>
       </c>
-      <c r="E23" s="28" t="s">
+      <c r="E26" s="28" t="s">
         <v>266</v>
       </c>
-      <c r="F23" s="28" t="s">
+      <c r="F26" s="28" t="s">
         <v>59</v>
       </c>
-      <c r="G23" s="29" t="s">
+      <c r="G26" s="29" t="s">
         <v>267</v>
       </c>
-      <c r="H23" s="28"/>
-      <c r="I23" s="28" t="s">
+      <c r="H26" s="28"/>
+      <c r="I26" s="28" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="24" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A24" s="76">
+    <row r="27" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A27" s="50">
         <v>12</v>
       </c>
-      <c r="B24" s="76" t="s">
+      <c r="B27" s="50" t="s">
         <v>60</v>
       </c>
-      <c r="C24" s="31">
+      <c r="C27" s="31">
         <v>12.1</v>
-      </c>
-      <c r="D24" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="E24" s="31" t="s">
-        <v>62</v>
-      </c>
-      <c r="F24" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="G24" s="32" t="s">
-        <v>64</v>
-      </c>
-      <c r="H24" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="I24" s="31" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="25" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A25" s="76"/>
-      <c r="B25" s="76"/>
-      <c r="C25" s="31">
-        <v>12.2</v>
-      </c>
-      <c r="D25" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="E25" s="31" t="s">
-        <v>67</v>
-      </c>
-      <c r="F25" s="31" t="s">
-        <v>68</v>
-      </c>
-      <c r="G25" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="H25" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="I25" s="31" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="26" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A26" s="76"/>
-      <c r="B26" s="76"/>
-      <c r="C26" s="31">
-        <v>12.3</v>
-      </c>
-      <c r="D26" s="31" t="s">
-        <v>61</v>
-      </c>
-      <c r="E26" s="31" t="s">
-        <v>70</v>
-      </c>
-      <c r="F26" s="31" t="s">
-        <v>71</v>
-      </c>
-      <c r="G26" s="32" t="s">
-        <v>72</v>
-      </c>
-      <c r="H26" s="31" t="s">
-        <v>65</v>
-      </c>
-      <c r="I26" s="31" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="27" spans="1:9" s="6" customFormat="1" ht="123.6" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="76"/>
-      <c r="B27" s="76"/>
-      <c r="C27" s="31">
-        <v>12.4</v>
       </c>
       <c r="D27" s="31" t="s">
         <v>61</v>
       </c>
       <c r="E27" s="31" t="s">
-        <v>227</v>
+        <v>62</v>
       </c>
       <c r="F27" s="31" t="s">
-        <v>228</v>
+        <v>63</v>
       </c>
       <c r="G27" s="32" t="s">
-        <v>229</v>
+        <v>64</v>
       </c>
       <c r="H27" s="31" t="s">
         <v>65</v>
@@ -6069,23 +6640,23 @@
         <v>66</v>
       </c>
     </row>
-    <row r="28" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A28" s="76"/>
-      <c r="B28" s="76"/>
+    <row r="28" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A28" s="50"/>
+      <c r="B28" s="50"/>
       <c r="C28" s="31">
-        <v>12.5</v>
+        <v>12.2</v>
       </c>
       <c r="D28" s="31" t="s">
-        <v>73</v>
+        <v>61</v>
       </c>
       <c r="E28" s="31" t="s">
-        <v>74</v>
+        <v>67</v>
       </c>
       <c r="F28" s="31" t="s">
-        <v>226</v>
+        <v>68</v>
       </c>
       <c r="G28" s="32" t="s">
-        <v>75</v>
+        <v>69</v>
       </c>
       <c r="H28" s="31" t="s">
         <v>65</v>
@@ -6095,118 +6666,118 @@
       </c>
     </row>
     <row r="29" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A29" s="30"/>
-      <c r="B29" s="30"/>
-      <c r="C29" s="16">
+      <c r="A29" s="50"/>
+      <c r="B29" s="50"/>
+      <c r="C29" s="31">
+        <v>12.3</v>
+      </c>
+      <c r="D29" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E29" s="31" t="s">
+        <v>70</v>
+      </c>
+      <c r="F29" s="31" t="s">
+        <v>71</v>
+      </c>
+      <c r="G29" s="32" t="s">
+        <v>72</v>
+      </c>
+      <c r="H29" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="I29" s="31" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="30" spans="1:9" s="6" customFormat="1" ht="123.6" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="50"/>
+      <c r="B30" s="50"/>
+      <c r="C30" s="31">
+        <v>12.4</v>
+      </c>
+      <c r="D30" s="31" t="s">
+        <v>61</v>
+      </c>
+      <c r="E30" s="31" t="s">
+        <v>227</v>
+      </c>
+      <c r="F30" s="31" t="s">
+        <v>228</v>
+      </c>
+      <c r="G30" s="32" t="s">
+        <v>229</v>
+      </c>
+      <c r="H30" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="I30" s="31" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="31" spans="1:9" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A31" s="50"/>
+      <c r="B31" s="50"/>
+      <c r="C31" s="31">
+        <v>12.5</v>
+      </c>
+      <c r="D31" s="31" t="s">
+        <v>73</v>
+      </c>
+      <c r="E31" s="31" t="s">
+        <v>74</v>
+      </c>
+      <c r="F31" s="31" t="s">
+        <v>226</v>
+      </c>
+      <c r="G31" s="32" t="s">
+        <v>75</v>
+      </c>
+      <c r="H31" s="31" t="s">
+        <v>65</v>
+      </c>
+      <c r="I31" s="31" t="s">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A32" s="30"/>
+      <c r="B32" s="30"/>
+      <c r="C32" s="16">
         <v>12.6</v>
       </c>
-      <c r="D29" s="16" t="s">
+      <c r="D32" s="16" t="s">
         <v>127</v>
       </c>
-      <c r="E29" s="16" t="s">
+      <c r="E32" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="F29" s="16"/>
-      <c r="G29" s="17"/>
-      <c r="H29" s="33"/>
-      <c r="I29" s="34"/>
-    </row>
-    <row r="30" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A30" s="77">
+      <c r="F32" s="16"/>
+      <c r="G32" s="17"/>
+      <c r="H32" s="33"/>
+      <c r="I32" s="34"/>
+    </row>
+    <row r="33" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A33" s="51">
         <v>14</v>
       </c>
-      <c r="B30" s="77" t="s">
+      <c r="B33" s="51" t="s">
         <v>76</v>
       </c>
-      <c r="C30" s="35">
+      <c r="C33" s="35">
         <v>14.1</v>
-      </c>
-      <c r="D30" s="36" t="s">
-        <v>124</v>
-      </c>
-      <c r="E30" s="36" t="s">
-        <v>268</v>
-      </c>
-      <c r="F30" s="36" t="s">
-        <v>269</v>
-      </c>
-      <c r="G30" s="37" t="s">
-        <v>270</v>
-      </c>
-      <c r="H30" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="I30" s="35" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="31" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A31" s="77"/>
-      <c r="B31" s="77"/>
-      <c r="C31" s="35">
-        <v>14.2</v>
-      </c>
-      <c r="D31" s="36" t="s">
-        <v>124</v>
-      </c>
-      <c r="E31" s="36" t="s">
-        <v>209</v>
-      </c>
-      <c r="F31" s="36" t="s">
-        <v>271</v>
-      </c>
-      <c r="G31" s="37" t="s">
-        <v>272</v>
-      </c>
-      <c r="H31" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="I31" s="35" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="32" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A32" s="77"/>
-      <c r="B32" s="77"/>
-      <c r="C32" s="35">
-        <v>14.3</v>
-      </c>
-      <c r="D32" s="36" t="s">
-        <v>180</v>
-      </c>
-      <c r="E32" s="36" t="s">
-        <v>210</v>
-      </c>
-      <c r="F32" s="36" t="s">
-        <v>211</v>
-      </c>
-      <c r="G32" s="37" t="s">
-        <v>219</v>
-      </c>
-      <c r="H32" s="35" t="s">
-        <v>77</v>
-      </c>
-      <c r="I32" s="35" t="s">
-        <v>78</v>
-      </c>
-    </row>
-    <row r="33" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A33" s="77"/>
-      <c r="B33" s="77"/>
-      <c r="C33" s="35">
-        <v>14.4</v>
       </c>
       <c r="D33" s="36" t="s">
         <v>124</v>
       </c>
       <c r="E33" s="36" t="s">
-        <v>212</v>
+        <v>268</v>
       </c>
       <c r="F33" s="36" t="s">
-        <v>250</v>
+        <v>269</v>
       </c>
       <c r="G33" s="37" t="s">
-        <v>220</v>
+        <v>270</v>
       </c>
       <c r="H33" s="35" t="s">
         <v>77</v>
@@ -6216,22 +6787,22 @@
       </c>
     </row>
     <row r="34" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A34" s="77"/>
-      <c r="B34" s="77"/>
+      <c r="A34" s="51"/>
+      <c r="B34" s="51"/>
       <c r="C34" s="35">
-        <v>14.5</v>
+        <v>14.2</v>
       </c>
       <c r="D34" s="36" t="s">
         <v>124</v>
       </c>
       <c r="E34" s="36" t="s">
-        <v>273</v>
+        <v>209</v>
       </c>
       <c r="F34" s="36" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="G34" s="37" t="s">
-        <v>221</v>
+        <v>272</v>
       </c>
       <c r="H34" s="35" t="s">
         <v>77</v>
@@ -6241,22 +6812,22 @@
       </c>
     </row>
     <row r="35" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A35" s="77"/>
-      <c r="B35" s="77"/>
+      <c r="A35" s="51"/>
+      <c r="B35" s="51"/>
       <c r="C35" s="35">
-        <v>14.6</v>
+        <v>14.3</v>
       </c>
       <c r="D35" s="36" t="s">
-        <v>124</v>
+        <v>180</v>
       </c>
       <c r="E35" s="36" t="s">
-        <v>213</v>
+        <v>210</v>
       </c>
       <c r="F35" s="36" t="s">
-        <v>275</v>
+        <v>211</v>
       </c>
       <c r="G35" s="37" t="s">
-        <v>276</v>
+        <v>219</v>
       </c>
       <c r="H35" s="35" t="s">
         <v>77</v>
@@ -6265,23 +6836,23 @@
         <v>78</v>
       </c>
     </row>
-    <row r="36" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A36" s="77"/>
-      <c r="B36" s="77"/>
+    <row r="36" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A36" s="51"/>
+      <c r="B36" s="51"/>
       <c r="C36" s="35">
-        <v>14.7</v>
+        <v>14.4</v>
       </c>
       <c r="D36" s="36" t="s">
         <v>124</v>
       </c>
       <c r="E36" s="36" t="s">
-        <v>251</v>
+        <v>212</v>
       </c>
       <c r="F36" s="36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="G36" s="37" t="s">
-        <v>253</v>
+        <v>220</v>
       </c>
       <c r="H36" s="35" t="s">
         <v>77</v>
@@ -6291,97 +6862,97 @@
       </c>
     </row>
     <row r="37" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A37" s="77"/>
-      <c r="B37" s="77"/>
+      <c r="A37" s="51"/>
+      <c r="B37" s="51"/>
       <c r="C37" s="35">
-        <v>14.8</v>
+        <v>14.5</v>
       </c>
       <c r="D37" s="36" t="s">
         <v>124</v>
       </c>
       <c r="E37" s="36" t="s">
-        <v>214</v>
+        <v>273</v>
       </c>
       <c r="F37" s="36" t="s">
-        <v>215</v>
+        <v>274</v>
       </c>
       <c r="G37" s="37" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="H37" s="35" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I37" s="35" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="38" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A38" s="77"/>
-      <c r="B38" s="77"/>
+      <c r="A38" s="51"/>
+      <c r="B38" s="51"/>
       <c r="C38" s="35">
-        <v>14.9</v>
+        <v>14.6</v>
       </c>
       <c r="D38" s="36" t="s">
         <v>124</v>
       </c>
       <c r="E38" s="36" t="s">
-        <v>216</v>
+        <v>213</v>
       </c>
       <c r="F38" s="36" t="s">
-        <v>254</v>
+        <v>275</v>
       </c>
       <c r="G38" s="37" t="s">
-        <v>223</v>
+        <v>276</v>
       </c>
       <c r="H38" s="35" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I38" s="35" t="s">
         <v>78</v>
       </c>
     </row>
-    <row r="39" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A39" s="77"/>
-      <c r="B39" s="77"/>
+    <row r="39" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A39" s="51"/>
+      <c r="B39" s="51"/>
       <c r="C39" s="35">
-        <v>14.1</v>
+        <v>14.7</v>
       </c>
       <c r="D39" s="36" t="s">
         <v>124</v>
       </c>
       <c r="E39" s="36" t="s">
-        <v>217</v>
+        <v>251</v>
       </c>
       <c r="F39" s="36" t="s">
-        <v>255</v>
+        <v>252</v>
       </c>
       <c r="G39" s="37" t="s">
-        <v>256</v>
+        <v>253</v>
       </c>
       <c r="H39" s="35" t="s">
-        <v>79</v>
+        <v>77</v>
       </c>
       <c r="I39" s="35" t="s">
         <v>78</v>
       </c>
     </row>
     <row r="40" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A40" s="77"/>
-      <c r="B40" s="77"/>
+      <c r="A40" s="51"/>
+      <c r="B40" s="51"/>
       <c r="C40" s="35">
-        <v>14.11</v>
+        <v>14.8</v>
       </c>
       <c r="D40" s="36" t="s">
         <v>124</v>
       </c>
       <c r="E40" s="36" t="s">
-        <v>218</v>
+        <v>214</v>
       </c>
       <c r="F40" s="36" t="s">
-        <v>277</v>
+        <v>215</v>
       </c>
       <c r="G40" s="37" t="s">
-        <v>257</v>
+        <v>222</v>
       </c>
       <c r="H40" s="35" t="s">
         <v>79</v>
@@ -6390,127 +6961,127 @@
         <v>78</v>
       </c>
     </row>
-    <row r="41" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A41" s="63">
+    <row r="41" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A41" s="51"/>
+      <c r="B41" s="51"/>
+      <c r="C41" s="35">
+        <v>14.9</v>
+      </c>
+      <c r="D41" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="E41" s="36" t="s">
+        <v>216</v>
+      </c>
+      <c r="F41" s="36" t="s">
+        <v>254</v>
+      </c>
+      <c r="G41" s="37" t="s">
+        <v>223</v>
+      </c>
+      <c r="H41" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="I41" s="35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="42" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A42" s="51"/>
+      <c r="B42" s="51"/>
+      <c r="C42" s="35">
+        <v>14.1</v>
+      </c>
+      <c r="D42" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="E42" s="36" t="s">
+        <v>217</v>
+      </c>
+      <c r="F42" s="36" t="s">
+        <v>255</v>
+      </c>
+      <c r="G42" s="37" t="s">
+        <v>256</v>
+      </c>
+      <c r="H42" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="I42" s="35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="43" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A43" s="51"/>
+      <c r="B43" s="51"/>
+      <c r="C43" s="35">
+        <v>14.11</v>
+      </c>
+      <c r="D43" s="36" t="s">
+        <v>124</v>
+      </c>
+      <c r="E43" s="36" t="s">
+        <v>218</v>
+      </c>
+      <c r="F43" s="36" t="s">
+        <v>277</v>
+      </c>
+      <c r="G43" s="37" t="s">
+        <v>257</v>
+      </c>
+      <c r="H43" s="35" t="s">
+        <v>79</v>
+      </c>
+      <c r="I43" s="35" t="s">
+        <v>78</v>
+      </c>
+    </row>
+    <row r="44" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A44" s="55">
         <v>15</v>
       </c>
-      <c r="B41" s="63" t="s">
+      <c r="B44" s="55" t="s">
         <v>80</v>
       </c>
-      <c r="C41" s="38">
+      <c r="C44" s="38">
         <v>15.1</v>
-      </c>
-      <c r="D41" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="E41" s="38" t="s">
-        <v>82</v>
-      </c>
-      <c r="F41" s="38" t="s">
-        <v>83</v>
-      </c>
-      <c r="G41" s="39" t="s">
-        <v>157</v>
-      </c>
-      <c r="H41" s="38" t="s">
-        <v>115</v>
-      </c>
-      <c r="I41" s="38" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="42" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A42" s="57"/>
-      <c r="B42" s="57"/>
-      <c r="C42" s="38">
-        <v>15.2</v>
-      </c>
-      <c r="D42" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="E42" s="38" t="s">
-        <v>84</v>
-      </c>
-      <c r="F42" s="38" t="s">
-        <v>85</v>
-      </c>
-      <c r="G42" s="39" t="s">
-        <v>158</v>
-      </c>
-      <c r="H42" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="I42" s="38" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="43" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A43" s="57"/>
-      <c r="B43" s="57"/>
-      <c r="C43" s="38">
-        <v>15.3</v>
-      </c>
-      <c r="D43" s="38" t="s">
-        <v>81</v>
-      </c>
-      <c r="E43" s="38" t="s">
-        <v>86</v>
-      </c>
-      <c r="F43" s="38" t="s">
-        <v>87</v>
-      </c>
-      <c r="G43" s="39" t="s">
-        <v>159</v>
-      </c>
-      <c r="H43" s="38" t="s">
-        <v>99</v>
-      </c>
-      <c r="I43" s="38" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="44" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A44" s="57"/>
-      <c r="B44" s="57"/>
-      <c r="C44" s="38">
-        <v>15.4</v>
       </c>
       <c r="D44" s="38" t="s">
         <v>81</v>
       </c>
       <c r="E44" s="38" t="s">
-        <v>278</v>
+        <v>82</v>
       </c>
       <c r="F44" s="38" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="G44" s="39" t="s">
-        <v>258</v>
+        <v>157</v>
       </c>
       <c r="H44" s="38" t="s">
-        <v>99</v>
+        <v>115</v>
       </c>
       <c r="I44" s="38" t="s">
         <v>100</v>
       </c>
     </row>
     <row r="45" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A45" s="57"/>
-      <c r="B45" s="57"/>
+      <c r="A45" s="56"/>
+      <c r="B45" s="56"/>
       <c r="C45" s="38">
-        <v>15.5</v>
+        <v>15.2</v>
       </c>
       <c r="D45" s="38" t="s">
         <v>81</v>
       </c>
       <c r="E45" s="38" t="s">
-        <v>89</v>
+        <v>84</v>
       </c>
       <c r="F45" s="38" t="s">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G45" s="39" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="H45" s="38" t="s">
         <v>99</v>
@@ -6520,22 +7091,22 @@
       </c>
     </row>
     <row r="46" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A46" s="57"/>
-      <c r="B46" s="57"/>
+      <c r="A46" s="56"/>
+      <c r="B46" s="56"/>
       <c r="C46" s="38">
-        <v>15.6</v>
+        <v>15.3</v>
       </c>
       <c r="D46" s="38" t="s">
         <v>81</v>
       </c>
       <c r="E46" s="38" t="s">
-        <v>91</v>
+        <v>86</v>
       </c>
       <c r="F46" s="38" t="s">
-        <v>259</v>
+        <v>87</v>
       </c>
       <c r="G46" s="39" t="s">
-        <v>279</v>
+        <v>159</v>
       </c>
       <c r="H46" s="38" t="s">
         <v>99</v>
@@ -6545,22 +7116,22 @@
       </c>
     </row>
     <row r="47" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A47" s="57"/>
-      <c r="B47" s="57"/>
+      <c r="A47" s="56"/>
+      <c r="B47" s="56"/>
       <c r="C47" s="38">
-        <v>15.7</v>
+        <v>15.4</v>
       </c>
       <c r="D47" s="38" t="s">
         <v>81</v>
       </c>
       <c r="E47" s="38" t="s">
-        <v>92</v>
+        <v>278</v>
       </c>
       <c r="F47" s="38" t="s">
-        <v>260</v>
+        <v>88</v>
       </c>
       <c r="G47" s="39" t="s">
-        <v>280</v>
+        <v>258</v>
       </c>
       <c r="H47" s="38" t="s">
         <v>99</v>
@@ -6570,22 +7141,22 @@
       </c>
     </row>
     <row r="48" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A48" s="57"/>
-      <c r="B48" s="57"/>
+      <c r="A48" s="56"/>
+      <c r="B48" s="56"/>
       <c r="C48" s="38">
-        <v>15.8</v>
+        <v>15.5</v>
       </c>
       <c r="D48" s="38" t="s">
         <v>81</v>
       </c>
       <c r="E48" s="38" t="s">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="F48" s="38" t="s">
-        <v>94</v>
+        <v>90</v>
       </c>
       <c r="G48" s="39" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="H48" s="38" t="s">
         <v>99</v>
@@ -6594,102 +7165,102 @@
         <v>100</v>
       </c>
     </row>
-    <row r="49" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A49" s="70">
+    <row r="49" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A49" s="56"/>
+      <c r="B49" s="56"/>
+      <c r="C49" s="38">
+        <v>15.6</v>
+      </c>
+      <c r="D49" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="E49" s="38" t="s">
+        <v>91</v>
+      </c>
+      <c r="F49" s="38" t="s">
+        <v>259</v>
+      </c>
+      <c r="G49" s="39" t="s">
+        <v>279</v>
+      </c>
+      <c r="H49" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="I49" s="38" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="50" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A50" s="56"/>
+      <c r="B50" s="56"/>
+      <c r="C50" s="38">
+        <v>15.7</v>
+      </c>
+      <c r="D50" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="E50" s="38" t="s">
+        <v>92</v>
+      </c>
+      <c r="F50" s="38" t="s">
+        <v>260</v>
+      </c>
+      <c r="G50" s="39" t="s">
+        <v>280</v>
+      </c>
+      <c r="H50" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="I50" s="38" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="51" spans="1:9" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A51" s="56"/>
+      <c r="B51" s="56"/>
+      <c r="C51" s="38">
+        <v>15.8</v>
+      </c>
+      <c r="D51" s="38" t="s">
+        <v>81</v>
+      </c>
+      <c r="E51" s="38" t="s">
+        <v>93</v>
+      </c>
+      <c r="F51" s="38" t="s">
+        <v>94</v>
+      </c>
+      <c r="G51" s="39" t="s">
+        <v>161</v>
+      </c>
+      <c r="H51" s="38" t="s">
+        <v>99</v>
+      </c>
+      <c r="I51" s="38" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="52" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A52" s="63">
         <v>16</v>
       </c>
-      <c r="B49" s="70" t="s">
+      <c r="B52" s="63" t="s">
         <v>95</v>
       </c>
-      <c r="C49" s="40">
+      <c r="C52" s="40">
         <v>16.100000000000001</v>
-      </c>
-      <c r="D49" s="41" t="s">
-        <v>96</v>
-      </c>
-      <c r="E49" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="F49" s="41" t="s">
-        <v>98</v>
-      </c>
-      <c r="G49" s="42" t="s">
-        <v>162</v>
-      </c>
-      <c r="H49" s="41" t="s">
-        <v>99</v>
-      </c>
-      <c r="I49" s="41" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="50" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A50" s="70"/>
-      <c r="B50" s="70"/>
-      <c r="C50" s="40">
-        <v>16.2</v>
-      </c>
-      <c r="D50" s="41" t="s">
-        <v>96</v>
-      </c>
-      <c r="E50" s="41" t="s">
-        <v>101</v>
-      </c>
-      <c r="F50" s="41" t="s">
-        <v>102</v>
-      </c>
-      <c r="G50" s="42" t="s">
-        <v>163</v>
-      </c>
-      <c r="H50" s="41" t="s">
-        <v>99</v>
-      </c>
-      <c r="I50" s="41" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="51" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A51" s="70"/>
-      <c r="B51" s="70"/>
-      <c r="C51" s="40">
-        <v>16.3</v>
-      </c>
-      <c r="D51" s="41" t="s">
-        <v>96</v>
-      </c>
-      <c r="E51" s="41" t="s">
-        <v>103</v>
-      </c>
-      <c r="F51" s="41" t="s">
-        <v>104</v>
-      </c>
-      <c r="G51" s="42" t="s">
-        <v>164</v>
-      </c>
-      <c r="H51" s="41" t="s">
-        <v>99</v>
-      </c>
-      <c r="I51" s="41" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="52" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A52" s="70"/>
-      <c r="B52" s="70"/>
-      <c r="C52" s="40">
-        <v>16.399999999999999</v>
       </c>
       <c r="D52" s="41" t="s">
         <v>96</v>
       </c>
       <c r="E52" s="41" t="s">
-        <v>105</v>
+        <v>97</v>
       </c>
       <c r="F52" s="41" t="s">
-        <v>106</v>
+        <v>98</v>
       </c>
       <c r="G52" s="42" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="H52" s="41" t="s">
         <v>99</v>
@@ -6699,22 +7270,22 @@
       </c>
     </row>
     <row r="53" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A53" s="70"/>
-      <c r="B53" s="70"/>
+      <c r="A53" s="63"/>
+      <c r="B53" s="63"/>
       <c r="C53" s="40">
-        <v>16.5</v>
+        <v>16.2</v>
       </c>
       <c r="D53" s="41" t="s">
         <v>96</v>
       </c>
       <c r="E53" s="41" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
       <c r="F53" s="41" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
       <c r="G53" s="42" t="s">
-        <v>166</v>
+        <v>163</v>
       </c>
       <c r="H53" s="41" t="s">
         <v>99</v>
@@ -6724,22 +7295,22 @@
       </c>
     </row>
     <row r="54" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A54" s="57"/>
-      <c r="B54" s="57"/>
+      <c r="A54" s="63"/>
+      <c r="B54" s="63"/>
       <c r="C54" s="40">
-        <v>16.600000000000001</v>
+        <v>16.3</v>
       </c>
       <c r="D54" s="41" t="s">
         <v>96</v>
       </c>
       <c r="E54" s="41" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
       <c r="F54" s="41" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
       <c r="G54" s="42" t="s">
-        <v>167</v>
+        <v>164</v>
       </c>
       <c r="H54" s="41" t="s">
         <v>99</v>
@@ -6749,101 +7320,101 @@
       </c>
     </row>
     <row r="55" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A55" s="71">
+      <c r="A55" s="63"/>
+      <c r="B55" s="63"/>
+      <c r="C55" s="40">
+        <v>16.399999999999999</v>
+      </c>
+      <c r="D55" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="E55" s="41" t="s">
+        <v>105</v>
+      </c>
+      <c r="F55" s="41" t="s">
+        <v>106</v>
+      </c>
+      <c r="G55" s="42" t="s">
+        <v>165</v>
+      </c>
+      <c r="H55" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="I55" s="41" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="56" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A56" s="63"/>
+      <c r="B56" s="63"/>
+      <c r="C56" s="40">
+        <v>16.5</v>
+      </c>
+      <c r="D56" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="E56" s="41" t="s">
+        <v>107</v>
+      </c>
+      <c r="F56" s="41" t="s">
+        <v>108</v>
+      </c>
+      <c r="G56" s="42" t="s">
+        <v>166</v>
+      </c>
+      <c r="H56" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="I56" s="41" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A57" s="56"/>
+      <c r="B57" s="56"/>
+      <c r="C57" s="40">
+        <v>16.600000000000001</v>
+      </c>
+      <c r="D57" s="41" t="s">
+        <v>96</v>
+      </c>
+      <c r="E57" s="41" t="s">
+        <v>109</v>
+      </c>
+      <c r="F57" s="41" t="s">
+        <v>110</v>
+      </c>
+      <c r="G57" s="42" t="s">
+        <v>167</v>
+      </c>
+      <c r="H57" s="41" t="s">
+        <v>99</v>
+      </c>
+      <c r="I57" s="41" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="58" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A58" s="64">
         <v>17</v>
       </c>
-      <c r="B55" s="74" t="s">
+      <c r="B58" s="67" t="s">
         <v>111</v>
       </c>
-      <c r="C55" s="43">
+      <c r="C58" s="43">
         <v>17.100000000000001</v>
-      </c>
-      <c r="D55" s="43" t="s">
-        <v>112</v>
-      </c>
-      <c r="E55" s="43" t="s">
-        <v>113</v>
-      </c>
-      <c r="F55" s="43" t="s">
-        <v>114</v>
-      </c>
-      <c r="G55" s="44" t="s">
-        <v>168</v>
-      </c>
-      <c r="H55" s="43" t="s">
-        <v>115</v>
-      </c>
-      <c r="I55" s="43" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="56" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A56" s="72"/>
-      <c r="B56" s="74"/>
-      <c r="C56" s="43">
-        <v>17.2</v>
-      </c>
-      <c r="D56" s="43" t="s">
-        <v>112</v>
-      </c>
-      <c r="E56" s="43" t="s">
-        <v>116</v>
-      </c>
-      <c r="F56" s="43" t="s">
-        <v>117</v>
-      </c>
-      <c r="G56" s="44" t="s">
-        <v>169</v>
-      </c>
-      <c r="H56" s="43" t="s">
-        <v>115</v>
-      </c>
-      <c r="I56" s="43" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="57" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A57" s="72"/>
-      <c r="B57" s="74"/>
-      <c r="C57" s="43">
-        <v>17.3</v>
-      </c>
-      <c r="D57" s="43" t="s">
-        <v>112</v>
-      </c>
-      <c r="E57" s="43" t="s">
-        <v>118</v>
-      </c>
-      <c r="F57" s="43" t="s">
-        <v>119</v>
-      </c>
-      <c r="G57" s="44" t="s">
-        <v>170</v>
-      </c>
-      <c r="H57" s="43" t="s">
-        <v>99</v>
-      </c>
-      <c r="I57" s="43" t="s">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="58" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A58" s="72"/>
-      <c r="B58" s="74"/>
-      <c r="C58" s="43">
-        <v>17.399999999999999</v>
       </c>
       <c r="D58" s="43" t="s">
         <v>112</v>
       </c>
       <c r="E58" s="43" t="s">
-        <v>120</v>
+        <v>113</v>
       </c>
       <c r="F58" s="43" t="s">
-        <v>121</v>
+        <v>114</v>
       </c>
       <c r="G58" s="44" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="H58" s="43" t="s">
         <v>115</v>
@@ -6853,22 +7424,22 @@
       </c>
     </row>
     <row r="59" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A59" s="73"/>
-      <c r="B59" s="74"/>
+      <c r="A59" s="65"/>
+      <c r="B59" s="67"/>
       <c r="C59" s="43">
-        <v>17.5</v>
+        <v>17.2</v>
       </c>
       <c r="D59" s="43" t="s">
         <v>112</v>
       </c>
       <c r="E59" s="43" t="s">
-        <v>122</v>
+        <v>116</v>
       </c>
       <c r="F59" s="43" t="s">
-        <v>123</v>
+        <v>117</v>
       </c>
       <c r="G59" s="44" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="H59" s="43" t="s">
         <v>115</v>
@@ -6877,102 +7448,102 @@
         <v>100</v>
       </c>
     </row>
-    <row r="60" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A60" s="75">
+    <row r="60" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A60" s="65"/>
+      <c r="B60" s="67"/>
+      <c r="C60" s="43">
+        <v>17.3</v>
+      </c>
+      <c r="D60" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="E60" s="43" t="s">
+        <v>118</v>
+      </c>
+      <c r="F60" s="43" t="s">
+        <v>119</v>
+      </c>
+      <c r="G60" s="44" t="s">
+        <v>170</v>
+      </c>
+      <c r="H60" s="43" t="s">
+        <v>99</v>
+      </c>
+      <c r="I60" s="43" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="61" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A61" s="65"/>
+      <c r="B61" s="67"/>
+      <c r="C61" s="43">
+        <v>17.399999999999999</v>
+      </c>
+      <c r="D61" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="E61" s="43" t="s">
+        <v>120</v>
+      </c>
+      <c r="F61" s="43" t="s">
+        <v>121</v>
+      </c>
+      <c r="G61" s="44" t="s">
+        <v>171</v>
+      </c>
+      <c r="H61" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="I61" s="43" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="62" spans="1:9" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A62" s="66"/>
+      <c r="B62" s="67"/>
+      <c r="C62" s="43">
+        <v>17.5</v>
+      </c>
+      <c r="D62" s="43" t="s">
+        <v>112</v>
+      </c>
+      <c r="E62" s="43" t="s">
+        <v>122</v>
+      </c>
+      <c r="F62" s="43" t="s">
+        <v>123</v>
+      </c>
+      <c r="G62" s="44" t="s">
+        <v>172</v>
+      </c>
+      <c r="H62" s="43" t="s">
+        <v>115</v>
+      </c>
+      <c r="I62" s="43" t="s">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="63" spans="1:9" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A63" s="68">
         <v>18</v>
       </c>
-      <c r="B60" s="75" t="s">
-        <v>289</v>
-      </c>
-      <c r="C60" s="18">
+      <c r="B63" s="76" t="s">
+        <v>286</v>
+      </c>
+      <c r="C63" s="18">
         <v>18.100000000000001</v>
-      </c>
-      <c r="D60" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="E60" s="18" t="s">
-        <v>290</v>
-      </c>
-      <c r="F60" s="18" t="s">
-        <v>291</v>
-      </c>
-      <c r="G60" s="19" t="s">
-        <v>293</v>
-      </c>
-      <c r="H60" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="I60" s="18" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="61" spans="1:9" s="6" customFormat="1" ht="199.2" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A61" s="57"/>
-      <c r="B61" s="57"/>
-      <c r="C61" s="18">
-        <v>18.2</v>
-      </c>
-      <c r="D61" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="E61" s="18" t="s">
-        <v>292</v>
-      </c>
-      <c r="F61" s="18" t="s">
-        <v>294</v>
-      </c>
-      <c r="G61" s="19" t="s">
-        <v>299</v>
-      </c>
-      <c r="H61" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="I61" s="18" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="62" spans="1:9" s="6" customFormat="1" ht="167.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A62" s="57"/>
-      <c r="B62" s="57"/>
-      <c r="C62" s="18">
-        <v>18.3</v>
-      </c>
-      <c r="D62" s="18" t="s">
-        <v>124</v>
-      </c>
-      <c r="E62" s="18" t="s">
-        <v>297</v>
-      </c>
-      <c r="F62" s="18" t="s">
-        <v>295</v>
-      </c>
-      <c r="G62" s="19" t="s">
-        <v>296</v>
-      </c>
-      <c r="H62" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="I62" s="18" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="63" spans="1:9" s="6" customFormat="1" ht="230.4" x14ac:dyDescent="0.3">
-      <c r="A63" s="57"/>
-      <c r="B63" s="57"/>
-      <c r="C63" s="18">
-        <v>18.399999999999999</v>
       </c>
       <c r="D63" s="18" t="s">
         <v>124</v>
       </c>
       <c r="E63" s="18" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="F63" s="18" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="G63" s="19" t="s">
-        <v>300</v>
+        <v>290</v>
       </c>
       <c r="H63" s="18" t="s">
         <v>77</v>
@@ -6981,213 +7552,224 @@
         <v>125</v>
       </c>
     </row>
-    <row r="64" spans="1:9" s="6" customFormat="1" ht="216" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A64" s="49"/>
-      <c r="B64" s="49"/>
-      <c r="C64" s="18"/>
+    <row r="64" spans="1:9" s="6" customFormat="1" ht="250.8" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A64" s="56"/>
+      <c r="B64" s="77"/>
+      <c r="C64" s="18">
+        <v>18.2</v>
+      </c>
       <c r="D64" s="18" t="s">
         <v>124</v>
       </c>
       <c r="E64" s="18" t="s">
-        <v>301</v>
+        <v>289</v>
       </c>
       <c r="F64" s="18" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="G64" s="19" t="s">
-        <v>303</v>
-      </c>
-      <c r="H64" s="18"/>
-      <c r="I64" s="18"/>
-    </row>
-    <row r="65" spans="1:12" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
-      <c r="A65" s="64">
+        <v>310</v>
+      </c>
+      <c r="H64" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="I64" s="18" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="65" spans="1:12" s="6" customFormat="1" ht="167.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A65" s="56"/>
+      <c r="B65" s="77"/>
+      <c r="C65" s="18">
+        <v>18.3</v>
+      </c>
+      <c r="D65" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="E65" s="18" t="s">
+        <v>294</v>
+      </c>
+      <c r="F65" s="18" t="s">
+        <v>292</v>
+      </c>
+      <c r="G65" s="19" t="s">
+        <v>293</v>
+      </c>
+      <c r="H65" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="I65" s="18" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="66" spans="1:12" s="6" customFormat="1" ht="244.8" x14ac:dyDescent="0.3">
+      <c r="A66" s="56"/>
+      <c r="B66" s="77"/>
+      <c r="C66" s="18">
+        <v>18.399999999999999</v>
+      </c>
+      <c r="D66" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="E66" s="18" t="s">
+        <v>297</v>
+      </c>
+      <c r="F66" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="G66" s="19" t="s">
+        <v>311</v>
+      </c>
+      <c r="H66" s="18" t="s">
+        <v>77</v>
+      </c>
+      <c r="I66" s="18" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="67" spans="1:12" s="6" customFormat="1" ht="216" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A67" s="49"/>
+      <c r="B67" s="78"/>
+      <c r="C67" s="18">
+        <v>18.5</v>
+      </c>
+      <c r="D67" s="18" t="s">
+        <v>124</v>
+      </c>
+      <c r="E67" s="18" t="s">
+        <v>295</v>
+      </c>
+      <c r="F67" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="G67" s="19" t="s">
+        <v>312</v>
+      </c>
+      <c r="H67" s="18"/>
+      <c r="I67" s="18"/>
+    </row>
+    <row r="68" spans="1:12" s="6" customFormat="1" ht="86.4" x14ac:dyDescent="0.3">
+      <c r="A68" s="57">
         <v>19</v>
       </c>
-      <c r="B65" s="67" t="s">
+      <c r="B68" s="60" t="s">
         <v>126</v>
       </c>
-      <c r="C65" s="45">
+      <c r="C68" s="45">
         <v>19.100000000000001</v>
       </c>
-      <c r="D65" s="46" t="s">
+      <c r="D68" s="46" t="s">
         <v>127</v>
       </c>
-      <c r="E65" s="46" t="s">
+      <c r="E68" s="46" t="s">
         <v>231</v>
       </c>
-      <c r="F65" s="46" t="s">
+      <c r="F68" s="46" t="s">
         <v>230</v>
       </c>
-      <c r="G65" s="47" t="s">
+      <c r="G68" s="47" t="s">
         <v>232</v>
-      </c>
-      <c r="H65" s="45"/>
-      <c r="I65" s="48"/>
-    </row>
-    <row r="66" spans="1:12" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A66" s="65"/>
-      <c r="B66" s="68"/>
-      <c r="C66" s="15">
-        <v>19.2</v>
-      </c>
-      <c r="D66" s="46" t="s">
-        <v>128</v>
-      </c>
-      <c r="E66" s="46" t="s">
-        <v>129</v>
-      </c>
-      <c r="F66" s="46" t="s">
-        <v>226</v>
-      </c>
-      <c r="G66" s="47" t="s">
-        <v>130</v>
-      </c>
-      <c r="H66" s="45"/>
-      <c r="I66" s="48"/>
-    </row>
-    <row r="67" spans="1:12" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
-      <c r="A67" s="66"/>
-      <c r="B67" s="69"/>
-      <c r="C67" s="34">
-        <v>19.3</v>
-      </c>
-      <c r="D67" s="16" t="s">
-        <v>127</v>
-      </c>
-      <c r="E67" s="16" t="s">
-        <v>131</v>
-      </c>
-      <c r="F67" s="16" t="s">
-        <v>132</v>
-      </c>
-      <c r="G67" s="17"/>
-      <c r="H67" s="33"/>
-      <c r="I67" s="34"/>
-    </row>
-    <row r="68" spans="1:12" s="6" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
-      <c r="A68" s="64">
-        <v>20</v>
-      </c>
-      <c r="B68" s="67" t="s">
-        <v>133</v>
-      </c>
-      <c r="C68" s="45">
-        <v>20.100000000000001</v>
-      </c>
-      <c r="D68" s="46" t="s">
-        <v>134</v>
-      </c>
-      <c r="E68" s="46" t="s">
-        <v>243</v>
-      </c>
-      <c r="F68" s="46" t="s">
-        <v>244</v>
-      </c>
-      <c r="G68" s="47" t="s">
-        <v>245</v>
       </c>
       <c r="H68" s="45"/>
       <c r="I68" s="48"/>
     </row>
-    <row r="69" spans="1:12" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
-      <c r="A69" s="65"/>
-      <c r="B69" s="68"/>
+    <row r="69" spans="1:12" s="6" customFormat="1" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A69" s="58"/>
+      <c r="B69" s="61"/>
       <c r="C69" s="15">
-        <v>20.2</v>
+        <v>19.2</v>
       </c>
       <c r="D69" s="46" t="s">
-        <v>135</v>
+        <v>128</v>
       </c>
       <c r="E69" s="46" t="s">
-        <v>233</v>
+        <v>129</v>
       </c>
       <c r="F69" s="46" t="s">
         <v>226</v>
       </c>
       <c r="G69" s="47" t="s">
-        <v>234</v>
+        <v>130</v>
       </c>
       <c r="H69" s="45"/>
       <c r="I69" s="48"/>
-      <c r="J69" s="1"/>
-      <c r="K69" s="1"/>
-      <c r="L69" s="1"/>
-    </row>
-    <row r="70" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A70" s="66"/>
-      <c r="B70" s="69"/>
-      <c r="C70" s="33">
-        <v>20.3</v>
+    </row>
+    <row r="70" spans="1:12" s="6" customFormat="1" ht="57.6" x14ac:dyDescent="0.3">
+      <c r="A70" s="59"/>
+      <c r="B70" s="62"/>
+      <c r="C70" s="34">
+        <v>19.3</v>
       </c>
       <c r="D70" s="16" t="s">
-        <v>134</v>
+        <v>127</v>
       </c>
       <c r="E70" s="16" t="s">
         <v>131</v>
       </c>
-      <c r="F70" s="16"/>
+      <c r="F70" s="16" t="s">
+        <v>132</v>
+      </c>
       <c r="G70" s="17"/>
       <c r="H70" s="33"/>
       <c r="I70" s="34"/>
-      <c r="J70" s="1"/>
-      <c r="K70" s="1"/>
-      <c r="L70" s="1"/>
-    </row>
-    <row r="71" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
-      <c r="A71" s="64">
-        <v>21</v>
-      </c>
-      <c r="B71" s="67" t="s">
-        <v>136</v>
+    </row>
+    <row r="71" spans="1:12" s="6" customFormat="1" ht="201.6" x14ac:dyDescent="0.3">
+      <c r="A71" s="57">
+        <v>20</v>
+      </c>
+      <c r="B71" s="60" t="s">
+        <v>133</v>
       </c>
       <c r="C71" s="45">
-        <v>21.1</v>
+        <v>20.100000000000001</v>
       </c>
       <c r="D71" s="46" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E71" s="46" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="F71" s="46" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="G71" s="47" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="H71" s="45"/>
       <c r="I71" s="48"/>
     </row>
-    <row r="72" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
-      <c r="A72" s="65"/>
-      <c r="B72" s="68"/>
+    <row r="72" spans="1:12" s="6" customFormat="1" ht="158.4" x14ac:dyDescent="0.3">
+      <c r="A72" s="58"/>
+      <c r="B72" s="61"/>
       <c r="C72" s="15">
-        <v>21.2</v>
+        <v>20.2</v>
       </c>
       <c r="D72" s="46" t="s">
-        <v>138</v>
+        <v>135</v>
       </c>
       <c r="E72" s="46" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="F72" s="46" t="s">
         <v>226</v>
       </c>
       <c r="G72" s="47" t="s">
-        <v>139</v>
+        <v>234</v>
       </c>
       <c r="H72" s="45"/>
       <c r="I72" s="48"/>
-    </row>
-    <row r="73" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A73" s="66"/>
-      <c r="B73" s="69"/>
+      <c r="J72" s="1"/>
+      <c r="K72" s="1"/>
+      <c r="L72" s="1"/>
+    </row>
+    <row r="73" spans="1:12" s="6" customFormat="1" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A73" s="59"/>
+      <c r="B73" s="62"/>
       <c r="C73" s="33">
-        <v>21.3</v>
+        <v>20.3</v>
       </c>
       <c r="D73" s="16" t="s">
-        <v>137</v>
+        <v>134</v>
       </c>
       <c r="E73" s="16" t="s">
         <v>131</v>
@@ -7196,63 +7778,66 @@
       <c r="G73" s="17"/>
       <c r="H73" s="33"/>
       <c r="I73" s="34"/>
-    </row>
-    <row r="74" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A74" s="64">
-        <v>22</v>
-      </c>
-      <c r="B74" s="67" t="s">
-        <v>140</v>
+      <c r="J73" s="1"/>
+      <c r="K73" s="1"/>
+      <c r="L73" s="1"/>
+    </row>
+    <row r="74" spans="1:12" ht="187.2" x14ac:dyDescent="0.3">
+      <c r="A74" s="57">
+        <v>21</v>
+      </c>
+      <c r="B74" s="60" t="s">
+        <v>136</v>
       </c>
       <c r="C74" s="45">
-        <v>22.1</v>
+        <v>21.1</v>
       </c>
       <c r="D74" s="46" t="s">
-        <v>141</v>
+        <v>137</v>
       </c>
       <c r="E74" s="46" t="s">
-        <v>240</v>
+        <v>235</v>
       </c>
       <c r="F74" s="46" t="s">
-        <v>241</v>
+        <v>236</v>
       </c>
       <c r="G74" s="47" t="s">
-        <v>242</v>
+        <v>237</v>
       </c>
       <c r="H74" s="45"/>
       <c r="I74" s="48"/>
     </row>
-    <row r="75" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
-      <c r="A75" s="65"/>
-      <c r="B75" s="68"/>
+    <row r="75" spans="1:12" ht="129.6" x14ac:dyDescent="0.3">
+      <c r="A75" s="58"/>
+      <c r="B75" s="61"/>
       <c r="C75" s="15">
-        <v>22.2</v>
+        <v>21.2</v>
       </c>
       <c r="D75" s="46" t="s">
-        <v>224</v>
-      </c>
-      <c r="E75" s="45" t="s">
-        <v>238</v>
+        <v>138</v>
+      </c>
+      <c r="E75" s="46" t="s">
+        <v>225</v>
       </c>
       <c r="F75" s="46" t="s">
         <v>226</v>
       </c>
       <c r="G75" s="47" t="s">
-        <v>239</v>
+        <v>139</v>
       </c>
       <c r="H75" s="45"/>
       <c r="I75" s="48"/>
     </row>
     <row r="76" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
-      <c r="A76" s="66"/>
-      <c r="B76" s="69"/>
+      <c r="A76" s="59"/>
+      <c r="B76" s="62"/>
       <c r="C76" s="33">
-        <v>22.3</v>
+        <v>21.3</v>
       </c>
       <c r="D76" s="16" t="s">
-        <v>141</v>
-      </c>
-      <c r="E76" s="33" t="s">
+        <v>137</v>
+      </c>
+      <c r="E76" s="16" t="s">
         <v>131</v>
       </c>
       <c r="F76" s="16"/>
@@ -7260,65 +7845,103 @@
       <c r="H76" s="33"/>
       <c r="I76" s="34"/>
     </row>
-    <row r="77" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A77" s="3"/>
-      <c r="B77" s="3"/>
-      <c r="C77" s="3"/>
-      <c r="E77" s="11"/>
-      <c r="H77" s="3"/>
-    </row>
-    <row r="78" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D78" s="2"/>
-      <c r="F78" s="2"/>
-      <c r="G78" s="2"/>
-      <c r="I78" s="2"/>
-    </row>
-    <row r="79" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="D79" s="2"/>
-      <c r="F79" s="2"/>
-      <c r="G79" s="2"/>
-      <c r="I79" s="2"/>
+    <row r="77" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A77" s="57">
+        <v>22</v>
+      </c>
+      <c r="B77" s="60" t="s">
+        <v>140</v>
+      </c>
+      <c r="C77" s="45">
+        <v>22.1</v>
+      </c>
+      <c r="D77" s="46" t="s">
+        <v>141</v>
+      </c>
+      <c r="E77" s="46" t="s">
+        <v>240</v>
+      </c>
+      <c r="F77" s="46" t="s">
+        <v>241</v>
+      </c>
+      <c r="G77" s="47" t="s">
+        <v>242</v>
+      </c>
+      <c r="H77" s="45"/>
+      <c r="I77" s="48"/>
+    </row>
+    <row r="78" spans="1:12" ht="259.2" x14ac:dyDescent="0.3">
+      <c r="A78" s="58"/>
+      <c r="B78" s="61"/>
+      <c r="C78" s="15">
+        <v>22.2</v>
+      </c>
+      <c r="D78" s="46" t="s">
+        <v>224</v>
+      </c>
+      <c r="E78" s="45" t="s">
+        <v>238</v>
+      </c>
+      <c r="F78" s="46" t="s">
+        <v>226</v>
+      </c>
+      <c r="G78" s="47" t="s">
+        <v>239</v>
+      </c>
+      <c r="H78" s="45"/>
+      <c r="I78" s="48"/>
+    </row>
+    <row r="79" spans="1:12" ht="43.2" x14ac:dyDescent="0.3">
+      <c r="A79" s="59"/>
+      <c r="B79" s="62"/>
+      <c r="C79" s="33">
+        <v>22.3</v>
+      </c>
+      <c r="D79" s="16" t="s">
+        <v>141</v>
+      </c>
+      <c r="E79" s="33" t="s">
+        <v>131</v>
+      </c>
+      <c r="F79" s="16"/>
+      <c r="G79" s="17"/>
+      <c r="H79" s="33"/>
+      <c r="I79" s="34"/>
     </row>
     <row r="80" spans="1:12" x14ac:dyDescent="0.3">
-      <c r="A80" s="7"/>
-      <c r="B80" s="7"/>
-      <c r="C80" s="7"/>
-      <c r="D80" s="7"/>
-      <c r="E80" s="7"/>
-      <c r="F80" s="7"/>
-      <c r="G80" s="7"/>
-      <c r="H80" s="7"/>
-      <c r="I80" s="7"/>
+      <c r="A80" s="3"/>
+      <c r="B80" s="3"/>
+      <c r="C80" s="3"/>
+      <c r="E80" s="11"/>
+      <c r="H80" s="3"/>
     </row>
     <row r="81" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="A81" s="3"/>
-      <c r="B81" s="3"/>
-      <c r="C81" s="3"/>
-      <c r="D81" s="10"/>
-      <c r="E81" s="10"/>
-      <c r="F81" s="10"/>
-      <c r="G81" s="8"/>
-      <c r="H81" s="10"/>
-      <c r="I81" s="10"/>
+      <c r="D81" s="2"/>
+      <c r="F81" s="2"/>
+      <c r="G81" s="2"/>
+      <c r="I81" s="2"/>
     </row>
     <row r="82" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="D82" s="10"/>
-      <c r="E82" s="10"/>
-      <c r="F82" s="10"/>
-      <c r="G82" s="8"/>
-      <c r="H82" s="10"/>
-      <c r="I82" s="10"/>
+      <c r="D82" s="2"/>
+      <c r="F82" s="2"/>
+      <c r="G82" s="2"/>
+      <c r="I82" s="2"/>
     </row>
     <row r="83" spans="1:9" x14ac:dyDescent="0.3">
-      <c r="B83" s="3"/>
-      <c r="D83" s="10"/>
-      <c r="E83" s="10"/>
-      <c r="F83" s="10"/>
-      <c r="G83" s="8"/>
-      <c r="H83" s="10"/>
-      <c r="I83" s="10"/>
+      <c r="A83" s="7"/>
+      <c r="B83" s="7"/>
+      <c r="C83" s="7"/>
+      <c r="D83" s="7"/>
+      <c r="E83" s="7"/>
+      <c r="F83" s="7"/>
+      <c r="G83" s="7"/>
+      <c r="H83" s="7"/>
+      <c r="I83" s="7"/>
     </row>
     <row r="84" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="A84" s="3"/>
+      <c r="B84" s="3"/>
+      <c r="C84" s="3"/>
       <c r="D84" s="10"/>
       <c r="E84" s="10"/>
       <c r="F84" s="10"/>
@@ -7335,6 +7958,7 @@
       <c r="I85" s="10"/>
     </row>
     <row r="86" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="B86" s="3"/>
       <c r="D86" s="10"/>
       <c r="E86" s="10"/>
       <c r="F86" s="10"/>
@@ -7358,51 +7982,75 @@
       <c r="H88" s="10"/>
       <c r="I88" s="10"/>
     </row>
+    <row r="89" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D89" s="10"/>
+      <c r="E89" s="10"/>
+      <c r="F89" s="10"/>
+      <c r="G89" s="8"/>
+      <c r="H89" s="10"/>
+      <c r="I89" s="10"/>
+    </row>
+    <row r="90" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D90" s="10"/>
+      <c r="E90" s="10"/>
+      <c r="F90" s="10"/>
+      <c r="G90" s="8"/>
+      <c r="H90" s="10"/>
+      <c r="I90" s="10"/>
+    </row>
+    <row r="91" spans="1:9" x14ac:dyDescent="0.3">
+      <c r="D91" s="10"/>
+      <c r="E91" s="10"/>
+      <c r="F91" s="10"/>
+      <c r="G91" s="8"/>
+      <c r="H91" s="10"/>
+      <c r="I91" s="10"/>
+    </row>
   </sheetData>
-  <autoFilter ref="I1:I26" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
+  <autoFilter ref="I1:I29" xr:uid="{00000000-0009-0000-0000-000000000000}"/>
   <mergeCells count="37">
-    <mergeCell ref="A24:A28"/>
-    <mergeCell ref="B24:B28"/>
-    <mergeCell ref="A30:A40"/>
-    <mergeCell ref="B30:B40"/>
-    <mergeCell ref="A21:A23"/>
-    <mergeCell ref="B21:B23"/>
-    <mergeCell ref="A41:A48"/>
-    <mergeCell ref="B41:B48"/>
-    <mergeCell ref="A71:A73"/>
-    <mergeCell ref="B71:B73"/>
-    <mergeCell ref="A74:A76"/>
-    <mergeCell ref="B74:B76"/>
-    <mergeCell ref="A49:A54"/>
-    <mergeCell ref="B49:B54"/>
-    <mergeCell ref="A55:A59"/>
-    <mergeCell ref="B55:B59"/>
-    <mergeCell ref="A60:A63"/>
-    <mergeCell ref="B60:B63"/>
-    <mergeCell ref="A65:A67"/>
-    <mergeCell ref="B65:B67"/>
-    <mergeCell ref="A68:A70"/>
-    <mergeCell ref="B68:B70"/>
-    <mergeCell ref="A13:A16"/>
-    <mergeCell ref="B13:B16"/>
-    <mergeCell ref="A17:A20"/>
+    <mergeCell ref="B63:B67"/>
+    <mergeCell ref="B3:B10"/>
+    <mergeCell ref="A16:A19"/>
+    <mergeCell ref="B16:B19"/>
+    <mergeCell ref="A20:A23"/>
     <mergeCell ref="H1:H2"/>
     <mergeCell ref="I1:I2"/>
-    <mergeCell ref="A8:A12"/>
-    <mergeCell ref="B8:B12"/>
+    <mergeCell ref="A11:A15"/>
+    <mergeCell ref="B11:B15"/>
     <mergeCell ref="A1:A2"/>
     <mergeCell ref="B1:B2"/>
     <mergeCell ref="C1:C2"/>
     <mergeCell ref="D1:F1"/>
     <mergeCell ref="G1:G2"/>
     <mergeCell ref="A3:A7"/>
-    <mergeCell ref="B3:B7"/>
-    <mergeCell ref="B17:B20"/>
+    <mergeCell ref="B20:B23"/>
+    <mergeCell ref="A44:A51"/>
+    <mergeCell ref="B44:B51"/>
+    <mergeCell ref="A74:A76"/>
+    <mergeCell ref="B74:B76"/>
+    <mergeCell ref="A77:A79"/>
+    <mergeCell ref="B77:B79"/>
+    <mergeCell ref="A52:A57"/>
+    <mergeCell ref="B52:B57"/>
+    <mergeCell ref="A58:A62"/>
+    <mergeCell ref="B58:B62"/>
+    <mergeCell ref="A63:A66"/>
+    <mergeCell ref="A68:A70"/>
+    <mergeCell ref="B68:B70"/>
+    <mergeCell ref="A71:A73"/>
+    <mergeCell ref="B71:B73"/>
+    <mergeCell ref="A27:A31"/>
+    <mergeCell ref="B27:B31"/>
+    <mergeCell ref="A33:A43"/>
+    <mergeCell ref="B33:B43"/>
+    <mergeCell ref="A24:A26"/>
+    <mergeCell ref="B24:B26"/>
   </mergeCells>
   <phoneticPr fontId="11" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait"/>
-  <legacyDrawing r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+  <legacyDrawing r:id="rId2"/>
 </worksheet>
 </file>
 
